--- a/check2.xlsx
+++ b/check2.xlsx
@@ -678,7 +678,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1h</t>
+          <t>2h</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -701,7 +701,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1h</t>
+          <t>2h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -872,7 +872,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1h</t>
+          <t>2h</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1052,7 +1052,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -1202,7 +1202,9 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Brought 17 Pro Max with discount for 1,14,000 in Virgin Megastore. Also got cashback of 8% with ENBD share card.</t>
+          <t>The iPhone 17 Pro Max price difference between India and UAE is ₹27,524.
+Take a flight from Mumbai to Dubai, buy an iPhone there, and return to Mumbai on the same day. This will cost you ₹27,550 with travel insurance.
+For just ₹26 more, you get a trip to Dubai. https://t.co/VOhzacVidp</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1221,7 +1223,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2h</t>
+          <t>3h</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1244,7 +1246,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -1256,16 +1258,28 @@
           <t>Brought 17 Pro Max with discount for 1,14,000 in Virgin Megastore. Also got cashback of 8% with ENBD share card.</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>https://x.com/soviergn/status/2036058390850654260</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>The iPhone 17 Pro Max price difference between India and UAE is ₹27,524.
+Take a flight from Mumbai to Dubai, buy an iPhone there, and return to Mumbai on the same day. This will cost you ₹27,550 with travel insurance.
+For just ₹26 more, you get a trip to Dubai. https://t.co/VOhzacVidp</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Brought 17 Pro Max with discount for 1,14,000 in Virgin Megastore. Also got cashback of 8% with ENBD share card.</t>
+          <t>The iPhone 17 Pro Max price difference between India and UAE is ₹27,524.
+Take a flight from Mumbai to Dubai, buy an iPhone there, and return to Mumbai on the same day. This will cost you ₹27,550 with travel insurance.
+For just ₹26 more, you get a trip to Dubai. https://t.co/VOhzacVidp</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Bought 17 Pro Max with a discount for 114,000 at Virgin Megastore. Also received 8% cashback with the ENBD share card.</t>
+          <t>The price difference for the iPhone 17 Pro Max between India and the UAE is ₹27,524. Take a flight from Mumbai to Dubai, buy an iPhone there, and return to Mumbai on the same day. This will cost you ₹27,550 with travel insurance. For just ₹26 more, you get a trip to Dubai.</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1275,7 +1289,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE5" s="2" t="n">
@@ -1298,7 +1312,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Bought 17 Pro Max with a discount for 114,000 at Virgin Megastore. • Also received 8% cashback with the ENBD share card.</t>
+          <t>The price difference for the iPhone 17 Pro Max between India and the UAE is ₹27,524. • Take a flight from Mumbai to Dubai, buy an iPhone there, and return to Mumbai on the same day. • This will cost you ₹27,550 with travel insurance.</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1371,7 +1385,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2h</t>
+          <t>3h</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1395,10 +1409,10 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V6" t="n">
-        <v>327</v>
+        <v>388</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1550,7 +1564,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>4h</t>
+          <t>5h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1573,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1622,8 +1636,8 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Takeoff 🦅  
-And we took off with the falcon ❤️‍🔥👏🏻  
+          <t>Takeoff snippet🦅  
+And we took off with the falcon❤️‍🔥👏🏻  
 #Rotana_Live  
 #Eid_Events  
 #Rabeh_Saqer_in_Riyadh</t>
@@ -1659,7 +1673,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Takeoff 🦅 And we took off with the falcon ❤️‍🔥👏🏻 #Rotana_Live #Eid_Events #Rabeh_Saqer_in_Riyadh</t>
+          <t>Takeoff snippet🦅 And we took off with the falcon❤️‍🔥👏🏻 #Rotana_Live #Eid_Events #Rabeh_Saqer_in_Riyadh</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1734,7 +1748,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>4h</t>
+          <t>5h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1757,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1911,7 +1925,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>4h</t>
+          <t>5h</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1938,7 +1952,7 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -2113,7 +2127,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>4h</t>
+          <t>5h</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -2140,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -2282,7 +2296,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>8h</t>
+          <t>9h</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -2334,7 +2348,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Operation epic bimbo has been closed for a small profit; there were too many significant threats to GCC key infrastructure, and honestly, I thought this would be a wrap.</t>
+          <t>Operation epic bimbo has been closed for a small profit; there were too many significant threats to GCC key infrastructure, and I honestly thought this would be a wrap.</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2367,7 +2381,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Operation epic bimbo has been closed for a small profit; there were too many significant threats to GCC key infrastructure, and honestly, I thought this would be a wrap.</t>
+          <t>Operation epic bimbo has been closed for a small profit; there were too many significant threats to GCC key infrastructure, and I honestly thought this would be a wrap.</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -2440,7 +2454,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>8h</t>
+          <t>9h</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -2463,7 +2477,7 @@
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -2492,7 +2506,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>The text is in Arabic and consists of social media handles and emojis, which do not require translation.</t>
+          <t>The text is in Arabic and consists of social media handles and emojis. There is no translatable content.</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2525,7 +2539,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>The text is in Arabic and consists of social media handles and emojis, which do not require translation.</t>
+          <t>The text is in Arabic and consists of social media handles and emojis. • There is no translatable content.</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2604,7 +2618,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -2631,7 +2645,7 @@
         <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -2673,12 +2687,12 @@
       <c r="AB13" t="inlineStr">
         <is>
           <t>Solve the Ramadan riddle and win 10,000 dirhams.
-From meal distribution to supporting workers and spending time with senior citizens, one program brings all of that under one umbrella.
+From meal distribution to supporting workers and spending time with senior citizens, one program brings all of this together under one umbrella.
 What is the name of this program?
 To participate:
 1. Follow the Emirates NBD account
 2. Tag 3 of your friends
-3. Write your answer in the comments below</t>
+3. Write your answer in the comments below.</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2711,7 +2725,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>From meal distribution to supporting workers and spending time with senior citizens, one program brings all of that under one umbrella. • Solve the Ramadan riddle and win 10,000 dirhams. • Follow the Emirates NBD account 2.</t>
+          <t>From meal distribution to supporting workers and spending time with senior citizens, one program brings all of this together under one umbrella. • Solve the Ramadan riddle and win 10,000 dirhams. • Follow the Emirates NBD account 2.</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2791,7 +2805,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -2818,7 +2832,7 @@
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -2967,7 +2981,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -2994,7 +3008,7 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -3023,7 +3037,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>The text appears to be a social media post or message that includes a percentage and usernames, rather than a coherent sentence in a specific language. Therefore, there is no translation needed as it does not contain translatable content.</t>
+          <t>The text appears to be a social media post or message that includes a percentage and mentions of users. There is no translatable content in terms of language, as it primarily consists of usernames and a numerical value.</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -3056,7 +3070,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>The text appears to be a social media post or message that includes a percentage and usernames, rather than a coherent sentence in a specific language. • Therefore, there is no translation needed as it does not contain translatable content.</t>
+          <t>The text appears to be a social media post or message that includes a percentage and mentions of users. • There is no translatable content in terms of language, as it primarily consists of usernames and a numerical value.</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -3129,7 +3143,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -3156,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -3185,7 +3199,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>The text appears to be a social media post or tweet, likely in English already, with mentions of users and a percentage. Therefore, no translation is needed.</t>
+          <t>The text appears to be a social media post or message that includes a percentage and mentions of users. There is no translatable content in terms of language, as it primarily consists of usernames and a numerical value.</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -3218,7 +3232,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>The text appears to be a social media post or tweet, likely in English already, with mentions of users and a percentage. • Therefore, no translation is needed.</t>
+          <t>The text appears to be a social media post or message that includes a percentage and mentions of users. • There is no translatable content in terms of language, as it primarily consists of usernames and a numerical value.</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -3291,7 +3305,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -3318,7 +3332,7 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
@@ -3347,7 +3361,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>B- 1.89%</t>
+          <t>The text appears to be in English and does not require translation.</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -3380,7 +3394,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>B- 1.89%</t>
+          <t>The text appears to be in English and does not require translation.</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -3453,7 +3467,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -3480,7 +3494,7 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -3509,7 +3523,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>The text appears to be a social media post or message that includes a percentage and mentions of users. There is no translatable content in terms of language, as it primarily consists of usernames and a numerical value.</t>
+          <t>The text appears to be a social media post or message that includes usernames and a percentage. There is no translatable content in a different language.</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -3542,7 +3556,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>The text appears to be a social media post or message that includes a percentage and mentions of users. • There is no translatable content in terms of language, as it primarily consists of usernames and a numerical value.</t>
+          <t>The text appears to be a social media post or message that includes usernames and a percentage. • There is no translatable content in a different language.</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -3615,7 +3629,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -3642,7 +3656,7 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -3671,7 +3685,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Emirates NBD AE Exchanger volunteer program</t>
+          <t>Emirates NBD_AE Exchanger volunteer program</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3704,7 +3718,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Emirates NBD AE Exchanger volunteer program</t>
+          <t>Emirates NBD_AE Exchanger volunteer program</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -3777,7 +3791,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -3804,7 +3818,7 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
@@ -3833,7 +3847,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>The text appears to be in English and does not require translation.</t>
+          <t>The text appears to be a mix of social media handles and a percentage, which does not require translation. The content is already in English.</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3866,7 +3880,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>The text appears to be in English and does not require translation.</t>
+          <t>The text appears to be a mix of social media handles and a percentage, which does not require translation. • The content is already in English.</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3920,7 +3934,7 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @ibushra_03 @Salma2232019</t>
+          <t>Exchanger volunteer program @semeet @ibushra_03 @Salma2232019</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3939,7 +3953,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -3966,7 +3980,7 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
@@ -3978,24 +3992,16 @@
           <t>Exchanger volunteer program @semeet @ibushra_03 @Salma2232019</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956637853421634</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @ibushra_03 @Salma2232019</t>
-        </is>
-      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @ibushra_03 @Salma2232019</t>
+          <t>Exchanger volunteer program @semeet @ibushra_03 @Salma2232019</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>Emirates NBD AE Exchanger volunteer program</t>
+          <t>Exchanger volunteer program</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -4028,7 +4034,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Emirates NBD AE Exchanger volunteer program</t>
+          <t>Exchanger volunteer program</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -4101,7 +4107,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -4128,7 +4134,7 @@
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -4157,7 +4163,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>Emirates NBD_AE Exchanger volunteer program</t>
+          <t>Emirates NBD AE Exchanger volunteer program</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -4190,7 +4196,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Emirates NBD_AE Exchanger volunteer program</t>
+          <t>Emirates NBD AE Exchanger volunteer program</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
@@ -4263,7 +4269,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -4290,7 +4296,7 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -4447,7 +4453,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -4663,7 +4669,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -4690,7 +4696,7 @@
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -4719,7 +4725,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Emirates NBD_AE Exchanger volunteer program</t>
+          <t>Emirates NBD AE Exchanger volunteer program</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -4752,7 +4758,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Emirates NBD_AE Exchanger volunteer program</t>
+          <t>Emirates NBD AE Exchanger volunteer program</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
@@ -4825,7 +4831,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -4852,7 +4858,7 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
@@ -4881,7 +4887,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Emirates NBD AE Exchanger volunteer program</t>
+          <t>Emirates NBD_AE Exchanger volunteer program</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -4914,7 +4920,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Emirates NBD AE Exchanger volunteer program</t>
+          <t>Emirates NBD_AE Exchanger volunteer program</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -4987,7 +4993,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -5149,7 +5155,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -5176,7 +5182,7 @@
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
@@ -5311,7 +5317,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -5338,7 +5344,7 @@
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
@@ -5473,7 +5479,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -5500,7 +5506,7 @@
         <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
@@ -5643,7 +5649,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -5670,7 +5676,7 @@
         <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
@@ -5820,7 +5826,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -5847,7 +5853,7 @@
         <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="W32" t="inlineStr">
         <is>
@@ -5982,7 +5988,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -6144,7 +6150,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -6171,7 +6177,7 @@
         <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
@@ -6306,7 +6312,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -6333,7 +6339,7 @@
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
@@ -6469,7 +6475,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -6496,7 +6502,7 @@
         <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
@@ -6634,7 +6640,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -6657,7 +6663,7 @@
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
@@ -6793,7 +6799,7 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -6820,7 +6826,7 @@
         <v>2</v>
       </c>
       <c r="V38" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
@@ -6850,7 +6856,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>Gold prices continued to decline today, Sunday, in Egypt, with the price of 21-carat gold, the most traded, reaching 6900 pounds, while the price of a gold pound in jewelry stores was 55200 pounds, with the gold pound weighing 8 grams.</t>
+          <t>Gold prices continued to decline today, Sunday, in Egypt, with the price of 21-carat gold, the most traded, reaching 6,900 pounds, while the price of a gold pound in jewelry stores was 55,200 pounds, with the gold pound weighing 8 grams.</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -6883,7 +6889,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Gold prices continued to decline today, Sunday, in Egypt, with the price of 21-carat gold, the most traded, reaching 690…</t>
+          <t>Gold prices continued to decline today, Sunday, in Egypt, with the price of 21-carat gold, the most traded, reaching 6,9…</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
@@ -6952,7 +6958,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -6975,7 +6981,7 @@
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
@@ -7106,7 +7112,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -7129,7 +7135,7 @@
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
@@ -7265,7 +7271,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -7288,7 +7294,7 @@
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
@@ -7441,7 +7447,7 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -7465,10 +7471,10 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="V42" t="n">
-        <v>2309</v>
+        <v>2411</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
@@ -7503,7 +7509,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>I can't wait for the day I see you.</t>
+          <t>I can't wait for the moment I see you.</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -7536,7 +7542,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>I can't wait for the day I see you.</t>
+          <t>I can't wait for the moment I see you.</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
@@ -7589,6 +7595,73 @@
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
+        <is>
+          <t>تقارير دولية: مستثمرون اجانب سحبوا من البنوك الاماراتية 800 مليار دولار وغادروا دبي
+#قناة_الدولة_الفضائية
+التردد 12688 V
+تابعونا على رابط البث المباشر :https://t.co/G1SU09Dfbd
+07755556393 إدارة قسم الأخبار
+07855556393 إدارة قسم البرامج وشكاوى المواطنين
+07855556292 إدارة قسم التسويق والإعلانات
+الإشـراف العــام
+ســعد الأوســي</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>تقارير دولية: مستثمرون اجانب سحبوا من البنوك الاماراتية 800 مليار دولار وغادروا دبي
+&lt;a href="/search?f=tweets&amp;amp;q=%23قناة_الدولة_الفضائية"&gt;#قناة_الدولة_الفضائية&lt;/a&gt;
+التردد 12688 V
+تابعونا على رابط البث المباشر :&lt;a href="https://ffs3.gulfsat.com/aldawlatv/index.m3u8"&gt;ffs3.gulfsat.com/aldawlatv/i…&lt;/a&gt;
+07755556393 إدارة قسم الأخبار
+07855556393 إدارة قسم البرامج وشكاوى المواطنين
+07855556292 إدارة قسم التسويق والإعلانات
+الإشـراف العــام
+ســعد الأوســي</t>
+        </is>
+      </c>
+      <c r="K43" t="b">
+        <v>0</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 5:51 PM UTC</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="n">
+        <v>46103.74375</v>
+      </c>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23قناة_الدولة_الفضائية', 'https://ffs3.gulfsat.com/aldawlatv/index.m3u8']</t>
+        </is>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>57</v>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
         <is>
           <t>تقارير دولية: مستثمرون اجانب سحبوا من البنوك الاماراتية 800 مليار دولار وغادروا دبي
 #قناة_الدولة_الفضائية
@@ -7601,12 +7674,17 @@
 ســعد الأوســي</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>https://x.com/AlDawlaTv/status/2035776470040334397</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
         <is>
           <t>تقارير دولية: مستثمرون اجانب سحبوا من البنوك الاماراتية 800 مليار دولار وغادروا دبي
-&lt;a href="/search?f=tweets&amp;amp;q=%23قناة_الدولة_الفضائية"&gt;#قناة_الدولة_الفضائية&lt;/a&gt;
+#قناة_الدولة_الفضائية
 التردد 12688 V
-تابعونا على رابط البث المباشر :&lt;a href="https://ffs3.gulfsat.com/aldawlatv/index.m3u8"&gt;ffs3.gulfsat.com/aldawlatv/i…&lt;/a&gt;
+تابعونا على رابط البث المباشر :https://t.co/G1SU09Dfbd
 07755556393 إدارة قسم الأخبار
 07855556393 إدارة قسم البرامج وشكاوى المواطنين
 07855556292 إدارة قسم التسويق والإعلانات
@@ -7614,53 +7692,12 @@
 ســعد الأوســي</t>
         </is>
       </c>
-      <c r="K43" t="b">
-        <v>0</v>
-      </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>21h</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>Mar 22, 2026 · 5:51 PM UTC</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="n">
-        <v>46103.74375</v>
-      </c>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23قناة_الدولة_الفضائية', 'https://ffs3.gulfsat.com/aldawlatv/index.m3u8']</t>
-        </is>
-      </c>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" t="n">
-        <v>57</v>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X43" t="inlineStr">
+      <c r="AA43" t="inlineStr">
         <is>
           <t>تقارير دولية: مستثمرون اجانب سحبوا من البنوك الاماراتية 800 مليار دولار وغادروا دبي
 #قناة_الدولة_الفضائية
 التردد 12688 V
-تابعونا على رابط البث المباشر :ffs3.gulfsat.com/aldawlatv/i…
+تابعونا على رابط البث المباشر :https://t.co/G1SU09Dfbd
 07755556393 إدارة قسم الأخبار
 07855556393 إدارة قسم البرامج وشكاوى المواطنين
 07855556292 إدارة قسم التسويق والإعلانات
@@ -7668,24 +7705,9 @@
 ســعد الأوســي</t>
         </is>
       </c>
-      <c r="Y43" t="inlineStr"/>
-      <c r="Z43" t="inlineStr"/>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>تقارير دولية: مستثمرون اجانب سحبوا من البنوك الاماراتية 800 مليار دولار وغادروا دبي
-#قناة_الدولة_الفضائية
-التردد 12688 V
-تابعونا على رابط البث المباشر :ffs3.gulfsat.com/aldawlatv/i…
-07755556393 إدارة قسم الأخبار
-07855556393 إدارة قسم البرامج وشكاوى المواطنين
-07855556292 إدارة قسم التسويق والإعلانات
-الإشـراف العــام
-ســعد الأوســي</t>
-        </is>
-      </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>International reports: Foreign investors withdrew 800 billion dollars from UAE banks and left Dubai.</t>
+          <t>International reports: Foreign investors withdrew $800 billion from UAE banks and left Dubai.</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -7718,7 +7740,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>International reports: Foreign investors withdrew 800 billion dollars from UAE banks and left Dubai.</t>
+          <t>International reports: Foreign investors withdrew $800 billion from UAE banks and left Dubai.</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
@@ -7797,7 +7819,7 @@
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -7811,16 +7833,16 @@
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="T44" t="n">
         <v>153</v>
       </c>
       <c r="U44" t="n">
-        <v>1050</v>
+        <v>1054</v>
       </c>
       <c r="V44" t="n">
-        <v>1779930</v>
+        <v>1789959</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
@@ -7963,7 +7985,7 @@
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -7990,7 +8012,7 @@
         <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
@@ -8158,7 +8180,7 @@
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="W46" t="inlineStr">
         <is>
@@ -8208,16 +8230,8 @@
       <c r="AB46" t="inlineStr">
         <is>
           <t>Tickets are now available 🔥  
-https://t.co/zCeyfXHLIV  
 #EidEvents  
-#RotanaLive  
-@Turki_alalshikh  
-@RashedTV  
-@walidfayed  
-@GEA_SA  
-@EidSeason  
-@Mabdoarena  
-@EmiratesNBD_KSA https://t.co/65wAQ54kr8</t>
+#RotanaLive</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -8250,7 +8264,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>Tickets are now available 🔥 https://t.co/zCeyfXHLIV #EidEvents #RotanaLive @Turki_alalshikh @RashedTV @walidfayed @GEA_SA @EidSeason @Mabdoarena @EmiratesNBD_KSA https://t.co/65wAQ54kr8</t>
+          <t>Tickets are now available 🔥 #EidEvents #RotanaLive</t>
         </is>
       </c>
       <c r="AJ46" t="inlineStr">
@@ -8357,7 +8371,7 @@
         <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>3242</v>
+        <v>3245</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
@@ -8544,10 +8558,10 @@
         <v>7</v>
       </c>
       <c r="U48" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="V48" t="n">
-        <v>12761</v>
+        <v>12847</v>
       </c>
       <c r="W48" t="inlineStr">
         <is>
@@ -8607,10 +8621,10 @@
       <c r="AB48" t="inlineStr">
         <is>
           <t>Rabeh Saqer opens the "Eid Events" in Riyadh, announcing "We are shields for your lands, Al Saud" on an unforgettable night supported by the Entertainment Authority and organized by Rotana.
-The audience has always been accustomed to the concerts held by Rotana Music Group being different in terms of artistic and organizational levels, achieving great success and interaction in the massive public event that marked the opening of the Eid al-Fitr celebrations for 2026, held in Riyadh under the slogan "Eid Events and Joy Increases," supported by the General Entertainment Authority, chaired by His Excellency Advisor Turki bin Abdul Mohsen Al Sheikh, and organized and supervised by Rotana Music Group at the "Mohammed Abdu Arena - Emirates NBD." 
-This night was doubly festive as it coincided with the second day of Eid al-Fitr and Mother's Day, thus delighting the large audience, whether filling the theater or watching the live broadcast on Rotana channels, with an exceptional night that combined love in its various forms and meanings, both national and emotional, along with its colors and musical styles, prepared well by "Abu Saqer" and the musical band led by Maestro Hani Farhat. Rabeh conducted intensive rehearsals on nearly 33 songs, selecting thirty works to perform in a program that included these masterpieces: (The Best of Times, I Understand You, Happy Eid, Long Live the Happy Land, You Can, Honestly, What Didn't Cross My Mind, Don't Come Near Me, Everyone Makes Mistakes, Believe Me, The Good News, Children's Love, Let's Be Beautiful, That's It, What Do You Think Tonight, The Elegant Abaya, You Are a King, The Gold is Original, The Night Passed, Don't Ask Anymore, Don't Be Grateful, Ten Things, His Eyes, Reality, Watered, My Weakness is Love, Proud, I Get Upset with You, Oh Land) presented in two segments with a short break in between.
-Mr. Salem Al Hindi, Chairman and CEO of Rotana Music Group, welcomed Rabeh Saqer upon his arrival at the event, and they took commemorative photos in front of the Media Wall before meeting with media and social media representatives. Saqer stated that his message through this concert is to bring happiness to people, adding: "I came to celebrate with you in a concert titled Eid and Joy... and I pray to God to continue blessing our homeland with security and safety under the leadership of my master, the Custodian of the Two Holy Mosques, King Salman bin Abdulaziz, may God protect him, and his trustworthy Crown Prince, His Royal Highness Prince Mohammed bin Salman, may God take care of him," praising the Saudi forces for fulfilling their duties in various sectors. Rabeh revealed that he is preparing to present a collection of new works soon, including national songs and a sports song to support the Saudi football team participating in the 2026 World Cup. Saqer praised Rotana's role in the music and entertainment industry, commending the great performance of its team in organizing this grand event.
-The conclusion of the concert was wonderful and moving, encapsulating its meaning and message with Rabeh Saqer's voice and the audience singing along to his masterpiece "Oh Land" and his phrase "We are shields for your lands, Al Saud..." Rabeh made sure to document the success of the Eid night by taking a selfie video with the audience, wishing, "May God make all your days celebrations."</t>
+The audience is always accustomed to the concerts held by Rotana Music Group being different in terms of artistic and organizational levels, achieving great success and interaction in the massive public event that marked the opening of the Eid al-Fitr celebrations for 2026, held in Riyadh under the slogan "Eid Events and Joy Increases," supported by the General Entertainment Authority, chaired by His Excellency Advisor Turki bin Abdul Mohsen Al Sheikh, and organized and supervised by Rotana Music Group at the "Mohammed Abdu Arena - Emirates NBD." 
+Since this night was a double celebration, coinciding with the second day of Eid al-Fitr and Mother's Day, Saqer entertained the large audience, whether filling the theater or watching the live broadcast on Rotana channels, with an exceptional night that combined love in its various forms and meanings, both national and emotional, along with its colors and musical styles, prepared well by "Abu Saqer" and the musical band led by Maestro Hani Farhat. Rabeh conducted intensive rehearsals on nearly 33 songs, selecting thirty works to perform in a program that included these masterpieces: (The Best of Times, I Understand You, Happy Eid, Long Live the Happy Home, You Can, Honestly, What Didn't Cross My Mind, Don't Come Near Me, Everyone Makes Mistakes, Believe Me, The Good News, Children's Love, Let's Be Beautiful, That's It, What Do You Think Tonight, The Elegant Abaya, You Are a King, The Gold is Original, The Night Passed, Don't Ask Anymore, Don't Be Grateful, Ten Things, His Eyes, Reality, Watered, My Weakness is Love, Arrogant, I Get Upset with You, Oh Home) presented in two segments with a short break in between.
+Mr. Salem Al Hindi, Chairman and CEO of Rotana Music Group, welcomed Rabeh Saqer upon his arrival at the event, and they took commemorative photos in front of the Media Wall before meeting with media and social media representatives. Saqer stated that his message through this concert is to bring happiness to people, adding: "I came to celebrate with you in a concert titled Eid and Joy... and I pray to God to continue blessing our homeland with security and safety under the leadership of my master, the Custodian of the Two Holy Mosques, King Salman bin Abdulaziz, may God protect him, and the trustworthy Crown Prince, His Royal Highness Prince Mohammed bin Salman, may God take care of him," praising the Saudi forces for fulfilling their duties in various sectors. Rabeh revealed that he is preparing to present a collection of new works, including national songs and a sports song to support the Saudi football team participating in the 2026 World Cup. Saqer praised Rotana's role in the music and entertainment industry, commending the great performance of its team in organizing this grand event.
+The conclusion of the concert was wonderful and moving, encapsulating its meaning and message with Rabeh Saqer's voice and the audience singing along to his masterpiece "Oh Home" and his phrase "We are shields for your lands, Al Saud..." Rabeh made sure to document the success of the Eid night by taking a selfie video with the audience, wishing, "May God make all your days celebrations."</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -8643,7 +8657,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Rabeh Saqer opens the "Eid Events" in Riyadh, announcing "We are shields for your lands, Al Saud" on an unforgettable night supported by the Entertainment Authority and organized by Rotana. • Rabeh revealed that he is preparing to present a collection of new works soon, including national songs and a sports song to support the Saudi football team participating in the 2026 World Cup. • Saqer praised Rotana's role in the music and entertainment industry, commending the great performance of its team in organizing this grand event.</t>
+          <t>Rabeh Saqer opens the "Eid Events" in Riyadh, announcing "We are shields for your lands, Al Saud" on an unforgettable night supported by the Entertainment Authority and organized by Rotana. • Rabeh revealed that he is preparing to present a collection of new works, including national songs and a sports song to support the Saudi football team participating in the 2026 World Cup. • Saqer praised Rotana's role in the music and entertainment industry, commending the great performance of its team in organizing this grand event.</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
@@ -8761,7 +8775,7 @@
         <v>41</v>
       </c>
       <c r="V49" t="n">
-        <v>9642</v>
+        <v>9705</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
@@ -8817,7 +8831,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>Falcon's selfie with the audience🦅❤️‍🔥
+          <t>Selfie of the falcon with the audience🦅❤️‍🔥
 #Rotana_Live
 #Eid_Events
 #Rabeh_Saqer_in_Riyadh</t>
@@ -8853,7 +8867,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Falcon's selfie with the audience🦅❤️‍🔥 #Rotana_Live #Eid_Events #Rabeh_Saqer_in_Riyadh</t>
+          <t>Selfie of the falcon with the audience🦅❤️‍🔥 #Rotana_Live #Eid_Events #Rabeh_Saqer_in_Riyadh</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
@@ -8907,7 +8921,18 @@
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>تفاعل الجمهور في حفل رابح صقر مع أغنية "يادار"🔥😍 https://t.co/kpnh3ss5Fo</t>
+          <t>الصقر بعد ختام حفلة الليلة🦅
+انتظروا الألبوم الجديد قريباً على #روتانا 💚😍
+#روتانا_لايف
+#فعاليات_العيد
+#رابح_صقر_في_الرياض 
+@Turki_alalshikh 
+@RabehSaqer 
+@salhendi 
+@GEA_SA 
+@EidSeason 
+@Mabdoarena 
+@EmiratesNBD_KSA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -8964,7 +8989,7 @@
         <v>139</v>
       </c>
       <c r="V50" t="n">
-        <v>27272</v>
+        <v>27713</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
@@ -8987,24 +9012,31 @@
 @EmiratesNBD_KSA</t>
         </is>
       </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>https://x.com/RotanaLive/status/2035516933039079770</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>تفاعل الجمهور في حفل رابح صقر مع أغنية "يادار"🔥😍 https://t.co/kpnh3ss5Fo</t>
-        </is>
-      </c>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>تفاعل الجمهور في حفل رابح صقر مع أغنية "يادار"🔥😍 https://t.co/kpnh3ss5Fo</t>
+          <t>الصقر بعد ختام حفلة الليلة🦅
+انتظروا الألبوم الجديد قريباً على #روتانا 💚😍
+#روتانا_لايف
+#فعاليات_العيد
+#رابح_صقر_في_الرياض 
+@Turki_alalshikh 
+@RabehSaqer 
+@salhendi 
+@GEA_SA 
+@EidSeason 
+@Mabdoarena 
+@EmiratesNBD_KSA</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>The audience interacted at Rabih Saqr's concert with the song "Yadar"🔥😍</t>
+          <t>The falcon after the end of tonight's party🦅
+Stay tuned for the new album coming soon on #Rotana 💚😍
+#Rotana_Live
+#Eid_Events
+#Rabeh_Saqer_in_Riyadh</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -9037,7 +9069,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>The audience interacted at Rabih Saqr's concert with the song "Yadar"🔥😍</t>
+          <t>The falcon after the end of tonight's party🦅 Stay tuned for the new album coming soon on #Rotana 💚😍 #Rotana_Live #Eid_Events #Rabeh_Saqer_in_Riyadh</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
@@ -9135,7 +9167,7 @@
         <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="W51" t="inlineStr">
         <is>
@@ -9306,7 +9338,7 @@
         <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="W52" t="inlineStr">
         <is>
@@ -9486,7 +9518,7 @@
         <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="W53" t="inlineStr">
         <is>
@@ -9614,7 +9646,7 @@
           <t>أجواء رمضان والرياضة وروح الفريق في بطولة بنك الإمارات دبي الوطني الرمضانية 2026 !
 بمشاركة 68 فريقًا و100 لاعب تنافسوا في رياضات متنوعة  في أجواء مليئة بالحماس والروح الرياضية.
 شكرًا لكل المشاركين على مساهمتهم في نجاحها، ومبروك للفائزين!
-رقم التسجيل الضريبي: 319-897-204 https://t.co/iL9aOmlC4j</t>
+رقم التسجيل الضريبي: 319-897-204</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -9655,7 +9687,7 @@
         <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="W54" t="inlineStr">
         <is>
@@ -9670,32 +9702,21 @@
 رقم التسجيل الضريبي: 319-897-204</t>
         </is>
       </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_EGY/status/2035718138285719777</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr">
         <is>
           <t>أجواء رمضان والرياضة وروح الفريق في بطولة بنك الإمارات دبي الوطني الرمضانية 2026 !
 بمشاركة 68 فريقًا و100 لاعب تنافسوا في رياضات متنوعة  في أجواء مليئة بالحماس والروح الرياضية.
 شكرًا لكل المشاركين على مساهمتهم في نجاحها، ومبروك للفائزين!
-رقم التسجيل الضريبي: 319-897-204 https://t.co/iL9aOmlC4j</t>
-        </is>
-      </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>أجواء رمضان والرياضة وروح الفريق في بطولة بنك الإمارات دبي الوطني الرمضانية 2026 !
-بمشاركة 68 فريقًا و100 لاعب تنافسوا في رياضات متنوعة  في أجواء مليئة بالحماس والروح الرياضية.
-شكرًا لكل المشاركين على مساهمتهم في نجاحها، ومبروك للفائزين!
-رقم التسجيل الضريبي: 319-897-204 https://t.co/iL9aOmlC4j</t>
+رقم التسجيل الضريبي: 319-897-204</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
           <t>The atmosphere of Ramadan, sports, and team spirit at the Emirates NBD Ramadan Championship 2026! With the participation of 68 teams and 100 players competing in various sports in an environment filled with enthusiasm and sportsmanship. 
 Thank you to all participants for their contribution to its success, and congratulations to the winners! 
-Tax registration number: 319-897-204 https://t.co/iL9aOmlC4j</t>
+Tax registration number: 319-897-204</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -9728,7 +9749,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Tax registration number: 319-897-204 https://t.co/iL9aOmlC4j • With the participation of 68 teams and 100 players competing in various sports in an environment filled with enthusiasm and sportsmanship. • The atmosphere of Ramadan, sports, and team spirit at the Emirates NBD Ramadan Championship 2026!</t>
+          <t>With the participation of 68 teams and 100 players competing in various sports in an environment filled with enthusiasm and sportsmanship. • Tax registration number: 319-897-204 • The atmosphere of Ramadan, sports, and team spirit at the Emirates NBD Ramadan Championship 2026!</t>
         </is>
       </c>
       <c r="AJ54" t="inlineStr">
@@ -9838,7 +9859,7 @@
         <v>0</v>
       </c>
       <c r="V55" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
@@ -10028,7 +10049,7 @@
         <v>0</v>
       </c>
       <c r="V56" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="W56" t="inlineStr">
         <is>
@@ -10057,7 +10078,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>B- 1.89%</t>
+          <t>The text appears to be a social media post or tweet, likely in English already, with some references to users and a percentage. Therefore, no translation is needed.</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -10090,7 +10111,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>B- 1.89%</t>
+          <t>The text appears to be a social media post or tweet, likely in English already, with some references to users and a percentage. • Therefore, no translation is needed.</t>
         </is>
       </c>
       <c r="AJ56" t="inlineStr">
@@ -10190,7 +10211,7 @@
         <v>0</v>
       </c>
       <c r="V57" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
@@ -10219,7 +10240,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>The text appears to be a social media post or message that includes a percentage and mentions of users. There is no translatable content in terms of language, as it primarily consists of usernames and a numerical value.</t>
+          <t>The text appears to be a social media post or tweet that includes a percentage and mentions of users. There is no translatable content in terms of language, as it primarily consists of usernames and a percentage.</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -10252,7 +10273,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>The text appears to be a social media post or message that includes a percentage and mentions of users. • There is no translatable content in terms of language, as it primarily consists of usernames and a numerical value.</t>
+          <t>The text appears to be a social media post or tweet that includes a percentage and mentions of users. • There is no translatable content in terms of language, as it primarily consists of usernames and a percentage.</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
@@ -10381,7 +10402,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>Emirates NBD AE Exchanger volunteer program Salma2232019 seemet Selma Romola</t>
+          <t>Emirates NBD AE Exchanger volunteer program Salma2232019 semeet Selma Romola</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
@@ -10414,7 +10435,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>Emirates NBD AE Exchanger volunteer program Salma2232019 seemet Selma Romola</t>
+          <t>Emirates NBD AE Exchanger volunteer program Salma2232019 semeet Selma Romola</t>
         </is>
       </c>
       <c r="AJ58" t="inlineStr">
@@ -10514,7 +10535,7 @@
         <v>0</v>
       </c>
       <c r="V59" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="W59" t="inlineStr">
         <is>
@@ -10840,7 +10861,7 @@
         <v>0</v>
       </c>
       <c r="V61" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="W61" t="inlineStr">
         <is>
@@ -10872,7 +10893,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>Emirates NBD FINEELL (Financial Well-being program) with Emirates NBD</t>
+          <t>FINEELL (Financial Well-being program) with Emirates NBD</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
@@ -10905,7 +10926,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Emirates NBD FINEELL (Financial Well-being program) with Emirates NBD</t>
+          <t>FINEELL (Financial Well-being program) with Emirates NBD</t>
         </is>
       </c>
       <c r="AJ61" t="inlineStr">
@@ -11005,7 +11026,7 @@
         <v>0</v>
       </c>
       <c r="V62" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="W62" t="inlineStr">
         <is>
@@ -11336,7 +11357,7 @@
         <v>0</v>
       </c>
       <c r="V64" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W64" t="inlineStr">
         <is>
@@ -11533,7 +11554,7 @@
         <v>0</v>
       </c>
       <c r="V65" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="W65" t="inlineStr">
         <is>
@@ -11587,18 +11608,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>An exceptional night with artist Rashed Al-Majed 🎼❤️ as part of the #Eid_Events
-March 23 🗓️
-Mohammed Abdu Theater By ENBD 📍
-Book now 🎟️
-https://t.co/vwq1i3xiLW
-#Rotana_Live
-@Turki_alalshikh 
-@RashedTV 
-@GEA_SA 
-@EidSeason 
-@Mabdoarena 
-@EmiratesNBD_KSA https://t.co/0tyXkt0dFp</t>
+          <t>An exceptional night with artist Rashed Al-Majed 🎼❤️ as part of the #EidEvents on March 23 🗓️ at Mohammed Abdu Theater By ENBD 📍 Book now 🎟️</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
@@ -11608,7 +11618,7 @@
       </c>
       <c r="AD65" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE65" s="2" t="n">
@@ -11631,7 +11641,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>An exceptional night with artist Rashed Al-Majed 🎼❤️ as part of the #Eid_Events March 23 🗓️ Mohammed Abdu Theater By ENB…</t>
+          <t>An exceptional night with artist Rashed Al-Majed 🎼❤️ as part of the #EidEvents on March 23 🗓️ at Mohammed Abdu Theater By ENBD 📍 Book now 🎟️</t>
         </is>
       </c>
       <c r="AJ65" t="inlineStr">
@@ -11761,7 +11771,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>Emirates NBD Egypt celebrates Mother's Day with its employees through an innovative experience "Video" Details| https://t.co/3UZjf90alc https://t.co/SVygnUYgZW</t>
+          <t>Emirates NBD Egypt celebrates Mother's Day with its employees through an innovative experience "Video" Details | https://t.co/3UZjf90alc https://t.co/SVygnUYgZW</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
@@ -11794,7 +11804,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>Emirates NBD Egypt celebrates Mother's Day with its employees through an innovative experience "Video" Details| https://t.co/3UZjf90alc https://t.co/SVygnUYgZW</t>
+          <t>Emirates NBD Egypt celebrates Mother's Day with its employees through an innovative experience "Video" Details | https://t.co/3UZjf90alc https://t.co/SVygnUYgZW</t>
         </is>
       </c>
       <c r="AJ66" t="inlineStr">
@@ -11906,7 +11916,7 @@
         <v>1</v>
       </c>
       <c r="V67" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="W67" t="inlineStr">
         <is>
@@ -11959,15 +11969,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>I swear by God, Jeddah is a Saudi city. 
-I swear by God, Jeddah is a Saudi city. 
-I swear by God, Jeddah is a Saudi city. 
-I swear by God, Jeddah is a Saudi city. 
-I swear by God, Jeddah is a Saudi city. 
-I swear by God, Jeddah is a Saudi city. 
-I swear by God, Jeddah is a Saudi city. 
-I swear by God, Jeddah is a Saudi city. 
-I swear by God, Jeddah is a Saudi city.</t>
+          <t>I swear by God, Jeddah is a Saudi city.</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
@@ -12000,7 +12002,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>I swear by God, Jeddah is a Saudi city. • I swear by God, Jeddah is a Saudi city. • I swear by God, Jeddah is a Saudi city.</t>
+          <t>I swear by God, Jeddah is a Saudi city.</t>
         </is>
       </c>
       <c r="AJ67" t="inlineStr">
@@ -12135,7 +12137,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>I am the one who announced the Epstein files from the White House 🇺🇸 I voted for that so the truth can be revealed and not be concealed from criminals.</t>
+          <t>I am the one who announced the Epstein files from the White House 🇺🇸 I voted for that so the truth can come out and not be hidden from criminals.</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
@@ -12168,7 +12170,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>I am the one who announced the Epstein files from the White House 🇺🇸 I voted for that so the truth can be revealed and not be concealed from criminals.</t>
+          <t>I am the one who announced the Epstein files from the White House 🇺🇸 I voted for that so the truth can come out and not be hidden from criminals.</t>
         </is>
       </c>
       <c r="AJ68" t="inlineStr">
@@ -12222,7 +12224,7 @@
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
-          <t>@GogoSs398132 @RotanaLive @RotanaMusic @Turki_alalshikh @RashedTV @walidfayed @GEA_SA @EidSeason @Mabdoarena @EmiratesNBD_KSA ملفات ابستين لاشكالك النجسة مثل الذباب ما تروحون الا للاشياء الوصخه</t>
+          <t>@RotanaLive @RotanaMusic @Turki_alalshikh @RashedTV @walidfayed @GEA_SA @EidSeason @Mabdoarena @EmiratesNBD_KSA يكفي يا حثثثثثثثثثاله العرب</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -12264,7 +12266,7 @@
         <v>0</v>
       </c>
       <c r="V69" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W69" t="inlineStr">
         <is>
@@ -12283,17 +12285,17 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>@GogoSs398132 @RotanaLive @RotanaMusic @Turki_alalshikh @RashedTV @walidfayed @GEA_SA @EidSeason @Mabdoarena @EmiratesNBD_KSA ملفات ابستين لاشكالك النجسة مثل الذباب ما تروحون الا للاشياء الوصخه</t>
+          <t>@RotanaLive @RotanaMusic @Turki_alalshikh @RashedTV @walidfayed @GEA_SA @EidSeason @Mabdoarena @EmiratesNBD_KSA يكفي يا حثثثثثثثثثاله العرب</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>@GogoSs398132 @RotanaLive @RotanaMusic @Turki_alalshikh @RashedTV @walidfayed @GEA_SA @EidSeason @Mabdoarena @EmiratesNBD_KSA ملفات ابستين لاشكالك النجسة مثل الذباب ما تروحون الا للاشياء الوصخه</t>
+          <t>@RotanaLive @RotanaMusic @Turki_alalshikh @RashedTV @walidfayed @GEA_SA @EidSeason @Mabdoarena @EmiratesNBD_KSA يكفي يا حثثثثثثثثثاله العرب</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>Files of Epstein for your filthy shapes like flies, you only go for dirty things.</t>
+          <t>Enough, oh the filth of the Arabs.</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
@@ -12326,7 +12328,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Files of Epstein for your filthy shapes like flies, you only go for dirty things.</t>
+          <t>Enough, oh the filth of the Arabs.</t>
         </is>
       </c>
       <c r="AJ69" t="inlineStr">
@@ -12422,7 +12424,7 @@
         <v>0</v>
       </c>
       <c r="V70" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="W70" t="inlineStr">
         <is>
@@ -12538,7 +12540,7 @@
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>@RotanaLive @RotanaMusic @Turki_alalshikh @RashedTV @walidfayed @GEA_SA @EidSeason @Mabdoarena @EmiratesNBD_KSA يكفي يا حثثثثثثثثثاله العرب</t>
+          <t>انت نايم اصحه و شوف ملفات ابستين</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -12592,24 +12594,16 @@
           <t>انت نايم اصحه و شوف ملفات ابستين</t>
         </is>
       </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>https://x.com/GogoSs398132/status/2035648162216427779</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>@RotanaLive @RotanaMusic @Turki_alalshikh @RashedTV @walidfayed @GEA_SA @EidSeason @Mabdoarena @EmiratesNBD_KSA يكفي يا حثثثثثثثثثاله العرب</t>
-        </is>
-      </c>
+      <c r="Y71" t="inlineStr"/>
+      <c r="Z71" t="inlineStr"/>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>@RotanaLive @RotanaMusic @Turki_alalshikh @RashedTV @walidfayed @GEA_SA @EidSeason @Mabdoarena @EmiratesNBD_KSA يكفي يا حثثثثثثثثثاله العرب</t>
+          <t>انت نايم اصحه و شوف ملفات ابستين</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>Enough, oh the trash of the Arabs.</t>
+          <t>You are sleeping, wake up and see the Epstein files.</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
@@ -12642,7 +12636,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>Enough, oh the trash of the Arabs.</t>
+          <t>You are sleeping, wake up and see the Epstein files.</t>
         </is>
       </c>
       <c r="AJ71" t="inlineStr">
@@ -12738,7 +12732,7 @@
         <v>0</v>
       </c>
       <c r="V72" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="W72" t="inlineStr">
         <is>
@@ -13046,7 +13040,7 @@
         <v>0</v>
       </c>
       <c r="V74" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W74" t="inlineStr">
         <is>
@@ -13196,7 +13190,7 @@
         <v>0</v>
       </c>
       <c r="V75" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="W75" t="inlineStr">
         <is>
@@ -13346,7 +13340,7 @@
         <v>0</v>
       </c>
       <c r="V76" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="W76" t="inlineStr">
         <is>
@@ -13496,7 +13490,7 @@
         <v>0</v>
       </c>
       <c r="V77" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="W77" t="inlineStr">
         <is>
@@ -13675,7 +13669,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>I mean the Libyan and Gulf abstainers.</t>
+          <t>I mean the Libyan and Gulf Abstein.</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
@@ -13708,7 +13702,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>I mean the Libyan and Gulf abstainers.</t>
+          <t>I mean the Libyan and Gulf Abstein.</t>
         </is>
       </c>
       <c r="AJ78" t="inlineStr">
@@ -13804,7 +13798,7 @@
         <v>0</v>
       </c>
       <c r="V79" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="W79" t="inlineStr">
         <is>
@@ -13975,7 +13969,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>I mean Abyssinia, Libya, and the Gulf.</t>
+          <t>I mean the Gulf and Libya.</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
@@ -14008,7 +14002,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>I mean Abyssinia, Libya, and the Gulf.</t>
+          <t>I mean the Gulf and Libya.</t>
         </is>
       </c>
       <c r="AJ80" t="inlineStr">
@@ -14264,7 +14258,7 @@
         <v>0</v>
       </c>
       <c r="V82" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="W82" t="inlineStr">
         <is>
@@ -14416,7 +14410,7 @@
         <v>0</v>
       </c>
       <c r="V83" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="W83" t="inlineStr">
         <is>
@@ -14437,7 +14431,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>You mean people, have the courage to specify who you mean, don't throw around general statements like this and say you mean certain individuals.</t>
+          <t>You mean people, have the courage to specify who you mean; don't throw around general statements like this and say you mean certain people.</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
@@ -14470,7 +14464,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>You mean people, have the courage to specify who you mean, don't throw around general statements like this and say you mean certain individuals.</t>
+          <t>You mean people, have the courage to specify who you mean; don't throw around general statements like this and say you mean certain people.</t>
         </is>
       </c>
       <c r="AJ83" t="inlineStr">
@@ -14566,7 +14560,7 @@
         <v>0</v>
       </c>
       <c r="V84" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="W84" t="inlineStr">
         <is>
@@ -14716,7 +14710,7 @@
         <v>0</v>
       </c>
       <c r="V85" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="W85" t="inlineStr">
         <is>
@@ -14866,7 +14860,7 @@
         <v>0</v>
       </c>
       <c r="V86" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="W86" t="inlineStr">
         <is>
@@ -15016,7 +15010,7 @@
         <v>0</v>
       </c>
       <c r="V87" t="n">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="W87" t="inlineStr">
         <is>
@@ -15186,7 +15180,7 @@
         <v>1</v>
       </c>
       <c r="V88" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W88" t="inlineStr">
         <is>
@@ -15376,7 +15370,7 @@
         <v>0</v>
       </c>
       <c r="V89" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="W89" t="inlineStr">
         <is>
@@ -15545,7 +15539,7 @@
         <v>0</v>
       </c>
       <c r="V90" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="W90" t="inlineStr">
         <is>
@@ -15717,7 +15711,7 @@
         <v>1</v>
       </c>
       <c r="V91" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W91" t="inlineStr">
         <is>
@@ -15837,7 +15831,10 @@
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Spot the red flags before it’s too late. Fake jobs ask for fees, transfers or banking information. Always verify, stay alert and protect yourself. #UnitedAgainstFraud https://t.co/d4EBXeNwqZ</t>
+          <t>Don’t click unfamiliar links.
+Especially in SMS, WhatsApp, or DMs. When in doubt, don’t tap.
+Stay safe. Stay vigilant. #UnitedAgainstFraud
+emiratesnbd.com/en/campaigns…</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -15882,7 +15879,7 @@
         <v>5</v>
       </c>
       <c r="V92" t="n">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="W92" t="inlineStr">
         <is>
@@ -15897,24 +15894,19 @@
 emiratesnbd.com/en/campaigns…</t>
         </is>
       </c>
-      <c r="Y92" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2035627541105348902</t>
-        </is>
-      </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>Spot the red flags before it’s too late. Fake jobs ask for fees, transfers or banking information. Always verify, stay alert and protect yourself. #UnitedAgainstFraud https://t.co/d4EBXeNwqZ</t>
-        </is>
-      </c>
+      <c r="Y92" t="inlineStr"/>
+      <c r="Z92" t="inlineStr"/>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>Spot the red flags before it’s too late. Fake jobs ask for fees, transfers or banking information. Always verify, stay alert and protect yourself. #UnitedAgainstFraud https://t.co/d4EBXeNwqZ</t>
+          <t>Don’t click unfamiliar links.
+Especially in SMS, WhatsApp, or DMs. When in doubt, don’t tap.
+Stay safe. Stay vigilant. #UnitedAgainstFraud
+emiratesnbd.com/en/campaigns…</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>Spot the red flags before it’s too late. Fake jobs ask for fees, transfers, or banking information. Always verify, stay alert, and protect yourself. #UnitedAgainstFraud</t>
+          <t>Don’t click unfamiliar links. Especially in SMS, WhatsApp, or DMs. When in doubt, don’t tap. Stay safe. Stay vigilant. #UnitedAgainstFraud</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
@@ -15947,7 +15939,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>Fake jobs ask for fees, transfers, or banking information. • Spot the red flags before it’s too late. • Always verify, stay alert, and protect yourself.</t>
+          <t>Don’t click unfamiliar links. • When in doubt, don’t tap. • Especially in SMS, WhatsApp, or DMs.</t>
         </is>
       </c>
       <c r="AJ92" t="inlineStr">
@@ -16043,7 +16035,7 @@
         <v>0</v>
       </c>
       <c r="V93" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="W93" t="inlineStr">
         <is>
@@ -16201,7 +16193,7 @@
         <v>0</v>
       </c>
       <c r="V94" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="W94" t="inlineStr">
         <is>
@@ -16361,7 +16353,7 @@
         <v>0</v>
       </c>
       <c r="V95" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="W95" t="inlineStr">
         <is>
@@ -16410,11 +16402,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>Please try for my sake to succeed in my absence. 🎵
-Audience interaction ❤️‍🔥
-#Rotana_Live
-#Eid_Events
-#Rabeh_Saqer_in_Riyadh</t>
+          <t>Please try for my sake to succeed in my absence. The audience's reaction.</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
@@ -16447,7 +16435,7 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>🎵 Audience interaction ❤️‍🔥 #Rotana_Live #Eid_Events #Rabeh_Saqer_in_Riyadh • Please try for my sake to succeed in my absence.</t>
+          <t>Please try for my sake to succeed in my absence.</t>
         </is>
       </c>
       <c r="AJ95" t="inlineStr">
@@ -16552,7 +16540,7 @@
         <v>0</v>
       </c>
       <c r="V96" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="W96" t="inlineStr">
         <is>
@@ -16686,7 +16674,7 @@
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Spot the red flags before it’s too late. Fake jobs ask for fees, transfers or banking information. Always verify, stay alert and protect yourself. #UnitedAgainstFraud</t>
+          <t>Spot the red flags before it’s too late. Fake jobs ask for fees, transfers or banking information. Always verify, stay alert and protect yourself. #UnitedAgainstFraud https://t.co/d4EBXeNwqZ</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -16728,7 +16716,7 @@
         <v>5</v>
       </c>
       <c r="V97" t="n">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="W97" t="inlineStr">
         <is>
@@ -16740,11 +16728,19 @@
           <t>Spot the red flags before it’s too late. Fake jobs ask for fees, transfers or banking information. Always verify, stay alert and protect yourself. #UnitedAgainstFraud</t>
         </is>
       </c>
-      <c r="Y97" t="inlineStr"/>
-      <c r="Z97" t="inlineStr"/>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2035612442487661044</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>Spot the red flags before it’s too late. Fake jobs ask for fees, transfers or banking information. Always verify, stay alert and protect yourself. #UnitedAgainstFraud https://t.co/d4EBXeNwqZ</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>Spot the red flags before it’s too late. Fake jobs ask for fees, transfers or banking information. Always verify, stay alert and protect yourself. #UnitedAgainstFraud</t>
+          <t>Spot the red flags before it’s too late. Fake jobs ask for fees, transfers or banking information. Always verify, stay alert and protect yourself. #UnitedAgainstFraud https://t.co/d4EBXeNwqZ</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
@@ -16882,7 +16878,7 @@
         <v>4</v>
       </c>
       <c r="V98" t="n">
-        <v>700</v>
+        <v>705</v>
       </c>
       <c r="W98" t="inlineStr">
         <is>
@@ -17036,7 +17032,7 @@
         <v>0</v>
       </c>
       <c r="V99" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="W99" t="inlineStr">
         <is>
@@ -17186,7 +17182,7 @@
         <v>0</v>
       </c>
       <c r="V100" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="W100" t="inlineStr">
         <is>
@@ -17336,7 +17332,7 @@
         <v>0</v>
       </c>
       <c r="V101" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="W101" t="inlineStr">
         <is>
@@ -17486,7 +17482,7 @@
         <v>0</v>
       </c>
       <c r="V102" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W102" t="inlineStr">
         <is>
@@ -17515,7 +17511,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>Welcome, thank you for contacting us, how can we assist you today.</t>
+          <t>Welcome, thank you for contacting us, how can we assist you today?</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
@@ -17548,7 +17544,7 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>Welcome, thank you for contacting us, how can we assist you today.</t>
+          <t>Welcome, thank you for contacting us, how can we assist you today?</t>
         </is>
       </c>
       <c r="AJ102" t="inlineStr">
@@ -17637,10 +17633,10 @@
         <v>10</v>
       </c>
       <c r="U103" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="V103" t="n">
-        <v>20615</v>
+        <v>20725</v>
       </c>
       <c r="W103" t="inlineStr">
         <is>
@@ -17798,7 +17794,7 @@
         <v>0</v>
       </c>
       <c r="V104" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="W104" t="inlineStr">
         <is>
@@ -17827,7 +17823,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>The text appears to be in English, but it consists mainly of social media handles and emoticons expressing sadness and heartbreak. There is no additional text to translate.</t>
+          <t>The text appears to be in English, but it consists mainly of social media handles and emoticons expressing sadness and heartbreak. Therefore, there is no translation needed.</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
@@ -17860,7 +17856,7 @@
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>The text appears to be in English, but it consists mainly of social media handles and emoticons expressing sadness and heartbreak. • There is no additional text to translate.</t>
+          <t>The text appears to be in English, but it consists mainly of social media handles and emoticons expressing sadness and heartbreak. • Therefore, there is no translation needed.</t>
         </is>
       </c>
       <c r="AJ104" t="inlineStr">
@@ -17965,7 +17961,7 @@
         <v>0</v>
       </c>
       <c r="V105" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="W105" t="inlineStr">
         <is>
@@ -18107,7 +18103,7 @@
       <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr">
         <is>
-          <t>@RotanaLive @Turki_alalshikh @RabehSaqer @GEA_SA @EidSeason @Mabdoarena @EmiratesNBD_KSA خل عندك شخصيه يا عديم الشخصيه لن تصبح حتى ربعه 😏</t>
+          <t>خل عندك شخصيه يا عديم الشخصيه لن تصبح حتى ربعه 😏</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -18149,7 +18145,7 @@
         <v>0</v>
       </c>
       <c r="V106" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="W106" t="inlineStr">
         <is>
@@ -18161,24 +18157,16 @@
           <t>خل عندك شخصيه يا عديم الشخصيه لن تصبح حتى ربعه 😏</t>
         </is>
       </c>
-      <c r="Y106" t="inlineStr">
-        <is>
-          <t>https://x.com/AbuSultan_89/status/2035547614117065127</t>
-        </is>
-      </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>@RotanaLive @Turki_alalshikh @RabehSaqer @GEA_SA @EidSeason @Mabdoarena @EmiratesNBD_KSA خل عندك شخصيه يا عديم الشخصيه لن تصبح حتى ربعه 😏</t>
-        </is>
-      </c>
+      <c r="Y106" t="inlineStr"/>
+      <c r="Z106" t="inlineStr"/>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>@RotanaLive @Turki_alalshikh @RabehSaqer @GEA_SA @EidSeason @Mabdoarena @EmiratesNBD_KSA خل عندك شخصيه يا عديم الشخصيه لن تصبح حتى ربعه 😏</t>
+          <t>خل عندك شخصيه يا عديم الشخصيه لن تصبح حتى ربعه 😏</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>Have some personality, you person without character; you won't even become a quarter of them. 😏</t>
+          <t>Have some personality, you person with no character; you won't even become a quarter of them.</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
@@ -18211,7 +18199,7 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>Have some personality, you person without character; you won't even become a quarter of them.</t>
+          <t>Have some personality, you person with no character; you won't even become a quarter of them.</t>
         </is>
       </c>
       <c r="AJ106" t="inlineStr">
@@ -18307,7 +18295,7 @@
         <v>0</v>
       </c>
       <c r="V107" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W107" t="inlineStr">
         <is>
@@ -18467,7 +18455,7 @@
         <v>0</v>
       </c>
       <c r="V108" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="W108" t="inlineStr">
         <is>
@@ -18630,7 +18618,7 @@
         <v>0</v>
       </c>
       <c r="V109" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="W109" t="inlineStr">
         <is>
@@ -18791,7 +18779,7 @@
         <v>0</v>
       </c>
       <c r="V110" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="W110" t="inlineStr">
         <is>
@@ -18953,7 +18941,7 @@
         <v>0</v>
       </c>
       <c r="V111" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="W111" t="inlineStr">
         <is>
@@ -19081,7 +19069,7 @@
       <c r="M112" t="inlineStr"/>
       <c r="N112" t="inlineStr">
         <is>
-          <t>3h</t>
+          <t>4h</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
@@ -19104,7 +19092,7 @@
         <v>0</v>
       </c>
       <c r="V112" t="n">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="W112" t="inlineStr">
         <is>
@@ -19245,7 +19233,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>6h</t>
+          <t>7h</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
@@ -19268,7 +19256,7 @@
         <v>0</v>
       </c>
       <c r="V113" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W113" t="inlineStr">
         <is>
@@ -19401,7 +19389,7 @@
       <c r="M114" t="inlineStr"/>
       <c r="N114" t="inlineStr">
         <is>
-          <t>7h</t>
+          <t>8h</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
@@ -19424,7 +19412,7 @@
         <v>0</v>
       </c>
       <c r="V114" t="n">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="W114" t="inlineStr">
         <is>
@@ -19551,7 +19539,7 @@
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr">
         <is>
-          <t>7h</t>
+          <t>8h</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
@@ -19574,7 +19562,7 @@
         <v>0</v>
       </c>
       <c r="V115" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="W115" t="inlineStr">
         <is>
@@ -19606,7 +19594,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>Stay alert to scams. Did you receive a renewal message from a Gmail or Yahoo address? What should you do?</t>
+          <t>Stay alert to scams. Received a renewal email from a Gmail or Yahoo address?</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
@@ -19639,7 +19627,7 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>Did you receive a renewal message from a Gmail or Yahoo address?</t>
+          <t>Received a renewal email from a Gmail or Yahoo address?</t>
         </is>
       </c>
       <c r="AJ115" t="inlineStr">
@@ -19733,7 +19721,7 @@
         <v>0</v>
       </c>
       <c r="V116" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="W116" t="inlineStr">
         <is>
@@ -19871,7 +19859,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
@@ -19894,7 +19882,7 @@
         <v>0</v>
       </c>
       <c r="V117" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="W117" t="inlineStr">
         <is>
@@ -19923,7 +19911,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>I have been struggling with my Apple Wallet for 4 months now. Since I changed from iPhone 14 to 17, I cannot add my cards (contact issuer). I have spoken to both of you and the problem has not been resolved yet. All steps were done from both sides too!</t>
+          <t>I have been struggling with my Apple Wallet for 4 months now. Since I changed from iPhone 14 to 17, I cannot add my cards (contact issuer). I have spoken to both of you, and the problem has not been resolved yet. All steps were done from both sides too!</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
@@ -19956,7 +19944,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>Since I changed from iPhone 14 to 17, I cannot add my cards (contact issuer). • I have spoken to both of you and the problem has not been resolved yet. • I have been struggling with my Apple Wallet for 4 months now.</t>
+          <t>Since I changed from iPhone 14 to 17, I cannot add my cards (contact issuer). • I have spoken to both of you, and the problem has not been resolved yet. • I have been struggling with my Apple Wallet for 4 months now.</t>
         </is>
       </c>
       <c r="AJ117" t="inlineStr">
@@ -20030,7 +20018,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>7h</t>
+          <t>8h</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
@@ -20053,7 +20041,7 @@
         <v>0</v>
       </c>
       <c r="V118" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="W118" t="inlineStr">
         <is>
@@ -20084,7 +20072,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>I raised a mail to customer care regarding the flight amount deduction discrepancy twice but didn't hear from Emirates NBD. This is not acceptable at all. I am very disappointed with the customer care service of Emirates NBD. Zero stars.</t>
+          <t>I raised an email to customer care regarding the discrepancy in the flight amount deduction twice but didn't hear from Emirates NBD. This is not acceptable at all. I am very disappointed with the customer care service of Emirates NBD. Zero stars.</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr">
@@ -20117,7 +20105,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>I raised a mail to customer care regarding the flight amount deduction discrepancy twice but didn't hear from Emirates NBD. • I am very disappointed with the customer care service of Emirates NBD. • This is not acceptable at all.</t>
+          <t>I raised an email to customer care regarding the discrepancy in the flight amount deduction twice but didn't hear from Emirates NBD. • I am very disappointed with the customer care service of Emirates NBD. • This is not acceptable at all.</t>
         </is>
       </c>
       <c r="AJ118" t="inlineStr">
@@ -20213,7 +20201,7 @@
         <v>0</v>
       </c>
       <c r="V119" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="W119" t="inlineStr">
         <is>
@@ -20343,7 +20331,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>23h</t>
+          <t>Mar 22</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
@@ -20366,7 +20354,7 @@
         <v>0</v>
       </c>
       <c r="V120" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W120" t="inlineStr">
         <is>
@@ -20507,7 +20495,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>4h</t>
+          <t>5h</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
@@ -20534,7 +20522,7 @@
         <v>0</v>
       </c>
       <c r="V121" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="W121" t="inlineStr">
         <is>
@@ -20661,7 +20649,7 @@
       <c r="M122" t="inlineStr"/>
       <c r="N122" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
@@ -20843,7 +20831,7 @@
         <v>0</v>
       </c>
       <c r="V123" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="W123" t="inlineStr">
         <is>
@@ -20993,7 +20981,7 @@
         <v>0</v>
       </c>
       <c r="V124" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="W124" t="inlineStr">
         <is>
@@ -21116,7 +21104,7 @@
       <c r="M125" t="inlineStr"/>
       <c r="N125" t="inlineStr">
         <is>
-          <t>59m</t>
+          <t>1h</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
@@ -21143,7 +21131,7 @@
         <v>0</v>
       </c>
       <c r="V125" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="W125" t="inlineStr">
         <is>
@@ -21155,16 +21143,8 @@
           <t>@EmiratesNBD_AE Money transfers on ENBD X don't support SWIFT-only beneficiaries for Indian accounts like GIFT City — the app forces an IFSC lookup, but GIFT City IBUs have no IFSC code, completely hindering transfers. Please allow manual SWIFT entry. #GIFTCITY #NRI</t>
         </is>
       </c>
-      <c r="Y125" t="inlineStr">
-        <is>
-          <t>https://x.com/mridulrb/status/2036081518607749454</t>
-        </is>
-      </c>
-      <c r="Z125" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Money transfers on ENBD X don't support SWIFT-only beneficiaries for Indian accounts like GIFT City — the app forces an IFSC lookup, but GIFT City IBUs have no IFSC code, completely hindering transfers. Please allow manual SWIFT entry. #GIFTCITY #NRI</t>
-        </is>
-      </c>
+      <c r="Y125" t="inlineStr"/>
+      <c r="Z125" t="inlineStr"/>
       <c r="AA125" t="inlineStr">
         <is>
           <t>@EmiratesNBD_AE Money transfers on ENBD X don't support SWIFT-only beneficiaries for Indian accounts like GIFT City — the app forces an IFSC lookup, but GIFT City IBUs have no IFSC code, completely hindering transfers. Please allow manual SWIFT entry. #GIFTCITY #NRI</t>
@@ -21274,7 +21254,7 @@
       <c r="M126" t="inlineStr"/>
       <c r="N126" t="inlineStr">
         <is>
-          <t>7h</t>
+          <t>8h</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">

--- a/check2.xlsx
+++ b/check2.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL51"/>
+  <dimension ref="A1:AL53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,32 +625,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2036181530364489860</t>
+          <t>2036300027933433945</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/AlyahiaMoh/status/2036181530364489860</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2036300027933433945</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/AlyahiaMoh</t>
+          <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AlyahiaMoh</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mohammed Alyahia</t>
+          <t>Emirates NBD</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1959335410070409216/2YvWCgCy_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -661,33 +661,34 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; ممكن احد يتواصل معي عن طريق الخاص للمساعدة؟؟</t>
+          <t>مرحباً بك, شكراً لتواصلك معنا, يرجى العلم اننا غير قادرين على التواصل معك على الرسائل, يمكنك الاتصال بنا على 600540000 
+أو عن طريق التحدث معنا من خلال الواتساب البنكي على 600540000 من الساعة 9 صباحا الى 7 مساء</t>
         </is>
       </c>
       <c r="K2" t="b">
         <v>0</v>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>['AlyahiaMoh']</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>7h</t>
+          <t>46m</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Mar 23, 2026 · 8:41 PM UTC</t>
+          <t>Mar 24, 2026 · 4:32 AM UTC</t>
         </is>
       </c>
       <c r="P2" s="2" t="n">
-        <v>46104.86180555556</v>
+        <v>46105.18888888889</v>
       </c>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>['https://x.com/EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
         <v>0</v>
       </c>
@@ -698,7 +699,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -707,24 +708,25 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
+          <t>مرحباً بك, شكراً لتواصلك معنا, يرجى العلم اننا غير قادرين على التواصل معك على الرسائل, يمكنك الاتصال بنا على 600540000 
+أو عن طريق التحدث معنا من خلال الواتساب البنكي على 600540000 من الساعة 9 صباحا الى 7 مساء</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2036300027933433945</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>@EmiratesNBD_AE ممكن احد يتواصل معي عن طريق الخاص للمساعدة؟؟</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>https://x.com/AlyahiaMoh/status/2036181530364489860</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>@EmiratesNBD_AE ممكن احد يتواصل معي عن طريق الخاص للمساعدة؟؟</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE ممكن احد يتواصل معي عن طريق الخاص للمساعدة؟؟</t>
-        </is>
-      </c>
       <c r="AB2" t="inlineStr">
         <is>
           <t>Can someone contact me privately for assistance?</t>
@@ -741,7 +743,7 @@
         </is>
       </c>
       <c r="AE2" s="2" t="n">
-        <v>46105.02847222222</v>
+        <v>46105.35555555556</v>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
@@ -773,7 +775,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>AlyahiaMoh</t>
         </is>
       </c>
     </row>
@@ -783,12 +785,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2036176545543266757</t>
+          <t>2036181530364489860</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://x.com/AlyahiaMoh/status/2036176545543266757</t>
+          <t>https://x.com/AlyahiaMoh/status/2036181530364489860</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -814,42 +816,40 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ما اقدر ارسلك شي ع الخاص لان حسابي مو موثق
-فيه احد يتواصل معي؟</t>
+          <t>@EmiratesNBD_AE ممكن احد يتواصل معي عن طريق الخاص للمساعدة؟؟</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>ما اقدر ارسلك شي ع الخاص لان حسابي مو موثق
-فيه احد يتواصل معي؟</t>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; ممكن احد يتواصل معي عن طريق الخاص للمساعدة؟؟</t>
         </is>
       </c>
       <c r="K3" t="b">
         <v>0</v>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>7h</t>
+          <t>8h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Mar 23, 2026 · 8:21 PM UTC</t>
+          <t>Mar 23, 2026 · 8:41 PM UTC</t>
         </is>
       </c>
       <c r="P3" s="2" t="n">
-        <v>46104.84791666667</v>
+        <v>46104.86180555556</v>
       </c>
       <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -858,7 +858,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -867,21 +867,19 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>ما اقدر ارسلك شي ع الخاص لان حسابي مو موثق
-فيه احد يتواصل معي؟</t>
+          <t>@EmiratesNBD_AE ممكن احد يتواصل معي عن طريق الخاص للمساعدة؟؟</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>ما اقدر ارسلك شي ع الخاص لان حسابي مو موثق
-فيه احد يتواصل معي؟</t>
+          <t>@EmiratesNBD_AE ممكن احد يتواصل معي عن طريق الخاص للمساعدة؟؟</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>I can't send you anything privately because my account is not verified. Is there anyone who can contact me?</t>
+          <t>Can someone contact me privately for assistance?</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -895,7 +893,7 @@
         </is>
       </c>
       <c r="AE3" s="2" t="n">
-        <v>46105.01458333333</v>
+        <v>46105.02847222222</v>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
@@ -914,7 +912,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>I can't send you anything privately because my account is not verified. • Is there anyone who can contact me?</t>
+          <t>Can someone contact me privately for assistance?</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -927,7 +925,7 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -937,36 +935,199 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2036171018964713797</t>
+          <t>2036176545543266757</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/Pjnw0/status/2036171018964713797</t>
+          <t>https://x.com/AlyahiaMoh/status/2036176545543266757</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://x.com/Pjnw0</t>
+          <t>https://x.com/AlyahiaMoh</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pjnw0</t>
+          <t>AlyahiaMoh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ًً</t>
+          <t>Mohammed Alyahia</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1917726644028014592/_A_c0Mka_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1959335410070409216/2YvWCgCy_bigger.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE 
+يعطيكم العافية ايش ال swift code الخاص بفرع طريق الشيخ زايد "رحمه الله" نفس اللي بالصورة https://t.co/kgaOc7hiuO</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ما اقدر ارسلك شي ع الخاص لان حسابي مو موثق
+فيه احد يتواصل معي؟</t>
+        </is>
+      </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>8h</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Mar 23, 2026 · 8:21 PM UTC</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>46104.84791666667</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>16</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>ما اقدر ارسلك شي ع الخاص لان حسابي مو موثق
+فيه احد يتواصل معي؟</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>https://x.com/AlyahiaMoh/status/2036176545543266757</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE 
+يعطيكم العافية ايش ال swift code الخاص بفرع طريق الشيخ زايد "رحمه الله" نفس اللي بالصورة https://t.co/kgaOc7hiuO</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE 
+يعطيكم العافية ايش ال swift code الخاص بفرع طريق الشيخ زايد "رحمه الله" نفس اللي بالصورة https://t.co/kgaOc7hiuO</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>What is the SWIFT code for the Sheikh Zayed Road branch "may he rest in peace," the same as in the picture?</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE4" s="2" t="n">
+        <v>46105.01458333333</v>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>24-03-2026</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>What is the SWIFT code for the Sheikh Zayed Road branch "may he rest in peace," the same as in the picture?</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK4" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2036171018964713797</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://x.com/Pjnw0/status/2036171018964713797</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://x.com/Pjnw0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Pjnw0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ًً</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1917726644028014592/_A_c0Mka_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
         <is>
           <t>الصقر بعد ختام حفلة الليلة🦅
 انتظروا الألبوم الجديد قريباً على #روتانا 💚😍
@@ -982,63 +1143,63 @@
 @EmiratesNBD_KSA https://t.co/X1Ds9wmkXZ</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>ما الومه يسال بيكمل سنه من الاعلان</t>
         </is>
       </c>
-      <c r="K4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
         <is>
           <t>['Sadziz13', 'RotanaLive', 'Turki_alalshikh', 'RabehSaqer', 'salhendi', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>8h</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>9h</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>Mar 23, 2026 · 7:59 PM UTC</t>
         </is>
       </c>
-      <c r="P4" s="2" t="n">
+      <c r="P5" s="2" t="n">
         <v>46104.83263888889</v>
       </c>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>31</v>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>33</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>ما الومه يسال بيكمل سنه من الاعلان</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>https://x.com/Pjnw0/status/2036171018964713797</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>الصقر بعد ختام حفلة الليلة🦅
 انتظروا الألبوم الجديد قريباً على #روتانا 💚😍
@@ -1054,7 +1215,7 @@
 @EmiratesNBD_KSA https://t.co/X1Ds9wmkXZ</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>الصقر بعد ختام حفلة الليلة🦅
 انتظروا الألبوم الجديد قريباً على #روتانا 💚😍
@@ -1070,7 +1231,7 @@
 @EmiratesNBD_KSA https://t.co/X1Ds9wmkXZ</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>The falcon after the conclusion of tonight's party🦅 Stay tuned for the new album coming soon on #Rotana 💚😍 
 #Rotana_Live 
@@ -1085,198 +1246,37 @@
 @EmiratesNBD_KSA</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="AE4" s="2" t="n">
+      <c r="AE5" s="2" t="n">
         <v>46104.99930555555</v>
       </c>
-      <c r="AF4" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>23-03-2026</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AI5" t="inlineStr">
         <is>
           <t>The falcon after the conclusion of tonight's party🦅 Stay tuned for the new album coming soon on #Rotana 💚😍 #Rotana_Live …</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AK4" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>Sadziz13, RotanaLive, Turki_alalshikh, RabehSaqer, salhendi, GEA_SA, EidSeason, Mabdoarena, EmiratesNBD_KSA</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2036140802057896269</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2036140802057896269</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>EmiratesNBD_AE</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Emirates NBD</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE 
-يعطيكم العافية ايش ال swift code الخاص بفرع طريق الشيخ زايد "رحمه الله" نفس اللي بالصورة https://t.co/kgaOc7hiuO</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>مرحبا محمد شكرا لتواصلك معنا برجاء إرسال تفاصيل إستفسارك عبر رسائل الخاص</t>
-        </is>
-      </c>
-      <c r="K5" t="b">
-        <v>0</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>['AlyahiaMoh']</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>10h</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Mar 23, 2026 · 5:59 PM UTC</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="n">
-        <v>46104.74930555555</v>
-      </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>19</v>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>مرحبا محمد شكرا لتواصلك معنا برجاء إرسال تفاصيل إستفسارك عبر رسائل الخاص</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2036140802057896269</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE 
-يعطيكم العافية ايش ال swift code الخاص بفرع طريق الشيخ زايد "رحمه الله" نفس اللي بالصورة https://t.co/kgaOc7hiuO</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE 
-يعطيكم العافية ايش ال swift code الخاص بفرع طريق الشيخ زايد "رحمه الله" نفس اللي بالصورة https://t.co/kgaOc7hiuO</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>What is the SWIFT code for the Sheikh Zayed Road branch "may he rest in peace," the same as in the picture?</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AE5" s="2" t="n">
-        <v>46104.91597222222</v>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>23-03-2026</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>What is the SWIFT code for the Sheikh Zayed Road branch "may he rest in peace," the same as in the picture?</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>AlyahiaMoh</t>
+          <t>Sadziz13, RotanaLive, Turki_alalshikh, RabehSaqer, salhendi, GEA_SA, EidSeason, Mabdoarena, EmiratesNBD_KSA</t>
         </is>
       </c>
     </row>
@@ -1299,36 +1299,186 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2036136587390533632</t>
+          <t>2036140802057896269</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://x.com/cas_2050001283/status/2036136587390533632</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2036140802057896269</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://x.com/cas_2050001283</t>
+          <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>cas_2050001283</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CASTest2050001283</t>
+          <t>Emirates NBD</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
+        <is>
+          <t>مرحبا محمد شكرا لتواصلك معنا برجاء إرسال تفاصيل إستفسارك عبر رسائل الخاص</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>مرحبا محمد شكرا لتواصلك معنا برجاء إرسال تفاصيل إستفسارك عبر رسائل الخاص</t>
+        </is>
+      </c>
+      <c r="K6" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>['AlyahiaMoh']</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>11h</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Mar 23, 2026 · 5:59 PM UTC</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>46104.74930555555</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>23</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>مرحبا محمد شكرا لتواصلك معنا برجاء إرسال تفاصيل إستفسارك عبر رسائل الخاص</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>مرحبا محمد شكرا لتواصلك معنا برجاء إرسال تفاصيل إستفسارك عبر رسائل الخاص</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>Hello Mohammed, thank you for contacting us. Please send the details of your inquiry via private messages.</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE6" s="2" t="n">
+        <v>46104.91597222222</v>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>23-03-2026</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Please send the details of your inquiry via private messages. • Hello Mohammed, thank you for contacting us.</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK6" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>AlyahiaMoh</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2036136587390533632</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://x.com/cas_2050001283/status/2036136587390533632</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://x.com/cas_2050001283</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>cas_2050001283</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>CASTest2050001283</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
         <is>
           <t>EnbD Uv6DtrmP Á7iLiMÁBpÁ
 0m&amp;gt;T⃑h&amp;gt;ÁE
@@ -1337,7 +1487,7 @@
 qpo🧑🏼‍❤️‍💋‍🧑🏾1A🧙🏿‍♂️7o💅🏿B👇🏻 https://t.co/SxESBo3MLg</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>EnbD Uv6DtrmP Á7iLiMÁBpÁ
 0m&amp;gt;T⃑h&amp;gt;ÁE
@@ -1346,44 +1496,44 @@
 qpo🧑🏼‍❤️‍💋‍🧑🏾1A🧙🏿‍♂️7o💅🏿B👇🏻</t>
         </is>
       </c>
-      <c r="K6" t="b">
-        <v>0</v>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>10h</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="K7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>11h</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>Mar 23, 2026 · 5:42 PM UTC</t>
         </is>
       </c>
-      <c r="P6" s="2" t="n">
+      <c r="P7" s="2" t="n">
         <v>46104.7375</v>
       </c>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>5</v>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>7</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>EnbD Uv6DtrmP Á7iLiMÁBpÁ
 0m&gt;T⃑h&gt;ÁE
@@ -1392,12 +1542,12 @@
 qpo🧑🏼‍❤️‍💋‍🧑🏾1A🧙🏿‍♂️7o💅🏿B👇🏻</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>https://x.com/cas_2050001283/status/2036136587390533632</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>EnbD Uv6DtrmP Á7iLiMÁBpÁ
 0m&amp;gt;T⃑h&amp;gt;ÁE
@@ -1406,7 +1556,7 @@
 qpo🧑🏼‍❤️‍💋‍🧑🏾1A🧙🏿‍♂️7o💅🏿B👇🏻 https://t.co/SxESBo3MLg</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>EnbD Uv6DtrmP Á7iLiMÁBpÁ
 0m&amp;gt;T⃑h&amp;gt;ÁE
@@ -1415,196 +1565,42 @@
 qpo🧑🏼‍❤️‍💋‍🧑🏾1A🧙🏿‍♂️7o💅🏿B👇🏻 https://t.co/SxESBo3MLg</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>The text appears to be a mix of characters, symbols, and emojis that do not form coherent sentences in any specific language. Therefore, it cannot be translated into fluent English.</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="AE6" s="2" t="n">
+      <c r="AE7" s="2" t="n">
         <v>46104.90416666667</v>
       </c>
-      <c r="AF6" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>23-03-2026</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AI7" t="inlineStr">
         <is>
           <t>The text appears to be a mix of characters, symbols, and emojis that do not form coherent sentences in any specific language. • Therefore, it cannot be translated into fluent English.</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AK6" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2036130140510449946</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://x.com/AlyahiaMoh/status/2036130140510449946</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>https://x.com/AlyahiaMoh</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>AlyahiaMoh</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Mohammed Alyahia</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1959335410070409216/2YvWCgCy_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE 
-يعطيكم العافية ايش ال swift code الخاص بفرع طريق الشيخ زايد "رحمه الله" نفس اللي بالصورة</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; 
-يعطيكم العافية ايش ال swift code الخاص بفرع طريق الشيخ زايد &amp;#34;رحمه الله&amp;#34; نفس اللي بالصورة</t>
-        </is>
-      </c>
-      <c r="K7" t="b">
-        <v>0</v>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>10h</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Mar 23, 2026 · 5:17 PM UTC</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="n">
-        <v>46104.72013888889</v>
-      </c>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>['https://x.com/EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>15</v>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE 
-يعطيكم العافية ايش ال swift code الخاص بفرع طريق الشيخ زايد "رحمه الله" نفس اللي بالصورة</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE 
-يعطيكم العافية ايش ال swift code الخاص بفرع طريق الشيخ زايد "رحمه الله" نفس اللي بالصورة</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Thank you, what is the SWIFT code for the Sheikh Zayed Road branch "may he rest in peace" like the one in the picture?</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AE7" s="2" t="n">
-        <v>46104.88680555556</v>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>23-03-2026</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Thank you, what is the SWIFT code for the Sheikh Zayed Road branch "may he rest in peace" like the one in the picture?</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1627,36 +1623,359 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2036080525308252666</t>
+          <t>2036130140510449946</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_EGY/status/2036080525308252666</t>
+          <t>https://x.com/AlyahiaMoh/status/2036130140510449946</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_EGY</t>
+          <t>https://x.com/AlyahiaMoh</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>EmiratesNBD_EGY</t>
+          <t>AlyahiaMoh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>Mohammed Alyahia</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427526482108416/qjFPlJ1n_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1959335410070409216/2YvWCgCy_bigger.jpg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE 
+يعطيكم العافية ايش ال swift code الخاص بفرع طريق الشيخ زايد "رحمه الله" نفس اللي بالصورة</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; 
+يعطيكم العافية ايش ال swift code الخاص بفرع طريق الشيخ زايد &amp;#34;رحمه الله&amp;#34; نفس اللي بالصورة</t>
+        </is>
+      </c>
+      <c r="K8" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>12h</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Mar 23, 2026 · 5:17 PM UTC</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>46104.72013888889</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>19</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE 
+يعطيكم العافية ايش ال swift code الخاص بفرع طريق الشيخ زايد "رحمه الله" نفس اللي بالصورة</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE 
+يعطيكم العافية ايش ال swift code الخاص بفرع طريق الشيخ زايد "رحمه الله" نفس اللي بالصورة</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>What is the SWIFT code for the Sheikh Zayed Road branch "may he rest in peace," the same as in the picture?</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE8" s="2" t="n">
+        <v>46104.88680555556</v>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>23-03-2026</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>What is the SWIFT code for the Sheikh Zayed Road branch "may he rest in peace," the same as in the picture?</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK8" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2036080525308252666</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_EGY/status/2036080525308252666</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_EGY</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_EGY</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Emirates NBD</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1762427526482108416/qjFPlJ1n_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Double click and instantly.
+Use Apple Pay with your Emirates NBD Cards for fast, secure payments in your iPhone or Apple Watch wherever contactless payments are accepted.
+Terms &amp;amp; Conditions Apply.
+Tax registration number: 204-897-319 https://t.co/VIYiv3iBPu</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Double click and instantly.
+Use Apple Pay with your Emirates NBD Cards for fast, secure payments in your iPhone or Apple Watch wherever contactless payments are accepted.
+Terms &amp;amp; Conditions Apply.
+Tax registration number: 204-897-319</t>
+        </is>
+      </c>
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Mar 23, 2026 · 2:00 PM UTC</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="n">
+        <v>46104.58333333334</v>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>50</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Double click and instantly.
+Use Apple Pay with your Emirates NBD Cards for fast, secure payments in your iPhone or Apple Watch wherever contactless payments are accepted.
+Terms &amp; Conditions Apply.
+Tax registration number: 204-897-319</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_EGY/status/2036080525308252666</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>Double click and instantly.
+Use Apple Pay with your Emirates NBD Cards for fast, secure payments in your iPhone or Apple Watch wherever contactless payments are accepted.
+Terms &amp;amp; Conditions Apply.
+Tax registration number: 204-897-319 https://t.co/VIYiv3iBPu</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Double click and instantly.
+Use Apple Pay with your Emirates NBD Cards for fast, secure payments in your iPhone or Apple Watch wherever contactless payments are accepted.
+Terms &amp;amp; Conditions Apply.
+Tax registration number: 204-897-319 https://t.co/VIYiv3iBPu</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>Double click and instantly. Use Apple Pay with your Emirates NBD Cards for fast, secure payments on your iPhone or Apple Watch wherever contactless payments are accepted. Terms &amp; Conditions Apply. Tax registration number: 204-897-319</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Bank</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AE9" s="2" t="n">
+        <v>46104.75</v>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>23-03-2026</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Use Apple Pay with your Emirates NBD Cards for fast, secure payments on your iPhone or Apple Watch wherever contactless payments are accepted. • Tax registration number: 204-897-319 • Double click and instantly.</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK9" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2036080525299925460</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_EGY/status/2036080525299925460</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_EGY</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_EGY</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Emirates NBD</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1762427526482108416/qjFPlJ1n_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
         <is>
           <t>تسوق  هدايا عيد الأم .. وادفع بطريقتك.
 اكتشف أشهر البراندات في مكان واحد في Jlood ب 0% مقدم، 0% فوائد  و0% مصاريف إدارية على 6 أشهر من خلال الموقع الإلكتروني عند الدفع باستخدام بطاقات بنك الإمارات دبي الوطني الائتمانية.
@@ -1665,65 +1984,65 @@
 رقم التسجيل الضريبي: 319-897-204</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Double click and instantly.
-Use Apple Pay with your Emirates NBD Cards for fast, secure payments in your iPhone or Apple Watch wherever contactless payments are accepted.
-Terms &amp;amp; Conditions Apply.
-Tax registration number: 204-897-319</t>
-        </is>
-      </c>
-      <c r="K8" t="b">
-        <v>0</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>14h</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>اضغط مرتين وادفع فورًا.
+استخدم Apple Pay مع بطاقات بنك الإمارات دبي الوطني وادفع بسهولة وأمان من خلال Apple Wallet أو iPhone 
+تطبق الشروط والأحكام.
+رقم التسجيل الضريبي: 319-897-204</t>
+        </is>
+      </c>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>Mar 23, 2026 · 2:00 PM UTC</t>
         </is>
       </c>
-      <c r="P8" s="2" t="n">
+      <c r="P10" s="2" t="n">
         <v>46104.58333333334</v>
       </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>48</v>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>Double click and instantly.
-Use Apple Pay with your Emirates NBD Cards for fast, secure payments in your iPhone or Apple Watch wherever contactless payments are accepted.
-Terms &amp; Conditions Apply.
-Tax registration number: 204-897-319</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_EGY/status/2036080525308252666</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>67</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>اضغط مرتين وادفع فورًا.
+استخدم Apple Pay مع بطاقات بنك الإمارات دبي الوطني وادفع بسهولة وأمان من خلال Apple Wallet أو iPhone 
+تطبق الشروط والأحكام.
+رقم التسجيل الضريبي: 319-897-204</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_EGY/status/2036080525299925460</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
         <is>
           <t>تسوق  هدايا عيد الأم .. وادفع بطريقتك.
 اكتشف أشهر البراندات في مكان واحد في Jlood ب 0% مقدم، 0% فوائد  و0% مصاريف إدارية على 6 أشهر من خلال الموقع الإلكتروني عند الدفع باستخدام بطاقات بنك الإمارات دبي الوطني الائتمانية.
@@ -1732,7 +2051,7 @@
 رقم التسجيل الضريبي: 319-897-204</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>تسوق  هدايا عيد الأم .. وادفع بطريقتك.
 اكتشف أشهر البراندات في مكان واحد في Jlood ب 0% مقدم، 0% فوائد  و0% مصاريف إدارية على 6 أشهر من خلال الموقع الإلكتروني عند الدفع باستخدام بطاقات بنك الإمارات دبي الوطني الائتمانية.
@@ -1741,370 +2060,42 @@
 رقم التسجيل الضريبي: 319-897-204</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>Shop for Mother's Day gifts and pay your way. Discover the most famous brands in one place at Jlood with 0% down payment, 0% interest, and 0% administrative fees for 6 months through the website when paying with Emirates NBD credit cards. The offer is valid until April 15, 2026. Terms and conditions apply. Tax registration number: 319-897-204.</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>Bank</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="AE8" s="2" t="n">
+      <c r="AE10" s="2" t="n">
         <v>46104.75</v>
       </c>
-      <c r="AF8" t="inlineStr">
+      <c r="AF10" t="inlineStr">
         <is>
           <t>23-03-2026</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AI10" t="inlineStr">
         <is>
           <t>Discover the most famous brands in one place at Jlood with 0% down payment, 0% interest, and 0% administrative fees for 6 months through the website when paying with Emirates NBD credit cards. • Tax registration number: 319-897-204. • The offer is valid until April 15, 2026.</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AK8" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2036080525299925460</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_EGY/status/2036080525299925460</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_EGY</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>EmiratesNBD_EGY</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Emirates NBD</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1762427526482108416/qjFPlJ1n_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>اضغط مرتين وادفع فورًا.
-استخدم Apple Pay مع بطاقات بنك الإمارات دبي الوطني وادفع بسهولة وأمان من خلال Apple Wallet أو iPhone 
-تطبق الشروط والأحكام.
-رقم التسجيل الضريبي: 319-897-204 https://t.co/gwVMTmxlJs</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>اضغط مرتين وادفع فورًا.
-استخدم Apple Pay مع بطاقات بنك الإمارات دبي الوطني وادفع بسهولة وأمان من خلال Apple Wallet أو iPhone 
-تطبق الشروط والأحكام.
-رقم التسجيل الضريبي: 319-897-204</t>
-        </is>
-      </c>
-      <c r="K9" t="b">
-        <v>0</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>14h</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Mar 23, 2026 · 2:00 PM UTC</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="n">
-        <v>46104.58333333334</v>
-      </c>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>65</v>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>اضغط مرتين وادفع فورًا.
-استخدم Apple Pay مع بطاقات بنك الإمارات دبي الوطني وادفع بسهولة وأمان من خلال Apple Wallet أو iPhone 
-تطبق الشروط والأحكام.
-رقم التسجيل الضريبي: 319-897-204</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_EGY/status/2036080525299925460</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>اضغط مرتين وادفع فورًا.
-استخدم Apple Pay مع بطاقات بنك الإمارات دبي الوطني وادفع بسهولة وأمان من خلال Apple Wallet أو iPhone 
-تطبق الشروط والأحكام.
-رقم التسجيل الضريبي: 319-897-204 https://t.co/gwVMTmxlJs</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>اضغط مرتين وادفع فورًا.
-استخدم Apple Pay مع بطاقات بنك الإمارات دبي الوطني وادفع بسهولة وأمان من خلال Apple Wallet أو iPhone 
-تطبق الشروط والأحكام.
-رقم التسجيل الضريبي: 319-897-204 https://t.co/gwVMTmxlJs</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>Double tap and pay instantly. Use Apple Pay with Emirates NBD cards and pay easily and securely through Apple Wallet or iPhone. Terms and conditions apply. Tax registration number: 319-897-204 https://t.co/gwVMTmxlJs</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="AE9" s="2" t="n">
-        <v>46104.75</v>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>23-03-2026</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Tax registration number: 319-897-204 https://t.co/gwVMTmxlJs • Use Apple Pay with Emirates NBD cards and pay easily and securely through Apple Wallet or iPhone. • Double tap and pay instantly.</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AK9" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2036079925136949553</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>https://x.com/Sadziz13/status/2036079925136949553</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>https://x.com/Sadziz13</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Sadziz13</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>مَ. سعـد عبدالعزيز</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1711030291840577537/3X1cIUsy_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>حبيبنا بو شليل والله 
-كل ما مسك المايك سأل بوصقر متى الالبوم ؟ 😂
-خلووو بوصقر على كيفه وبراحته 🦅😍</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>حبيبنا بو شليل والله 
-كل ما مسك المايك سأل بوصقر متى الالبوم ؟ 😂
-خلووو بوصقر على كيفه وبراحته 🦅😍</t>
-        </is>
-      </c>
-      <c r="K10" t="b">
-        <v>0</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>['RotanaLive', 'Turki_alalshikh', 'RabehSaqer', 'salhendi', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>14h</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Mar 23, 2026 · 1:57 PM UTC</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="n">
-        <v>46104.58125</v>
-      </c>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="n">
-        <v>1</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V10" t="n">
-        <v>98</v>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>حبيبنا بو شليل والله 
-كل ما مسك المايك سأل بوصقر متى الالبوم ؟ 😂
-خلووو بوصقر على كيفه وبراحته 🦅😍</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>حبيبنا بو شليل والله 
-كل ما مسك المايك سأل بوصقر متى الالبوم ؟ 😂
-خلووو بوصقر على كيفه وبراحته 🦅😍</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Our dear Abu Shalil, every time he grabs the mic, he asks Abu Saqr when the album is coming out? 😂
-Let Abu Saqr take his time and do it at his own pace. 🦅😍</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AE10" s="2" t="n">
-        <v>46104.74791666667</v>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>23-03-2026</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Our dear Abu Shalil, every time he grabs the mic, he asks Abu Saqr when the album is coming out? • 😂 Let Abu Saqr take his time and do it at his own pace.</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -2117,7 +2108,7 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>RotanaLive, Turki_alalshikh, RabehSaqer, salhendi, GEA_SA, EidSeason, Mabdoarena, EmiratesNBD_KSA</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2127,45 +2118,47 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2036058390850654260</t>
+          <t>2036079925136949553</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://x.com/soviergn/status/2036058390850654260</t>
+          <t>https://x.com/Sadziz13/status/2036079925136949553</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://x.com/soviergn</t>
+          <t>https://x.com/Sadziz13</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>soviergn</t>
+          <t>Sadziz13</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sovereign Alpha</t>
+          <t>مَ. سعـد عبدالعزيز</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2027700895899914242/dNUJuxkf_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1711030291840577537/3X1cIUsy_bigger.jpg</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>The iPhone 17 Pro Max price difference between India and UAE is ₹27,524.
-Take a flight from Mumbai to Dubai, buy an iPhone there, and return to Mumbai on the same day. This will cost you ₹27,550 with travel insurance.
-For just ₹26 more, you get a trip to Dubai. https://t.co/VOhzacVidp</t>
+          <t>حبيبنا بو شليل والله 
+كل ما مسك المايك سأل بوصقر متى الالبوم ؟ 😂
+خلووو بوصقر على كيفه وبراحته 🦅😍</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Brought 17 Pro Max with discount for 1,14,000 in Virgin Megastore. Also got cashback of 8% with ENBD share card.</t>
+          <t>حبيبنا بو شليل والله 
+كل ما مسك المايك سأل بوصقر متى الالبوم ؟ 😂
+خلووو بوصقر على كيفه وبراحته 🦅😍</t>
         </is>
       </c>
       <c r="K11" t="b">
@@ -2174,7 +2167,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>['NalinisKitchen']</t>
+          <t>['RotanaLive', 'Turki_alalshikh', 'RabehSaqer', 'salhendi', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -2184,25 +2177,25 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Mar 23, 2026 · 12:32 PM UTC</t>
+          <t>Mar 23, 2026 · 1:57 PM UTC</t>
         </is>
       </c>
       <c r="P11" s="2" t="n">
-        <v>46104.52222222222</v>
+        <v>46104.58125</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" t="n">
-        <v>36</v>
+        <v>101</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -2211,31 +2204,24 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Brought 17 Pro Max with discount for 1,14,000 in Virgin Megastore. Also got cashback of 8% with ENBD share card.</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>https://x.com/soviergn/status/2036058390850654260</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>The iPhone 17 Pro Max price difference between India and UAE is ₹27,524.
-Take a flight from Mumbai to Dubai, buy an iPhone there, and return to Mumbai on the same day. This will cost you ₹27,550 with travel insurance.
-For just ₹26 more, you get a trip to Dubai. https://t.co/VOhzacVidp</t>
-        </is>
-      </c>
+          <t>حبيبنا بو شليل والله 
+كل ما مسك المايك سأل بوصقر متى الالبوم ؟ 😂
+خلووو بوصقر على كيفه وبراحته 🦅😍</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>The iPhone 17 Pro Max price difference between India and UAE is ₹27,524.
-Take a flight from Mumbai to Dubai, buy an iPhone there, and return to Mumbai on the same day. This will cost you ₹27,550 with travel insurance.
-For just ₹26 more, you get a trip to Dubai. https://t.co/VOhzacVidp</t>
+          <t>حبيبنا بو شليل والله 
+كل ما مسك المايك سأل بوصقر متى الالبوم ؟ 😂
+خلووو بوصقر على كيفه وبراحته 🦅😍</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>The price difference for the iPhone 17 Pro Max between India and the UAE is ₹27,524. Take a flight from Mumbai to Dubai, buy an iPhone there, and return to Mumbai on the same day. This will cost you ₹27,550 with travel insurance. For just ₹26 more, you get a trip to Dubai.</t>
+          <t>Our dear Abu Shalil, every time he grabs the mic, he asks Abu Saqr when the album is coming out? 😂
+Let Abu Saqr take his time and do it at his own pace. 🦅😍</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2249,7 +2235,7 @@
         </is>
       </c>
       <c r="AE11" s="2" t="n">
-        <v>46104.68888888889</v>
+        <v>46104.74791666667</v>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
@@ -2268,7 +2254,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>The price difference for the iPhone 17 Pro Max between India and the UAE is ₹27,524. • Take a flight from Mumbai to Dubai, buy an iPhone there, and return to Mumbai on the same day. • This will cost you ₹27,550 with travel insurance.</t>
+          <t>Our dear Abu Shalil, every time he grabs the mic, he asks Abu Saqr when the album is coming out? • 😂 Let Abu Saqr take his time and do it at his own pace.</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -2281,7 +2267,7 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>NalinisKitchen</t>
+          <t>RotanaLive, Turki_alalshikh, RabehSaqer, salhendi, GEA_SA, EidSeason, Mabdoarena, EmiratesNBD_KSA</t>
         </is>
       </c>
     </row>
@@ -2291,36 +2277,200 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2036055087643042221</t>
+          <t>2036058390850654260</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2036055087643042221</t>
+          <t>https://x.com/soviergn/status/2036058390850654260</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/soviergn</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>soviergn</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>Sovereign Alpha</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2027700895899914242/dNUJuxkf_bigger.jpg</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
+        <is>
+          <t>The iPhone 17 Pro Max price difference between India and UAE is ₹27,524.
+Take a flight from Mumbai to Dubai, buy an iPhone there, and return to Mumbai on the same day. This will cost you ₹27,550 with travel insurance.
+For just ₹26 more, you get a trip to Dubai. https://t.co/VOhzacVidp</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Brought 17 Pro Max with discount for 1,14,000 in Virgin Megastore. Also got cashback of 8% with ENBD share card.</t>
+        </is>
+      </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>['NalinisKitchen']</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>16h</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Mar 23, 2026 · 12:32 PM UTC</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="n">
+        <v>46104.52222222222</v>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>39</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Brought 17 Pro Max with discount for 1,14,000 in Virgin Megastore. Also got cashback of 8% with ENBD share card.</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>https://x.com/soviergn/status/2036058390850654260</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>The iPhone 17 Pro Max price difference between India and UAE is ₹27,524.
+Take a flight from Mumbai to Dubai, buy an iPhone there, and return to Mumbai on the same day. This will cost you ₹27,550 with travel insurance.
+For just ₹26 more, you get a trip to Dubai. https://t.co/VOhzacVidp</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>The iPhone 17 Pro Max price difference between India and UAE is ₹27,524.
+Take a flight from Mumbai to Dubai, buy an iPhone there, and return to Mumbai on the same day. This will cost you ₹27,550 with travel insurance.
+For just ₹26 more, you get a trip to Dubai. https://t.co/VOhzacVidp</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>The price difference for the iPhone 17 Pro Max between India and the UAE is ₹27,524. Take a flight from Mumbai to Dubai, buy an iPhone there, and return to Mumbai on the same day. This will cost you ₹27,550 with travel insurance. For just ₹26 more, you get a trip to Dubai.</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE12" s="2" t="n">
+        <v>46104.68888888889</v>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>23-03-2026</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>The price difference for the iPhone 17 Pro Max between India and the UAE is ₹27,524. • Take a flight from Mumbai to Dubai, buy an iPhone there, and return to Mumbai on the same day. • This will cost you ₹27,550 with travel insurance.</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK12" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>NalinisKitchen</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2036055087643042221</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2036055087643042221</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Emirates NBD</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
         <is>
           <t>Don’t click unfamiliar links.
 Especially in SMS, WhatsApp, or DMs. When in doubt, don’t tap.
@@ -2328,65 +2478,65 @@
 https://t.co/YpRWtBZrhq</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>Apply for an Emirates NBD Visa Credit Card for a chance to watch FIFA World Cup 26™ live with Pep.
 &lt;a href="https://www.emiratesnbd.com/en/campaigns/visa-pep-promotion"&gt;emiratesnbd.com/en/campaigns…&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K12" t="b">
-        <v>0</v>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>15h</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>16h</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
         <is>
           <t>Mar 23, 2026 · 12:18 PM UTC</t>
         </is>
       </c>
-      <c r="P12" s="2" t="n">
+      <c r="P13" s="2" t="n">
         <v>46104.5125</v>
       </c>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr">
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
         <is>
           <t>['https://www.emiratesnbd.com/en/campaigns/visa-pep-promotion']</t>
         </is>
       </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
         <v>5</v>
       </c>
-      <c r="V12" t="n">
-        <v>644</v>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="V13" t="n">
+        <v>662</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
         <is>
           <t>Apply for an Emirates NBD Visa Credit Card for a chance to watch FIFA World Cup 26™ live with Pep.
 emiratesnbd.com/en/campaigns…</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2036055087643042221</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>Don’t click unfamiliar links.
 Especially in SMS, WhatsApp, or DMs. When in doubt, don’t tap.
@@ -2394,7 +2544,7 @@
 https://t.co/YpRWtBZrhq</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>Don’t click unfamiliar links.
 Especially in SMS, WhatsApp, or DMs. When in doubt, don’t tap.
@@ -2402,94 +2552,94 @@
 https://t.co/YpRWtBZrhq</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Don’t click unfamiliar links. Especially in SMS, WhatsApp, or DMs. When in doubt, don’t tap. Stay safe. Stay vigilant. #UnitedAgainstFraud</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>Don't click unfamiliar links. Especially in SMS, WhatsApp, or DMs. When in doubt, don't tap. Stay safe. Stay vigilant. #UnitedAgainstFraud</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
         <is>
           <t>Bank</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AD13" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="AE12" s="2" t="n">
+      <c r="AE13" s="2" t="n">
         <v>46104.67916666667</v>
       </c>
-      <c r="AF12" t="inlineStr">
+      <c r="AF13" t="inlineStr">
         <is>
           <t>23-03-2026</t>
         </is>
       </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH12" t="inlineStr">
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Don’t click unfamiliar links. • When in doubt, don’t tap. • Especially in SMS, WhatsApp, or DMs.</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Don't click unfamiliar links. • When in doubt, don't tap. • Especially in SMS, WhatsApp, or DMs.</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
         <is>
           <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AK12" t="n">
+      <c r="AK13" t="n">
         <v>2026</v>
       </c>
-      <c r="AL12" t="inlineStr">
+      <c r="AL13" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
         <is>
           <t>2036035724667974026</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>https://x.com/li_yxe/status/2036035724667974026</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>https://x.com/li_yxe</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>li_yxe</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>محب موسس نادي الجاليات احمد البربري💛💙</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/2002729561453203456/9mjw63eM_bigger.jpg</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
         <is>
           <t>نسفة الإقلاع🦅
 وأقلعنا مع الصقر❤️‍🔥👏🏻
@@ -2504,63 +2654,63 @@
 @EmiratesNBD_KSA https://t.co/UVb6tMol4M</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>غلطة العمر دخولك على الفن</t>
         </is>
       </c>
-      <c r="K13" t="b">
-        <v>0</v>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
         <is>
           <t>['RotanaLive', 'Turki_alalshikh', 'RabehSaqer', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>17h</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>Mar 23, 2026 · 11:01 AM UTC</t>
         </is>
       </c>
-      <c r="P13" s="2" t="n">
+      <c r="P14" s="2" t="n">
         <v>46104.45902777778</v>
       </c>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>25</v>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>28</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
         <is>
           <t>غلطة العمر دخولك على الفن</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>https://x.com/li_yxe/status/2036035724667974026</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>نسفة الإقلاع🦅
 وأقلعنا مع الصقر❤️‍🔥👏🏻
@@ -2575,7 +2725,7 @@
 @EmiratesNBD_KSA https://t.co/UVb6tMol4M</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>نسفة الإقلاع🦅
 وأقلعنا مع الصقر❤️‍🔥👏🏻
@@ -2590,7 +2740,7 @@
 @EmiratesNBD_KSA https://t.co/UVb6tMol4M</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>Takeoff 🦅  
 And we took off with the falcon ❤️‍🔥👏🏻  
@@ -2599,89 +2749,254 @@
 #Rabeh_Saqer_in_Riyadh</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
+      <c r="AC14" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="AD13" t="inlineStr">
+      <c r="AD14" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="AE13" s="2" t="n">
+      <c r="AE14" s="2" t="n">
         <v>46104.62569444445</v>
       </c>
-      <c r="AF13" t="inlineStr">
+      <c r="AF14" t="inlineStr">
         <is>
           <t>23-03-2026</t>
         </is>
       </c>
-      <c r="AG13" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH13" t="inlineStr">
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AI13" t="inlineStr">
+      <c r="AI14" t="inlineStr">
         <is>
           <t>Takeoff 🦅 And we took off with the falcon ❤️‍🔥👏🏻 #Rotana_Live #Eid_Events #Rabeh_Saqer_in_Riyadh</t>
         </is>
       </c>
-      <c r="AJ13" t="inlineStr">
+      <c r="AJ14" t="inlineStr">
         <is>
           <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AK13" t="n">
+      <c r="AK14" t="n">
         <v>2026</v>
       </c>
-      <c r="AL13" t="inlineStr">
+      <c r="AL14" t="inlineStr">
         <is>
           <t>RotanaLive, Turki_alalshikh, RabehSaqer, GEA_SA, EidSeason, Mabdoarena, EmiratesNBD_KSA</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2036034615769518550</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2036034615769518550</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Emirates NBD</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>What would you do if a delivery agent asks for a ‘small online fee’?
+Stay safe. Stay vigilant. #UnitedAgainstFraud
+https://t.co/YpRWtBZrhq</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>We are so sorry to hear you had an unpleasant experience, please share with us your concern from your registered email address for further communication to social@emiratesnbd.com and tag the case reference number #987474 in the subject line.</t>
+        </is>
+      </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>['Nightowl263']</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Mar 23, 2026 · 10:57 AM UTC</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="n">
+        <v>46104.45625</v>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>37</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>We are so sorry to hear you had an unpleasant experience, please share with us your concern from your registered email address for further communication to social@emiratesnbd.com and tag the case reference number #987474 in the subject line.</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2036034615769518550</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>What would you do if a delivery agent asks for a ‘small online fee’?
+Stay safe. Stay vigilant. #UnitedAgainstFraud
+https://t.co/YpRWtBZrhq</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>What would you do if a delivery agent asks for a ‘small online fee’?
+Stay safe. Stay vigilant. #UnitedAgainstFraud
+https://t.co/YpRWtBZrhq</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>What would you do if a delivery agent asks for a 'small online fee'? 
+Stay safe. Stay vigilant. #UnitedAgainstFraud</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE15" s="2" t="n">
+        <v>46104.62291666667</v>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>23-03-2026</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>What would you do if a delivery agent asks for a 'small online fee'?</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK15" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>Nightowl263</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>2036029459585781847</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>https://x.com/Prahmatic17/status/2036029459585781847</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>https://x.com/Prahmatic17</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Prahmatic17</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>PragmaticWatcher</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/2005896675047403521/VCdF3HFl_bigger.jpg</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
         <is>
           <t>UAE equities — Monday open.
 🔴 #Dubai DFM: -2.5%
@@ -2695,7 +3010,7 @@
 #UAE #DFM #Iran #Markets</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>UAE equities — Monday open.
 🔴 &lt;a href="/search?f=tweets&amp;amp;q=%23Dubai"&gt;#Dubai&lt;/a&gt; DFM: -2.5%
@@ -2709,48 +3024,48 @@
 &lt;a href="/search?f=tweets&amp;amp;q=%23UAE"&gt;#UAE&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23DFM"&gt;#DFM&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Iran"&gt;#Iran&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Markets"&gt;#Markets&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K14" t="b">
-        <v>0</v>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>17h</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>Mar 23, 2026 · 10:37 AM UTC</t>
         </is>
       </c>
-      <c r="P14" s="2" t="n">
+      <c r="P16" s="2" t="n">
         <v>46104.44236111111</v>
       </c>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr">
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
         <is>
           <t>['https://x.com/search?f=tweets&amp;q=%23Dubai', 'https://x.com/search?f=tweets&amp;q=%23UAE', 'https://x.com/search?f=tweets&amp;q=%23DFM', 'https://x.com/search?f=tweets&amp;q=%23Iran', 'https://x.com/search?f=tweets&amp;q=%23Markets']</t>
         </is>
       </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>416</v>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>422</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
         <is>
           <t>UAE equities — Monday open.
 🔴 #Dubai DFM: -2.5%
@@ -2764,12 +3079,12 @@
 #UAE #DFM #Iran #Markets</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>https://x.com/Prahmatic17/status/2036029459585781847</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>UAE equities — Monday open.
 🔴 #Dubai DFM: -2.5%
@@ -2783,7 +3098,7 @@
 #UAE #DFM #Iran #Markets</t>
         </is>
       </c>
-      <c r="AA14" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>UAE equities — Monday open.
 🔴 #Dubai DFM: -2.5%
@@ -2797,7 +3112,7 @@
 #UAE #DFM #Iran #Markets</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>UAE equities — Monday open.  
 🔴 #Dubai DFM: -2.5%  
@@ -2811,89 +3126,89 @@
 #UAE #DFM #Iran #Markets</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
+      <c r="AC16" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="AD14" t="inlineStr">
+      <c r="AD16" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="AE14" s="2" t="n">
+      <c r="AE16" s="2" t="n">
         <v>46104.60902777778</v>
       </c>
-      <c r="AF14" t="inlineStr">
+      <c r="AF16" t="inlineStr">
         <is>
           <t>23-03-2026</t>
         </is>
       </c>
-      <c r="AG14" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH14" t="inlineStr">
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AI14" t="inlineStr">
+      <c r="AI16" t="inlineStr">
         <is>
           <t>🔴 #Dubai DFM: -2.5% 🔴 Emaar: -4.9% 🔴 Emirates NBD: -1.7% 🔴 Abu Dhabi: -0.2% 🔴 Qatar: -1.2% 🔴 Kuwait: -0.4% Iran: “If you hit electricity — we hit electricity.” Markets believed them. • UAE equities — Monday open.</t>
         </is>
       </c>
-      <c r="AJ14" t="inlineStr">
+      <c r="AJ16" t="inlineStr">
         <is>
           <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AK14" t="n">
+      <c r="AK16" t="n">
         <v>2026</v>
       </c>
-      <c r="AL14" t="inlineStr">
+      <c r="AL16" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>2036024666901668316</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>https://x.com/coolmomdxb/status/2036024666901668316</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>https://x.com/coolmomdxb</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>coolmomdxb</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Anuradha</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1576510705481678850/3vJsydFv_bigger.jpg</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
         <is>
           <t>حل اللغز واربح 10,000 درهم.💰
 أم علاوي تعبت من مشاكل السيارة، ومستعدة لسيارة جديدة بفضل قرض السيارات السريع من بنك الإمارات دبي الوطني، من خلال طلب سهل وسريع عبر الإنترنت.
@@ -2902,67 +3217,67 @@
 حل اللغز لفرصة الفوز بـ 10 آلاف درهم. https://t.co/NBQE3PzfgZ</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>1.89% &lt;a href="/fatema_painter" title="FATEMA"&gt;@fatema_painter&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/Harshabhatia2" title="Harsha bhatia"&gt;@Harshabhatia2&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K15" t="b">
-        <v>0</v>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
+      <c r="K17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>17h</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>19h</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
         <is>
           <t>Mar 23, 2026 · 10:18 AM UTC</t>
         </is>
       </c>
-      <c r="P15" s="2" t="n">
+      <c r="P17" s="2" t="n">
         <v>46104.42916666667</v>
       </c>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr">
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
         <is>
           <t>['https://x.com/fatema_painter', 'https://x.com/SelmaRomola', 'https://x.com/Harshabhatia2']</t>
         </is>
       </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>12</v>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>14</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
         <is>
           <t>1.89% @fatema_painter @SelmaRomola @Harshabhatia2</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>https://x.com/coolmomdxb/status/2036024666901668316</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>حل اللغز واربح 10,000 درهم.💰
 أم علاوي تعبت من مشاكل السيارة، ومستعدة لسيارة جديدة بفضل قرض السيارات السريع من بنك الإمارات دبي الوطني، من خلال طلب سهل وسريع عبر الإنترنت.
@@ -2971,7 +3286,7 @@
 حل اللغز لفرصة الفوز بـ 10 آلاف درهم. https://t.co/NBQE3PzfgZ</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>حل اللغز واربح 10,000 درهم.💰
 أم علاوي تعبت من مشاكل السيارة، ومستعدة لسيارة جديدة بفضل قرض السيارات السريع من بنك الإمارات دبي الوطني، من خلال طلب سهل وسريع عبر الإنترنت.
@@ -2980,7 +3295,7 @@
 حل اللغز لفرصة الفوز بـ 10 آلاف درهم. https://t.co/NBQE3PzfgZ</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>Solve the puzzle and win 10,000 dirhams.💰 Um Alawi is tired of car problems and is ready for a new car thanks to the quick car loan from Emirates NBD, through an easy and fast online application. 
 Follow @EmiratesNBD_ae 
@@ -2988,243 +3303,243 @@
 Solve the puzzle for a chance to win 10,000 dirhams. https://t.co/NBQE3PzfgZ</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
+      <c r="AC17" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr">
+      <c r="AD17" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="AE15" s="2" t="n">
+      <c r="AE17" s="2" t="n">
         <v>46104.59583333333</v>
       </c>
-      <c r="AF15" t="inlineStr">
+      <c r="AF17" t="inlineStr">
         <is>
           <t>23-03-2026</t>
         </is>
       </c>
-      <c r="AG15" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH15" t="inlineStr">
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AI15" t="inlineStr">
+      <c r="AI17" t="inlineStr">
         <is>
           <t>Solve the puzzle and win 10,000 dirhams.💰 Um Alawi is tired of car problems and is ready for a new car thanks to the quick car loan from Emirates NBD, through an easy and fast online application. • Follow @EmiratesNBD_ae Tag 3 of your friends Solve the puzzle for a chance to win 10,000 dirhams.</t>
         </is>
       </c>
-      <c r="AJ15" t="inlineStr">
+      <c r="AJ17" t="inlineStr">
         <is>
           <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AK15" t="n">
+      <c r="AK17" t="n">
         <v>2026</v>
       </c>
-      <c r="AL15" t="inlineStr">
+      <c r="AL17" t="inlineStr">
         <is>
           <t>EmiratesNBD_AE</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
         <is>
           <t>2035964468413493475</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>https://x.com/Mr__Krabs___/status/2035964468413493475</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>https://x.com/Mr__Krabs___</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Mr__Krabs___</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Eugene H Krabs</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1439693335644487683/C-FPyRyf_bigger.jpg</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
         <is>
           <t>Operation epic bimbo has been closed for a small profit; too many significant threats to GCC key infrastructure and honestly had thought this would be wrap</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Operation epic bimbo has been closed for a small profit; too many significant threats to GCC key infrastructure and honestly had thought this would be wrap</t>
         </is>
       </c>
-      <c r="K16" t="b">
-        <v>0</v>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>21h</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
         <is>
           <t>Mar 23, 2026 · 6:18 AM UTC</t>
         </is>
       </c>
-      <c r="P16" s="2" t="n">
+      <c r="P18" s="2" t="n">
         <v>46104.2625</v>
       </c>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>98</v>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>99</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
         <is>
           <t>Operation epic bimbo has been closed for a small profit; too many significant threats to GCC key infrastructure and honestly had thought this would be wrap</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>https://x.com/Mr__Krabs___/status/2035964468413493475</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>Operation epic bimbo has been closed for a small profit; too many significant threats to GCC key infrastructure and honestly had thought this would be wrap</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>Operation epic bimbo has been closed for a small profit; too many significant threats to GCC key infrastructure and honestly had thought this would be wrap</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>Operation epic bimbo has been closed for a small profit; there were too many significant threats to GCC key infrastructure, and I honestly thought this would be a wrap.</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
+      <c r="AC18" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="AD16" t="inlineStr">
+      <c r="AD18" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="AE16" s="2" t="n">
+      <c r="AE18" s="2" t="n">
         <v>46104.42916666667</v>
       </c>
-      <c r="AF16" t="inlineStr">
+      <c r="AF18" t="inlineStr">
         <is>
           <t>23-03-2026</t>
         </is>
       </c>
-      <c r="AG16" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH16" t="inlineStr">
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AI16" t="inlineStr">
+      <c r="AI18" t="inlineStr">
         <is>
           <t>Operation epic bimbo has been closed for a small profit; there were too many significant threats to GCC key infrastructure, and I honestly thought this would be a wrap.</t>
         </is>
       </c>
-      <c r="AJ16" t="inlineStr">
+      <c r="AJ18" t="inlineStr">
         <is>
           <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AK16" t="n">
+      <c r="AK18" t="n">
         <v>2026</v>
       </c>
-      <c r="AL16" t="inlineStr">
+      <c r="AL18" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
         <is>
           <t>2035957508989444417</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>https://x.com/parulghalout/status/2035957508989444417</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>https://x.com/parulghalout</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>parulghalout</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>parul ghalout</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/589412760515031040/ehckyrV3_bigger.jpg</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
         <is>
           <t>حلّ فزورة رمضان واربح 10,000 درهم.
 من توزيع الوجبات، إلى دعم العاملين وقضاء الوقت مع كبار المواطنين، يجمع برنامج واحد كل ذلك تحت مظلًة واحدة.
@@ -3235,67 +3550,67 @@
 3.اكتب إجابتك في التعليقات أدناه https://t.co/aADoQF5a2E</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>Exchanger volunteer program &lt;a href="/skrana111" title="sandeep kumar"&gt;@skrana111&lt;/a&gt; &lt;a href="/krahman_4" title="Kinza Rehman"&gt;@krahman_4&lt;/a&gt; &lt;a href="/Shilpa4669" title="Shilpa Jain"&gt;@Shilpa4669&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K17" t="b">
-        <v>0</v>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
+      <c r="K19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>22h</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>23h</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
         <is>
           <t>Mar 23, 2026 · 5:51 AM UTC</t>
         </is>
       </c>
-      <c r="P17" s="2" t="n">
+      <c r="P19" s="2" t="n">
         <v>46104.24375</v>
       </c>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr">
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
         <is>
           <t>['https://x.com/skrana111', 'https://x.com/krahman_4', 'https://x.com/Shilpa4669']</t>
         </is>
       </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>15</v>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>17</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
         <is>
           <t>Exchanger volunteer program @skrana111 @krahman_4 @Shilpa4669</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>https://x.com/parulghalout/status/2035957508989444417</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>حلّ فزورة رمضان واربح 10,000 درهم.
 من توزيع الوجبات، إلى دعم العاملين وقضاء الوقت مع كبار المواطنين، يجمع برنامج واحد كل ذلك تحت مظلًة واحدة.
@@ -3306,7 +3621,7 @@
 3.اكتب إجابتك في التعليقات أدناه https://t.co/aADoQF5a2E</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AA19" t="inlineStr">
         <is>
           <t>حلّ فزورة رمضان واربح 10,000 درهم.
 من توزيع الوجبات، إلى دعم العاملين وقضاء الوقت مع كبار المواطنين، يجمع برنامج واحد كل ذلك تحت مظلًة واحدة.
@@ -3317,10 +3632,10 @@
 3.اكتب إجابتك في التعليقات أدناه https://t.co/aADoQF5a2E</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>Solve the Ramadan riddle and win 10,000 dirhams.
-From meal distribution to supporting workers and spending time with senior citizens, one program brings all of this together under one umbrella.
+From meal distribution to supporting workers and spending time with senior citizens, one program brings all of that under one umbrella.
 What is the name of this program?
 To participate:
 1. Follow the Emirates NBD account
@@ -3328,89 +3643,89 @@
 3. Write your answer in the comments below</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
+      <c r="AC19" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="AD17" t="inlineStr">
+      <c r="AD19" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="AE17" s="2" t="n">
+      <c r="AE19" s="2" t="n">
         <v>46104.41041666667</v>
       </c>
-      <c r="AF17" t="inlineStr">
+      <c r="AF19" t="inlineStr">
         <is>
           <t>23-03-2026</t>
         </is>
       </c>
-      <c r="AG17" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH17" t="inlineStr">
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>From meal distribution to supporting workers and spending time with senior citizens, one program brings all of this together under one umbrella. • Solve the Ramadan riddle and win 10,000 dirhams. • Follow the Emirates NBD account 2.</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>From meal distribution to supporting workers and spending time with senior citizens, one program brings all of that under one umbrella. • Solve the Ramadan riddle and win 10,000 dirhams. • Follow the Emirates NBD account 2.</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
         <is>
           <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AK17" t="n">
+      <c r="AK19" t="n">
         <v>2026</v>
       </c>
-      <c r="AL17" t="inlineStr">
+      <c r="AL19" t="inlineStr">
         <is>
           <t>EmiratesNBD_AE</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
         <is>
           <t>2035957290990498203</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>https://x.com/parulghalout/status/2035957290990498203</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>https://x.com/parulghalout</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>parulghalout</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>parul ghalout</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/589412760515031040/ehckyrV3_bigger.jpg</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
         <is>
           <t>Make Eid surprises even more valuable.
 From silver to gold, discover a smarter way to own or gift something truly precious.
@@ -3422,67 +3737,67 @@
 Drop your answer below for a chance to win AED 10,000</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>Via the ENBD X Mobile App.  &lt;a href="/Shilpa4669" title="Shilpa Jain"&gt;@Shilpa4669&lt;/a&gt; &lt;a href="/mnsadiq84" title="naveed sadiq"&gt;@mnsadiq84&lt;/a&gt; &lt;a href="/FazilAnas" title="Tosifmuhammad 🇦🇪"&gt;@FazilAnas&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K18" t="b">
-        <v>0</v>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>22h</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>23h</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
         <is>
           <t>Mar 23, 2026 · 5:50 AM UTC</t>
         </is>
       </c>
-      <c r="P18" s="2" t="n">
+      <c r="P20" s="2" t="n">
         <v>46104.24305555555</v>
       </c>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr">
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
         <is>
           <t>['https://x.com/Shilpa4669', 'https://x.com/mnsadiq84', 'https://x.com/FazilAnas']</t>
         </is>
       </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>25</v>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>27</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
         <is>
           <t>Via the ENBD X Mobile App.  @Shilpa4669 @mnsadiq84 @FazilAnas</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>https://x.com/parulghalout/status/2035957290990498203</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>Make Eid surprises even more valuable.
 From silver to gold, discover a smarter way to own or gift something truly precious.
@@ -3494,7 +3809,7 @@
 Drop your answer below for a chance to win AED 10,000</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr">
+      <c r="AA20" t="inlineStr">
         <is>
           <t>Make Eid surprises even more valuable.
 From silver to gold, discover a smarter way to own or gift something truly precious.
@@ -3506,366 +3821,42 @@
 Drop your answer below for a chance to win AED 10,000</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
+      <c r="AB20" t="inlineStr">
         <is>
           <t>Make Eid surprises even more valuable. From silver to gold, discover a smarter way to own or gift something truly precious. Watch this episode and tell us: How can you buy gold and silver from the bank? To participate: Follow Emirates NBD Tag 3 friends Drop your answer below for a chance to win AED 10,000</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
+      <c r="AC20" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="AD18" t="inlineStr">
+      <c r="AD20" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="AE18" s="2" t="n">
+      <c r="AE20" s="2" t="n">
         <v>46104.40972222222</v>
       </c>
-      <c r="AF18" t="inlineStr">
+      <c r="AF20" t="inlineStr">
         <is>
           <t>23-03-2026</t>
         </is>
       </c>
-      <c r="AG18" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH18" t="inlineStr">
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AI18" t="inlineStr">
+      <c r="AI20" t="inlineStr">
         <is>
           <t>To participate: Follow Emirates NBD Tag 3 friends Drop your answer below for a chance to win AED 10,000 • From silver to gold, discover a smarter way to own or gift something truly precious. • Watch this episode and tell us: How can you buy gold and silver from the bank?</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AK18" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>EmiratesNBD_AE</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2035957091601657909</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2035957091601657909</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Sosomostafa729S</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Soha.mostafa77</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE B- 1.89% @Emy191990 @parulghalout @Salma2232019</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>B- 1.89% &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K19" t="b">
-        <v>0</v>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>22h</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>Mar 23, 2026 · 5:49 AM UTC</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="n">
-        <v>46104.24236111111</v>
-      </c>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/parulghalout', 'https://x.com/Salma2232019']</t>
-        </is>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>19</v>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>B- 1.89% @Emy191990 @parulghalout @Salma2232019</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2035957091601657909</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE B- 1.89% @Emy191990 @parulghalout @Salma2232019</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE B- 1.89% @Emy191990 @parulghalout @Salma2232019</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>The text appears to be a social media post or message that includes a percentage and usernames, rather than a coherent sentence in a specific language. Therefore, there is no translation needed as it does not contain translatable content.</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AE19" s="2" t="n">
-        <v>46104.40902777778</v>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>23-03-2026</t>
-        </is>
-      </c>
-      <c r="AG19" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>The text appears to be a social media post or message that includes a percentage and usernames, rather than a coherent sentence in a specific language. • Therefore, there is no translation needed as it does not contain translatable content.</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AK19" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>EmiratesNBD_AE</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2035956997238165721</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956997238165721</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Sosomostafa729S</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Soha.mostafa77</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE B- 1.89% @ibushra_03 @parulghalout @Salma2232019</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>B- 1.89% &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>22h</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>Mar 23, 2026 · 5:49 AM UTC</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="n">
-        <v>46104.24236111111</v>
-      </c>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>['https://x.com/ibushra_03', 'https://x.com/parulghalout', 'https://x.com/Salma2232019']</t>
-        </is>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>19</v>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>B- 1.89% @ibushra_03 @parulghalout @Salma2232019</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956997238165721</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE B- 1.89% @ibushra_03 @parulghalout @Salma2232019</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE B- 1.89% @ibushra_03 @parulghalout @Salma2232019</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>The text appears to be a social media post or message that includes a reference to a financial figure (B- 1.89%) and mentions of users or accounts. There is no translatable content in terms of language, as it primarily consists of usernames and a percentage. Therefore, there is no translation to provide.</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AE20" s="2" t="n">
-        <v>46104.40902777778</v>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>23-03-2026</t>
-        </is>
-      </c>
-      <c r="AG20" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>The text appears to be a social media post or message that includes a reference to a financial figure (B- 1.89%) and mentions of users or accounts. • There is no translatable content in terms of language, as it primarily consists of usernames and a percentage. • Therefore, there is no translation to provide.</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3888,12 +3879,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2035956939956642179</t>
+          <t>2035957091601657909</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956939956642179</t>
+          <t>https://x.com/Sosomostafa729S/status/2035957091601657909</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3919,12 +3910,12 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE B- 1.89% @semeet @SelmaRomola @Emy191990</t>
+          <t>B- 1.89% @Emy191990 @parulghalout @Salma2232019</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>B- 1.89% &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt;</t>
+          <t>B- 1.89% &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K21" t="b">
@@ -3938,21 +3929,21 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Mar 23, 2026 · 5:48 AM UTC</t>
+          <t>Mar 23, 2026 · 5:49 AM UTC</t>
         </is>
       </c>
       <c r="P21" s="2" t="n">
-        <v>46104.24166666667</v>
+        <v>46104.24236111111</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
         <is>
-          <t>['https://x.com/semeet', 'https://x.com/SelmaRomola', 'https://x.com/Emy191990']</t>
+          <t>['https://x.com/Emy191990', 'https://x.com/parulghalout', 'https://x.com/Salma2232019']</t>
         </is>
       </c>
       <c r="S21" t="n">
@@ -3965,7 +3956,7 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
@@ -3974,27 +3965,19 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>B- 1.89% @semeet @SelmaRomola @Emy191990</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956939956642179</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE B- 1.89% @semeet @SelmaRomola @Emy191990</t>
-        </is>
-      </c>
+          <t>B- 1.89% @Emy191990 @parulghalout @Salma2232019</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE B- 1.89% @semeet @SelmaRomola @Emy191990</t>
+          <t>B- 1.89% @Emy191990 @parulghalout @Salma2232019</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>The text appears to be in English and does not require translation.</t>
+          <t>B- 1.89% @Emy191990 @parulghalout @Salma2232019</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -4008,7 +3991,7 @@
         </is>
       </c>
       <c r="AE21" s="2" t="n">
-        <v>46104.40833333333</v>
+        <v>46104.40902777778</v>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
@@ -4027,7 +4010,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>The text appears to be in English and does not require translation.</t>
+          <t>B- 1.89% @Emy191990 @parulghalout @Salma2232019</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -4050,12 +4033,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2035956878518460827</t>
+          <t>2035956997238165721</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956878518460827</t>
+          <t>https://x.com/Sosomostafa729S/status/2035956997238165721</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4081,12 +4064,12 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE B- 1.89% @Emy191990 @parulghalout @SelmaRomola</t>
+          <t>@EmiratesNBD_AE B- 1.89% @ibushra_03 @parulghalout @Salma2232019</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>B- 1.89% &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt;</t>
+          <t>B- 1.89% &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K22" t="b">
@@ -4100,21 +4083,21 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Mar 23, 2026 · 5:48 AM UTC</t>
+          <t>Mar 23, 2026 · 5:49 AM UTC</t>
         </is>
       </c>
       <c r="P22" s="2" t="n">
-        <v>46104.24166666667</v>
+        <v>46104.24236111111</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/parulghalout', 'https://x.com/SelmaRomola']</t>
+          <t>['https://x.com/ibushra_03', 'https://x.com/parulghalout', 'https://x.com/Salma2232019']</t>
         </is>
       </c>
       <c r="S22" t="n">
@@ -4127,7 +4110,7 @@
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -4136,27 +4119,27 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>B- 1.89% @Emy191990 @parulghalout @SelmaRomola</t>
+          <t>B- 1.89% @ibushra_03 @parulghalout @Salma2232019</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956878518460827</t>
+          <t>https://x.com/Sosomostafa729S/status/2035956997238165721</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE B- 1.89% @Emy191990 @parulghalout @SelmaRomola</t>
+          <t>@EmiratesNBD_AE B- 1.89% @ibushra_03 @parulghalout @Salma2232019</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE B- 1.89% @Emy191990 @parulghalout @SelmaRomola</t>
+          <t>@EmiratesNBD_AE B- 1.89% @ibushra_03 @parulghalout @Salma2232019</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>The text appears to be a social media post or message that includes a reference to a financial figure (B- 1.89%) and mentions of users or accounts. There is no translatable content in terms of language, as it primarily consists of usernames and a percentage.</t>
+          <t>The text appears to be a social media post or message that includes a percentage and mentions of users. There is no translatable content in terms of language, as it primarily consists of usernames and a numerical value. Therefore, there is no translation to provide.</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -4170,7 +4153,7 @@
         </is>
       </c>
       <c r="AE22" s="2" t="n">
-        <v>46104.40833333333</v>
+        <v>46104.40902777778</v>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
@@ -4189,7 +4172,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>The text appears to be a social media post or message that includes a reference to a financial figure (B- 1.89%) and mentions of users or accounts. • There is no translatable content in terms of language, as it primarily consists of usernames and a percentage.</t>
+          <t>There is no translatable content in terms of language, as it primarily consists of usernames and a numerical value. • The text appears to be a social media post or message that includes a percentage and mentions of users. • Therefore, there is no translation to provide.</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
@@ -4212,12 +4195,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2035956707604705316</t>
+          <t>2035956939956642179</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956707604705316</t>
+          <t>https://x.com/Sosomostafa729S/status/2035956939956642179</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4243,12 +4226,12 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @parulghalout @semeet @SelmaRomola</t>
+          <t>@EmiratesNBD_AE B- 1.89% @semeet @SelmaRomola @Emy191990</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt;</t>
+          <t>B- 1.89% &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K23" t="b">
@@ -4262,21 +4245,21 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Mar 23, 2026 · 5:47 AM UTC</t>
+          <t>Mar 23, 2026 · 5:48 AM UTC</t>
         </is>
       </c>
       <c r="P23" s="2" t="n">
-        <v>46104.24097222222</v>
+        <v>46104.24166666667</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
         <is>
-          <t>['https://x.com/parulghalout', 'https://x.com/semeet', 'https://x.com/SelmaRomola']</t>
+          <t>['https://x.com/semeet', 'https://x.com/SelmaRomola', 'https://x.com/Emy191990']</t>
         </is>
       </c>
       <c r="S23" t="n">
@@ -4289,7 +4272,7 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -4298,27 +4281,27 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program @parulghalout @semeet @SelmaRomola</t>
+          <t>B- 1.89% @semeet @SelmaRomola @Emy191990</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956707604705316</t>
+          <t>https://x.com/Sosomostafa729S/status/2035956939956642179</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @parulghalout @semeet @SelmaRomola</t>
+          <t>@EmiratesNBD_AE B- 1.89% @semeet @SelmaRomola @Emy191990</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @parulghalout @semeet @SelmaRomola</t>
+          <t>@EmiratesNBD_AE B- 1.89% @semeet @SelmaRomola @Emy191990</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Emirates NBD_AE Exchanger volunteer program</t>
+          <t>The text appears to be in English and does not require translation.</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -4332,7 +4315,7 @@
         </is>
       </c>
       <c r="AE23" s="2" t="n">
-        <v>46104.40763888889</v>
+        <v>46104.40833333333</v>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
@@ -4351,7 +4334,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Emirates NBD_AE Exchanger volunteer program</t>
+          <t>The text appears to be in English and does not require translation.</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -4374,43 +4357,43 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2035956681939828984</t>
+          <t>2035956878518460827</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://x.com/parulghalout/status/2035956681939828984</t>
+          <t>https://x.com/Sosomostafa729S/status/2035956878518460827</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://x.com/parulghalout</t>
+          <t>https://x.com/Sosomostafa729S</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>parulghalout</t>
+          <t>Sosomostafa729S</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>parul ghalout</t>
+          <t>Soha.mostafa77</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/589412760515031040/ehckyrV3_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE B. 1.89%  @skrana111 @sehar_beg @semeet</t>
+          <t>@EmiratesNBD_AE B- 1.89% @Emy191990 @parulghalout @SelmaRomola</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>B. 1.89%  &lt;a href="/skrana111" title="sandeep kumar"&gt;@skrana111&lt;/a&gt; &lt;a href="/sehar_beg" title="Sehar Umar Beg"&gt;@sehar_beg&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt;</t>
+          <t>B- 1.89% &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K24" t="b">
@@ -4424,21 +4407,21 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Mar 23, 2026 · 5:47 AM UTC</t>
+          <t>Mar 23, 2026 · 5:48 AM UTC</t>
         </is>
       </c>
       <c r="P24" s="2" t="n">
-        <v>46104.24097222222</v>
+        <v>46104.24166666667</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
-          <t>['https://x.com/skrana111', 'https://x.com/sehar_beg', 'https://x.com/semeet']</t>
+          <t>['https://x.com/Emy191990', 'https://x.com/parulghalout', 'https://x.com/SelmaRomola']</t>
         </is>
       </c>
       <c r="S24" t="n">
@@ -4451,7 +4434,7 @@
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
@@ -4460,27 +4443,27 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>B. 1.89%  @skrana111 @sehar_beg @semeet</t>
+          <t>B- 1.89% @Emy191990 @parulghalout @SelmaRomola</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>https://x.com/parulghalout/status/2035956681939828984</t>
+          <t>https://x.com/Sosomostafa729S/status/2035956878518460827</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE B. 1.89%  @skrana111 @sehar_beg @semeet</t>
+          <t>@EmiratesNBD_AE B- 1.89% @Emy191990 @parulghalout @SelmaRomola</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE B. 1.89%  @skrana111 @sehar_beg @semeet</t>
+          <t>@EmiratesNBD_AE B- 1.89% @Emy191990 @parulghalout @SelmaRomola</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>The text appears to be in English and does not require translation.</t>
+          <t>The text appears to be a social media post or message that includes usernames and a percentage. There is no translatable content in a different language.</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -4494,7 +4477,7 @@
         </is>
       </c>
       <c r="AE24" s="2" t="n">
-        <v>46104.40763888889</v>
+        <v>46104.40833333333</v>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
@@ -4513,7 +4496,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>The text appears to be in English and does not require translation.</t>
+          <t>The text appears to be a social media post or message that includes usernames and a percentage. • There is no translatable content in a different language.</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -4536,12 +4519,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2035956637853421634</t>
+          <t>2035956707604705316</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956637853421634</t>
+          <t>https://x.com/Sosomostafa729S/status/2035956707604705316</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4567,12 +4550,12 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @ibushra_03 @Salma2232019</t>
+          <t>@EmiratesNBD_AE Exchanger volunteer program @parulghalout @semeet @SelmaRomola</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
+          <t>Exchanger volunteer program &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K25" t="b">
@@ -4586,7 +4569,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -4600,7 +4583,7 @@
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
         <is>
-          <t>['https://x.com/semeet', 'https://x.com/ibushra_03', 'https://x.com/Salma2232019']</t>
+          <t>['https://x.com/parulghalout', 'https://x.com/semeet', 'https://x.com/SelmaRomola']</t>
         </is>
       </c>
       <c r="S25" t="n">
@@ -4613,7 +4596,7 @@
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -4622,22 +4605,22 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program @semeet @ibushra_03 @Salma2232019</t>
+          <t>Exchanger volunteer program @parulghalout @semeet @SelmaRomola</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956637853421634</t>
+          <t>https://x.com/Sosomostafa729S/status/2035956707604705316</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @ibushra_03 @Salma2232019</t>
+          <t>@EmiratesNBD_AE Exchanger volunteer program @parulghalout @semeet @SelmaRomola</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @ibushra_03 @Salma2232019</t>
+          <t>@EmiratesNBD_AE Exchanger volunteer program @parulghalout @semeet @SelmaRomola</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -4698,43 +4681,43 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2035956572711710976</t>
+          <t>2035956681939828984</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956572711710976</t>
+          <t>https://x.com/parulghalout/status/2035956681939828984</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S</t>
+          <t>https://x.com/parulghalout</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sosomostafa729S</t>
+          <t>parulghalout</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Soha.mostafa77</t>
+          <t>parul ghalout</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/589412760515031040/ehckyrV3_bigger.jpg</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @Emy191990 @Salma2232019 @SelmaRomola</t>
+          <t>@EmiratesNBD_AE B. 1.89%  @skrana111 @sehar_beg @semeet</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt;</t>
+          <t>B. 1.89%  &lt;a href="/skrana111" title="sandeep kumar"&gt;@skrana111&lt;/a&gt; &lt;a href="/sehar_beg" title="Sehar Umar Beg"&gt;@sehar_beg&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K26" t="b">
@@ -4748,7 +4731,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -4762,7 +4745,7 @@
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
         <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/Salma2232019', 'https://x.com/SelmaRomola']</t>
+          <t>['https://x.com/skrana111', 'https://x.com/sehar_beg', 'https://x.com/semeet']</t>
         </is>
       </c>
       <c r="S26" t="n">
@@ -4775,7 +4758,7 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
@@ -4784,27 +4767,27 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program @Emy191990 @Salma2232019 @SelmaRomola</t>
+          <t>B. 1.89%  @skrana111 @sehar_beg @semeet</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956572711710976</t>
+          <t>https://x.com/parulghalout/status/2035956681939828984</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @Emy191990 @Salma2232019 @SelmaRomola</t>
+          <t>@EmiratesNBD_AE B. 1.89%  @skrana111 @sehar_beg @semeet</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @Emy191990 @Salma2232019 @SelmaRomola</t>
+          <t>@EmiratesNBD_AE B. 1.89%  @skrana111 @sehar_beg @semeet</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Emirates NBD AE Exchanger volunteer program</t>
+          <t>The text appears to be in English and does not require translation.</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -4837,7 +4820,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Emirates NBD AE Exchanger volunteer program</t>
+          <t>The text appears to be in English and does not require translation.</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -4860,12 +4843,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2035956477169631536</t>
+          <t>2035956637853421634</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956477169631536</t>
+          <t>https://x.com/Sosomostafa729S/status/2035956637853421634</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4891,12 +4874,12 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @Salma2232019 @Emy191990 @parulghalout</t>
+          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @ibushra_03 @Salma2232019</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt;</t>
+          <t>Exchanger volunteer program &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K27" t="b">
@@ -4910,7 +4893,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -4924,7 +4907,7 @@
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
         <is>
-          <t>['https://x.com/Salma2232019', 'https://x.com/Emy191990', 'https://x.com/parulghalout']</t>
+          <t>['https://x.com/semeet', 'https://x.com/ibushra_03', 'https://x.com/Salma2232019']</t>
         </is>
       </c>
       <c r="S27" t="n">
@@ -4937,7 +4920,7 @@
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
@@ -4946,27 +4929,27 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program @Salma2232019 @Emy191990 @parulghalout</t>
+          <t>Exchanger volunteer program @semeet @ibushra_03 @Salma2232019</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956477169631536</t>
+          <t>https://x.com/Sosomostafa729S/status/2035956637853421634</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @Salma2232019 @Emy191990 @parulghalout</t>
+          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @ibushra_03 @Salma2232019</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @Salma2232019 @Emy191990 @parulghalout</t>
+          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @ibushra_03 @Salma2232019</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Emirates NBD_AE Exchanger volunteer program Salma2232019 Emy191990 parulghalout</t>
+          <t>Emirates NBD AE Exchanger volunteer program</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4999,7 +4982,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Emirates NBD_AE Exchanger volunteer program Salma2232019 Emy191990 parulghalout</t>
+          <t>Emirates NBD AE Exchanger volunteer program</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -5022,36 +5005,352 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2035956416520069280</t>
+          <t>2035956572711710976</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://x.com/parulghalout/status/2035956416520069280</t>
+          <t>https://x.com/Sosomostafa729S/status/2035956572711710976</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://x.com/parulghalout</t>
+          <t>https://x.com/Sosomostafa729S</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>parulghalout</t>
+          <t>Sosomostafa729S</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>parul ghalout</t>
+          <t>Soha.mostafa77</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/589412760515031040/ehckyrV3_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
+        <is>
+          <t>Exchanger volunteer program @Emy191990 @Salma2232019 @SelmaRomola</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Exchanger volunteer program &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K28" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>23h</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Mar 23, 2026 · 5:47 AM UTC</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="n">
+        <v>46104.24097222222</v>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>['https://x.com/Emy191990', 'https://x.com/Salma2232019', 'https://x.com/SelmaRomola']</t>
+        </is>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>19</v>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Exchanger volunteer program @Emy191990 @Salma2232019 @SelmaRomola</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>Exchanger volunteer program @Emy191990 @Salma2232019 @SelmaRomola</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>Exchanger volunteer program</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE28" s="2" t="n">
+        <v>46104.40763888889</v>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>23-03-2026</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Exchanger volunteer program</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK28" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2035956477169631536</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2035956477169631536</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Exchanger volunteer program @Salma2232019 @Emy191990 @parulghalout</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Exchanger volunteer program &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K29" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>23h</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Mar 23, 2026 · 5:47 AM UTC</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="n">
+        <v>46104.24097222222</v>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>['https://x.com/Salma2232019', 'https://x.com/Emy191990', 'https://x.com/parulghalout']</t>
+        </is>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>16</v>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Exchanger volunteer program @Salma2232019 @Emy191990 @parulghalout</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2035956477169631536</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Exchanger volunteer program @Salma2232019 @Emy191990 @parulghalout</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Exchanger volunteer program @Salma2232019 @Emy191990 @parulghalout</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>Emirates NBD AE Exchanger volunteer program Salma2232019 Emy191990 parulghalout</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE29" s="2" t="n">
+        <v>46104.40763888889</v>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>23-03-2026</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Emirates NBD AE Exchanger volunteer program Salma2232019 Emy191990 parulghalout</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK29" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2035956416520069280</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://x.com/parulghalout/status/2035956416520069280</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://x.com/parulghalout</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>parulghalout</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>parul ghalout</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/589412760515031040/ehckyrV3_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
         <is>
           <t>نفذت أموال أم خماس قبل نهاية الشهر.
 هناك قاعدة بسيطة تُساعدها على إدارة أموالها بحكمة:
@@ -5078,67 +5377,67 @@
 - Drop your answer below for a chance to win AED 10,000</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>FINEELL ( Financial Well-being program) with Emirates NBD  &lt;a href="/mnsadiq84" title="naveed sadiq"&gt;@mnsadiq84&lt;/a&gt; &lt;a href="/skrana111" title="sandeep kumar"&gt;@skrana111&lt;/a&gt; &lt;a href="/dxb_sknj" title="dxb_sknj"&gt;@dxb_sknj&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K28" t="b">
-        <v>0</v>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
+      <c r="K30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>22h</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>23h</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
         <is>
           <t>Mar 23, 2026 · 5:46 AM UTC</t>
         </is>
       </c>
-      <c r="P28" s="2" t="n">
+      <c r="P30" s="2" t="n">
         <v>46104.24027777778</v>
       </c>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr">
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
         <is>
           <t>['https://x.com/mnsadiq84', 'https://x.com/skrana111', 'https://x.com/dxb_sknj']</t>
         </is>
       </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>18</v>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>19</v>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
         <is>
           <t>FINEELL ( Financial Well-being program) with Emirates NBD  @mnsadiq84 @skrana111 @dxb_sknj</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>https://x.com/parulghalout/status/2035956416520069280</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>نفذت أموال أم خماس قبل نهاية الشهر.
 هناك قاعدة بسيطة تُساعدها على إدارة أموالها بحكمة:
@@ -5165,7 +5464,7 @@
 - Drop your answer below for a chance to win AED 10,000</t>
         </is>
       </c>
-      <c r="AA28" t="inlineStr">
+      <c r="AA30" t="inlineStr">
         <is>
           <t>نفذت أموال أم خماس قبل نهاية الشهر.
 هناك قاعدة بسيطة تُساعدها على إدارة أموالها بحكمة:
@@ -5192,7 +5491,7 @@
 - Drop your answer below for a chance to win AED 10,000</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
+      <c r="AB30" t="inlineStr">
         <is>
           <t>Um Khammas ran out of cash before the month ended.
 A simple rule can help her stay on track:
@@ -5208,338 +5507,14 @@
 - Drop your answer below for a chance to win AED 10,000</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
+      <c r="AC30" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="AD28" t="inlineStr">
+      <c r="AD30" t="inlineStr">
         <is>
           <t>Positive</t>
-        </is>
-      </c>
-      <c r="AE28" s="2" t="n">
-        <v>46104.40694444445</v>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>23-03-2026</t>
-        </is>
-      </c>
-      <c r="AG28" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>A simple rule can help her stay on track: 50% for needs 30% for wants 20% for savings A smart plan that helps you spend, save, and stay in control. • To participate: - Follow Emirates NBD - Tag 3 friends - Drop your answer below for a chance to win AED 10,000 • This is one of the many tips that the bank’s program has in store.</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AK28" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL28" t="inlineStr">
-        <is>
-          <t>EmiratesNBD_AE</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2035956407212925393</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956407212925393</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Sosomostafa729S</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Soha.mostafa77</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @SelmaRomola @ibushra_03</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Exchanger volunteer program &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K29" t="b">
-        <v>0</v>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>22h</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>Mar 23, 2026 · 5:46 AM UTC</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="n">
-        <v>46104.24027777778</v>
-      </c>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>['https://x.com/semeet', 'https://x.com/SelmaRomola', 'https://x.com/ibushra_03']</t>
-        </is>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>13</v>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>Exchanger volunteer program @semeet @SelmaRomola @ibushra_03</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956407212925393</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @SelmaRomola @ibushra_03</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @SelmaRomola @ibushra_03</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>Emirates NBD_AE Exchanger volunteer program</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AE29" s="2" t="n">
-        <v>46104.40694444445</v>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>23-03-2026</t>
-        </is>
-      </c>
-      <c r="AG29" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>Emirates NBD_AE Exchanger volunteer program</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AK29" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL29" t="inlineStr">
-        <is>
-          <t>EmiratesNBD_AE</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2035956342763258332</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956342763258332</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Sosomostafa729S</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Soha.mostafa77</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @Emy191990 @ibushra_03 @parulghalout</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Exchanger volunteer program &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K30" t="b">
-        <v>0</v>
-      </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>22h</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>Mar 23, 2026 · 5:46 AM UTC</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="n">
-        <v>46104.24027777778</v>
-      </c>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/parulghalout']</t>
-        </is>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>15</v>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>Exchanger volunteer program @Emy191990 @ibushra_03 @parulghalout</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956342763258332</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @Emy191990 @ibushra_03 @parulghalout</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @Emy191990 @ibushra_03 @parulghalout</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>Emirates NBD AE Exchanger volunteer program</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD30" t="inlineStr">
-        <is>
-          <t>Neutral</t>
         </is>
       </c>
       <c r="AE30" s="2" t="n">
@@ -5562,7 +5537,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Emirates NBD AE Exchanger volunteer program</t>
+          <t>A simple rule can help her stay on track: 50% for needs 30% for wants 20% for savings A smart plan that helps you spend, save, and stay in control. • To participate: - Follow Emirates NBD - Tag 3 friends - Drop your answer below for a chance to win AED 10,000 • This is one of the many tips that the bank’s program has in store.</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -5585,12 +5560,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2035956152442449955</t>
+          <t>2035956407212925393</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956152442449955</t>
+          <t>https://x.com/Sosomostafa729S/status/2035956407212925393</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5616,12 +5591,12 @@
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE FINEELL ( Financial Well-being program) with Emirates NBD @parulghalout @Emy191990 @Salma2232019</t>
+          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @SelmaRomola @ibushra_03</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>FINEELL ( Financial Well-being program) with Emirates NBD &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
+          <t>Exchanger volunteer program &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K31" t="b">
@@ -5635,21 +5610,21 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Mar 23, 2026 · 5:45 AM UTC</t>
+          <t>Mar 23, 2026 · 5:46 AM UTC</t>
         </is>
       </c>
       <c r="P31" s="2" t="n">
-        <v>46104.23958333334</v>
+        <v>46104.24027777778</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
         <is>
-          <t>['https://x.com/parulghalout', 'https://x.com/Emy191990', 'https://x.com/Salma2232019']</t>
+          <t>['https://x.com/semeet', 'https://x.com/SelmaRomola', 'https://x.com/ibushra_03']</t>
         </is>
       </c>
       <c r="S31" t="n">
@@ -5662,7 +5637,7 @@
         <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
@@ -5671,27 +5646,27 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>FINEELL ( Financial Well-being program) with Emirates NBD @parulghalout @Emy191990 @Salma2232019</t>
+          <t>Exchanger volunteer program @semeet @SelmaRomola @ibushra_03</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956152442449955</t>
+          <t>https://x.com/Sosomostafa729S/status/2035956407212925393</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE FINEELL ( Financial Well-being program) with Emirates NBD @parulghalout @Emy191990 @Salma2232019</t>
+          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @SelmaRomola @ibushra_03</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE FINEELL ( Financial Well-being program) with Emirates NBD @parulghalout @Emy191990 @Salma2232019</t>
+          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @SelmaRomola @ibushra_03</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>Emirates NBD FINEELL (Financial Well-being program) with Emirates NBD.</t>
+          <t>Emirates NBD_AE Exchanger volunteer program</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -5701,11 +5676,11 @@
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE31" s="2" t="n">
-        <v>46104.40625</v>
+        <v>46104.40694444445</v>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
@@ -5724,7 +5699,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Emirates NBD FINEELL (Financial Well-being program) with Emirates NBD.</t>
+          <t>Emirates NBD_AE Exchanger volunteer program</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -5747,12 +5722,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2035956075355361747</t>
+          <t>2035956342763258332</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956075355361747</t>
+          <t>https://x.com/Sosomostafa729S/status/2035956342763258332</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5778,12 +5753,12 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE FINEELL ( Financial Well-being program) with Emirates NBD @SelmaRomola @Salma2232019 @semeet</t>
+          <t>@EmiratesNBD_AE Exchanger volunteer program @Emy191990 @ibushra_03 @parulghalout</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>FINEELL ( Financial Well-being program) with Emirates NBD &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt;</t>
+          <t>Exchanger volunteer program &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K32" t="b">
@@ -5797,21 +5772,21 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Mar 23, 2026 · 5:45 AM UTC</t>
+          <t>Mar 23, 2026 · 5:46 AM UTC</t>
         </is>
       </c>
       <c r="P32" s="2" t="n">
-        <v>46104.23958333334</v>
+        <v>46104.24027777778</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
         <is>
-          <t>['https://x.com/SelmaRomola', 'https://x.com/Salma2232019', 'https://x.com/semeet']</t>
+          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/parulghalout']</t>
         </is>
       </c>
       <c r="S32" t="n">
@@ -5833,27 +5808,27 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>FINEELL ( Financial Well-being program) with Emirates NBD @SelmaRomola @Salma2232019 @semeet</t>
+          <t>Exchanger volunteer program @Emy191990 @ibushra_03 @parulghalout</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956075355361747</t>
+          <t>https://x.com/Sosomostafa729S/status/2035956342763258332</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE FINEELL ( Financial Well-being program) with Emirates NBD @SelmaRomola @Salma2232019 @semeet</t>
+          <t>@EmiratesNBD_AE Exchanger volunteer program @Emy191990 @ibushra_03 @parulghalout</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE FINEELL ( Financial Well-being program) with Emirates NBD @SelmaRomola @Salma2232019 @semeet</t>
+          <t>@EmiratesNBD_AE Exchanger volunteer program @Emy191990 @ibushra_03 @parulghalout</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>Emirates NBD FINEELL (Financial Well-being program) with Emirates NBD</t>
+          <t>Emirates NBD AE Exchanger volunteer program</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -5863,11 +5838,11 @@
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE32" s="2" t="n">
-        <v>46104.40625</v>
+        <v>46104.40694444445</v>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
@@ -5886,7 +5861,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Emirates NBD FINEELL (Financial Well-being program) with Emirates NBD</t>
+          <t>Emirates NBD AE Exchanger volunteer program</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -5909,12 +5884,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2035956001279775104</t>
+          <t>2035956152442449955</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956001279775104</t>
+          <t>https://x.com/Sosomostafa729S/status/2035956152442449955</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5940,12 +5915,12 @@
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE FINEELL ( Financial Well-being program) with Emirates NBD @Emy191990 @parulghalout @ibushra_03</t>
+          <t>@EmiratesNBD_AE FINEELL ( Financial Well-being program) with Emirates NBD @parulghalout @Emy191990 @Salma2232019</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>FINEELL ( Financial Well-being program) with Emirates NBD &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt;</t>
+          <t>FINEELL ( Financial Well-being program) with Emirates NBD &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K33" t="b">
@@ -5959,7 +5934,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -5973,7 +5948,7 @@
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
         <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/parulghalout', 'https://x.com/ibushra_03']</t>
+          <t>['https://x.com/parulghalout', 'https://x.com/Emy191990', 'https://x.com/Salma2232019']</t>
         </is>
       </c>
       <c r="S33" t="n">
@@ -5995,27 +5970,27 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>FINEELL ( Financial Well-being program) with Emirates NBD @Emy191990 @parulghalout @ibushra_03</t>
+          <t>FINEELL ( Financial Well-being program) with Emirates NBD @parulghalout @Emy191990 @Salma2232019</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956001279775104</t>
+          <t>https://x.com/Sosomostafa729S/status/2035956152442449955</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE FINEELL ( Financial Well-being program) with Emirates NBD @Emy191990 @parulghalout @ibushra_03</t>
+          <t>@EmiratesNBD_AE FINEELL ( Financial Well-being program) with Emirates NBD @parulghalout @Emy191990 @Salma2232019</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE FINEELL ( Financial Well-being program) with Emirates NBD @Emy191990 @parulghalout @ibushra_03</t>
+          <t>@EmiratesNBD_AE FINEELL ( Financial Well-being program) with Emirates NBD @parulghalout @Emy191990 @Salma2232019</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Emirates NBD FINEELL (Financial Well-being program) with Emirates NBD</t>
+          <t>Emirates NBD FINEELL (Financial Well-being program) with Emirates NBD.</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -6048,7 +6023,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Emirates NBD FINEELL (Financial Well-being program) with Emirates NBD</t>
+          <t>Emirates NBD FINEELL (Financial Well-being program) with Emirates NBD.</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
@@ -6071,12 +6046,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2035955834002501721</t>
+          <t>2035956075355361747</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035955834002501721</t>
+          <t>https://x.com/Sosomostafa729S/status/2035956075355361747</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -6102,12 +6077,12 @@
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App. @Emy191990 @Salma2232019 @Salma2232019</t>
+          <t>@EmiratesNBD_AE FINEELL ( Financial Well-being program) with Emirates NBD @SelmaRomola @Salma2232019 @semeet</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App. &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
+          <t>FINEELL ( Financial Well-being program) with Emirates NBD &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K34" t="b">
@@ -6121,21 +6096,21 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Mar 23, 2026 · 5:44 AM UTC</t>
+          <t>Mar 23, 2026 · 5:45 AM UTC</t>
         </is>
       </c>
       <c r="P34" s="2" t="n">
-        <v>46104.23888888889</v>
+        <v>46104.23958333334</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
         <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/Salma2232019', 'https://x.com/Salma2232019']</t>
+          <t>['https://x.com/SelmaRomola', 'https://x.com/Salma2232019', 'https://x.com/semeet']</t>
         </is>
       </c>
       <c r="S34" t="n">
@@ -6148,7 +6123,7 @@
         <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
@@ -6157,19 +6132,27 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App. @Emy191990 @Salma2232019 @Salma2232019</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr"/>
+          <t>FINEELL ( Financial Well-being program) with Emirates NBD @SelmaRomola @Salma2232019 @semeet</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2035956075355361747</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE FINEELL ( Financial Well-being program) with Emirates NBD @SelmaRomola @Salma2232019 @semeet</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App. @Emy191990 @Salma2232019 @Salma2232019</t>
+          <t>@EmiratesNBD_AE FINEELL ( Financial Well-being program) with Emirates NBD @SelmaRomola @Salma2232019 @semeet</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Through the ENBD X Mobile App.</t>
+          <t>Emirates NBD FINEELL (Financial Well-being program) with Emirates NBD</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -6179,11 +6162,11 @@
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE34" s="2" t="n">
-        <v>46104.40555555555</v>
+        <v>46104.40625</v>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
@@ -6202,7 +6185,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Through the ENBD X Mobile App.</t>
+          <t>Emirates NBD FINEELL (Financial Well-being program) with Emirates NBD</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
@@ -6225,12 +6208,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2035955759859834985</t>
+          <t>2035956001279775104</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035955759859834985</t>
+          <t>https://x.com/Sosomostafa729S/status/2035956001279775104</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -6256,12 +6239,12 @@
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Via the ENBD X Mobile App. @SelmaRomola @semeet @ibushra_03</t>
+          <t>@EmiratesNBD_AE FINEELL ( Financial Well-being program) with Emirates NBD @Emy191990 @parulghalout @ibushra_03</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App. &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt;</t>
+          <t>FINEELL ( Financial Well-being program) with Emirates NBD &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K35" t="b">
@@ -6275,21 +6258,21 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Mar 23, 2026 · 5:44 AM UTC</t>
+          <t>Mar 23, 2026 · 5:45 AM UTC</t>
         </is>
       </c>
       <c r="P35" s="2" t="n">
-        <v>46104.23888888889</v>
+        <v>46104.23958333334</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
         <is>
-          <t>['https://x.com/SelmaRomola', 'https://x.com/semeet', 'https://x.com/ibushra_03']</t>
+          <t>['https://x.com/Emy191990', 'https://x.com/parulghalout', 'https://x.com/ibushra_03']</t>
         </is>
       </c>
       <c r="S35" t="n">
@@ -6302,7 +6285,7 @@
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
@@ -6311,27 +6294,27 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App. @SelmaRomola @semeet @ibushra_03</t>
+          <t>FINEELL ( Financial Well-being program) with Emirates NBD @Emy191990 @parulghalout @ibushra_03</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035955759859834985</t>
+          <t>https://x.com/Sosomostafa729S/status/2035956001279775104</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Via the ENBD X Mobile App. @SelmaRomola @semeet @ibushra_03</t>
+          <t>@EmiratesNBD_AE FINEELL ( Financial Well-being program) with Emirates NBD @Emy191990 @parulghalout @ibushra_03</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Via the ENBD X Mobile App. @SelmaRomola @semeet @ibushra_03</t>
+          <t>@EmiratesNBD_AE FINEELL ( Financial Well-being program) with Emirates NBD @Emy191990 @parulghalout @ibushra_03</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App.</t>
+          <t>Emirates NBD FINEELL (Financial Well-being program) with Emirates NBD</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -6341,11 +6324,11 @@
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE35" s="2" t="n">
-        <v>46104.40555555555</v>
+        <v>46104.40625</v>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
@@ -6364,7 +6347,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App.</t>
+          <t>Emirates NBD FINEELL (Financial Well-being program) with Emirates NBD</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -6387,12 +6370,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2035955684098163029</t>
+          <t>2035955834002501721</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035955684098163029</t>
+          <t>https://x.com/Sosomostafa729S/status/2035955834002501721</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6430,7 +6413,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App. &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
+          <t>Via the ENBD X Mobile App. &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K36" t="b">
@@ -6444,21 +6427,21 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Mar 23, 2026 · 5:43 AM UTC</t>
+          <t>Mar 23, 2026 · 5:44 AM UTC</t>
         </is>
       </c>
       <c r="P36" s="2" t="n">
-        <v>46104.23819444444</v>
+        <v>46104.23888888889</v>
       </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
         <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/parulghalout', 'https://x.com/Salma2232019']</t>
+          <t>['https://x.com/Emy191990', 'https://x.com/Salma2232019', 'https://x.com/Salma2232019']</t>
         </is>
       </c>
       <c r="S36" t="n">
@@ -6471,7 +6454,7 @@
         <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
@@ -6480,12 +6463,12 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App. @Emy191990 @parulghalout @Salma2232019</t>
+          <t>Via the ENBD X Mobile App. @Emy191990 @Salma2232019 @Salma2232019</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035955684098163029</t>
+          <t>https://x.com/Sosomostafa729S/status/2035955834002501721</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
@@ -6529,7 +6512,7 @@
         </is>
       </c>
       <c r="AE36" s="2" t="n">
-        <v>46104.40486111111</v>
+        <v>46104.40555555555</v>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
@@ -6571,12 +6554,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2035955579966173454</t>
+          <t>2035955759859834985</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035955579966173454</t>
+          <t>https://x.com/Sosomostafa729S/status/2035955759859834985</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6602,12 +6585,12 @@
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App. @semeet @SelmaRomola @Salma2232019</t>
+          <t>@EmiratesNBD_AE Via the ENBD X Mobile App. @SelmaRomola @semeet @ibushra_03</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App. &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
+          <t>Via the ENBD X Mobile App. &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K37" t="b">
@@ -6621,21 +6604,21 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Mar 23, 2026 · 5:43 AM UTC</t>
+          <t>Mar 23, 2026 · 5:44 AM UTC</t>
         </is>
       </c>
       <c r="P37" s="2" t="n">
-        <v>46104.23819444444</v>
+        <v>46104.23888888889</v>
       </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
         <is>
-          <t>['https://x.com/semeet', 'https://x.com/SelmaRomola', 'https://x.com/Salma2232019']</t>
+          <t>['https://x.com/SelmaRomola', 'https://x.com/semeet', 'https://x.com/ibushra_03']</t>
         </is>
       </c>
       <c r="S37" t="n">
@@ -6648,7 +6631,7 @@
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
@@ -6657,19 +6640,27 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App. @semeet @SelmaRomola @Salma2232019</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="inlineStr"/>
+          <t>Via the ENBD X Mobile App. @SelmaRomola @semeet @ibushra_03</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2035955759859834985</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Via the ENBD X Mobile App. @SelmaRomola @semeet @ibushra_03</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App. @semeet @SelmaRomola @Salma2232019</t>
+          <t>@EmiratesNBD_AE Via the ENBD X Mobile App. @SelmaRomola @semeet @ibushra_03</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>Through the ENBD X Mobile App.</t>
+          <t>Via the ENBD X Mobile App.</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -6683,7 +6674,7 @@
         </is>
       </c>
       <c r="AE37" s="2" t="n">
-        <v>46104.40486111111</v>
+        <v>46104.40555555555</v>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
@@ -6702,7 +6693,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Through the ENBD X Mobile App.</t>
+          <t>Via the ENBD X Mobile App.</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -6725,12 +6716,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2035955485564936537</t>
+          <t>2035955684098163029</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035955485564936537</t>
+          <t>https://x.com/Sosomostafa729S/status/2035955684098163029</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6756,12 +6747,12 @@
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Via the ENBD X Mobile App. @SelmaRomola @Emy191990 @parulghalout</t>
+          <t>@EmiratesNBD_AE Via the ENBD X Mobile App. @Emy191990 @parulghalout @Salma2232019</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App. &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt;</t>
+          <t>Via the ENBD X Mobile App. &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K38" t="b">
@@ -6775,7 +6766,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -6789,7 +6780,7 @@
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
         <is>
-          <t>['https://x.com/SelmaRomola', 'https://x.com/Emy191990', 'https://x.com/parulghalout']</t>
+          <t>['https://x.com/Emy191990', 'https://x.com/parulghalout', 'https://x.com/Salma2232019']</t>
         </is>
       </c>
       <c r="S38" t="n">
@@ -6811,22 +6802,22 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App. @SelmaRomola @Emy191990 @parulghalout</t>
+          <t>Via the ENBD X Mobile App. @Emy191990 @parulghalout @Salma2232019</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035955485564936537</t>
+          <t>https://x.com/Sosomostafa729S/status/2035955684098163029</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Via the ENBD X Mobile App. @SelmaRomola @Emy191990 @parulghalout</t>
+          <t>@EmiratesNBD_AE Via the ENBD X Mobile App. @Emy191990 @parulghalout @Salma2232019</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Via the ENBD X Mobile App. @SelmaRomola @Emy191990 @parulghalout</t>
+          <t>@EmiratesNBD_AE Via the ENBD X Mobile App. @Emy191990 @parulghalout @Salma2232019</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
@@ -6887,12 +6878,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2035955401255235904</t>
+          <t>2035955579966173454</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035955401255235904</t>
+          <t>https://x.com/Sosomostafa729S/status/2035955579966173454</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6918,12 +6909,12 @@
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Via the ENBD X Mobile App. @Emy191990 @Salma2232019 @semeet</t>
+          <t>@EmiratesNBD_AE Via the ENBD X Mobile App. @semeet @SelmaRomola @Salma2232019</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App. &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt;</t>
+          <t>Via the ENBD X Mobile App. &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K39" t="b">
@@ -6937,21 +6928,21 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Mar 23, 2026 · 5:42 AM UTC</t>
+          <t>Mar 23, 2026 · 5:43 AM UTC</t>
         </is>
       </c>
       <c r="P39" s="2" t="n">
-        <v>46104.2375</v>
+        <v>46104.23819444444</v>
       </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
         <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/Salma2232019', 'https://x.com/semeet']</t>
+          <t>['https://x.com/semeet', 'https://x.com/SelmaRomola', 'https://x.com/Salma2232019']</t>
         </is>
       </c>
       <c r="S39" t="n">
@@ -6964,7 +6955,7 @@
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
@@ -6973,22 +6964,22 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App. @Emy191990 @Salma2232019 @semeet</t>
+          <t>Via the ENBD X Mobile App. @semeet @SelmaRomola @Salma2232019</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035955401255235904</t>
+          <t>https://x.com/Sosomostafa729S/status/2035955579966173454</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Via the ENBD X Mobile App. @Emy191990 @Salma2232019 @semeet</t>
+          <t>@EmiratesNBD_AE Via the ENBD X Mobile App. @semeet @SelmaRomola @Salma2232019</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Via the ENBD X Mobile App. @Emy191990 @Salma2232019 @semeet</t>
+          <t>@EmiratesNBD_AE Via the ENBD X Mobile App. @semeet @SelmaRomola @Salma2232019</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
@@ -7007,7 +6998,7 @@
         </is>
       </c>
       <c r="AE39" s="2" t="n">
-        <v>46104.40416666667</v>
+        <v>46104.40486111111</v>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
@@ -7049,44 +7040,43 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2035937800336384350</t>
+          <t>2035955485564936537</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2035937800336384350</t>
+          <t>https://x.com/Sosomostafa729S/status/2035955485564936537</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA</t>
+          <t>https://x.com/Sosomostafa729S</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>EmiratesNBD_KSA</t>
+          <t>Sosomostafa729S</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>EmiratesNBD KSA</t>
+          <t>Soha.mostafa77</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427762424385536/iUFFKIOK_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>نسعد بخدمتكم في الفروع العاملة خلال اجازة عيد الفطر المبارك https://t.co/JCrAQwDiwz</t>
+          <t>Via the ENBD X Mobile App. @SelmaRomola @Emy191990 @parulghalout</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>مرحباً بك, يمكنك الأن معرفة المزيد عن اماكن الفروع و أوقات العمل من خلال الضغط على الرابط ادناه.
-&lt;a href="http://ms.spr.ly/6016Qszsr"&gt;ms.spr.ly/6016Qszsr&lt;/a&gt;</t>
+          <t>Via the ENBD X Mobile App. &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K40" t="b">
@@ -7095,7 +7085,7 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>['c65kg']</t>
+          <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -7105,16 +7095,16 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Mar 23, 2026 · 4:32 AM UTC</t>
+          <t>Mar 23, 2026 · 5:43 AM UTC</t>
         </is>
       </c>
       <c r="P40" s="2" t="n">
-        <v>46104.18888888889</v>
+        <v>46104.23819444444</v>
       </c>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr">
         <is>
-          <t>['http://ms.spr.ly/6016Qszsr']</t>
+          <t>['https://x.com/SelmaRomola', 'https://x.com/Emy191990', 'https://x.com/parulghalout']</t>
         </is>
       </c>
       <c r="S40" t="n">
@@ -7127,7 +7117,7 @@
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
@@ -7136,28 +7126,19 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>مرحباً بك, يمكنك الأن معرفة المزيد عن اماكن الفروع و أوقات العمل من خلال الضغط على الرابط ادناه.
-ms.spr.ly/6016Qszsr</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2035937800336384350</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>نسعد بخدمتكم في الفروع العاملة خلال اجازة عيد الفطر المبارك https://t.co/JCrAQwDiwz</t>
-        </is>
-      </c>
+          <t>Via the ENBD X Mobile App. @SelmaRomola @Emy191990 @parulghalout</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>نسعد بخدمتكم في الفروع العاملة خلال اجازة عيد الفطر المبارك https://t.co/JCrAQwDiwz</t>
+          <t>Via the ENBD X Mobile App. @SelmaRomola @Emy191990 @parulghalout</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>We are pleased to serve you at the operating branches during the Eid al-Fitr holiday.</t>
+          <t>Through the ENBD X Mobile App.</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -7171,7 +7152,7 @@
         </is>
       </c>
       <c r="AE40" s="2" t="n">
-        <v>46104.35555555556</v>
+        <v>46104.40486111111</v>
       </c>
       <c r="AF40" t="inlineStr">
         <is>
@@ -7190,7 +7171,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>We are pleased to serve you at the operating branches during the Eid al-Fitr holiday.</t>
+          <t>Through the ENBD X Mobile App.</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
@@ -7203,7 +7184,7 @@
       </c>
       <c r="AL40" t="inlineStr">
         <is>
-          <t>c65kg</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
     </row>
@@ -7213,45 +7194,43 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2035887867075948831</t>
+          <t>2035955401255235904</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://x.com/ahmd_4050/status/2035887867075948831</t>
+          <t>https://x.com/Sosomostafa729S/status/2035955401255235904</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://x.com/ahmd_4050</t>
+          <t>https://x.com/Sosomostafa729S</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ahmd_4050</t>
+          <t>Sosomostafa729S</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>ahmd</t>
+          <t>Soha.mostafa77</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1686557037948276736/wZXFbO-o_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>انتبه إلى الإشارات التحذيرية قبل فوات الأوان. تطلب الوظائف الوهمية عادةً رسومًا أو تحويلات مالية أو معلومات مصرفية. -احرص دائمًا على التحقق، وابقَ يقظًا لحماية نفسك.
-#متحدون_ضد_الاحتيال https://t.co/tRBGQGbIbF</t>
+          <t>@EmiratesNBD_AE Via the ENBD X Mobile App. @Emy191990 @Salma2232019 @semeet</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>كم تعطون قروض</t>
+          <t>Via the ENBD X Mobile App. &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K41" t="b">
@@ -7265,19 +7244,23 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Mar 23</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Mar 23, 2026 · 1:14 AM UTC</t>
+          <t>Mar 23, 2026 · 5:42 AM UTC</t>
         </is>
       </c>
       <c r="P41" s="2" t="n">
-        <v>46104.05138888889</v>
+        <v>46104.2375</v>
       </c>
       <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>['https://x.com/Emy191990', 'https://x.com/Salma2232019', 'https://x.com/semeet']</t>
+        </is>
+      </c>
       <c r="S41" t="n">
         <v>0</v>
       </c>
@@ -7288,7 +7271,7 @@
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
@@ -7297,31 +7280,27 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>كم تعطون قروض</t>
+          <t>Via the ENBD X Mobile App. @Emy191990 @Salma2232019 @semeet</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>https://x.com/ahmd_4050/status/2035887867075948831</t>
+          <t>https://x.com/Sosomostafa729S/status/2035955401255235904</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>انتبه إلى الإشارات التحذيرية قبل فوات الأوان. تطلب الوظائف الوهمية عادةً رسومًا أو تحويلات مالية أو معلومات مصرفية. -احرص دائمًا على التحقق، وابقَ يقظًا لحماية نفسك.
-#متحدون_ضد_الاحتيال https://t.co/tRBGQGbIbF</t>
+          <t>@EmiratesNBD_AE Via the ENBD X Mobile App. @Emy191990 @Salma2232019 @semeet</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>انتبه إلى الإشارات التحذيرية قبل فوات الأوان. تطلب الوظائف الوهمية عادةً رسومًا أو تحويلات مالية أو معلومات مصرفية. -احرص دائمًا على التحقق، وابقَ يقظًا لحماية نفسك.
-#متحدون_ضد_الاحتيال https://t.co/tRBGQGbIbF</t>
+          <t>@EmiratesNBD_AE Via the ENBD X Mobile App. @Emy191990 @Salma2232019 @semeet</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>Pay attention to warning signs before it's too late. Fake jobs usually ask for fees, money transfers, or banking information. Always make sure to verify and stay alert to protect yourself.</t>
+          <t>Via the ENBD X Mobile App.</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -7335,7 +7314,7 @@
         </is>
       </c>
       <c r="AE41" s="2" t="n">
-        <v>46104.21805555555</v>
+        <v>46104.40416666667</v>
       </c>
       <c r="AF41" t="inlineStr">
         <is>
@@ -7354,7 +7333,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Fake jobs usually ask for fees, money transfers, or banking information. • Always make sure to verify and stay alert to protect yourself. • Pay attention to warning signs before it's too late.</t>
+          <t>Via the ENBD X Mobile App.</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
@@ -7377,42 +7356,370 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2036045570406535456</t>
+          <t>2035937800336384350</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2036045570406535456</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2035937800336384350</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/EmiratesNBD_KSA</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>EmiratesNBD_KSA</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>EmiratesNBD KSA</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1762427762424385536/iUFFKIOK_bigger.jpg</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
+          <t>نسعد بخدمتكم في الفروع العاملة خلال اجازة عيد الفطر المبارك https://t.co/JCrAQwDiwz</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>مرحباً بك, يمكنك الأن معرفة المزيد عن اماكن الفروع و أوقات العمل من خلال الضغط على الرابط ادناه.
+&lt;a href="http://ms.spr.ly/6016Qszsr"&gt;ms.spr.ly/6016Qszsr&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K42" t="b">
+        <v>0</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>['c65kg']</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Mar 23</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Mar 23, 2026 · 4:32 AM UTC</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="n">
+        <v>46104.18888888889</v>
+      </c>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>['http://ms.spr.ly/6016Qszsr']</t>
+        </is>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>38</v>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>مرحباً بك, يمكنك الأن معرفة المزيد عن اماكن الفروع و أوقات العمل من خلال الضغط على الرابط ادناه.
+ms.spr.ly/6016Qszsr</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_KSA/status/2035937800336384350</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>نسعد بخدمتكم في الفروع العاملة خلال اجازة عيد الفطر المبارك https://t.co/JCrAQwDiwz</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>نسعد بخدمتكم في الفروع العاملة خلال اجازة عيد الفطر المبارك https://t.co/JCrAQwDiwz</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>We are pleased to serve you at the operating branches during the Eid al-Fitr holiday.</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE42" s="2" t="n">
+        <v>46104.35555555556</v>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>23-03-2026</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>We are pleased to serve you at the operating branches during the Eid al-Fitr holiday.</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK42" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL42" t="inlineStr">
+        <is>
+          <t>c65kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2035887867075948831</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://x.com/ahmd_4050/status/2035887867075948831</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://x.com/ahmd_4050</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>ahmd_4050</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>ahmd</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1686557037948276736/wZXFbO-o_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>انتبه إلى الإشارات التحذيرية قبل فوات الأوان. تطلب الوظائف الوهمية عادةً رسومًا أو تحويلات مالية أو معلومات مصرفية. +احرص دائمًا على التحقق، وابقَ يقظًا لحماية نفسك.
+#متحدون_ضد_الاحتيال https://t.co/tRBGQGbIbF</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>كم تعطون قروض</t>
+        </is>
+      </c>
+      <c r="K43" t="b">
+        <v>0</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Mar 23</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Mar 23, 2026 · 1:14 AM UTC</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="n">
+        <v>46104.05138888889</v>
+      </c>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>17</v>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>كم تعطون قروض</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>https://x.com/ahmd_4050/status/2035887867075948831</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>انتبه إلى الإشارات التحذيرية قبل فوات الأوان. تطلب الوظائف الوهمية عادةً رسومًا أو تحويلات مالية أو معلومات مصرفية. +احرص دائمًا على التحقق، وابقَ يقظًا لحماية نفسك.
+#متحدون_ضد_الاحتيال https://t.co/tRBGQGbIbF</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>انتبه إلى الإشارات التحذيرية قبل فوات الأوان. تطلب الوظائف الوهمية عادةً رسومًا أو تحويلات مالية أو معلومات مصرفية. +احرص دائمًا على التحقق، وابقَ يقظًا لحماية نفسك.
+#متحدون_ضد_الاحتيال https://t.co/tRBGQGbIbF</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>Pay attention to warning signs before it's too late. Fake jobs usually ask for fees, money transfers, or banking information. Always make sure to verify and stay alert to protect yourself.</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE43" s="2" t="n">
+        <v>46104.21805555555</v>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>23-03-2026</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Fake jobs usually ask for fees, money transfers, or banking information. • Always make sure to verify and stay alert to protect yourself. • Pay attention to warning signs before it's too late.</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK43" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL43" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2036045570406535456</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2036045570406535456</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
           <t>وصلتك رسالة بريد إلكتروني لتجديد اشتراك تحتوي على أخطاء إملائية، ماذا تفعل؟
 You just received a subscription renewal email with spelling mistakes. What would you do?</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>الحين وقتك مع الإمارات الإسلامي.
 احصل على مزايا خاصة واسترداد نقدي مضمون عند تحويل الراتب واستمتع بمعدلات أرباح تنافسية مع تمويل السيارات. وفر واحصل على أرباح متوقعة تصل إلى %6.00 سنوياً.
@@ -7421,44 +7728,44 @@
 تُطبق الشروط والأحكام.</t>
         </is>
       </c>
-      <c r="K42" t="b">
-        <v>0</v>
-      </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>16h</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
+      <c r="K44" t="b">
+        <v>0</v>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
         <is>
           <t>Mar 23, 2026 · 11:41 AM UTC</t>
         </is>
       </c>
-      <c r="P42" s="2" t="n">
+      <c r="P44" s="2" t="n">
         <v>46104.48680555556</v>
       </c>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" t="n">
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="n">
         <v>1</v>
       </c>
-      <c r="V42" t="n">
-        <v>135</v>
-      </c>
-      <c r="W42" t="inlineStr">
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
+      </c>
+      <c r="V44" t="n">
+        <v>149</v>
+      </c>
+      <c r="W44" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>الحين وقتك مع الإمارات الإسلامي.
 احصل على مزايا خاصة واسترداد نقدي مضمون عند تحويل الراتب واستمتع بمعدلات أرباح تنافسية مع تمويل السيارات. وفر واحصل على أرباح متوقعة تصل إلى %6.00 سنوياً.
@@ -7467,348 +7774,40 @@
 تُطبق الشروط والأحكام.</t>
         </is>
       </c>
-      <c r="Y42" t="inlineStr">
+      <c r="Y44" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2036045570406535456</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
+      <c r="Z44" t="inlineStr">
         <is>
           <t>وصلتك رسالة بريد إلكتروني لتجديد اشتراك تحتوي على أخطاء إملائية، ماذا تفعل؟
 You just received a subscription renewal email with spelling mistakes. What would you do?</t>
         </is>
       </c>
-      <c r="AA42" t="inlineStr">
+      <c r="AA44" t="inlineStr">
         <is>
           <t>وصلتك رسالة بريد إلكتروني لتجديد اشتراك تحتوي على أخطاء إملائية، ماذا تفعل؟
 You just received a subscription renewal email with spelling mistakes. What would you do?</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
+      <c r="AB44" t="inlineStr">
         <is>
           <t>You just received a subscription renewal email with spelling mistakes. What would you do?</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
+      <c r="AC44" t="inlineStr">
         <is>
           <t>Bank</t>
         </is>
       </c>
-      <c r="AD42" t="inlineStr">
+      <c r="AD44" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="AE42" s="2" t="n">
+      <c r="AE44" s="2" t="n">
         <v>46104.65347222222</v>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>23-03-2026</t>
-        </is>
-      </c>
-      <c r="AG42" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>You just received a subscription renewal email with spelling mistakes.</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AK42" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL42" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="n">
-        <v>41</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2035996471896449306</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2035996471896449306</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>@emiratesislamic I saw an ad for e savings account with a profit rate of 6%. If I kept 50K in the account wha is the profit amount ? Thanks</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
-        </is>
-      </c>
-      <c r="K43" t="b">
-        <v>0</v>
-      </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>['Ben252024']</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>19h</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>Mar 23, 2026 · 8:26 AM UTC</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="n">
-        <v>46104.35138888889</v>
-      </c>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" t="n">
-        <v>11</v>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2035996471896449306</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>@emiratesislamic I saw an ad for e savings account with a profit rate of 6%. If I kept 50K in the account wha is the profit amount ? Thanks</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>@emiratesislamic I saw an ad for e savings account with a profit rate of 6%. If I kept 50K in the account wha is the profit amount ? Thanks</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>I saw an ad for an e-savings account with a profit rate of 6%. If I kept 50K in the account, what is the profit amount? Thanks</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD43" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AE43" s="2" t="n">
-        <v>46104.51805555556</v>
-      </c>
-      <c r="AF43" t="inlineStr">
-        <is>
-          <t>23-03-2026</t>
-        </is>
-      </c>
-      <c r="AG43" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>If I kept 50K in the account, what is the profit amount? • I saw an ad for an e-savings account with a profit rate of 6%.</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AK43" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL43" t="inlineStr">
-        <is>
-          <t>Ben252024</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="n">
-        <v>42</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2035989928291488100</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2035989928291488100</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>وصلتك رسالة بريد إلكتروني لتجديد اشتراك تحتوي على أخطاء إملائية، ماذا تفعل؟
-You just received a subscription renewal email with spelling mistakes. What would you do?</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>وصلتك رسالة بريد إلكتروني لتجديد اشتراك تحتوي على أخطاء إملائية، ماذا تفعل؟
-You just received a subscription renewal email with spelling mistakes. What would you do?</t>
-        </is>
-      </c>
-      <c r="K44" t="b">
-        <v>0</v>
-      </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>20h</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>Mar 23, 2026 · 8:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="n">
-        <v>46104.33333333334</v>
-      </c>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" t="n">
-        <v>0</v>
-      </c>
-      <c r="U44" t="n">
-        <v>0</v>
-      </c>
-      <c r="V44" t="n">
-        <v>253</v>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>وصلتك رسالة بريد إلكتروني لتجديد اشتراك تحتوي على أخطاء إملائية، ماذا تفعل؟
-You just received a subscription renewal email with spelling mistakes. What would you do?</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr"/>
-      <c r="Z44" t="inlineStr"/>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>وصلتك رسالة بريد إلكتروني لتجديد اشتراك تحتوي على أخطاء إملائية، ماذا تفعل؟
-You just received a subscription renewal email with spelling mistakes. What would you do?</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>You just received a subscription renewal email with spelling mistakes. What would you do?</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="AD44" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AE44" s="2" t="n">
-        <v>46104.5</v>
       </c>
       <c r="AF44" t="inlineStr">
         <is>
@@ -7850,12 +7849,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2035989927905693845</t>
+          <t>2035996471896449306</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2035989927905693845</t>
+          <t>https://x.com/emiratesislamic/status/2035996471896449306</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7881,21 +7880,23 @@
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>احذر الاحتيال. وصلتك رسالة تجديد من بريد جي ميل أو ياهو، ماذا تفعل؟
-Stay alert to scams. Received a renewal email from a Gmail/Yahoo address?</t>
+          <t>@emiratesislamic I saw an ad for e savings account with a profit rate of 6%. If I kept 50K in the account wha is the profit amount ? Thanks</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>احذر الاحتيال. وصلتك رسالة تجديد من بريد جي ميل أو ياهو، ماذا تفعل؟
-Stay alert to scams. Received a renewal email from a Gmail/Yahoo address?</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
         </is>
       </c>
       <c r="K45" t="b">
         <v>0</v>
       </c>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>['Ben252024']</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr">
         <is>
           <t>20h</t>
@@ -7903,11 +7904,11 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Mar 23, 2026 · 8:00 AM UTC</t>
+          <t>Mar 23, 2026 · 8:26 AM UTC</t>
         </is>
       </c>
       <c r="P45" s="2" t="n">
-        <v>46104.33333333334</v>
+        <v>46104.35138888889</v>
       </c>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
@@ -7921,7 +7922,7 @@
         <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>163</v>
+        <v>13</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
@@ -7930,35 +7931,32 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>احذر الاحتيال. وصلتك رسالة تجديد من بريد جي ميل أو ياهو، ماذا تفعل؟
-Stay alert to scams. Received a renewal email from a Gmail/Yahoo address?</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2035989927905693845</t>
+          <t>https://x.com/emiratesislamic/status/2035996471896449306</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>احذر الاحتيال. وصلتك رسالة تجديد من بريد جي ميل أو ياهو، ماذا تفعل؟
-Stay alert to scams. Received a renewal email from a Gmail/Yahoo address?</t>
+          <t>@emiratesislamic I saw an ad for e savings account with a profit rate of 6%. If I kept 50K in the account wha is the profit amount ? Thanks</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>احذر الاحتيال. وصلتك رسالة تجديد من بريد جي ميل أو ياهو، ماذا تفعل؟
-Stay alert to scams. Received a renewal email from a Gmail/Yahoo address?</t>
+          <t>@emiratesislamic I saw an ad for e savings account with a profit rate of 6%. If I kept 50K in the account wha is the profit amount ? Thanks</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>Stay alert to scams. Did you receive a renewal email from a Gmail or Yahoo address? What should you do?</t>
+          <t>I saw an ad for an e-savings account with a profit rate of 6%. If I kept 50K in the account, what is the profit amount? Thanks</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Cust</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr">
@@ -7967,7 +7965,7 @@
         </is>
       </c>
       <c r="AE45" s="2" t="n">
-        <v>46104.5</v>
+        <v>46104.51805555556</v>
       </c>
       <c r="AF45" t="inlineStr">
         <is>
@@ -7986,7 +7984,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Did you receive a renewal email from a Gmail or Yahoo address?</t>
+          <t>If I kept 50K in the account, what is the profit amount? • I saw an ad for an e-savings account with a profit rate of 6%.</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
@@ -7999,7 +7997,7 @@
       </c>
       <c r="AL45" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Ben252024</t>
         </is>
       </c>
     </row>
@@ -8009,67 +8007,64 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2035976151764549748</t>
+          <t>2035989928291488100</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2035976151764549748</t>
+          <t>https://x.com/emiratesislamic/status/2035989928291488100</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>EmiratesNBD_KSA</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>EmiratesNBD KSA</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427762424385536/iUFFKIOK_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA 
-I raised mail to customer care regarding flight amount deduction descripancy twice but didn't hear from Emirates NBD. This is not acceptable at all. I am very much disappointed with customer care service of Emirates NBD. Zero star.</t>
+          <t>احذر الاحتيال. وصلتك رسالة تجديد من بريد جي ميل أو ياهو، ماذا تفعل؟
+Stay alert to scams. Received a renewal email from a Gmail/Yahoo address?</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Hi Rakshit, our team tried to contact you, but there was no answer from your side, we have asked our team to contact you again as soon as possible.</t>
+          <t>وصلتك رسالة بريد إلكتروني لتجديد اشتراك تحتوي على أخطاء إملائية، ماذا تفعل؟
+You just received a subscription renewal email with spelling mistakes. What would you do?</t>
         </is>
       </c>
       <c r="K46" t="b">
         <v>0</v>
       </c>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>['RakshtVaghasiya']</t>
-        </is>
-      </c>
+      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Mar 23, 2026 · 7:05 AM UTC</t>
+          <t>Mar 23, 2026 · 8:00 AM UTC</t>
         </is>
       </c>
       <c r="P46" s="2" t="n">
-        <v>46104.29513888889</v>
+        <v>46104.33333333334</v>
       </c>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
@@ -8083,52 +8078,53 @@
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>27</v>
+        <v>258</v>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Hi Rakshit, our team tried to contact you, but there was no answer from your side, we have asked our team to contact you again as soon as possible.</t>
+          <t>وصلتك رسالة بريد إلكتروني لتجديد اشتراك تحتوي على أخطاء إملائية، ماذا تفعل؟
+You just received a subscription renewal email with spelling mistakes. What would you do?</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2035976151764549748</t>
+          <t>https://x.com/emiratesislamic/status/2035989928291488100</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA 
-I raised mail to customer care regarding flight amount deduction descripancy twice but didn't hear from Emirates NBD. This is not acceptable at all. I am very much disappointed with customer care service of Emirates NBD. Zero star.</t>
+          <t>احذر الاحتيال. وصلتك رسالة تجديد من بريد جي ميل أو ياهو، ماذا تفعل؟
+Stay alert to scams. Received a renewal email from a Gmail/Yahoo address?</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA 
-I raised mail to customer care regarding flight amount deduction descripancy twice but didn't hear from Emirates NBD. This is not acceptable at all. I am very much disappointed with customer care service of Emirates NBD. Zero star.</t>
+          <t>احذر الاحتيال. وصلتك رسالة تجديد من بريد جي ميل أو ياهو، ماذا تفعل؟
+Stay alert to scams. Received a renewal email from a Gmail/Yahoo address?</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>I raised an email to customer care regarding the discrepancy in the flight amount deduction twice but didn't hear from Emirates NBD. This is not acceptable at all. I am very disappointed with the customer care service of Emirates NBD. Zero stars.</t>
+          <t>Beware of scams. Did you receive a renewal message from a Gmail or Yahoo address? What should you do?</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Cust</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE46" s="2" t="n">
-        <v>46104.46180555555</v>
+        <v>46104.5</v>
       </c>
       <c r="AF46" t="inlineStr">
         <is>
@@ -8137,22 +8133,22 @@
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
+          <t>2. Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>I raised an email to customer care regarding the discrepancy in the flight amount deduction twice but didn't hear from Emirates NBD. • I am very disappointed with the customer care service of Emirates NBD. • This is not acceptable at all.</t>
+          <t>Did you receive a renewal message from a Gmail or Yahoo address?</t>
         </is>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank (ENBD)</t>
+          <t>Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AK46" t="n">
@@ -8160,7 +8156,7 @@
       </c>
       <c r="AL46" t="inlineStr">
         <is>
-          <t>RakshtVaghasiya</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8170,75 +8166,69 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2036027630722617585</t>
+          <t>2035989927905693845</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://x.com/Nightowl263/status/2036027630722617585</t>
+          <t>https://x.com/emiratesislamic/status/2035989927905693845</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://x.com/Nightowl263</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Nightowl263</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Priya George</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1718237295055433728/mRkQyUDb_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>I’ve been waiting a month for this bank to process account application. Every day I follow up, they say “wait 5 more days.” And yet, they’re busy educating customers on small delivery fees. Can I trust them with my money? 😕 what would you do in this case ? #UnitedAgainstFraud</t>
+          <t>احذر الاحتيال. وصلتك رسالة تجديد من بريد جي ميل أو ياهو، ماذا تفعل؟
+Stay alert to scams. Received a renewal email from a Gmail/Yahoo address?</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>I’ve been waiting a month for this bank to process account application. Every day I follow up, they say “wait 5 more days.” And yet, they’re busy educating customers on small delivery fees. Can I trust them with my money? 😕 what would you do in this case ? &lt;a href="/search?f=tweets&amp;amp;q=%23UnitedAgainstFraud"&gt;#UnitedAgainstFraud&lt;/a&gt;</t>
+          <t>احذر الاحتيال. وصلتك رسالة تجديد من بريد جي ميل أو ياهو، ماذا تفعل؟
+Stay alert to scams. Received a renewal email from a Gmail/Yahoo address?</t>
         </is>
       </c>
       <c r="K47" t="b">
         <v>0</v>
       </c>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Mar 23, 2026 · 10:29 AM UTC</t>
+          <t>Mar 23, 2026 · 8:00 AM UTC</t>
         </is>
       </c>
       <c r="P47" s="2" t="n">
-        <v>46104.43680555555</v>
+        <v>46104.33333333334</v>
       </c>
       <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23UnitedAgainstFraud']</t>
-        </is>
-      </c>
+      <c r="R47" t="inlineStr"/>
       <c r="S47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
         <v>0</v>
@@ -8247,42 +8237,44 @@
         <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>36</v>
+        <v>168</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>I’ve been waiting a month for this bank to process account application. Every day I follow up, they say “wait 5 more days.” And yet, they’re busy educating customers on small delivery fees. Can I trust them with my money? 😕 what would you do in this case ? #UnitedAgainstFraud</t>
+          <t>احذر الاحتيال. وصلتك رسالة تجديد من بريد جي ميل أو ياهو، ماذا تفعل؟
+Stay alert to scams. Received a renewal email from a Gmail/Yahoo address?</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="inlineStr"/>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>I’ve been waiting a month for this bank to process account application. Every day I follow up, they say “wait 5 more days.” And yet, they’re busy educating customers on small delivery fees. Can I trust them with my money? 😕 what would you do in this case ? #UnitedAgainstFraud</t>
+          <t>احذر الاحتيال. وصلتك رسالة تجديد من بريد جي ميل أو ياهو، ماذا تفعل؟
+Stay alert to scams. Received a renewal email from a Gmail/Yahoo address?</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>I’ve been waiting a month for this bank to process my account application. Every day I follow up, and they say “wait 5 more days.” Yet, they’re busy educating customers on small delivery fees. Can I trust them with my money? 😕 What would you do in this case? #UnitedAgainstFraud</t>
+          <t>Stay alert to scams. Did you receive a renewal message from a Gmail or Yahoo address? What should you do?</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Cust</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE47" s="2" t="n">
-        <v>46104.60347222222</v>
+        <v>46104.5</v>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
@@ -8291,22 +8283,22 @@
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
+          <t>2. Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Every day I follow up, and they say “wait 5 more days.” Yet, they’re busy educating customers on small delivery fees. • I’ve been waiting a month for this bank to process my account application. • Can I trust them with my money?</t>
+          <t>Did you receive a renewal message from a Gmail or Yahoo address?</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank (ENBD)</t>
+          <t>Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AK47" t="n">
@@ -8314,7 +8306,7 @@
       </c>
       <c r="AL47" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8324,75 +8316,72 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2035879255176093818</t>
+          <t>2035976151764549748</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://x.com/ShagilShams/status/2035879255176093818</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2035976151764549748</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://x.com/ShagilShams</t>
+          <t>https://x.com/EmiratesNBD_KSA</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ShagilShams</t>
+          <t>EmiratesNBD_KSA</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Shagil Shams</t>
+          <t>EmiratesNBD KSA</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1618258890503901184/GcGIQNmE_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1762427762424385536/iUFFKIOK_bigger.jpg</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Hi Team , 
-I'm in India , Unable to transfer money to myself. Payment getting declined . 
-Please check .</t>
+          <t>@EmiratesNBD_KSA 
+I raised mail to customer care regarding flight amount deduction descripancy twice but didn't hear from Emirates NBD. This is not acceptable at all. I am very much disappointed with customer care service of Emirates NBD. Zero star.</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; Hi Team , 
-I&amp;#39;m in India , Unable to transfer money to myself. Payment getting declined . 
-Please check .</t>
+          <t>Hi Rakshit, our team tried to contact you, but there was no answer from your side, we have asked our team to contact you again as soon as possible.</t>
         </is>
       </c>
       <c r="K48" t="b">
         <v>0</v>
       </c>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>['RakshtVaghasiya']</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Mar 23</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Mar 23, 2026 · 12:40 AM UTC</t>
+          <t>Mar 23, 2026 · 7:05 AM UTC</t>
         </is>
       </c>
       <c r="P48" s="2" t="n">
-        <v>46104.02777777778</v>
+        <v>46104.29513888889</v>
       </c>
       <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>['https://x.com/EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="R48" t="inlineStr"/>
       <c r="S48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
         <v>0</v>
@@ -8410,24 +8399,29 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Hi Team , 
-I'm in India , Unable to transfer money to myself. Payment getting declined . 
-Please check .</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr"/>
-      <c r="Z48" t="inlineStr"/>
+          <t>Hi Rakshit, our team tried to contact you, but there was no answer from your side, we have asked our team to contact you again as soon as possible.</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_KSA/status/2035976151764549748</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA 
+I raised mail to customer care regarding flight amount deduction descripancy twice but didn't hear from Emirates NBD. This is not acceptable at all. I am very much disappointed with customer care service of Emirates NBD. Zero star.</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Hi Team , 
-I'm in India , Unable to transfer money to myself. Payment getting declined . 
-Please check .</t>
+          <t>@EmiratesNBD_KSA 
+I raised mail to customer care regarding flight amount deduction descripancy twice but didn't hear from Emirates NBD. This is not acceptable at all. I am very much disappointed with customer care service of Emirates NBD. Zero star.</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>Hi Team, 
-I'm in India and unable to transfer money to myself. The payment is getting declined. Please check.</t>
+          <t>I raised an email to customer care regarding the discrepancy in the flight amount deduction twice but didn't hear from Emirates NBD. This is not acceptable at all. I am very disappointed with the customer care service of Emirates NBD. Zero stars.</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -8441,7 +8435,7 @@
         </is>
       </c>
       <c r="AE48" s="2" t="n">
-        <v>46104.19444444445</v>
+        <v>46104.46180555555</v>
       </c>
       <c r="AF48" t="inlineStr">
         <is>
@@ -8460,7 +8454,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Hi Team, I'm in India and unable to transfer money to myself. • The payment is getting declined.</t>
+          <t>I raised an email to customer care regarding the discrepancy in the flight amount deduction twice but didn't hear from Emirates NBD. • I am very disappointed with the customer care service of Emirates NBD. • This is not acceptable at all.</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
@@ -8473,7 +8467,7 @@
       </c>
       <c r="AL48" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>RakshtVaghasiya</t>
         </is>
       </c>
     </row>
@@ -8483,67 +8477,71 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2036081518607749454</t>
+          <t>2036027630722617585</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://x.com/mridulrb/status/2036081518607749454</t>
+          <t>https://x.com/Nightowl263/status/2036027630722617585</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://x.com/mridulrb</t>
+          <t>https://x.com/Nightowl263</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>mridulrb</t>
+          <t>Nightowl263</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mridul Bhandari</t>
+          <t>Priya George</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1260543244464787456/hi1vRK1o_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1718237295055433728/mRkQyUDb_bigger.jpg</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Money transfers on ENBD X don't support SWIFT-only beneficiaries for Indian accounts like GIFT City — the app forces an IFSC lookup, but GIFT City IBUs have no IFSC code, completely hindering transfers. Please allow manual SWIFT entry. #GIFTCITY #NRI</t>
+          <t>I’ve been waiting a month for this bank to process account application. Every day I follow up, they say “wait 5 more days.” And yet, they’re busy educating customers on small delivery fees. Can I trust them with my money? 😕 what would you do in this case ? #UnitedAgainstFraud</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; Money transfers on ENBD X don&amp;#39;t support SWIFT-only beneficiaries for Indian accounts like GIFT City — the app forces an IFSC lookup, but GIFT City IBUs have no IFSC code, completely hindering transfers. Please allow manual SWIFT entry. &lt;a href="/search?f=tweets&amp;amp;q=%23GIFTCITY"&gt;#GIFTCITY&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23NRI"&gt;#NRI&lt;/a&gt;</t>
+          <t>I’ve been waiting a month for this bank to process account application. Every day I follow up, they say “wait 5 more days.” And yet, they’re busy educating customers on small delivery fees. Can I trust them with my money? 😕 what would you do in this case ? &lt;a href="/search?f=tweets&amp;amp;q=%23UnitedAgainstFraud"&gt;#UnitedAgainstFraud&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K49" t="b">
         <v>0</v>
       </c>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Mar 23, 2026 · 2:03 PM UTC</t>
+          <t>Mar 23, 2026 · 10:29 AM UTC</t>
         </is>
       </c>
       <c r="P49" s="2" t="n">
-        <v>46104.58541666667</v>
+        <v>46104.43680555555</v>
       </c>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr">
         <is>
-          <t>['https://x.com/EmiratesNBD_AE', 'https://x.com/search?f=tweets&amp;q=%23GIFTCITY', 'https://x.com/search?f=tweets&amp;q=%23NRI']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23UnitedAgainstFraud']</t>
         </is>
       </c>
       <c r="S49" t="n">
@@ -8556,7 +8554,7 @@
         <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
@@ -8565,19 +8563,19 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Money transfers on ENBD X don't support SWIFT-only beneficiaries for Indian accounts like GIFT City — the app forces an IFSC lookup, but GIFT City IBUs have no IFSC code, completely hindering transfers. Please allow manual SWIFT entry. #GIFTCITY #NRI</t>
+          <t>I’ve been waiting a month for this bank to process account application. Every day I follow up, they say “wait 5 more days.” And yet, they’re busy educating customers on small delivery fees. Can I trust them with my money? 😕 what would you do in this case ? #UnitedAgainstFraud</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Money transfers on ENBD X don't support SWIFT-only beneficiaries for Indian accounts like GIFT City — the app forces an IFSC lookup, but GIFT City IBUs have no IFSC code, completely hindering transfers. Please allow manual SWIFT entry. #GIFTCITY #NRI</t>
+          <t>I’ve been waiting a month for this bank to process account application. Every day I follow up, they say “wait 5 more days.” And yet, they’re busy educating customers on small delivery fees. Can I trust them with my money? 😕 what would you do in this case ? #UnitedAgainstFraud</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>Money transfers on ENBD X don't support SWIFT-only beneficiaries for Indian accounts like GIFT City — the app forces an IFSC lookup, but GIFT City IBUs have no IFSC code, completely hindering transfers. Please allow manual SWIFT entry. #GIFTCITY #NRI</t>
+          <t>I’ve been waiting a month for this bank to process my account application. Every day I follow up, and they say “wait 5 more days.” And yet, they’re busy educating customers on small delivery fees. Can I trust them with my money? 😕 What would you do in this case? #UnitedAgainstFraud</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -8591,7 +8589,7 @@
         </is>
       </c>
       <c r="AE49" s="2" t="n">
-        <v>46104.75208333333</v>
+        <v>46104.60347222222</v>
       </c>
       <c r="AF49" t="inlineStr">
         <is>
@@ -8610,7 +8608,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Please allow manual SWIFT entry.</t>
+          <t>Every day I follow up, and they say “wait 5 more days.” And yet, they’re busy educating customers on small delivery fees. • I’ve been waiting a month for this bank to process my account application. • Can I trust them with my money?</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
@@ -8623,7 +8621,7 @@
       </c>
       <c r="AL49" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
     </row>
@@ -8633,43 +8631,47 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2035983374574059838</t>
+          <t>2035879255176093818</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://x.com/netdiscussion/status/2035983374574059838</t>
+          <t>https://x.com/ShagilShams/status/2035879255176093818</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://x.com/netdiscussion</t>
+          <t>https://x.com/ShagilShams</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>netdiscussion</t>
+          <t>ShagilShams</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Muhammad Kashif Ashraf</t>
+          <t>Shagil Shams</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1618258890503901184/GcGIQNmE_bigger.jpg</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA I don't understand, why no response/update on any official Channel by phone, email, Twitter??, since 8 of March, dispute case is registered.</t>
+          <t>@EmiratesNBD_AE Hi Team , 
+I'm in India , Unable to transfer money to myself. Payment getting declined . 
+Please check .</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>&lt;a href="/EmiratesNBD_KSA" title="EmiratesNBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt; I don&amp;#39;t understand, why no response/update on any official Channel by phone, email, Twitter??, since 8 of March, dispute case is registered.</t>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; Hi Team , 
+I&amp;#39;m in India , Unable to transfer money to myself. Payment getting declined . 
+Please check .</t>
         </is>
       </c>
       <c r="K50" t="b">
@@ -8679,21 +8681,21 @@
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>Mar 23</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Mar 23, 2026 · 7:33 AM UTC</t>
+          <t>Mar 23, 2026 · 12:40 AM UTC</t>
         </is>
       </c>
       <c r="P50" s="2" t="n">
-        <v>46104.31458333333</v>
+        <v>46104.02777777778</v>
       </c>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr">
         <is>
-          <t>['https://x.com/EmiratesNBD_KSA']</t>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="S50" t="n">
@@ -8706,7 +8708,7 @@
         <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
@@ -8715,19 +8717,24 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA I don't understand, why no response/update on any official Channel by phone, email, Twitter??, since 8 of March, dispute case is registered.</t>
+          <t>@EmiratesNBD_AE Hi Team , 
+I'm in India , Unable to transfer money to myself. Payment getting declined . 
+Please check .</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA I don't understand, why no response/update on any official Channel by phone, email, Twitter??, since 8 of March, dispute case is registered.</t>
+          <t>@EmiratesNBD_AE Hi Team , 
+I'm in India , Unable to transfer money to myself. Payment getting declined . 
+Please check .</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>I don't understand why there has been no response or update on any official channel by phone, email, or Twitter since March 8, when the dispute case was registered.</t>
+          <t>Hi Team, 
+I'm in India and unable to transfer money to myself. The payment is getting declined. Please check.</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -8741,7 +8748,7 @@
         </is>
       </c>
       <c r="AE50" s="2" t="n">
-        <v>46104.48125</v>
+        <v>46104.19444444445</v>
       </c>
       <c r="AF50" t="inlineStr">
         <is>
@@ -8760,7 +8767,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>I don't understand why there has been no response or update on any official channel by phone, email, or Twitter since March 8, when the dispute case was registered.</t>
+          <t>Hi Team, I'm in India and unable to transfer money to myself. • The payment is getting declined.</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
@@ -8783,159 +8790,459 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2036269961057018273</t>
+          <t>2036081518607749454</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://x.com/saimas89/status/2036269961057018273</t>
+          <t>https://x.com/mridulrb/status/2036081518607749454</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://x.com/saimas89</t>
+          <t>https://x.com/mridulrb</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>saimas89</t>
+          <t>mridulrb</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Saima | صائمہ</t>
+          <t>Mridul Bhandari</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1613505962098282497/lNPa9Or8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1260543244464787456/hi1vRK1o_bigger.jpg</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Money transfers on ENBD X don't support SWIFT-only beneficiaries for Indian accounts like GIFT City — the app forces an IFSC lookup, but GIFT City IBUs have no IFSC code, completely hindering transfers. Please allow manual SWIFT entry. #GIFTCITY #NRI</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; Money transfers on ENBD X don&amp;#39;t support SWIFT-only beneficiaries for Indian accounts like GIFT City — the app forces an IFSC lookup, but GIFT City IBUs have no IFSC code, completely hindering transfers. Please allow manual SWIFT entry. &lt;a href="/search?f=tweets&amp;amp;q=%23GIFTCITY"&gt;#GIFTCITY&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23NRI"&gt;#NRI&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K51" t="b">
+        <v>0</v>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Mar 23, 2026 · 2:03 PM UTC</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="n">
+        <v>46104.58541666667</v>
+      </c>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_AE', 'https://x.com/search?f=tweets&amp;q=%23GIFTCITY', 'https://x.com/search?f=tweets&amp;q=%23NRI']</t>
+        </is>
+      </c>
+      <c r="S51" t="n">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" t="n">
+        <v>64</v>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Money transfers on ENBD X don't support SWIFT-only beneficiaries for Indian accounts like GIFT City — the app forces an IFSC lookup, but GIFT City IBUs have no IFSC code, completely hindering transfers. Please allow manual SWIFT entry. #GIFTCITY #NRI</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Money transfers on ENBD X don't support SWIFT-only beneficiaries for Indian accounts like GIFT City — the app forces an IFSC lookup, but GIFT City IBUs have no IFSC code, completely hindering transfers. Please allow manual SWIFT entry. #GIFTCITY #NRI</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>Money transfers on ENBD X don't support SWIFT-only beneficiaries for Indian accounts like GIFT City — the app forces an IFSC lookup, but GIFT City IBUs have no IFSC code, completely hindering transfers. Please allow manual SWIFT entry.</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AE51" s="2" t="n">
+        <v>46104.75208333333</v>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>23-03-2026</t>
+        </is>
+      </c>
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>Please allow manual SWIFT entry.</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK51" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL51" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2035983374574059838</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://x.com/netdiscussion/status/2035983374574059838</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://x.com/netdiscussion</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>netdiscussion</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Muhammad Kashif Ashraf</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA I don't understand, why no response/update on any official Channel by phone, email, Twitter??, since 8 of March, dispute case is registered.</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>&lt;a href="/EmiratesNBD_KSA" title="EmiratesNBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt; I don&amp;#39;t understand, why no response/update on any official Channel by phone, email, Twitter??, since 8 of March, dispute case is registered.</t>
+        </is>
+      </c>
+      <c r="K52" t="b">
+        <v>0</v>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Mar 23, 2026 · 7:33 AM UTC</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="n">
+        <v>46104.31458333333</v>
+      </c>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="S52" t="n">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" t="n">
+        <v>27</v>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA I don't understand, why no response/update on any official Channel by phone, email, Twitter??, since 8 of March, dispute case is registered.</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA I don't understand, why no response/update on any official Channel by phone, email, Twitter??, since 8 of March, dispute case is registered.</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>I don't understand why there has been no response or update on any official channel by phone, email, or Twitter since March 8, when the dispute case was registered.</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AE52" s="2" t="n">
+        <v>46104.48125</v>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>23-03-2026</t>
+        </is>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>I don't understand why there has been no response or update on any official channel by phone, email, or Twitter since March 8, when the dispute case was registered.</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK52" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL52" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2036269961057018273</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://x.com/saimas89/status/2036269961057018273</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://x.com/saimas89</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>saimas89</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Saima | صائمہ</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1613505962098282497/lNPa9Or8_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
         <is>
           <t>.@flyspicejet booked a flight DXB-BOM, you guys cancelled, I requested a refund which was “initiated” on March 10, 2026.
 It has now been more than 7 working days, but the refund has still not been credited to me as stated/promised.
 @DGCAIndia @RamMNK @MoCA_GoI @jagograhakjago https://t.co/L4So4pzq9f</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>Can you not take another 7 days and give me the refund sooner? FYI I have paid using my ENBD card.</t>
         </is>
       </c>
-      <c r="K51" t="b">
-        <v>0</v>
-      </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
+      <c r="K53" t="b">
+        <v>0</v>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
         <is>
           <t>['flyspicejet']</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>1h</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>2h</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
         <is>
           <t>Mar 24, 2026 · 2:32 AM UTC</t>
         </is>
       </c>
-      <c r="P51" s="2" t="n">
+      <c r="P53" s="2" t="n">
         <v>46105.10555555556</v>
       </c>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="n">
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="n">
         <v>1</v>
       </c>
-      <c r="T51" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" t="n">
-        <v>12</v>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" t="n">
+        <v>17</v>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
         <is>
           <t>Can you not take another 7 days and give me the refund sooner? FYI I have paid using my ENBD card.</t>
         </is>
       </c>
-      <c r="Y51" t="inlineStr">
+      <c r="Y53" t="inlineStr">
         <is>
           <t>https://x.com/saimas89/status/2036269961057018273</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
+      <c r="Z53" t="inlineStr">
         <is>
           <t>.@flyspicejet booked a flight DXB-BOM, you guys cancelled, I requested a refund which was “initiated” on March 10, 2026.
 It has now been more than 7 working days, but the refund has still not been credited to me as stated/promised.
 @DGCAIndia @RamMNK @MoCA_GoI @jagograhakjago https://t.co/L4So4pzq9f</t>
         </is>
       </c>
-      <c r="AA51" t="inlineStr">
+      <c r="AA53" t="inlineStr">
         <is>
           <t>.@flyspicejet booked a flight DXB-BOM, you guys cancelled, I requested a refund which was “initiated” on March 10, 2026.
 It has now been more than 7 working days, but the refund has still not been credited to me as stated/promised.
 @DGCAIndia @RamMNK @MoCA_GoI @jagograhakjago https://t.co/L4So4pzq9f</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>I booked a flight from Dubai to Mumbai with SpiceJet, which you guys canceled. I requested a refund that was "initiated" on March 10, 2026. It has now been more than 7 working days, but the refund has still not been credited to me as stated/promised.</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>I booked a flight from DXB to BOM with @flyspicejet, which you guys canceled. I requested a refund that was "initiated" on March 10, 2026. It has now been more than 7 working days, but the refund has still not been credited to me as stated/promised.</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="AD51" t="inlineStr">
+      <c r="AD53" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="AE51" s="2" t="n">
+      <c r="AE53" s="2" t="n">
         <v>46105.27222222222</v>
       </c>
-      <c r="AF51" t="inlineStr">
+      <c r="AF53" t="inlineStr">
         <is>
           <t>24-03-2026</t>
         </is>
       </c>
-      <c r="AG51" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH51" t="inlineStr">
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH53" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>It has now been more than 7 working days, but the refund has still not been credited to me as stated/promised. • I requested a refund that was "initiated" on March 10, 2026. • I booked a flight from Dubai to Mumbai with SpiceJet, which you guys canceled.</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>It has now been more than 7 working days, but the refund has still not been credited to me as stated/promised. • I requested a refund that was "initiated" on March 10, 2026. • I booked a flight from DXB to BOM with @flyspicejet, which you guys canceled.</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
         <is>
           <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AK51" t="n">
+      <c r="AK53" t="n">
         <v>2026</v>
       </c>
-      <c r="AL51" t="inlineStr">
+      <c r="AL53" t="inlineStr">
         <is>
           <t>flyspicejet</t>
         </is>

--- a/check2.xlsx
+++ b/check2.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL63"/>
+  <dimension ref="A1:AL64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,12 +625,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2036654307596992707</t>
+          <t>2036665227840803080</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2036654307596992707</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2036665227840803080</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -656,40 +656,40 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Your financial tip of the week
-#FinancialWellbeing #EmiratesNBDTips #SmartMoney #FinWell https://t.co/FUf7oWsLyQ</t>
+          <t>What would you do if a delivery agent asks for a ‘small online fee’?
+Stay safe. Stay vigilant. #UnitedAgainstFraud
+https://t.co/YpRWtBZrhq</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Your financial tip of the week
-&lt;a href="/search?f=tweets&amp;amp;q=%23FinancialWellbeing"&gt;#FinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBDTips"&gt;#EmiratesNBDTips&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoney"&gt;#SmartMoney&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23FinWell"&gt;#FinWell&lt;/a&gt;</t>
+          <t>Thanks for writing to us, kindly note that we have replied to your email</t>
         </is>
       </c>
       <c r="K2" t="b">
         <v>0</v>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>['ZahidanMuhamma']</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>4m</t>
+          <t>37m</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 4:00 AM UTC</t>
+          <t>Mar 25, 2026 · 4:43 AM UTC</t>
         </is>
       </c>
       <c r="P2" s="2" t="n">
-        <v>46106.16666666666</v>
+        <v>46106.19652777778</v>
       </c>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23FinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23EmiratesNBDTips', 'https://x.com/search?f=tweets&amp;q=%23SmartMoney', 'https://x.com/search?f=tweets&amp;q=%23FinWell']</t>
-        </is>
-      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
         <v>0</v>
       </c>
@@ -700,7 +700,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -709,35 +709,37 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Your financial tip of the week
-#FinancialWellbeing #EmiratesNBDTips #SmartMoney #FinWell</t>
+          <t>Thanks for writing to us, kindly note that we have replied to your email</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2036654307596992707</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2036665227840803080</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Your financial tip of the week
-#FinancialWellbeing #EmiratesNBDTips #SmartMoney #FinWell https://t.co/FUf7oWsLyQ</t>
+          <t>What would you do if a delivery agent asks for a ‘small online fee’?
+Stay safe. Stay vigilant. #UnitedAgainstFraud
+https://t.co/YpRWtBZrhq</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Your financial tip of the week
-#FinancialWellbeing #EmiratesNBDTips #SmartMoney #FinWell https://t.co/FUf7oWsLyQ</t>
+          <t>What would you do if a delivery agent asks for a ‘small online fee’?
+Stay safe. Stay vigilant. #UnitedAgainstFraud
+https://t.co/YpRWtBZrhq</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Your financial tip of the week</t>
+          <t>What would you do if a delivery agent asks for a 'small online fee'? 
+Stay safe. Stay vigilant. #UnitedAgainstFraud</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Cust</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -746,7 +748,7 @@
         </is>
       </c>
       <c r="AE2" s="2" t="n">
-        <v>46106.33333333334</v>
+        <v>46106.36319444444</v>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
@@ -765,7 +767,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Your financial tip of the week</t>
+          <t>What would you do if a delivery agent asks for a 'small online fee'?</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -778,7 +780,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>ZahidanMuhamma</t>
         </is>
       </c>
     </row>
@@ -788,12 +790,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2036654307383111761</t>
+          <t>2036654307596992707</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2036654307383111761</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2036654307596992707</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -827,8 +829,8 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>نصيحتك المالية لهذا الأسبوع
-&lt;a href="/search?f=tweets&amp;amp;q=%23FinancialWellbeing"&gt;#FinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBDTips"&gt;#EmiratesNBDTips&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23FinWell"&gt;#FinWell&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoney"&gt;#SmartMoney&lt;/a&gt;</t>
+          <t>Your financial tip of the week
+&lt;a href="/search?f=tweets&amp;amp;q=%23FinancialWellbeing"&gt;#FinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBDTips"&gt;#EmiratesNBDTips&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoney"&gt;#SmartMoney&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23FinWell"&gt;#FinWell&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K3" t="b">
@@ -838,7 +840,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>4m</t>
+          <t>1h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -852,7 +854,7 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23FinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23EmiratesNBDTips', 'https://x.com/search?f=tweets&amp;q=%23FinWell', 'https://x.com/search?f=tweets&amp;q=%23SmartMoney']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23FinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23EmiratesNBDTips', 'https://x.com/search?f=tweets&amp;q=%23SmartMoney', 'https://x.com/search?f=tweets&amp;q=%23FinWell']</t>
         </is>
       </c>
       <c r="S3" t="n">
@@ -865,7 +867,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>42</v>
+        <v>227</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -874,13 +876,13 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>نصيحتك المالية لهذا الأسبوع
-#FinancialWellbeing #EmiratesNBDTips #FinWell #SmartMoney</t>
+          <t>Your financial tip of the week
+#FinancialWellbeing #EmiratesNBDTips #SmartMoney #FinWell</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2036654307383111761</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2036654307596992707</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -902,7 +904,7 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>A new month with more winners.
-Congratulations to the grand prize winner of the ROX 01 car, and to the winners of the 10-gram gold piece for participating in the "It's Time to Win Grand Prizes" campaign offered by business banking for January 2026.
+Congratulations to the grand prize winner of a ROX 01 car, and to the winners of the 10-gram gold piece for participating in the "It's Time to Win Grand Prizes" campaign offered by business banking for January 2026.
 Continue using your business account to carry out foreign exchange transactions and trade financing to increase your company's chances of winning. The offer is valid until March 31, 2026.</t>
         </is>
       </c>
@@ -959,36 +961,199 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2036586113079328797</t>
+          <t>2036654307383111761</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/semeet/status/2036586113079328797</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2036654307383111761</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://x.com/semeet</t>
+          <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>semeet</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>seema shelat</t>
+          <t>Emirates NBD</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1376978771538898945/X-iaSTLK_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
+        <is>
+          <t>نصيحتك المالية لهذا الأسبوع
+#FinancialWellbeing #EmiratesNBDTips #FinWell #SmartMoney https://t.co/61XmkWn3XT</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>نصيحتك المالية لهذا الأسبوع
+&lt;a href="/search?f=tweets&amp;amp;q=%23FinancialWellbeing"&gt;#FinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBDTips"&gt;#EmiratesNBDTips&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23FinWell"&gt;#FinWell&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoney"&gt;#SmartMoney&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Mar 25, 2026 · 4:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>46106.16666666666</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23FinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23EmiratesNBDTips', 'https://x.com/search?f=tweets&amp;q=%23FinWell', 'https://x.com/search?f=tweets&amp;q=%23SmartMoney']</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>210</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>نصيحتك المالية لهذا الأسبوع
+#FinancialWellbeing #EmiratesNBDTips #FinWell #SmartMoney</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2036654307383111761</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>نصيحتك المالية لهذا الأسبوع
+#FinancialWellbeing #EmiratesNBDTips #FinWell #SmartMoney https://t.co/61XmkWn3XT</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>نصيحتك المالية لهذا الأسبوع
+#FinancialWellbeing #EmiratesNBDTips #FinWell #SmartMoney https://t.co/61XmkWn3XT</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>Your financial advice for this week</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Bank</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE4" s="2" t="n">
+        <v>46106.33333333334</v>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>25-03-2026</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Your financial advice for this week</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK4" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2036586113079328797</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://x.com/semeet/status/2036586113079328797</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://x.com/semeet</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>semeet</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>seema shelat</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1376978771538898945/X-iaSTLK_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
         <is>
           <t>Another month. More winners.
 Congratulations to the ROX 01 grand prize winner and 10-gram gold winners from our Business Banking ‘Time to Win Big’ January 2026 draw.
@@ -996,63 +1161,63 @@
 Offer is valid until 31 March 2026.</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Congratulations 🎊</t>
         </is>
       </c>
-      <c r="K4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>4h</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>5h</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>Mar 24, 2026 · 11:29 PM UTC</t>
         </is>
       </c>
-      <c r="P4" s="2" t="n">
+      <c r="P5" s="2" t="n">
         <v>46105.97847222222</v>
       </c>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1</v>
-      </c>
-      <c r="W4" t="inlineStr">
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>5</v>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>Congratulations 🎊</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>https://x.com/semeet/status/2036586113079328797</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>Another month. More winners.
 Congratulations to the ROX 01 grand prize winner and 10-gram gold winners from our Business Banking ‘Time to Win Big’ January 2026 draw.
@@ -1060,7 +1225,7 @@
 Offer is valid until 31 March 2026.</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Another month. More winners.
 Congratulations to the ROX 01 grand prize winner and 10-gram gold winners from our Business Banking ‘Time to Win Big’ January 2026 draw.
@@ -1068,7 +1233,7 @@
 Offer is valid until 31 March 2026.</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>Another month. More winners.
 Congratulations to the ROX 01 grand prize winner and 10-gram gold winners from our Business Banking ‘Time to Win Big’ January 2026 draw.
@@ -1076,205 +1241,37 @@
 Offer is valid until 31 March 2026.</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="AE4" s="2" t="n">
+      <c r="AE5" s="2" t="n">
         <v>46106.14513888889</v>
       </c>
-      <c r="AF4" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>25-03-2026</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AH5" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AI5" t="inlineStr">
         <is>
           <t>Congratulations to the ROX 01 grand prize winner and 10-gram gold winners from our Business Banking ‘Time to Win Big’ January 2026 draw. • Continue using your Business Account for all your foreign exchange and trade finance transactions for a chance to win in the next draw. • Offer is valid until 31 March 2026.</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AK4" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>EmiratesNBD_AE</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2036561511594991637</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://x.com/Ridvan_Dayanc/status/2036561511594991637</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>https://x.com/Ridvan_Dayanc</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Ridvan_Dayanc</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Rıdvan Dayanç</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/891319667645702144/MaGwpQS6_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>General Information ⚠️
-Nothing happened 🤲
-#dubai #attack #besafe https://t.co/nVS9pjoGAj</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>General Information ⚠️
-All clear 🤲
-&lt;a href="/search?f=tweets&amp;amp;q=%23dubai"&gt;#dubai&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23attack"&gt;#attack&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23besafe"&gt;#besafe&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K5" t="b">
-        <v>0</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>6h</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Mar 24, 2026 · 9:51 PM UTC</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="n">
-        <v>46105.91041666667</v>
-      </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23dubai', 'https://x.com/search?f=tweets&amp;q=%23attack', 'https://x.com/search?f=tweets&amp;q=%23besafe']</t>
-        </is>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>218</v>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>General Information ⚠️
-All clear 🤲
-#dubai #attack #besafe</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>https://x.com/Ridvan_Dayanc/status/2036561511594991637</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>General Information ⚠️
-Nothing happened 🤲
-#dubai #attack #besafe https://t.co/nVS9pjoGAj</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>General Information ⚠️
-Nothing happened 🤲
-#dubai #attack #besafe https://t.co/nVS9pjoGAj</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>General Information ⚠️ Nothing happened 🤲 #dubai #attack #besafe</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AE5" s="2" t="n">
-        <v>46106.07708333333</v>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>25-03-2026</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>General Information ⚠️ Nothing happened 🤲 #dubai #attack #besafe</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1287,7 +1284,7 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
     </row>
@@ -1297,71 +1294,73 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2036558462906409266</t>
+          <t>2036561511594991637</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://x.com/ZahidanMuhamma/status/2036558462906409266</t>
+          <t>https://x.com/Ridvan_Dayanc/status/2036561511594991637</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://x.com/ZahidanMuhamma</t>
+          <t>https://x.com/Ridvan_Dayanc</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ZahidanMuhamma</t>
+          <t>Ridvan_Dayanc</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Muhammad Zahidan</t>
+          <t>Rıdvan Dayanç</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1827047486680137728/R86Fb-lT_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/891319667645702144/MaGwpQS6_bigger.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>What would you do if a delivery agent asks for a ‘small online fee’?
-Stay safe. Stay vigilant. #UnitedAgainstFraud
-https://t.co/YpRWtBZrhq</t>
+          <t>General Information ⚠️
+Nothing happened 🤲
+#dubai #attack #besafe https://t.co/nVS9pjoGAj</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>It&amp;#39;s a joke I will wait for 90 days to receive my fund what a joke</t>
+          <t>General Information ⚠️
+All clear 🤲
+&lt;a href="/search?f=tweets&amp;amp;q=%23dubai"&gt;#dubai&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23attack"&gt;#attack&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23besafe"&gt;#besafe&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K6" t="b">
         <v>0</v>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>6h</t>
+          <t>7h</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 9:39 PM UTC</t>
+          <t>Mar 24, 2026 · 9:51 PM UTC</t>
         </is>
       </c>
       <c r="P6" s="2" t="n">
-        <v>46105.90208333333</v>
+        <v>46105.91041666667</v>
       </c>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23dubai', 'https://x.com/search?f=tweets&amp;q=%23attack', 'https://x.com/search?f=tweets&amp;q=%23besafe']</t>
+        </is>
+      </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
@@ -1372,7 +1371,7 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>5</v>
+        <v>244</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1381,32 +1380,33 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>It's a joke I will wait for 90 days to receive my fund what a joke</t>
+          <t>General Information ⚠️
+All clear 🤲
+#dubai #attack #besafe</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>https://x.com/ZahidanMuhamma/status/2036558462906409266</t>
+          <t>https://x.com/Ridvan_Dayanc/status/2036561511594991637</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>What would you do if a delivery agent asks for a ‘small online fee’?
-Stay safe. Stay vigilant. #UnitedAgainstFraud
-https://t.co/YpRWtBZrhq</t>
+          <t>General Information ⚠️
+Nothing happened 🤲
+#dubai #attack #besafe https://t.co/nVS9pjoGAj</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>What would you do if a delivery agent asks for a ‘small online fee’?
-Stay safe. Stay vigilant. #UnitedAgainstFraud
-https://t.co/YpRWtBZrhq</t>
+          <t>General Information ⚠️
+Nothing happened 🤲
+#dubai #attack #besafe https://t.co/nVS9pjoGAj</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>What would you do if a delivery agent asks for a 'small online fee'? 
-Stay safe. Stay vigilant. #UnitedAgainstFraud</t>
+          <t>General Information ⚠️ Nothing happened 🤲 #dubai #attack #besafe</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="AE6" s="2" t="n">
-        <v>46106.06875</v>
+        <v>46106.07708333333</v>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>What would you do if a delivery agent asks for a 'small online fee'?</t>
+          <t>General Information ⚠️ Nothing happened 🤲 #dubai #attack #besafe</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1508,7 +1508,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>6h</t>
+          <t>7h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1531,7 +1531,7 @@
         <v>1</v>
       </c>
       <c r="V7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1709,7 +1709,7 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1844,10 +1844,10 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Buy your hair essentials with 0% down payment, 0% interest, and 0% processing fees on 6 months from CH&amp;amp;BE through their website using Emirates NBD credit cards.
+          <t>Buy your hair essentials with 0% down payment, 0% interest, and 0% processing fees on 6 months from CH&amp;BE through their website using Emirates NBD credit cards.
 Offer is valid till 15th of April 2026.
 Terms and conditions apply.
-Tax registration number: 204-897-319 https://t.co/rNTFQ9BURr</t>
+Tax registration number: 204-897-319</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1865,7 +1865,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>12h</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1888,7 +1888,7 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1903,31 +1903,20 @@
 Tax registration number: 204-897-319</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_EGY/status/2036488212902731999</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Buy your hair essentials with 0% down payment, 0% interest, and 0% processing fees on 6 months from CH&amp;amp;BE through their website using Emirates NBD credit cards.
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Buy your hair essentials with 0% down payment, 0% interest, and 0% processing fees on 6 months from CH&amp;BE through their website using Emirates NBD credit cards.
 Offer is valid till 15th of April 2026.
 Terms and conditions apply.
-Tax registration number: 204-897-319 https://t.co/rNTFQ9BURr</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Buy your hair essentials with 0% down payment, 0% interest, and 0% processing fees on 6 months from CH&amp;amp;BE through their website using Emirates NBD credit cards.
-Offer is valid till 15th of April 2026.
-Terms and conditions apply.
-Tax registration number: 204-897-319 https://t.co/rNTFQ9BURr</t>
+Tax registration number: 204-897-319</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
           <t>Buy your hair essentials with 0% down payment, 0% interest, and 0% processing fees for 6 months from CH&amp;BE through their website using Emirates NBD credit cards. 
-Offer is valid until April 15, 2026. 
+The offer is valid until April 15, 2026. 
 Terms and conditions apply. 
 Tax registration number: 204-897-319</t>
         </is>
@@ -1962,7 +1951,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Buy your hair essentials with 0% down payment, 0% interest, and 0% processing fees for 6 months from CH&amp;BE through their website using Emirates NBD credit cards. • Tax registration number: 204-897-319 • Offer is valid until April 15, 2026.</t>
+          <t>Buy your hair essentials with 0% down payment, 0% interest, and 0% processing fees for 6 months from CH&amp;BE through their website using Emirates NBD credit cards. • Tax registration number: 204-897-319 • The offer is valid until April 15, 2026.</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -2016,81 +2005,92 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
+          <t>استعدي لإطلالة جديدة واشتري منتاجات العناية بالشعر من CH&amp;amp;BE ب0% مقدم، 0% فوائد، و 0% مصاريف إدارية على 6 أشهر من خلال الموقع الإلكتروني باستخدام بطاقات بنك الإمارات دبي الوطني الائتمانية.
+العرض سارى حتى 15 أبريل 2026
+تطبق الشروط والأحكام.
+رقم التسجيل الضريبي: 319-897-204 https://t.co/uTR0Y8lyWz</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>استعدي لإطلالة جديدة واشتري منتاجات العناية بالشعر من CH&amp;amp;BE ب0% مقدم، 0% فوائد، و 0% مصاريف إدارية على 6 أشهر من خلال الموقع الإلكتروني باستخدام بطاقات بنك الإمارات دبي الوطني الائتمانية.
+العرض سارى حتى 15 أبريل 2026
+تطبق الشروط والأحكام.
+رقم التسجيل الضريبي: 319-897-204</t>
+        </is>
+      </c>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>12h</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Mar 24, 2026 · 5:00 PM UTC</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>46105.70833333334</v>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>55</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
           <t>استعدي لإطلالة جديدة واشتري منتاجات العناية بالشعر من CH&amp;BE ب0% مقدم، 0% فوائد، و 0% مصاريف إدارية على 6 أشهر من خلال الموقع الإلكتروني باستخدام بطاقات بنك الإمارات دبي الوطني الائتمانية.
 العرض سارى حتى 15 أبريل 2026
 تطبق الشروط والأحكام.
 رقم التسجيل الضريبي: 319-897-204</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_EGY/status/2036488212877648052</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
         <is>
           <t>استعدي لإطلالة جديدة واشتري منتاجات العناية بالشعر من CH&amp;amp;BE ب0% مقدم، 0% فوائد، و 0% مصاريف إدارية على 6 أشهر من خلال الموقع الإلكتروني باستخدام بطاقات بنك الإمارات دبي الوطني الائتمانية.
 العرض سارى حتى 15 أبريل 2026
 تطبق الشروط والأحكام.
-رقم التسجيل الضريبي: 319-897-204</t>
-        </is>
-      </c>
-      <c r="K10" t="b">
-        <v>0</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>11h</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Mar 24, 2026 · 5:00 PM UTC</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="n">
-        <v>46105.70833333334</v>
-      </c>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>52</v>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>استعدي لإطلالة جديدة واشتري منتاجات العناية بالشعر من CH&amp;BE ب0% مقدم، 0% فوائد، و 0% مصاريف إدارية على 6 أشهر من خلال الموقع الإلكتروني باستخدام بطاقات بنك الإمارات دبي الوطني الائتمانية.
+رقم التسجيل الضريبي: 319-897-204 https://t.co/uTR0Y8lyWz</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>استعدي لإطلالة جديدة واشتري منتاجات العناية بالشعر من CH&amp;amp;BE ب0% مقدم، 0% فوائد، و 0% مصاريف إدارية على 6 أشهر من خلال الموقع الإلكتروني باستخدام بطاقات بنك الإمارات دبي الوطني الائتمانية.
 العرض سارى حتى 15 أبريل 2026
 تطبق الشروط والأحكام.
-رقم التسجيل الضريبي: 319-897-204</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>استعدي لإطلالة جديدة واشتري منتاجات العناية بالشعر من CH&amp;BE ب0% مقدم، 0% فوائد، و 0% مصاريف إدارية على 6 أشهر من خلال الموقع الإلكتروني باستخدام بطاقات بنك الإمارات دبي الوطني الائتمانية.
-العرض سارى حتى 15 أبريل 2026
-تطبق الشروط والأحكام.
-رقم التسجيل الضريبي: 319-897-204</t>
+رقم التسجيل الضريبي: 319-897-204 https://t.co/uTR0Y8lyWz</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Get ready for a new look and purchase hair care products from CH&amp;BE with 0% down payment, 0% interest, and 0% administrative fees over 6 months through the website using Emirates NBD credit cards.
+          <t>Get ready for a new look and purchase hair care products from CH&amp;BE with 0% down payment, 0% interest, and 0% administrative fees over 6 months through the website using Emirates NBD credit cards. 
 The offer is valid until April 15, 2026.
-Terms and conditions apply.
-Tax registration number: 319-897-204</t>
+Terms and conditions apply. 
+Tax registration number: 319-897-204 https://t.co/uTR0Y8lyWz</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Get ready for a new look and purchase hair care products from CH&amp;BE with 0% down payment, 0% interest, and 0% administrative fees over 6 months through the website using Emirates NBD credit cards. • Tax registration number: 319-897-204 • The offer is valid until April 15, 2026.</t>
+          <t>Get ready for a new look and purchase hair care products from CH&amp;BE with 0% down payment, 0% interest, and 0% administrative fees over 6 months through the website using Emirates NBD credit cards. • Tax registration number: 319-897-204 https://t.co/uTR0Y8lyWz • The offer is valid until April 15, 2026.</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -2202,7 +2202,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>12h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -2229,7 +2229,7 @@
         <v>4</v>
       </c>
       <c r="V11" t="n">
-        <v>407</v>
+        <v>424</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -2276,8 +2276,9 @@
           <t>A moment of pride. A manifestation of trust.
 We are proud to receive this recognition at the 2026 Euromoney Private Banking Awards:
 • Best Private Bank in the Middle East
-• Best Family Office Services Bank in the Middle East
-We extend our sincere thanks to our clients for their continued trust and enduring partnership. This achievement is a testament to our steadfast commitment to excellence.</t>
+• Best Family Office Services in the Middle East
+We extend our sincere thanks to our clients for their continued trust and enduring partnership. This achievement is a testament to our unwavering commitment to excellence.
+#EuromoneyAwards #ExcellenceInPrivateBanking</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2310,7 +2311,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>This achievement is a testament to our steadfast commitment to excellence. • A manifestation of trust.</t>
+          <t>This achievement is a testament to our unwavering commitment to excellence. • A manifestation of trust. • #EuromoneyAwards #ExcellenceInPrivateBanking</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -2391,7 +2392,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>12h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -2418,7 +2419,7 @@
         <v>3</v>
       </c>
       <c r="V12" t="n">
-        <v>351</v>
+        <v>366</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -2572,7 +2573,7 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>12h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -2599,7 +2600,7 @@
         <v>1</v>
       </c>
       <c r="V13" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -2738,7 +2739,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -2761,7 +2762,7 @@
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -2913,7 +2914,7 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -2933,10 +2934,10 @@
         <v>10</v>
       </c>
       <c r="U15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V15" t="n">
-        <v>923</v>
+        <v>945</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -3114,7 +3115,7 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -3141,7 +3142,7 @@
         <v>2</v>
       </c>
       <c r="V16" t="n">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -3195,9 +3196,9 @@
       <c r="AB16" t="inlineStr">
         <is>
           <t>5.41 trillion dirhams with a growth rate of 1.4%
-The monetary and banking indicators in the UAE continued to show positive performance at the beginning of 2026, as total banking assets increased by 1.4% to exceed 5.413 trillion dirhams at the end of January 2026 compared to approximately 5.339 trillion dirhams at the end of December 2025.
+The monetary and banking indicators in the UAE continued to show positive performance at the beginning of 2026, as total banking assets increased by 1.4% to exceed 5.413 trillion dirhams at the end of January 2026 compared to about 5.339 trillion dirhams at the end of December 2025.
 Total credit rose by 1.1%, from about 2.57 trillion dirhams at the end of December, exceeding 2.598 trillion dirhams by the end of January 2026, supported by an increase in domestic credit of 27.9 billion dirhams.
-The growth in domestic credit is attributed to a 2.5% increase in credit granted to the government sector and a 0.6% increase in the private sector, contributing approximately 0.4 percentage points to the overall growth.
+The growth in domestic credit is attributed to a 2.5% increase in credit granted to the government sector and a 0.6% increase in the private sector, contributing about 0.4 percentage points to the overall growth.
 Total bank deposits increased by 0.9% to reach about 3.337 trillion dirhams at the end of January 2026, compared to 3.307 trillion dirhams at the end of December, supported by a 1.2% increase in resident deposits, reaching 3.046 trillion dirhams.</t>
         </is>
       </c>
@@ -3300,7 +3301,7 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -3327,7 +3328,7 @@
         <v>2</v>
       </c>
       <c r="V17" t="n">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
@@ -3458,7 +3459,7 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -3481,7 +3482,7 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -3621,7 +3622,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -3648,7 +3649,7 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -3793,7 +3794,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -3820,7 +3821,7 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
@@ -3849,7 +3850,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE B- 1.89% @semeet @SelmaRomola @ibushra_03</t>
+          <t>The text appears to be a social media post or tweet, likely in English already, with some references to users and a percentage. Therefore, no translation is needed.</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3882,7 +3883,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE B- 1.89% @semeet @SelmaRomola @ibushra_03</t>
+          <t>The text appears to be a social media post or tweet, likely in English already, with some references to users and a percentage. • Therefore, no translation is needed.</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3955,7 +3956,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -3982,7 +3983,7 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
@@ -4117,7 +4118,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -4144,7 +4145,7 @@
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -4259,168 +4260,6 @@
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @Salma2232019 @SelmaRomola</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Exchanger volunteer program &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K23" t="b">
-        <v>0</v>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>19h</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>Mar 24, 2026 · 9:01 AM UTC</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="n">
-        <v>46105.37569444445</v>
-      </c>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>['https://x.com/semeet', 'https://x.com/Salma2232019', 'https://x.com/SelmaRomola']</t>
-        </is>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>6</v>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>Exchanger volunteer program @semeet @Salma2232019 @SelmaRomola</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2036367691980873799</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @Salma2232019 @SelmaRomola</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @Salma2232019 @SelmaRomola</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>Emirates NBD AE Exchanger volunteer program</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD23" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AE23" s="2" t="n">
-        <v>46105.54236111111</v>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>24-03-2026</t>
-        </is>
-      </c>
-      <c r="AG23" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Emirates NBD AE Exchanger volunteer program</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AK23" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>EmiratesNBD_AE</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2036367634590212403</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2036367634590212403</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Sosomostafa729S</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Soha.mostafa77</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
         <is>
           <t>حلّ فزورة رمضان واربح 10,000 درهم.
 من توزيع الوجبات، إلى دعم العاملين وقضاء الوقت مع كبار المواطنين، يجمع برنامج واحد كل ذلك تحت مظلًة واحدة.
@@ -4431,67 +4270,67 @@
 3.اكتب إجابتك في التعليقات أدناه https://t.co/aADoQF5a2E</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Exchanger volunteer program &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K24" t="b">
-        <v>0</v>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Exchanger volunteer program &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K23" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>19h</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>Mar 24, 2026 · 9:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="n">
-        <v>46105.375</v>
-      </c>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/parulghalout', 'https://x.com/parulghalout']</t>
-        </is>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>4</v>
-      </c>
-      <c r="W24" t="inlineStr">
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Mar 24, 2026 · 9:01 AM UTC</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="n">
+        <v>46105.37569444445</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>['https://x.com/semeet', 'https://x.com/Salma2232019', 'https://x.com/SelmaRomola']</t>
+        </is>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>7</v>
+      </c>
+      <c r="W23" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>Exchanger volunteer program @Emy191990 @parulghalout @parulghalout</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2036367634590212403</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Exchanger volunteer program @semeet @Salma2232019 @SelmaRomola</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2036367691980873799</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
         <is>
           <t>حلّ فزورة رمضان واربح 10,000 درهم.
 من توزيع الوجبات، إلى دعم العاملين وقضاء الوقت مع كبار المواطنين، يجمع برنامج واحد كل ذلك تحت مظلًة واحدة.
@@ -4502,7 +4341,7 @@
 3.اكتب إجابتك في التعليقات أدناه https://t.co/aADoQF5a2E</t>
         </is>
       </c>
-      <c r="AA24" t="inlineStr">
+      <c r="AA23" t="inlineStr">
         <is>
           <t>حلّ فزورة رمضان واربح 10,000 درهم.
 من توزيع الوجبات، إلى دعم العاملين وقضاء الوقت مع كبار المواطنين، يجمع برنامج واحد كل ذلك تحت مظلًة واحدة.
@@ -4513,15 +4352,177 @@
 3.اكتب إجابتك في التعليقات أدناه https://t.co/aADoQF5a2E</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
+      <c r="AB23" t="inlineStr">
         <is>
           <t>Solve the Ramadan riddle and win 10,000 dirhams.
-From meal distribution to supporting workers and spending time with senior citizens, one program brings all of this together under one umbrella.
+From meal distribution to supporting workers and spending time with senior citizens, one program brings all of that under one umbrella.
 What is the name of this program?
 To participate:
 1. Follow the Emirates NBD account
 2. Tag 3 of your friends
-3. Write your answer in the comments below</t>
+3. Write your answer in the comments below.</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE23" s="2" t="n">
+        <v>46105.54236111111</v>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>24-03-2026</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>From meal distribution to supporting workers and spending time with senior citizens, one program brings all of that under one umbrella. • Solve the Ramadan riddle and win 10,000 dirhams. • Follow the Emirates NBD account 2.</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK23" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2036367634590212403</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2036367634590212403</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Exchanger volunteer program @Emy191990 @parulghalout @parulghalout</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Exchanger volunteer program &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K24" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Mar 24, 2026 · 9:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="n">
+        <v>46105.375</v>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>['https://x.com/Emy191990', 'https://x.com/parulghalout', 'https://x.com/parulghalout']</t>
+        </is>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>6</v>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Exchanger volunteer program @Emy191990 @parulghalout @parulghalout</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2036367634590212403</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Exchanger volunteer program @Emy191990 @parulghalout @parulghalout</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Exchanger volunteer program @Emy191990 @parulghalout @parulghalout</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>Emirates NBD_AE Exchanger volunteer program Emy191990 parulghalout parulghalout</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -4554,7 +4555,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>From meal distribution to supporting workers and spending time with senior citizens, one program brings all of this together under one umbrella. • Solve the Ramadan riddle and win 10,000 dirhams. • Follow the Emirates NBD account 2.</t>
+          <t>Emirates NBD_AE Exchanger volunteer program Emy191990 parulghalout parulghalout</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -4627,7 +4628,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -4654,7 +4655,7 @@
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -4789,7 +4790,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -4816,7 +4817,7 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
@@ -4951,7 +4952,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -4978,7 +4979,7 @@
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
@@ -5135,7 +5136,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -5162,7 +5163,7 @@
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
@@ -5240,9 +5241,9 @@
 50% for needs
 30% for wants
 20% for savings
-A smart plan that helps you spend, save and stay in control.
-This is one of the many tips that the bank’s programme has in store.
-Watch the episode and tell us the name of the programme?
+A smart plan that helps you spend, save, and stay in control.
+This is one of the many tips that the bank’s program has in store.
+Watch the episode and tell us the name of the program?
 To participate:
 - Follow Emirates NBD
 - Tag 3 friends
@@ -5279,7 +5280,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>A simple rule can help her stay on track: 50% for needs 30% for wants 20% for savings A smart plan that helps you spend, save and stay in control. • To participate: - Follow Emirates NBD - Tag 3 friends - Drop your answer below for a chance to win AED 10,000 • This is one of the many tips that the bank’s programme has in store.</t>
+          <t>A simple rule can help her stay on track: 50% for needs 30% for wants 20% for savings A smart plan that helps you spend, save, and stay in control. • To participate: - Follow Emirates NBD - Tag 3 friends - Drop your answer below for a chance to win AED 10,000 • This is one of the many tips that the bank’s program has in store.</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -5352,7 +5353,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -5379,7 +5380,7 @@
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
@@ -5514,7 +5515,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -5541,7 +5542,7 @@
         <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
@@ -5683,7 +5684,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -5710,7 +5711,7 @@
         <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
@@ -5860,7 +5861,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -5887,7 +5888,7 @@
         <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W32" t="inlineStr">
         <is>
@@ -6022,7 +6023,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -6049,7 +6050,7 @@
         <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
@@ -6191,7 +6192,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -6218,7 +6219,7 @@
         <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
@@ -6367,7 +6368,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -6394,7 +6395,7 @@
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
@@ -6529,7 +6530,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -6556,7 +6557,7 @@
         <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
@@ -6691,7 +6692,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -6714,7 +6715,7 @@
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
@@ -6843,7 +6844,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -6870,7 +6871,7 @@
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
@@ -6999,7 +7000,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -7022,7 +7023,7 @@
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
@@ -7151,7 +7152,7 @@
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -7174,7 +7175,7 @@
         <v>8</v>
       </c>
       <c r="V40" t="n">
-        <v>871</v>
+        <v>890</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
@@ -7202,7 +7203,7 @@
       <c r="AB40" t="inlineStr">
         <is>
           <t>A new month with more winners.
-Congratulations to the grand prize winner of a ROX 01 car, and to the winners of the 10-gram gold piece for participating in the "It's Time to Win Grand Prizes" campaign offered by business banking for January 2026.
+Congratulations to the grand prize winner of the ROX 01 car, and to the winners of the 10-gram gold piece for participating in the "It's Time to Win Grand Prizes" campaign offered by business banking for January 2026.
 Continue using your business account to carry out foreign exchange transactions and trade financing to increase your company's chances of winning. The offer is valid until March 31, 2026.</t>
         </is>
       </c>
@@ -7311,7 +7312,7 @@
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -7334,7 +7335,7 @@
         <v>8</v>
       </c>
       <c r="V41" t="n">
-        <v>679</v>
+        <v>701</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
@@ -7466,7 +7467,7 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -7493,7 +7494,7 @@
         <v>5</v>
       </c>
       <c r="V42" t="n">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
@@ -7629,7 +7630,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>23h</t>
+          <t>Mar 24</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -7652,7 +7653,7 @@
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="W43" t="inlineStr">
         <is>
@@ -7792,7 +7793,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -7815,7 +7816,7 @@
         <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
@@ -7943,9 +7944,10 @@
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Drive home your dream car with Emirates Islamic Auto Finance!
-📊 Attractive profit rates starting from 1.89% flat p.a. (equivalent to 3.61% reducing profit rate p.a.)
-📅Payment holiday of up to 6 months https://t.co/kNYdVe2AYC</t>
+          <t>💳 0% Easy Payment Plan on Emirates Islamic Credit Card spends at select auto dealerships
+📅Offer valid till 31 March 2026.
+Terms &amp; Conditions apply.
+emiratesislamic.ae/en/offers…</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -7963,7 +7965,7 @@
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -7990,7 +7992,7 @@
         <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
@@ -8005,29 +8007,19 @@
 emiratesislamic.ae/en/offers…</t>
         </is>
       </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2036385610118623239</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>Drive home your dream car with Emirates Islamic Auto Finance!
-📊 Attractive profit rates starting from 1.89% flat p.a. (equivalent to 3.61% reducing profit rate p.a.)
-📅Payment holiday of up to 6 months https://t.co/kNYdVe2AYC</t>
-        </is>
-      </c>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>Drive home your dream car with Emirates Islamic Auto Finance!
-📊 Attractive profit rates starting from 1.89% flat p.a. (equivalent to 3.61% reducing profit rate p.a.)
-📅Payment holiday of up to 6 months https://t.co/kNYdVe2AYC</t>
+          <t>💳 0% Easy Payment Plan on Emirates Islamic Credit Card spends at select auto dealerships
+📅Offer valid till 31 March 2026.
+Terms &amp; Conditions apply.
+emiratesislamic.ae/en/offers…</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>Drive home your dream car with Emirates Islamic Auto Finance!
-Attractive profit rates starting from 1.89% flat per annum (equivalent to 3.61% reducing profit rate per annum). Payment holiday of up to 6 months.</t>
+          <t>0% Easy Payment Plan on Emirates Islamic Credit Card spends at select auto dealerships. Offer valid until 31 March 2026. Terms &amp; Conditions apply.</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -8060,7 +8052,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Attractive profit rates starting from 1.89% flat per annum (equivalent to 3.61% reducing profit rate per annum). • Drive home your dream car with Emirates Islamic Auto Finance! • Payment holiday of up to 6 months.</t>
+          <t>Offer valid until 31 March 2026. • 0% Easy Payment Plan on Emirates Islamic Credit Card spends at select auto dealerships. • Terms &amp; Conditions apply.</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
@@ -8133,7 +8125,7 @@
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -8156,7 +8148,7 @@
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="W46" t="inlineStr">
         <is>
@@ -8301,7 +8293,7 @@
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -8328,7 +8320,7 @@
         <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
@@ -8366,7 +8358,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>Easy payment program 0% on purchases with Emirates Islamic credit card at car dealers. Valid until March 31, 2026. Terms and conditions apply.</t>
+          <t>Easy payment program 0% on purchases made with Emirates Islamic credit card at car dealers. Valid until March 31, 2026. Terms and conditions apply.</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -8399,7 +8391,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Valid until March 31, 2026. • Easy payment program 0% on purchases with Emirates Islamic credit card at car dealers. • Terms and conditions apply.</t>
+          <t>Valid until March 31, 2026. • Easy payment program 0% on purchases made with Emirates Islamic credit card at car dealers. • Terms and conditions apply.</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
@@ -8472,7 +8464,7 @@
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -8495,7 +8487,7 @@
         <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="W48" t="inlineStr">
         <is>
@@ -8521,7 +8513,7 @@
       <c r="AB48" t="inlineStr">
         <is>
           <t>Enjoy driving your dream car with car financing from Emirates Islamic
-📊 Special profit rates starting from 1.89% fixed annually (equivalent to 3.61% as a declining profit rate annually)
+📊 Special profit rates starting from 1.89% fixed annually (equivalent to 3.61% as a declining annual profit rate)
 📅 Repayment grace period of up to 6 months</t>
         </is>
       </c>
@@ -8630,7 +8622,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -8653,7 +8645,7 @@
         <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
@@ -8786,7 +8778,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -8809,7 +8801,7 @@
         <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
@@ -8834,8 +8826,8 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>Hi, happy to connect.
-I didn’t receive your DM, and my replies don’t seem to be going through either. Not sure if there’s a technical issue.
+          <t>Hi, happy to connect. 
+I didn’t receive your DM, and my replies don’t seem to be going through either. Not sure if there’s a technical issue. 
 I’m available now, please feel free to message.</t>
         </is>
       </c>
@@ -8942,7 +8934,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -8965,7 +8957,7 @@
         <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="W51" t="inlineStr">
         <is>
@@ -9100,7 +9092,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -9123,7 +9115,7 @@
         <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="W52" t="inlineStr">
         <is>
@@ -9250,7 +9242,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -9273,7 +9265,7 @@
         <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W53" t="inlineStr">
         <is>
@@ -9408,7 +9400,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -9431,7 +9423,7 @@
         <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="W54" t="inlineStr">
         <is>
@@ -9558,7 +9550,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -9581,7 +9573,7 @@
         <v>0</v>
       </c>
       <c r="V55" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
@@ -9720,7 +9712,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -9747,7 +9739,7 @@
         <v>0</v>
       </c>
       <c r="V56" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="W56" t="inlineStr">
         <is>
@@ -9884,7 +9876,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -9907,7 +9899,7 @@
         <v>0</v>
       </c>
       <c r="V57" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
@@ -9990,43 +9982,43 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2036319304132473271</t>
+          <t>2036558462906409266</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2036319304132473271</t>
+          <t>https://x.com/ZahidanMuhamma/status/2036558462906409266</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/ZahidanMuhamma</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>ZahidanMuhamma</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Muhammad Zahidan</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1827047486680137728/R86Fb-lT_bigger.jpg</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
-          <t>@emiratesislamic hello, i have been trying to reach your redemption department for a week now, i need someone to talk to or i will only do my own solution which is moving my salary to another bank.</t>
+          <t>It's a joke I will wait for 90 days to receive my fund what a joke</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+          <t>It&amp;#39;s a joke I will wait for 90 days to receive my fund what a joke</t>
         </is>
       </c>
       <c r="K58" t="b">
@@ -10035,21 +10027,21 @@
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>['wasishion']</t>
+          <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>7h</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 5:48 AM UTC</t>
+          <t>Mar 24, 2026 · 9:39 PM UTC</t>
         </is>
       </c>
       <c r="P58" s="2" t="n">
-        <v>46105.24166666667</v>
+        <v>46105.90208333333</v>
       </c>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
@@ -10063,36 +10055,28 @@
         <v>0</v>
       </c>
       <c r="V58" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>ENBD</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2036319304132473271</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>@emiratesislamic hello, i have been trying to reach your redemption department for a week now, i need someone to talk to or i will only do my own solution which is moving my salary to another bank.</t>
-        </is>
-      </c>
+          <t>It's a joke I will wait for 90 days to receive my fund what a joke</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr"/>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>@emiratesislamic hello, i have been trying to reach your redemption department for a week now, i need someone to talk to or i will only do my own solution which is moving my salary to another bank.</t>
+          <t>It's a joke I will wait for 90 days to receive my fund what a joke</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>Hello, I have been trying to reach your redemption department for a week now. I need someone to talk to, or I will only do my own solution, which is moving my salary to another bank.</t>
+          <t>It's a joke that I will wait for 90 days to receive my funds; what a joke.</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
@@ -10106,31 +10090,31 @@
         </is>
       </c>
       <c r="AE58" s="2" t="n">
-        <v>46105.40833333333</v>
+        <v>46106.06875</v>
       </c>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>24-03-2026</t>
+          <t>25-03-2026</t>
         </is>
       </c>
       <c r="AG58" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>ENBD</t>
         </is>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
+          <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>I need someone to talk to, or I will only do my own solution, which is moving my salary to another bank. • Hello, I have been trying to reach your redemption department for a week now.</t>
+          <t>It's a joke that I will wait for 90 days to receive my funds; what a joke.</t>
         </is>
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>Emirates Islamic Bank (EIB)</t>
+          <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
       <c r="AK58" t="n">
@@ -10138,7 +10122,7 @@
       </c>
       <c r="AL58" t="inlineStr">
         <is>
-          <t>wasishion</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
     </row>
@@ -10148,44 +10132,43 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2036400751896043863</t>
+          <t>2036319304132473271</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://x.com/koko_isa8/status/2036400751896043863</t>
+          <t>https://x.com/emiratesislamic/status/2036319304132473271</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://x.com/koko_isa8</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>koko_isa8</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>κoκo мadeмöıseιιe⁸ 💅🏽</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2035262775103242240/J6m7iJmF_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE @AppleSupport i have been struggling with my apple wallet for 4 months now. Since i changed from iphone14 to 17. I cannot add my cards (contact issuer) i have spoken to both of you &amp;amp; the problem has not been resolved yet. All steps were done from both sides too!</t>
+          <t>@emiratesislamic hello, i have been trying to reach your redemption department for a week now, i need someone to talk to or i will only do my own solution which is moving my salary to another bank.</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>So? 
-Am i expecting any call from your side?</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
         </is>
       </c>
       <c r="K59" t="b">
@@ -10194,21 +10177,21 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>['EmiratesNBD_AE']</t>
+          <t>['wasishion']</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 11:12 AM UTC</t>
+          <t>Mar 24, 2026 · 5:48 AM UTC</t>
         </is>
       </c>
       <c r="P59" s="2" t="n">
-        <v>46105.46666666667</v>
+        <v>46105.24166666667</v>
       </c>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
@@ -10222,37 +10205,36 @@
         <v>0</v>
       </c>
       <c r="V59" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>So? 
-Am i expecting any call from your side?</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>https://x.com/koko_isa8/status/2036400751896043863</t>
+          <t>https://x.com/emiratesislamic/status/2036319304132473271</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE @AppleSupport i have been struggling with my apple wallet for 4 months now. Since i changed from iphone14 to 17. I cannot add my cards (contact issuer) i have spoken to both of you &amp;amp; the problem has not been resolved yet. All steps were done from both sides too!</t>
+          <t>@emiratesislamic hello, i have been trying to reach your redemption department for a week now, i need someone to talk to or i will only do my own solution which is moving my salary to another bank.</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE @AppleSupport i have been struggling with my apple wallet for 4 months now. Since i changed from iphone14 to 17. I cannot add my cards (contact issuer) i have spoken to both of you &amp;amp; the problem has not been resolved yet. All steps were done from both sides too!</t>
+          <t>@emiratesislamic hello, i have been trying to reach your redemption department for a week now, i need someone to talk to or i will only do my own solution which is moving my salary to another bank.</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>I have been struggling with my Apple Wallet for 4 months now. Since I changed from iPhone 14 to 17, I cannot add my cards (contact issuer). I have spoken to both of you, and the problem has not been resolved yet. All steps were done from both sides too!</t>
+          <t>Hello, I have been trying to reach your redemption department for a week now. I need someone to talk to, or I will only do my own solution, which is moving my salary to another bank.</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
@@ -10266,7 +10248,7 @@
         </is>
       </c>
       <c r="AE59" s="2" t="n">
-        <v>46105.63333333333</v>
+        <v>46105.40833333333</v>
       </c>
       <c r="AF59" t="inlineStr">
         <is>
@@ -10275,22 +10257,22 @@
       </c>
       <c r="AG59" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
+          <t>2. Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>Since I changed from iPhone 14 to 17, I cannot add my cards (contact issuer). • I have spoken to both of you, and the problem has not been resolved yet. • I have been struggling with my Apple Wallet for 4 months now.</t>
+          <t>I need someone to talk to, or I will only do my own solution, which is moving my salary to another bank. • Hello, I have been trying to reach your redemption department for a week now.</t>
         </is>
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank (ENBD)</t>
+          <t>Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AK59" t="n">
@@ -10298,7 +10280,7 @@
       </c>
       <c r="AL59" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>wasishion</t>
         </is>
       </c>
     </row>
@@ -10308,71 +10290,72 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2036414919394971981</t>
+          <t>2036400751896043863</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://x.com/motsafeh057/status/2036414919394971981</t>
+          <t>https://x.com/koko_isa8/status/2036400751896043863</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://x.com/motsafeh057</t>
+          <t>https://x.com/koko_isa8</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>motsafeh057</t>
+          <t>koko_isa8</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>متصفح وقارئ للأخبار</t>
+          <t>κoκo мadeмöıseιιe⁸ 💅🏽</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1996323967443881984/qDVGWeO0_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2035262775103242240/J6m7iJmF_bigger.jpg</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA البنك رافض قطعيا يفتح لي حساب حاولت عن طريق خدمة العملاء رفض</t>
+          <t>@EmiratesNBD_AE @AppleSupport i have been struggling with my apple wallet for 4 months now. Since i changed from iphone14 to 17. I cannot add my cards (contact issuer) i have spoken to both of you &amp;amp; the problem has not been resolved yet. All steps were done from both sides too!</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>&lt;a href="/EmiratesNBD_KSA" title="EmiratesNBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt; البنك رافض قطعيا يفتح لي حساب حاولت عن طريق خدمة العملاء رفض</t>
+          <t>So? 
+Am i expecting any call from your side?</t>
         </is>
       </c>
       <c r="K60" t="b">
         <v>0</v>
       </c>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 12:08 PM UTC</t>
+          <t>Mar 24, 2026 · 11:12 AM UTC</t>
         </is>
       </c>
       <c r="P60" s="2" t="n">
-        <v>46105.50555555556</v>
+        <v>46105.46666666667</v>
       </c>
       <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr">
-        <is>
-          <t>['https://x.com/EmiratesNBD_KSA']</t>
-        </is>
-      </c>
+      <c r="R60" t="inlineStr"/>
       <c r="S60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T60" t="n">
         <v>0</v>
@@ -10381,7 +10364,7 @@
         <v>0</v>
       </c>
       <c r="V60" t="n">
-        <v>61</v>
+        <v>9</v>
       </c>
       <c r="W60" t="inlineStr">
         <is>
@@ -10390,27 +10373,28 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA البنك رافض قطعيا يفتح لي حساب حاولت عن طريق خدمة العملاء رفض</t>
+          <t>So? 
+Am i expecting any call from your side?</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>https://x.com/motsafeh057/status/2036414919394971981</t>
+          <t>https://x.com/koko_isa8/status/2036400751896043863</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA البنك رافض قطعيا يفتح لي حساب حاولت عن طريق خدمة العملاء رفض</t>
+          <t>@EmiratesNBD_AE @AppleSupport i have been struggling with my apple wallet for 4 months now. Since i changed from iphone14 to 17. I cannot add my cards (contact issuer) i have spoken to both of you &amp;amp; the problem has not been resolved yet. All steps were done from both sides too!</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA البنك رافض قطعيا يفتح لي حساب حاولت عن طريق خدمة العملاء رفض</t>
+          <t>@EmiratesNBD_AE @AppleSupport i have been struggling with my apple wallet for 4 months now. Since i changed from iphone14 to 17. I cannot add my cards (contact issuer) i have spoken to both of you &amp;amp; the problem has not been resolved yet. All steps were done from both sides too!</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>Emirates NBD bank categorically refuses to open an account for me; I tried through customer service and they rejected it.</t>
+          <t>I have been struggling with my Apple Wallet for 4 months now. Since I changed from iPhone 14 to 17, I cannot add my cards (contact issuer). I have spoken to both of you, and the problem has not been resolved yet. All steps were done from both sides too!</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -10424,7 +10408,7 @@
         </is>
       </c>
       <c r="AE60" s="2" t="n">
-        <v>46105.67222222222</v>
+        <v>46105.63333333333</v>
       </c>
       <c r="AF60" t="inlineStr">
         <is>
@@ -10443,7 +10427,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>Emirates NBD bank categorically refuses to open an account for me; I tried through customer service and they rejected it.</t>
+          <t>Since I changed from iPhone 14 to 17, I cannot add my cards (contact issuer). • I have spoken to both of you, and the problem has not been resolved yet. • I have been struggling with my Apple Wallet for 4 months now.</t>
         </is>
       </c>
       <c r="AJ60" t="inlineStr">
@@ -10456,7 +10440,7 @@
       </c>
       <c r="AL60" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
     </row>
@@ -10466,71 +10450,71 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2036345221831905561</t>
+          <t>2036414919394971981</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://x.com/msafrh79/status/2036345221831905561</t>
+          <t>https://x.com/motsafeh057/status/2036414919394971981</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://x.com/msafrh79</t>
+          <t>https://x.com/motsafeh057</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>msafrh79</t>
+          <t>motsafeh057</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>mervet foad</t>
+          <t>متصفح وقارئ للأخبار</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2027681283045003266/D4AYhe6v_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1996323967443881984/qDVGWeO0_bigger.jpg</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE مرحبا اين يتم اعلان الفائزين في مسابقة مواقع التواصل الاجتماعي؟؟ راسلتكم كثيرا على الخاص ومافي اي رد</t>
+          <t>@EmiratesNBD_KSA البنك رافض قطعيا يفتح لي حساب حاولت عن طريق خدمة العملاء رفض</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>مرحبا اين يتم اعلان الفائزين في مسابقة مواقع التواصل الاجتماعي؟؟ راسلتكم كثيرا على الخاص ومافي اي رد</t>
+          <t>&lt;a href="/EmiratesNBD_KSA" title="EmiratesNBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt; البنك رافض قطعيا يفتح لي حساب حاولت عن طريق خدمة العملاء رفض</t>
         </is>
       </c>
       <c r="K61" t="b">
         <v>0</v>
       </c>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 7:31 AM UTC</t>
+          <t>Mar 24, 2026 · 12:08 PM UTC</t>
         </is>
       </c>
       <c r="P61" s="2" t="n">
-        <v>46105.31319444445</v>
+        <v>46105.50555555556</v>
       </c>
       <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_KSA']</t>
+        </is>
+      </c>
       <c r="S61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T61" t="n">
         <v>0</v>
@@ -10539,7 +10523,7 @@
         <v>0</v>
       </c>
       <c r="V61" t="n">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="W61" t="inlineStr">
         <is>
@@ -10548,27 +10532,19 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>مرحبا اين يتم اعلان الفائزين في مسابقة مواقع التواصل الاجتماعي؟؟ راسلتكم كثيرا على الخاص ومافي اي رد</t>
-        </is>
-      </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>https://x.com/msafrh79/status/2036345221831905561</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE مرحبا اين يتم اعلان الفائزين في مسابقة مواقع التواصل الاجتماعي؟؟ راسلتكم كثيرا على الخاص ومافي اي رد</t>
-        </is>
-      </c>
+          <t>@EmiratesNBD_KSA البنك رافض قطعيا يفتح لي حساب حاولت عن طريق خدمة العملاء رفض</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE مرحبا اين يتم اعلان الفائزين في مسابقة مواقع التواصل الاجتماعي؟؟ راسلتكم كثيرا على الخاص ومافي اي رد</t>
+          <t>@EmiratesNBD_KSA البنك رافض قطعيا يفتح لي حساب حاولت عن طريق خدمة العملاء رفض</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>Hello, where are the winners of the social media competition announced? I have messaged you many times privately and there has been no response.</t>
+          <t>Emirates NBD bank categorically refuses to open an account for me; I tried through customer service, and they rejected it.</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
@@ -10582,7 +10558,7 @@
         </is>
       </c>
       <c r="AE61" s="2" t="n">
-        <v>46105.47986111111</v>
+        <v>46105.67222222222</v>
       </c>
       <c r="AF61" t="inlineStr">
         <is>
@@ -10601,7 +10577,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>I have messaged you many times privately and there has been no response. • Hello, where are the winners of the social media competition announced?</t>
+          <t>Emirates NBD bank categorically refuses to open an account for me; I tried through customer service, and they rejected it.</t>
         </is>
       </c>
       <c r="AJ61" t="inlineStr">
@@ -10614,7 +10590,7 @@
       </c>
       <c r="AL61" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -10624,43 +10600,43 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2036389317132583041</t>
+          <t>2036345221831905561</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://x.com/netdiscussion/status/2036389317132583041</t>
+          <t>https://x.com/msafrh79/status/2036345221831905561</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://x.com/netdiscussion</t>
+          <t>https://x.com/msafrh79</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>netdiscussion</t>
+          <t>msafrh79</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Muhammad Kashif Ashraf</t>
+          <t>mervet foad</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/2027681283045003266/D4AYhe6v_bigger.jpg</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA I don't understand, why no response/update on any official Channel by phone, email, Twitter??, since 8 of March, dispute case is registered.</t>
+          <t>@EmiratesNBD_AE مرحبا اين يتم اعلان الفائزين في مسابقة مواقع التواصل الاجتماعي؟؟ راسلتكم كثيرا على الخاص ومافي اي رد</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>&lt;a href="/SAMAcares" title="SAMACares | ساما تهتم"&gt;@SAMAcares&lt;/a&gt; There&amp;#39;s no response on the dispute query for the wrong/back dated fee applied, pending since 8 March</t>
+          <t>مرحبا اين يتم اعلان الفائزين في مسابقة مواقع التواصل الاجتماعي؟؟ راسلتكم كثيرا على الخاص ومافي اي رد</t>
         </is>
       </c>
       <c r="K62" t="b">
@@ -10669,28 +10645,24 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>['EmiratesNBD_KSA']</t>
+          <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 10:27 AM UTC</t>
+          <t>Mar 24, 2026 · 7:31 AM UTC</t>
         </is>
       </c>
       <c r="P62" s="2" t="n">
-        <v>46105.43541666667</v>
+        <v>46105.31319444445</v>
       </c>
       <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t>['https://x.com/SAMAcares']</t>
-        </is>
-      </c>
+      <c r="R62" t="inlineStr"/>
       <c r="S62" t="n">
         <v>0</v>
       </c>
@@ -10701,7 +10673,7 @@
         <v>0</v>
       </c>
       <c r="V62" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="W62" t="inlineStr">
         <is>
@@ -10710,27 +10682,27 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>@SAMAcares There's no response on the dispute query for the wrong/back dated fee applied, pending since 8 March</t>
+          <t>مرحبا اين يتم اعلان الفائزين في مسابقة مواقع التواصل الاجتماعي؟؟ راسلتكم كثيرا على الخاص ومافي اي رد</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>https://x.com/netdiscussion/status/2036389317132583041</t>
+          <t>https://x.com/msafrh79/status/2036345221831905561</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA I don't understand, why no response/update on any official Channel by phone, email, Twitter??, since 8 of March, dispute case is registered.</t>
+          <t>@EmiratesNBD_AE مرحبا اين يتم اعلان الفائزين في مسابقة مواقع التواصل الاجتماعي؟؟ راسلتكم كثيرا على الخاص ومافي اي رد</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA I don't understand, why no response/update on any official Channel by phone, email, Twitter??, since 8 of March, dispute case is registered.</t>
+          <t>@EmiratesNBD_AE مرحبا اين يتم اعلان الفائزين في مسابقة مواقع التواصل الاجتماعي؟؟ راسلتكم كثيرا على الخاص ومافي اي رد</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>I don't understand why there has been no response or update on any official channel by phone, email, or Twitter since March 8, when the dispute case was registered.</t>
+          <t>Hello, where are the winners of the social media competition announced? I have messaged you many times privately and there has been no response.</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
@@ -10744,7 +10716,7 @@
         </is>
       </c>
       <c r="AE62" s="2" t="n">
-        <v>46105.60208333333</v>
+        <v>46105.47986111111</v>
       </c>
       <c r="AF62" t="inlineStr">
         <is>
@@ -10763,7 +10735,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>I don't understand why there has been no response or update on any official channel by phone, email, or Twitter since March 8, when the dispute case was registered.</t>
+          <t>I have messaged you many times privately and there has been no response. • Hello, where are the winners of the social media competition announced?</t>
         </is>
       </c>
       <c r="AJ62" t="inlineStr">
@@ -10776,7 +10748,7 @@
       </c>
       <c r="AL62" t="inlineStr">
         <is>
-          <t>EmiratesNBD_KSA</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
     </row>
@@ -10786,159 +10758,321 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2036269961057018273</t>
+          <t>2036389317132583041</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://x.com/saimas89/status/2036269961057018273</t>
+          <t>https://x.com/netdiscussion/status/2036389317132583041</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://x.com/saimas89</t>
+          <t>https://x.com/netdiscussion</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>saimas89</t>
+          <t>netdiscussion</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Saima | صائمہ</t>
+          <t>Muhammad Kashif Ashraf</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1613505962098282497/lNPa9Or8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA I don't understand, why no response/update on any official Channel by phone, email, Twitter??, since 8 of March, dispute case is registered.</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>&lt;a href="/SAMAcares" title="SAMACares | ساما تهتم"&gt;@SAMAcares&lt;/a&gt; There&amp;#39;s no response on the dispute query for the wrong/back dated fee applied, pending since 8 March</t>
+        </is>
+      </c>
+      <c r="K63" t="b">
+        <v>0</v>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Mar 24, 2026 · 10:27 AM UTC</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="n">
+        <v>46105.43541666667</v>
+      </c>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>['https://x.com/SAMAcares']</t>
+        </is>
+      </c>
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" t="n">
+        <v>17</v>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>@SAMAcares There's no response on the dispute query for the wrong/back dated fee applied, pending since 8 March</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>https://x.com/netdiscussion/status/2036389317132583041</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA I don't understand, why no response/update on any official Channel by phone, email, Twitter??, since 8 of March, dispute case is registered.</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA I don't understand, why no response/update on any official Channel by phone, email, Twitter??, since 8 of March, dispute case is registered.</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>I don't understand why there has been no response or update on any official channel by phone, email, or Twitter since March 8, when the dispute case was registered.</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AE63" s="2" t="n">
+        <v>46105.60208333333</v>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>24-03-2026</t>
+        </is>
+      </c>
+      <c r="AG63" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>I don't understand why there has been no response or update on any official channel by phone, email, or Twitter since March 8, when the dispute case was registered.</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK63" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL63" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_KSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2036269961057018273</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>https://x.com/saimas89/status/2036269961057018273</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://x.com/saimas89</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>saimas89</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Saima | صائمہ</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1613505962098282497/lNPa9Or8_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
         <is>
           <t>.@flyspicejet booked a flight DXB-BOM, you guys cancelled, I requested a refund which was “initiated” on March 10, 2026.
 It has now been more than 7 working days, but the refund has still not been credited to me as stated/promised.
 @DGCAIndia @RamMNK @MoCA_GoI @jagograhakjago https://t.co/L4So4pzq9f</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>Can you not take another 7 days and give me the refund sooner? FYI I have paid using my ENBD card.</t>
         </is>
       </c>
-      <c r="K63" t="b">
-        <v>0</v>
-      </c>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
+      <c r="K64" t="b">
+        <v>0</v>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
         <is>
           <t>['flyspicejet']</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t>Mar 24</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t>Mar 24, 2026 · 2:32 AM UTC</t>
         </is>
       </c>
-      <c r="P63" s="2" t="n">
+      <c r="P64" s="2" t="n">
         <v>46105.10555555556</v>
       </c>
-      <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr"/>
-      <c r="S63" t="n">
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="n">
         <v>1</v>
       </c>
-      <c r="T63" t="n">
-        <v>0</v>
-      </c>
-      <c r="U63" t="n">
-        <v>0</v>
-      </c>
-      <c r="V63" t="n">
-        <v>30</v>
-      </c>
-      <c r="W63" t="inlineStr">
+      <c r="T64" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" t="n">
+        <v>31</v>
+      </c>
+      <c r="W64" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
+      <c r="X64" t="inlineStr">
         <is>
           <t>Can you not take another 7 days and give me the refund sooner? FYI I have paid using my ENBD card.</t>
         </is>
       </c>
-      <c r="Y63" t="inlineStr">
+      <c r="Y64" t="inlineStr">
         <is>
           <t>https://x.com/saimas89/status/2036269961057018273</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
+      <c r="Z64" t="inlineStr">
         <is>
           <t>.@flyspicejet booked a flight DXB-BOM, you guys cancelled, I requested a refund which was “initiated” on March 10, 2026.
 It has now been more than 7 working days, but the refund has still not been credited to me as stated/promised.
 @DGCAIndia @RamMNK @MoCA_GoI @jagograhakjago https://t.co/L4So4pzq9f</t>
         </is>
       </c>
-      <c r="AA63" t="inlineStr">
+      <c r="AA64" t="inlineStr">
         <is>
           <t>.@flyspicejet booked a flight DXB-BOM, you guys cancelled, I requested a refund which was “initiated” on March 10, 2026.
 It has now been more than 7 working days, but the refund has still not been credited to me as stated/promised.
 @DGCAIndia @RamMNK @MoCA_GoI @jagograhakjago https://t.co/L4So4pzq9f</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>I booked a flight from DXB to BOM with @flyspicejet, which you guys canceled. I requested a refund that was "initiated" on March 10, 2026. It has now been more than 7 working days, but the refund has still not been credited to me as stated/promised.</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>I booked a flight from Dubai to Mumbai with SpiceJet, which you guys canceled. I requested a refund that was "initiated" on March 10, 2026. It has now been more than 7 working days, but the refund has still not been credited to me as stated/promised.</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="AD63" t="inlineStr">
+      <c r="AD64" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="AE63" s="2" t="n">
+      <c r="AE64" s="2" t="n">
         <v>46105.27222222222</v>
       </c>
-      <c r="AF63" t="inlineStr">
+      <c r="AF64" t="inlineStr">
         <is>
           <t>24-03-2026</t>
         </is>
       </c>
-      <c r="AG63" t="inlineStr">
+      <c r="AG64" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="AH63" t="inlineStr">
+      <c r="AH64" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>It has now been more than 7 working days, but the refund has still not been credited to me as stated/promised. • I requested a refund that was "initiated" on March 10, 2026. • I booked a flight from DXB to BOM with @flyspicejet, which you guys canceled.</t>
-        </is>
-      </c>
-      <c r="AJ63" t="inlineStr">
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>It has now been more than 7 working days, but the refund has still not been credited to me as stated/promised. • I requested a refund that was "initiated" on March 10, 2026. • I booked a flight from Dubai to Mumbai with SpiceJet, which you guys canceled.</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
         <is>
           <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AK63" t="n">
+      <c r="AK64" t="n">
         <v>2026</v>
       </c>
-      <c r="AL63" t="inlineStr">
+      <c r="AL64" t="inlineStr">
         <is>
           <t>flyspicejet</t>
         </is>

--- a/check2.xlsx
+++ b/check2.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL45"/>
+  <dimension ref="A1:AL46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -676,7 +676,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>48m</t>
+          <t>3h</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -699,7 +699,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>5h</t>
+          <t>7h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -872,7 +872,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -917,12 +917,12 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>Solve the Ramadan riddle and win 10,000 dirhams.
-From meal distribution to supporting workers and spending time with senior citizens, one program brings all of that under one umbrella.
+From meal distribution to supporting workers and spending time with senior citizens, one program brings all of this together under one umbrella.
 What is the name of this program?
 To participate:
 1. Follow the Emirates NBD account
 2. Tag 3 of your friends
-3. Write your answer in the comments below.</t>
+3. Write your answer in the comments below</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>From meal distribution to supporting workers and spending time with senior citizens, one program brings all of that under one umbrella. • Solve the Ramadan riddle and win 10,000 dirhams. • Follow the Emirates NBD account 2.</t>
+          <t>From meal distribution to supporting workers and spending time with senior citizens, one program brings all of this together under one umbrella. • Solve the Ramadan riddle and win 10,000 dirhams. • Follow the Emirates NBD account 2.</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>12h</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1053,7 +1053,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>12h</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1217,7 +1217,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1381,7 +1381,7 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1545,7 +1545,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Middle East Stocks: UAE equities reverse early gains on Iran ceasefire uncertainty</t>
+          <t>Middle East Stocks: UAE equities reverse early gains due to uncertainty over the Iran ceasefire.</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Middle East Stocks: UAE equities reverse early gains on Iran ceasefire uncertainty</t>
+          <t>Middle East Stocks: UAE equities reverse early gains due to uncertainty over the Iran ceasefire.</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>12h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1708,7 +1708,7 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>12h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1876,7 +1876,7 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>The best bank in the UAE @EmiratesNBD_AE</t>
+          <t>The best bank in the UAE</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>The best bank in the UAE @EmiratesNBD_AE</t>
+          <t>The best bank in the UAE</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -2034,7 +2034,7 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Mutual fund/ Investment Fund
+          <t>Mutual fund/ Investment Fund
 #ENBDRiddleOfTheWeek 
 #financialwellbeing</t>
         </is>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -2192,7 +2192,7 @@
         <v>1</v>
       </c>
       <c r="V11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -2206,21 +2206,11 @@
 #financialwellbeing</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>https://x.com/HomszRami/status/2037511645971583026</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Mutual fund/ Investment Fund
-#ENBDRiddleOfTheWeek 
-#financialwellbeing</t>
-        </is>
-      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Mutual fund/ Investment Fund
+          <t>Mutual fund/ Investment Fund
 #ENBDRiddleOfTheWeek 
 #financialwellbeing</t>
         </is>
@@ -2338,7 +2328,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -2361,7 +2351,7 @@
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -2395,7 +2385,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Hello Ahmad, thank you for contacting us. How can we assist you?</t>
+          <t>Hello Ahmed, thank you for contacting us. How can we assist you?</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2428,7 +2418,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Hello Ahmad, thank you for contacting us.</t>
+          <t>Hello Ahmed, thank you for contacting us.</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2509,7 +2499,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -2532,7 +2522,7 @@
         <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -2685,7 +2675,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -2708,7 +2698,7 @@
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -2744,7 +2734,7 @@
       <c r="AB14" t="inlineStr">
         <is>
           <t>A new month with more winners.
-Congratulations to the grand prize winner of a ROX 01 car, and to the winners of the 10-gram gold piece for participating in the "It's Time to Win Grand Prizes" campaign offered by business banking for January 2026.
+Congratulations to the grand prize winner of the ROX 01 car, and to the winners of the 10-gram gold piece for participating in the "It's Time to Win Grand Prizes" campaign offered by business banking services for January 2026.
 Continue using your business account to carry out foreign exchange transactions and trade financing to increase your company's chances of winning. The offer is valid until March 31, 2026.</t>
         </is>
       </c>
@@ -2851,7 +2841,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -2874,7 +2864,7 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -2999,7 +2989,7 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -3026,7 +3016,7 @@
         <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -3165,7 +3155,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -3192,7 +3182,7 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
@@ -3324,7 +3314,7 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -3351,7 +3341,7 @@
         <v>1</v>
       </c>
       <c r="V18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -3486,7 +3476,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -3509,7 +3499,7 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -3616,6 +3606,184 @@
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
+        <is>
+          <t>Every time you dine at any restaurant inside TMG, you’ll earn 5%cashback when you pay using your Emirates NBD Mastercard credit card x TMG.
+Apply now and benefit from a dedicated program for TMG clients.
+Together .. it pays off.
+Terms and conditions apply.
+Tax registration number: 204-897-319</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Every time you dine at any restaurant inside TMG, you’ll earn 5%cashback when you pay using your Emirates NBD Mastercard credit card x TMG.
+Apply now and benefit from a dedicated program for TMG clients.
+Together .. it pays off.
+Terms and conditions apply.
+Tax registration number: 204-897-319</t>
+        </is>
+      </c>
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>19h</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Mar 27, 2026 · 11:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="n">
+        <v>46108.45833333334</v>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>65</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Every time you dine at any restaurant inside TMG, you’ll earn 5%cashback when you pay using your Emirates NBD Mastercard credit card x TMG.
+Apply now and benefit from a dedicated program for TMG clients.
+Together .. it pays off.
+Terms and conditions apply.
+Tax registration number: 204-897-319</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_EGY/status/2037484781038862844</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>Every time you dine at any restaurant inside TMG, you’ll earn 5%cashback when you pay using your Emirates NBD Mastercard credit card x TMG.
+Apply now and benefit from a dedicated program for TMG clients.
+Together .. it pays off.
+Terms and conditions apply.
+Tax registration number: 204-897-319</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>Every time you dine at any restaurant inside TMG, you’ll earn 5%cashback when you pay using your Emirates NBD Mastercard credit card x TMG.
+Apply now and benefit from a dedicated program for TMG clients.
+Together .. it pays off.
+Terms and conditions apply.
+Tax registration number: 204-897-319</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>Every time you dine at any restaurant inside TMG, you’ll earn 5% cashback when you pay using your Emirates NBD Mastercard credit card x TMG. 
+Apply now and benefit from a dedicated program for TMG clients. 
+Together .. it pays off. 
+Terms and conditions apply. 
+Tax registration number: 204-897-319</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Bank</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AE20" s="2" t="n">
+        <v>46108.625</v>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>27-03-2026</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Every time you dine at any restaurant inside TMG, you’ll earn 5% cashback when you pay using your Emirates NBD Mastercard credit card x TMG. • Tax registration number: 204-897-319 • Apply now and benefit from a dedicated program for TMG clients.</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK20" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2037484780925644991</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_EGY/status/2037484780925644991</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_EGY</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_EGY</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Emirates NBD</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1762427526482108416/qjFPlJ1n_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
         <is>
           <t>Plan your vacation now!
 Get 5% off flights and 10% off hotels with Flyin when you pay with your Emirates NBD credit card using code: FAWRY
@@ -3624,67 +3792,67 @@
 Tax registration number: 204-897-319 https://t.co/RR0ArWOU9A</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Every time you dine at any restaurant inside TMG, you’ll earn 5%cashback when you pay using your Emirates NBD Mastercard credit card x TMG.
-Apply now and benefit from a dedicated program for TMG clients.
-Together .. it pays off.
-Terms and conditions apply.
-Tax registration number: 204-897-319</t>
-        </is>
-      </c>
-      <c r="K20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>17h</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>كل مرة تدفع فيها في أي مطعم داخل مجموعة طلعت مصطفى، هيرجعلك 5% كاش باك لما تدفع ببطاقة بنك الإمارات دبي الوطني ماستركارد الائتمانية بالتعاون مع مجموعة طلعت مصطفى.
+قدم الان بتسهيلات خاصة لعملاء المجموعة.
+مع بعض .. تفرق.
+تطبق الشروط والأحكام
+رقم التسجيل الضريبي: 319-897-204</t>
+        </is>
+      </c>
+      <c r="K21" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>19h</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
         <is>
           <t>Mar 27, 2026 · 11:00 AM UTC</t>
         </is>
       </c>
-      <c r="P20" s="2" t="n">
+      <c r="P21" s="2" t="n">
         <v>46108.45833333334</v>
       </c>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>64</v>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>Every time you dine at any restaurant inside TMG, you’ll earn 5%cashback when you pay using your Emirates NBD Mastercard credit card x TMG.
-Apply now and benefit from a dedicated program for TMG clients.
-Together .. it pays off.
-Terms and conditions apply.
-Tax registration number: 204-897-319</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_EGY/status/2037484781038862844</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>85</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>كل مرة تدفع فيها في أي مطعم داخل مجموعة طلعت مصطفى، هيرجعلك 5% كاش باك لما تدفع ببطاقة بنك الإمارات دبي الوطني ماستركارد الائتمانية بالتعاون مع مجموعة طلعت مصطفى.
+قدم الان بتسهيلات خاصة لعملاء المجموعة.
+مع بعض .. تفرق.
+تطبق الشروط والأحكام
+رقم التسجيل الضريبي: 319-897-204</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_EGY/status/2037484780925644991</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
         <is>
           <t>Plan your vacation now!
 Get 5% off flights and 10% off hotels with Flyin when you pay with your Emirates NBD credit card using code: FAWRY
@@ -3693,7 +3861,7 @@
 Tax registration number: 204-897-319 https://t.co/RR0ArWOU9A</t>
         </is>
       </c>
-      <c r="AA20" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>Plan your vacation now!
 Get 5% off flights and 10% off hotels with Flyin when you pay with your Emirates NBD credit card using code: FAWRY
@@ -3702,187 +3870,9 @@
 Tax registration number: 204-897-319 https://t.co/RR0ArWOU9A</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>Plan your vacation now! Get 5% off flights and 10% off hotels with Flyin when you pay with your Emirates NBD credit card using code: FAWRY. Offer valid until 30th of March 2026. Terms and conditions apply. Tax registration number: 204-897-319.</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="AE20" s="2" t="n">
-        <v>46108.625</v>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>27-03-2026</t>
-        </is>
-      </c>
-      <c r="AG20" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Get 5% off flights and 10% off hotels with Flyin when you pay with your Emirates NBD credit card using code: FAWRY. • Tax registration number: 204-897-319. • Offer valid until 30th of March 2026.</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AK20" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL20" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2037484780925644991</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_EGY/status/2037484780925644991</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_EGY</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>EmiratesNBD_EGY</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Emirates NBD</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1762427526482108416/qjFPlJ1n_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>كل مرة تدفع فيها في أي مطعم داخل مجموعة طلعت مصطفى، هيرجعلك 5% كاش باك لما تدفع ببطاقة بنك الإمارات دبي الوطني ماستركارد الائتمانية بالتعاون مع مجموعة طلعت مصطفى.
-قدم الان بتسهيلات خاصة لعملاء المجموعة.
-مع بعض .. تفرق.
-تطبق الشروط والأحكام
-رقم التسجيل الضريبي: 319-897-204 https://t.co/ABhnylgeTj</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>كل مرة تدفع فيها في أي مطعم داخل مجموعة طلعت مصطفى، هيرجعلك 5% كاش باك لما تدفع ببطاقة بنك الإمارات دبي الوطني ماستركارد الائتمانية بالتعاون مع مجموعة طلعت مصطفى.
-قدم الان بتسهيلات خاصة لعملاء المجموعة.
-مع بعض .. تفرق.
-تطبق الشروط والأحكام
-رقم التسجيل الضريبي: 319-897-204</t>
-        </is>
-      </c>
-      <c r="K21" t="b">
-        <v>0</v>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>17h</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>Mar 27, 2026 · 11:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="n">
-        <v>46108.45833333334</v>
-      </c>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>84</v>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>كل مرة تدفع فيها في أي مطعم داخل مجموعة طلعت مصطفى، هيرجعلك 5% كاش باك لما تدفع ببطاقة بنك الإمارات دبي الوطني ماستركارد الائتمانية بالتعاون مع مجموعة طلعت مصطفى.
-قدم الان بتسهيلات خاصة لعملاء المجموعة.
-مع بعض .. تفرق.
-تطبق الشروط والأحكام
-رقم التسجيل الضريبي: 319-897-204</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_EGY/status/2037484780925644991</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>كل مرة تدفع فيها في أي مطعم داخل مجموعة طلعت مصطفى، هيرجعلك 5% كاش باك لما تدفع ببطاقة بنك الإمارات دبي الوطني ماستركارد الائتمانية بالتعاون مع مجموعة طلعت مصطفى.
-قدم الان بتسهيلات خاصة لعملاء المجموعة.
-مع بعض .. تفرق.
-تطبق الشروط والأحكام
-رقم التسجيل الضريبي: 319-897-204 https://t.co/ABhnylgeTj</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>كل مرة تدفع فيها في أي مطعم داخل مجموعة طلعت مصطفى، هيرجعلك 5% كاش باك لما تدفع ببطاقة بنك الإمارات دبي الوطني ماستركارد الائتمانية بالتعاون مع مجموعة طلعت مصطفى.
-قدم الان بتسهيلات خاصة لعملاء المجموعة.
-مع بعض .. تفرق.
-تطبق الشروط والأحكام
-رقم التسجيل الضريبي: 319-897-204 https://t.co/ABhnylgeTj</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>Every time you pay at any restaurant within the Talaat Moustafa Group, you will receive 5% cash back when you pay with the Emirates NBD Mastercard credit card in collaboration with the Talaat Moustafa Group.
-Apply now with special facilities for group customers.
-Together, we make a difference.
-Terms and conditions apply.
-Tax registration number: 319-897-204</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3915,7 +3905,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Tax registration number: 319-897-204 • Apply now with special facilities for group customers. • Terms and conditions apply.</t>
+          <t>Get 5% off flights and 10% off hotels with Flyin when you pay with your Emirates NBD credit card using code: FAWRY. • Tax registration number: 204-897-319. • Offer valid until 30th of March 2026.</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -3988,7 +3978,7 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -4015,7 +4005,7 @@
         <v>2</v>
       </c>
       <c r="V22" t="n">
-        <v>914</v>
+        <v>918</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -4163,7 +4153,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -4190,7 +4180,7 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -4339,7 +4329,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -4362,7 +4352,7 @@
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
@@ -4485,7 +4475,7 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -4512,7 +4502,7 @@
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -4639,7 +4629,7 @@
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -4666,7 +4656,7 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
@@ -4805,7 +4795,7 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -4832,7 +4822,7 @@
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
@@ -4974,7 +4964,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -5001,7 +4991,7 @@
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
@@ -5140,7 +5130,7 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -5167,7 +5157,7 @@
         <v>7</v>
       </c>
       <c r="V29" t="n">
-        <v>788</v>
+        <v>817</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
@@ -5190,7 +5180,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Stay safe and bank with ease with ENBD X and businessONLINE. 
+          <t>Stay safe and bank with ease with ENBD X and businessONLINE 
 Visit emiratesnbd.com</t>
         </is>
       </c>
@@ -5224,7 +5214,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Stay safe and bank with ease with ENBD X and businessONLINE.</t>
+          <t>Stay safe and bank with ease with ENBD X and businessONLINE Visit emiratesnbd.com</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -5297,7 +5287,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -5320,7 +5310,7 @@
         <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
@@ -5457,7 +5447,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -5480,7 +5470,7 @@
         <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
@@ -5615,7 +5605,7 @@
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -5642,7 +5632,7 @@
         <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="W32" t="inlineStr">
         <is>
@@ -5776,7 +5766,7 @@
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>23h</t>
+          <t>Mar 27</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -5803,7 +5793,7 @@
         <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
@@ -5945,7 +5935,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>23h</t>
+          <t>Mar 27</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -5972,7 +5962,7 @@
         <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
@@ -6007,7 +5997,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Emirates NBD Mutual Fund #ENBDRiddleOfTheWeek #financialwellbeing</t>
+          <t>Emirates NBD Mutual Fund Riddle of the Week financial wellbeing</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -6040,7 +6030,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Emirates NBD Mutual Fund #ENBDRiddleOfTheWeek #financialwellbeing</t>
+          <t>Emirates NBD Mutual Fund Riddle of the Week financial wellbeing</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
@@ -6145,7 +6135,7 @@
         <v>1</v>
       </c>
       <c r="V35" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
@@ -6188,7 +6178,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Good Morning, Markets! 27th March | 06:40 AM IST From FOMO to FMA — your pre-opening bell edge. Full coverage 👉 https://t.co/Y5CfIAZZlN Market pulse 🧵 #WOWNEWS24x7 #FromFOMOtoFMA https://t.co/TmnAR3J8EH</t>
+          <t>Good Morning, Markets! 27th March | 06:40 AM IST From FOMO to FMA — your pre-opening bell edge. Full coverage 👉 https://t.co/Y5CfIAZZlN Market pulse 🧵 #WOWNEWS24x7 #FromFOMOtoFMA</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -6221,7 +6211,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Full coverage 👉 https://t.co/Y5CfIAZZlN Market pulse 🧵 #WOWNEWS24x7 #FromFOMOtoFMA https://t.co/TmnAR3J8EH • 27th March | 06:40 AM IST From FOMO to FMA — your pre-opening bell edge.</t>
+          <t>27th March | 06:40 AM IST From FOMO to FMA — your pre-opening bell edge. • Full coverage 👉 https://t.co/Y5CfIAZZlN Market pulse 🧵 #WOWNEWS24x7 #FromFOMOtoFMA</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -6492,7 +6482,7 @@
         <v>1</v>
       </c>
       <c r="V37" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
@@ -6524,7 +6514,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>IndoThai Securities: The Company (Indo Thai Financial Services) has increased the authorized share capital from Rs. 3 million to Rs. 150 million.
+          <t>IndoThai Securities: The Company (Indo Thai Financial Services) has increased the authorized Share Capital from Rs. 3 million to Rs. 150 million.
 RBL Bank: Announced that Emirates NBD Bank has received approval from the Central Bank of UAE to acquire a majority stake in RBL Bank.</t>
         </is>
       </c>
@@ -6558,7 +6548,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>RBL Bank: Announced that Emirates NBD Bank has received approval from the Central Bank of UAE to acquire a majority stake in RBL Bank. • IndoThai Securities: The Company (Indo Thai Financial Services) has increased the authorized share capital from Rs.</t>
+          <t>RBL Bank: Announced that Emirates NBD Bank has received approval from the Central Bank of UAE to acquire a majority stake in RBL Bank. • IndoThai Securities: The Company (Indo Thai Financial Services) has increased the authorized Share Capital from Rs.</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -6654,7 +6644,7 @@
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
@@ -6683,7 +6673,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA Could you please respond privately?</t>
+          <t>@EmiratesNBD_KSA Can you respond privately?</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -6716,7 +6706,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA Could you please respond privately?</t>
+          <t>@EmiratesNBD_KSA Can you respond privately?</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
@@ -6739,36 +6729,206 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2037462241591615667</t>
+          <t>2037499728318116157</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2037462241591615667</t>
+          <t>https://x.com/SanadakUAE/status/2037499728318116157</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/SanadakUAE</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>SanadakUAE</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Sanadak</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2012879499768049664/EHCzbImW_bigger.jpg</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
+        <is>
+          <t>Dear Safwan,
+Thank you for contacting Sanadak, Ombudsman Unit for the UAE.
+For more information about our services, please call 800SANADAK or visit our website sanadak.gov.ae/en/.  
+Best regards,
+Sanadak Team</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Dear Safwan,
+Thank you for contacting Sanadak, Ombudsman Unit for the UAE.
+For more information about our services, please call 800SANADAK or visit our website &lt;a href="https://www.sanadak.gov.ae/en/"&gt;sanadak.gov.ae/en/&lt;/a&gt;.  
+Best regards,
+Sanadak Team</t>
+        </is>
+      </c>
+      <c r="K39" t="b">
+        <v>0</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>['abuzubayr1987', 'emiratesislamic', 'JamalIslamic']</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Mar 27, 2026 · 11:59 AM UTC</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="n">
+        <v>46108.49930555555</v>
+      </c>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>['https://www.sanadak.gov.ae/en/']</t>
+        </is>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>14</v>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Dear Safwan,
+Thank you for contacting Sanadak, Ombudsman Unit for the UAE.
+For more information about our services, please call 800SANADAK or visit our website sanadak.gov.ae/en/.  
+Best regards,
+Sanadak Team</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>Dear Safwan,
+Thank you for contacting Sanadak, Ombudsman Unit for the UAE.
+For more information about our services, please call 800SANADAK or visit our website sanadak.gov.ae/en/.  
+Best regards,
+Sanadak Team</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>Dear Safwan, Thank you for contacting Sanadak, Ombudsman Unit for the UAE. For more information about our services, please call 800SANADAK or visit our website sanadak.gov.ae/en/. Best regards, Sanadak Team</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE39" s="2" t="n">
+        <v>46108.66597222222</v>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>27-03-2026</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>2. Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>For more information about our services, please call 800SANADAK or visit our website sanadak.gov.ae/en/. • Dear Safwan, Thank you for contacting Sanadak, Ombudsman Unit for the UAE. • Best regards, Sanadak Team</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AK39" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL39" t="inlineStr">
+        <is>
+          <t>abuzubayr1987, emiratesislamic, JamalIslamic</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2037462241591615667</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2037462241591615667</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
         <is>
           <t>Small choices can make a big difference.
 Staying aware of your spending helps you stay in control — today and tomorrow.
@@ -6777,7 +6937,7 @@
 https://t.co/XvyZgR87nM https://t.co/qmzRHQJjQ8</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>سلامتكم أولويتنا.
 نوصي باستخدام تطبيق + EI ومنصة businessONLINE لإنجاز معاملاتكم المصرفية بسهولة وأمان.
@@ -6785,44 +6945,44 @@
 Use EI + Mobile &amp;amp; Online Banking and businessONLINE with ease and security.</t>
         </is>
       </c>
-      <c r="K39" t="b">
-        <v>0</v>
-      </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>18h</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
+      <c r="K40" t="b">
+        <v>0</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
         <is>
           <t>Mar 27, 2026 · 9:30 AM UTC</t>
         </is>
       </c>
-      <c r="P39" s="2" t="n">
+      <c r="P40" s="2" t="n">
         <v>46108.39583333334</v>
       </c>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
         <v>1</v>
       </c>
-      <c r="U39" t="n">
+      <c r="U40" t="n">
         <v>2</v>
       </c>
-      <c r="V39" t="n">
-        <v>88</v>
-      </c>
-      <c r="W39" t="inlineStr">
+      <c r="V40" t="n">
+        <v>90</v>
+      </c>
+      <c r="W40" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>سلامتكم أولويتنا.
 نوصي باستخدام تطبيق + EI ومنصة businessONLINE لإنجاز معاملاتكم المصرفية بسهولة وأمان.
@@ -6830,12 +6990,12 @@
 Use EI + Mobile &amp; Online Banking and businessONLINE with ease and security.</t>
         </is>
       </c>
-      <c r="Y39" t="inlineStr">
+      <c r="Y40" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2037462241591615667</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
+      <c r="Z40" t="inlineStr">
         <is>
           <t>Small choices can make a big difference.
 Staying aware of your spending helps you stay in control — today and tomorrow.
@@ -6844,7 +7004,7 @@
 https://t.co/XvyZgR87nM https://t.co/qmzRHQJjQ8</t>
         </is>
       </c>
-      <c r="AA39" t="inlineStr">
+      <c r="AA40" t="inlineStr">
         <is>
           <t>Small choices can make a big difference.
 Staying aware of your spending helps you stay in control — today and tomorrow.
@@ -6853,211 +7013,47 @@
 https://t.co/XvyZgR87nM https://t.co/qmzRHQJjQ8</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>Small choices can make a big difference. Staying aware of your spending helps you stay in control — today and tomorrow. #FinancialWellbeing #Finwell #Spending #EmiratesIslamic To know more, Visit: https://t.co/XvyZgR87nM https://t.co/qmzRHQJjQ8</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>Small choices can make a big difference. Staying aware of your spending helps you stay in control — today and tomorrow. #FinancialWellbeing #Finwell #Spending #EmiratesIslamic To know more, visit: https://t.co/XvyZgR87nM https://t.co/qmzRHQJjQ8</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
         <is>
           <t>Bank</t>
         </is>
       </c>
-      <c r="AD39" t="inlineStr">
+      <c r="AD40" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="AE39" s="2" t="n">
+      <c r="AE40" s="2" t="n">
         <v>46108.5625</v>
       </c>
-      <c r="AF39" t="inlineStr">
+      <c r="AF40" t="inlineStr">
         <is>
           <t>27-03-2026</t>
         </is>
       </c>
-      <c r="AG39" t="inlineStr">
+      <c r="AG40" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="AH39" t="inlineStr">
+      <c r="AH40" t="inlineStr">
         <is>
           <t>2. Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>#FinancialWellbeing #Finwell #Spending #EmiratesIslamic To know more, Visit: https://t.co/XvyZgR87nM https://t.co/qmzRHQJjQ8 • Staying aware of your spending helps you stay in control — today and tomorrow. • Small choices can make a big difference.</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>#FinancialWellbeing #Finwell #Spending #EmiratesIslamic To know more, visit: https://t.co/XvyZgR87nM https://t.co/qmzRHQJjQ8 • Staying aware of your spending helps you stay in control — today and tomorrow. • Small choices can make a big difference.</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
         <is>
           <t>Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AK39" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL39" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="n">
-        <v>38</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2037466808576266477</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037466808576266477</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>EmiratesNBD_AE</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Emirates NBD</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>@xlcsp We sincerely regret for the inconvenience To be able to assist further, we kindly request you to reach out to us
-livsocialconnect@liv.me
-Quoting case 988539 in the subject line of the email from your registered email address We will make every effort to address the matter</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>Kindly be informed that Liv team will be checking and responding to your email shortly, thank you for your patience.</t>
-        </is>
-      </c>
-      <c r="K40" t="b">
-        <v>0</v>
-      </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>['xlcsp']</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>18h</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>Mar 27, 2026 · 9:48 AM UTC</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="n">
-        <v>46108.40833333333</v>
-      </c>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" t="n">
-        <v>8</v>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>Kindly be informed that Liv team will be checking and responding to your email shortly, thank you for your patience.</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037466808576266477</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>@xlcsp We sincerely regret for the inconvenience To be able to assist further, we kindly request you to reach out to us
-livsocialconnect@liv.me
-Quoting case 988539 in the subject line of the email from your registered email address We will make every effort to address the matter</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>@xlcsp We sincerely regret for the inconvenience To be able to assist further, we kindly request you to reach out to us
-livsocialconnect@liv.me
-Quoting case 988539 in the subject line of the email from your registered email address We will make every effort to address the matter</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>We sincerely regret the inconvenience. To assist you further, we kindly request that you reach out to us at livsocialconnect@liv.me, quoting case 988539 in the subject line of the email from your registered email address. We will make every effort to address the matter.</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD40" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="AE40" s="2" t="n">
-        <v>46108.575</v>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>27-03-2026</t>
-        </is>
-      </c>
-      <c r="AG40" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>To assist you further, we kindly request that you reach out to us at livsocialconnect@liv.me, quoting case 988539 in the subject line of the email from your registered email address. • We will make every effort to address the matter. • We sincerely regret the inconvenience.</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
       <c r="AK40" t="n">
@@ -7065,7 +7061,7 @@
       </c>
       <c r="AL40" t="inlineStr">
         <is>
-          <t>xlcsp</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -7075,43 +7071,45 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2037506557190021420</t>
+          <t>2037466808576266477</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://x.com/HashemTakriti/status/2037506557190021420</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2037466808576266477</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://x.com/HashemTakriti</t>
+          <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>HashemTakriti</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hashem Takriti</t>
+          <t>Emirates NBD</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1081667250761990144/23AHZt15_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE  I’m still waiting to fix my issue, nothing happened since last week.</t>
+          <t>@xlcsp We sincerely regret for the inconvenience To be able to assist further, we kindly request you to reach out to us
+livsocialconnect@liv.me
+Quoting case 988539 in the subject line of the email from your registered email address We will make every effort to address the matter</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;  I’m still waiting to fix my issue, nothing happened since last week.</t>
+          <t>Kindly be informed that Liv team will be checking and responding to your email shortly, thank you for your patience.</t>
         </is>
       </c>
       <c r="K41" t="b">
@@ -7120,30 +7118,26 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>['EmiratesNBD_AE']</t>
+          <t>['xlcsp']</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Mar 27, 2026 · 12:26 PM UTC</t>
+          <t>Mar 27, 2026 · 9:48 AM UTC</t>
         </is>
       </c>
       <c r="P41" s="2" t="n">
-        <v>46108.51805555556</v>
+        <v>46108.40833333333</v>
       </c>
       <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>['https://x.com/EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="R41" t="inlineStr"/>
       <c r="S41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
         <v>0</v>
@@ -7152,7 +7146,7 @@
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
@@ -7161,19 +7155,31 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE  I’m still waiting to fix my issue, nothing happened since last week.</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr"/>
-      <c r="Z41" t="inlineStr"/>
+          <t>Kindly be informed that Liv team will be checking and responding to your email shortly, thank you for your patience.</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037466808576266477</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>@xlcsp We sincerely regret for the inconvenience To be able to assist further, we kindly request you to reach out to us
+livsocialconnect@liv.me
+Quoting case 988539 in the subject line of the email from your registered email address We will make every effort to address the matter</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE  I’m still waiting to fix my issue, nothing happened since last week.</t>
+          <t>@xlcsp We sincerely regret for the inconvenience To be able to assist further, we kindly request you to reach out to us
+livsocialconnect@liv.me
+Quoting case 988539 in the subject line of the email from your registered email address We will make every effort to address the matter</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>I’m still waiting to fix my issue, nothing has happened since last week.</t>
+          <t>We sincerely regret the inconvenience. To assist you further, we kindly request that you reach out to us at livsocialconnect@liv.me, quoting case 988539 in the subject line of the email from your registered email address. We will make every effort to address the matter.</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -7187,7 +7193,7 @@
         </is>
       </c>
       <c r="AE41" s="2" t="n">
-        <v>46108.68472222222</v>
+        <v>46108.575</v>
       </c>
       <c r="AF41" t="inlineStr">
         <is>
@@ -7206,7 +7212,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>I’m still waiting to fix my issue, nothing has happened since last week.</t>
+          <t>To assist you further, we kindly request that you reach out to us at livsocialconnect@liv.me, quoting case 988539 in the subject line of the email from your registered email address. • We will make every effort to address the matter. • We sincerely regret the inconvenience.</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
@@ -7219,7 +7225,7 @@
       </c>
       <c r="AL41" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>xlcsp</t>
         </is>
       </c>
     </row>
@@ -7229,43 +7235,43 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2037491991504998834</t>
+          <t>2037506557190021420</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://x.com/HimanshuMotiyan/status/2037491991504998834</t>
+          <t>https://x.com/HashemTakriti/status/2037506557190021420</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://x.com/HimanshuMotiyan</t>
+          <t>https://x.com/HashemTakriti</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>HimanshuMotiyan</t>
+          <t>HashemTakriti</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Himanshu Motiyani</t>
+          <t>Hashem Takriti</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2032072703134613504/JzErzVWc_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1081667250761990144/23AHZt15_bigger.jpg</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Hello still the solution has not been provided by your team its more then a month @EmiratesNBD_AE</t>
+          <t>@EmiratesNBD_AE  I’m still waiting to fix my issue, nothing happened since last week.</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Hello still the solution has not been provided by your team its more then a month &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;</t>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;  I’m still waiting to fix my issue, nothing happened since last week.</t>
         </is>
       </c>
       <c r="K42" t="b">
@@ -7279,16 +7285,16 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Mar 27, 2026 · 11:28 AM UTC</t>
+          <t>Mar 27, 2026 · 12:26 PM UTC</t>
         </is>
       </c>
       <c r="P42" s="2" t="n">
-        <v>46108.47777777778</v>
+        <v>46108.51805555556</v>
       </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr">
@@ -7306,7 +7312,7 @@
         <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
@@ -7315,19 +7321,19 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Hello still the solution has not been provided by your team its more then a month @EmiratesNBD_AE</t>
+          <t>@EmiratesNBD_AE  I’m still waiting to fix my issue, nothing happened since last week.</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>Hello still the solution has not been provided by your team its more then a month @EmiratesNBD_AE</t>
+          <t>@EmiratesNBD_AE  I’m still waiting to fix my issue, nothing happened since last week.</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>Hello, the solution has still not been provided by your team; it's been more than a month.</t>
+          <t>I’m still waiting to fix my issue, nothing has happened since last week.</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -7341,7 +7347,7 @@
         </is>
       </c>
       <c r="AE42" s="2" t="n">
-        <v>46108.64444444444</v>
+        <v>46108.68472222222</v>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
@@ -7360,7 +7366,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Hello, the solution has still not been provided by your team; it's been more than a month.</t>
+          <t>I’m still waiting to fix my issue, nothing has happened since last week.</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
@@ -7383,43 +7389,43 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2037502797097361735</t>
+          <t>2037491991504998834</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://x.com/Ibn_3ali/status/2037502797097361735</t>
+          <t>https://x.com/HimanshuMotiyan/status/2037491991504998834</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://x.com/Ibn_3ali</t>
+          <t>https://x.com/HimanshuMotiyan</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ibn_3ali</t>
+          <t>HimanshuMotiyan</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ahmed Ali</t>
+          <t>Himanshu Motiyani</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1836334761129721856/vSK3evXJ_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2032072703134613504/JzErzVWc_bigger.jpg</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>كنت عايز أقفل حسابي</t>
+          <t>Hello still the solution has not been provided by your team its more then a month @EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>كنت عايز أقفل حسابي</t>
+          <t>Hello still the solution has not been provided by your team its more then a month &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K43" t="b">
@@ -7433,19 +7439,23 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Mar 27, 2026 · 12:11 PM UTC</t>
+          <t>Mar 27, 2026 · 11:28 AM UTC</t>
         </is>
       </c>
       <c r="P43" s="2" t="n">
-        <v>46108.50763888889</v>
+        <v>46108.47777777778</v>
       </c>
       <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="S43" t="n">
         <v>1</v>
       </c>
@@ -7456,7 +7466,7 @@
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="W43" t="inlineStr">
         <is>
@@ -7465,19 +7475,19 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>كنت عايز أقفل حسابي</t>
+          <t>Hello still the solution has not been provided by your team its more then a month @EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>كنت عايز أقفل حسابي</t>
+          <t>Hello still the solution has not been provided by your team its more then a month @EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>I wanted to close my account.</t>
+          <t>Hello, the solution has still not been provided by your team; it's been more than a month.</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -7491,7 +7501,7 @@
         </is>
       </c>
       <c r="AE43" s="2" t="n">
-        <v>46108.67430555556</v>
+        <v>46108.64444444444</v>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
@@ -7510,7 +7520,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>I wanted to close my account.</t>
+          <t>Hello, the solution has still not been provided by your team; it's been more than a month.</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
@@ -7533,45 +7543,43 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2037480161797722518</t>
+          <t>2037502797097361735</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://x.com/abuzubayr1987/status/2037480161797722518</t>
+          <t>https://x.com/Ibn_3ali/status/2037502797097361735</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://x.com/abuzubayr1987</t>
+          <t>https://x.com/Ibn_3ali</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>abuzubayr1987</t>
+          <t>Ibn_3ali</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Safwan</t>
+          <t>Ahmed Ali</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1836334761129721856/vSK3evXJ_bigger.jpg</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Hello
-I got a call from your social media team, with no real solution because they cannot access my account from alternative number. While all other departments are quick enough to access details and deduct undue amounts without prior notice.</t>
+          <t>كنت عايز أقفل حسابي</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Hello
-I got a call from your social media team, with no real solution because they cannot access my account from alternative number. While all other departments are quick enough to access details and deduct undue amounts without prior notice.</t>
+          <t>كنت عايز أقفل حسابي</t>
         </is>
       </c>
       <c r="K44" t="b">
@@ -7580,21 +7588,21 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>['emiratesislamic']</t>
+          <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Mar 27, 2026 · 10:41 AM UTC</t>
+          <t>Mar 27, 2026 · 12:11 PM UTC</t>
         </is>
       </c>
       <c r="P44" s="2" t="n">
-        <v>46108.44513888889</v>
+        <v>46108.50763888889</v>
       </c>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
@@ -7608,30 +7616,28 @@
         <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>ENBD</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Hello
-I got a call from your social media team, with no real solution because they cannot access my account from alternative number. While all other departments are quick enough to access details and deduct undue amounts without prior notice.</t>
+          <t>كنت عايز أقفل حسابي</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>Hello
-I got a call from your social media team, with no real solution because they cannot access my account from alternative number. While all other departments are quick enough to access details and deduct undue amounts without prior notice.</t>
+          <t>كنت عايز أقفل حسابي</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>Hello I received a call from your social media team, but they didn't provide a real solution because they cannot access my account using an alternative number. Meanwhile, all other departments are quick to access details and deduct incorrect amounts without prior notice.</t>
+          <t>I wanted to close my account.</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -7645,7 +7651,7 @@
         </is>
       </c>
       <c r="AE44" s="2" t="n">
-        <v>46108.61180555556</v>
+        <v>46108.67430555556</v>
       </c>
       <c r="AF44" t="inlineStr">
         <is>
@@ -7654,22 +7660,22 @@
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>ENBD</t>
         </is>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
+          <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Hello I received a call from your social media team, but they didn't provide a real solution because they cannot access my account using an alternative number. • Meanwhile, all other departments are quick to access details and deduct incorrect amounts without prior notice.</t>
+          <t>I wanted to close my account.</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>Emirates Islamic Bank (EIB)</t>
+          <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
       <c r="AK44" t="n">
@@ -7677,7 +7683,7 @@
       </c>
       <c r="AL44" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
     </row>
@@ -7687,69 +7693,71 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2037464657695563894</t>
+          <t>2037480161797722518</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://x.com/harrissayoub/status/2037464657695563894</t>
+          <t>https://x.com/abuzubayr1987/status/2037480161797722518</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://x.com/harrissayoub</t>
+          <t>https://x.com/abuzubayr1987</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>harrissayoub</t>
+          <t>abuzubayr1987</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Harris</t>
+          <t>Safwan</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1941456770540417024/W7CsxFZc_bigger.jpg</t>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Dealing with @EmiratesNBD_AE always follows the same pattern. Stage 1: Delays. Stage 2: Unclear responses. And finally Stage 3: Multiple follow-ups just to get the simplest things done. Currently at Stage 3.</t>
+          <t>Hello
+I got a call from your social media team, with no real solution because they cannot access my account from alternative number. While all other departments are quick enough to access details and deduct undue amounts without prior notice.</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Dealing with &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; always follows the same pattern. Stage 1: Delays. Stage 2: Unclear responses. And finally Stage 3: Multiple follow-ups just to get the simplest things done. Currently at Stage 3.</t>
+          <t>Hello
+I got a call from your social media team, with no real solution because they cannot access my account from alternative number. While all other departments are quick enough to access details and deduct undue amounts without prior notice.</t>
         </is>
       </c>
       <c r="K45" t="b">
         <v>0</v>
       </c>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Mar 27, 2026 · 9:40 AM UTC</t>
+          <t>Mar 27, 2026 · 10:41 AM UTC</t>
         </is>
       </c>
       <c r="P45" s="2" t="n">
-        <v>46108.40277777778</v>
+        <v>46108.44513888889</v>
       </c>
       <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>['https://x.com/EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="R45" t="inlineStr"/>
       <c r="S45" t="n">
         <v>1</v>
       </c>
@@ -7760,28 +7768,30 @@
         <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Dealing with @EmiratesNBD_AE always follows the same pattern. Stage 1: Delays. Stage 2: Unclear responses. And finally Stage 3: Multiple follow-ups just to get the simplest things done. Currently at Stage 3.</t>
+          <t>Hello
+I got a call from your social media team, with no real solution because they cannot access my account from alternative number. While all other departments are quick enough to access details and deduct undue amounts without prior notice.</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="inlineStr"/>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>Dealing with @EmiratesNBD_AE always follows the same pattern. Stage 1: Delays. Stage 2: Unclear responses. And finally Stage 3: Multiple follow-ups just to get the simplest things done. Currently at Stage 3.</t>
+          <t>Hello
+I got a call from your social media team, with no real solution because they cannot access my account from alternative number. While all other departments are quick enough to access details and deduct undue amounts without prior notice.</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>Dealing with Emirates NBD always follows the same pattern. Stage 1: Delays. Stage 2: Unclear responses. And finally Stage 3: Multiple follow-ups just to get the simplest things done. Currently at Stage 3.</t>
+          <t>Hello I received a call from your social media team, but they didn't provide a real solution because they cannot access my account using an alternative number. Meanwhile, all other departments are quick to access details and deduct incorrect amounts without prior notice.</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -7795,7 +7805,7 @@
         </is>
       </c>
       <c r="AE45" s="2" t="n">
-        <v>46108.56944444445</v>
+        <v>46108.61180555556</v>
       </c>
       <c r="AF45" t="inlineStr">
         <is>
@@ -7804,28 +7814,178 @@
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
+          <t>2. Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>And finally Stage 3: Multiple follow-ups just to get the simplest things done. • Stage 2: Unclear responses. • Dealing with Emirates NBD always follows the same pattern.</t>
+          <t>Hello I received a call from your social media team, but they didn't provide a real solution because they cannot access my account using an alternative number. • Meanwhile, all other departments are quick to access details and deduct incorrect amounts without prior notice.</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank (ENBD)</t>
+          <t>Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AK45" t="n">
         <v>2026</v>
       </c>
       <c r="AL45" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2037464657695563894</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://x.com/harrissayoub/status/2037464657695563894</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://x.com/harrissayoub</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>harrissayoub</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Harris</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1941456770540417024/W7CsxFZc_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Dealing with @EmiratesNBD_AE always follows the same pattern. Stage 1: Delays. Stage 2: Unclear responses. And finally Stage 3: Multiple follow-ups just to get the simplest things done. Currently at Stage 3.</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Dealing with &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; always follows the same pattern. Stage 1: Delays. Stage 2: Unclear responses. And finally Stage 3: Multiple follow-ups just to get the simplest things done. Currently at Stage 3.</t>
+        </is>
+      </c>
+      <c r="K46" t="b">
+        <v>0</v>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Mar 27, 2026 · 9:40 AM UTC</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="n">
+        <v>46108.40277777778</v>
+      </c>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="S46" t="n">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>12</v>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Dealing with @EmiratesNBD_AE always follows the same pattern. Stage 1: Delays. Stage 2: Unclear responses. And finally Stage 3: Multiple follow-ups just to get the simplest things done. Currently at Stage 3.</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>Dealing with @EmiratesNBD_AE always follows the same pattern. Stage 1: Delays. Stage 2: Unclear responses. And finally Stage 3: Multiple follow-ups just to get the simplest things done. Currently at Stage 3.</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>Dealing with Emirates NBD always follows the same pattern. Stage 1: Delays. Stage 2: Unclear responses. And finally Stage 3: Multiple follow-ups just to get the simplest things done. Currently at Stage 3.</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AE46" s="2" t="n">
+        <v>46108.56944444445</v>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>27-03-2026</t>
+        </is>
+      </c>
+      <c r="AG46" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>And finally Stage 3: Multiple follow-ups just to get the simplest things done. • Stage 2: Unclear responses. • Dealing with Emirates NBD always follows the same pattern.</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK46" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL46" t="inlineStr">
         <is>
           <t>None</t>
         </is>

--- a/check2.xlsx
+++ b/check2.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL40"/>
+  <dimension ref="A1:AL39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -677,7 +677,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -700,7 +700,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -821,7 +821,9 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>We regret to inform you that this process can be done only by a branch visit within the UAE.</t>
+          <t>What’s more suspicious?
+Stay Safe, Stay Vigilant. #UnitedAgainstFraud
+https://t.co/YpRWtBZrhq</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -840,7 +842,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>12h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -863,7 +865,7 @@
         <v>1</v>
       </c>
       <c r="V3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -875,16 +877,29 @@
           <t>We regret to inform you that this process can be done only by a branch visit within the UAE.</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037936526093430909</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>What’s more suspicious?
+Stay Safe, Stay Vigilant. #UnitedAgainstFraud
+https://t.co/YpRWtBZrhq</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>We regret to inform you that this process can be done only by a branch visit within the UAE.</t>
+          <t>What’s more suspicious?
+Stay Safe, Stay Vigilant. #UnitedAgainstFraud
+https://t.co/YpRWtBZrhq</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>We regret to inform you that this process can only be completed by visiting a branch within the UAE.</t>
+          <t>What’s more suspicious? 
+Stay Safe, Stay Vigilant. #UnitedAgainstFraud</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -917,7 +932,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>We regret to inform you that this process can only be completed by visiting a branch within the UAE.</t>
+          <t>Stay Safe, Stay Vigilant.</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -971,9 +986,7 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>What’s more suspicious?
-Stay Safe, Stay Vigilant. #UnitedAgainstFraud
-https://t.co/YpRWtBZrhq</t>
+          <t>I just got back from the UAE, is there any chance I can start the process online. I'll probably go again in august.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,7 +1005,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>12h</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1015,7 +1028,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -1027,29 +1040,16 @@
           <t>I just got back from the UAE, is there any chance I can start the process online. I'll probably go again in august.</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>https://x.com/cruizomfs/status/2037928218003382573</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>What’s more suspicious?
-Stay Safe, Stay Vigilant. #UnitedAgainstFraud
-https://t.co/YpRWtBZrhq</t>
-        </is>
-      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>What’s more suspicious?
-Stay Safe, Stay Vigilant. #UnitedAgainstFraud
-https://t.co/YpRWtBZrhq</t>
+          <t>I just got back from the UAE, is there any chance I can start the process online. I'll probably go again in august.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>What’s more suspicious? 
-Stay Safe, Stay Vigilant. #UnitedAgainstFraud</t>
+          <t>I just got back from the UAE, is there any chance I can start the process online? I'll probably go again in August.</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Stay Safe, Stay Vigilant.</t>
+          <t>I just got back from the UAE, is there any chance I can start the process online? • I'll probably go again in August.</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>12h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1210,7 +1210,7 @@
         <v>1</v>
       </c>
       <c r="V5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -1266,9 +1266,9 @@
           <t>Hi, thank you for reaching out. Please be informed that you can apply for a non-resident account by visiting one of our branches within the UAE.  
 Documents:  
 Proof of Identification:  
-Original passport for sighting.  
+Original Passport for sighting  
 In case of dual nationality, copies of both passports are required.  
-Proof of Income / Employment:  
+Proof of Income / Employment  
 For employed individuals, any one of the following documents is required:  
 Salary letter/certificate  
 Employment contract  
@@ -1312,7 +1312,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Proof of Address: Two months of utility bills that show a normal range of consumption at the time of billing (The bill should not be more than 3 months old) • Please be informed that you can apply for a non-resident account by visiting one of our branches within the UAE. • Documents: Proof of Identification: Original passport for sighting.</t>
+          <t>Proof of Address: Two months of utility bills that show a normal range of consumption at the time of billing (The bill should not be more than 3 months old) • Documents: Proof of Identification: Original Passport for sighting In case of dual nationality, copies of both passports are required. • Please be informed that you can apply for a non-resident account by visiting one of our branches within the UAE.</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>12h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1408,7 +1408,7 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1562,7 +1562,7 @@
         <v>2</v>
       </c>
       <c r="V7" t="n">
-        <v>641</v>
+        <v>651</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1717,7 +1717,7 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1868,7 +1868,7 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -2030,7 +2030,7 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -2178,7 +2178,7 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>The woman who carried you for 9 months, may she live long and witness you succeed.</t>
+          <t>The woman who carried you for 9 months may she live long and witness you succeed 🤍</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2240,7 +2240,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>The woman who carried you for 9 months, may she live long and witness you succeed.</t>
+          <t>The woman who carried you for 9 months may she live long and witness you succeed 🤍</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -2313,7 +2313,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -2340,7 +2340,7 @@
         <v>3</v>
       </c>
       <c r="V12" t="n">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -2375,8 +2375,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Before clicking a link, what do you do?
-Stay Safe, Stay Vigilant. #UnitedAgainstFraud</t>
+          <t>Before clicking a link, what do you do? Stay safe, stay vigilant. #UnitedAgainstFraud</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2409,7 +2408,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Stay Safe, Stay Vigilant. • Before clicking a link, what do you do?</t>
+          <t>Stay safe, stay vigilant. • Before clicking a link, what do you do?</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2484,7 +2483,7 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -2511,7 +2510,7 @@
         <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -2606,186 +2605,36 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2037796434725269639</t>
+          <t>2037796009921900610</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://x.com/ZaibKang/status/2037796434725269639</t>
+          <t>https://x.com/MazBalushi35285/status/2037796009921900610</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://x.com/ZaibKang</t>
+          <t>https://x.com/MazBalushi35285</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ZaibKang</t>
+          <t>MazBalushi35285</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Jahan Zaib Akbar Kang</t>
+          <t>مازن البلوشي</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2028644994790436864/h-Avrj3s_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2018589030322253824/-R_IX5Kh_bigger.jpg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
-        <is>
-          <t>Thanks for your timely response.</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Thanks for your timely response.</t>
-        </is>
-      </c>
-      <c r="K14" t="b">
-        <v>0</v>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>20h</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Mar 28, 2026 · 7:38 AM UTC</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="n">
-        <v>46109.31805555556</v>
-      </c>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>9</v>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>Thanks for your timely response.</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Thanks for your timely response.</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Thank you for your timely response.</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AE14" s="2" t="n">
-        <v>46109.48472222222</v>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>28-03-2026</t>
-        </is>
-      </c>
-      <c r="AG14" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Thank you for your timely response.</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AK14" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>EmiratesNBD_AE</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2037796009921900610</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>https://x.com/MazBalushi35285/status/2037796009921900610</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>https://x.com/MazBalushi35285</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>MazBalushi35285</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>مازن البلوشي</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2018589030322253824/-R_IX5Kh_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
         <is>
           <t>جمهور الصقر جاهزين لحفل العيد مع صقر الأغنية الخليجية #رابح_صقر ؟🦅🎶
 #روتانا_لايف
@@ -2799,63 +2648,63 @@
 @EmiratesNBD_KSA https://t.co/0V3B6UgNKV</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>🥳مزيد من النواة الفн على مسابقة رابح صقر! راحت لكم الحفل العيد في الرياض! 🎉 فوق_النهاية فقط</t>
         </is>
       </c>
-      <c r="K15" t="b">
-        <v>0</v>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
         <is>
           <t>['RotanaLive', 'Turki_alalshikh', 'RabehSaqer', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>20h</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 7:36 AM UTC</t>
         </is>
       </c>
-      <c r="P15" s="2" t="n">
+      <c r="P14" s="2" t="n">
         <v>46109.31666666667</v>
       </c>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>26</v>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>27</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
         <is>
           <t>🥳مزيد من النواة الفн على مسابقة رابح صقر! راحت لكم الحفل العيد في الرياض! 🎉 فوق_النهاية فقط</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>https://x.com/MazBalushi35285/status/2037796009921900610</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>جمهور الصقر جاهزين لحفل العيد مع صقر الأغنية الخليجية #رابح_صقر ؟🦅🎶
 #روتانا_لايف
@@ -2869,7 +2718,7 @@
 @EmiratesNBD_KSA https://t.co/0V3B6UgNKV</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>جمهور الصقر جاهزين لحفل العيد مع صقر الأغنية الخليجية #رابح_صقر ؟🦅🎶
 #روتانا_لايف
@@ -2883,94 +2732,94 @@
 @EmiratesNBD_KSA https://t.co/0V3B6UgNKV</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>The audience of Saqr is ready for the Eid celebration with the falcon of Gulf music, Rabeh Saqr? 🦅🎶</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
+      <c r="AC14" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr">
+      <c r="AD14" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="AE15" s="2" t="n">
+      <c r="AE14" s="2" t="n">
         <v>46109.48333333333</v>
       </c>
-      <c r="AF15" t="inlineStr">
+      <c r="AF14" t="inlineStr">
         <is>
           <t>28-03-2026</t>
         </is>
       </c>
-      <c r="AG15" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH15" t="inlineStr">
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AI15" t="inlineStr">
+      <c r="AI14" t="inlineStr">
         <is>
           <t>The audience of Saqr is ready for the Eid celebration with the falcon of Gulf music, Rabeh Saqr?</t>
         </is>
       </c>
-      <c r="AJ15" t="inlineStr">
+      <c r="AJ14" t="inlineStr">
         <is>
           <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AK15" t="n">
+      <c r="AK14" t="n">
         <v>2026</v>
       </c>
-      <c r="AL15" t="inlineStr">
+      <c r="AL14" t="inlineStr">
         <is>
           <t>RotanaLive, Turki_alalshikh, RabehSaqer, GEA_SA, EidSeason, Mabdoarena, EmiratesNBD_KSA</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>2037790087141101872</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola/status/2037790087141101872</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>SelmaRomola</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Selma Romola</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1118152018995105792/5fyZOTth_bigger.jpg</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
         <is>
           <t>نفذت أموال أم خماس قبل نهاية الشهر.
 هناك قاعدة بسيطة تُساعدها على إدارة أموالها بحكمة:
@@ -2997,7 +2846,7 @@
 - Drop your answer below for a chance to win AED 10,000</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>Fin well Financial well-being program with Emirates NBD 
 &lt;a href="/Sabaashraff" title="Saba Ashraf"&gt;@Sabaashraff&lt;/a&gt;
@@ -3005,52 +2854,52 @@
 &lt;a href="/Amanekhattab1" title="Amanekhattab"&gt;@Amanekhattab1&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K16" t="b">
-        <v>0</v>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>20h</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 7:13 AM UTC</t>
         </is>
       </c>
-      <c r="P16" s="2" t="n">
+      <c r="P15" s="2" t="n">
         <v>46109.30069444444</v>
       </c>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr">
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
         <is>
           <t>['https://x.com/Sabaashraff', 'https://x.com/Sosomostafa729S', 'https://x.com/Amanekhattab1']</t>
         </is>
       </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>7</v>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>8</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
         <is>
           <t>Fin well Financial well-being program with Emirates NBD 
 @Sabaashraff
@@ -3058,12 +2907,12 @@
 @Amanekhattab1</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola/status/2037790087141101872</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>نفذت أموال أم خماس قبل نهاية الشهر.
 هناك قاعدة بسيطة تُساعدها على إدارة أموالها بحكمة:
@@ -3090,7 +2939,7 @@
 - Drop your answer below for a chance to win AED 10,000</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>نفذت أموال أم خماس قبل نهاية الشهر.
 هناك قاعدة بسيطة تُساعدها على إدارة أموالها بحكمة:
@@ -3117,105 +2966,105 @@
 - Drop your answer below for a chance to win AED 10,000</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>Um Khammas ran out of cash before the month ended.
 A simple rule can help her stay on track:
 50% for needs
 30% for wants
 20% for savings
-A smart plan that helps you spend, save, and stay in control.
-This is one of the many tips that the bank’s program has in store.
-Watch the episode and tell us the name of the program?
+A smart plan that helps you spend, save and stay in control.
+This is one of the many tips that the bank’s programme has in store.
+Watch the episode and tell us the name of the programme?
 To participate:
 - Follow Emirates NBD
 - Tag 3 friends
 - Drop your answer below for a chance to win AED 10,000</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
+      <c r="AC15" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="AD16" t="inlineStr">
+      <c r="AD15" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="AE16" s="2" t="n">
+      <c r="AE15" s="2" t="n">
         <v>46109.46736111111</v>
       </c>
-      <c r="AF16" t="inlineStr">
+      <c r="AF15" t="inlineStr">
         <is>
           <t>28-03-2026</t>
         </is>
       </c>
-      <c r="AG16" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH16" t="inlineStr">
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>A simple rule can help her stay on track: 50% for needs 30% for wants 20% for savings A smart plan that helps you spend, save, and stay in control. • To participate: - Follow Emirates NBD - Tag 3 friends - Drop your answer below for a chance to win AED 10,000 • This is one of the many tips that the bank’s program has in store.</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>A simple rule can help her stay on track: 50% for needs 30% for wants 20% for savings A smart plan that helps you spend, save and stay in control. • To participate: - Follow Emirates NBD - Tag 3 friends - Drop your answer below for a chance to win AED 10,000 • This is one of the many tips that the bank’s programme has in store.</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
         <is>
           <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AK16" t="n">
+      <c r="AK15" t="n">
         <v>2026</v>
       </c>
-      <c r="AL16" t="inlineStr">
+      <c r="AL15" t="inlineStr">
         <is>
           <t>EmiratesNBD_AE</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>2037789707321622955</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola/status/2037789707321622955</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>SelmaRomola</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Selma Romola</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1118152018995105792/5fyZOTth_bigger.jpg</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
         <is>
           <t>اجعل مفاجآت العيد أكثر قيمة.
 من الفضة إلى الذهب، اكتشف طريقة أذكى لامتلاك أو إهداء شيء ثمين بحق.
@@ -3227,7 +3076,7 @@
 اكتب إجابتك في التعليقات أدناه لفرصة ربح 10,000 درهم</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>To buy gold and silver through Emirates NBD, the fastest way is using the ENBD X mobile app. 
 Tagging 
@@ -3236,52 +3085,52 @@
 &lt;a href="/Bushrasabih2" title="Bu_shaikh🌸❤️"&gt;@Bushrasabih2&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K17" t="b">
-        <v>0</v>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>20h</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 7:11 AM UTC</t>
         </is>
       </c>
-      <c r="P17" s="2" t="n">
+      <c r="P16" s="2" t="n">
         <v>46109.29930555556</v>
       </c>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr">
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
         <is>
           <t>['https://x.com/FazilAnas', 'https://x.com/Emy191990', 'https://x.com/Bushrasabih2']</t>
         </is>
       </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>9</v>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>11</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
         <is>
           <t>To buy gold and silver through Emirates NBD, the fastest way is using the ENBD X mobile app. 
 Tagging 
@@ -3290,12 +3139,12 @@
 @Bushrasabih2</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola/status/2037789707321622955</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>اجعل مفاجآت العيد أكثر قيمة.
 من الفضة إلى الذهب، اكتشف طريقة أذكى لامتلاك أو إهداء شيء ثمين بحق.
@@ -3307,7 +3156,7 @@
 اكتب إجابتك في التعليقات أدناه لفرصة ربح 10,000 درهم</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>اجعل مفاجآت العيد أكثر قيمة.
 من الفضة إلى الذهب، اكتشف طريقة أذكى لامتلاك أو إهداء شيء ثمين بحق.
@@ -3319,95 +3168,95 @@
 اكتب إجابتك في التعليقات أدناه لفرصة ربح 10,000 درهم</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>Make holiday surprises more valuable. From silver to gold, discover a smarter way to own or gift something truly precious. Watch this episode and tell us: How can you buy gold and silver from the bank? 
 To participate: Follow the Emirates NBD account Tag 3 of your friends Write your answer in the comments below for a chance to win 10,000 dirhams.</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
+      <c r="AC16" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="AD17" t="inlineStr">
+      <c r="AD16" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="AE17" s="2" t="n">
+      <c r="AE16" s="2" t="n">
         <v>46109.46597222222</v>
       </c>
-      <c r="AF17" t="inlineStr">
+      <c r="AF16" t="inlineStr">
         <is>
           <t>28-03-2026</t>
         </is>
       </c>
-      <c r="AG17" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH17" t="inlineStr">
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AI17" t="inlineStr">
+      <c r="AI16" t="inlineStr">
         <is>
           <t>To participate: Follow the Emirates NBD account Tag 3 of your friends Write your answer in the comments below for a chance to win 10,000 dirhams. • From silver to gold, discover a smarter way to own or gift something truly precious. • Watch this episode and tell us: How can you buy gold and silver from the bank?</t>
         </is>
       </c>
-      <c r="AJ17" t="inlineStr">
+      <c r="AJ16" t="inlineStr">
         <is>
           <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AK17" t="n">
+      <c r="AK16" t="n">
         <v>2026</v>
       </c>
-      <c r="AL17" t="inlineStr">
+      <c r="AL16" t="inlineStr">
         <is>
           <t>EmiratesNBD_AE</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>2037789510478843981</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola/status/2037789510478843981</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>SelmaRomola</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Selma Romola</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1118152018995105792/5fyZOTth_bigger.jpg</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
         <is>
           <t>@EmiratesNBD_AE To buy gold and silver through Emirates NBD, the fastest way is using the ENBD X mobile app. 
 Tagging 
@@ -3416,7 +3265,7 @@
 @yasar8212</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>To buy gold and silver through Emirates NBD, the fastest way is using the ENBD X mobile app. 
 Tagging 
@@ -3425,52 +3274,52 @@
 &lt;a href="/yasar8212" title="shaniyadu"&gt;@yasar8212&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K18" t="b">
-        <v>0</v>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
+      <c r="K17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>20h</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 7:10 AM UTC</t>
         </is>
       </c>
-      <c r="P18" s="2" t="n">
+      <c r="P17" s="2" t="n">
         <v>46109.29861111111</v>
       </c>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr">
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
         <is>
           <t>['https://x.com/Sosomostafa729S', 'https://x.com/Nur_Munem', 'https://x.com/yasar8212']</t>
         </is>
       </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>7</v>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>8</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
         <is>
           <t>To buy gold and silver through Emirates NBD, the fastest way is using the ENBD X mobile app. 
 Tagging 
@@ -3479,12 +3328,12 @@
 @yasar8212</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola/status/2037789510478843981</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>@EmiratesNBD_AE To buy gold and silver through Emirates NBD, the fastest way is using the ENBD X mobile app. 
 Tagging 
@@ -3493,7 +3342,7 @@
 @yasar8212</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>@EmiratesNBD_AE To buy gold and silver through Emirates NBD, the fastest way is using the ENBD X mobile app. 
 Tagging 
@@ -3502,94 +3351,94 @@
 @yasar8212</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>To buy gold and silver through Emirates NBD, the fastest way is using the ENBD X mobile app.</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
+      <c r="AC17" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AE18" s="2" t="n">
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AE17" s="2" t="n">
         <v>46109.46527777778</v>
       </c>
-      <c r="AF18" t="inlineStr">
+      <c r="AF17" t="inlineStr">
         <is>
           <t>28-03-2026</t>
         </is>
       </c>
-      <c r="AG18" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH18" t="inlineStr">
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AI18" t="inlineStr">
+      <c r="AI17" t="inlineStr">
         <is>
           <t>To buy gold and silver through Emirates NBD, the fastest way is using the ENBD X mobile app.</t>
         </is>
       </c>
-      <c r="AJ18" t="inlineStr">
+      <c r="AJ17" t="inlineStr">
         <is>
           <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AK18" t="n">
+      <c r="AK17" t="n">
         <v>2026</v>
       </c>
-      <c r="AL18" t="inlineStr">
+      <c r="AL17" t="inlineStr">
         <is>
           <t>EmiratesNBD_AE</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
         <is>
           <t>2037788447910564341</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola/status/2037788447910564341</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>SelmaRomola</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Selma Romola</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1118152018995105792/5fyZOTth_bigger.jpg</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
         <is>
           <t>Make Eid surprises even more valuable.
 From silver to gold, discover a smarter way to own or gift something truly precious.
@@ -3601,7 +3450,7 @@
 Drop your answer below for a chance to win AED 10,000</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>To buy gold and silver through Emirates NBD, the fastest way is using the ENBD X mobile app. 
 Tagging 
@@ -3610,52 +3459,52 @@
 &lt;a href="/Sosomostafa729S" title="Soha.mostafa77"&gt;@Sosomostafa729S&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K19" t="b">
-        <v>0</v>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>20h</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 7:06 AM UTC</t>
         </is>
       </c>
-      <c r="P19" s="2" t="n">
+      <c r="P18" s="2" t="n">
         <v>46109.29583333333</v>
       </c>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr">
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
         <is>
           <t>['https://x.com/Bushrasabih2', 'https://x.com/AmalBeevi', 'https://x.com/Sosomostafa729S']</t>
         </is>
       </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>9</v>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>10</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
         <is>
           <t>To buy gold and silver through Emirates NBD, the fastest way is using the ENBD X mobile app. 
 Tagging 
@@ -3664,12 +3513,12 @@
 @Sosomostafa729S</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola/status/2037788447910564341</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>Make Eid surprises even more valuable.
 From silver to gold, discover a smarter way to own or gift something truly precious.
@@ -3681,7 +3530,7 @@
 Drop your answer below for a chance to win AED 10,000</t>
         </is>
       </c>
-      <c r="AA19" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>Make Eid surprises even more valuable.
 From silver to gold, discover a smarter way to own or gift something truly precious.
@@ -3693,9 +3542,163 @@
 Drop your answer below for a chance to win AED 10,000</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>Make Eid surprises even more valuable. From silver to gold, discover a smarter way to own or gift something truly precious. Watch this episode and tell us: How can you buy gold and silver from the bank? To participate: Follow Emirates NBD Tag 3 friends Drop your answer below for a chance to win AED 10,000</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AE18" s="2" t="n">
+        <v>46109.4625</v>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>28-03-2026</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>To participate: Follow Emirates NBD Tag 3 friends Drop your answer below for a chance to win AED 10,000 • From silver to gold, discover a smarter way to own or gift something truly precious. • Watch this episode and tell us: How can you buy gold and silver from the bank?</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK18" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2037784853866029145</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784853866029145</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>B- 1.89% @zeynp_qas @Salma2232019 @semeet 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>B- 1.89% &lt;a href="/zeynp_qas" title="zeynab kasem"&gt;@zeynp_qas&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="K19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 6:52 AM UTC</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="n">
+        <v>46109.28611111111</v>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>['https://x.com/zeynp_qas', 'https://x.com/Salma2232019', 'https://x.com/semeet']</t>
+        </is>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>4</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>B- 1.89% @zeynp_qas @Salma2232019 @semeet 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>B- 1.89% @zeynp_qas @Salma2232019 @semeet 🌿🇦🇪❤️</t>
+        </is>
+      </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Make Eid surprises even more valuable. From silver to gold, discover a smarter way to own or gift something truly precious. Watch this episode and tell us: How can you buy gold and silver from the bank? To participate: Follow Emirates NBD Tag 3 friends Drop your answer below for a chance to win AED 10,000</t>
+          <t>B- 1.89% @zeynp_qas @Salma2232019 @semeet 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3705,11 +3708,11 @@
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE19" s="2" t="n">
-        <v>46109.4625</v>
+        <v>46109.45277777778</v>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
@@ -3728,7 +3731,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>To participate: Follow Emirates NBD Tag 3 friends Drop your answer below for a chance to win AED 10,000 • From silver to gold, discover a smarter way to own or gift something truly precious. • Watch this episode and tell us: How can you buy gold and silver from the bank?</t>
+          <t>B- 1.89% @zeynp_qas @Salma2232019 @semeet 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -3751,12 +3754,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2037784853866029145</t>
+          <t>2037784763122217375</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784853866029145</t>
+          <t>https://x.com/Sosomostafa729S/status/2037784763122217375</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3781,6 +3784,168 @@
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE B- 1.89% @semeet @Salma2232019 @SelmaRomola 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>B- 1.89% &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 6:52 AM UTC</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="n">
+        <v>46109.28611111111</v>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>['https://x.com/semeet', 'https://x.com/Salma2232019', 'https://x.com/SelmaRomola']</t>
+        </is>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>7</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>B- 1.89% @semeet @Salma2232019 @SelmaRomola 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784763122217375</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE B- 1.89% @semeet @Salma2232019 @SelmaRomola 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE B- 1.89% @semeet @Salma2232019 @SelmaRomola 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>The text appears to be a social media post or tweet that includes a percentage and mentions of users or accounts, along with emojis. There is no translatable content in terms of language, as it primarily consists of usernames and symbols.</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE20" s="2" t="n">
+        <v>46109.45277777778</v>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>28-03-2026</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>The text appears to be a social media post or tweet that includes a percentage and mentions of users or accounts, along with emojis. • There is no translatable content in terms of language, as it primarily consists of usernames and symbols.</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK20" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2037784668028985459</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784668028985459</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
         <is>
           <t>حل اللغز واربح 10,000 درهم.💰
 أم علاوي تعبت من مشاكل السيارة، ومستعدة لسيارة جديدة بفضل قرض السيارات السريع من بنك الإمارات دبي الوطني، من خلال طلب سهل وسريع عبر الإنترنت.
@@ -3789,67 +3954,67 @@
 حل اللغز لفرصة الفوز بـ 10 آلاف درهم. https://t.co/NBQE3PzfgZ</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>B- 1.89% &lt;a href="/zeynp_qas" title="zeynab kasem"&gt;@zeynp_qas&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="K20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>B- 1.89% &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="K21" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>21h</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>Mar 28, 2026 · 6:52 AM UTC</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="n">
-        <v>46109.28611111111</v>
-      </c>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>['https://x.com/zeynp_qas', 'https://x.com/Salma2232019', 'https://x.com/semeet']</t>
-        </is>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>4</v>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>B- 1.89% @zeynp_qas @Salma2232019 @semeet 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784853866029145</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 6:51 AM UTC</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="n">
+        <v>46109.28541666667</v>
+      </c>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/parulghalout']</t>
+        </is>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>6</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>B- 1.89% @Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784668028985459</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
         <is>
           <t>حل اللغز واربح 10,000 درهم.💰
 أم علاوي تعبت من مشاكل السيارة، ومستعدة لسيارة جديدة بفضل قرض السيارات السريع من بنك الإمارات دبي الوطني، من خلال طلب سهل وسريع عبر الإنترنت.
@@ -3858,7 +4023,7 @@
 حل اللغز لفرصة الفوز بـ 10 آلاف درهم. https://t.co/NBQE3PzfgZ</t>
         </is>
       </c>
-      <c r="AA20" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>حل اللغز واربح 10,000 درهم.💰
 أم علاوي تعبت من مشاكل السيارة، ومستعدة لسيارة جديدة بفضل قرض السيارات السريع من بنك الإمارات دبي الوطني، من خلال طلب سهل وسريع عبر الإنترنت.
@@ -3867,7 +4032,7 @@
 حل اللغز لفرصة الفوز بـ 10 آلاف درهم. https://t.co/NBQE3PzfgZ</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>Solve the puzzle and win 10,000 dirhams.💰 Um Alawi is tired of car problems and is ready for a new car thanks to the quick car loan from Emirates NBD, through an easy and fast online application. 
 Follow @EmiratesNBD_ae 
@@ -3875,199 +4040,37 @@
 Solve the puzzle for a chance to win 10,000 dirhams. https://t.co/NBQE3PzfgZ</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
+      <c r="AC21" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="AD20" t="inlineStr">
+      <c r="AD21" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="AE20" s="2" t="n">
-        <v>46109.45277777778</v>
-      </c>
-      <c r="AF20" t="inlineStr">
+      <c r="AE21" s="2" t="n">
+        <v>46109.45208333333</v>
+      </c>
+      <c r="AF21" t="inlineStr">
         <is>
           <t>28-03-2026</t>
         </is>
       </c>
-      <c r="AG20" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH20" t="inlineStr">
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AI20" t="inlineStr">
+      <c r="AI21" t="inlineStr">
         <is>
           <t>Solve the puzzle and win 10,000 dirhams.💰 Um Alawi is tired of car problems and is ready for a new car thanks to the quick car loan from Emirates NBD, through an easy and fast online application. • Follow @EmiratesNBD_ae Tag 3 of your friends Solve the puzzle for a chance to win 10,000 dirhams.</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AK20" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL20" t="inlineStr">
-        <is>
-          <t>EmiratesNBD_AE</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2037784763122217375</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784763122217375</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Sosomostafa729S</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Soha.mostafa77</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE B- 1.89% @semeet @Salma2232019 @SelmaRomola 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>B- 1.89% &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="K21" t="b">
-        <v>0</v>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>21h</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>Mar 28, 2026 · 6:52 AM UTC</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="n">
-        <v>46109.28611111111</v>
-      </c>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>['https://x.com/semeet', 'https://x.com/Salma2232019', 'https://x.com/SelmaRomola']</t>
-        </is>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>6</v>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>B- 1.89% @semeet @Salma2232019 @SelmaRomola 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784763122217375</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE B- 1.89% @semeet @Salma2232019 @SelmaRomola 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE B- 1.89% @semeet @Salma2232019 @SelmaRomola 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>The text appears to be a social media post or message that includes a percentage and mentions of users or accounts, along with emojis. There is no translatable content in terms of language, as it primarily consists of usernames and symbols.</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD21" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AE21" s="2" t="n">
-        <v>46109.45277777778</v>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>28-03-2026</t>
-        </is>
-      </c>
-      <c r="AG21" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>The text appears to be a social media post or message that includes a percentage and mentions of users or accounts, along with emojis. • There is no translatable content in terms of language, as it primarily consists of usernames and symbols.</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -4090,12 +4093,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2037784668028985459</t>
+          <t>2037784498885243377</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784668028985459</t>
+          <t>https://x.com/Sosomostafa729S/status/2037784498885243377</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4120,168 +4123,6 @@
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE B- 1.89% @Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>B- 1.89% &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="K22" t="b">
-        <v>0</v>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>21h</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>Mar 28, 2026 · 6:51 AM UTC</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="n">
-        <v>46109.28541666667</v>
-      </c>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/parulghalout']</t>
-        </is>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>4</v>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>B- 1.89% @Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784668028985459</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE B- 1.89% @Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE B- 1.89% @Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>The text appears to be a social media post with mentions and emojis, and it does not contain any translatable content. Therefore, there is no translation needed.</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AE22" s="2" t="n">
-        <v>46109.45208333333</v>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>28-03-2026</t>
-        </is>
-      </c>
-      <c r="AG22" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>The text appears to be a social media post with mentions and emojis, and it does not contain any translatable content. • Therefore, there is no translation needed.</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AK22" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>EmiratesNBD_AE</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2037784498885243377</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784498885243377</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Sosomostafa729S</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Soha.mostafa77</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
         <is>
           <t>حلّ فزورة رمضان واربح 10,000 درهم.
 من توزيع الوجبات، إلى دعم العاملين وقضاء الوقت مع كبار المواطنين، يجمع برنامج واحد كل ذلك تحت مظلًة واحدة.
@@ -4292,69 +4133,69 @@
 3.اكتب إجابتك في التعليقات أدناه https://t.co/aADoQF5a2E</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>Exchanger volunteer program 
 &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; 🌿🇦🇪❤️</t>
         </is>
       </c>
-      <c r="K23" t="b">
-        <v>0</v>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>21h</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 6:50 AM UTC</t>
         </is>
       </c>
-      <c r="P23" s="2" t="n">
+      <c r="P22" s="2" t="n">
         <v>46109.28472222222</v>
       </c>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr">
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
         <is>
           <t>['https://x.com/semeet', 'https://x.com/Emy191990', 'https://x.com/ibushra_03']</t>
         </is>
       </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>5</v>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>6</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
         <is>
           <t>Exchanger volunteer program 
 @semeet @Emy191990 @ibushra_03 🌿🇦🇪❤️</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>https://x.com/Sosomostafa729S/status/2037784498885243377</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>حلّ فزورة رمضان واربح 10,000 درهم.
 من توزيع الوجبات، إلى دعم العاملين وقضاء الوقت مع كبار المواطنين، يجمع برنامج واحد كل ذلك تحت مظلًة واحدة.
@@ -4365,7 +4206,7 @@
 3.اكتب إجابتك في التعليقات أدناه https://t.co/aADoQF5a2E</t>
         </is>
       </c>
-      <c r="AA23" t="inlineStr">
+      <c r="AA22" t="inlineStr">
         <is>
           <t>حلّ فزورة رمضان واربح 10,000 درهم.
 من توزيع الوجبات، إلى دعم العاملين وقضاء الوقت مع كبار المواطنين، يجمع برنامج واحد كل ذلك تحت مظلًة واحدة.
@@ -4376,7 +4217,7 @@
 3.اكتب إجابتك في التعليقات أدناه https://t.co/aADoQF5a2E</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>Solve the Ramadan riddle and win 10,000 dirhams.
 From meal distribution to supporting workers and spending time with senior citizens, one program brings all of this together under one umbrella.
@@ -4384,7 +4225,169 @@
 To participate:
 1. Follow the Emirates NBD account
 2. Tag 3 of your friends
-3. Write your answer in the comments below</t>
+3. Write your answer in the comments below.</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE22" s="2" t="n">
+        <v>46109.45138888889</v>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>28-03-2026</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>From meal distribution to supporting workers and spending time with senior citizens, one program brings all of this together under one umbrella. • Solve the Ramadan riddle and win 10,000 dirhams. • Follow the Emirates NBD account 2.</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK22" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2037784405700419683</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784405700419683</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @zeynp_qas @SelmaRomola 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Exchanger volunteer program &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/zeynp_qas" title="zeynab kasem"&gt;@zeynp_qas&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="K23" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 6:50 AM UTC</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="n">
+        <v>46109.28472222222</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>['https://x.com/semeet', 'https://x.com/zeynp_qas', 'https://x.com/SelmaRomola']</t>
+        </is>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>6</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Exchanger volunteer program @semeet @zeynp_qas @SelmaRomola 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784405700419683</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @zeynp_qas @SelmaRomola 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @zeynp_qas @SelmaRomola 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>Emirates NBD_AE Exchanger volunteer program</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -4417,7 +4420,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>From meal distribution to supporting workers and spending time with senior citizens, one program brings all of this together under one umbrella. • Solve the Ramadan riddle and win 10,000 dirhams. • Follow the Emirates NBD account 2.</t>
+          <t>Emirates NBD_AE Exchanger volunteer program</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -4440,57 +4443,57 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2037784405700419683</t>
+          <t>2037784344333275440</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784405700419683</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2037784344333275440</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S</t>
+          <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sosomostafa729S</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Soha.mostafa77</t>
+          <t>Emirates NBD</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @zeynp_qas @SelmaRomola 🌿🇦🇪❤️</t>
+          <t>Before clicking a link, what do you do?
+Stay Safe, Stay Vigilant. #UnitedAgainstFraud
+emiratesnbd.com/en/campaigns…</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/zeynp_qas" title="zeynab kasem"&gt;@zeynp_qas&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; 🌿🇦🇪❤️</t>
+          <t>Before clicking a link, what do you do?
+Stay Safe, Stay Vigilant. &lt;a href="/search?f=tweets&amp;amp;q=%23UnitedAgainstFraud"&gt;#UnitedAgainstFraud&lt;/a&gt;
+&lt;a href="https://www.emiratesnbd.com/en/campaigns/united-against-fraud"&gt;emiratesnbd.com/en/campaigns…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K24" t="b">
         <v>0</v>
       </c>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -4504,20 +4507,20 @@
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
-          <t>['https://x.com/semeet', 'https://x.com/zeynp_qas', 'https://x.com/SelmaRomola']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23UnitedAgainstFraud', 'https://www.emiratesnbd.com/en/campaigns/united-against-fraud']</t>
         </is>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T24" t="n">
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V24" t="n">
-        <v>5</v>
+        <v>525</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
@@ -4526,32 +4529,29 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program @semeet @zeynp_qas @SelmaRomola 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784405700419683</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @zeynp_qas @SelmaRomola 🌿🇦🇪❤️</t>
-        </is>
-      </c>
+          <t>Before clicking a link, what do you do?
+Stay Safe, Stay Vigilant. #UnitedAgainstFraud
+emiratesnbd.com/en/campaigns…</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @zeynp_qas @SelmaRomola 🌿🇦🇪❤️</t>
+          <t>Before clicking a link, what do you do?
+Stay Safe, Stay Vigilant. #UnitedAgainstFraud
+emiratesnbd.com/en/campaigns…</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Emirates NBD_AE Exchanger volunteer program</t>
+          <t>Before clicking a link, what do you do?
+Stay Safe, Stay Vigilant. #UnitedAgainstFraud</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Cust</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Emirates NBD_AE Exchanger volunteer program</t>
+          <t>Stay Safe, Stay Vigilant. • Before clicking a link, what do you do?</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4602,57 +4602,57 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2037784344333275440</t>
+          <t>2037784337337532619</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037784344333275440</t>
+          <t>https://x.com/Sosomostafa729S/status/2037784337337532619</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/Sosomostafa729S</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>Sosomostafa729S</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>Soha.mostafa77</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Before clicking a link, what do you do?
-Stay Safe, Stay Vigilant. #UnitedAgainstFraud
-emiratesnbd.com/en/campaigns…</t>
+          <t>@EmiratesNBD_AE Exchanger volunteer program @Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Before clicking a link, what do you do?
-Stay Safe, Stay Vigilant. &lt;a href="/search?f=tweets&amp;amp;q=%23UnitedAgainstFraud"&gt;#UnitedAgainstFraud&lt;/a&gt;
-&lt;a href="https://www.emiratesnbd.com/en/campaigns/united-against-fraud"&gt;emiratesnbd.com/en/campaigns…&lt;/a&gt;</t>
+          <t>Exchanger volunteer program &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="K25" t="b">
         <v>0</v>
       </c>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -4666,20 +4666,20 @@
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23UnitedAgainstFraud', 'https://www.emiratesnbd.com/en/campaigns/united-against-fraud']</t>
+          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/parulghalout']</t>
         </is>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>517</v>
+        <v>7</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -4688,29 +4688,32 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Before clicking a link, what do you do?
-Stay Safe, Stay Vigilant. #UnitedAgainstFraud
-emiratesnbd.com/en/campaigns…</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
+          <t>Exchanger volunteer program @Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784337337532619</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Exchanger volunteer program @Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>Before clicking a link, what do you do?
-Stay Safe, Stay Vigilant. #UnitedAgainstFraud
-emiratesnbd.com/en/campaigns…</t>
+          <t>@EmiratesNBD_AE Exchanger volunteer program @Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Before clicking a link, what do you do?
-Stay Safe, Stay Vigilant. #UnitedAgainstFraud</t>
+          <t>Emirates NBD_AE Exchanger volunteer program Emy191990 ibushra_03 parulghalout 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Cust</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -4738,7 +4741,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Stay Safe, Stay Vigilant. • Before clicking a link, what do you do?</t>
+          <t>Emirates NBD_AE Exchanger volunteer program Emy191990 ibushra_03 parulghalout 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
@@ -4751,7 +4754,7 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
     </row>
@@ -4761,12 +4764,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2037784337337532619</t>
+          <t>2037784225022365938</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784337337532619</t>
+          <t>https://x.com/Sosomostafa729S/status/2037784225022365938</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4792,12 +4795,12 @@
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @parulghalout @Salma2232019 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; 🌿🇦🇪❤️</t>
+          <t>Exchanger volunteer program &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="K26" t="b">
@@ -4811,21 +4814,21 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Mar 28, 2026 · 6:50 AM UTC</t>
+          <t>Mar 28, 2026 · 6:49 AM UTC</t>
         </is>
       </c>
       <c r="P26" s="2" t="n">
-        <v>46109.28472222222</v>
+        <v>46109.28402777778</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
         <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/parulghalout']</t>
+          <t>['https://x.com/semeet', 'https://x.com/parulghalout', 'https://x.com/Salma2232019']</t>
         </is>
       </c>
       <c r="S26" t="n">
@@ -4847,27 +4850,27 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program @Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
+          <t>Exchanger volunteer program @semeet @parulghalout @Salma2232019 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784337337532619</t>
+          <t>https://x.com/Sosomostafa729S/status/2037784225022365938</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @parulghalout @Salma2232019 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @parulghalout @Salma2232019 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Emirates NBD_AE Exchanger volunteer program Emy191990 ibushra_03 parulghalout 🌿🇦🇪❤️</t>
+          <t>Emirates NBD_AE Exchanger volunteer program</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -4881,7 +4884,7 @@
         </is>
       </c>
       <c r="AE26" s="2" t="n">
-        <v>46109.45138888889</v>
+        <v>46109.45069444444</v>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
@@ -4900,7 +4903,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Emirates NBD_AE Exchanger volunteer program Emy191990 ibushra_03 parulghalout 🌿🇦🇪❤️</t>
+          <t>Emirates NBD_AE Exchanger volunteer program</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -4923,12 +4926,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2037784225022365938</t>
+          <t>2037784141006344295</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784225022365938</t>
+          <t>https://x.com/Sosomostafa729S/status/2037784141006344295</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4954,12 +4957,12 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @parulghalout @Salma2232019 🌿🇦🇪❤️</t>
+          <t>Exchanger volunteer program @semeet @Salma2232019 @ibushra_03 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; 🌿🇦🇪❤️</t>
+          <t>Exchanger volunteer program &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="K27" t="b">
@@ -4973,7 +4976,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -4987,7 +4990,7 @@
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
         <is>
-          <t>['https://x.com/semeet', 'https://x.com/parulghalout', 'https://x.com/Salma2232019']</t>
+          <t>['https://x.com/semeet', 'https://x.com/Salma2232019', 'https://x.com/ibushra_03']</t>
         </is>
       </c>
       <c r="S27" t="n">
@@ -5000,7 +5003,7 @@
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
@@ -5009,27 +5012,19 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program @semeet @parulghalout @Salma2232019 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784225022365938</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @parulghalout @Salma2232019 🌿🇦🇪❤️</t>
-        </is>
-      </c>
+          <t>Exchanger volunteer program @semeet @Salma2232019 @ibushra_03 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @parulghalout @Salma2232019 🌿🇦🇪❤️</t>
+          <t>Exchanger volunteer program @semeet @Salma2232019 @ibushra_03 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Emirates NBD_AE Exchanger volunteer program</t>
+          <t>Exchanger volunteer program</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -5062,7 +5057,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Emirates NBD_AE Exchanger volunteer program</t>
+          <t>Exchanger volunteer program</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -5085,12 +5080,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2037784141006344295</t>
+          <t>2037784038774317555</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784141006344295</t>
+          <t>https://x.com/Sosomostafa729S/status/2037784038774317555</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5116,12 +5111,14 @@
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @Salma2232019 @ibushra_03 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE Exchanger volunteer program 
+@Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; 🌿🇦🇪❤️</t>
+          <t>Exchanger volunteer program 
+&lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="K28" t="b">
@@ -5135,7 +5132,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -5149,7 +5146,7 @@
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
         <is>
-          <t>['https://x.com/semeet', 'https://x.com/Salma2232019', 'https://x.com/ibushra_03']</t>
+          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/parulghalout']</t>
         </is>
       </c>
       <c r="S28" t="n">
@@ -5171,22 +5168,25 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program @semeet @Salma2232019 @ibushra_03 🌿🇦🇪❤️</t>
+          <t>Exchanger volunteer program 
+@Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784141006344295</t>
+          <t>https://x.com/Sosomostafa729S/status/2037784038774317555</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @Salma2232019 @ibushra_03 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE Exchanger volunteer program 
+@Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @Salma2232019 @ibushra_03 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE Exchanger volunteer program 
+@Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2037784038774317555</t>
+          <t>2037783859769876728</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784038774317555</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783859769876728</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5278,14 +5278,12 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program 
-@Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE FINWELL ( Financial Well-being program) with Emirates NBD @semeet @zeynp_qas @Emy191990 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program 
-&lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; 🌿🇦🇪❤️</t>
+          <t>FINWELL ( Financial Well-being program) with Emirates NBD &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/zeynp_qas" title="zeynab kasem"&gt;@zeynp_qas&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="K29" t="b">
@@ -5299,21 +5297,21 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Mar 28, 2026 · 6:49 AM UTC</t>
+          <t>Mar 28, 2026 · 6:48 AM UTC</t>
         </is>
       </c>
       <c r="P29" s="2" t="n">
-        <v>46109.28402777778</v>
+        <v>46109.28333333333</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
         <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/parulghalout']</t>
+          <t>['https://x.com/semeet', 'https://x.com/zeynp_qas', 'https://x.com/Emy191990']</t>
         </is>
       </c>
       <c r="S29" t="n">
@@ -5326,7 +5324,7 @@
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
@@ -5335,30 +5333,27 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program 
-@Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
+          <t>FINWELL ( Financial Well-being program) with Emirates NBD @semeet @zeynp_qas @Emy191990 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784038774317555</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783859769876728</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program 
-@Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE FINWELL ( Financial Well-being program) with Emirates NBD @semeet @zeynp_qas @Emy191990 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program 
-@Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE FINWELL ( Financial Well-being program) with Emirates NBD @semeet @zeynp_qas @Emy191990 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Emirates NBD_AE Exchanger volunteer program</t>
+          <t>FINWELL (Financial Well-being program) with Emirates NBD</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -5368,11 +5363,11 @@
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE29" s="2" t="n">
-        <v>46109.45069444444</v>
+        <v>46109.45</v>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
@@ -5391,7 +5386,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Emirates NBD_AE Exchanger volunteer program</t>
+          <t>FINWELL (Financial Well-being program) with Emirates NBD</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -5414,12 +5409,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2037783859769876728</t>
+          <t>2037783775896313876</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783859769876728</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783775896313876</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5445,12 +5440,12 @@
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE FINWELL ( Financial Well-being program) with Emirates NBD @semeet @zeynp_qas @Emy191990 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE FINWELL ( Financial Well-being program) with Emirates NBD @SelmaRomola @Emy191990 @parulghalout 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>FINWELL ( Financial Well-being program) with Emirates NBD &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/zeynp_qas" title="zeynab kasem"&gt;@zeynp_qas&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; 🌿🇦🇪❤️</t>
+          <t>FINWELL ( Financial Well-being program) with Emirates NBD &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="K30" t="b">
@@ -5464,7 +5459,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -5478,7 +5473,7 @@
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
         <is>
-          <t>['https://x.com/semeet', 'https://x.com/zeynp_qas', 'https://x.com/Emy191990']</t>
+          <t>['https://x.com/SelmaRomola', 'https://x.com/Emy191990', 'https://x.com/parulghalout']</t>
         </is>
       </c>
       <c r="S30" t="n">
@@ -5491,7 +5486,7 @@
         <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
@@ -5500,22 +5495,22 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>FINWELL ( Financial Well-being program) with Emirates NBD @semeet @zeynp_qas @Emy191990 🌿🇦🇪❤️</t>
+          <t>FINWELL ( Financial Well-being program) with Emirates NBD @SelmaRomola @Emy191990 @parulghalout 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783859769876728</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783775896313876</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE FINWELL ( Financial Well-being program) with Emirates NBD @semeet @zeynp_qas @Emy191990 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE FINWELL ( Financial Well-being program) with Emirates NBD @SelmaRomola @Emy191990 @parulghalout 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE FINWELL ( Financial Well-being program) with Emirates NBD @semeet @zeynp_qas @Emy191990 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE FINWELL ( Financial Well-being program) with Emirates NBD @SelmaRomola @Emy191990 @parulghalout 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -5576,12 +5571,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2037783775896313876</t>
+          <t>2037783673144230370</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783775896313876</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783673144230370</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5607,12 +5602,14 @@
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE FINWELL ( Financial Well-being program) with Emirates NBD @SelmaRomola @Emy191990 @parulghalout 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE FINWELL ( Financial Well-being program) with Emirates NBD 
+@Emy191990 @ibushra_03 @SelmaRomola 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>FINWELL ( Financial Well-being program) with Emirates NBD &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; 🌿🇦🇪❤️</t>
+          <t>FINWELL ( Financial Well-being program) with Emirates NBD 
+&lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="K31" t="b">
@@ -5626,21 +5623,21 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Mar 28, 2026 · 6:48 AM UTC</t>
+          <t>Mar 28, 2026 · 6:47 AM UTC</t>
         </is>
       </c>
       <c r="P31" s="2" t="n">
-        <v>46109.28333333333</v>
+        <v>46109.28263888889</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
         <is>
-          <t>['https://x.com/SelmaRomola', 'https://x.com/Emy191990', 'https://x.com/parulghalout']</t>
+          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/SelmaRomola']</t>
         </is>
       </c>
       <c r="S31" t="n">
@@ -5653,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
@@ -5662,22 +5659,25 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>FINWELL ( Financial Well-being program) with Emirates NBD @SelmaRomola @Emy191990 @parulghalout 🌿🇦🇪❤️</t>
+          <t>FINWELL ( Financial Well-being program) with Emirates NBD 
+@Emy191990 @ibushra_03 @SelmaRomola 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783775896313876</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783673144230370</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE FINWELL ( Financial Well-being program) with Emirates NBD @SelmaRomola @Emy191990 @parulghalout 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE FINWELL ( Financial Well-being program) with Emirates NBD 
+@Emy191990 @ibushra_03 @SelmaRomola 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE FINWELL ( Financial Well-being program) with Emirates NBD @SelmaRomola @Emy191990 @parulghalout 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE FINWELL ( Financial Well-being program) with Emirates NBD 
+@Emy191990 @ibushra_03 @SelmaRomola 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -5696,7 +5696,7 @@
         </is>
       </c>
       <c r="AE31" s="2" t="n">
-        <v>46109.45</v>
+        <v>46109.44930555556</v>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2037783673144230370</t>
+          <t>2037783477979091314</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783673144230370</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783477979091314</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5769,14 +5769,12 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE FINWELL ( Financial Well-being program) with Emirates NBD 
-@Emy191990 @ibushra_03 @SelmaRomola 🌿🇦🇪❤️</t>
+          <t>Through ENBD X Mobile Banking's App @parulghalout @semeet @Emy191990 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>FINWELL ( Financial Well-being program) with Emirates NBD 
-&lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; 🌿🇦🇪❤️</t>
+          <t>Through ENBD X Mobile Banking&amp;#39;s App &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="K32" t="b">
@@ -5790,21 +5788,21 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Mar 28, 2026 · 6:47 AM UTC</t>
+          <t>Mar 28, 2026 · 6:46 AM UTC</t>
         </is>
       </c>
       <c r="P32" s="2" t="n">
-        <v>46109.28263888889</v>
+        <v>46109.28194444445</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
         <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/SelmaRomola']</t>
+          <t>['https://x.com/parulghalout', 'https://x.com/semeet', 'https://x.com/Emy191990']</t>
         </is>
       </c>
       <c r="S32" t="n">
@@ -5826,30 +5824,19 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>FINWELL ( Financial Well-being program) with Emirates NBD 
-@Emy191990 @ibushra_03 @SelmaRomola 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783673144230370</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE FINWELL ( Financial Well-being program) with Emirates NBD 
-@Emy191990 @ibushra_03 @SelmaRomola 🌿🇦🇪❤️</t>
-        </is>
-      </c>
+          <t>Through ENBD X Mobile Banking's App @parulghalout @semeet @Emy191990 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE FINWELL ( Financial Well-being program) with Emirates NBD 
-@Emy191990 @ibushra_03 @SelmaRomola 🌿🇦🇪❤️</t>
+          <t>Through ENBD X Mobile Banking's App @parulghalout @semeet @Emy191990 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>FINWELL (Financial Well-being program) with Emirates NBD</t>
+          <t>Through ENBD X Mobile Banking's App</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -5859,11 +5846,11 @@
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE32" s="2" t="n">
-        <v>46109.44930555556</v>
+        <v>46109.44861111111</v>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
@@ -5882,7 +5869,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>FINWELL (Financial Well-being program) with Emirates NBD</t>
+          <t>Through ENBD X Mobile Banking's App</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -5905,12 +5892,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2037783477979091314</t>
+          <t>2037783402758508685</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783477979091314</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783402758508685</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5936,12 +5923,12 @@
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @parulghalout @semeet @Emy191990 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @zeynp_qas @SelmaRomola @Salma2232019 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Through ENBD X Mobile Banking&amp;#39;s App &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; 🌿🇦🇪❤️</t>
+          <t>Through ENBD X Mobile Banking&amp;#39;s App &lt;a href="/zeynp_qas" title="zeynab kasem"&gt;@zeynp_qas&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="K33" t="b">
@@ -5955,7 +5942,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -5969,7 +5956,7 @@
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
         <is>
-          <t>['https://x.com/parulghalout', 'https://x.com/semeet', 'https://x.com/Emy191990']</t>
+          <t>['https://x.com/zeynp_qas', 'https://x.com/SelmaRomola', 'https://x.com/Salma2232019']</t>
         </is>
       </c>
       <c r="S33" t="n">
@@ -5982,7 +5969,7 @@
         <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
@@ -5991,27 +5978,27 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Through ENBD X Mobile Banking's App @parulghalout @semeet @Emy191990 🌿🇦🇪❤️</t>
+          <t>Through ENBD X Mobile Banking's App @zeynp_qas @SelmaRomola @Salma2232019 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783477979091314</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783402758508685</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @parulghalout @semeet @Emy191990 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @zeynp_qas @SelmaRomola @Salma2232019 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @parulghalout @semeet @Emy191990 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @zeynp_qas @SelmaRomola @Salma2232019 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Through Emirates NBD X Mobile Banking's App</t>
+          <t>Through ENBD X Mobile Banking's App</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -6044,7 +6031,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Through Emirates NBD X Mobile Banking's App</t>
+          <t>Through ENBD X Mobile Banking's App</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
@@ -6067,12 +6054,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2037783402758508685</t>
+          <t>2037783335389540775</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783402758508685</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783335389540775</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -6098,12 +6085,12 @@
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @zeynp_qas @SelmaRomola @Salma2232019 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @Emy191990 @parulghalout @ibushra_03 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Through ENBD X Mobile Banking&amp;#39;s App &lt;a href="/zeynp_qas" title="zeynab kasem"&gt;@zeynp_qas&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; 🌿🇦🇪❤️</t>
+          <t>Through ENBD X Mobile Banking&amp;#39;s App &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="K34" t="b">
@@ -6117,7 +6104,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -6131,7 +6118,7 @@
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
         <is>
-          <t>['https://x.com/zeynp_qas', 'https://x.com/SelmaRomola', 'https://x.com/Salma2232019']</t>
+          <t>['https://x.com/Emy191990', 'https://x.com/parulghalout', 'https://x.com/ibushra_03']</t>
         </is>
       </c>
       <c r="S34" t="n">
@@ -6144,7 +6131,7 @@
         <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
@@ -6153,27 +6140,27 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Through ENBD X Mobile Banking's App @zeynp_qas @SelmaRomola @Salma2232019 🌿🇦🇪❤️</t>
+          <t>Through ENBD X Mobile Banking's App @Emy191990 @parulghalout @ibushra_03 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783402758508685</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783335389540775</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @zeynp_qas @SelmaRomola @Salma2232019 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @Emy191990 @parulghalout @ibushra_03 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @zeynp_qas @SelmaRomola @Salma2232019 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @Emy191990 @parulghalout @ibushra_03 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Through ENBD X Mobile Banking's App</t>
+          <t>Through Emirates NBD X Mobile Banking's App</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -6206,7 +6193,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Through ENBD X Mobile Banking's App</t>
+          <t>Through Emirates NBD X Mobile Banking's App</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
@@ -6229,12 +6216,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2037783335389540775</t>
+          <t>2037783125854679453</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783335389540775</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783125854679453</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -6260,12 +6247,12 @@
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @Emy191990 @parulghalout @ibushra_03 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @parulghalout @Salma2232019 @semeet 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Through ENBD X Mobile Banking&amp;#39;s App &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; 🌿🇦🇪❤️</t>
+          <t>Through ENBD X Mobile Banking&amp;#39;s App &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="K35" t="b">
@@ -6279,21 +6266,21 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Mar 28, 2026 · 6:46 AM UTC</t>
+          <t>Mar 28, 2026 · 6:45 AM UTC</t>
         </is>
       </c>
       <c r="P35" s="2" t="n">
-        <v>46109.28194444445</v>
+        <v>46109.28125</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
         <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/parulghalout', 'https://x.com/ibushra_03']</t>
+          <t>['https://x.com/parulghalout', 'https://x.com/Salma2232019', 'https://x.com/semeet']</t>
         </is>
       </c>
       <c r="S35" t="n">
@@ -6306,7 +6293,7 @@
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
@@ -6315,22 +6302,22 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Through ENBD X Mobile Banking's App @Emy191990 @parulghalout @ibushra_03 🌿🇦🇪❤️</t>
+          <t>Through ENBD X Mobile Banking's App @parulghalout @Salma2232019 @semeet 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783335389540775</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783125854679453</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @Emy191990 @parulghalout @ibushra_03 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @parulghalout @Salma2232019 @semeet 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @Emy191990 @parulghalout @ibushra_03 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @parulghalout @Salma2232019 @semeet 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
@@ -6349,7 +6336,7 @@
         </is>
       </c>
       <c r="AE35" s="2" t="n">
-        <v>46109.44861111111</v>
+        <v>46109.44791666666</v>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
@@ -6391,12 +6378,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2037783125854679453</t>
+          <t>2037783049065390446</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783125854679453</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783049065390446</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6422,12 +6409,14 @@
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @parulghalout @Salma2232019 @semeet 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App 
+@Emy191990 @ibushra_03 @semeet 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Through ENBD X Mobile Banking&amp;#39;s App &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; 🌿🇦🇪❤️</t>
+          <t>Through ENBD X Mobile Banking&amp;#39;s App 
+&lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="K36" t="b">
@@ -6441,7 +6430,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -6455,7 +6444,7 @@
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
         <is>
-          <t>['https://x.com/parulghalout', 'https://x.com/Salma2232019', 'https://x.com/semeet']</t>
+          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/semeet']</t>
         </is>
       </c>
       <c r="S36" t="n">
@@ -6468,7 +6457,7 @@
         <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
@@ -6477,22 +6466,25 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Through ENBD X Mobile Banking's App @parulghalout @Salma2232019 @semeet 🌿🇦🇪❤️</t>
+          <t>Through ENBD X Mobile Banking's App 
+@Emy191990 @ibushra_03 @semeet 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783125854679453</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783049065390446</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @parulghalout @Salma2232019 @semeet 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App 
+@Emy191990 @ibushra_03 @semeet 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @parulghalout @Salma2232019 @semeet 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App 
+@Emy191990 @ibushra_03 @semeet 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
@@ -6553,45 +6545,44 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2037783049065390446</t>
+          <t>2037730056920088898</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783049065390446</t>
+          <t>https://x.com/wil3020/status/2037730056920088898</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S</t>
+          <t>https://x.com/wil3020</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sosomostafa729S</t>
+          <t>wil3020</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Soha.mostafa77</t>
+          <t>wiil</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1939900695018106882/lxZGZx9Y_bigger.jpg</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App 
-@Emy191990 @ibushra_03 @semeet 🌿🇦🇪❤️</t>
+          <t>Stay safe and bank with ease with ENBD X and businessONLINE 
+Visit https://t.co/0Z1tddYvqD https://t.co/l7XrKjfHOu</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Through ENBD X Mobile Banking&amp;#39;s App 
-&lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; 🌿🇦🇪❤️</t>
+          <t>The UAE is no longer safe Continuous and comprehensive bombing of the UAE now</t>
         </is>
       </c>
       <c r="K37" t="b">
@@ -6605,23 +6596,19 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>Mar 28</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Mar 28, 2026 · 6:45 AM UTC</t>
+          <t>Mar 28, 2026 · 3:14 AM UTC</t>
         </is>
       </c>
       <c r="P37" s="2" t="n">
-        <v>46109.28125</v>
+        <v>46109.13472222222</v>
       </c>
       <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/semeet']</t>
-        </is>
-      </c>
+      <c r="R37" t="inlineStr"/>
       <c r="S37" t="n">
         <v>0</v>
       </c>
@@ -6632,7 +6619,7 @@
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
@@ -6641,30 +6628,29 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Through ENBD X Mobile Banking's App 
-@Emy191990 @ibushra_03 @semeet 🌿🇦🇪❤️</t>
+          <t>The UAE is no longer safe Continuous and comprehensive bombing of the UAE now</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783049065390446</t>
+          <t>https://x.com/wil3020/status/2037730056920088898</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App 
-@Emy191990 @ibushra_03 @semeet 🌿🇦🇪❤️</t>
+          <t>Stay safe and bank with ease with ENBD X and businessONLINE 
+Visit https://t.co/0Z1tddYvqD https://t.co/l7XrKjfHOu</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App 
-@Emy191990 @ibushra_03 @semeet 🌿🇦🇪❤️</t>
+          <t>Stay safe and bank with ease with ENBD X and businessONLINE 
+Visit https://t.co/0Z1tddYvqD https://t.co/l7XrKjfHOu</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>Through ENBD X Mobile Banking's App</t>
+          <t>Stay safe and bank with ease with ENBD X and businessONLINE.</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -6674,11 +6660,11 @@
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE37" s="2" t="n">
-        <v>46109.44791666666</v>
+        <v>46109.30138888889</v>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
@@ -6697,7 +6683,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Through ENBD X Mobile Banking's App</t>
+          <t>Stay safe and bank with ease with ENBD X and businessONLINE.</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -6720,44 +6706,43 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2037730056920088898</t>
+          <t>2037785071189671937</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://x.com/wil3020/status/2037730056920088898</t>
+          <t>https://x.com/ZaibKang/status/2037785071189671937</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://x.com/wil3020</t>
+          <t>https://x.com/ZaibKang</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>wil3020</t>
+          <t>ZaibKang</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>wiil</t>
+          <t>Jahan Zaib Akbar Kang</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1939900695018106882/lxZGZx9Y_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2028644994790436864/h-Avrj3s_bigger.jpg</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Stay safe and bank with ease with ENBD X and businessONLINE 
-Visit https://t.co/0Z1tddYvqD https://t.co/l7XrKjfHOu</t>
+          <t>@EmiratesNBD_AE @EmiratesNBD_AE I applied for liv X account 3 days ago still not received any response please Check and respond as soon as possible https://t.co/LXfxy0AGqW</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>The UAE is no longer safe Continuous and comprehensive bombing of the UAE now</t>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; I applied for liv X account 3 days ago still not received any response please Check and respond as soon as possible</t>
         </is>
       </c>
       <c r="K38" t="b">
@@ -6771,19 +6756,23 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Mar 28</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Mar 28, 2026 · 3:14 AM UTC</t>
+          <t>Mar 28, 2026 · 6:53 AM UTC</t>
         </is>
       </c>
       <c r="P38" s="2" t="n">
-        <v>46109.13472222222</v>
+        <v>46109.28680555556</v>
       </c>
       <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="S38" t="n">
         <v>0</v>
       </c>
@@ -6794,7 +6783,7 @@
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
@@ -6803,29 +6792,27 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>The UAE is no longer safe Continuous and comprehensive bombing of the UAE now</t>
+          <t>@EmiratesNBD_AE I applied for liv X account 3 days ago still not received any response please Check and respond as soon as possible</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>https://x.com/wil3020/status/2037730056920088898</t>
+          <t>https://x.com/ZaibKang/status/2037785071189671937</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>Stay safe and bank with ease with ENBD X and businessONLINE 
-Visit https://t.co/0Z1tddYvqD https://t.co/l7XrKjfHOu</t>
+          <t>@EmiratesNBD_AE @EmiratesNBD_AE I applied for liv X account 3 days ago still not received any response please Check and respond as soon as possible https://t.co/LXfxy0AGqW</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>Stay safe and bank with ease with ENBD X and businessONLINE 
-Visit https://t.co/0Z1tddYvqD https://t.co/l7XrKjfHOu</t>
+          <t>@EmiratesNBD_AE @EmiratesNBD_AE I applied for liv X account 3 days ago still not received any response please Check and respond as soon as possible https://t.co/LXfxy0AGqW</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>Stay safe and bank with ease with ENBD X and businessONLINE.</t>
+          <t>I applied for a liv X account 3 days ago and still have not received any response. Please check and respond as soon as possible.</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -6835,11 +6822,11 @@
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="AE38" s="2" t="n">
-        <v>46109.30138888889</v>
+        <v>46109.45347222222</v>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
@@ -6858,7 +6845,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Stay safe and bank with ease with ENBD X and businessONLINE.</t>
+          <t>I applied for a liv X account 3 days ago and still have not received any response. • Please check and respond as soon as possible.</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
@@ -6881,66 +6868,62 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2037785071189671937</t>
+          <t>2037865010320539854</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://x.com/ZaibKang/status/2037785071189671937</t>
+          <t>https://x.com/rated_sm/status/2037865010320539854</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://x.com/ZaibKang</t>
+          <t>https://x.com/rated_sm</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ZaibKang</t>
+          <t>rated_sm</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Jahan Zaib Akbar Kang</t>
+          <t>rated_sm</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2028644994790436864/h-Avrj3s_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1870693863452524544/xTAmP9KA_bigger.jpg</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE @EmiratesNBD_AE I applied for liv X account 3 days ago still not received any response please Check and respond as soon as possible https://t.co/LXfxy0AGqW</t>
+          <t>@EmiratesNBD_AE My phone is broken and is pending repair with Apple. I need to make a payment and I logged into the website using OTP, but when attempting payment, its still asking for Smart Pass confirmation and no OTP option. Same when attempting to contact Whatsapp Support.</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; I applied for liv X account 3 days ago still not received any response please Check and respond as soon as possible</t>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; My phone is broken and is pending repair with Apple. I need to make a payment and I logged into the website using OTP, but when attempting payment, its still asking for Smart Pass confirmation and no OTP option. Same when attempting to contact Whatsapp Support.</t>
         </is>
       </c>
       <c r="K39" t="b">
         <v>0</v>
       </c>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Mar 28, 2026 · 6:53 AM UTC</t>
+          <t>Mar 28, 2026 · 12:10 PM UTC</t>
         </is>
       </c>
       <c r="P39" s="2" t="n">
-        <v>46109.28680555556</v>
+        <v>46109.50694444445</v>
       </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
@@ -6949,7 +6932,7 @@
         </is>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T39" t="n">
         <v>0</v>
@@ -6958,7 +6941,7 @@
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
@@ -6967,27 +6950,19 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE I applied for liv X account 3 days ago still not received any response please Check and respond as soon as possible</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>https://x.com/ZaibKang/status/2037785071189671937</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE @EmiratesNBD_AE I applied for liv X account 3 days ago still not received any response please Check and respond as soon as possible https://t.co/LXfxy0AGqW</t>
-        </is>
-      </c>
+          <t>@EmiratesNBD_AE My phone is broken and is pending repair with Apple. I need to make a payment and I logged into the website using OTP, but when attempting payment, its still asking for Smart Pass confirmation and no OTP option. Same when attempting to contact Whatsapp Support.</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE @EmiratesNBD_AE I applied for liv X account 3 days ago still not received any response please Check and respond as soon as possible https://t.co/LXfxy0AGqW</t>
+          <t>@EmiratesNBD_AE My phone is broken and is pending repair with Apple. I need to make a payment and I logged into the website using OTP, but when attempting payment, its still asking for Smart Pass confirmation and no OTP option. Same when attempting to contact Whatsapp Support.</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>I applied for a liv X account 3 days ago and still have not received any response. Please check and respond as soon as possible.</t>
+          <t>My phone is broken and is pending repair with Apple. I need to make a payment and I logged into the website using OTP, but when attempting payment, it's still asking for Smart Pass confirmation and no OTP option. The same happens when attempting to contact WhatsApp Support.</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -7001,7 +6976,7 @@
         </is>
       </c>
       <c r="AE39" s="2" t="n">
-        <v>46109.45347222222</v>
+        <v>46109.67361111111</v>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
@@ -7020,7 +6995,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>I applied for a liv X account 3 days ago and still have not received any response. • Please check and respond as soon as possible.</t>
+          <t>I need to make a payment and I logged into the website using OTP, but when attempting payment, it's still asking for Smart Pass confirmation and no OTP option. • The same happens when attempting to contact WhatsApp Support. • My phone is broken and is pending repair with Apple.</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
@@ -7032,156 +7007,6 @@
         <v>2026</v>
       </c>
       <c r="AL39" t="inlineStr">
-        <is>
-          <t>EmiratesNBD_AE</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="n">
-        <v>38</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2037865010320539854</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>https://x.com/rated_sm/status/2037865010320539854</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>https://x.com/rated_sm</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>rated_sm</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>rated_sm</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1870693863452524544/xTAmP9KA_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE My phone is broken and is pending repair with Apple. I need to make a payment and I logged into the website using OTP, but when attempting payment, its still asking for Smart Pass confirmation and no OTP option. Same when attempting to contact Whatsapp Support.</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; My phone is broken and is pending repair with Apple. I need to make a payment and I logged into the website using OTP, but when attempting payment, its still asking for Smart Pass confirmation and no OTP option. Same when attempting to contact Whatsapp Support.</t>
-        </is>
-      </c>
-      <c r="K40" t="b">
-        <v>0</v>
-      </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>15h</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>Mar 28, 2026 · 12:10 PM UTC</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="n">
-        <v>46109.50694444445</v>
-      </c>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>['https://x.com/EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="S40" t="n">
-        <v>1</v>
-      </c>
-      <c r="T40" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" t="n">
-        <v>17</v>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE My phone is broken and is pending repair with Apple. I need to make a payment and I logged into the website using OTP, but when attempting payment, its still asking for Smart Pass confirmation and no OTP option. Same when attempting to contact Whatsapp Support.</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr"/>
-      <c r="Z40" t="inlineStr"/>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE My phone is broken and is pending repair with Apple. I need to make a payment and I logged into the website using OTP, but when attempting payment, its still asking for Smart Pass confirmation and no OTP option. Same when attempting to contact Whatsapp Support.</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>My phone is broken and is pending repair with Apple. I need to make a payment and I logged into the website using OTP, but when attempting payment, it's still asking for Smart Pass confirmation and no OTP option. The same happens when attempting to contact WhatsApp Support.</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD40" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="AE40" s="2" t="n">
-        <v>46109.67361111111</v>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>28-03-2026</t>
-        </is>
-      </c>
-      <c r="AG40" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>I need to make a payment and I logged into the website using OTP, but when attempting payment, it's still asking for Smart Pass confirmation and no OTP option. • The same happens when attempting to contact WhatsApp Support. • My phone is broken and is pending repair with Apple.</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AK40" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL40" t="inlineStr">
         <is>
           <t>None</t>
         </is>

--- a/check2.xlsx
+++ b/check2.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL39"/>
+  <dimension ref="A1:AL40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -700,7 +700,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -821,9 +821,7 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>What’s more suspicious?
-Stay Safe, Stay Vigilant. #UnitedAgainstFraud
-https://t.co/YpRWtBZrhq</t>
+          <t>We regret to inform you that this process can be done only by a branch visit within the UAE.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -865,7 +863,7 @@
         <v>1</v>
       </c>
       <c r="V3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -877,29 +875,16 @@
           <t>We regret to inform you that this process can be done only by a branch visit within the UAE.</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037936526093430909</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>What’s more suspicious?
-Stay Safe, Stay Vigilant. #UnitedAgainstFraud
-https://t.co/YpRWtBZrhq</t>
-        </is>
-      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>What’s more suspicious?
-Stay Safe, Stay Vigilant. #UnitedAgainstFraud
-https://t.co/YpRWtBZrhq</t>
+          <t>We regret to inform you that this process can be done only by a branch visit within the UAE.</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>What’s more suspicious? 
-Stay Safe, Stay Vigilant. #UnitedAgainstFraud</t>
+          <t>We regret to inform you that this process can only be completed by visiting a branch within the UAE.</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -932,7 +917,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Stay Safe, Stay Vigilant.</t>
+          <t>We regret to inform you that this process can only be completed by visiting a branch within the UAE.</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -986,7 +971,9 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>I just got back from the UAE, is there any chance I can start the process online. I'll probably go again in august.</t>
+          <t>What’s more suspicious?
+Stay Safe, Stay Vigilant. #UnitedAgainstFraud
+https://t.co/YpRWtBZrhq</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1005,7 +992,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>12h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1028,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -1040,16 +1027,29 @@
           <t>I just got back from the UAE, is there any chance I can start the process online. I'll probably go again in august.</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>https://x.com/cruizomfs/status/2037928218003382573</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>What’s more suspicious?
+Stay Safe, Stay Vigilant. #UnitedAgainstFraud
+https://t.co/YpRWtBZrhq</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>I just got back from the UAE, is there any chance I can start the process online. I'll probably go again in august.</t>
+          <t>What’s more suspicious?
+Stay Safe, Stay Vigilant. #UnitedAgainstFraud
+https://t.co/YpRWtBZrhq</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>I just got back from the UAE, is there any chance I can start the process online? I'll probably go again in August.</t>
+          <t>What’s more suspicious? 
+Stay Safe, Stay Vigilant. #UnitedAgainstFraud</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>I just got back from the UAE, is there any chance I can start the process online? • I'll probably go again in August.</t>
+          <t>Stay Safe, Stay Vigilant.</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1210,7 +1210,7 @@
         <v>1</v>
       </c>
       <c r="V5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1408,7 +1408,7 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1559,10 +1559,10 @@
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V7" t="n">
-        <v>651</v>
+        <v>663</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1825,8 +1825,7 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA بالنسبة للتقسيط بدون هامش ربح هل لو سددت من خلال الفيزا ابل باي اقدر استفيد من العرض ؟ 
-يعني ععندب في نون اشتري ابل باي وبعدها اقسطها ؟</t>
+          <t>نعم يمكنك تقسيط المبلغ, لطلب التقسيط وتفاصيل أكثر قبل إجراء المعاملة يرجى الاتصال بنا على الرقم المجاني 8007547777</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1868,7 +1867,7 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1880,26 +1879,16 @@
           <t>نعم يمكنك تقسيط المبلغ, لطلب التقسيط وتفاصيل أكثر قبل إجراء المعاملة يرجى الاتصال بنا على الرقم المجاني 8007547777</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2037827252075839770</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_KSA بالنسبة للتقسيط بدون هامش ربح هل لو سددت من خلال الفيزا ابل باي اقدر استفيد من العرض ؟ 
-يعني ععندب في نون اشتري ابل باي وبعدها اقسطها ؟</t>
-        </is>
-      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA بالنسبة للتقسيط بدون هامش ربح هل لو سددت من خلال الفيزا ابل باي اقدر استفيد من العرض ؟ 
-يعني ععندب في نون اشتري ابل باي وبعدها اقسطها ؟</t>
+          <t>نعم يمكنك تقسيط المبلغ, لطلب التقسيط وتفاصيل أكثر قبل إجراء المعاملة يرجى الاتصال بنا على الرقم المجاني 8007547777</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Regarding the installment plan without profit margin, if I pay through Visa Apple Pay, can I benefit from the offer? I mean, can I buy through Noon using Apple Pay and then pay in installments?</t>
+          <t>Yes, you can pay in installments. To request installment details before making the transaction, please contact us at the toll-free number 8007547777.</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1932,7 +1921,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Regarding the installment plan without profit margin, if I pay through Visa Apple Pay, can I benefit from the offer? • I mean, can I buy through Noon using Apple Pay and then pay in installments?</t>
+          <t>To request installment details before making the transaction, please contact us at the toll-free number 8007547777. • Yes, you can pay in installments.</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -2030,7 +2019,7 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -2043,8 +2032,17 @@
 يعني ععندب في نون اشتري ابل باي وبعدها اقسطها ؟</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>https://x.com/Talal_Hus/status/2037818020597215557</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA بالنسبة للتقسيط بدون هامش ربح هل لو سددت من خلال الفيزا ابل باي اقدر استفيد من العرض ؟ 
+يعني ععندب في نون اشتري ابل باي وبعدها اقسطها ؟</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>@EmiratesNBD_KSA بالنسبة للتقسيط بدون هامش ربح هل لو سددت من خلال الفيزا ابل باي اقدر استفيد من العرض ؟ 
@@ -2140,7 +2138,7 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>THE WOMAN DAT CARRIED YOU FOR 9 MONTHS MAY SHE LIVE LONG AND WITNESS YOU SUCCEED 🤍 https://t.co/0XDJyqkART</t>
+          <t>THE WOMAN DAT CARRIED YOU FOR 9 MONTHS MAY SHE LIVE LONG AND WITNESS YOU SUCCEED 🤍</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -2178,7 +2176,7 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -2190,24 +2188,16 @@
           <t>THE WOMAN DAT CARRIED YOU FOR 9 MONTHS MAY SHE LIVE LONG AND WITNESS YOU SUCCEED 🤍</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>https://x.com/eazyislit/status/2037804608517509572</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>THE WOMAN DAT CARRIED YOU FOR 9 MONTHS MAY SHE LIVE LONG AND WITNESS YOU SUCCEED 🤍 https://t.co/0XDJyqkART</t>
-        </is>
-      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>THE WOMAN DAT CARRIED YOU FOR 9 MONTHS MAY SHE LIVE LONG AND WITNESS YOU SUCCEED 🤍 https://t.co/0XDJyqkART</t>
+          <t>THE WOMAN DAT CARRIED YOU FOR 9 MONTHS MAY SHE LIVE LONG AND WITNESS YOU SUCCEED 🤍</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>The woman who carried you for 9 months may she live long and witness you succeed 🤍</t>
+          <t>The woman who carried you for 9 months may she live long and witness you succeed.</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2240,7 +2230,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>The woman who carried you for 9 months may she live long and witness you succeed 🤍</t>
+          <t>The woman who carried you for 9 months may she live long and witness you succeed.</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -2294,9 +2284,9 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Before clicking a link, what do you do?
+          <t>What’s more suspicious?
 Stay Safe, Stay Vigilant. #UnitedAgainstFraud
-https://t.co/YpRWtBZrhq</t>
+emiratesnbd.com/en/campaigns…</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2337,10 +2327,10 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V12" t="n">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -2354,28 +2344,19 @@
 emiratesnbd.com/en/campaigns…</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037801868244533349</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Before clicking a link, what do you do?
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>What’s more suspicious?
 Stay Safe, Stay Vigilant. #UnitedAgainstFraud
-https://t.co/YpRWtBZrhq</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Before clicking a link, what do you do?
-Stay Safe, Stay Vigilant. #UnitedAgainstFraud
-https://t.co/YpRWtBZrhq</t>
+emiratesnbd.com/en/campaigns…</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Before clicking a link, what do you do? Stay safe, stay vigilant. #UnitedAgainstFraud</t>
+          <t>What’s more suspicious? 
+Stay Safe, Stay Vigilant. #UnitedAgainstFraud</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2408,7 +2389,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Stay safe, stay vigilant. • Before clicking a link, what do you do?</t>
+          <t>Stay Safe, Stay Vigilant.</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2510,7 +2491,7 @@
         <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -2605,36 +2586,201 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2037796009921900610</t>
+          <t>2037796434725269639</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://x.com/MazBalushi35285/status/2037796009921900610</t>
+          <t>https://x.com/ZaibKang/status/2037796434725269639</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://x.com/MazBalushi35285</t>
+          <t>https://x.com/ZaibKang</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MazBalushi35285</t>
+          <t>ZaibKang</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>مازن البلوشي</t>
+          <t>Jahan Zaib Akbar Kang</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2018589030322253824/-R_IX5Kh_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2028644994790436864/h-Avrj3s_bigger.jpg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
+        <is>
+          <t>Before clicking a link, what do you do?
+Stay Safe, Stay Vigilant. #UnitedAgainstFraud
+https://t.co/YpRWtBZrhq</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Thanks for your timely response.</t>
+        </is>
+      </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 7:38 AM UTC</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>46109.31805555556</v>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>14</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Thanks for your timely response.</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>https://x.com/ZaibKang/status/2037796434725269639</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>Before clicking a link, what do you do?
+Stay Safe, Stay Vigilant. #UnitedAgainstFraud
+https://t.co/YpRWtBZrhq</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Before clicking a link, what do you do?
+Stay Safe, Stay Vigilant. #UnitedAgainstFraud
+https://t.co/YpRWtBZrhq</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>Before clicking a link, what do you do?
+Stay Safe, Stay Vigilant. #UnitedAgainstFraud</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE14" s="2" t="n">
+        <v>46109.48472222222</v>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>28-03-2026</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Stay Safe, Stay Vigilant. • Before clicking a link, what do you do?</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK14" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2037796009921900610</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://x.com/MazBalushi35285/status/2037796009921900610</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://x.com/MazBalushi35285</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>MazBalushi35285</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>مازن البلوشي</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2018589030322253824/-R_IX5Kh_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
         <is>
           <t>جمهور الصقر جاهزين لحفل العيد مع صقر الأغنية الخليجية #رابح_صقر ؟🦅🎶
 #روتانا_لايف
@@ -2648,63 +2794,63 @@
 @EmiratesNBD_KSA https://t.co/0V3B6UgNKV</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>🥳مزيد من النواة الفн على مسابقة رابح صقر! راحت لكم الحفل العيد في الرياض! 🎉 فوق_النهاية فقط</t>
         </is>
       </c>
-      <c r="K14" t="b">
-        <v>0</v>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
         <is>
           <t>['RotanaLive', 'Turki_alalshikh', 'RabehSaqer', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>21h</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 7:36 AM UTC</t>
         </is>
       </c>
-      <c r="P14" s="2" t="n">
+      <c r="P15" s="2" t="n">
         <v>46109.31666666667</v>
       </c>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>27</v>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>28</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
         <is>
           <t>🥳مزيد من النواة الفн على مسابقة رابح صقر! راحت لكم الحفل العيد في الرياض! 🎉 فوق_النهاية فقط</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>https://x.com/MazBalushi35285/status/2037796009921900610</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>جمهور الصقر جاهزين لحفل العيد مع صقر الأغنية الخليجية #رابح_صقر ؟🦅🎶
 #روتانا_لايف
@@ -2718,7 +2864,7 @@
 @EmiratesNBD_KSA https://t.co/0V3B6UgNKV</t>
         </is>
       </c>
-      <c r="AA14" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>جمهور الصقر جاهزين لحفل العيد مع صقر الأغنية الخليجية #رابح_صقر ؟🦅🎶
 #روتانا_لايف
@@ -2732,94 +2878,94 @@
 @EmiratesNBD_KSA https://t.co/0V3B6UgNKV</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>The audience of Saqr is ready for the Eid celebration with the falcon of Gulf music, Rabeh Saqr? 🦅🎶</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>The Falcon audience is ready for the Eid celebration with the Gulf songbird #Rabeh_Saqer? 🦅🎶</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="AD14" t="inlineStr">
+      <c r="AD15" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="AE14" s="2" t="n">
+      <c r="AE15" s="2" t="n">
         <v>46109.48333333333</v>
       </c>
-      <c r="AF14" t="inlineStr">
+      <c r="AF15" t="inlineStr">
         <is>
           <t>28-03-2026</t>
         </is>
       </c>
-      <c r="AG14" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH14" t="inlineStr">
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>The audience of Saqr is ready for the Eid celebration with the falcon of Gulf music, Rabeh Saqr?</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>The Falcon audience is ready for the Eid celebration with the Gulf songbird #Rabeh_Saqer?</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
         <is>
           <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AK14" t="n">
+      <c r="AK15" t="n">
         <v>2026</v>
       </c>
-      <c r="AL14" t="inlineStr">
+      <c r="AL15" t="inlineStr">
         <is>
           <t>RotanaLive, Turki_alalshikh, RabehSaqer, GEA_SA, EidSeason, Mabdoarena, EmiratesNBD_KSA</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>2037790087141101872</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola/status/2037790087141101872</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>SelmaRomola</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Selma Romola</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1118152018995105792/5fyZOTth_bigger.jpg</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
         <is>
           <t>نفذت أموال أم خماس قبل نهاية الشهر.
 هناك قاعدة بسيطة تُساعدها على إدارة أموالها بحكمة:
@@ -2846,7 +2992,7 @@
 - Drop your answer below for a chance to win AED 10,000</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>Fin well Financial well-being program with Emirates NBD 
 &lt;a href="/Sabaashraff" title="Saba Ashraf"&gt;@Sabaashraff&lt;/a&gt;
@@ -2854,52 +3000,52 @@
 &lt;a href="/Amanekhattab1" title="Amanekhattab"&gt;@Amanekhattab1&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K15" t="b">
-        <v>0</v>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>22h</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 7:13 AM UTC</t>
         </is>
       </c>
-      <c r="P15" s="2" t="n">
+      <c r="P16" s="2" t="n">
         <v>46109.30069444444</v>
       </c>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr">
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
         <is>
           <t>['https://x.com/Sabaashraff', 'https://x.com/Sosomostafa729S', 'https://x.com/Amanekhattab1']</t>
         </is>
       </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>8</v>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>9</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
         <is>
           <t>Fin well Financial well-being program with Emirates NBD 
 @Sabaashraff
@@ -2907,12 +3053,12 @@
 @Amanekhattab1</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola/status/2037790087141101872</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>نفذت أموال أم خماس قبل نهاية الشهر.
 هناك قاعدة بسيطة تُساعدها على إدارة أموالها بحكمة:
@@ -2939,7 +3085,7 @@
 - Drop your answer below for a chance to win AED 10,000</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>نفذت أموال أم خماس قبل نهاية الشهر.
 هناك قاعدة بسيطة تُساعدها على إدارة أموالها بحكمة:
@@ -2966,105 +3112,104 @@
 - Drop your answer below for a chance to win AED 10,000</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>Um Khammas ran out of cash before the month ended.
-A simple rule can help her stay on track:
-50% for needs
-30% for wants
+A simple rule can help her manage her money wisely:
+50% for basic needs
+30% for luxuries
 20% for savings
-A smart plan that helps you spend, save and stay in control.
-This is one of the many tips that the bank’s programme has in store.
-Watch the episode and tell us the name of the programme?
+A smart plan that enables you to spend, save, and maintain control over your budget. This is one of the many tips offered by the bank's program.
+Watch the episode and tell us the name of the program?
 To participate:
 - Follow Emirates NBD
-- Tag 3 friends
-- Drop your answer below for a chance to win AED 10,000</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
+- Tag 3 of your friends
+- Write your answer in the comments below for a chance to win AED 10,000.</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr">
+      <c r="AD16" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="AE15" s="2" t="n">
+      <c r="AE16" s="2" t="n">
         <v>46109.46736111111</v>
       </c>
-      <c r="AF15" t="inlineStr">
+      <c r="AF16" t="inlineStr">
         <is>
           <t>28-03-2026</t>
         </is>
       </c>
-      <c r="AG15" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH15" t="inlineStr">
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>A simple rule can help her stay on track: 50% for needs 30% for wants 20% for savings A smart plan that helps you spend, save and stay in control. • To participate: - Follow Emirates NBD - Tag 3 friends - Drop your answer below for a chance to win AED 10,000 • This is one of the many tips that the bank’s programme has in store.</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>A simple rule can help her manage her money wisely: 50% for basic needs 30% for luxuries 20% for savings A smart plan that enables you to spend, save, and maintain control over your budget. • To participate: - Follow Emirates NBD - Tag 3 of your friends - Write your answer in the comments below for a chance to win AED 10,000. • This is one of the many tips offered by the bank's program.</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
         <is>
           <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AK15" t="n">
+      <c r="AK16" t="n">
         <v>2026</v>
       </c>
-      <c r="AL15" t="inlineStr">
+      <c r="AL16" t="inlineStr">
         <is>
           <t>EmiratesNBD_AE</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>2037789707321622955</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola/status/2037789707321622955</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>SelmaRomola</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Selma Romola</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1118152018995105792/5fyZOTth_bigger.jpg</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
         <is>
           <t>اجعل مفاجآت العيد أكثر قيمة.
 من الفضة إلى الذهب، اكتشف طريقة أذكى لامتلاك أو إهداء شيء ثمين بحق.
@@ -3076,7 +3221,7 @@
 اكتب إجابتك في التعليقات أدناه لفرصة ربح 10,000 درهم</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>To buy gold and silver through Emirates NBD, the fastest way is using the ENBD X mobile app. 
 Tagging 
@@ -3085,52 +3230,52 @@
 &lt;a href="/Bushrasabih2" title="Bu_shaikh🌸❤️"&gt;@Bushrasabih2&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K16" t="b">
-        <v>0</v>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
+      <c r="K17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>22h</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 7:11 AM UTC</t>
         </is>
       </c>
-      <c r="P16" s="2" t="n">
+      <c r="P17" s="2" t="n">
         <v>46109.29930555556</v>
       </c>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr">
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
         <is>
           <t>['https://x.com/FazilAnas', 'https://x.com/Emy191990', 'https://x.com/Bushrasabih2']</t>
         </is>
       </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>11</v>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>12</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
         <is>
           <t>To buy gold and silver through Emirates NBD, the fastest way is using the ENBD X mobile app. 
 Tagging 
@@ -3139,12 +3284,12 @@
 @Bushrasabih2</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola/status/2037789707321622955</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>اجعل مفاجآت العيد أكثر قيمة.
 من الفضة إلى الذهب، اكتشف طريقة أذكى لامتلاك أو إهداء شيء ثمين بحق.
@@ -3156,7 +3301,7 @@
 اكتب إجابتك في التعليقات أدناه لفرصة ربح 10,000 درهم</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>اجعل مفاجآت العيد أكثر قيمة.
 من الفضة إلى الذهب، اكتشف طريقة أذكى لامتلاك أو إهداء شيء ثمين بحق.
@@ -3168,95 +3313,95 @@
 اكتب إجابتك في التعليقات أدناه لفرصة ربح 10,000 درهم</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>Make holiday surprises more valuable. From silver to gold, discover a smarter way to own or gift something truly precious. Watch this episode and tell us: How can you buy gold and silver from the bank? 
 To participate: Follow the Emirates NBD account Tag 3 of your friends Write your answer in the comments below for a chance to win 10,000 dirhams.</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
+      <c r="AC17" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="AD16" t="inlineStr">
+      <c r="AD17" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="AE16" s="2" t="n">
+      <c r="AE17" s="2" t="n">
         <v>46109.46597222222</v>
       </c>
-      <c r="AF16" t="inlineStr">
+      <c r="AF17" t="inlineStr">
         <is>
           <t>28-03-2026</t>
         </is>
       </c>
-      <c r="AG16" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH16" t="inlineStr">
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AI16" t="inlineStr">
+      <c r="AI17" t="inlineStr">
         <is>
           <t>To participate: Follow the Emirates NBD account Tag 3 of your friends Write your answer in the comments below for a chance to win 10,000 dirhams. • From silver to gold, discover a smarter way to own or gift something truly precious. • Watch this episode and tell us: How can you buy gold and silver from the bank?</t>
         </is>
       </c>
-      <c r="AJ16" t="inlineStr">
+      <c r="AJ17" t="inlineStr">
         <is>
           <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AK16" t="n">
+      <c r="AK17" t="n">
         <v>2026</v>
       </c>
-      <c r="AL16" t="inlineStr">
+      <c r="AL17" t="inlineStr">
         <is>
           <t>EmiratesNBD_AE</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
         <is>
           <t>2037789510478843981</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola/status/2037789510478843981</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>SelmaRomola</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Selma Romola</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1118152018995105792/5fyZOTth_bigger.jpg</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
         <is>
           <t>@EmiratesNBD_AE To buy gold and silver through Emirates NBD, the fastest way is using the ENBD X mobile app. 
 Tagging 
@@ -3265,7 +3410,7 @@
 @yasar8212</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>To buy gold and silver through Emirates NBD, the fastest way is using the ENBD X mobile app. 
 Tagging 
@@ -3274,52 +3419,52 @@
 &lt;a href="/yasar8212" title="shaniyadu"&gt;@yasar8212&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K17" t="b">
-        <v>0</v>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>22h</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 7:10 AM UTC</t>
         </is>
       </c>
-      <c r="P17" s="2" t="n">
+      <c r="P18" s="2" t="n">
         <v>46109.29861111111</v>
       </c>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr">
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
         <is>
           <t>['https://x.com/Sosomostafa729S', 'https://x.com/Nur_Munem', 'https://x.com/yasar8212']</t>
         </is>
       </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>8</v>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>9</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
         <is>
           <t>To buy gold and silver through Emirates NBD, the fastest way is using the ENBD X mobile app. 
 Tagging 
@@ -3328,12 +3473,12 @@
 @yasar8212</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola/status/2037789510478843981</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>@EmiratesNBD_AE To buy gold and silver through Emirates NBD, the fastest way is using the ENBD X mobile app. 
 Tagging 
@@ -3342,7 +3487,7 @@
 @yasar8212</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>@EmiratesNBD_AE To buy gold and silver through Emirates NBD, the fastest way is using the ENBD X mobile app. 
 Tagging 
@@ -3351,94 +3496,94 @@
 @yasar8212</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>To buy gold and silver through Emirates NBD, the fastest way is using the ENBD X mobile app.</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
+      <c r="AC18" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="AD17" t="inlineStr">
+      <c r="AD18" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="AE17" s="2" t="n">
+      <c r="AE18" s="2" t="n">
         <v>46109.46527777778</v>
       </c>
-      <c r="AF17" t="inlineStr">
+      <c r="AF18" t="inlineStr">
         <is>
           <t>28-03-2026</t>
         </is>
       </c>
-      <c r="AG17" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH17" t="inlineStr">
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AI17" t="inlineStr">
+      <c r="AI18" t="inlineStr">
         <is>
           <t>To buy gold and silver through Emirates NBD, the fastest way is using the ENBD X mobile app.</t>
         </is>
       </c>
-      <c r="AJ17" t="inlineStr">
+      <c r="AJ18" t="inlineStr">
         <is>
           <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AK17" t="n">
+      <c r="AK18" t="n">
         <v>2026</v>
       </c>
-      <c r="AL17" t="inlineStr">
+      <c r="AL18" t="inlineStr">
         <is>
           <t>EmiratesNBD_AE</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
         <is>
           <t>2037788447910564341</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola/status/2037788447910564341</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>SelmaRomola</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Selma Romola</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1118152018995105792/5fyZOTth_bigger.jpg</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
         <is>
           <t>Make Eid surprises even more valuable.
 From silver to gold, discover a smarter way to own or gift something truly precious.
@@ -3450,7 +3595,7 @@
 Drop your answer below for a chance to win AED 10,000</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>To buy gold and silver through Emirates NBD, the fastest way is using the ENBD X mobile app. 
 Tagging 
@@ -3459,52 +3604,52 @@
 &lt;a href="/Sosomostafa729S" title="Soha.mostafa77"&gt;@Sosomostafa729S&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K18" t="b">
-        <v>0</v>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
+      <c r="K19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>22h</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 7:06 AM UTC</t>
         </is>
       </c>
-      <c r="P18" s="2" t="n">
+      <c r="P19" s="2" t="n">
         <v>46109.29583333333</v>
       </c>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr">
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
         <is>
           <t>['https://x.com/Bushrasabih2', 'https://x.com/AmalBeevi', 'https://x.com/Sosomostafa729S']</t>
         </is>
       </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>10</v>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>11</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
         <is>
           <t>To buy gold and silver through Emirates NBD, the fastest way is using the ENBD X mobile app. 
 Tagging 
@@ -3513,12 +3658,12 @@
 @Sosomostafa729S</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola/status/2037788447910564341</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>Make Eid surprises even more valuable.
 From silver to gold, discover a smarter way to own or gift something truly precious.
@@ -3530,7 +3675,7 @@
 Drop your answer below for a chance to win AED 10,000</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr">
+      <c r="AA19" t="inlineStr">
         <is>
           <t>Make Eid surprises even more valuable.
 From silver to gold, discover a smarter way to own or gift something truly precious.
@@ -3542,196 +3687,42 @@
 Drop your answer below for a chance to win AED 10,000</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>Make Eid surprises even more valuable. From silver to gold, discover a smarter way to own or gift something truly precious. Watch this episode and tell us: How can you buy gold and silver from the bank? To participate: Follow Emirates NBD Tag 3 friends Drop your answer below for a chance to win AED 10,000</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
+      <c r="AC19" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="AD18" t="inlineStr">
+      <c r="AD19" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="AE18" s="2" t="n">
+      <c r="AE19" s="2" t="n">
         <v>46109.4625</v>
       </c>
-      <c r="AF18" t="inlineStr">
+      <c r="AF19" t="inlineStr">
         <is>
           <t>28-03-2026</t>
         </is>
       </c>
-      <c r="AG18" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH18" t="inlineStr">
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AI18" t="inlineStr">
+      <c r="AI19" t="inlineStr">
         <is>
           <t>To participate: Follow Emirates NBD Tag 3 friends Drop your answer below for a chance to win AED 10,000 • From silver to gold, discover a smarter way to own or gift something truly precious. • Watch this episode and tell us: How can you buy gold and silver from the bank?</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AK18" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>EmiratesNBD_AE</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2037784853866029145</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784853866029145</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Sosomostafa729S</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Soha.mostafa77</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>B- 1.89% @zeynp_qas @Salma2232019 @semeet 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>B- 1.89% &lt;a href="/zeynp_qas" title="zeynab kasem"&gt;@zeynp_qas&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="K19" t="b">
-        <v>0</v>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>22h</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>Mar 28, 2026 · 6:52 AM UTC</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="n">
-        <v>46109.28611111111</v>
-      </c>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>['https://x.com/zeynp_qas', 'https://x.com/Salma2232019', 'https://x.com/semeet']</t>
-        </is>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>4</v>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>B- 1.89% @zeynp_qas @Salma2232019 @semeet 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>B- 1.89% @zeynp_qas @Salma2232019 @semeet 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>B- 1.89% @zeynp_qas @Salma2232019 @semeet 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AE19" s="2" t="n">
-        <v>46109.45277777778</v>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>28-03-2026</t>
-        </is>
-      </c>
-      <c r="AG19" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>B- 1.89% @zeynp_qas @Salma2232019 @semeet 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -3754,12 +3745,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2037784763122217375</t>
+          <t>2037784853866029145</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784763122217375</t>
+          <t>https://x.com/Sosomostafa729S/status/2037784853866029145</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3784,168 +3775,6 @@
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE B- 1.89% @semeet @Salma2232019 @SelmaRomola 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>B- 1.89% &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="K20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>22h</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>Mar 28, 2026 · 6:52 AM UTC</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="n">
-        <v>46109.28611111111</v>
-      </c>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>['https://x.com/semeet', 'https://x.com/Salma2232019', 'https://x.com/SelmaRomola']</t>
-        </is>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>7</v>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>B- 1.89% @semeet @Salma2232019 @SelmaRomola 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784763122217375</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE B- 1.89% @semeet @Salma2232019 @SelmaRomola 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE B- 1.89% @semeet @Salma2232019 @SelmaRomola 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>The text appears to be a social media post or tweet that includes a percentage and mentions of users or accounts, along with emojis. There is no translatable content in terms of language, as it primarily consists of usernames and symbols.</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AE20" s="2" t="n">
-        <v>46109.45277777778</v>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>28-03-2026</t>
-        </is>
-      </c>
-      <c r="AG20" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>The text appears to be a social media post or tweet that includes a percentage and mentions of users or accounts, along with emojis. • There is no translatable content in terms of language, as it primarily consists of usernames and symbols.</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AK20" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL20" t="inlineStr">
-        <is>
-          <t>EmiratesNBD_AE</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2037784668028985459</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784668028985459</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Sosomostafa729S</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Soha.mostafa77</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
         <is>
           <t>حل اللغز واربح 10,000 درهم.💰
 أم علاوي تعبت من مشاكل السيارة، ومستعدة لسيارة جديدة بفضل قرض السيارات السريع من بنك الإمارات دبي الوطني، من خلال طلب سهل وسريع عبر الإنترنت.
@@ -3954,67 +3783,67 @@
 حل اللغز لفرصة الفوز بـ 10 آلاف درهم. https://t.co/NBQE3PzfgZ</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>B- 1.89% &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="K21" t="b">
-        <v>0</v>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>B- 1.89% &lt;a href="/zeynp_qas" title="zeynab kasem"&gt;@zeynp_qas&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>22h</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>Mar 28, 2026 · 6:51 AM UTC</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="n">
-        <v>46109.28541666667</v>
-      </c>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/parulghalout']</t>
-        </is>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>6</v>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>B- 1.89% @Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784668028985459</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 6:52 AM UTC</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="n">
+        <v>46109.28611111111</v>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>['https://x.com/zeynp_qas', 'https://x.com/Salma2232019', 'https://x.com/semeet']</t>
+        </is>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>4</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>B- 1.89% @zeynp_qas @Salma2232019 @semeet 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784853866029145</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
         <is>
           <t>حل اللغز واربح 10,000 درهم.💰
 أم علاوي تعبت من مشاكل السيارة، ومستعدة لسيارة جديدة بفضل قرض السيارات السريع من بنك الإمارات دبي الوطني، من خلال طلب سهل وسريع عبر الإنترنت.
@@ -4023,7 +3852,7 @@
 حل اللغز لفرصة الفوز بـ 10 آلاف درهم. https://t.co/NBQE3PzfgZ</t>
         </is>
       </c>
-      <c r="AA21" t="inlineStr">
+      <c r="AA20" t="inlineStr">
         <is>
           <t>حل اللغز واربح 10,000 درهم.💰
 أم علاوي تعبت من مشاكل السيارة، ومستعدة لسيارة جديدة بفضل قرض السيارات السريع من بنك الإمارات دبي الوطني، من خلال طلب سهل وسريع عبر الإنترنت.
@@ -4032,7 +3861,7 @@
 حل اللغز لفرصة الفوز بـ 10 آلاف درهم. https://t.co/NBQE3PzfgZ</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
+      <c r="AB20" t="inlineStr">
         <is>
           <t>Solve the puzzle and win 10,000 dirhams.💰 Um Alawi is tired of car problems and is ready for a new car thanks to the quick car loan from Emirates NBD, through an easy and fast online application. 
 Follow @EmiratesNBD_ae 
@@ -4040,6 +3869,168 @@
 Solve the puzzle for a chance to win 10,000 dirhams. https://t.co/NBQE3PzfgZ</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AE20" s="2" t="n">
+        <v>46109.45277777778</v>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>28-03-2026</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Solve the puzzle and win 10,000 dirhams.💰 Um Alawi is tired of car problems and is ready for a new car thanks to the quick car loan from Emirates NBD, through an easy and fast online application. • Follow @EmiratesNBD_ae Tag 3 of your friends Solve the puzzle for a chance to win 10,000 dirhams.</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK20" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2037784763122217375</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784763122217375</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE B- 1.89% @semeet @Salma2232019 @SelmaRomola 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>B- 1.89% &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="K21" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 6:52 AM UTC</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="n">
+        <v>46109.28611111111</v>
+      </c>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>['https://x.com/semeet', 'https://x.com/Salma2232019', 'https://x.com/SelmaRomola']</t>
+        </is>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>9</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>B- 1.89% @semeet @Salma2232019 @SelmaRomola 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784763122217375</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE B- 1.89% @semeet @Salma2232019 @SelmaRomola 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE B- 1.89% @semeet @Salma2232019 @SelmaRomola 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE B- 1.89% @semeet @Salma2232019 @SelmaRomola 🌿🇦🇪❤️</t>
+        </is>
+      </c>
       <c r="AC21" t="inlineStr">
         <is>
           <t>Cust</t>
@@ -4047,11 +4038,11 @@
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE21" s="2" t="n">
-        <v>46109.45208333333</v>
+        <v>46109.45277777778</v>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
@@ -4070,7 +4061,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Solve the puzzle and win 10,000 dirhams.💰 Um Alawi is tired of car problems and is ready for a new car thanks to the quick car loan from Emirates NBD, through an easy and fast online application. • Follow @EmiratesNBD_ae Tag 3 of your friends Solve the puzzle for a chance to win 10,000 dirhams.</t>
+          <t>@EmiratesNBD_AE B- 1.89% @semeet @Salma2232019 @SelmaRomola 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -4093,12 +4084,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2037784498885243377</t>
+          <t>2037784668028985459</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784498885243377</t>
+          <t>https://x.com/Sosomostafa729S/status/2037784668028985459</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4123,6 +4114,168 @@
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE B- 1.89% @Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>B- 1.89% &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 6:51 AM UTC</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="n">
+        <v>46109.28541666667</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/parulghalout']</t>
+        </is>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>7</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>B- 1.89% @Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784668028985459</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE B- 1.89% @Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE B- 1.89% @Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>The text appears to be a social media post with mentions and emojis, and it does not contain any translatable content.</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE22" s="2" t="n">
+        <v>46109.45208333333</v>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>28-03-2026</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>The text appears to be a social media post with mentions and emojis, and it does not contain any translatable content.</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK22" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2037784498885243377</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784498885243377</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
         <is>
           <t>حلّ فزورة رمضان واربح 10,000 درهم.
 من توزيع الوجبات، إلى دعم العاملين وقضاء الوقت مع كبار المواطنين، يجمع برنامج واحد كل ذلك تحت مظلًة واحدة.
@@ -4133,69 +4286,69 @@
 3.اكتب إجابتك في التعليقات أدناه https://t.co/aADoQF5a2E</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>Exchanger volunteer program 
 &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; 🌿🇦🇪❤️</t>
         </is>
       </c>
-      <c r="K22" t="b">
-        <v>0</v>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
+      <c r="K23" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>22h</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 6:50 AM UTC</t>
         </is>
       </c>
-      <c r="P22" s="2" t="n">
+      <c r="P23" s="2" t="n">
         <v>46109.28472222222</v>
       </c>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr">
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
         <is>
           <t>['https://x.com/semeet', 'https://x.com/Emy191990', 'https://x.com/ibushra_03']</t>
         </is>
       </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>6</v>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>7</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
         <is>
           <t>Exchanger volunteer program 
 @semeet @Emy191990 @ibushra_03 🌿🇦🇪❤️</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>https://x.com/Sosomostafa729S/status/2037784498885243377</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>حلّ فزورة رمضان واربح 10,000 درهم.
 من توزيع الوجبات، إلى دعم العاملين وقضاء الوقت مع كبار المواطنين، يجمع برنامج واحد كل ذلك تحت مظلًة واحدة.
@@ -4206,7 +4359,7 @@
 3.اكتب إجابتك في التعليقات أدناه https://t.co/aADoQF5a2E</t>
         </is>
       </c>
-      <c r="AA22" t="inlineStr">
+      <c r="AA23" t="inlineStr">
         <is>
           <t>حلّ فزورة رمضان واربح 10,000 درهم.
 من توزيع الوجبات، إلى دعم العاملين وقضاء الوقت مع كبار المواطنين، يجمع برنامج واحد كل ذلك تحت مظلًة واحدة.
@@ -4217,7 +4370,7 @@
 3.اكتب إجابتك في التعليقات أدناه https://t.co/aADoQF5a2E</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
+      <c r="AB23" t="inlineStr">
         <is>
           <t>Solve the Ramadan riddle and win 10,000 dirhams.
 From meal distribution to supporting workers and spending time with senior citizens, one program brings all of this together under one umbrella.
@@ -4228,168 +4381,6 @@
 3. Write your answer in the comments below.</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AE22" s="2" t="n">
-        <v>46109.45138888889</v>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>28-03-2026</t>
-        </is>
-      </c>
-      <c r="AG22" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>From meal distribution to supporting workers and spending time with senior citizens, one program brings all of this together under one umbrella. • Solve the Ramadan riddle and win 10,000 dirhams. • Follow the Emirates NBD account 2.</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AK22" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>EmiratesNBD_AE</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2037784405700419683</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784405700419683</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Sosomostafa729S</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Soha.mostafa77</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @zeynp_qas @SelmaRomola 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Exchanger volunteer program &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/zeynp_qas" title="zeynab kasem"&gt;@zeynp_qas&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="K23" t="b">
-        <v>0</v>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>22h</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>Mar 28, 2026 · 6:50 AM UTC</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="n">
-        <v>46109.28472222222</v>
-      </c>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>['https://x.com/semeet', 'https://x.com/zeynp_qas', 'https://x.com/SelmaRomola']</t>
-        </is>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>6</v>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>Exchanger volunteer program @semeet @zeynp_qas @SelmaRomola 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784405700419683</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @zeynp_qas @SelmaRomola 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @zeynp_qas @SelmaRomola 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>Emirates NBD_AE Exchanger volunteer program</t>
-        </is>
-      </c>
       <c r="AC23" t="inlineStr">
         <is>
           <t>Cust</t>
@@ -4420,7 +4411,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Emirates NBD_AE Exchanger volunteer program</t>
+          <t>From meal distribution to supporting workers and spending time with senior citizens, one program brings all of this together under one umbrella. • Solve the Ramadan riddle and win 10,000 dirhams. • Follow the Emirates NBD account 2.</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -4443,54 +4434,54 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2037784344333275440</t>
+          <t>2037784405700419683</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037784344333275440</t>
+          <t>https://x.com/Sosomostafa729S/status/2037784405700419683</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/Sosomostafa729S</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>Sosomostafa729S</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>Soha.mostafa77</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Before clicking a link, what do you do?
-Stay Safe, Stay Vigilant. #UnitedAgainstFraud
-emiratesnbd.com/en/campaigns…</t>
+          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @zeynp_qas @SelmaRomola 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Before clicking a link, what do you do?
-Stay Safe, Stay Vigilant. &lt;a href="/search?f=tweets&amp;amp;q=%23UnitedAgainstFraud"&gt;#UnitedAgainstFraud&lt;/a&gt;
-&lt;a href="https://www.emiratesnbd.com/en/campaigns/united-against-fraud"&gt;emiratesnbd.com/en/campaigns…&lt;/a&gt;</t>
+          <t>Exchanger volunteer program &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/zeynp_qas" title="zeynab kasem"&gt;@zeynp_qas&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="K24" t="b">
         <v>0</v>
       </c>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr">
         <is>
           <t>22h</t>
@@ -4507,20 +4498,20 @@
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23UnitedAgainstFraud', 'https://www.emiratesnbd.com/en/campaigns/united-against-fraud']</t>
+          <t>['https://x.com/semeet', 'https://x.com/zeynp_qas', 'https://x.com/SelmaRomola']</t>
         </is>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>525</v>
+        <v>7</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
@@ -4529,29 +4520,32 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Before clicking a link, what do you do?
-Stay Safe, Stay Vigilant. #UnitedAgainstFraud
-emiratesnbd.com/en/campaigns…</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
+          <t>Exchanger volunteer program @semeet @zeynp_qas @SelmaRomola 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784405700419683</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @zeynp_qas @SelmaRomola 🌿🇦🇪❤️</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>Before clicking a link, what do you do?
-Stay Safe, Stay Vigilant. #UnitedAgainstFraud
-emiratesnbd.com/en/campaigns…</t>
+          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @zeynp_qas @SelmaRomola 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Before clicking a link, what do you do?
-Stay Safe, Stay Vigilant. #UnitedAgainstFraud</t>
+          <t>Emirates NBD_AE Exchanger volunteer program</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Cust</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -4579,7 +4573,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Stay Safe, Stay Vigilant. • Before clicking a link, what do you do?</t>
+          <t>Emirates NBD_AE Exchanger volunteer program</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -4592,7 +4586,7 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
     </row>
@@ -4602,54 +4596,54 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2037784337337532619</t>
+          <t>2037784344333275440</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784337337532619</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2037784344333275440</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S</t>
+          <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sosomostafa729S</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Soha.mostafa77</t>
+          <t>Emirates NBD</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
+          <t>Before clicking a link, what do you do?
+Stay Safe, Stay Vigilant. #UnitedAgainstFraud
+emiratesnbd.com/en/campaigns…</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; 🌿🇦🇪❤️</t>
+          <t>Before clicking a link, what do you do?
+Stay Safe, Stay Vigilant. &lt;a href="/search?f=tweets&amp;amp;q=%23UnitedAgainstFraud"&gt;#UnitedAgainstFraud&lt;/a&gt;
+&lt;a href="https://www.emiratesnbd.com/en/campaigns/united-against-fraud"&gt;emiratesnbd.com/en/campaigns…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K25" t="b">
         <v>0</v>
       </c>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
           <t>22h</t>
@@ -4666,20 +4660,20 @@
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
         <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/parulghalout']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23UnitedAgainstFraud', 'https://www.emiratesnbd.com/en/campaigns/united-against-fraud']</t>
         </is>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V25" t="n">
-        <v>7</v>
+        <v>532</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -4688,32 +4682,29 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program @Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784337337532619</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
-        </is>
-      </c>
+          <t>Before clicking a link, what do you do?
+Stay Safe, Stay Vigilant. #UnitedAgainstFraud
+emiratesnbd.com/en/campaigns…</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
+          <t>Before clicking a link, what do you do?
+Stay Safe, Stay Vigilant. #UnitedAgainstFraud
+emiratesnbd.com/en/campaigns…</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Emirates NBD_AE Exchanger volunteer program Emy191990 ibushra_03 parulghalout 🌿🇦🇪❤️</t>
+          <t>Before clicking a link, what do you do?
+Stay Safe, Stay Vigilant. #UnitedAgainstFraud</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Cust</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -4741,7 +4732,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Emirates NBD_AE Exchanger volunteer program Emy191990 ibushra_03 parulghalout 🌿🇦🇪❤️</t>
+          <t>Stay Safe, Stay Vigilant. • Before clicking a link, what do you do?</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
@@ -4754,7 +4745,7 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4764,12 +4755,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2037784225022365938</t>
+          <t>2037784337337532619</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784225022365938</t>
+          <t>https://x.com/Sosomostafa729S/status/2037784337337532619</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4795,12 +4786,12 @@
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @parulghalout @Salma2232019 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE Exchanger volunteer program @Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; 🌿🇦🇪❤️</t>
+          <t>Exchanger volunteer program &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="K26" t="b">
@@ -4819,16 +4810,16 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Mar 28, 2026 · 6:49 AM UTC</t>
+          <t>Mar 28, 2026 · 6:50 AM UTC</t>
         </is>
       </c>
       <c r="P26" s="2" t="n">
-        <v>46109.28402777778</v>
+        <v>46109.28472222222</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
         <is>
-          <t>['https://x.com/semeet', 'https://x.com/parulghalout', 'https://x.com/Salma2232019']</t>
+          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/parulghalout']</t>
         </is>
       </c>
       <c r="S26" t="n">
@@ -4841,7 +4832,7 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
@@ -4850,27 +4841,27 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program @semeet @parulghalout @Salma2232019 🌿🇦🇪❤️</t>
+          <t>Exchanger volunteer program @Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784225022365938</t>
+          <t>https://x.com/Sosomostafa729S/status/2037784337337532619</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @parulghalout @Salma2232019 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE Exchanger volunteer program @Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @parulghalout @Salma2232019 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE Exchanger volunteer program @Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Emirates NBD_AE Exchanger volunteer program</t>
+          <t>Emirates NBD AE Exchanger volunteer program</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -4884,7 +4875,7 @@
         </is>
       </c>
       <c r="AE26" s="2" t="n">
-        <v>46109.45069444444</v>
+        <v>46109.45138888889</v>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
@@ -4903,7 +4894,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Emirates NBD_AE Exchanger volunteer program</t>
+          <t>Emirates NBD AE Exchanger volunteer program</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -4926,12 +4917,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2037784141006344295</t>
+          <t>2037784225022365938</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784141006344295</t>
+          <t>https://x.com/Sosomostafa729S/status/2037784225022365938</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4957,12 +4948,12 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program @semeet @Salma2232019 @ibushra_03 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @parulghalout @Salma2232019 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; 🌿🇦🇪❤️</t>
+          <t>Exchanger volunteer program &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="K27" t="b">
@@ -4990,7 +4981,7 @@
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
         <is>
-          <t>['https://x.com/semeet', 'https://x.com/Salma2232019', 'https://x.com/ibushra_03']</t>
+          <t>['https://x.com/semeet', 'https://x.com/parulghalout', 'https://x.com/Salma2232019']</t>
         </is>
       </c>
       <c r="S27" t="n">
@@ -5003,7 +4994,7 @@
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
@@ -5012,19 +5003,27 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program @semeet @Salma2232019 @ibushra_03 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
+          <t>Exchanger volunteer program @semeet @parulghalout @Salma2232019 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784225022365938</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @parulghalout @Salma2232019 🌿🇦🇪❤️</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program @semeet @Salma2232019 @ibushra_03 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE Exchanger volunteer program @semeet @parulghalout @Salma2232019 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program</t>
+          <t>Emirates NBD_AE Exchanger volunteer program</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -5057,7 +5056,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program</t>
+          <t>Emirates NBD_AE Exchanger volunteer program</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -5080,12 +5079,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2037784038774317555</t>
+          <t>2037784141006344295</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784038774317555</t>
+          <t>https://x.com/Sosomostafa729S/status/2037784141006344295</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5111,14 +5110,12 @@
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program 
-@Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
+          <t>Exchanger volunteer program @semeet @Salma2232019 @ibushra_03 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program 
-&lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; 🌿🇦🇪❤️</t>
+          <t>Exchanger volunteer program &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="K28" t="b">
@@ -5146,7 +5143,7 @@
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
         <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/parulghalout']</t>
+          <t>['https://x.com/semeet', 'https://x.com/Salma2232019', 'https://x.com/ibushra_03']</t>
         </is>
       </c>
       <c r="S28" t="n">
@@ -5159,7 +5156,7 @@
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
@@ -5168,30 +5165,19 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program 
-@Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784038774317555</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program 
-@Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
-        </is>
-      </c>
+          <t>Exchanger volunteer program @semeet @Salma2232019 @ibushra_03 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Exchanger volunteer program 
-@Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
+          <t>Exchanger volunteer program @semeet @Salma2232019 @ibushra_03 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Emirates NBD_AE Exchanger volunteer program</t>
+          <t>Exchanger volunteer program</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -5224,7 +5210,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Emirates NBD_AE Exchanger volunteer program</t>
+          <t>Exchanger volunteer program</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -5247,12 +5233,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2037783859769876728</t>
+          <t>2037784038774317555</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783859769876728</t>
+          <t>https://x.com/Sosomostafa729S/status/2037784038774317555</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5278,12 +5264,14 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE FINWELL ( Financial Well-being program) with Emirates NBD @semeet @zeynp_qas @Emy191990 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE Exchanger volunteer program 
+@Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>FINWELL ( Financial Well-being program) with Emirates NBD &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/zeynp_qas" title="zeynab kasem"&gt;@zeynp_qas&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; 🌿🇦🇪❤️</t>
+          <t>Exchanger volunteer program 
+&lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="K29" t="b">
@@ -5302,16 +5290,16 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Mar 28, 2026 · 6:48 AM UTC</t>
+          <t>Mar 28, 2026 · 6:49 AM UTC</t>
         </is>
       </c>
       <c r="P29" s="2" t="n">
-        <v>46109.28333333333</v>
+        <v>46109.28402777778</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
         <is>
-          <t>['https://x.com/semeet', 'https://x.com/zeynp_qas', 'https://x.com/Emy191990']</t>
+          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/parulghalout']</t>
         </is>
       </c>
       <c r="S29" t="n">
@@ -5324,7 +5312,7 @@
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
@@ -5333,27 +5321,30 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>FINWELL ( Financial Well-being program) with Emirates NBD @semeet @zeynp_qas @Emy191990 🌿🇦🇪❤️</t>
+          <t>Exchanger volunteer program 
+@Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783859769876728</t>
+          <t>https://x.com/Sosomostafa729S/status/2037784038774317555</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE FINWELL ( Financial Well-being program) with Emirates NBD @semeet @zeynp_qas @Emy191990 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE Exchanger volunteer program 
+@Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE FINWELL ( Financial Well-being program) with Emirates NBD @semeet @zeynp_qas @Emy191990 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE Exchanger volunteer program 
+@Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>FINWELL (Financial Well-being program) with Emirates NBD</t>
+          <t>Emirates NBD_AE Exchanger volunteer program</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -5363,11 +5354,11 @@
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE29" s="2" t="n">
-        <v>46109.45</v>
+        <v>46109.45069444444</v>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
@@ -5386,7 +5377,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>FINWELL (Financial Well-being program) with Emirates NBD</t>
+          <t>Emirates NBD_AE Exchanger volunteer program</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -5409,12 +5400,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2037783775896313876</t>
+          <t>2037783859769876728</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783775896313876</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783859769876728</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5440,12 +5431,12 @@
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE FINWELL ( Financial Well-being program) with Emirates NBD @SelmaRomola @Emy191990 @parulghalout 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE FINWELL ( Financial Well-being program) with Emirates NBD @semeet @zeynp_qas @Emy191990 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>FINWELL ( Financial Well-being program) with Emirates NBD &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; 🌿🇦🇪❤️</t>
+          <t>FINWELL ( Financial Well-being program) with Emirates NBD &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/zeynp_qas" title="zeynab kasem"&gt;@zeynp_qas&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="K30" t="b">
@@ -5473,7 +5464,7 @@
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
         <is>
-          <t>['https://x.com/SelmaRomola', 'https://x.com/Emy191990', 'https://x.com/parulghalout']</t>
+          <t>['https://x.com/semeet', 'https://x.com/zeynp_qas', 'https://x.com/Emy191990']</t>
         </is>
       </c>
       <c r="S30" t="n">
@@ -5495,22 +5486,22 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>FINWELL ( Financial Well-being program) with Emirates NBD @SelmaRomola @Emy191990 @parulghalout 🌿🇦🇪❤️</t>
+          <t>FINWELL ( Financial Well-being program) with Emirates NBD @semeet @zeynp_qas @Emy191990 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783775896313876</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783859769876728</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE FINWELL ( Financial Well-being program) with Emirates NBD @SelmaRomola @Emy191990 @parulghalout 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE FINWELL ( Financial Well-being program) with Emirates NBD @semeet @zeynp_qas @Emy191990 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE FINWELL ( Financial Well-being program) with Emirates NBD @SelmaRomola @Emy191990 @parulghalout 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE FINWELL ( Financial Well-being program) with Emirates NBD @semeet @zeynp_qas @Emy191990 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -5571,12 +5562,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2037783673144230370</t>
+          <t>2037783775896313876</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783673144230370</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783775896313876</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5602,14 +5593,12 @@
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE FINWELL ( Financial Well-being program) with Emirates NBD 
-@Emy191990 @ibushra_03 @SelmaRomola 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE FINWELL ( Financial Well-being program) with Emirates NBD @SelmaRomola @Emy191990 @parulghalout 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>FINWELL ( Financial Well-being program) with Emirates NBD 
-&lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; 🌿🇦🇪❤️</t>
+          <t>FINWELL ( Financial Well-being program) with Emirates NBD &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="K31" t="b">
@@ -5628,16 +5617,16 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Mar 28, 2026 · 6:47 AM UTC</t>
+          <t>Mar 28, 2026 · 6:48 AM UTC</t>
         </is>
       </c>
       <c r="P31" s="2" t="n">
-        <v>46109.28263888889</v>
+        <v>46109.28333333333</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
         <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/SelmaRomola']</t>
+          <t>['https://x.com/SelmaRomola', 'https://x.com/Emy191990', 'https://x.com/parulghalout']</t>
         </is>
       </c>
       <c r="S31" t="n">
@@ -5650,7 +5639,7 @@
         <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
@@ -5659,25 +5648,22 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>FINWELL ( Financial Well-being program) with Emirates NBD 
-@Emy191990 @ibushra_03 @SelmaRomola 🌿🇦🇪❤️</t>
+          <t>FINWELL ( Financial Well-being program) with Emirates NBD @SelmaRomola @Emy191990 @parulghalout 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783673144230370</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783775896313876</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE FINWELL ( Financial Well-being program) with Emirates NBD 
-@Emy191990 @ibushra_03 @SelmaRomola 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE FINWELL ( Financial Well-being program) with Emirates NBD @SelmaRomola @Emy191990 @parulghalout 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE FINWELL ( Financial Well-being program) with Emirates NBD 
-@Emy191990 @ibushra_03 @SelmaRomola 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE FINWELL ( Financial Well-being program) with Emirates NBD @SelmaRomola @Emy191990 @parulghalout 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -5696,7 +5682,7 @@
         </is>
       </c>
       <c r="AE31" s="2" t="n">
-        <v>46109.44930555556</v>
+        <v>46109.45</v>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
@@ -5738,12 +5724,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2037783477979091314</t>
+          <t>2037783673144230370</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783477979091314</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783673144230370</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5769,12 +5755,14 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Through ENBD X Mobile Banking's App @parulghalout @semeet @Emy191990 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE FINWELL ( Financial Well-being program) with Emirates NBD 
+@Emy191990 @ibushra_03 @SelmaRomola 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Through ENBD X Mobile Banking&amp;#39;s App &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; 🌿🇦🇪❤️</t>
+          <t>FINWELL ( Financial Well-being program) with Emirates NBD 
+&lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="K32" t="b">
@@ -5793,16 +5781,16 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Mar 28, 2026 · 6:46 AM UTC</t>
+          <t>Mar 28, 2026 · 6:47 AM UTC</t>
         </is>
       </c>
       <c r="P32" s="2" t="n">
-        <v>46109.28194444445</v>
+        <v>46109.28263888889</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
         <is>
-          <t>['https://x.com/parulghalout', 'https://x.com/semeet', 'https://x.com/Emy191990']</t>
+          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/SelmaRomola']</t>
         </is>
       </c>
       <c r="S32" t="n">
@@ -5815,7 +5803,7 @@
         <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W32" t="inlineStr">
         <is>
@@ -5824,19 +5812,30 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Through ENBD X Mobile Banking's App @parulghalout @semeet @Emy191990 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
+          <t>FINWELL ( Financial Well-being program) with Emirates NBD 
+@Emy191990 @ibushra_03 @SelmaRomola 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037783673144230370</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE FINWELL ( Financial Well-being program) with Emirates NBD 
+@Emy191990 @ibushra_03 @SelmaRomola 🌿🇦🇪❤️</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>Through ENBD X Mobile Banking's App @parulghalout @semeet @Emy191990 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE FINWELL ( Financial Well-being program) with Emirates NBD 
+@Emy191990 @ibushra_03 @SelmaRomola 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>Through ENBD X Mobile Banking's App</t>
+          <t>FINWELL (Financial Well-being program) with Emirates NBD</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -5846,11 +5845,11 @@
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE32" s="2" t="n">
-        <v>46109.44861111111</v>
+        <v>46109.44930555556</v>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
@@ -5869,7 +5868,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Through ENBD X Mobile Banking's App</t>
+          <t>FINWELL (Financial Well-being program) with Emirates NBD</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -5892,12 +5891,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2037783402758508685</t>
+          <t>2037783477979091314</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783402758508685</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783477979091314</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5923,12 +5922,12 @@
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @zeynp_qas @SelmaRomola @Salma2232019 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @parulghalout @semeet @Emy191990 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Through ENBD X Mobile Banking&amp;#39;s App &lt;a href="/zeynp_qas" title="zeynab kasem"&gt;@zeynp_qas&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; 🌿🇦🇪❤️</t>
+          <t>Through ENBD X Mobile Banking&amp;#39;s App &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="K33" t="b">
@@ -5956,7 +5955,7 @@
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
         <is>
-          <t>['https://x.com/zeynp_qas', 'https://x.com/SelmaRomola', 'https://x.com/Salma2232019']</t>
+          <t>['https://x.com/parulghalout', 'https://x.com/semeet', 'https://x.com/Emy191990']</t>
         </is>
       </c>
       <c r="S33" t="n">
@@ -5969,7 +5968,7 @@
         <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
@@ -5978,27 +5977,27 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Through ENBD X Mobile Banking's App @zeynp_qas @SelmaRomola @Salma2232019 🌿🇦🇪❤️</t>
+          <t>Through ENBD X Mobile Banking's App @parulghalout @semeet @Emy191990 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783402758508685</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783477979091314</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @zeynp_qas @SelmaRomola @Salma2232019 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @parulghalout @semeet @Emy191990 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @zeynp_qas @SelmaRomola @Salma2232019 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @parulghalout @semeet @Emy191990 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Through ENBD X Mobile Banking's App</t>
+          <t>Through Emirates NBD X Mobile Banking's App</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -6031,7 +6030,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Through ENBD X Mobile Banking's App</t>
+          <t>Through Emirates NBD X Mobile Banking's App</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
@@ -6054,12 +6053,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2037783335389540775</t>
+          <t>2037783402758508685</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783335389540775</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783402758508685</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -6085,12 +6084,12 @@
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @Emy191990 @parulghalout @ibushra_03 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @zeynp_qas @SelmaRomola @Salma2232019 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Through ENBD X Mobile Banking&amp;#39;s App &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; 🌿🇦🇪❤️</t>
+          <t>Through ENBD X Mobile Banking&amp;#39;s App &lt;a href="/zeynp_qas" title="zeynab kasem"&gt;@zeynp_qas&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="K34" t="b">
@@ -6118,7 +6117,7 @@
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
         <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/parulghalout', 'https://x.com/ibushra_03']</t>
+          <t>['https://x.com/zeynp_qas', 'https://x.com/SelmaRomola', 'https://x.com/Salma2232019']</t>
         </is>
       </c>
       <c r="S34" t="n">
@@ -6131,7 +6130,7 @@
         <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
@@ -6140,27 +6139,27 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Through ENBD X Mobile Banking's App @Emy191990 @parulghalout @ibushra_03 🌿🇦🇪❤️</t>
+          <t>Through ENBD X Mobile Banking's App @zeynp_qas @SelmaRomola @Salma2232019 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783335389540775</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783402758508685</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @Emy191990 @parulghalout @ibushra_03 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @zeynp_qas @SelmaRomola @Salma2232019 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @Emy191990 @parulghalout @ibushra_03 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @zeynp_qas @SelmaRomola @Salma2232019 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Through Emirates NBD X Mobile Banking's App</t>
+          <t>Through ENBD X Mobile Banking's App</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -6193,7 +6192,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Through Emirates NBD X Mobile Banking's App</t>
+          <t>Through ENBD X Mobile Banking's App</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
@@ -6216,12 +6215,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2037783125854679453</t>
+          <t>2037783335389540775</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783125854679453</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783335389540775</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -6247,12 +6246,12 @@
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @parulghalout @Salma2232019 @semeet 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @Emy191990 @parulghalout @ibushra_03 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Through ENBD X Mobile Banking&amp;#39;s App &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; 🌿🇦🇪❤️</t>
+          <t>Through ENBD X Mobile Banking&amp;#39;s App &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="K35" t="b">
@@ -6271,16 +6270,16 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Mar 28, 2026 · 6:45 AM UTC</t>
+          <t>Mar 28, 2026 · 6:46 AM UTC</t>
         </is>
       </c>
       <c r="P35" s="2" t="n">
-        <v>46109.28125</v>
+        <v>46109.28194444445</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
         <is>
-          <t>['https://x.com/parulghalout', 'https://x.com/Salma2232019', 'https://x.com/semeet']</t>
+          <t>['https://x.com/Emy191990', 'https://x.com/parulghalout', 'https://x.com/ibushra_03']</t>
         </is>
       </c>
       <c r="S35" t="n">
@@ -6293,7 +6292,7 @@
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
@@ -6302,22 +6301,22 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Through ENBD X Mobile Banking's App @parulghalout @Salma2232019 @semeet 🌿🇦🇪❤️</t>
+          <t>Through ENBD X Mobile Banking's App @Emy191990 @parulghalout @ibushra_03 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783125854679453</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783335389540775</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @parulghalout @Salma2232019 @semeet 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @Emy191990 @parulghalout @ibushra_03 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @parulghalout @Salma2232019 @semeet 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @Emy191990 @parulghalout @ibushra_03 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
@@ -6336,7 +6335,7 @@
         </is>
       </c>
       <c r="AE35" s="2" t="n">
-        <v>46109.44791666666</v>
+        <v>46109.44861111111</v>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
@@ -6378,12 +6377,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2037783049065390446</t>
+          <t>2037783125854679453</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783049065390446</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783125854679453</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6409,14 +6408,12 @@
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App 
-@Emy191990 @ibushra_03 @semeet 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @parulghalout @Salma2232019 @semeet 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Through ENBD X Mobile Banking&amp;#39;s App 
-&lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; 🌿🇦🇪❤️</t>
+          <t>Through ENBD X Mobile Banking&amp;#39;s App &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="K36" t="b">
@@ -6444,7 +6441,7 @@
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
         <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/semeet']</t>
+          <t>['https://x.com/parulghalout', 'https://x.com/Salma2232019', 'https://x.com/semeet']</t>
         </is>
       </c>
       <c r="S36" t="n">
@@ -6457,7 +6454,7 @@
         <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
@@ -6466,25 +6463,22 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Through ENBD X Mobile Banking's App 
-@Emy191990 @ibushra_03 @semeet 🌿🇦🇪❤️</t>
+          <t>Through ENBD X Mobile Banking's App @parulghalout @Salma2232019 @semeet 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783049065390446</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783125854679453</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App 
-@Emy191990 @ibushra_03 @semeet 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @parulghalout @Salma2232019 @semeet 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App 
-@Emy191990 @ibushra_03 @semeet 🌿🇦🇪❤️</t>
+          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App @parulghalout @Salma2232019 @semeet 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
@@ -6545,44 +6539,45 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2037730056920088898</t>
+          <t>2037783049065390446</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://x.com/wil3020/status/2037730056920088898</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783049065390446</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://x.com/wil3020</t>
+          <t>https://x.com/Sosomostafa729S</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>wil3020</t>
+          <t>Sosomostafa729S</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>wiil</t>
+          <t>Soha.mostafa77</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1939900695018106882/lxZGZx9Y_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Stay safe and bank with ease with ENBD X and businessONLINE 
-Visit https://t.co/0Z1tddYvqD https://t.co/l7XrKjfHOu</t>
+          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App 
+@Emy191990 @ibushra_03 @semeet 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>The UAE is no longer safe Continuous and comprehensive bombing of the UAE now</t>
+          <t>Through ENBD X Mobile Banking&amp;#39;s App 
+&lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="K37" t="b">
@@ -6596,19 +6591,23 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Mar 28</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Mar 28, 2026 · 3:14 AM UTC</t>
+          <t>Mar 28, 2026 · 6:45 AM UTC</t>
         </is>
       </c>
       <c r="P37" s="2" t="n">
-        <v>46109.13472222222</v>
+        <v>46109.28125</v>
       </c>
       <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/semeet']</t>
+        </is>
+      </c>
       <c r="S37" t="n">
         <v>0</v>
       </c>
@@ -6619,7 +6618,7 @@
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
@@ -6628,29 +6627,30 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>The UAE is no longer safe Continuous and comprehensive bombing of the UAE now</t>
+          <t>Through ENBD X Mobile Banking's App 
+@Emy191990 @ibushra_03 @semeet 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>https://x.com/wil3020/status/2037730056920088898</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783049065390446</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>Stay safe and bank with ease with ENBD X and businessONLINE 
-Visit https://t.co/0Z1tddYvqD https://t.co/l7XrKjfHOu</t>
+          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App 
+@Emy191990 @ibushra_03 @semeet 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>Stay safe and bank with ease with ENBD X and businessONLINE 
-Visit https://t.co/0Z1tddYvqD https://t.co/l7XrKjfHOu</t>
+          <t>@EmiratesNBD_AE Through ENBD X Mobile Banking's App 
+@Emy191990 @ibushra_03 @semeet 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>Stay safe and bank with ease with ENBD X and businessONLINE.</t>
+          <t>Through ENBD X Mobile Banking's App</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -6660,11 +6660,11 @@
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE37" s="2" t="n">
-        <v>46109.30138888889</v>
+        <v>46109.44791666666</v>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
@@ -6683,7 +6683,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Stay safe and bank with ease with ENBD X and businessONLINE.</t>
+          <t>Through ENBD X Mobile Banking's App</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -6706,43 +6706,44 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2037785071189671937</t>
+          <t>2037730056920088898</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://x.com/ZaibKang/status/2037785071189671937</t>
+          <t>https://x.com/wil3020/status/2037730056920088898</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://x.com/ZaibKang</t>
+          <t>https://x.com/wil3020</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ZaibKang</t>
+          <t>wil3020</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Jahan Zaib Akbar Kang</t>
+          <t>wiil</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2028644994790436864/h-Avrj3s_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1939900695018106882/lxZGZx9Y_bigger.jpg</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE @EmiratesNBD_AE I applied for liv X account 3 days ago still not received any response please Check and respond as soon as possible https://t.co/LXfxy0AGqW</t>
+          <t>Stay safe and bank with ease with ENBD X and businessONLINE 
+Visit https://t.co/0Z1tddYvqD https://t.co/l7XrKjfHOu</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; I applied for liv X account 3 days ago still not received any response please Check and respond as soon as possible</t>
+          <t>The UAE is no longer safe Continuous and comprehensive bombing of the UAE now</t>
         </is>
       </c>
       <c r="K38" t="b">
@@ -6756,23 +6757,19 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>Mar 28</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Mar 28, 2026 · 6:53 AM UTC</t>
+          <t>Mar 28, 2026 · 3:14 AM UTC</t>
         </is>
       </c>
       <c r="P38" s="2" t="n">
-        <v>46109.28680555556</v>
+        <v>46109.13472222222</v>
       </c>
       <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>['https://x.com/EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="R38" t="inlineStr"/>
       <c r="S38" t="n">
         <v>0</v>
       </c>
@@ -6783,7 +6780,7 @@
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
@@ -6792,27 +6789,29 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE I applied for liv X account 3 days ago still not received any response please Check and respond as soon as possible</t>
+          <t>The UAE is no longer safe Continuous and comprehensive bombing of the UAE now</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>https://x.com/ZaibKang/status/2037785071189671937</t>
+          <t>https://x.com/wil3020/status/2037730056920088898</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE @EmiratesNBD_AE I applied for liv X account 3 days ago still not received any response please Check and respond as soon as possible https://t.co/LXfxy0AGqW</t>
+          <t>Stay safe and bank with ease with ENBD X and businessONLINE 
+Visit https://t.co/0Z1tddYvqD https://t.co/l7XrKjfHOu</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE @EmiratesNBD_AE I applied for liv X account 3 days ago still not received any response please Check and respond as soon as possible https://t.co/LXfxy0AGqW</t>
+          <t>Stay safe and bank with ease with ENBD X and businessONLINE 
+Visit https://t.co/0Z1tddYvqD https://t.co/l7XrKjfHOu</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>I applied for a liv X account 3 days ago and still have not received any response. Please check and respond as soon as possible.</t>
+          <t>Stay safe and bank with ease with ENBD X and businessONLINE.</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -6822,11 +6821,11 @@
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE38" s="2" t="n">
-        <v>46109.45347222222</v>
+        <v>46109.30138888889</v>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
@@ -6845,7 +6844,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>I applied for a liv X account 3 days ago and still have not received any response. • Please check and respond as soon as possible.</t>
+          <t>Stay safe and bank with ease with ENBD X and businessONLINE.</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
@@ -6868,62 +6867,66 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2037865010320539854</t>
+          <t>2037785071189671937</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://x.com/rated_sm/status/2037865010320539854</t>
+          <t>https://x.com/ZaibKang/status/2037785071189671937</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://x.com/rated_sm</t>
+          <t>https://x.com/ZaibKang</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>rated_sm</t>
+          <t>ZaibKang</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>rated_sm</t>
+          <t>Jahan Zaib Akbar Kang</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1870693863452524544/xTAmP9KA_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2028644994790436864/h-Avrj3s_bigger.jpg</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE My phone is broken and is pending repair with Apple. I need to make a payment and I logged into the website using OTP, but when attempting payment, its still asking for Smart Pass confirmation and no OTP option. Same when attempting to contact Whatsapp Support.</t>
+          <t>@EmiratesNBD_AE @EmiratesNBD_AE I applied for liv X account 3 days ago still not received any response please Check and respond as soon as possible https://t.co/LXfxy0AGqW</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; My phone is broken and is pending repair with Apple. I need to make a payment and I logged into the website using OTP, but when attempting payment, its still asking for Smart Pass confirmation and no OTP option. Same when attempting to contact Whatsapp Support.</t>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; I applied for liv X account 3 days ago still not received any response please Check and respond as soon as possible</t>
         </is>
       </c>
       <c r="K39" t="b">
         <v>0</v>
       </c>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Mar 28, 2026 · 12:10 PM UTC</t>
+          <t>Mar 28, 2026 · 6:53 AM UTC</t>
         </is>
       </c>
       <c r="P39" s="2" t="n">
-        <v>46109.50694444445</v>
+        <v>46109.28680555556</v>
       </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
@@ -6932,7 +6935,7 @@
         </is>
       </c>
       <c r="S39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
         <v>0</v>
@@ -6941,7 +6944,7 @@
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
@@ -6950,19 +6953,27 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE My phone is broken and is pending repair with Apple. I need to make a payment and I logged into the website using OTP, but when attempting payment, its still asking for Smart Pass confirmation and no OTP option. Same when attempting to contact Whatsapp Support.</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr"/>
-      <c r="Z39" t="inlineStr"/>
+          <t>@EmiratesNBD_AE I applied for liv X account 3 days ago still not received any response please Check and respond as soon as possible</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>https://x.com/ZaibKang/status/2037785071189671937</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE @EmiratesNBD_AE I applied for liv X account 3 days ago still not received any response please Check and respond as soon as possible https://t.co/LXfxy0AGqW</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE My phone is broken and is pending repair with Apple. I need to make a payment and I logged into the website using OTP, but when attempting payment, its still asking for Smart Pass confirmation and no OTP option. Same when attempting to contact Whatsapp Support.</t>
+          <t>@EmiratesNBD_AE @EmiratesNBD_AE I applied for liv X account 3 days ago still not received any response please Check and respond as soon as possible https://t.co/LXfxy0AGqW</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>My phone is broken and is pending repair with Apple. I need to make a payment and I logged into the website using OTP, but when attempting payment, it's still asking for Smart Pass confirmation and no OTP option. The same happens when attempting to contact WhatsApp Support.</t>
+          <t>I applied for a liv X account 3 days ago and still have not received any response. Please check and respond as soon as possible.</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -6976,7 +6987,7 @@
         </is>
       </c>
       <c r="AE39" s="2" t="n">
-        <v>46109.67361111111</v>
+        <v>46109.45347222222</v>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
@@ -6995,7 +7006,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>I need to make a payment and I logged into the website using OTP, but when attempting payment, it's still asking for Smart Pass confirmation and no OTP option. • The same happens when attempting to contact WhatsApp Support. • My phone is broken and is pending repair with Apple.</t>
+          <t>I applied for a liv X account 3 days ago and still have not received any response. • Please check and respond as soon as possible.</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
@@ -7007,6 +7018,156 @@
         <v>2026</v>
       </c>
       <c r="AL39" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2037865010320539854</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://x.com/rated_sm/status/2037865010320539854</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://x.com/rated_sm</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>rated_sm</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>rated_sm</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1870693863452524544/xTAmP9KA_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE My phone is broken and is pending repair with Apple. I need to make a payment and I logged into the website using OTP, but when attempting payment, its still asking for Smart Pass confirmation and no OTP option. Same when attempting to contact Whatsapp Support.</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; My phone is broken and is pending repair with Apple. I need to make a payment and I logged into the website using OTP, but when attempting payment, its still asking for Smart Pass confirmation and no OTP option. Same when attempting to contact Whatsapp Support.</t>
+        </is>
+      </c>
+      <c r="K40" t="b">
+        <v>0</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 12:10 PM UTC</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="n">
+        <v>46109.50694444445</v>
+      </c>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="S40" t="n">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>19</v>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE My phone is broken and is pending repair with Apple. I need to make a payment and I logged into the website using OTP, but when attempting payment, its still asking for Smart Pass confirmation and no OTP option. Same when attempting to contact Whatsapp Support.</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE My phone is broken and is pending repair with Apple. I need to make a payment and I logged into the website using OTP, but when attempting payment, its still asking for Smart Pass confirmation and no OTP option. Same when attempting to contact Whatsapp Support.</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>My phone is broken and is pending repair with Apple. I need to make a payment and I logged into the website using OTP, but when attempting payment, it's still asking for Smart Pass confirmation and no OTP option. The same happens when attempting to contact WhatsApp Support.</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AE40" s="2" t="n">
+        <v>46109.67361111111</v>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>28-03-2026</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>I need to make a payment and I logged into the website using OTP, but when attempting payment, it's still asking for Smart Pass confirmation and no OTP option. • The same happens when attempting to contact WhatsApp Support. • My phone is broken and is pending repair with Apple.</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK40" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL40" t="inlineStr">
         <is>
           <t>None</t>
         </is>

--- a/check2.xlsx
+++ b/check2.xlsx
@@ -769,15 +769,15 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>My last experience in meeting the entry requirement for airport lounges with VISA cards 🛋️ 💳
-I made an online purchase worth 364 Qatari Riyals 🇶🇦 
-(equivalent to 375 Saudi Riyals) 💰🇸🇦 
+I made an online purchase worth 364 Qatari riyals 🇶🇦 
+(equivalent to 375 Saudi riyals) 💰🇸🇦 
 and the activation took exactly 5 days from the date of the transaction.
 This activated my entry for only 85 days ‼️ 
 💡 Of course, to continue enjoying free entry, you must repeat this process 4 times a year (every 90 days) 🗓️ 
 *The card used is a Visa Infinite 💳 
 which provides unlimited access for the cardholder + two guests for free.
 Note that most Infinite cards only offer free entry for one guest. 
-🎤 Share your latest experience with us 
+🎤 Share with us your latest experience 
 • Was it with Visa or Mastercard? 
 • How long did it take for activation?</t>
         </is>
@@ -812,7 +812,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Note that most Infinite cards only offer free entry for one guest. • 🎤 Share your latest experience with us • Was it with Visa or Mastercard? • • How long did it take for activation?</t>
+          <t>Note that most Infinite cards only offer free entry for one guest. • 🎤 Share with us your latest experience • Was it with Visa or Mastercard? • • How long did it take for activation?</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE6" s="2" t="n">
@@ -1513,7 +1513,7 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Emirates NBD, a leading banking group in the #MiddleEast, #NorthAfrica and #Türkiye (MENAT) region, has announced that International Securities, the #UAE based brokerage firm, is now live on Emirates NBD Pay using Visa’s Account Funding Transaction (AFT) model, https://t.co/58cmlm0ryB</t>
+          <t>#FintechNewsUAE #EmiratesNBDPay #InternationalSecurities #Visa #AFT #Trading #DigitalPayments #UAE #MiddleEast</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1572,17 +1572,17 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>Emirates NBD, a leading banking group in the #MiddleEast, #NorthAfrica and #Türkiye (MENAT) region, has announced that International Securities, the #UAE based brokerage firm, is now live on Emirates NBD Pay using Visa’s Account Funding Transaction (AFT) model, https://t.co/58cmlm0ryB</t>
+          <t>#FintechNewsUAE #EmiratesNBDPay #InternationalSecurities #Visa #AFT #Trading #DigitalPayments #UAE #MiddleEast</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Emirates NBD, a leading banking group in the #MiddleEast, #NorthAfrica and #Türkiye (MENAT) region, has announced that International Securities, the #UAE based brokerage firm, is now live on Emirates NBD Pay using Visa’s Account Funding Transaction (AFT) model, https://t.co/58cmlm0ryB</t>
+          <t>#FintechNewsUAE #EmiratesNBDPay #InternationalSecurities #Visa #AFT #Trading #DigitalPayments #UAE #MiddleEast</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Emirates NBD, a leading banking group in the Middle East, North Africa, and Türkiye (MENAT) region, has announced that International Securities, the UAE-based brokerage firm, is now live on Emirates NBD Pay using Visa’s Account Funding Transaction (AFT) model.</t>
+          <t>Fintech News UAE Emirates NBD Pay International Securities Visa AFT Trading Digital Payments UAE Middle East</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Emirates NBD, a leading banking group in the Middle East, North Africa, and Türkiye (MENAT) region, has announced that I…</t>
+          <t>Fintech News UAE Emirates NBD Pay International Securities Visa AFT Trading Digital Payments UAE Middle East</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>The Abu Dhabi Securities Exchange gives you access to the key sectors of the economy. Explore the opportunities and start trading with confidence!</t>
+          <t>Abu Dhabi Securities Exchange gives you access to the key sectors of the economy. Explore the opportunities and start trading with confidence!</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>The Abu Dhabi Securities Exchange gives you access to the key sectors of the economy. • Explore the opportunities and start trading with confidence!</t>
+          <t>Abu Dhabi Securities Exchange gives you access to the key sectors of the economy. • Explore the opportunities and start trading with confidence!</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -2004,8 +2004,7 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>خصم 22% على طلباتك من نون مع بطاقات بنك الإمارات دبي الوطني الائتمانية باستخدام الكود ENBD 💳 
-للتفاصيل:https://t.co/RZ3m0A3tFV https://t.co/XRtMkvS0M6</t>
+          <t>شوف الخاص</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -2059,27 +2058,16 @@
           <t>شوف الخاص</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>https://x.com/coool_o7/status/2038663903719121402</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>خصم 22% على طلباتك من نون مع بطاقات بنك الإمارات دبي الوطني الائتمانية باستخدام الكود ENBD 💳 
-للتفاصيل:https://t.co/RZ3m0A3tFV https://t.co/XRtMkvS0M6</t>
-        </is>
-      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>خصم 22% على طلباتك من نون مع بطاقات بنك الإمارات دبي الوطني الائتمانية باستخدام الكود ENBD 💳 
-للتفاصيل:https://t.co/RZ3m0A3tFV https://t.co/XRtMkvS0M6</t>
+          <t>شوف الخاص</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>22% discount on your orders from Noon with Emirates NBD credit cards using the code ENBD 💳 
-For details: https://t.co/RZ3m0A3tFV https://t.co/XRtMkvS0M6</t>
+          <t>Check the private message.</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -2089,7 +2077,7 @@
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE10" s="2" t="n">
@@ -2112,7 +2100,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>22% discount on your orders from Noon with Emirates NBD credit cards using the code ENBD 💳 For details: https://t.co/RZ3m0A3tFV https://t.co/XRtMkvS0M6</t>
+          <t>Check the private message.</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -2244,8 +2232,8 @@
       <c r="AB11" t="inlineStr">
         <is>
           <t>Discover the foreign currency debit cards from Emirates NBD!
-Planning to travel or study abroad? The foreign currency debit card is with you wherever you go to meet your various needs.
-Put the world in your hands and issue your foreign currency debit card now!</t>
+Planning to travel or study abroad? The foreign currency debit card is with you wherever you go to meet your different needs.
+Keep the world in your hands and issue the foreign currency debit card now!</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2278,7 +2266,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Put the world in your hands and issue your foreign currency debit card now! • The foreign currency debit card is with you wherever you go to meet your various needs. • Discover the foreign currency debit cards from Emirates NBD!</t>
+          <t>Keep the world in your hands and issue the foreign currency debit card now! • The foreign currency debit card is with you wherever you go to meet your different needs. • Discover the foreign currency debit cards from Emirates NBD!</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -2332,9 +2320,7 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Ignore “too good to be true” offers. They usually are.
-Stay Safe, Stay Vigilant. #UnitedAgainstFraud 
-https://t.co/YpRWtBZrhq</t>
+          <t>Our team will check it and reply as soon as possible</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2388,29 +2374,16 @@
           <t>Our team will check it and reply as soon as possible</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2038601841227726900</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Ignore “too good to be true” offers. They usually are.
-Stay Safe, Stay Vigilant. #UnitedAgainstFraud 
-https://t.co/YpRWtBZrhq</t>
-        </is>
-      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Ignore “too good to be true” offers. They usually are.
-Stay Safe, Stay Vigilant. #UnitedAgainstFraud 
-https://t.co/YpRWtBZrhq</t>
+          <t>Our team will check it and reply as soon as possible</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Ignore "too good to be true" offers. They usually are.
-Stay Safe, Stay Vigilant. #UnitedAgainstFraud</t>
+          <t>Our team will check it and respond as soon as possible.</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2443,7 +2416,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Stay Safe, Stay Vigilant. • Ignore "too good to be true" offers.</t>
+          <t>Our team will check it and respond as soon as possible.</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2497,7 +2470,9 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Hello please respond, jus sent the email</t>
+          <t>Ignore “too good to be true” offers. They usually are.
+Stay Safe, Stay Vigilant. #UnitedAgainstFraud 
+https://t.co/YpRWtBZrhq</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2551,16 +2526,29 @@
           <t>Hello please respond, jus sent the email</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>https://x.com/gaurav_2/status/2038600901817246006</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>Ignore “too good to be true” offers. They usually are.
+Stay Safe, Stay Vigilant. #UnitedAgainstFraud 
+https://t.co/YpRWtBZrhq</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Hello please respond, jus sent the email</t>
+          <t>Ignore “too good to be true” offers. They usually are.
+Stay Safe, Stay Vigilant. #UnitedAgainstFraud 
+https://t.co/YpRWtBZrhq</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Hello, please respond, I just sent the email.</t>
+          <t>Ignore "too good to be true" offers. They usually are.
+Stay Safe, Stay Vigilant. #UnitedAgainstFraud</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2593,7 +2581,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Hello, please respond, I just sent the email.</t>
+          <t>Stay Safe, Stay Vigilant. • Ignore "too good to be true" offers.</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2648,7 +2636,7 @@
       <c r="I14" t="inlineStr">
         <is>
           <t>Emirates NBD launches instant funding service for UAE trading accounts, letting investors top up funds in near real-time and act quickly on market opportunities.  #UAE #EmiratesNBD #investing #FinanceGoals 
-https://t.co/7AhPrbT8Uj</t>
+khaleejbusinessinsight.com/e…</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2704,26 +2692,17 @@
 khaleejbusinessinsight.com/e…</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>https://x.com/khaleejinsight/status/2038600152705818745</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr">
         <is>
           <t>Emirates NBD launches instant funding service for UAE trading accounts, letting investors top up funds in near real-time and act quickly on market opportunities.  #UAE #EmiratesNBD #investing #FinanceGoals 
-https://t.co/7AhPrbT8Uj</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Emirates NBD launches instant funding service for UAE trading accounts, letting investors top up funds in near real-time and act quickly on market opportunities.  #UAE #EmiratesNBD #investing #FinanceGoals 
-https://t.co/7AhPrbT8Uj</t>
+khaleejbusinessinsight.com/e…</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Emirates NBD launches an instant funding service for UAE trading accounts, allowing investors to top up funds in near real-time and act quickly on market opportunities.</t>
+          <t>Emirates NBD launches instant funding service for UAE trading accounts, allowing investors to top up funds in near real-time and act quickly on market opportunities.</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2756,7 +2735,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Emirates NBD launches an instant funding service for UAE trading accounts, allowing investors to top up funds in near real-time and act quickly on market opportunities.</t>
+          <t>Emirates NBD launches instant funding service for UAE trading accounts, allowing investors to top up funds in near real-time and act quickly on market opportunities.</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2963,7 +2942,7 @@
           <t>Emirates NBD Pay Broker Entegrasyonu Başladı!
 Orta Doğu’da ödeme ve yatırım altyapısının kesiştiği yeni bir adım atıldı. Emirates NBD, Visa’nın AFT (Account Funding Transaction) modeli üzerinden International Securities’i Emirates NBD Pay platformuna entegre ederek broker hesaplarına kartla fonlama dönemini başlattı. 
 Söz konusu entegrasyon, yatırım işlemlerinde hız ve erişim açısından yeni bir standardın kapısını aralıyor.
-https://t.co/tViGD9cjVx</t>
+fintekwins.com/emirates-nbd-…</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -3023,25 +3002,14 @@
 fintekwins.com/emirates-nbd-…</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>https://x.com/fintekwins/status/2038585144240394241</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr">
         <is>
           <t>Emirates NBD Pay Broker Entegrasyonu Başladı!
 Orta Doğu’da ödeme ve yatırım altyapısının kesiştiği yeni bir adım atıldı. Emirates NBD, Visa’nın AFT (Account Funding Transaction) modeli üzerinden International Securities’i Emirates NBD Pay platformuna entegre ederek broker hesaplarına kartla fonlama dönemini başlattı. 
 Söz konusu entegrasyon, yatırım işlemlerinde hız ve erişim açısından yeni bir standardın kapısını aralıyor.
-https://t.co/tViGD9cjVx</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Emirates NBD Pay Broker Entegrasyonu Başladı!
-Orta Doğu’da ödeme ve yatırım altyapısının kesiştiği yeni bir adım atıldı. Emirates NBD, Visa’nın AFT (Account Funding Transaction) modeli üzerinden International Securities’i Emirates NBD Pay platformuna entegre ederek broker hesaplarına kartla fonlama dönemini başlattı. 
-Söz konusu entegrasyon, yatırım işlemlerinde hız ve erişim açısından yeni bir standardın kapısını aralıyor.
-https://t.co/tViGD9cjVx</t>
+fintekwins.com/emirates-nbd-…</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -3104,43 +3072,43 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2038576820270870686</t>
+          <t>2038573849885950406</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2038576820270870686</t>
+          <t>https://x.com/gaurav_2/status/2038573849885950406</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/gaurav_2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>gaurav_2</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>Gaurav Srivastava</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1244581966831185922/lGeLbO4o_bigger.jpg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Thanks for sharing, our team will check and update you accordingly</t>
+          <t>Done sent!</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Thanks for sharing, our team will check and update you accordingly</t>
+          <t>Done sent!</t>
         </is>
       </c>
       <c r="K17" t="b">
@@ -3149,7 +3117,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>['gaurav_2']</t>
+          <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -3159,11 +3127,11 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Mar 30, 2026 · 11:19 AM UTC</t>
+          <t>Mar 30, 2026 · 11:07 AM UTC</t>
         </is>
       </c>
       <c r="P17" s="2" t="n">
-        <v>46111.47152777778</v>
+        <v>46111.46319444444</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
@@ -3186,19 +3154,19 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Thanks for sharing, our team will check and update you accordingly</t>
+          <t>Done sent!</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Thanks for sharing, our team will check and update you accordingly</t>
+          <t>Done sent!</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Thank you for sharing; our team will review it and update you accordingly.</t>
+          <t>Done sent!</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -3212,7 +3180,7 @@
         </is>
       </c>
       <c r="AE17" s="2" t="n">
-        <v>46111.63819444444</v>
+        <v>46111.62986111111</v>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
@@ -3231,7 +3199,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Thank you for sharing; our team will review it and update you accordingly.</t>
+          <t>Done sent!</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -3244,7 +3212,7 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>gaurav_2</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
     </row>
@@ -3254,12 +3222,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2038573849885950406</t>
+          <t>2038571587944001693</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://x.com/gaurav_2/status/2038573849885950406</t>
+          <t>https://x.com/gaurav_2/status/2038571587944001693</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3285,12 +3253,12 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Done sent!</t>
+          <t>Where do i send the email?</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Done sent!</t>
+          <t>Where do i send the email?</t>
         </is>
       </c>
       <c r="K18" t="b">
@@ -3304,16 +3272,16 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Mar 30, 2026 · 11:07 AM UTC</t>
+          <t>Mar 30, 2026 · 10:58 AM UTC</t>
         </is>
       </c>
       <c r="P18" s="2" t="n">
-        <v>46111.46319444444</v>
+        <v>46111.45694444444</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
@@ -3327,7 +3295,7 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -3336,19 +3304,19 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Done sent!</t>
+          <t>Where do i send the email?</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Done sent!</t>
+          <t>Where do i send the email?</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Done sent!</t>
+          <t>Where do I send the email?</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -3362,7 +3330,7 @@
         </is>
       </c>
       <c r="AE18" s="2" t="n">
-        <v>46111.62986111111</v>
+        <v>46111.62361111111</v>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
@@ -3381,7 +3349,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Done sent!</t>
+          <t>Where do I send the email?</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -3404,54 +3372,54 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2038571587944001693</t>
+          <t>2038566897197736039</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://x.com/gaurav_2/status/2038571587944001693</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2038566897197736039</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://x.com/gaurav_2</t>
+          <t>https://x.com/EmiratesNBD_KSA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>gaurav_2</t>
+          <t>EmiratesNBD_KSA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gaurav Srivastava</t>
+          <t>EmiratesNBD KSA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1244581966831185922/lGeLbO4o_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1762427762424385536/iUFFKIOK_bigger.jpg</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Where do i send the email?</t>
+          <t>جمّع أميالك، من مشترياتك المحلية والدولية ✈️
+مع بطاقة رحالة الائتمانية من #بنك_الإمارات_دبي_الوطني 💙
+للتفاصيل:https://t.co/Lj22BZ7E5k https://t.co/VwLKvAqAZ5</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Where do i send the email?</t>
+          <t>استثمر في الذهب بأسهل طريقة 👌🏼
+افتح حساب الذهب، واشتري وبيع الذهب بكل سهولة من &lt;a href="/search?f=tweets&amp;amp;q=%23بنك_الإمارات_دبي_الوطني"&gt;#بنك_الإمارات_دبي_الوطني&lt;/a&gt; 💙 
+للتفاصيل:&lt;a href="http://ms.spr.ly/6014Qxuwg"&gt;ms.spr.ly/6014Qxuwg&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K19" t="b">
         <v>0</v>
       </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>17h</t>
@@ -3459,25 +3427,29 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Mar 30, 2026 · 10:58 AM UTC</t>
+          <t>Mar 30, 2026 · 10:39 AM UTC</t>
         </is>
       </c>
       <c r="P19" s="2" t="n">
-        <v>46111.45694444444</v>
+        <v>46111.44375</v>
       </c>
       <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23بنك_الإمارات_دبي_الوطني', 'http://ms.spr.ly/6014Qxuwg']</t>
+        </is>
+      </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V19" t="n">
-        <v>7</v>
+        <v>524</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -3486,33 +3458,47 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Where do i send the email?</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
+          <t>استثمر في الذهب بأسهل طريقة 👌🏼
+افتح حساب الذهب، واشتري وبيع الذهب بكل سهولة من #بنك_الإمارات_دبي_الوطني 💙 
+للتفاصيل:ms.spr.ly/6014Qxuwg</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_KSA/status/2038566897197736039</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>جمّع أميالك، من مشترياتك المحلية والدولية ✈️
+مع بطاقة رحالة الائتمانية من #بنك_الإمارات_دبي_الوطني 💙
+للتفاصيل:https://t.co/Lj22BZ7E5k https://t.co/VwLKvAqAZ5</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Where do i send the email?</t>
+          <t>جمّع أميالك، من مشترياتك المحلية والدولية ✈️
+مع بطاقة رحالة الائتمانية من #بنك_الإمارات_دبي_الوطني 💙
+للتفاصيل:https://t.co/Lj22BZ7E5k https://t.co/VwLKvAqAZ5</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Where do I send the email?</t>
+          <t>Gather your miles from your local and international purchases ✈️ with the Traveler credit card from #Emirates_NBD 💙 For details: https://t.co/Lj22BZ7E5k https://t.co/VwLKvAqAZ5</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Cust</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE19" s="2" t="n">
-        <v>46111.62361111111</v>
+        <v>46111.61041666667</v>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
@@ -3531,7 +3517,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Where do I send the email?</t>
+          <t>Gather your miles from your local and international purchases ✈️ with the Traveler credit card from #Emirates_NBD 💙 For details: https://t.co/Lj22BZ7E5k https://t.co/VwLKvAqAZ5</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -3544,7 +3530,7 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3554,54 +3540,54 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2038566897197736039</t>
+          <t>2038563627083460663</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2038566897197736039</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2038563627083460663</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA</t>
+          <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>EmiratesNBD_KSA</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>EmiratesNBD KSA</t>
+          <t>Emirates NBD</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427762424385536/iUFFKIOK_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>جمّع أميالك، من مشترياتك المحلية والدولية ✈️
-مع بطاقة رحالة الائتمانية من #بنك_الإمارات_دبي_الوطني 💙
-للتفاصيل:https://t.co/Lj22BZ7E5k https://t.co/VwLKvAqAZ5</t>
+          <t>. Please mention in the email subject social media case #990664. Thanks- Zubair</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>استثمر في الذهب بأسهل طريقة 👌🏼
-افتح حساب الذهب، واشتري وبيع الذهب بكل سهولة من &lt;a href="/search?f=tweets&amp;amp;q=%23بنك_الإمارات_دبي_الوطني"&gt;#بنك_الإمارات_دبي_الوطني&lt;/a&gt; 💙 
-للتفاصيل:&lt;a href="http://ms.spr.ly/6014Qxuwg"&gt;ms.spr.ly/6014Qxuwg&lt;/a&gt;</t>
+          <t>. Please mention in the email subject social media case #990664. Thanks- Zubair</t>
         </is>
       </c>
       <c r="K20" t="b">
         <v>0</v>
       </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>['gaurav_2']</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
           <t>17h</t>
@@ -3609,29 +3595,25 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Mar 30, 2026 · 10:39 AM UTC</t>
+          <t>Mar 30, 2026 · 10:26 AM UTC</t>
         </is>
       </c>
       <c r="P20" s="2" t="n">
-        <v>46111.44375</v>
+        <v>46111.43472222222</v>
       </c>
       <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23بنك_الإمارات_دبي_الوطني', 'http://ms.spr.ly/6014Qxuwg']</t>
-        </is>
-      </c>
+      <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>524</v>
+        <v>12</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
@@ -3640,47 +3622,33 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>استثمر في الذهب بأسهل طريقة 👌🏼
-افتح حساب الذهب، واشتري وبيع الذهب بكل سهولة من #بنك_الإمارات_دبي_الوطني 💙 
-للتفاصيل:ms.spr.ly/6014Qxuwg</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2038566897197736039</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>جمّع أميالك، من مشترياتك المحلية والدولية ✈️
-مع بطاقة رحالة الائتمانية من #بنك_الإمارات_دبي_الوطني 💙
-للتفاصيل:https://t.co/Lj22BZ7E5k https://t.co/VwLKvAqAZ5</t>
-        </is>
-      </c>
+          <t>. Please mention in the email subject social media case #990664. Thanks- Zubair</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>جمّع أميالك، من مشترياتك المحلية والدولية ✈️
-مع بطاقة رحالة الائتمانية من #بنك_الإمارات_دبي_الوطني 💙
-للتفاصيل:https://t.co/Lj22BZ7E5k https://t.co/VwLKvAqAZ5</t>
+          <t>. Please mention in the email subject social media case #990664. Thanks- Zubair</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Gather your miles from your local and international purchases ✈️ with the Traveler credit card from #Emirates_NBD 💙 For details: https://t.co/Lj22BZ7E5k https://t.co/VwLKvAqAZ5</t>
+          <t>Please mention in the email subject social media case #990664. Thanks, Zubair.</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Cust</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE20" s="2" t="n">
-        <v>46111.61041666667</v>
+        <v>46111.60138888889</v>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
@@ -3699,7 +3667,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Gather your miles from your local and international purchases ✈️ with the Traveler credit card from #Emirates_NBD 💙 For details: https://t.co/Lj22BZ7E5k https://t.co/VwLKvAqAZ5</t>
+          <t>Please mention in the email subject social media case #990664.</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3712,7 +3680,7 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>gaurav_2</t>
         </is>
       </c>
     </row>
@@ -3722,43 +3690,44 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2038563627083460663</t>
+          <t>2038559393231339820</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2038563627083460663</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2038559393231339820</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/EmiratesNBD_KSA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>EmiratesNBD_KSA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>EmiratesNBD KSA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1762427762424385536/iUFFKIOK_bigger.jpg</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>. Please mention in the email subject social media case #990664. Thanks- Zubair</t>
+          <t>خصم 22% على طلباتك من نون مع بطاقات بنك الإمارات دبي الوطني الائتمانية باستخدام الكود ENBD 💳 
+للتفاصيل:https://t.co/RZ3m0A3tFV https://t.co/XRtMkvS0M6</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>. Please mention in the email subject social media case #990664. Thanks- Zubair</t>
+          <t>يُرجى إرسال التفاصيل الخاصه بشكواك  ورقم هاتفك إلى رسائل الخاص حتي نتمكن من مساعدتك بشكل أفضل</t>
         </is>
       </c>
       <c r="K21" t="b">
@@ -3767,7 +3736,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>['gaurav_2']</t>
+          <t>['coool_o7']</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3777,11 +3746,11 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Mar 30, 2026 · 10:26 AM UTC</t>
+          <t>Mar 30, 2026 · 10:10 AM UTC</t>
         </is>
       </c>
       <c r="P21" s="2" t="n">
-        <v>46111.43472222222</v>
+        <v>46111.42361111111</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
@@ -3795,7 +3764,7 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
@@ -3804,19 +3773,30 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>. Please mention in the email subject social media case #990664. Thanks- Zubair</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
+          <t>يُرجى إرسال التفاصيل الخاصه بشكواك  ورقم هاتفك إلى رسائل الخاص حتي نتمكن من مساعدتك بشكل أفضل</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_KSA/status/2038559393231339820</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>خصم 22% على طلباتك من نون مع بطاقات بنك الإمارات دبي الوطني الائتمانية باستخدام الكود ENBD 💳 
+للتفاصيل:https://t.co/RZ3m0A3tFV https://t.co/XRtMkvS0M6</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>. Please mention in the email subject social media case #990664. Thanks- Zubair</t>
+          <t>خصم 22% على طلباتك من نون مع بطاقات بنك الإمارات دبي الوطني الائتمانية باستخدام الكود ENBD 💳 
+للتفاصيل:https://t.co/RZ3m0A3tFV https://t.co/XRtMkvS0M6</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>Please mention in the email subject social media case #990664. Thanks, Zubair.</t>
+          <t>22% discount on your orders from Noon with Emirates NBD credit cards using the code ENBD 💳 
+For details: https://t.co/RZ3m0A3tFV https://t.co/XRtMkvS0M6</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3826,11 +3806,11 @@
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE21" s="2" t="n">
-        <v>46111.60138888889</v>
+        <v>46111.59027777778</v>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
@@ -3849,7 +3829,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Please mention in the email subject social media case #990664.</t>
+          <t>22% discount on your orders from Noon with Emirates NBD credit cards using the code ENBD 💳 For details: https://t.co/RZ3m0A3tFV https://t.co/XRtMkvS0M6</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -3862,7 +3842,7 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>gaurav_2</t>
+          <t>coool_o7</t>
         </is>
       </c>
     </row>
@@ -3903,7 +3883,7 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA الرد ع الخاص</t>
+          <t>شكراً لتواصلكم معنا، لقد أجبنا عليكم عبر الرسائل الخاصة. شكراً.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3957,24 +3937,16 @@
           <t>شكراً لتواصلكم معنا، لقد أجبنا عليكم عبر الرسائل الخاصة. شكراً.</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2038558482941542427</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_KSA الرد ع الخاص</t>
-        </is>
-      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA الرد ع الخاص</t>
+          <t>شكراً لتواصلكم معنا، لقد أجبنا عليكم عبر الرسائل الخاصة. شكراً.</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA reply in private</t>
+          <t>Thank you for contacting us, we have responded to you via private messages. Thank you.</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -4007,7 +3979,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA reply in private</t>
+          <t>Thank you for contacting us, we have responded to you via private messages.</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
@@ -4273,8 +4245,16 @@
           <t>@EmiratesNBD_KSA الرد ع الخاص</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>https://x.com/abode_14088/status/2038551131236831660</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA الرد ع الخاص</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>@EmiratesNBD_KSA الرد ع الخاص</t>
@@ -5504,17 +5484,16 @@
       <c r="AB31" t="inlineStr">
         <is>
           <t>Um Khammas ran out of cash before the month ended.
-A simple rule can help her stay on track:
-50% for needs
-30% for wants
+A simple rule can help her manage her money wisely:
+50% for basic needs
+30% for luxuries
 20% for savings
-A smart plan that helps you spend, save, and stay in control.
-This is one of the many tips that the bank’s program has in store.
+A smart plan that enables you to spend, save, and maintain control over your budget. This is one of the many tips offered by the bank's program.
 Watch the episode and tell us the name of the program?
 To participate:
 - Follow Emirates NBD
-- Tag 3 friends
-- Drop your answer below for a chance to win AED 10,000</t>
+- Tag 3 of your friends
+- Write your answer in the comments below for a chance to win AED 10,000.</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -5547,7 +5526,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>A simple rule can help her stay on track: 50% for needs 30% for wants 20% for savings A smart plan that helps you spend, save, and stay in control. • To participate: - Follow Emirates NBD - Tag 3 friends - Drop your answer below for a chance to win AED 10,000 • This is one of the many tips that the bank’s program has in store.</t>
+          <t>A simple rule can help her manage her money wisely: 50% for basic needs 30% for luxuries 20% for savings A smart plan that enables you to spend, save, and maintain control over your budget. • To participate: - Follow Emirates NBD - Tag 3 of your friends - Write your answer in the comments below for a chance to win AED 10,000. • This is one of the many tips offered by the bank's program.</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -5687,7 +5666,7 @@
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE32" s="2" t="n">
@@ -6031,7 +6010,7 @@
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE34" s="2" t="n">
@@ -6375,7 +6354,7 @@
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE36" s="2" t="n">
@@ -6895,7 +6874,7 @@
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE39" s="2" t="n">
@@ -7417,7 +7396,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>@JarirBookstore What's wrong with you? Why aren't you responding here, in private, or anywhere?</t>
+          <t>@JarirBookstore What's wrong with you? You don't respond here, privately, or anywhere else.</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -7450,7 +7429,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Why aren't you responding here, in private, or anywhere? • @JarirBookstore What's wrong with you?</t>
+          <t>You don't respond here, privately, or anywhere else. • @JarirBookstore What's wrong with you?</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
@@ -7763,7 +7742,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>Through ENBD X Mobile Banking's App</t>
+          <t>Through Emirates NBD X Mobile Banking's App</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -7796,7 +7775,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Through ENBD X Mobile Banking's App</t>
+          <t>Through Emirates NBD X Mobile Banking's App</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
@@ -8173,168 +8152,6 @@
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Exchanger volunteering program @mnsadiq84 @khushbuag88 @Ajay142951</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>Exchanger volunteering program &lt;a href="/mnsadiq84" title="naveed sadiq"&gt;@mnsadiq84&lt;/a&gt; &lt;a href="/khushbuag88" title="Khushbu Agarwal"&gt;@khushbuag88&lt;/a&gt; &lt;a href="/Ajay142951" title="Ajay14295"&gt;@Ajay142951&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K47" t="b">
-        <v>0</v>
-      </c>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>22h</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>Mar 30, 2026 · 5:23 AM UTC</t>
-        </is>
-      </c>
-      <c r="P47" s="2" t="n">
-        <v>46111.22430555556</v>
-      </c>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>['https://x.com/mnsadiq84', 'https://x.com/khushbuag88', 'https://x.com/Ajay142951']</t>
-        </is>
-      </c>
-      <c r="S47" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" t="n">
-        <v>0</v>
-      </c>
-      <c r="U47" t="n">
-        <v>0</v>
-      </c>
-      <c r="V47" t="n">
-        <v>4</v>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>Exchanger volunteering program @mnsadiq84 @khushbuag88 @Ajay142951</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>https://x.com/parulghalout/status/2038487250900865345</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Exchanger volunteering program @mnsadiq84 @khushbuag88 @Ajay142951</t>
-        </is>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Exchanger volunteering program @mnsadiq84 @khushbuag88 @Ajay142951</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>Emirates NBD AE Exchanger volunteering program</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD47" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AE47" s="2" t="n">
-        <v>46111.39097222222</v>
-      </c>
-      <c r="AF47" t="inlineStr">
-        <is>
-          <t>30-03-2026</t>
-        </is>
-      </c>
-      <c r="AG47" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>Emirates NBD AE Exchanger volunteering program</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AK47" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL47" t="inlineStr">
-        <is>
-          <t>EmiratesNBD_AE</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="n">
-        <v>46</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2038487154515669376</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>https://x.com/parulghalout/status/2038487154515669376</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>https://x.com/parulghalout</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>parulghalout</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>parul ghalout</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/589412760515031040/ehckyrV3_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr">
         <is>
           <t>حلّ فزورة رمضان واربح 10,000 درهم.
 من توزيع الوجبات، إلى دعم العاملين وقضاء الوقت مع كبار المواطنين، يجمع برنامج واحد كل ذلك تحت مظلًة واحدة.
@@ -8345,69 +8162,67 @@
 3.اكتب إجابتك في التعليقات أدناه https://t.co/aADoQF5a2E</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Exchanger volunteering program  
-&lt;a href="/shifajasminekt" title="Shifa Jasmine"&gt;@shifajasminekt&lt;/a&gt; &lt;a href="/jamila_sherwala" title="Jamila Sherwala"&gt;@jamila_sherwala&lt;/a&gt; &lt;a href="/sar_a1999ali" title="sar_a1999ali"&gt;@sar_a1999ali&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K48" t="b">
-        <v>0</v>
-      </c>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Exchanger volunteering program &lt;a href="/mnsadiq84" title="naveed sadiq"&gt;@mnsadiq84&lt;/a&gt; &lt;a href="/khushbuag88" title="Khushbu Agarwal"&gt;@khushbuag88&lt;/a&gt; &lt;a href="/Ajay142951" title="Ajay14295"&gt;@Ajay142951&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K47" t="b">
+        <v>0</v>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>22h</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>Mar 30, 2026 · 5:23 AM UTC</t>
         </is>
       </c>
-      <c r="P48" s="2" t="n">
+      <c r="P47" s="2" t="n">
         <v>46111.22430555556</v>
       </c>
-      <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>['https://x.com/shifajasminekt', 'https://x.com/jamila_sherwala', 'https://x.com/sar_a1999ali']</t>
-        </is>
-      </c>
-      <c r="S48" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" t="n">
-        <v>0</v>
-      </c>
-      <c r="U48" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" t="n">
-        <v>1</v>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>Exchanger volunteering program  
-@shifajasminekt @jamila_sherwala @sar_a1999ali</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>https://x.com/parulghalout/status/2038487154515669376</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>['https://x.com/mnsadiq84', 'https://x.com/khushbuag88', 'https://x.com/Ajay142951']</t>
+        </is>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" t="n">
+        <v>4</v>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Exchanger volunteering program @mnsadiq84 @khushbuag88 @Ajay142951</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>https://x.com/parulghalout/status/2038487250900865345</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
         <is>
           <t>حلّ فزورة رمضان واربح 10,000 درهم.
 من توزيع الوجبات، إلى دعم العاملين وقضاء الوقت مع كبار المواطنين، يجمع برنامج واحد كل ذلك تحت مظلًة واحدة.
@@ -8418,7 +8233,7 @@
 3.اكتب إجابتك في التعليقات أدناه https://t.co/aADoQF5a2E</t>
         </is>
       </c>
-      <c r="AA48" t="inlineStr">
+      <c r="AA47" t="inlineStr">
         <is>
           <t>حلّ فزورة رمضان واربح 10,000 درهم.
 من توزيع الوجبات، إلى دعم العاملين وقضاء الوقت مع كبار المواطنين، يجمع برنامج واحد كل ذلك تحت مظلًة واحدة.
@@ -8429,7 +8244,7 @@
 3.اكتب إجابتك في التعليقات أدناه https://t.co/aADoQF5a2E</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
+      <c r="AB47" t="inlineStr">
         <is>
           <t>Solve the Ramadan riddle and win 10,000 dirhams.
 From meal distribution to supporting workers and spending time with senior citizens, one program brings all of this together under one umbrella.
@@ -8440,6 +8255,173 @@
 3. Write your answer in the comments below.</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE47" s="2" t="n">
+        <v>46111.39097222222</v>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>30-03-2026</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>From meal distribution to supporting workers and spending time with senior citizens, one program brings all of this together under one umbrella. • Solve the Ramadan riddle and win 10,000 dirhams. • Follow the Emirates NBD account 2.</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK47" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL47" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2038487154515669376</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://x.com/parulghalout/status/2038487154515669376</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://x.com/parulghalout</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>parulghalout</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>parul ghalout</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/589412760515031040/ehckyrV3_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Exchanger volunteering program  
+@shifajasminekt @jamila_sherwala @sar_a1999ali</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Exchanger volunteering program  
+&lt;a href="/shifajasminekt" title="Shifa Jasmine"&gt;@shifajasminekt&lt;/a&gt; &lt;a href="/jamila_sherwala" title="Jamila Sherwala"&gt;@jamila_sherwala&lt;/a&gt; &lt;a href="/sar_a1999ali" title="sar_a1999ali"&gt;@sar_a1999ali&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K48" t="b">
+        <v>0</v>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Mar 30, 2026 · 5:23 AM UTC</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="n">
+        <v>46111.22430555556</v>
+      </c>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>['https://x.com/shifajasminekt', 'https://x.com/jamila_sherwala', 'https://x.com/sar_a1999ali']</t>
+        </is>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1</v>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Exchanger volunteering program  
+@shifajasminekt @jamila_sherwala @sar_a1999ali</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>https://x.com/parulghalout/status/2038487154515669376</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Exchanger volunteering program  
+@shifajasminekt @jamila_sherwala @sar_a1999ali</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Exchanger volunteering program  
+@shifajasminekt @jamila_sherwala @sar_a1999ali</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>Emirates NBD_AE Exchanger volunteering program</t>
+        </is>
+      </c>
       <c r="AC48" t="inlineStr">
         <is>
           <t>Cust</t>
@@ -8470,7 +8452,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>From meal distribution to supporting workers and spending time with senior citizens, one program brings all of this together under one umbrella. • Solve the Ramadan riddle and win 10,000 dirhams. • Follow the Emirates NBD account 2.</t>
+          <t>Emirates NBD_AE Exchanger volunteering program</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
@@ -8681,6 +8663,67 @@
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
+        <is>
+          <t>🤔Are you interested in the biliary branching pattern of the caudate lobe in PHCC?
+📄Here is a report on its assessment using ENBD-CT cholangiography from Japan 🇯🇵
+👉 Read the article:
+https://t.co/kw1J18gV7F
+👉 And join the webinar on April 20 as well!
+https://t.co/kyfumdJ1tQ</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>🤔Are you interested in the biliary branching pattern of the caudate lobe in PHCC?
+📄Here is a report on its assessment using ENBD-CT cholangiography from Japan 🇯🇵
+👉 Read the article:
+&lt;a href="https://onlinelibrary.wiley.com/doi/abs/10.1002/jhbp.12073"&gt;onlinelibrary.wiley.com/doi/…&lt;/a&gt;
+👉 And join the webinar on April 20 as well!
+&lt;a href="https://www.jshbps.jp/modules/en/index.php?content_id=64"&gt;jshbps.jp/modules/en/index.p…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K50" t="b">
+        <v>0</v>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Mar 30</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Mar 30, 2026 · 2:10 AM UTC</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="n">
+        <v>46111.09027777778</v>
+      </c>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>['https://onlinelibrary.wiley.com/doi/abs/10.1002/jhbp.12073', 'https://www.jshbps.jp/modules/en/index.php?content_id=64']</t>
+        </is>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>8</v>
+      </c>
+      <c r="V50" t="n">
+        <v>756</v>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
         <is>
           <t>🤔Are you interested in the biliary branching pattern of the caudate lobe in PHCC?
 📄Here is a report on its assessment using ENBD-CT cholangiography from Japan 🇯🇵
@@ -8690,82 +8733,34 @@
 jshbps.jp/modules/en/index.p…</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>https://x.com/JSHBPS/status/2038438591886761989</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
         <is>
           <t>🤔Are you interested in the biliary branching pattern of the caudate lobe in PHCC?
 📄Here is a report on its assessment using ENBD-CT cholangiography from Japan 🇯🇵
 👉 Read the article:
-&lt;a href="https://onlinelibrary.wiley.com/doi/abs/10.1002/jhbp.12073"&gt;onlinelibrary.wiley.com/doi/…&lt;/a&gt;
+https://t.co/kw1J18gV7F
 👉 And join the webinar on April 20 as well!
-&lt;a href="https://www.jshbps.jp/modules/en/index.php?content_id=64"&gt;jshbps.jp/modules/en/index.p…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K50" t="b">
-        <v>0</v>
-      </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>Mar 30</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>Mar 30, 2026 · 2:10 AM UTC</t>
-        </is>
-      </c>
-      <c r="P50" s="2" t="n">
-        <v>46111.09027777778</v>
-      </c>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t>['https://onlinelibrary.wiley.com/doi/abs/10.1002/jhbp.12073', 'https://www.jshbps.jp/modules/en/index.php?content_id=64']</t>
-        </is>
-      </c>
-      <c r="S50" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" t="n">
-        <v>3</v>
-      </c>
-      <c r="U50" t="n">
-        <v>8</v>
-      </c>
-      <c r="V50" t="n">
-        <v>756</v>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr">
+https://t.co/kyfumdJ1tQ</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
         <is>
           <t>🤔Are you interested in the biliary branching pattern of the caudate lobe in PHCC?
 📄Here is a report on its assessment using ENBD-CT cholangiography from Japan 🇯🇵
 👉 Read the article:
-onlinelibrary.wiley.com/doi/…
+https://t.co/kw1J18gV7F
 👉 And join the webinar on April 20 as well!
-jshbps.jp/modules/en/index.p…</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr"/>
-      <c r="Z50" t="inlineStr"/>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>🤔Are you interested in the biliary branching pattern of the caudate lobe in PHCC?
-📄Here is a report on its assessment using ENBD-CT cholangiography from Japan 🇯🇵
-👉 Read the article:
-onlinelibrary.wiley.com/doi/…
-👉 And join the webinar on April 20 as well!
-jshbps.jp/modules/en/index.p…</t>
+https://t.co/kyfumdJ1tQ</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>Are you interested in the biliary branching pattern of the caudate lobe in PHCC? Here is a report on its assessment using ENBD-CT cholangiography from Japan. Read the article: onlinelibrary.wiley.com/doi/… And join the webinar on April 20 as well! jshbps.jp/modules/en/index.p…</t>
+          <t>Are you interested in the biliary branching pattern of the caudate lobe in PHCC? Here is a report on its assessment using ENBD-CT cholangiography from Japan. Read the article: https://t.co/kw1J18gV7F And join the webinar on April 20 as well! https://t.co/kyfumdJ1tQ</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -8798,7 +8793,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Read the article: onlinelibrary.wiley.com/doi/… And join the webinar on April 20 as well! • Are you interested in the biliary branching pattern of the caudate lobe in PHCC? • Here is a report on its assessment using ENBD-CT cholangiography from Japan.</t>
+          <t>Read the article: https://t.co/kw1J18gV7F And join the webinar on April 20 as well! • Are you interested in the biliary branching pattern of the caudate lobe in PHCC? • Here is a report on its assessment using ENBD-CT cholangiography from Japan.</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
@@ -9398,7 +9393,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>I have a Visa card and I want to cancel it. I contacted customer service by phone, but I couldn't find any specific option for Visa cards. Also, my account in the app is not working and I can't log in to check the status of the card or manage it. I was forced to pay an amount for the card without being notified of the payment due date.</t>
+          <t>I have a Visa card and I would like to cancel it. I contacted customer service by phone, but I couldn't find any specific option for Visa cards. Also, my account in the app is not working and I can't log in to check the status of the card or manage it. I was forced to pay an amount for the card without being notified of the payment due date.</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -9866,9 +9861,12 @@
 Tried your WhatsApp and call support which are just time killers and below par intelligence</t>
         </is>
       </c>
-      <c r="Y57" t="inlineStr"/>
-      <c r="Z57" t="inlineStr"/>
-      <c r="AA57" t="inlineStr">
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>https://x.com/MNadaver/status/2038702486702461222</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
         <is>
           <t>@emiratesislamic , your cards services still seem to have impact.
 Bills not getting generated 
@@ -9877,9 +9875,18 @@
 Tried your WhatsApp and call support which are just time killers and below par intelligence</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>@emiratesislamic , your cards services still seem to have impact.
+Bills not getting generated 
+Not been able to switch between cash back and travel 
+Rewards option not working
+Tried your WhatsApp and call support which are just time killers and below par intelligence</t>
+        </is>
+      </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>Your card services still seem to have issues.
+          <t>@emiratesislamic, your card services still seem to have issues.
 Bills are not being generated.
 I haven't been able to switch between cash back and travel.
 The rewards option is not working.
@@ -9916,7 +9923,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>I tried your WhatsApp and call support, which are just time-wasters and below standard. • I haven't been able to switch between cash back and travel. • Your card services still seem to have issues.</t>
+          <t>I tried your WhatsApp and call support, which are just time-wasters and below standard. • @emiratesislamic, your card services still seem to have issues. • I haven't been able to switch between cash back and travel.</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
@@ -10176,7 +10183,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>I am writing this post after exhausting all attempts to communicate without any significant results with Emirates Islamic Bank @emiratesislamic, in a state of astonishment and frustration at what I am facing.
+          <t>I am writing this post after exhausting all attempts to communicate with Emirates Islamic Bank @emiratesislamic without any significant results, in a state of astonishment and frustration at what I am facing.
 I filed an official complaint regarding the complete freezing of my bank accounts, despite a clear court ruling, and the court kindly issued a clear interpretation of the ruling to eliminate any ambiguity.
 Nevertheless, the bank continues to take actions that do not align with the wording of the ruling or its interpretation.
 🔹 For clarification:
@@ -10196,13 +10203,13 @@
 My mental state.
 My social stability.
 My financial and living obligations.
-Moreover, the absence of a clear entity to take responsibility and the lack of serious handling complicates the situation further.
-I demand the senior management of Emirates Islamic Bank to:
+Moreover, the absence of a clear entity to take responsibility and the lack of serious resolution complicate the situation further.
+I demand that the senior management of Emirates Islamic Bank:
 ✔️ Adhere to the court ruling and its interpretation.
 ✔️ Cease any actions inconsistent with it.
 ✔️ Lift the unjustified freeze.
 ✔️ Provide an official clarification of the situation and address it urgently.
-I hope that this matter will be treated with the necessary seriousness, as the situation can no longer tolerate further delays. 
+I hope this matter is treated with the necessary seriousness, as the situation can no longer tolerate further delays. 
 #Complaint #Escalation #EmiratesIslamicBank #Justice #Rights #UAE #emiratesislamic</t>
         </is>
       </c>
@@ -10236,7 +10243,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>🔹 For clarification: The court ruling does not include any clause for freezing accounts or seizing funds. • I demand the senior management of Emirates Islamic Bank to: ✔️ Adhere to the court ruling and its interpretation. • When inquiring, the response is: "This is the bank's right." This raises a legitimate question: ❗ If the funds are subject to freezing, how can deductions be made from them?</t>
+          <t>🔹 For clarification: The court ruling does not include any clause for freezing accounts or seizing funds. • I demand that the senior management of Emirates Islamic Bank: ✔️ Adhere to the court ruling and its interpretation. • When inquiring, the response is: "This is the bank's right." This raises a legitimate question: ❗ If the funds are subject to freezing, how can deductions be made from them?</t>
         </is>
       </c>
       <c r="AJ58" t="inlineStr">
@@ -10758,7 +10765,7 @@
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Dear Emirates NBD, I have been locked out of my business banking apps and retrieval is so painful. My RM- Sujith has left ENBD and I am not informed about the same. I was expecting smooth service but unfortunately not</t>
+          <t>@gaurav_2 Hi Gaurav, we’re sorry to hear that you’re having unpleasant experience. We will be glad to assist you and have it fixed. Kindly send us the details at social@EmiratesNBD.com from your registered email address so we can review and assist.</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -10812,16 +10819,24 @@
           <t>Dear Emirates NBD, I have been locked out of my business banking apps and retrieval is so painful. My RM- Sujith has left ENBD and I am not informed about the same. I was expecting smooth service but unfortunately not</t>
         </is>
       </c>
-      <c r="Y62" t="inlineStr"/>
-      <c r="Z62" t="inlineStr"/>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>https://x.com/gaurav_2/status/2038562189414740028</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>@gaurav_2 Hi Gaurav, we’re sorry to hear that you’re having unpleasant experience. We will be glad to assist you and have it fixed. Kindly send us the details at social@EmiratesNBD.com from your registered email address so we can review and assist.</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>Dear Emirates NBD, I have been locked out of my business banking apps and retrieval is so painful. My RM- Sujith has left ENBD and I am not informed about the same. I was expecting smooth service but unfortunately not</t>
+          <t>@gaurav_2 Hi Gaurav, we’re sorry to hear that you’re having unpleasant experience. We will be glad to assist you and have it fixed. Kindly send us the details at social@EmiratesNBD.com from your registered email address so we can review and assist.</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>Dear Emirates NBD, I have been locked out of my business banking apps and the retrieval process is very difficult. My relationship manager, Sujith, has left ENBD and I was not informed about it. I was expecting smooth service, but unfortunately, that has not been the case.</t>
+          <t>Hi Gaurav, we’re sorry to hear that you’re having an unpleasant experience. We will be glad to assist you and have it fixed. Kindly send us the details at social@EmiratesNBD.com from your registered email address so we can review and assist.</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
@@ -10854,7 +10869,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>Dear Emirates NBD, I have been locked out of my business banking apps and the retrieval process is very difficult. • My relationship manager, Sujith, has left ENBD and I was not informed about it. • I was expecting smooth service, but unfortunately, that has not been the case.</t>
+          <t>Kindly send us the details at social@EmiratesNBD.com from your registered email address so we can review and assist. • Hi Gaurav, we’re sorry to hear that you’re having an unpleasant experience. • We will be glad to assist you and have it fixed.</t>
         </is>
       </c>
       <c r="AJ62" t="inlineStr">
@@ -10979,7 +10994,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank made a debt purchase for me from Al-Awwal Financing Company, and when I went to obtain a clearance certificate from Al-Awwal Financing Company, they asked me for proof of payment. However, Emirates NBD refused to provide me with proof of payment, and my business has been disrupted due to not being given what proves the payment.</t>
+          <t>Emirates NBD Bank made a debt purchase for me from First Finance Company, and when I went to obtain a clearance certificate from First Finance Company, they asked me for proof of payment. However, Emirates NBD refused to provide me with proof of payment, and my business has been disrupted due to not being given what proves the payment.</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
@@ -11012,7 +11027,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank made a debt purchase for me from Al-Awwal Financing Company, and when I went to obtain a clearance certificate from Al-Awwal Financing Company, they asked me for proof of payment. • However, Emirates NBD refused to provide me with proof of payment, and my business has been disrupted due to not being given what proves the payment.</t>
+          <t>Emirates NBD Bank made a debt purchase for me from First Finance Company, and when I went to obtain a clearance certificate from First Finance Company, they asked me for proof of payment. • However, Emirates NBD refused to provide me with proof of payment, and my business has been disrupted due to not being given what proves the payment.</t>
         </is>
       </c>
       <c r="AJ63" t="inlineStr">

--- a/check2.xlsx
+++ b/check2.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL44"/>
+  <dimension ref="A1:AL45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>At Emirates NBD, we continue to strengthen our position at the forefront of digital transformation. Through our partnership with AlphaSense, we are equipping our teams with advanced AI tools that enable the extraction of valuable analytical data, accelerating the decision-making process with greater confidence and efficiency.
+          <t>At Emirates NBD, we continue to strengthen our position at the forefront of digital transformation. Through our partnership with AlphaSense, we equip our teams with advanced AI tools that enable the extraction of valuable analytical data, accelerating the decision-making process with greater confidence and efficiency.
 Learn about our experts' views on the role this technology plays in reshaping the future of decision-making.</t>
         </is>
       </c>
@@ -2079,36 +2079,186 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2038986467318677604</t>
+          <t>2038993347155485168</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://x.com/ali4bit/status/2038986467318677604</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2038993347155485168</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://x.com/ali4bit</t>
+          <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ali4bit</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>راکی زیر خاکی 👑 Rocky Antiquey</t>
+          <t>Emirates NBD</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2015894831462301696/T3XcXmSt_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
+        <is>
+          <t>يُرجى تزويدنا برقم هاتفك المسجل لدينا حتى نتمكن من التواصل معك من قِبل فريقنا لمساعدتك. مع تحياتنا.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>يُرجى تزويدنا برقم هاتفك المسجل لدينا حتى نتمكن من التواصل معك من قِبل فريقنا لمساعدتك. مع تحياتنا.</t>
+        </is>
+      </c>
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>['SultanAlhreago']</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>13h</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Mar 31, 2026 · 2:54 PM UTC</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>46112.62083333333</v>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>5</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>يُرجى تزويدنا برقم هاتفك المسجل لدينا حتى نتمكن من التواصل معك من قِبل فريقنا لمساعدتك. مع تحياتنا.</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>يُرجى تزويدنا برقم هاتفك المسجل لدينا حتى نتمكن من التواصل معك من قِبل فريقنا لمساعدتك. مع تحياتنا.</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>Please provide us with your registered phone number so that our team can contact you to assist you. Best regards.</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE11" s="2" t="n">
+        <v>46112.7875</v>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>31-03-2026</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Please provide us with your registered phone number so that our team can contact you to assist you.</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK11" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>SultanAlhreago</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2038986467318677604</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://x.com/ali4bit/status/2038986467318677604</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://x.com/ali4bit</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>ali4bit</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>راکی زیر خاکی 👑 Rocky Antiquey</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2015894831462301696/T3XcXmSt_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
         <is>
           <t>دو  صرافی Royal Lion و Crypto از عمده‌ترین ماموران سپاه پاسداران و پتروشیمی در دوبی هستند:
 No. 808,ENBD Building, Baniyas Road
@@ -2116,7 +2266,7 @@
 و برایان اعتماد بزرگترین عامل پولشویی سپاه است.</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>دو  صرافی Royal Lion و Crypto از عمده‌ترین ماموران سپاه پاسداران و پتروشیمی در دوبی هستند:
 No. 808,ENBD Building, Baniyas Road
@@ -2124,44 +2274,44 @@
 و برایان اعتماد بزرگترین عامل پولشویی سپاه است.</t>
         </is>
       </c>
-      <c r="K11" t="b">
-        <v>0</v>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
         <is>
           <t>13h</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Mar 31, 2026 · 2:27 PM UTC</t>
         </is>
       </c>
-      <c r="P11" s="2" t="n">
+      <c r="P12" s="2" t="n">
         <v>46112.60208333333</v>
       </c>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
         <v>4</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U12" t="n">
         <v>8</v>
       </c>
-      <c r="V11" t="n">
+      <c r="V12" t="n">
         <v>124</v>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>دو  صرافی Royal Lion و Crypto از عمده‌ترین ماموران سپاه پاسداران و پتروشیمی در دوبی هستند:
 No. 808,ENBD Building, Baniyas Road
@@ -2169,12 +2319,12 @@
 و برایان اعتماد بزرگترین عامل پولشویی سپاه است.</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>https://x.com/ali4bit/status/2038986467318677604</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>دو  صرافی Royal Lion و Crypto از عمده‌ترین ماموران سپاه پاسداران و پتروشیمی در دوبی هستند:
 No. 808,ENBD Building, Baniyas Road
@@ -2182,7 +2332,7 @@
 و برایان اعتماد بزرگترین عامل پولشویی سپاه است.</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>دو  صرافی Royal Lion و Crypto از عمده‌ترین ماموران سپاه پاسداران و پتروشیمی در دوبی هستند:
 No. 808,ENBD Building, Baniyas Road
@@ -2190,199 +2340,45 @@
 و برایان اعتماد بزرگترین عامل پولشویی سپاه است.</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>The Royal Lion and Crypto exchanges are among the main agents of the Revolutionary Guard and petrochemicals in Dubai:
 No. 808, ENBD Building, Baniyas Road
 No. 409, 4th floor, The Plaza, Baniyas Rd, Deira Al Rigga,
-and Brian Etemad is the largest money laundering agent of the Revolutionary Guard.</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
+and Brian Etemad is the largest money laundering agent of the Guard.</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="AE11" s="2" t="n">
+      <c r="AE12" s="2" t="n">
         <v>46112.76875</v>
       </c>
-      <c r="AF11" t="inlineStr">
+      <c r="AF12" t="inlineStr">
         <is>
           <t>31-03-2026</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
+      <c r="AG12" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="AH11" t="inlineStr">
+      <c r="AH12" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>409, 4th floor, The Plaza, Baniyas Rd, Deira Al Rigga, and Brian Etemad is the largest money laundering agent of the Revolutionary Guard. • The Royal Lion and Crypto exchanges are among the main agents of the Revolutionary Guard and petrochemicals in Dubai: No. • 808, ENBD Building, Baniyas Road No.</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AK11" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2038976125725249571</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>https://x.com/CNNBusinessAr/status/2038976125725249571</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>https://x.com/CNNBusinessAr</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CNNBusinessAr</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>الاقتصادية CNN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1983169168221581314/PRz7ULw2_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>أغلقت مجموعة الإمارات دبي الوطني جولة تمويل طويلة الأجل بقيمة 2.25 مليار دولار، في واحدة من أكبر الصفقات المجمعة في الخليج، مدعومة بإقبال قوي من 15 مؤسسة عالمية https://t.co/Gw5Nv9csFP</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>أغلقت مجموعة الإمارات دبي الوطني جولة تمويل طويلة الأجل بقيمة 2.25 مليار دولار، في واحدة من أكبر الصفقات المجمعة في الخليج، مدعومة بإقبال قوي من 15 مؤسسة عالمية</t>
-        </is>
-      </c>
-      <c r="K12" t="b">
-        <v>0</v>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>14h</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Mar 31, 2026 · 1:46 PM UTC</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="n">
-        <v>46112.57361111111</v>
-      </c>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>4</v>
-      </c>
-      <c r="V12" t="n">
-        <v>603</v>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>أغلقت مجموعة الإمارات دبي الوطني جولة تمويل طويلة الأجل بقيمة 2.25 مليار دولار، في واحدة من أكبر الصفقات المجمعة في الخليج، مدعومة بإقبال قوي من 15 مؤسسة عالمية</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>https://x.com/CNNBusinessAr/status/2038976125725249571</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>أغلقت مجموعة الإمارات دبي الوطني جولة تمويل طويلة الأجل بقيمة 2.25 مليار دولار، في واحدة من أكبر الصفقات المجمعة في الخليج، مدعومة بإقبال قوي من 15 مؤسسة عالمية https://t.co/Gw5Nv9csFP</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>أغلقت مجموعة الإمارات دبي الوطني جولة تمويل طويلة الأجل بقيمة 2.25 مليار دولار، في واحدة من أكبر الصفقات المجمعة في الخليج، مدعومة بإقبال قوي من 15 مؤسسة عالمية https://t.co/Gw5Nv9csFP</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Emirates NBD Group has closed a long-term financing round worth $2.25 billion, in one of the largest syndicated deals in the Gulf, supported by strong demand from 15 global institutions.</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="AE12" s="2" t="n">
-        <v>46112.74027777778</v>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>31-03-2026</t>
-        </is>
-      </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Emirates NBD Group has closed a long-term financing round worth $2.25 billion, in one of the largest syndicated deals in the Gulf, supported by strong demand from 15 global institutions.</t>
+          <t>409, 4th floor, The Plaza, Baniyas Rd, Deira Al Rigga, and Brian Etemad is the largest money laundering agent of the Guard. • The Royal Lion and Crypto exchanges are among the main agents of the Revolutionary Guard and petrochemicals in Dubai: No. • 808, ENBD Building, Baniyas Road No.</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2405,46 +2401,43 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2038964528314986898</t>
+          <t>2038976125725249571</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2038964528314986898</t>
+          <t>https://x.com/CNNBusinessAr/status/2038976125725249571</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA</t>
+          <t>https://x.com/CNNBusinessAr</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>EmiratesNBD_KSA</t>
+          <t>CNNBusinessAr</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>EmiratesNBD KSA</t>
+          <t>الاقتصادية CNN</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427762424385536/iUFFKIOK_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1983169168221581314/PRz7ULw2_bigger.jpg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>استثمر في الذهب بأسهل طريقة 👌🏼
-افتح حساب الذهب، واشتري وبيع الذهب بكل سهولة من #بنك_الإمارات_دبي_الوطني 💙 
-للتفاصيل:https://t.co/WLh4ZwvjCH https://t.co/uHYPfu5tf2</t>
+          <t>أغلقت مجموعة الإمارات دبي الوطني جولة تمويل طويلة الأجل بقيمة 2.25 مليار دولار، في واحدة من أكبر الصفقات المجمعة في الخليج، مدعومة بإقبال قوي من 15 مؤسسة عالمية https://t.co/Gw5Nv9csFP</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>قبل أي خطوة، استشر المختصين📱
-تواصل مع المستشار الائتماني في ⁧&lt;a href="/search?f=tweets&amp;amp;q=%23بنك_الإمارات_دبي_الوطني"&gt;#بنك_الإمارات_دبي_الوطني&lt;/a&gt;⁩ وخذ القرار بثقة✨</t>
+          <t>أغلقت مجموعة الإمارات دبي الوطني جولة تمويل طويلة الأجل بقيمة 2.25 مليار دولار، في واحدة من أكبر الصفقات المجمعة في الخليج، مدعومة بإقبال قوي من 15 مؤسسة عالمية</t>
         </is>
       </c>
       <c r="K13" t="b">
@@ -2454,34 +2447,30 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 1:00 PM UTC</t>
+          <t>Mar 31, 2026 · 1:46 PM UTC</t>
         </is>
       </c>
       <c r="P13" s="2" t="n">
-        <v>46112.54166666666</v>
+        <v>46112.57361111111</v>
       </c>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23بنك_الإمارات_دبي_الوطني']</t>
-        </is>
-      </c>
+      <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V13" t="n">
-        <v>451</v>
+        <v>603</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -2490,37 +2479,32 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>قبل أي خطوة، استشر المختصين📱
-تواصل مع المستشار الائتماني في ⁧#بنك_الإمارات_دبي_الوطني⁩ وخذ القرار بثقة✨</t>
+          <t>أغلقت مجموعة الإمارات دبي الوطني جولة تمويل طويلة الأجل بقيمة 2.25 مليار دولار، في واحدة من أكبر الصفقات المجمعة في الخليج، مدعومة بإقبال قوي من 15 مؤسسة عالمية</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2038964528314986898</t>
+          <t>https://x.com/CNNBusinessAr/status/2038976125725249571</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>استثمر في الذهب بأسهل طريقة 👌🏼
-افتح حساب الذهب، واشتري وبيع الذهب بكل سهولة من #بنك_الإمارات_دبي_الوطني 💙 
-للتفاصيل:https://t.co/WLh4ZwvjCH https://t.co/uHYPfu5tf2</t>
+          <t>أغلقت مجموعة الإمارات دبي الوطني جولة تمويل طويلة الأجل بقيمة 2.25 مليار دولار، في واحدة من أكبر الصفقات المجمعة في الخليج، مدعومة بإقبال قوي من 15 مؤسسة عالمية https://t.co/Gw5Nv9csFP</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>استثمر في الذهب بأسهل طريقة 👌🏼
-افتح حساب الذهب، واشتري وبيع الذهب بكل سهولة من #بنك_الإمارات_دبي_الوطني 💙 
-للتفاصيل:https://t.co/WLh4ZwvjCH https://t.co/uHYPfu5tf2</t>
+          <t>أغلقت مجموعة الإمارات دبي الوطني جولة تمويل طويلة الأجل بقيمة 2.25 مليار دولار، في واحدة من أكبر الصفقات المجمعة في الخليج، مدعومة بإقبال قوي من 15 مؤسسة عالمية https://t.co/Gw5Nv9csFP</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Invest in gold the easy way 👌🏼 Open a gold account and buy and sell gold effortlessly with #Emirates_NBD 💙 For details: https://t.co/WLh4ZwvjCH https://t.co/uHYPfu5tf2</t>
+          <t>Emirates NBD Group has closed a long-term financing round worth $2.25 billion, in one of the largest syndicated deals in the Gulf, supported by strong demand from 15 global institutions.</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Cust</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -2529,7 +2513,7 @@
         </is>
       </c>
       <c r="AE13" s="2" t="n">
-        <v>46112.70833333334</v>
+        <v>46112.74027777778</v>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
@@ -2548,7 +2532,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Invest in gold the easy way 👌🏼 Open a gold account and buy and sell gold effortlessly with #Emirates_NBD 💙 For details: https://t.co/WLh4ZwvjCH https://t.co/uHYPfu5tf2</t>
+          <t>Emirates NBD Group has closed a long-term financing round worth $2.25 billion, in one of the largest syndicated deals in the Gulf, supported by strong demand from 15 global institutions.</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2571,54 +2555,53 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2038956251225129344</t>
+          <t>2038964528314986898</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2038956251225129344</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2038964528314986898</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/EmiratesNBD_KSA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>EmiratesNBD_KSA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>EmiratesNBD KSA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1762427762424385536/iUFFKIOK_bigger.jpg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>مرحبًا، هل يمكننا معرفة سبب عدم رضاك؟ سيكون من المفيد جدًا إذا كان بإمكانك مشاركة المزيد من التفاصيل حول ذلك ورقم اتصالك معنا عبر الرسائل الخاصة.</t>
+          <t>استثمر في الذهب بأسهل طريقة 👌🏼
+افتح حساب الذهب، واشتري وبيع الذهب بكل سهولة من #بنك_الإمارات_دبي_الوطني 💙 
+للتفاصيل:https://t.co/WLh4ZwvjCH https://t.co/uHYPfu5tf2</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>مرحبًا، هل يمكننا معرفة سبب عدم رضاك؟ سيكون من المفيد جدًا إذا كان بإمكانك مشاركة المزيد من التفاصيل حول ذلك ورقم اتصالك معنا عبر الرسائل الخاصة.</t>
+          <t>قبل أي خطوة، استشر المختصين📱
+تواصل مع المستشار الائتماني في ⁧&lt;a href="/search?f=tweets&amp;amp;q=%23بنك_الإمارات_دبي_الوطني"&gt;#بنك_الإمارات_دبي_الوطني&lt;/a&gt;⁩ وخذ القرار بثقة✨</t>
         </is>
       </c>
       <c r="K14" t="b">
         <v>0</v>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>['SultanAlhreago']</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>15h</t>
@@ -2626,14 +2609,18 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 12:27 PM UTC</t>
+          <t>Mar 31, 2026 · 1:00 PM UTC</t>
         </is>
       </c>
       <c r="P14" s="2" t="n">
-        <v>46112.51875</v>
+        <v>46112.54166666666</v>
       </c>
       <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23بنك_الإمارات_دبي_الوطني']</t>
+        </is>
+      </c>
       <c r="S14" t="n">
         <v>1</v>
       </c>
@@ -2644,7 +2631,7 @@
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>3</v>
+        <v>451</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -2653,33 +2640,46 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>مرحبًا، هل يمكننا معرفة سبب عدم رضاك؟ سيكون من المفيد جدًا إذا كان بإمكانك مشاركة المزيد من التفاصيل حول ذلك ورقم اتصالك معنا عبر الرسائل الخاصة.</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
+          <t>قبل أي خطوة، استشر المختصين📱
+تواصل مع المستشار الائتماني في ⁧#بنك_الإمارات_دبي_الوطني⁩ وخذ القرار بثقة✨</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_KSA/status/2038964528314986898</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>استثمر في الذهب بأسهل طريقة 👌🏼
+افتح حساب الذهب، واشتري وبيع الذهب بكل سهولة من #بنك_الإمارات_دبي_الوطني 💙 
+للتفاصيل:https://t.co/WLh4ZwvjCH https://t.co/uHYPfu5tf2</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>مرحبًا، هل يمكننا معرفة سبب عدم رضاك؟ سيكون من المفيد جدًا إذا كان بإمكانك مشاركة المزيد من التفاصيل حول ذلك ورقم اتصالك معنا عبر الرسائل الخاصة.</t>
+          <t>استثمر في الذهب بأسهل طريقة 👌🏼
+افتح حساب الذهب، واشتري وبيع الذهب بكل سهولة من #بنك_الإمارات_دبي_الوطني 💙 
+للتفاصيل:https://t.co/WLh4ZwvjCH https://t.co/uHYPfu5tf2</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Hello, can we know the reason for your dissatisfaction? It would be very helpful if you could share more details about it and your contact number with us via private messages.</t>
+          <t>Invest in gold the easy way 👌🏼 Open a gold account and buy and sell gold effortlessly with #EmiratesNBD 💙 For details: https://t.co/WLh4ZwvjCH https://t.co/uHYPfu5tf2</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Cust</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE14" s="2" t="n">
-        <v>46112.68541666667</v>
+        <v>46112.70833333334</v>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>It would be very helpful if you could share more details about it and your contact number with us via private messages. • Hello, can we know the reason for your dissatisfaction?</t>
+          <t>Invest in gold the easy way 👌🏼 Open a gold account and buy and sell gold effortlessly with #EmiratesNBD 💙 For details: https://t.co/WLh4ZwvjCH https://t.co/uHYPfu5tf2</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>SultanAlhreago</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2721,43 +2721,43 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2038954975590588824</t>
+          <t>2038956251225129344</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://x.com/SultanAlhreago/status/2038954975590588824</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2038956251225129344</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://x.com/SultanAlhreago</t>
+          <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SultanAlhreago</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sultan Al hrbi</t>
+          <t>Emirates NBD</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>اتمنى ان يرد على رسالتي البنك بكل وضوح</t>
+          <t>مرحبًا، هل يمكننا معرفة سبب عدم رضاك؟ سيكون من المفيد جدًا إذا كان بإمكانك مشاركة المزيد من التفاصيل حول ذلك ورقم اتصالك معنا عبر الرسائل الخاصة.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>اتمنى ان يرد على رسالتي البنك بكل وضوح</t>
+          <t>مرحبًا، هل يمكننا معرفة سبب عدم رضاك؟ سيكون من المفيد جدًا إذا كان بإمكانك مشاركة المزيد من التفاصيل حول ذلك ورقم اتصالك معنا عبر الرسائل الخاصة.</t>
         </is>
       </c>
       <c r="K15" t="b">
@@ -2766,7 +2766,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>['EmiratesNBD_AE']</t>
+          <t>['SultanAlhreago']</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 12:22 PM UTC</t>
+          <t>Mar 31, 2026 · 12:27 PM UTC</t>
         </is>
       </c>
       <c r="P15" s="2" t="n">
-        <v>46112.51527777778</v>
+        <v>46112.51875</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
@@ -2794,7 +2794,7 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -2803,19 +2803,19 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>اتمنى ان يرد على رسالتي البنك بكل وضوح</t>
+          <t>مرحبًا، هل يمكننا معرفة سبب عدم رضاك؟ سيكون من المفيد جدًا إذا كان بإمكانك مشاركة المزيد من التفاصيل حول ذلك ورقم اتصالك معنا عبر الرسائل الخاصة.</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>اتمنى ان يرد على رسالتي البنك بكل وضوح</t>
+          <t>مرحبًا، هل يمكننا معرفة سبب عدم رضاك؟ سيكون من المفيد جدًا إذا كان بإمكانك مشاركة المزيد من التفاصيل حول ذلك ورقم اتصالك معنا عبر الرسائل الخاصة.</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>I hope the bank responds to my message clearly.</t>
+          <t>Hello, can we know the reason for your dissatisfaction? It would be very helpful if you could share more details about it and your contact number with us via private messages.</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2829,7 +2829,7 @@
         </is>
       </c>
       <c r="AE15" s="2" t="n">
-        <v>46112.68194444444</v>
+        <v>46112.68541666667</v>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>I hope the bank responds to my message clearly.</t>
+          <t>It would be very helpful if you could share more details about it and your contact number with us via private messages. • Hello, can we know the reason for your dissatisfaction?</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>SultanAlhreago</t>
         </is>
       </c>
     </row>
@@ -2871,50 +2871,54 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2038954879092445695</t>
+          <t>2038954975590588824</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide/status/2038954879092445695</t>
+          <t>https://x.com/SultanAlhreago/status/2038954975590588824</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide</t>
+          <t>https://x.com/SultanAlhreago</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>dcgguide</t>
+          <t>SultanAlhreago</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>DUBAI CITY GUIDE from Cyber Gear</t>
+          <t>Sultan Al hrbi</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1780203891230945280/ODQLZiT__bigger.jpg</t>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Emirates NBD Group Successfully Closes USD 2.25 Billion In Long-Term Financing https://t.co/RdxvnZDQCF</t>
+          <t>اتمنى ان يرد على رسالتي البنك بكل وضوح</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Emirates NBD Group Successfully Closes USD 2.25 Billion In Long-Term Financing &lt;a href="https://blog.dubaicityguide.com/site/emirates-nbd-group-successfully-closes-usd-2-25-billion-in-long-term-financing/"&gt;blog.dubaicityguide.com/site…&lt;/a&gt;</t>
+          <t>اتمنى ان يرد على رسالتي البنك بكل وضوح</t>
         </is>
       </c>
       <c r="K16" t="b">
         <v>0</v>
       </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr">
         <is>
           <t>15h</t>
@@ -2922,20 +2926,16 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 12:21 PM UTC</t>
+          <t>Mar 31, 2026 · 12:22 PM UTC</t>
         </is>
       </c>
       <c r="P16" s="2" t="n">
-        <v>46112.51458333333</v>
+        <v>46112.51527777778</v>
       </c>
       <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>['https://blog.dubaicityguide.com/site/emirates-nbd-group-successfully-closes-usd-2-25-billion-in-long-term-financing/']</t>
-        </is>
-      </c>
+      <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -2944,7 +2944,7 @@
         <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>139</v>
+        <v>2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -2953,27 +2953,19 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Emirates NBD Group Successfully Closes USD 2.25 Billion In Long-Term Financing blog.dubaicityguide.com/site…</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>https://x.com/dcgguide/status/2038954879092445695</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Emirates NBD Group Successfully Closes USD 2.25 Billion In Long-Term Financing https://t.co/RdxvnZDQCF</t>
-        </is>
-      </c>
+          <t>اتمنى ان يرد على رسالتي البنك بكل وضوح</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>Emirates NBD Group Successfully Closes USD 2.25 Billion In Long-Term Financing https://t.co/RdxvnZDQCF</t>
+          <t>اتمنى ان يرد على رسالتي البنك بكل وضوح</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Emirates NBD Group Successfully Closes USD 2.25 Billion In Long-Term Financing</t>
+          <t>I hope the bank responds to my message clearly.</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2983,11 +2975,11 @@
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE16" s="2" t="n">
-        <v>46112.68125</v>
+        <v>46112.68194444444</v>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
@@ -3006,7 +2998,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Emirates NBD Group Successfully Closes USD 2.25 Billion In Long-Term Financing</t>
+          <t>I hope the bank responds to my message clearly.</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -3019,7 +3011,7 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
     </row>
@@ -3029,71 +3021,69 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2038948346396655877</t>
+          <t>2038954879092445695</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://x.com/alqreshe/status/2038948346396655877</t>
+          <t>https://x.com/dcgguide/status/2038954879092445695</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://x.com/alqreshe</t>
+          <t>https://x.com/dcgguide</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>alqreshe</t>
+          <t>dcgguide</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>راعي الاوله ❤️</t>
+          <t>DUBAI CITY GUIDE from Cyber Gear</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1808896727937687552/54A2iFyt_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1780203891230945280/ODQLZiT__bigger.jpg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>— من الخاص 🎙️ 
-ابي اقل بنك فائدة في القروض الشخصية ؟
-#استمتع_بالرحلة</t>
+          <t>Emirates NBD Group Successfully Closes USD 2.25 Billion In Long-Term Financing https://t.co/RdxvnZDQCF</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>ياليت عالخاص</t>
+          <t>Emirates NBD Group Successfully Closes USD 2.25 Billion In Long-Term Financing &lt;a href="https://blog.dubaicityguide.com/site/emirates-nbd-group-successfully-closes-usd-2-25-billion-in-long-term-financing/"&gt;blog.dubaicityguide.com/site…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K17" t="b">
         <v>0</v>
       </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>['t14l7', 'bandr88081', 'Vc7Jy', 'AskCFO', 'EmiratesNBD_KSA']</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 11:55 AM UTC</t>
+          <t>Mar 31, 2026 · 12:21 PM UTC</t>
         </is>
       </c>
       <c r="P17" s="2" t="n">
-        <v>46112.49652777778</v>
+        <v>46112.51458333333</v>
       </c>
       <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>['https://blog.dubaicityguide.com/site/emirates-nbd-group-successfully-closes-usd-2-25-billion-in-long-term-financing/']</t>
+        </is>
+      </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
@@ -3104,7 +3094,7 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>12</v>
+        <v>139</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
@@ -3113,31 +3103,27 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>ياليت عالخاص</t>
+          <t>Emirates NBD Group Successfully Closes USD 2.25 Billion In Long-Term Financing blog.dubaicityguide.com/site…</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>https://x.com/alqreshe/status/2038948346396655877</t>
+          <t>https://x.com/dcgguide/status/2038954879092445695</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>— من الخاص 🎙️ 
-ابي اقل بنك فائدة في القروض الشخصية ؟
-#استمتع_بالرحلة</t>
+          <t>Emirates NBD Group Successfully Closes USD 2.25 Billion In Long-Term Financing https://t.co/RdxvnZDQCF</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>— من الخاص 🎙️ 
-ابي اقل بنك فائدة في القروض الشخصية ؟
-#استمتع_بالرحلة</t>
+          <t>Emirates NBD Group Successfully Closes USD 2.25 Billion In Long-Term Financing https://t.co/RdxvnZDQCF</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>I want to know which bank has the lowest interest rate for personal loans?</t>
+          <t>Emirates NBD Group Successfully Closes USD 2.25 Billion In Long-Term Financing</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -3147,11 +3133,11 @@
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE17" s="2" t="n">
-        <v>46112.66319444445</v>
+        <v>46112.68125</v>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
@@ -3170,7 +3156,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>I want to know which bank has the lowest interest rate for personal loans?</t>
+          <t>Emirates NBD Group Successfully Closes USD 2.25 Billion In Long-Term Financing</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -3183,7 +3169,7 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>t14l7, bandr88081, Vc7Jy, AskCFO, EmiratesNBD_KSA</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3193,36 +3179,200 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2038919235049849068</t>
+          <t>2038948346396655877</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://x.com/proofoftalk/status/2038919235049849068</t>
+          <t>https://x.com/alqreshe/status/2038948346396655877</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://x.com/proofoftalk</t>
+          <t>https://x.com/alqreshe</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>proofoftalk</t>
+          <t>alqreshe</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Proof of Talk</t>
+          <t>راعي الاوله ❤️</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1995454205461762048/NF7boqts_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1808896727937687552/54A2iFyt_bigger.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
+        <is>
+          <t>— من الخاص 🎙️ 
+ابي اقل بنك فائدة في القروض الشخصية ؟
+#استمتع_بالرحلة</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>ياليت عالخاص</t>
+        </is>
+      </c>
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>['t14l7', 'bandr88081', 'Vc7Jy', 'AskCFO', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>16h</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Mar 31, 2026 · 11:55 AM UTC</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="n">
+        <v>46112.49652777778</v>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>12</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>ياليت عالخاص</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>https://x.com/alqreshe/status/2038948346396655877</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>— من الخاص 🎙️ 
+ابي اقل بنك فائدة في القروض الشخصية ؟
+#استمتع_بالرحلة</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>— من الخاص 🎙️ 
+ابي اقل بنك فائدة في القروض الشخصية ؟
+#استمتع_بالرحلة</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>I want to know which bank has the lowest interest rate for personal loans?</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE18" s="2" t="n">
+        <v>46112.66319444445</v>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>31-03-2026</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>I want to know which bank has the lowest interest rate for personal loans?</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK18" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>t14l7, bandr88081, Vc7Jy, AskCFO, EmiratesNBD_KSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2038919235049849068</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://x.com/proofoftalk/status/2038919235049849068</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://x.com/proofoftalk</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>proofoftalk</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Proof of Talk</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1995454205461762048/NF7boqts_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
         <is>
           <t>Mark Jeffrey @markjeffrey, Partner at @stillcorecap, joins Proof of Talk 2026 as a speaker this June. He wrote the book on Bitcoin, and is now deploying capital into what he believes is the next foundational layer of the internet.
 Stillcore Capital is an open-end, evergreen hedge fund focused on Bittensor, subnet alpha tokens, and decentralized AI opportunities across the Bittensor ecosystem.
@@ -3233,7 +3383,7 @@
 See you there → https://t.co/ol4EWRrKxo</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>Julian Sawyer &lt;a href="/julian_sawyer" title="Julian Sawyer"&gt;@julian_sawyer&lt;/a&gt;, CEO of &lt;a href="/ZodiaCustody" title="Zodia"&gt;@ZodiaCustody&lt;/a&gt;, joins the Proof of Talk stage.
 $36M raised to scale institutional crypto custody. Backed by Standard Chartered, Northern Trust, SBI Holdings, NAB National Australia Bank, and Emirates NBD.
@@ -3246,48 +3396,48 @@
 &lt;a href="https://tickets.proofoftalk.io/passes"&gt;tickets.proofoftalk.io/passe…&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K18" t="b">
-        <v>0</v>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
+      <c r="K19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
         <is>
           <t>18h</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>Mar 31, 2026 · 10:00 AM UTC</t>
         </is>
       </c>
-      <c r="P18" s="2" t="n">
+      <c r="P19" s="2" t="n">
         <v>46112.41666666666</v>
       </c>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr">
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
         <is>
           <t>['https://x.com/julian_sawyer', 'https://x.com/ZodiaCustody', 'https://x.com/Bitstamp', 'https://tickets.proofoftalk.io/passes']</t>
         </is>
       </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
         <v>4</v>
       </c>
-      <c r="U18" t="n">
+      <c r="U19" t="n">
         <v>11</v>
       </c>
-      <c r="V18" t="n">
+      <c r="V19" t="n">
         <v>247</v>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>Julian Sawyer @julian_sawyer, CEO of @ZodiaCustody, joins the Proof of Talk stage.
 $36M raised to scale institutional crypto custody. Backed by Standard Chartered, Northern Trust, SBI Holdings, NAB National Australia Bank, and Emirates NBD.
@@ -3300,12 +3450,12 @@
 tickets.proofoftalk.io/passe…</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>https://x.com/proofoftalk/status/2038919235049849068</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>Mark Jeffrey @markjeffrey, Partner at @stillcorecap, joins Proof of Talk 2026 as a speaker this June. He wrote the book on Bitcoin, and is now deploying capital into what he believes is the next foundational layer of the internet.
 Stillcore Capital is an open-end, evergreen hedge fund focused on Bittensor, subnet alpha tokens, and decentralized AI opportunities across the Bittensor ecosystem.
@@ -3316,7 +3466,7 @@
 See you there → https://t.co/ol4EWRrKxo</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr">
+      <c r="AA19" t="inlineStr">
         <is>
           <t>Mark Jeffrey @markjeffrey, Partner at @stillcorecap, joins Proof of Talk 2026 as a speaker this June. He wrote the book on Bitcoin, and is now deploying capital into what he believes is the next foundational layer of the internet.
 Stillcore Capital is an open-end, evergreen hedge fund focused on Bittensor, subnet alpha tokens, and decentralized AI opportunities across the Bittensor ecosystem.
@@ -3327,9 +3477,9 @@
 See you there → https://t.co/ol4EWRrKxo</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Mark Jeffrey, Partner at Stillcore Capital, joins Proof of Talk 2026 as a speaker this June. He wrote the book on Bitcoin and is now deploying capital into what he believes is the next foundational layer of the internet.
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>Mark Jeffrey @markjeffrey, Partner at @stillcorecap, joins Proof of Talk 2026 as a speaker this June. He wrote the book on Bitcoin and is now deploying capital into what he believes is the next foundational layer of the internet.
 Stillcore Capital is an open-end, evergreen hedge fund focused on Bittensor, subnet alpha tokens, and decentralized AI opportunities across the Bittensor ecosystem.
 The fund publicly targets roughly 1% of TAO's liquid supply and combines capital deployment with active ecosystem participation.
 Mark is a serial entrepreneur and early Bitcoin adopter. He co-founded The Palace, ZeroDegrees, and Guardian Circle, and hosts Hash Rate, a research-driven show covering Bittensor, AI, and crypto.
@@ -3338,199 +3488,37 @@
 See you there → https://t.co/ol4EWRrKxo</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
+      <c r="AC19" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="AD18" t="inlineStr">
+      <c r="AD19" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="AE18" s="2" t="n">
+      <c r="AE19" s="2" t="n">
         <v>46112.58333333334</v>
       </c>
-      <c r="AF18" t="inlineStr">
+      <c r="AF19" t="inlineStr">
         <is>
           <t>31-03-2026</t>
         </is>
       </c>
-      <c r="AG18" t="inlineStr">
+      <c r="AG19" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="AH18" t="inlineStr">
+      <c r="AH19" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>At Proof of Talk on June 2–3, he joins the builders and allocators who are making the same kind of early bets on decentralized AI that he made on Bitcoin fifteen years ago. • Stillcore Capital is an open-end, evergreen hedge fund focused on Bittensor, subnet alpha tokens, and decentralized AI opportunities across the Bittensor ecosystem. • Mark Jeffrey, Partner at Stillcore Capital, joins Proof of Talk 2026 as a speaker this June.</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AK18" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2038911516687163856</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>https://x.com/theeb20202/status/2038911516687163856</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>https://x.com/theeb20202</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>theeb20202</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>ⒶⓁⓏⒶⒾⓂ</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1517954735902441472/qwtsMbj0_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>رأيك يهمنا 💬
-تواصل معنا عبر التطبيق أو الموقع أو الهاتف، وخلنا نجاوب على استفسارك https://t.co/OPblTwxpnZ</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>ابي قرض شخصي كيف</t>
-        </is>
-      </c>
-      <c r="K19" t="b">
-        <v>0</v>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_KSA']</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>18h</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>Mar 31, 2026 · 9:29 AM UTC</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="n">
-        <v>46112.39513888889</v>
-      </c>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="n">
-        <v>1</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1</v>
-      </c>
-      <c r="V19" t="n">
-        <v>16</v>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>ابي قرض شخصي كيف</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>https://x.com/theeb20202/status/2038911516687163856</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>رأيك يهمنا 💬
-تواصل معنا عبر التطبيق أو الموقع أو الهاتف، وخلنا نجاوب على استفسارك https://t.co/OPblTwxpnZ</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>رأيك يهمنا 💬
-تواصل معنا عبر التطبيق أو الموقع أو الهاتف، وخلنا نجاوب على استفسارك https://t.co/OPblTwxpnZ</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Your opinion matters to us 💬  
-Contact us through the app, website, or phone, and let us answer your inquiry.</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AE19" s="2" t="n">
-        <v>46112.56180555555</v>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>31-03-2026</t>
-        </is>
-      </c>
-      <c r="AG19" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Your opinion matters to us 💬 Contact us through the app, website, or phone, and let us answer your inquiry.</t>
+          <t>At Proof of Talk on June 2–3, he joins the builders and allocators who are making the same kind of early bets on decentralized AI that he made on Bitcoin fifteen years ago. • Stillcore Capital is an open-end, evergreen hedge fund focused on Bittensor, subnet alpha tokens, and decentralized AI opportunities across the Bittensor ecosystem. • Mark Jeffrey @markjeffrey, Partner at @stillcorecap, joins Proof of Talk 2026 as a speaker this June.</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -3543,7 +3531,7 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>EmiratesNBD_KSA</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3553,84 +3541,81 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2038889032826982535</t>
+          <t>2038911516687163856</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2038889032826982535</t>
+          <t>https://x.com/theeb20202/status/2038911516687163856</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/theeb20202</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>theeb20202</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>ⒶⓁⓏⒶⒾⓂ</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1517954735902441472/qwtsMbj0_bigger.jpg</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Scammers can pretend to be banks. Avoid unknown callers. 
-Stay Safe, Stay Vigilant. #UnitedAgainstFraud
-https://t.co/YpRWtBZrhq</t>
+          <t>رأيك يهمنا 💬
+تواصل معنا عبر التطبيق أو الموقع أو الهاتف، وخلنا نجاوب على استفسارك https://t.co/OPblTwxpnZ</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Scammers can pretend to be banks. Avoid unknown callers. 
-Stay Safe, Stay Vigilant. &lt;a href="/search?f=tweets&amp;amp;q=%23UnitedAgainstFraud"&gt;#UnitedAgainstFraud&lt;/a&gt;
-&lt;a href="https://www.emiratesnbd.com/en/campaigns/united-against-fraud"&gt;emiratesnbd.com/en/campaigns…&lt;/a&gt;</t>
+          <t>ابي قرض شخصي كيف</t>
         </is>
       </c>
       <c r="K20" t="b">
         <v>0</v>
       </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_KSA']</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 8:00 AM UTC</t>
+          <t>Mar 31, 2026 · 9:29 AM UTC</t>
         </is>
       </c>
       <c r="P20" s="2" t="n">
-        <v>46112.33333333334</v>
+        <v>46112.39513888889</v>
       </c>
       <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23UnitedAgainstFraud', 'https://www.emiratesnbd.com/en/campaigns/united-against-fraud']</t>
-        </is>
-      </c>
+      <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
         <v>1</v>
       </c>
       <c r="V20" t="n">
-        <v>430</v>
+        <v>16</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
@@ -3639,39 +3624,35 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Scammers can pretend to be banks. Avoid unknown callers. 
-Stay Safe, Stay Vigilant. #UnitedAgainstFraud
-emiratesnbd.com/en/campaigns…</t>
+          <t>ابي قرض شخصي كيف</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2038889032826982535</t>
+          <t>https://x.com/theeb20202/status/2038911516687163856</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>Scammers can pretend to be banks. Avoid unknown callers. 
-Stay Safe, Stay Vigilant. #UnitedAgainstFraud
-https://t.co/YpRWtBZrhq</t>
+          <t>رأيك يهمنا 💬
+تواصل معنا عبر التطبيق أو الموقع أو الهاتف، وخلنا نجاوب على استفسارك https://t.co/OPblTwxpnZ</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>Scammers can pretend to be banks. Avoid unknown callers. 
-Stay Safe, Stay Vigilant. #UnitedAgainstFraud
-https://t.co/YpRWtBZrhq</t>
+          <t>رأيك يهمنا 💬
+تواصل معنا عبر التطبيق أو الموقع أو الهاتف، وخلنا نجاوب على استفسارك https://t.co/OPblTwxpnZ</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Scammers can pretend to be banks. Avoid unknown callers. 
-Stay Safe, Stay Vigilant. #UnitedAgainstFraud</t>
+          <t>Your opinion matters to us 💬
+Contact us through the app, website, or phone, and let us answer your inquiry.</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Cust</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -3680,7 +3661,7 @@
         </is>
       </c>
       <c r="AE20" s="2" t="n">
-        <v>46112.5</v>
+        <v>46112.56180555555</v>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
@@ -3699,7 +3680,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Stay Safe, Stay Vigilant. • Scammers can pretend to be banks.</t>
+          <t>Your opinion matters to us 💬 Contact us through the app, website, or phone, and let us answer your inquiry.</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3712,7 +3693,7 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>EmiratesNBD_KSA</t>
         </is>
       </c>
     </row>
@@ -3722,45 +3703,47 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2038888971627897329</t>
+          <t>2038889032826982535</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2038888971627897329</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2038889032826982535</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA</t>
+          <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>EmiratesNBD_KSA</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>EmiratesNBD KSA</t>
+          <t>Emirates NBD</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427762424385536/iUFFKIOK_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>رأيك يهمنا 💬
-تواصل معنا عبر التطبيق أو الموقع أو الهاتف، وخلنا نجاوب على استفسارك</t>
+          <t>Scammers can pretend to be banks. Avoid unknown callers. 
+Stay Safe, Stay Vigilant. #UnitedAgainstFraud
+https://t.co/YpRWtBZrhq</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>رأيك يهمنا 💬
-تواصل معنا عبر التطبيق أو الموقع أو الهاتف، وخلنا نجاوب على استفسارك</t>
+          <t>Scammers can pretend to be banks. Avoid unknown callers. 
+Stay Safe, Stay Vigilant. &lt;a href="/search?f=tweets&amp;amp;q=%23UnitedAgainstFraud"&gt;#UnitedAgainstFraud&lt;/a&gt;
+&lt;a href="https://www.emiratesnbd.com/en/campaigns/united-against-fraud"&gt;emiratesnbd.com/en/campaigns…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K21" t="b">
@@ -3775,16 +3758,20 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 7:59 AM UTC</t>
+          <t>Mar 31, 2026 · 8:00 AM UTC</t>
         </is>
       </c>
       <c r="P21" s="2" t="n">
-        <v>46112.33263888889</v>
+        <v>46112.33333333334</v>
       </c>
       <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23UnitedAgainstFraud', 'https://www.emiratesnbd.com/en/campaigns/united-against-fraud']</t>
+        </is>
+      </c>
       <c r="S21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
@@ -3793,7 +3780,7 @@
         <v>1</v>
       </c>
       <c r="V21" t="n">
-        <v>666</v>
+        <v>430</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
@@ -3802,22 +3789,34 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>رأيك يهمنا 💬
-تواصل معنا عبر التطبيق أو الموقع أو الهاتف، وخلنا نجاوب على استفسارك</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
+          <t>Scammers can pretend to be banks. Avoid unknown callers. 
+Stay Safe, Stay Vigilant. #UnitedAgainstFraud
+emiratesnbd.com/en/campaigns…</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2038889032826982535</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>Scammers can pretend to be banks. Avoid unknown callers. 
+Stay Safe, Stay Vigilant. #UnitedAgainstFraud
+https://t.co/YpRWtBZrhq</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>رأيك يهمنا 💬
-تواصل معنا عبر التطبيق أو الموقع أو الهاتف، وخلنا نجاوب على استفسارك</t>
+          <t>Scammers can pretend to be banks. Avoid unknown callers. 
+Stay Safe, Stay Vigilant. #UnitedAgainstFraud
+https://t.co/YpRWtBZrhq</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>Your opinion matters to us 💬
-Contact us through the app, website, or phone, and let us answer your inquiry.</t>
+          <t>Scammers can pretend to be banks. Avoid unknown callers. 
+Stay Safe, Stay Vigilant. #UnitedAgainstFraud</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3831,7 +3830,7 @@
         </is>
       </c>
       <c r="AE21" s="2" t="n">
-        <v>46112.49930555555</v>
+        <v>46112.5</v>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
@@ -3850,7 +3849,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Your opinion matters to us 💬 Contact us through the app, website, or phone, and let us answer your inquiry.</t>
+          <t>Stay Safe, Stay Vigilant. • Scammers can pretend to be banks.</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -3873,54 +3872,52 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2038884971977314696</t>
+          <t>2038888971627897329</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://x.com/mms5350/status/2038884971977314696</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2038888971627897329</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://x.com/mms5350</t>
+          <t>https://x.com/EmiratesNBD_KSA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>mms5350</t>
+          <t>EmiratesNBD_KSA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>🇸🇦🇸🇦🇸🇦 مم</t>
+          <t>EmiratesNBD KSA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1846628803612639232/GNQdlN9v_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1762427762424385536/iUFFKIOK_bigger.jpg</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>@AymanAlHarbiSF @EmiratesNBD_KSA @SAMA_GOV عزيزنا العميل شكراً لتواصلكم عبر حساب البنك المركزي السعودي ، بإمكانك رفع الطلب الخاص بك عن طريق زيارة الموقع التالي : https://t.co/DtvCdpTRLn.</t>
+          <t>رأيك يهمنا 💬
+تواصل معنا عبر التطبيق أو الموقع أو الهاتف، وخلنا نجاوب على استفسارك</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>&lt;a href="/SAMA_GOV" title="SAMA | البنك المركزي السعودي"&gt;@SAMA_GOV&lt;/a&gt; معالي المحافظ لدي شكوى على &lt;a href="/alrajhibank" title="مصرف الراجحي"&gt;@alrajhibank&lt;/a&gt; لم تعالج والرد في الخاص جاري معالجه الشكوى او تم تصعيدها لماذا التأخير في معالجة الشكاوي؟ انا متضرر من التأخير في حل شكواي</t>
+          <t>رأيك يهمنا 💬
+تواصل معنا عبر التطبيق أو الموقع أو الهاتف، وخلنا نجاوب على استفسارك</t>
         </is>
       </c>
       <c r="K22" t="b">
         <v>0</v>
       </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>['SAMAcares', 'AymanAlHarbiSF', 'EmiratesNBD_KSA']</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>20h</t>
@@ -3928,29 +3925,25 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 7:43 AM UTC</t>
+          <t>Mar 31, 2026 · 7:59 AM UTC</t>
         </is>
       </c>
       <c r="P22" s="2" t="n">
-        <v>46112.32152777778</v>
+        <v>46112.33263888889</v>
       </c>
       <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>['https://x.com/SAMA_GOV', 'https://x.com/alrajhibank']</t>
-        </is>
-      </c>
+      <c r="R22" t="inlineStr"/>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" t="n">
-        <v>12</v>
+        <v>666</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -3959,32 +3952,27 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>@SAMA_GOV معالي المحافظ لدي شكوى على @alrajhibank لم تعالج والرد في الخاص جاري معالجه الشكوى او تم تصعيدها لماذا التأخير في معالجة الشكاوي؟ انا متضرر من التأخير في حل شكواي</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>https://x.com/mms5350/status/2038884971977314696</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>@AymanAlHarbiSF @EmiratesNBD_KSA @SAMA_GOV عزيزنا العميل شكراً لتواصلكم عبر حساب البنك المركزي السعودي ، بإمكانك رفع الطلب الخاص بك عن طريق زيارة الموقع التالي : https://t.co/DtvCdpTRLn.</t>
-        </is>
-      </c>
+          <t>رأيك يهمنا 💬
+تواصل معنا عبر التطبيق أو الموقع أو الهاتف، وخلنا نجاوب على استفسارك</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>@AymanAlHarbiSF @EmiratesNBD_KSA @SAMA_GOV عزيزنا العميل شكراً لتواصلكم عبر حساب البنك المركزي السعودي ، بإمكانك رفع الطلب الخاص بك عن طريق زيارة الموقع التالي : https://t.co/DtvCdpTRLn.</t>
+          <t>رأيك يهمنا 💬
+تواصل معنا عبر التطبيق أو الموقع أو الهاتف، وخلنا نجاوب على استفسارك</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>Dear valued customer, thank you for contacting us through the Saudi Central Bank account. You can submit your request by visiting the following website: https://t.co/DtvCdpTRLn.</t>
+          <t>Your opinion matters to us 💬  
+Contact us through the app, website, or phone, and let us answer your inquiry.</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Cust</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -3993,7 +3981,7 @@
         </is>
       </c>
       <c r="AE22" s="2" t="n">
-        <v>46112.48819444444</v>
+        <v>46112.49930555555</v>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
@@ -4012,7 +4000,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Dear valued customer, thank you for contacting us through the Saudi Central Bank account. • You can submit your request by visiting the following website: https://t.co/DtvCdpTRLn.</t>
+          <t>Your opinion matters to us 💬 Contact us through the app, website, or phone, and let us answer your inquiry.</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
@@ -4025,7 +4013,7 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>SAMAcares, AymanAlHarbiSF, EmiratesNBD_KSA</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4035,44 +4023,43 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2038884890695831893</t>
+          <t>2038884971977314696</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2038884890695831893</t>
+          <t>https://x.com/mms5350/status/2038884971977314696</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/mms5350</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>mms5350</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>🇸🇦🇸🇦🇸🇦 مم</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1846628803612639232/GNQdlN9v_bigger.jpg</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE هل يوجد لديكم تمويل عقاري؟</t>
+          <t>@AymanAlHarbiSF @EmiratesNBD_KSA @SAMA_GOV عزيزنا العميل شكراً لتواصلكم عبر حساب البنك المركزي السعودي ، بإمكانك رفع الطلب الخاص بك عن طريق زيارة الموقع التالي : https://t.co/DtvCdpTRLn.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>نشكركم على اهتمامكم بمنتجاتنا، يرجى زيارة الرابط أدناه وملء بياناتكم وسيتصل بكم فريق المبيعات لدينا في غضون يومي عمل.
-&lt;a href="http://ms.spr.ly/6015QxfsS"&gt;ms.spr.ly/6015QxfsS&lt;/a&gt;</t>
+          <t>&lt;a href="/SAMA_GOV" title="SAMA | البنك المركزي السعودي"&gt;@SAMA_GOV&lt;/a&gt; معالي المحافظ لدي شكوى على &lt;a href="/alrajhibank" title="مصرف الراجحي"&gt;@alrajhibank&lt;/a&gt; لم تعالج والرد في الخاص جاري معالجه الشكوى او تم تصعيدها لماذا التأخير في معالجة الشكاوي؟ انا متضرر من التأخير في حل شكواي</t>
         </is>
       </c>
       <c r="K23" t="b">
@@ -4081,7 +4068,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>['Sd67239684']</t>
+          <t>['SAMAcares', 'AymanAlHarbiSF', 'EmiratesNBD_KSA']</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -4100,7 +4087,7 @@
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
         <is>
-          <t>['http://ms.spr.ly/6015QxfsS']</t>
+          <t>['https://x.com/SAMA_GOV', 'https://x.com/alrajhibank']</t>
         </is>
       </c>
       <c r="S23" t="n">
@@ -4122,28 +4109,27 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>نشكركم على اهتمامكم بمنتجاتنا، يرجى زيارة الرابط أدناه وملء بياناتكم وسيتصل بكم فريق المبيعات لدينا في غضون يومي عمل.
-ms.spr.ly/6015QxfsS</t>
+          <t>@SAMA_GOV معالي المحافظ لدي شكوى على @alrajhibank لم تعالج والرد في الخاص جاري معالجه الشكوى او تم تصعيدها لماذا التأخير في معالجة الشكاوي؟ انا متضرر من التأخير في حل شكواي</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2038884890695831893</t>
+          <t>https://x.com/mms5350/status/2038884971977314696</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE هل يوجد لديكم تمويل عقاري؟</t>
+          <t>@AymanAlHarbiSF @EmiratesNBD_KSA @SAMA_GOV عزيزنا العميل شكراً لتواصلكم عبر حساب البنك المركزي السعودي ، بإمكانك رفع الطلب الخاص بك عن طريق زيارة الموقع التالي : https://t.co/DtvCdpTRLn.</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE هل يوجد لديكم تمويل عقاري؟</t>
+          <t>@AymanAlHarbiSF @EmiratesNBD_KSA @SAMA_GOV عزيزنا العميل شكراً لتواصلكم عبر حساب البنك المركزي السعودي ، بإمكانك رفع الطلب الخاص بك عن طريق زيارة الموقع التالي : https://t.co/DtvCdpTRLn.</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Do you have mortgage financing?</t>
+          <t>Dear valued customer, thank you for contacting us through the Saudi Central Bank account. You can submit your request by visiting the following website: https://t.co/DtvCdpTRLn.</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -4176,7 +4162,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Do you have mortgage financing?</t>
+          <t>Dear valued customer, thank you for contacting us through the Saudi Central Bank account. • You can submit your request by visiting the following website: https://t.co/DtvCdpTRLn.</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -4189,7 +4175,7 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>Sd67239684</t>
+          <t>SAMAcares, AymanAlHarbiSF, EmiratesNBD_KSA</t>
         </is>
       </c>
     </row>
@@ -4199,43 +4185,44 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2038875337212170347</t>
+          <t>2038884890695831893</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://x.com/SAMAcares/status/2038875337212170347</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2038884890695831893</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://x.com/SAMAcares</t>
+          <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SAMAcares</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SAMACares | ساما تهتم</t>
+          <t>Emirates NBD</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2008124521111252992/bcIs6E4Y_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>عزيزنا العميل شكراً لتواصلكم عبر حساب البنك المركزي السعودي ، بإمكانك رفع الطلب الخاص بك عن طريق زيارة الموقع التالي : complaints-consumer.sama.gov….</t>
+          <t>@EmiratesNBD_AE هل يوجد لديكم تمويل عقاري؟</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>عزيزنا العميل شكراً لتواصلكم عبر حساب البنك المركزي السعودي ، بإمكانك رفع الطلب الخاص بك عن طريق زيارة الموقع التالي : &lt;a href="https://complaints-consumer.sama.gov.sa"&gt;complaints-consumer.sama.gov…&lt;/a&gt;.</t>
+          <t>نشكركم على اهتمامكم بمنتجاتنا، يرجى زيارة الرابط أدناه وملء بياناتكم وسيتصل بكم فريق المبيعات لدينا في غضون يومي عمل.
+&lt;a href="http://ms.spr.ly/6015QxfsS"&gt;ms.spr.ly/6015QxfsS&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K24" t="b">
@@ -4244,7 +4231,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>['AymanAlHarbiSF', 'EmiratesNBD_KSA', 'SAMA_GOV']</t>
+          <t>['Sd67239684']</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -4254,20 +4241,20 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 7:05 AM UTC</t>
+          <t>Mar 31, 2026 · 7:43 AM UTC</t>
         </is>
       </c>
       <c r="P24" s="2" t="n">
-        <v>46112.29513888889</v>
+        <v>46112.32152777778</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
-          <t>['https://complaints-consumer.sama.gov.sa']</t>
+          <t>['http://ms.spr.ly/6015QxfsS']</t>
         </is>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
         <v>0</v>
@@ -4276,7 +4263,7 @@
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
@@ -4285,19 +4272,28 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>عزيزنا العميل شكراً لتواصلكم عبر حساب البنك المركزي السعودي ، بإمكانك رفع الطلب الخاص بك عن طريق زيارة الموقع التالي : complaints-consumer.sama.gov….</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
+          <t>نشكركم على اهتمامكم بمنتجاتنا، يرجى زيارة الرابط أدناه وملء بياناتكم وسيتصل بكم فريق المبيعات لدينا في غضون يومي عمل.
+ms.spr.ly/6015QxfsS</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2038884890695831893</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE هل يوجد لديكم تمويل عقاري؟</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>عزيزنا العميل شكراً لتواصلكم عبر حساب البنك المركزي السعودي ، بإمكانك رفع الطلب الخاص بك عن طريق زيارة الموقع التالي : complaints-consumer.sama.gov….</t>
+          <t>@EmiratesNBD_AE هل يوجد لديكم تمويل عقاري؟</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Dear valued customer, thank you for contacting us through the Saudi Central Bank account. You can submit your request by visiting the following website: complaints-consumer.sama.gov….</t>
+          <t>Do you have mortgage financing?</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -4311,7 +4307,7 @@
         </is>
       </c>
       <c r="AE24" s="2" t="n">
-        <v>46112.46180555555</v>
+        <v>46112.48819444444</v>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
@@ -4330,7 +4326,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Dear valued customer, thank you for contacting us through the Saudi Central Bank account. • You can submit your request by visiting the following website: complaints-consumer.sama.gov….</t>
+          <t>Do you have mortgage financing?</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -4343,7 +4339,7 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>AymanAlHarbiSF, EmiratesNBD_KSA, SAMA_GOV</t>
+          <t>Sd67239684</t>
         </is>
       </c>
     </row>
@@ -4353,43 +4349,43 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2038863571656770036</t>
+          <t>2038875337212170347</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2038863571656770036</t>
+          <t>https://x.com/SAMAcares/status/2038875337212170347</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/SAMAcares</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>SAMAcares</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>SAMACares | ساما تهتم</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2008124521111252992/bcIs6E4Y_bigger.jpg</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Thanks</t>
+          <t>عزيزنا العميل شكراً لتواصلكم عبر حساب البنك المركزي السعودي ، بإمكانك رفع الطلب الخاص بك عن طريق زيارة الموقع التالي : complaints-consumer.sama.gov….</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Thanks</t>
+          <t>عزيزنا العميل شكراً لتواصلكم عبر حساب البنك المركزي السعودي ، بإمكانك رفع الطلب الخاص بك عن طريق زيارة الموقع التالي : &lt;a href="https://complaints-consumer.sama.gov.sa"&gt;complaints-consumer.sama.gov…&lt;/a&gt;.</t>
         </is>
       </c>
       <c r="K25" t="b">
@@ -4398,26 +4394,30 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>['ASaleemLaw']</t>
+          <t>['AymanAlHarbiSF', 'EmiratesNBD_KSA', 'SAMA_GOV']</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 6:18 AM UTC</t>
+          <t>Mar 31, 2026 · 7:05 AM UTC</t>
         </is>
       </c>
       <c r="P25" s="2" t="n">
-        <v>46112.2625</v>
+        <v>46112.29513888889</v>
       </c>
       <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>['https://complaints-consumer.sama.gov.sa']</t>
+        </is>
+      </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -4426,7 +4426,7 @@
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -4435,19 +4435,19 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Thanks</t>
+          <t>عزيزنا العميل شكراً لتواصلكم عبر حساب البنك المركزي السعودي ، بإمكانك رفع الطلب الخاص بك عن طريق زيارة الموقع التالي : complaints-consumer.sama.gov….</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>Thanks</t>
+          <t>عزيزنا العميل شكراً لتواصلكم عبر حساب البنك المركزي السعودي ، بإمكانك رفع الطلب الخاص بك عن طريق زيارة الموقع التالي : complaints-consumer.sama.gov….</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Thank you</t>
+          <t>Dear valued customer, thank you for contacting us through the Saudi Central Bank account. You can submit your request by visiting the following website: complaints-consumer.sama.gov….</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -4461,7 +4461,7 @@
         </is>
       </c>
       <c r="AE25" s="2" t="n">
-        <v>46112.42916666667</v>
+        <v>46112.46180555555</v>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Thank you</t>
+          <t>Dear valued customer, thank you for contacting us through the Saudi Central Bank account. • You can submit your request by visiting the following website: complaints-consumer.sama.gov….</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
@@ -4493,7 +4493,7 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>ASaleemLaw</t>
+          <t>AymanAlHarbiSF, EmiratesNBD_KSA, SAMA_GOV</t>
         </is>
       </c>
     </row>
@@ -4503,43 +4503,43 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2038853926556938342</t>
+          <t>2038859041032843469</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2038853926556938342</t>
+          <t>https://x.com/ASaleemLaw/status/2038859041032843469</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/ASaleemLaw</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>ASaleemLaw</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>ASaleem</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Thank you! Our team will check and revert to you.</t>
+          <t>Appreciate</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Thank you! Our team will check and revert to you.</t>
+          <t>Appreciate</t>
         </is>
       </c>
       <c r="K26" t="b">
@@ -4548,7 +4548,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>['ASaleemLaw']</t>
+          <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -4558,11 +4558,11 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 5:40 AM UTC</t>
+          <t>Mar 31, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P26" s="2" t="n">
-        <v>46112.23611111111</v>
+        <v>46112.25</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
@@ -4576,7 +4576,7 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
@@ -4585,19 +4585,19 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Thank you! Our team will check and revert to you.</t>
+          <t>Appreciate</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>Thank you! Our team will check and revert to you.</t>
+          <t>Appreciate</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Thank you! Our team will check and get back to you.</t>
+          <t>Appreciate</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="AE26" s="2" t="n">
-        <v>46112.40277777778</v>
+        <v>46112.41666666666</v>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Our team will check and get back to you.</t>
+          <t>Appreciate</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>ASaleemLaw</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
     </row>
@@ -4653,36 +4653,186 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2038834682196849032</t>
+          <t>2038853926556938342</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2038834682196849032</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2038853926556938342</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA</t>
+          <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>EmiratesNBD_KSA</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>EmiratesNBD KSA</t>
+          <t>Emirates NBD</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427762424385536/iUFFKIOK_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
+        <is>
+          <t>Thank you! Our team will check and revert to you.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Thank you! Our team will check and revert to you.</t>
+        </is>
+      </c>
+      <c r="K27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>['ASaleemLaw']</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Mar 31, 2026 · 5:40 AM UTC</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="n">
+        <v>46112.23611111111</v>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>21</v>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Thank you! Our team will check and revert to you.</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>Thank you! Our team will check and revert to you.</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>Thank you! Our team will check and get back to you.</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE27" s="2" t="n">
+        <v>46112.40277777778</v>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>31-03-2026</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Our team will check and get back to you.</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK27" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>ASaleemLaw</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2038834682196849032</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_KSA/status/2038834682196849032</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_KSA</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_KSA</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>EmiratesNBD KSA</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1762427762424385536/iUFFKIOK_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
         <is>
           <t>اخر تجربة لي في تحقيق شرط دخول صالات المطارات ببطاقات فيزا VISA 🛋️ 💳
 سويت عملية شراء أونلاين بقيمة 364 ريال قطري 🇶🇦
@@ -4698,63 +4848,63 @@
 • وكم أخذت وقت للتفعيل؟</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>مرحباً، نأسف لسماع أنك تواجه تجربة غير سارة. يسعدنا مساعدتك وحلها. يُرجى إرسال التفاصيل الخاصه بشكواك و رقم الهاتف المسجل إلى رسائل الخاص حتي نتمكن من مساعدتك بشكل أفضل</t>
         </is>
       </c>
-      <c r="K27" t="b">
-        <v>0</v>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
+      <c r="K28" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
         <is>
           <t>['Mr_FibO0']</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>23h</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>Mar 31, 2026 · 4:24 AM UTC</t>
         </is>
       </c>
-      <c r="P27" s="2" t="n">
+      <c r="P28" s="2" t="n">
         <v>46112.18333333333</v>
       </c>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
         <v>54</v>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>مرحباً، نأسف لسماع أنك تواجه تجربة غير سارة. يسعدنا مساعدتك وحلها. يُرجى إرسال التفاصيل الخاصه بشكواك و رقم الهاتف المسجل إلى رسائل الخاص حتي نتمكن من مساعدتك بشكل أفضل</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_KSA/status/2038834682196849032</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>اخر تجربة لي في تحقيق شرط دخول صالات المطارات ببطاقات فيزا VISA 🛋️ 💳
 سويت عملية شراء أونلاين بقيمة 364 ريال قطري 🇶🇦
@@ -4770,7 +4920,7 @@
 • وكم أخذت وقت للتفعيل؟</t>
         </is>
       </c>
-      <c r="AA27" t="inlineStr">
+      <c r="AA28" t="inlineStr">
         <is>
           <t>اخر تجربة لي في تحقيق شرط دخول صالات المطارات ببطاقات فيزا VISA 🛋️ 💳
 سويت عملية شراء أونلاين بقيمة 364 ريال قطري 🇶🇦
@@ -4786,7 +4936,7 @@
 • وكم أخذت وقت للتفعيل؟</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
+      <c r="AB28" t="inlineStr">
         <is>
           <t>My last experience in meeting the entry requirement for airport lounges with VISA cards 🛋️ 💳
 I made an online purchase worth 364 Qatari Riyals 🇶🇦 
@@ -4802,89 +4952,89 @@
 • How long did it take for activation?</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
+      <c r="AC28" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="AD27" t="inlineStr">
+      <c r="AD28" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="AE27" s="2" t="n">
+      <c r="AE28" s="2" t="n">
         <v>46112.35</v>
       </c>
-      <c r="AF27" t="inlineStr">
+      <c r="AF28" t="inlineStr">
         <is>
           <t>31-03-2026</t>
         </is>
       </c>
-      <c r="AG27" t="inlineStr">
+      <c r="AG28" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="AH27" t="inlineStr">
+      <c r="AH28" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AI27" t="inlineStr">
+      <c r="AI28" t="inlineStr">
         <is>
           <t>Note that most Infinite cards only offer free entry for one guest. • 🎤 Share your latest experience with us • Was it with Visa or Mastercard? • • How long did it take for activation?</t>
         </is>
       </c>
-      <c r="AJ27" t="inlineStr">
+      <c r="AJ28" t="inlineStr">
         <is>
           <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AK27" t="n">
+      <c r="AK28" t="n">
         <v>2026</v>
       </c>
-      <c r="AL27" t="inlineStr">
+      <c r="AL28" t="inlineStr">
         <is>
           <t>Mr_FibO0</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="B28" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="inlineStr">
         <is>
           <t>2038790469157851494</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>https://x.com/yucaidisplaymfg/status/2038790469157851494</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>https://x.com/yucaidisplaymfg</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>yucaidisplaymfg</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>Yucai Display</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/2033714569294843904/TdGNH-a9_bigger.jpg</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
         <is>
           <t>•Customize portable fabric counter -factory direct
 •DM for full catalog about fabric counter, display racks, banner stands, display shelves,
@@ -4893,7 +5043,7 @@
 •Email: vancead926@gmail.com https://t.co/QAzvDfZtuh</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>•Customize portable fabric counter -factory direct
 •DM for full catalog about fabric counter, display racks, banner stands, display shelves,
@@ -4902,44 +5052,44 @@
 •Email: vancead926@gmail.com</t>
         </is>
       </c>
-      <c r="K28" t="b">
-        <v>0</v>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
+      <c r="K29" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
         <is>
           <t>Mar 31</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>Mar 31, 2026 · 1:28 AM UTC</t>
         </is>
       </c>
-      <c r="P28" s="2" t="n">
+      <c r="P29" s="2" t="n">
         <v>46112.06111111111</v>
       </c>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
         <v>6</v>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>•Customize portable fabric counter -factory direct
 •DM for full catalog about fabric counter, display racks, banner stands, display shelves,
@@ -4948,12 +5098,12 @@
 •Email: vancead926@gmail.com</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>https://x.com/yucaidisplaymfg/status/2038790469157851494</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>•Customize portable fabric counter -factory direct
 •DM for full catalog about fabric counter, display racks, banner stands, display shelves,
@@ -4962,7 +5112,7 @@
 •Email: vancead926@gmail.com https://t.co/QAzvDfZtuh</t>
         </is>
       </c>
-      <c r="AA28" t="inlineStr">
+      <c r="AA29" t="inlineStr">
         <is>
           <t>•Customize portable fabric counter -factory direct
 •DM for full catalog about fabric counter, display racks, banner stands, display shelves,
@@ -4971,7 +5121,7 @@
 •Email: vancead926@gmail.com https://t.co/QAzvDfZtuh</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
+      <c r="AB29" t="inlineStr">
         <is>
           <t>•Customize portable fabric counter - factory direct  
 •DM for full catalog about fabric counter, display racks, banner stands, display shelves,  
@@ -4980,205 +5130,42 @@
 •Email: vancead926@gmail.com https://t.co/QAzvDfZtuh</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
+      <c r="AC29" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="AD28" t="inlineStr">
+      <c r="AD29" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="AE28" s="2" t="n">
+      <c r="AE29" s="2" t="n">
         <v>46112.22777777778</v>
       </c>
-      <c r="AF28" t="inlineStr">
+      <c r="AF29" t="inlineStr">
         <is>
           <t>31-03-2026</t>
         </is>
       </c>
-      <c r="AG28" t="inlineStr">
+      <c r="AG29" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="AH28" t="inlineStr">
+      <c r="AH29" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AI28" t="inlineStr">
+      <c r="AI29" t="inlineStr">
         <is>
           <t>•WA: +86 13651815206 •Email: vancead926@gmail.com https://t.co/QAzvDfZtuh</t>
         </is>
       </c>
-      <c r="AJ28" t="inlineStr">
+      <c r="AJ29" t="inlineStr">
         <is>
           <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AK28" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2039029089705591194</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2039029089705591194</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>انجاز جديد يضاف إلى مسيرة التمويل طويل الأجل، حيث يواصل الإمارات الإسلامي تعزيز قوته المالية من خلال الإتمام الناجح لتسهيل تمويل جماعي لمدة خمس سنوات.
-اقرأ المقال هنا:  https://t.co/66GzGPXmCh https://t.co/a9ATCYQMae</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Another milestone in long‑term funding. Emirates Islamic reinforces its financial strength with the successful completion of a 5‑year club financing facility.
-Read the article here:- &lt;a href="https://www.emiratesislamic.ae/en/news-and-updates/2026/March/emirates-islamic-concludes-five-year-club-commodity-murabaha-term-facility"&gt;emiratesislamic.ae/en/news-a…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K29" t="b">
-        <v>0</v>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>10h</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>Mar 31, 2026 · 5:16 PM UTC</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="n">
-        <v>46112.71944444445</v>
-      </c>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/news-and-updates/2026/March/emirates-islamic-concludes-five-year-club-commodity-murabaha-term-facility']</t>
-        </is>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1</v>
-      </c>
-      <c r="V29" t="n">
-        <v>76</v>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>Another milestone in long‑term funding. Emirates Islamic reinforces its financial strength with the successful completion of a 5‑year club financing facility.
-Read the article here:- emiratesislamic.ae/en/news-a…</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2039029089705591194</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>انجاز جديد يضاف إلى مسيرة التمويل طويل الأجل، حيث يواصل الإمارات الإسلامي تعزيز قوته المالية من خلال الإتمام الناجح لتسهيل تمويل جماعي لمدة خمس سنوات.
-اقرأ المقال هنا:  https://t.co/66GzGPXmCh https://t.co/a9ATCYQMae</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>انجاز جديد يضاف إلى مسيرة التمويل طويل الأجل، حيث يواصل الإمارات الإسلامي تعزيز قوته المالية من خلال الإتمام الناجح لتسهيل تمويل جماعي لمدة خمس سنوات.
-اقرأ المقال هنا:  https://t.co/66GzGPXmCh https://t.co/a9ATCYQMae</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>A new achievement is added to the long-term financing journey, as Emirates Islamic continues to strengthen its financial position by successfully completing a five-year syndicated financing facility.</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="AE29" s="2" t="n">
-        <v>46112.88611111111</v>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>31-03-2026</t>
-        </is>
-      </c>
-      <c r="AG29" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>A new achievement is added to the long-term financing journey, as Emirates Islamic continues to strengthen its financial position by successfully completing a five-year syndicated financing facility.</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AK29" t="n">
@@ -5196,12 +5183,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2039029079148536148</t>
+          <t>2039029089705591194</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2039029079148536148</t>
+          <t>https://x.com/emiratesislamic/status/2039029089705591194</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5226,6 +5213,160 @@
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
+        <is>
+          <t>Another milestone in long‑term funding. Emirates Islamic reinforces its financial strength with the successful completion of a 5‑year club financing facility.
+Read the article here:- emiratesislamic.ae/en/news-a…</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Another milestone in long‑term funding. Emirates Islamic reinforces its financial strength with the successful completion of a 5‑year club financing facility.
+Read the article here:- &lt;a href="https://www.emiratesislamic.ae/en/news-and-updates/2026/March/emirates-islamic-concludes-five-year-club-commodity-murabaha-term-facility"&gt;emiratesislamic.ae/en/news-a…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>10h</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Mar 31, 2026 · 5:16 PM UTC</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="n">
+        <v>46112.71944444445</v>
+      </c>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/news-and-updates/2026/March/emirates-islamic-concludes-five-year-club-commodity-murabaha-term-facility']</t>
+        </is>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
+      </c>
+      <c r="V30" t="n">
+        <v>76</v>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Another milestone in long‑term funding. Emirates Islamic reinforces its financial strength with the successful completion of a 5‑year club financing facility.
+Read the article here:- emiratesislamic.ae/en/news-a…</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>Another milestone in long‑term funding. Emirates Islamic reinforces its financial strength with the successful completion of a 5‑year club financing facility.
+Read the article here:- emiratesislamic.ae/en/news-a…</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>Another milestone in long-term funding. Emirates Islamic reinforces its financial strength with the successful completion of a 5-year club financing facility.</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Bank</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AE30" s="2" t="n">
+        <v>46112.88611111111</v>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>31-03-2026</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>2. Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Emirates Islamic reinforces its financial strength with the successful completion of a 5-year club financing facility. • Another milestone in long-term funding.</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AK30" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2039029079148536148</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2039029079148536148</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
         <is>
           <t>احمي نفسك ومن حولك
 لا تقم بمشاركة رقم التعريف الشخصي، كلمة المرور او رمز التحقق للمرة الواحدة.
@@ -5233,65 +5374,65 @@
 #متحّدون_ضد_الاحتيال مع الإمارات الإسلامي. https://t.co/hEKTgT2FCH</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>انجاز جديد يضاف إلى مسيرة التمويل طويل الأجل، حيث يواصل الإمارات الإسلامي تعزيز قوته المالية من خلال الإتمام الناجح لتسهيل تمويل جماعي لمدة خمس سنوات.
 اقرأ المقال هنا:  &lt;a href="https://www.emiratesislamic.ae/ar/news-and-updates/2026/March/emirates-islamic-concludes-five-year-club-commodity-murabaha-term-facility"&gt;emiratesislamic.ae/ar/news-a…&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K30" t="b">
-        <v>0</v>
-      </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr">
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
         <is>
           <t>10h</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>Mar 31, 2026 · 5:16 PM UTC</t>
         </is>
       </c>
-      <c r="P30" s="2" t="n">
+      <c r="P31" s="2" t="n">
         <v>46112.71944444445</v>
       </c>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr">
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
         <is>
           <t>['https://www.emiratesislamic.ae/ar/news-and-updates/2026/March/emirates-islamic-concludes-five-year-club-commodity-murabaha-term-facility']</t>
         </is>
       </c>
-      <c r="S30" t="n">
+      <c r="S31" t="n">
         <v>1</v>
       </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
         <v>1</v>
       </c>
-      <c r="V30" t="n">
+      <c r="V31" t="n">
         <v>99</v>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>انجاز جديد يضاف إلى مسيرة التمويل طويل الأجل، حيث يواصل الإمارات الإسلامي تعزيز قوته المالية من خلال الإتمام الناجح لتسهيل تمويل جماعي لمدة خمس سنوات.
 اقرأ المقال هنا:  emiratesislamic.ae/ar/news-a…</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="Y31" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2039029079148536148</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
+      <c r="Z31" t="inlineStr">
         <is>
           <t>احمي نفسك ومن حولك
 لا تقم بمشاركة رقم التعريف الشخصي، كلمة المرور او رمز التحقق للمرة الواحدة.
@@ -5299,7 +5440,7 @@
 #متحّدون_ضد_الاحتيال مع الإمارات الإسلامي. https://t.co/hEKTgT2FCH</t>
         </is>
       </c>
-      <c r="AA30" t="inlineStr">
+      <c r="AA31" t="inlineStr">
         <is>
           <t>احمي نفسك ومن حولك
 لا تقم بمشاركة رقم التعريف الشخصي، كلمة المرور او رمز التحقق للمرة الواحدة.
@@ -5307,95 +5448,94 @@
 #متحّدون_ضد_الاحتيال مع الإمارات الإسلامي. https://t.co/hEKTgT2FCH</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>Protect yourself and those around you. Do not share your PIN, password, or verification code even once. Don't fall into the trap. Beware of fraud. 
-#United_Against_Fraud with Emirates Islamic.</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>Protect yourself and those around you. Do not share your PIN, password, or one-time verification code. Don't fall into the trap. Beware of fraud.</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
         <is>
           <t>Bank</t>
         </is>
       </c>
-      <c r="AD30" t="inlineStr">
+      <c r="AD31" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="AE30" s="2" t="n">
+      <c r="AE31" s="2" t="n">
         <v>46112.88611111111</v>
       </c>
-      <c r="AF30" t="inlineStr">
+      <c r="AF31" t="inlineStr">
         <is>
           <t>31-03-2026</t>
         </is>
       </c>
-      <c r="AG30" t="inlineStr">
+      <c r="AG31" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="AH30" t="inlineStr">
+      <c r="AH31" t="inlineStr">
         <is>
           <t>2. Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>Do not share your PIN, password, or verification code even once. • #United_Against_Fraud with Emirates Islamic. • Protect yourself and those around you.</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Do not share your PIN, password, or one-time verification code. • Protect yourself and those around you. • Don't fall into the trap.</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
         <is>
           <t>Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
-      <c r="AK30" t="n">
+      <c r="AK31" t="n">
         <v>2026</v>
       </c>
-      <c r="AL30" t="inlineStr">
+      <c r="AL31" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="1" t="n">
-        <v>29</v>
-      </c>
-      <c r="B31" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="inlineStr">
         <is>
           <t>2039017522863669449</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>https://x.com/nasnews_e/status/2039017522863669449</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>https://x.com/nasnews_e</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>nasnews_e</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>Nas News Emirates</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/2034790571630575616/O8W30no3_bigger.jpg</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr">
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
         <is>
           <t>The 23rd #Dubai International Arabian Horse Championship is set to welcome 155 horses from 12 countries, bringing together some of the world’s finest Arabian breeds 
 Taking place from 3–5 April at the Dubai World Trade Centre, the event highlights Dubai’s global status in equestrian excellence and showcases top owners and breeders from across the region and beyond.
@@ -5403,7 +5543,7 @@
 #UAE | #nas_news_emirates</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>&lt;a href="/search?f=tweets&amp;amp;q=%23Emirates"&gt;#Emirates&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23NBD"&gt;#NBD&lt;/a&gt; has successfully closed a US$2.25 billion long-term financing transaction, reinforcing its strong credit profile and market confidence.
 The deal includes a US$1.75 billion oversubscribed sustainability-linked loan and a US$500 million Murabaha facility arranged through Emirates Islamic.
@@ -5411,48 +5551,48 @@
 &lt;a href="/search?f=tweets&amp;amp;q=%23UAE"&gt;#UAE&lt;/a&gt; | &lt;a href="/search?f=tweets&amp;amp;q=%23nas_news_emirates"&gt;#nas_news_emirates&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K31" t="b">
-        <v>0</v>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
+      <c r="K32" t="b">
+        <v>0</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
         <is>
           <t>11h</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>Mar 31, 2026 · 4:30 PM UTC</t>
         </is>
       </c>
-      <c r="P31" s="2" t="n">
+      <c r="P32" s="2" t="n">
         <v>46112.6875</v>
       </c>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr">
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
         <is>
           <t>['https://x.com/search?f=tweets&amp;q=%23Emirates', 'https://x.com/search?f=tweets&amp;q=%23NBD', 'https://x.com/search?f=tweets&amp;q=%23UAE', 'https://x.com/search?f=tweets&amp;q=%23nas_news_emirates']</t>
         </is>
       </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
         <v>32</v>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>#Emirates #NBD has successfully closed a US$2.25 billion long-term financing transaction, reinforcing its strong credit profile and market confidence.
 The deal includes a US$1.75 billion oversubscribed sustainability-linked loan and a US$500 million Murabaha facility arranged through Emirates Islamic.
@@ -5460,12 +5600,12 @@
 #UAE | #nas_news_emirates</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>https://x.com/nasnews_e/status/2039017522863669449</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>The 23rd #Dubai International Arabian Horse Championship is set to welcome 155 horses from 12 countries, bringing together some of the world’s finest Arabian breeds 
 Taking place from 3–5 April at the Dubai World Trade Centre, the event highlights Dubai’s global status in equestrian excellence and showcases top owners and breeders from across the region and beyond.
@@ -5473,7 +5613,7 @@
 #UAE | #nas_news_emirates</t>
         </is>
       </c>
-      <c r="AA31" t="inlineStr">
+      <c r="AA32" t="inlineStr">
         <is>
           <t>The 23rd #Dubai International Arabian Horse Championship is set to welcome 155 horses from 12 countries, bringing together some of the world’s finest Arabian breeds 
 Taking place from 3–5 April at the Dubai World Trade Centre, the event highlights Dubai’s global status in equestrian excellence and showcases top owners and breeders from across the region and beyond.
@@ -5481,94 +5621,94 @@
 #UAE | #nas_news_emirates</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>The 23rd Dubai International Arabian Horse Championship is set to welcome 155 horses from 12 countries, bringing together some of the world’s finest Arabian breeds. Taking place from 3–5 April at the Dubai World Trade Centre, the event highlights Dubai’s global status in equestrian excellence and showcases top owners and breeders from across the region and beyond. With strong international participation, the championship continues to play a key role in celebrating and advancing the beauty and heritage of Arabian horses.</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>The 23rd Dubai International Arabian Horse Championship is set to welcome 155 horses from 12 countries, bringing together some of the world’s finest Arabian breeds. Taking place from April 3 to 5 at the Dubai World Trade Centre, the event highlights Dubai’s global status in equestrian excellence and showcases top owners and breeders from across the region and beyond. With strong international participation, the championship continues to play a key role in celebrating and advancing the beauty and heritage of Arabian horses.</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="AD31" t="inlineStr">
+      <c r="AD32" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="AE31" s="2" t="n">
+      <c r="AE32" s="2" t="n">
         <v>46112.85416666666</v>
       </c>
-      <c r="AF31" t="inlineStr">
+      <c r="AF32" t="inlineStr">
         <is>
           <t>31-03-2026</t>
         </is>
       </c>
-      <c r="AG31" t="inlineStr">
+      <c r="AG32" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="AH31" t="inlineStr">
+      <c r="AH32" t="inlineStr">
         <is>
           <t>2. Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
-      <c r="AI31" t="inlineStr">
+      <c r="AI32" t="inlineStr">
         <is>
           <t>The 23rd Dubai International Arabian Horse Championship is set to welcome 155 horses from 12 countries, bringing together some of the world’s finest Arabian breeds. • With strong international participation, the championship continues to play a key role in celebrating and advancing the beauty and heritage of Arabian horses.</t>
         </is>
       </c>
-      <c r="AJ31" t="inlineStr">
+      <c r="AJ32" t="inlineStr">
         <is>
           <t>Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
-      <c r="AK31" t="n">
+      <c r="AK32" t="n">
         <v>2026</v>
       </c>
-      <c r="AL31" t="inlineStr">
+      <c r="AL32" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="1" t="n">
-        <v>30</v>
-      </c>
-      <c r="B32" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="inlineStr">
         <is>
           <t>2038995248009842862</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2038995248009842862</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>EmiratesNBD_AE</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>Emirates NBD</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr">
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
         <is>
           <t>At Emirates NBD, we are committed to staying at the forefront of digital transformation. By partnering with AlphaSense, we’re equipping our teams with cutting-edge AI to surface high-value insights and drive faster, smarter decisions.
 Hear directly from our experts on how this technology is redefining our research and strategy.
@@ -5576,7 +5716,7 @@
 تعرّفوا على آراء خبرائنا حول الدور الذي تلعبه هذه التقنية في إعادة صياغة مستقبل صناعة القرار.</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>Emirates NBD Group has successfully closed a USD 2.25 billion long‑term financing - one of the largest syndicated borrowings in the GCC.
 The transaction includes a USD 1.75 billion sustainability‑linked syndicated loan, alongside a USD 500 million five‑year Club Commodity Murabaha facility by &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; .
@@ -5585,48 +5725,48 @@
 &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBD"&gt;#EmiratesNBD&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Banking"&gt;#Banking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23CapitalMarkets"&gt;#CapitalMarkets&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SustainableFinance"&gt;#SustainableFinance&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23UAE"&gt;#UAE&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K32" t="b">
-        <v>0</v>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
+      <c r="K33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
         <is>
           <t>12h</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>Mar 31, 2026 · 3:02 PM UTC</t>
         </is>
       </c>
-      <c r="P32" s="2" t="n">
+      <c r="P33" s="2" t="n">
         <v>46112.62638888889</v>
       </c>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr">
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
         <is>
           <t>['https://x.com/emiratesislamic', 'https://www.emiratesnbd.com/en/media-center/emirates-nbd-group-successfully-closes-usd-2-25-billion-in-long-term-financing', 'https://x.com/search?f=tweets&amp;q=%23EmiratesNBD', 'https://x.com/search?f=tweets&amp;q=%23Banking', 'https://x.com/search?f=tweets&amp;q=%23CapitalMarkets', 'https://x.com/search?f=tweets&amp;q=%23SustainableFinance', 'https://x.com/search?f=tweets&amp;q=%23UAE']</t>
         </is>
       </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
         <v>7</v>
       </c>
-      <c r="U32" t="n">
+      <c r="U33" t="n">
         <v>11</v>
       </c>
-      <c r="V32" t="n">
+      <c r="V33" t="n">
         <v>1097</v>
       </c>
-      <c r="W32" t="inlineStr">
+      <c r="W33" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>Emirates NBD Group has successfully closed a USD 2.25 billion long‑term financing - one of the largest syndicated borrowings in the GCC.
 The transaction includes a USD 1.75 billion sustainability‑linked syndicated loan, alongside a USD 500 million five‑year Club Commodity Murabaha facility by @emiratesislamic .
@@ -5635,12 +5775,12 @@
 #EmiratesNBD #Banking #CapitalMarkets #SustainableFinance #UAE</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr">
+      <c r="Y33" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2038995248009842862</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
+      <c r="Z33" t="inlineStr">
         <is>
           <t>At Emirates NBD, we are committed to staying at the forefront of digital transformation. By partnering with AlphaSense, we’re equipping our teams with cutting-edge AI to surface high-value insights and drive faster, smarter decisions.
 Hear directly from our experts on how this technology is redefining our research and strategy.
@@ -5648,7 +5788,7 @@
 تعرّفوا على آراء خبرائنا حول الدور الذي تلعبه هذه التقنية في إعادة صياغة مستقبل صناعة القرار.</t>
         </is>
       </c>
-      <c r="AA32" t="inlineStr">
+      <c r="AA33" t="inlineStr">
         <is>
           <t>At Emirates NBD, we are committed to staying at the forefront of digital transformation. By partnering with AlphaSense, we’re equipping our teams with cutting-edge AI to surface high-value insights and drive faster, smarter decisions.
 Hear directly from our experts on how this technology is redefining our research and strategy.
@@ -5656,201 +5796,43 @@
 تعرّفوا على آراء خبرائنا حول الدور الذي تلعبه هذه التقنية في إعادة صياغة مستقبل صناعة القرار.</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
+      <c r="AB33" t="inlineStr">
         <is>
           <t>At Emirates NBD, we continue to strengthen our position at the forefront of digital transformation. Through our partnership with AlphaSense, we are equipping our teams with advanced AI tools that enable the extraction of valuable analytical data, accelerating the decision-making process with greater confidence and efficiency.
 Learn about our experts' views on the role this technology plays in reshaping the future of decision-making.</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
+      <c r="AC33" t="inlineStr">
         <is>
           <t>Bank</t>
         </is>
       </c>
-      <c r="AD32" t="inlineStr">
+      <c r="AD33" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="AE32" s="2" t="n">
+      <c r="AE33" s="2" t="n">
         <v>46112.79305555556</v>
       </c>
-      <c r="AF32" t="inlineStr">
+      <c r="AF33" t="inlineStr">
         <is>
           <t>31-03-2026</t>
         </is>
       </c>
-      <c r="AG32" t="inlineStr">
+      <c r="AG33" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="AH32" t="inlineStr">
+      <c r="AH33" t="inlineStr">
         <is>
           <t>2. Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
-      <c r="AI32" t="inlineStr">
+      <c r="AI33" t="inlineStr">
         <is>
           <t>Learn about our experts' views on the role this technology plays in reshaping the future of decision-making. • At Emirates NBD, we continue to strengthen our position at the forefront of digital transformation.</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AK32" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL32" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="n">
-        <v>31</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2038972592858534070</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>https://x.com/gold_hadas/status/2038972592858534070</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>https://x.com/gold_hadas</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>gold_hadas</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Nicholas MOLODYKO, writer</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2026237940993552385/baDKDoMV_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Emirates Islamic successfully concludes its five-year Club Commodity Murabaha term facility https://t.co/S2UswsbF1t</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Emirates Islamic successfully concludes its five-year Club Commodity Murabaha term facility &lt;a href="https://www.zawya.com/en/press-release/companies-news/emirates-islamic-successfully-concludes-its-five-year-club-commodity-murabaha-term-facility-ah1svn56"&gt;zawya.com/en/press-release/c…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K33" t="b">
-        <v>0</v>
-      </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>14h</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>Mar 31, 2026 · 1:32 PM UTC</t>
-        </is>
-      </c>
-      <c r="P33" s="2" t="n">
-        <v>46112.56388888889</v>
-      </c>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>['https://www.zawya.com/en/press-release/companies-news/emirates-islamic-successfully-concludes-its-five-year-club-commodity-murabaha-term-facility-ah1svn56']</t>
-        </is>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>9</v>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>Emirates Islamic successfully concludes its five-year Club Commodity Murabaha term facility zawya.com/en/press-release/c…</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>https://x.com/gold_hadas/status/2038972592858534070</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>Emirates Islamic successfully concludes its five-year Club Commodity Murabaha term facility https://t.co/S2UswsbF1t</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>Emirates Islamic successfully concludes its five-year Club Commodity Murabaha term facility https://t.co/S2UswsbF1t</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>Emirates Islamic successfully concludes its five-year Club Commodity Murabaha term facility.</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD33" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="AE33" s="2" t="n">
-        <v>46112.73055555556</v>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>31-03-2026</t>
-        </is>
-      </c>
-      <c r="AG33" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>Emirates Islamic successfully concludes its five-year Club Commodity Murabaha term facility.</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
@@ -5873,36 +5855,194 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2038970467663368198</t>
+          <t>2038972592858534070</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2038970467663368198</t>
+          <t>https://x.com/gold_hadas/status/2038972592858534070</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/gold_hadas</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>gold_hadas</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Nicholas MOLODYKO, writer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2026237940993552385/baDKDoMV_bigger.jpg</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
+        <is>
+          <t>Emirates Islamic successfully concludes its five-year Club Commodity Murabaha term facility https://t.co/S2UswsbF1t</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Emirates Islamic successfully concludes its five-year Club Commodity Murabaha term facility &lt;a href="https://www.zawya.com/en/press-release/companies-news/emirates-islamic-successfully-concludes-its-five-year-club-commodity-murabaha-term-facility-ah1svn56"&gt;zawya.com/en/press-release/c…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K34" t="b">
+        <v>0</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>14h</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Mar 31, 2026 · 1:32 PM UTC</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="n">
+        <v>46112.56388888889</v>
+      </c>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>['https://www.zawya.com/en/press-release/companies-news/emirates-islamic-successfully-concludes-its-five-year-club-commodity-murabaha-term-facility-ah1svn56']</t>
+        </is>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>9</v>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Emirates Islamic successfully concludes its five-year Club Commodity Murabaha term facility zawya.com/en/press-release/c…</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>https://x.com/gold_hadas/status/2038972592858534070</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>Emirates Islamic successfully concludes its five-year Club Commodity Murabaha term facility https://t.co/S2UswsbF1t</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>Emirates Islamic successfully concludes its five-year Club Commodity Murabaha term facility https://t.co/S2UswsbF1t</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>Emirates Islamic successfully concludes its five-year Club Commodity Murabaha term facility.</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AE34" s="2" t="n">
+        <v>46112.73055555556</v>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>31-03-2026</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>2. Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Emirates Islamic successfully concludes its five-year Club Commodity Murabaha term facility.</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AK34" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL34" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2038970467663368198</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2038970467663368198</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
         <is>
           <t>Protect yourself and those around you.
 Never share your PIN, password, or OTP.
@@ -5910,7 +6050,7 @@
 #EIAgainstFraud #TogetherAgainstFraud</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>Protect yourself and those around you.
 Never share your PIN, password, or OTP.
@@ -5918,48 +6058,48 @@
 &lt;a href="/search?f=tweets&amp;amp;q=%23EIAgainstFraud"&gt;#EIAgainstFraud&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23TogetherAgainstFraud"&gt;#TogetherAgainstFraud&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K34" t="b">
-        <v>0</v>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr">
+      <c r="K35" t="b">
+        <v>0</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
         <is>
           <t>14h</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>Mar 31, 2026 · 1:23 PM UTC</t>
         </is>
       </c>
-      <c r="P34" s="2" t="n">
+      <c r="P35" s="2" t="n">
         <v>46112.55763888889</v>
       </c>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr">
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
         <is>
           <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud']</t>
         </is>
       </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
         <v>1</v>
       </c>
-      <c r="V34" t="n">
+      <c r="V35" t="n">
         <v>65</v>
       </c>
-      <c r="W34" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>Protect yourself and those around you.
 Never share your PIN, password, or OTP.
@@ -5967,12 +6107,12 @@
 #EIAgainstFraud #TogetherAgainstFraud</t>
         </is>
       </c>
-      <c r="Y34" t="inlineStr">
+      <c r="Y35" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2038970467663368198</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
+      <c r="Z35" t="inlineStr">
         <is>
           <t>Protect yourself and those around you.
 Never share your PIN, password, or OTP.
@@ -5980,7 +6120,7 @@
 #EIAgainstFraud #TogetherAgainstFraud</t>
         </is>
       </c>
-      <c r="AA34" t="inlineStr">
+      <c r="AA35" t="inlineStr">
         <is>
           <t>Protect yourself and those around you.
 Never share your PIN, password, or OTP.
@@ -5988,94 +6128,94 @@
 #EIAgainstFraud #TogetherAgainstFraud</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
+      <c r="AB35" t="inlineStr">
         <is>
           <t>Protect yourself and those around you. Never share your PIN, password, or OTP. Do not fall for the traps. Stay alert to scams.</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
+      <c r="AC35" t="inlineStr">
         <is>
           <t>Bank</t>
         </is>
       </c>
-      <c r="AD34" t="inlineStr">
+      <c r="AD35" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="AE34" s="2" t="n">
+      <c r="AE35" s="2" t="n">
         <v>46112.72430555556</v>
       </c>
-      <c r="AF34" t="inlineStr">
+      <c r="AF35" t="inlineStr">
         <is>
           <t>31-03-2026</t>
         </is>
       </c>
-      <c r="AG34" t="inlineStr">
+      <c r="AG35" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="AH34" t="inlineStr">
+      <c r="AH35" t="inlineStr">
         <is>
           <t>2. Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
-      <c r="AI34" t="inlineStr">
+      <c r="AI35" t="inlineStr">
         <is>
           <t>Never share your PIN, password, or OTP. • Protect yourself and those around you. • Do not fall for the traps.</t>
         </is>
       </c>
-      <c r="AJ34" t="inlineStr">
+      <c r="AJ35" t="inlineStr">
         <is>
           <t>Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
-      <c r="AK34" t="n">
+      <c r="AK35" t="n">
         <v>2026</v>
       </c>
-      <c r="AL34" t="inlineStr">
+      <c r="AL35" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="1" t="n">
-        <v>33</v>
-      </c>
-      <c r="B35" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="inlineStr">
         <is>
           <t>2038970465432011060</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2038970465432011060</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>emiratesislamic</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>emiratesislamic</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr">
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
         <is>
           <t>احمي نفسك ومن حولك
 لا تقم بمشاركة رقم التعريف الشخصي، كلمة المرور او رمز التحقق للمرة الواحدة.
@@ -6083,7 +6223,7 @@
 #متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>احمي نفسك ومن حولك
 لا تقم بمشاركة رقم التعريف الشخصي، كلمة المرور او رمز التحقق للمرة الواحدة.
@@ -6091,48 +6231,48 @@
 &lt;a href="/search?f=tweets&amp;amp;q=%23متحّدون_ضد_الاحتيال"&gt;#متحّدون_ضد_الاحتيال&lt;/a&gt; مع الإمارات الإسلامي.</t>
         </is>
       </c>
-      <c r="K35" t="b">
-        <v>0</v>
-      </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr">
+      <c r="K36" t="b">
+        <v>0</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
         <is>
           <t>14h</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>Mar 31, 2026 · 1:23 PM UTC</t>
         </is>
       </c>
-      <c r="P35" s="2" t="n">
+      <c r="P36" s="2" t="n">
         <v>46112.55763888889</v>
       </c>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr">
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
         <is>
           <t>['https://x.com/search?f=tweets&amp;q=%23متحّدون_ضد_الاحتيال']</t>
         </is>
       </c>
-      <c r="S35" t="n">
+      <c r="S36" t="n">
         <v>1</v>
       </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
         <v>1</v>
       </c>
-      <c r="V35" t="n">
+      <c r="V36" t="n">
         <v>86</v>
       </c>
-      <c r="W35" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>احمي نفسك ومن حولك
 لا تقم بمشاركة رقم التعريف الشخصي، كلمة المرور او رمز التحقق للمرة الواحدة.
@@ -6140,9 +6280,9 @@
 #متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.</t>
         </is>
       </c>
-      <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr"/>
-      <c r="AA35" t="inlineStr">
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr">
         <is>
           <t>احمي نفسك ومن حولك
 لا تقم بمشاركة رقم التعريف الشخصي، كلمة المرور او رمز التحقق للمرة الواحدة.
@@ -6150,206 +6290,48 @@
 #متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
+      <c r="AB36" t="inlineStr">
         <is>
           <t>Protect yourself and those around you. Do not share your PIN, password, or one-time verification code. Don't fall into the trap. Beware of fraud. 
 #United_Against_Fraud with Emirates Islamic.</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
+      <c r="AC36" t="inlineStr">
         <is>
           <t>Bank</t>
         </is>
       </c>
-      <c r="AD35" t="inlineStr">
+      <c r="AD36" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="AE35" s="2" t="n">
+      <c r="AE36" s="2" t="n">
         <v>46112.72430555556</v>
       </c>
-      <c r="AF35" t="inlineStr">
+      <c r="AF36" t="inlineStr">
         <is>
           <t>31-03-2026</t>
         </is>
       </c>
-      <c r="AG35" t="inlineStr">
+      <c r="AG36" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="AH35" t="inlineStr">
+      <c r="AH36" t="inlineStr">
         <is>
           <t>2. Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
-      <c r="AI35" t="inlineStr">
+      <c r="AI36" t="inlineStr">
         <is>
           <t>Do not share your PIN, password, or one-time verification code. • #United_Against_Fraud with Emirates Islamic. • Protect yourself and those around you.</t>
         </is>
       </c>
-      <c r="AJ35" t="inlineStr">
+      <c r="AJ36" t="inlineStr">
         <is>
           <t>Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AK35" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL35" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="n">
-        <v>34</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2038792972549190038</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>https://x.com/ASaleemLaw/status/2038792972549190038</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>https://x.com/ASaleemLaw</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>ASaleemLaw</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>ASaleem</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Now that I’ve requested to cancel the credit card&amp;amp;close the account, I’m being told to wait 45 days.This delay is unacceptable,especially when the issue arose due to unprofessional staff behavior.</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; As a new customer, I’m extremely disappointed with my experience.I was issued a credit card with incorrect information&amp;amp;was misled by staff a fixed account opened without proper clarity or consent.</t>
-        </is>
-      </c>
-      <c r="K36" t="b">
-        <v>0</v>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>Mar 31</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>Mar 31, 2026 · 1:38 AM UTC</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="n">
-        <v>46112.06805555556</v>
-      </c>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>['https://x.com/EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="S36" t="n">
-        <v>3</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="n">
-        <v>11</v>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE As a new customer, I’m extremely disappointed with my experience.I was issued a credit card with incorrect information&amp;was misled by staff a fixed account opened without proper clarity or consent.</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>https://x.com/ASaleemLaw/status/2038792972549190038</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>Now that I’ve requested to cancel the credit card&amp;amp;close the account, I’m being told to wait 45 days.This delay is unacceptable,especially when the issue arose due to unprofessional staff behavior.</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>Now that I’ve requested to cancel the credit card&amp;amp;close the account, I’m being told to wait 45 days.This delay is unacceptable,especially when the issue arose due to unprofessional staff behavior.</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>Now that I’ve requested to cancel the credit card and close the account, I’m being told to wait 45 days. This delay is unacceptable, especially when the issue arose due to unprofessional staff behavior.</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD36" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="AE36" s="2" t="n">
-        <v>46112.23472222222</v>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>31-03-2026</t>
-        </is>
-      </c>
-      <c r="AG36" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>Now that I’ve requested to cancel the credit card and close the account, I’m being told to wait 45 days. • This delay is unacceptable, especially when the issue arose due to unprofessional staff behavior.</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
       <c r="AK36" t="n">
@@ -6367,73 +6349,71 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2039011794040070545</t>
+          <t>2038792972549190038</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://x.com/AbduAlnahari/status/2039011794040070545</t>
+          <t>https://x.com/ASaleemLaw/status/2038792972549190038</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://x.com/AbduAlnahari</t>
+          <t>https://x.com/ASaleemLaw</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AbduAlnahari</t>
+          <t>ASaleemLaw</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Abdulrahman AlNahari</t>
+          <t>ASaleem</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1193479361229459456/3jAF_JGC_bigger.jpg</t>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>اسوأ خدمة عملاء
-اسبوعين ما تقدرو تحدثوا معلومات</t>
+          <t>Now that I’ve requested to cancel the credit card&amp;amp;close the account, I’m being told to wait 45 days.This delay is unacceptable,especially when the issue arose due to unprofessional staff behavior.</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>اسوأ خدمة عملاء
-اسبوعين ما تقدرو تحدثوا معلومات</t>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; As a new customer, I’m extremely disappointed with my experience.I was issued a credit card with incorrect information&amp;amp;was misled by staff a fixed account opened without proper clarity or consent.</t>
         </is>
       </c>
       <c r="K37" t="b">
         <v>0</v>
       </c>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_KSA']</t>
-        </is>
-      </c>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>Mar 31</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 4:07 PM UTC</t>
+          <t>Mar 31, 2026 · 1:38 AM UTC</t>
         </is>
       </c>
       <c r="P37" s="2" t="n">
-        <v>46112.67152777778</v>
+        <v>46112.06805555556</v>
       </c>
       <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -6442,7 +6422,7 @@
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
@@ -6451,21 +6431,27 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>اسوأ خدمة عملاء
-اسبوعين ما تقدرو تحدثوا معلومات</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="inlineStr"/>
+          <t>@EmiratesNBD_AE As a new customer, I’m extremely disappointed with my experience.I was issued a credit card with incorrect information&amp;was misled by staff a fixed account opened without proper clarity or consent.</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>https://x.com/ASaleemLaw/status/2038792972549190038</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>Now that I’ve requested to cancel the credit card&amp;amp;close the account, I’m being told to wait 45 days.This delay is unacceptable,especially when the issue arose due to unprofessional staff behavior.</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>اسوأ خدمة عملاء
-اسبوعين ما تقدرو تحدثوا معلومات</t>
+          <t>Now that I’ve requested to cancel the credit card&amp;amp;close the account, I’m being told to wait 45 days.This delay is unacceptable,especially when the issue arose due to unprofessional staff behavior.</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>Worst customer service. It's been two weeks and you can't update the information.</t>
+          <t>Now that I’ve requested to cancel the credit card and close the account, I’m being told to wait 45 days. This delay is unacceptable, especially when the issue arose due to unprofessional staff behavior.</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -6479,7 +6465,7 @@
         </is>
       </c>
       <c r="AE37" s="2" t="n">
-        <v>46112.83819444444</v>
+        <v>46112.23472222222</v>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
@@ -6498,7 +6484,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>It's been two weeks and you can't update the information.</t>
+          <t>Now that I’ve requested to cancel the credit card and close the account, I’m being told to wait 45 days. • This delay is unacceptable, especially when the issue arose due to unprofessional staff behavior.</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -6511,7 +6497,7 @@
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>EmiratesNBD_KSA</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -6521,44 +6507,45 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2038903815626281446</t>
+          <t>2039011794040070545</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://x.com/AymanAlHarbiSF/status/2038903815626281446</t>
+          <t>https://x.com/AbduAlnahari/status/2039011794040070545</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://x.com/AymanAlHarbiSF</t>
+          <t>https://x.com/AbduAlnahari</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AymanAlHarbiSF</t>
+          <t>AbduAlnahari</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>AymanAlHarbi-SF</t>
+          <t>Abdulrahman AlNahari</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/646693781132152832/IIqkzitH_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1193479361229459456/3jAF_JGC_bigger.jpg</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA @SAMA_GOV 
-لدي بطاقة فيزا وأرغب في إلغائها. تواصلت عبر الهاتف المصرفي، لكن لم أجد أي خيار مخصص لبطاقات الفيزا. كما أن حسابي في التطبيق لا يعمل ولا أتمكن من تسجيل الدخول لمعرفة حالة البطاقة أو إدارتها. وتم اجباري على دفع مبلغ للبطاقة ما غير تنبهي بموعد السداد</t>
+          <t>اسوأ خدمة عملاء
+اسبوعين ما تقدرو تحدثوا معلومات</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>عزيزي تم الرد و التواصل و البطاقة لم تلغى و طلبتوا مبلغ تجديد البطاقة و البطاقة و الحساب مغلق من شهر ٣ ٢٠٢٥</t>
+          <t>اسوأ خدمة عملاء
+اسبوعين ما تقدرو تحدثوا معلومات</t>
         </is>
       </c>
       <c r="K38" t="b">
@@ -6572,21 +6559,21 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 8:58 AM UTC</t>
+          <t>Mar 31, 2026 · 4:07 PM UTC</t>
         </is>
       </c>
       <c r="P38" s="2" t="n">
-        <v>46112.37361111111</v>
+        <v>46112.67152777778</v>
       </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
@@ -6595,7 +6582,7 @@
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
@@ -6604,29 +6591,21 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>عزيزي تم الرد و التواصل و البطاقة لم تلغى و طلبتوا مبلغ تجديد البطاقة و البطاقة و الحساب مغلق من شهر ٣ ٢٠٢٥</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>https://x.com/AymanAlHarbiSF/status/2038903815626281446</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_KSA @SAMA_GOV 
-لدي بطاقة فيزا وأرغب في إلغائها. تواصلت عبر الهاتف المصرفي، لكن لم أجد أي خيار مخصص لبطاقات الفيزا. كما أن حسابي في التطبيق لا يعمل ولا أتمكن من تسجيل الدخول لمعرفة حالة البطاقة أو إدارتها. وتم اجباري على دفع مبلغ للبطاقة ما غير تنبهي بموعد السداد</t>
-        </is>
-      </c>
+          <t>اسوأ خدمة عملاء
+اسبوعين ما تقدرو تحدثوا معلومات</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA @SAMA_GOV 
-لدي بطاقة فيزا وأرغب في إلغائها. تواصلت عبر الهاتف المصرفي، لكن لم أجد أي خيار مخصص لبطاقات الفيزا. كما أن حسابي في التطبيق لا يعمل ولا أتمكن من تسجيل الدخول لمعرفة حالة البطاقة أو إدارتها. وتم اجباري على دفع مبلغ للبطاقة ما غير تنبهي بموعد السداد</t>
+          <t>اسوأ خدمة عملاء
+اسبوعين ما تقدرو تحدثوا معلومات</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>I have a Visa card and I want to cancel it. I contacted customer service by phone, but I couldn't find any specific option for Visa cards. Also, my account in the app is not working and I can't log in to check the status of the card or manage it. I was forced to pay an amount for the card without being notified of the payment due date.</t>
+          <t>Worst customer service. It's been two weeks and you can't update the information.</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -6640,7 +6619,7 @@
         </is>
       </c>
       <c r="AE38" s="2" t="n">
-        <v>46112.54027777778</v>
+        <v>46112.83819444444</v>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
@@ -6659,7 +6638,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>I contacted customer service by phone, but I couldn't find any specific option for Visa cards. • Also, my account in the app is not working and I can't log in to check the status of the card or manage it. • I was forced to pay an amount for the card without being notified of the payment due date.</t>
+          <t>It's been two weeks and you can't update the information.</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
@@ -6682,47 +6661,44 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2038848292981715352</t>
+          <t>2038903815626281446</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2038848292981715352</t>
+          <t>https://x.com/AymanAlHarbiSF/status/2038903815626281446</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/AymanAlHarbiSF</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>AymanAlHarbiSF</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>AymanAlHarbi-SF</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/646693781132152832/IIqkzitH_bigger.jpg</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>We sincerely regret for the inconvenience To be able to assist further, we kindly request you to reach out to us at 
-social@emiratesnbd.com 
-Quoting case #990937  in the subject line of the email from your registered email address We will make every effort to address the matter promptly and provide the necessary support. Thanks</t>
+          <t>@EmiratesNBD_KSA @SAMA_GOV 
+لدي بطاقة فيزا وأرغب في إلغائها. تواصلت عبر الهاتف المصرفي، لكن لم أجد أي خيار مخصص لبطاقات الفيزا. كما أن حسابي في التطبيق لا يعمل ولا أتمكن من تسجيل الدخول لمعرفة حالة البطاقة أو إدارتها. وتم اجباري على دفع مبلغ للبطاقة ما غير تنبهي بموعد السداد</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>We sincerely regret for the inconvenience To be able to assist further, we kindly request you to reach out to us at 
-social@emiratesnbd.com 
-Quoting case #990937  in the subject line of the email from your registered email address We will make every effort to address the matter promptly and provide the necessary support. Thanks</t>
+          <t>عزيزي تم الرد و التواصل و البطاقة لم تلغى و طلبتوا مبلغ تجديد البطاقة و البطاقة و الحساب مغلق من شهر ٣ ٢٠٢٥</t>
         </is>
       </c>
       <c r="K39" t="b">
@@ -6731,21 +6707,21 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>['goaroundflaps15']</t>
+          <t>['EmiratesNBD_KSA']</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 5:18 AM UTC</t>
+          <t>Mar 31, 2026 · 8:58 AM UTC</t>
         </is>
       </c>
       <c r="P39" s="2" t="n">
-        <v>46112.22083333333</v>
+        <v>46112.37361111111</v>
       </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
@@ -6759,7 +6735,7 @@
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
@@ -6768,33 +6744,29 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>We sincerely regret for the inconvenience To be able to assist further, we kindly request you to reach out to us at 
-social@emiratesnbd.com 
-Quoting case #990937  in the subject line of the email from your registered email address We will make every effort to address the matter promptly and provide the necessary support. Thanks</t>
+          <t>عزيزي تم الرد و التواصل و البطاقة لم تلغى و طلبتوا مبلغ تجديد البطاقة و البطاقة و الحساب مغلق من شهر ٣ ٢٠٢٥</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2038848292981715352</t>
+          <t>https://x.com/AymanAlHarbiSF/status/2038903815626281446</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>We sincerely regret for the inconvenience To be able to assist further, we kindly request you to reach out to us at 
-social@emiratesnbd.com 
-Quoting case #990937  in the subject line of the email from your registered email address We will make every effort to address the matter promptly and provide the necessary support. Thanks</t>
+          <t>@EmiratesNBD_KSA @SAMA_GOV 
+لدي بطاقة فيزا وأرغب في إلغائها. تواصلت عبر الهاتف المصرفي، لكن لم أجد أي خيار مخصص لبطاقات الفيزا. كما أن حسابي في التطبيق لا يعمل ولا أتمكن من تسجيل الدخول لمعرفة حالة البطاقة أو إدارتها. وتم اجباري على دفع مبلغ للبطاقة ما غير تنبهي بموعد السداد</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>We sincerely regret for the inconvenience To be able to assist further, we kindly request you to reach out to us at 
-social@emiratesnbd.com 
-Quoting case #990937  in the subject line of the email from your registered email address We will make every effort to address the matter promptly and provide the necessary support. Thanks</t>
+          <t>@EmiratesNBD_KSA @SAMA_GOV 
+لدي بطاقة فيزا وأرغب في إلغائها. تواصلت عبر الهاتف المصرفي، لكن لم أجد أي خيار مخصص لبطاقات الفيزا. كما أن حسابي في التطبيق لا يعمل ولا أتمكن من تسجيل الدخول لمعرفة حالة البطاقة أو إدارتها. وتم اجباري على دفع مبلغ للبطاقة ما غير تنبهي بموعد السداد</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>We sincerely regret the inconvenience. To assist you further, we kindly request that you reach out to us at social@emiratesnbd.com, quoting case #990937 in the subject line of the email from your registered email address. We will make every effort to address the matter promptly and provide the necessary support. Thank you.</t>
+          <t>I have a Visa card and I want to cancel it. I contacted customer service by phone, but I couldn't find any specific option for Visa cards. Also, my account in the app is not working and I can't log in to check the status of the card or manage it. I was forced to pay an amount for the card without being notified of the payment due date.</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -6808,7 +6780,7 @@
         </is>
       </c>
       <c r="AE39" s="2" t="n">
-        <v>46112.3875</v>
+        <v>46112.54027777778</v>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
@@ -6827,7 +6799,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>To assist you further, we kindly request that you reach out to us at social@emiratesnbd.com, quoting case #990937 in the subject line of the email from your registered email address. • We will make every effort to address the matter promptly and provide the necessary support. • We sincerely regret the inconvenience.</t>
+          <t>I contacted customer service by phone, but I couldn't find any specific option for Visa cards. • Also, my account in the app is not working and I can't log in to check the status of the card or manage it. • I was forced to pay an amount for the card without being notified of the payment due date.</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
@@ -6840,7 +6812,7 @@
       </c>
       <c r="AL39" t="inlineStr">
         <is>
-          <t>goaroundflaps15</t>
+          <t>EmiratesNBD_KSA</t>
         </is>
       </c>
     </row>
@@ -6850,47 +6822,47 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2038807060091974007</t>
+          <t>2038848292981715352</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://x.com/Mr_FibO0/status/2038807060091974007</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2038848292981715352</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://x.com/Mr_FibO0</t>
+          <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Mr_FibO0</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mr.Fibo</t>
+          <t>Emirates NBD</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2031661540890525696/UwnLAlx7_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA 
-بطاقه اينفينت تجربه فاشله التطبيق يقول دخول زياره لا محدود وبعدها يجي يقول في شرط داخلي طيب ليه تفتح لي الزيارات لا وفوقها حاسب لي 4 زيارات وانا فقط زياره شخصين وشكاوي بدون فائده لعب ع العميل  وبالاخير قلت خلاص باسدد بس خذو حقكم مو 4 ولا يوجد حل منهم 
-@SAMA_GOV</t>
+          <t>We sincerely regret for the inconvenience To be able to assist further, we kindly request you to reach out to us at 
+social@emiratesnbd.com 
+Quoting case #990937  in the subject line of the email from your registered email address We will make every effort to address the matter promptly and provide the necessary support. Thanks</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>&lt;a href="/EmiratesNBD_KSA" title="EmiratesNBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt; 
-بطاقه اينفينت تجربه فاشله التطبيق يقول دخول زياره لا محدود وبعدها يجي يقول في شرط داخلي طيب ليه تفتح لي الزيارات لا وفوقها حاسب لي 4 زيارات وانا فقط زياره شخصين وشكاوي بدون فائده لعب ع العميل  وبالاخير قلت خلاص باسدد بس خذو حقكم مو 4 ولا يوجد حل منهم 
-&lt;a href="/SAMA_GOV" title="SAMA | البنك المركزي السعودي"&gt;@SAMA_GOV&lt;/a&gt;</t>
+          <t>We sincerely regret for the inconvenience To be able to assist further, we kindly request you to reach out to us at 
+social@emiratesnbd.com 
+Quoting case #990937  in the subject line of the email from your registered email address We will make every effort to address the matter promptly and provide the necessary support. Thanks</t>
         </is>
       </c>
       <c r="K40" t="b">
@@ -6899,30 +6871,26 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>['aziz_credit']</t>
+          <t>['goaroundflaps15']</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Mar 31</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 2:34 AM UTC</t>
+          <t>Mar 31, 2026 · 5:18 AM UTC</t>
         </is>
       </c>
       <c r="P40" s="2" t="n">
-        <v>46112.10694444444</v>
+        <v>46112.22083333333</v>
       </c>
       <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>['https://x.com/EmiratesNBD_KSA', 'https://x.com/SAMA_GOV']</t>
-        </is>
-      </c>
+      <c r="R40" t="inlineStr"/>
       <c r="S40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -6931,7 +6899,7 @@
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>360</v>
+        <v>12</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
@@ -6940,23 +6908,33 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA 
-بطاقه اينفينت تجربه فاشله التطبيق يقول دخول زياره لا محدود وبعدها يجي يقول في شرط داخلي طيب ليه تفتح لي الزيارات لا وفوقها حاسب لي 4 زيارات وانا فقط زياره شخصين وشكاوي بدون فائده لعب ع العميل  وبالاخير قلت خلاص باسدد بس خذو حقكم مو 4 ولا يوجد حل منهم 
-@SAMA_GOV</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr"/>
-      <c r="Z40" t="inlineStr"/>
+          <t>We sincerely regret for the inconvenience To be able to assist further, we kindly request you to reach out to us at 
+social@emiratesnbd.com 
+Quoting case #990937  in the subject line of the email from your registered email address We will make every effort to address the matter promptly and provide the necessary support. Thanks</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2038848292981715352</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>We sincerely regret for the inconvenience To be able to assist further, we kindly request you to reach out to us at 
+social@emiratesnbd.com 
+Quoting case #990937  in the subject line of the email from your registered email address We will make every effort to address the matter promptly and provide the necessary support. Thanks</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA 
-بطاقه اينفينت تجربه فاشله التطبيق يقول دخول زياره لا محدود وبعدها يجي يقول في شرط داخلي طيب ليه تفتح لي الزيارات لا وفوقها حاسب لي 4 زيارات وانا فقط زياره شخصين وشكاوي بدون فائده لعب ع العميل  وبالاخير قلت خلاص باسدد بس خذو حقكم مو 4 ولا يوجد حل منهم 
-@SAMA_GOV</t>
+          <t>We sincerely regret for the inconvenience To be able to assist further, we kindly request you to reach out to us at 
+social@emiratesnbd.com 
+Quoting case #990937  in the subject line of the email from your registered email address We will make every effort to address the matter promptly and provide the necessary support. Thanks</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>The Infinite card experience is a failure. The app says unlimited visits, then it says there is an internal condition. Why do you allow me to book visits and then charge me for 4 visits when I only have 2 people visiting? Complaints are useless; it's a game with the customer. In the end, I said fine, I will pay, but take what you deserve, not 4 visits, and there is no solution from them.</t>
+          <t>We sincerely regret the inconvenience. To assist you further, we kindly request that you reach out to us at social@emiratesnbd.com, quoting case #990937 in the subject line of the email from your registered email address. We will make every effort to address the matter promptly and provide the necessary support. Thank you.</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -6970,7 +6948,7 @@
         </is>
       </c>
       <c r="AE40" s="2" t="n">
-        <v>46112.27361111111</v>
+        <v>46112.3875</v>
       </c>
       <c r="AF40" t="inlineStr">
         <is>
@@ -6989,7 +6967,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Why do you allow me to book visits and then charge me for 4 visits when I only have 2 people visiting? • In the end, I said fine, I will pay, but take what you deserve, not 4 visits, and there is no solution from them. • The app says unlimited visits, then it says there is an internal condition.</t>
+          <t>To assist you further, we kindly request that you reach out to us at social@emiratesnbd.com, quoting case #990937 in the subject line of the email from your registered email address. • We will make every effort to address the matter promptly and provide the necessary support. • We sincerely regret the inconvenience.</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
@@ -7002,7 +6980,7 @@
       </c>
       <c r="AL40" t="inlineStr">
         <is>
-          <t>aziz_credit</t>
+          <t>goaroundflaps15</t>
         </is>
       </c>
     </row>
@@ -7012,43 +6990,47 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2038941653596324169</t>
+          <t>2038807060091974007</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://x.com/Saeed_20212/status/2038941653596324169</t>
+          <t>https://x.com/Mr_FibO0/status/2038807060091974007</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://x.com/Saeed_20212</t>
+          <t>https://x.com/Mr_FibO0</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Saeed_20212</t>
+          <t>Mr_FibO0</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>سعيد UAE</t>
+          <t>Mr.Fibo</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1525071063662661637/25A1SNZT_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2031661540890525696/UwnLAlx7_bigger.jpg</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>@emiratesislamic مشكلة غريبة معاكم !؟ممكن حد يتواصل</t>
+          <t>@EmiratesNBD_KSA 
+بطاقه اينفينت تجربه فاشله التطبيق يقول دخول زياره لا محدود وبعدها يجي يقول في شرط داخلي طيب ليه تفتح لي الزيارات لا وفوقها حاسب لي 4 زيارات وانا فقط زياره شخصين وشكاوي بدون فائده لعب ع العميل  وبالاخير قلت خلاص باسدد بس خذو حقكم مو 4 ولا يوجد حل منهم 
+@SAMA_GOV</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>مشكلة غريبة معاكم !؟ممكن حد يتواصل</t>
+          <t>&lt;a href="/EmiratesNBD_KSA" title="EmiratesNBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt; 
+بطاقه اينفينت تجربه فاشله التطبيق يقول دخول زياره لا محدود وبعدها يجي يقول في شرط داخلي طيب ليه تفتح لي الزيارات لا وفوقها حاسب لي 4 زيارات وانا فقط زياره شخصين وشكاوي بدون فائده لعب ع العميل  وبالاخير قلت خلاص باسدد بس خذو حقكم مو 4 ولا يوجد حل منهم 
+&lt;a href="/SAMA_GOV" title="SAMA | البنك المركزي السعودي"&gt;@SAMA_GOV&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K41" t="b">
@@ -7057,24 +7039,28 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>['emiratesislamic']</t>
+          <t>['aziz_credit']</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>Mar 31</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 11:29 AM UTC</t>
+          <t>Mar 31, 2026 · 2:34 AM UTC</t>
         </is>
       </c>
       <c r="P41" s="2" t="n">
-        <v>46112.47847222222</v>
+        <v>46112.10694444444</v>
       </c>
       <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_KSA', 'https://x.com/SAMA_GOV']</t>
+        </is>
+      </c>
       <c r="S41" t="n">
         <v>1</v>
       </c>
@@ -7085,36 +7071,32 @@
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>8</v>
+        <v>360</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>ENBD</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>مشكلة غريبة معاكم !؟ممكن حد يتواصل</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>https://x.com/Saeed_20212/status/2038941653596324169</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>@emiratesislamic مشكلة غريبة معاكم !؟ممكن حد يتواصل</t>
-        </is>
-      </c>
+          <t>@EmiratesNBD_KSA 
+بطاقه اينفينت تجربه فاشله التطبيق يقول دخول زياره لا محدود وبعدها يجي يقول في شرط داخلي طيب ليه تفتح لي الزيارات لا وفوقها حاسب لي 4 زيارات وانا فقط زياره شخصين وشكاوي بدون فائده لعب ع العميل  وبالاخير قلت خلاص باسدد بس خذو حقكم مو 4 ولا يوجد حل منهم 
+@SAMA_GOV</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>@emiratesislamic مشكلة غريبة معاكم !؟ممكن حد يتواصل</t>
+          <t>@EmiratesNBD_KSA 
+بطاقه اينفينت تجربه فاشله التطبيق يقول دخول زياره لا محدود وبعدها يجي يقول في شرط داخلي طيب ليه تفتح لي الزيارات لا وفوقها حاسب لي 4 زيارات وانا فقط زياره شخصين وشكاوي بدون فائده لعب ع العميل  وبالاخير قلت خلاص باسدد بس خذو حقكم مو 4 ولا يوجد حل منهم 
+@SAMA_GOV</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>Strange problem with you! Can someone get in touch?</t>
+          <t>The Infinite card experience is a failure. The app says unlimited visits, then it says there is an internal condition. Why do you allow me to book visits and then charge me for 4 visits when I only have 2 people visiting? Complaints are useless; it's a game with the customer. In the end, I said fine, I will pay, but take your due, not 4 visits, and there is no solution from them.</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -7128,7 +7110,7 @@
         </is>
       </c>
       <c r="AE41" s="2" t="n">
-        <v>46112.64513888889</v>
+        <v>46112.27361111111</v>
       </c>
       <c r="AF41" t="inlineStr">
         <is>
@@ -7137,22 +7119,22 @@
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>ENBD</t>
         </is>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
+          <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Can someone get in touch? • Strange problem with you!</t>
+          <t>Why do you allow me to book visits and then charge me for 4 visits when I only have 2 people visiting? • In the end, I said fine, I will pay, but take your due, not 4 visits, and there is no solution from them. • The app says unlimited visits, then it says there is an internal condition.</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>Emirates Islamic Bank (EIB)</t>
+          <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
       <c r="AK41" t="n">
@@ -7160,7 +7142,7 @@
       </c>
       <c r="AL41" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>aziz_credit</t>
         </is>
       </c>
     </row>
@@ -7170,43 +7152,43 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2038954812801191946</t>
+          <t>2038941653596324169</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://x.com/SultanAlhreago/status/2038954812801191946</t>
+          <t>https://x.com/Saeed_20212/status/2038941653596324169</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://x.com/SultanAlhreago</t>
+          <t>https://x.com/Saeed_20212</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SultanAlhreago</t>
+          <t>Saeed_20212</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sultan Al hrbi</t>
+          <t>سعيد UAE</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1525071063662661637/25A1SNZT_bigger.jpg</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE من اسوا البنوك . جيتهم باخذ تمويل وكان راتبي على الراجحي فقالوا اذا تحول الراتب علينا نعطيك نسبة 1:85 . ولما حولت الراتب عليهم قلت يلا ابغى التمويل على اساس انه 1:85  . فقالوا لا نعطيك تمويل بنسبة 3:49 . ليه اللعب هذا بعد ماتعبت وحولت الراتب غيروا كلامهم . حسبي الله ونعم الوكيل</t>
+          <t>@emiratesislamic مشكلة غريبة معاكم !؟ممكن حد يتواصل</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>من اسوا البنوك . جيتهم باخذ تمويل وكان راتبي على الراجحي فقالوا اذا تحول الراتب علينا نعطيك نسبة 1:85 . ولما حولت الراتب عليهم قلت يلا ابغى التمويل على اساس انه 1:85  . فقالوا لا نعطيك تمويل بنسبة 3:49 . ليه اللعب هذا بعد ماتعبت وحولت الراتب غيروا كلامهم . حسبي الله ونعم الوكيل</t>
+          <t>مشكلة غريبة معاكم !؟ممكن حد يتواصل</t>
         </is>
       </c>
       <c r="K42" t="b">
@@ -7215,21 +7197,21 @@
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>['EmiratesNBD_AE']</t>
+          <t>['emiratesislamic']</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 12:21 PM UTC</t>
+          <t>Mar 31, 2026 · 11:29 AM UTC</t>
         </is>
       </c>
       <c r="P42" s="2" t="n">
-        <v>46112.51458333333</v>
+        <v>46112.47847222222</v>
       </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
@@ -7237,42 +7219,42 @@
         <v>1</v>
       </c>
       <c r="T42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>من اسوا البنوك . جيتهم باخذ تمويل وكان راتبي على الراجحي فقالوا اذا تحول الراتب علينا نعطيك نسبة 1:85 . ولما حولت الراتب عليهم قلت يلا ابغى التمويل على اساس انه 1:85  . فقالوا لا نعطيك تمويل بنسبة 3:49 . ليه اللعب هذا بعد ماتعبت وحولت الراتب غيروا كلامهم . حسبي الله ونعم الوكيل</t>
+          <t>مشكلة غريبة معاكم !؟ممكن حد يتواصل</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>https://x.com/SultanAlhreago/status/2038954812801191946</t>
+          <t>https://x.com/Saeed_20212/status/2038941653596324169</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE من اسوا البنوك . جيتهم باخذ تمويل وكان راتبي على الراجحي فقالوا اذا تحول الراتب علينا نعطيك نسبة 1:85 . ولما حولت الراتب عليهم قلت يلا ابغى التمويل على اساس انه 1:85  . فقالوا لا نعطيك تمويل بنسبة 3:49 . ليه اللعب هذا بعد ماتعبت وحولت الراتب غيروا كلامهم . حسبي الله ونعم الوكيل</t>
+          <t>@emiratesislamic مشكلة غريبة معاكم !؟ممكن حد يتواصل</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE من اسوا البنوك . جيتهم باخذ تمويل وكان راتبي على الراجحي فقالوا اذا تحول الراتب علينا نعطيك نسبة 1:85 . ولما حولت الراتب عليهم قلت يلا ابغى التمويل على اساس انه 1:85  . فقالوا لا نعطيك تمويل بنسبة 3:49 . ليه اللعب هذا بعد ماتعبت وحولت الراتب غيروا كلامهم . حسبي الله ونعم الوكيل</t>
+          <t>@emiratesislamic مشكلة غريبة معاكم !؟ممكن حد يتواصل</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>Emirates NBD is one of the worst banks. I approached them to get financing while my salary was with Al Rajhi, and they said if I transferred my salary to them, they would give me a ratio of 1:85. When I transferred my salary to them, I said I wanted the financing based on the 1:85 ratio. They then said no, we will give you financing at a ratio of 3:49. Why this game? After I worked hard and transferred my salary, they changed their words. God is sufficient for me, and He is the best disposer of affairs.</t>
+          <t>Strange problem with you! Can someone get in touch?</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -7286,7 +7268,7 @@
         </is>
       </c>
       <c r="AE42" s="2" t="n">
-        <v>46112.68125</v>
+        <v>46112.64513888889</v>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
@@ -7295,22 +7277,22 @@
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
+          <t>2. Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>I approached them to get financing while my salary was with Al Rajhi, and they said if I transferred my salary to them, they would give me a ratio of 1:85. • When I transferred my salary to them, I said I wanted the financing based on the 1:85 ratio. • They then said no, we will give you financing at a ratio of 3:49.</t>
+          <t>Can someone get in touch? • Strange problem with you!</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank (ENBD)</t>
+          <t>Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AK42" t="n">
@@ -7318,7 +7300,7 @@
       </c>
       <c r="AL42" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
     </row>
@@ -7328,43 +7310,43 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2038864454222262474</t>
+          <t>2038954812801191946</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2038864454222262474</t>
+          <t>https://x.com/SultanAlhreago/status/2038954812801191946</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/SultanAlhreago</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>SultanAlhreago</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Sultan Al hrbi</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Dear Customer, Thanks for getting in touch. We apologize for any inconvenience caused. Your privacy is important to us, and to ensure your confidentiality, we've sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
+          <t>@EmiratesNBD_AE من اسوا البنوك . جيتهم باخذ تمويل وكان راتبي على الراجحي فقالوا اذا تحول الراتب علينا نعطيك نسبة 1:85 . ولما حولت الراتب عليهم قلت يلا ابغى التمويل على اساس انه 1:85  . فقالوا لا نعطيك تمويل بنسبة 3:49 . ليه اللعب هذا بعد ماتعبت وحولت الراتب غيروا كلامهم . حسبي الله ونعم الوكيل</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Dear Customer, Thanks for getting in touch. We apologize for any inconvenience caused. Your privacy is important to us, and to ensure your confidentiality, we&amp;#39;ve sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
+          <t>من اسوا البنوك . جيتهم باخذ تمويل وكان راتبي على الراجحي فقالوا اذا تحول الراتب علينا نعطيك نسبة 1:85 . ولما حولت الراتب عليهم قلت يلا ابغى التمويل على اساس انه 1:85  . فقالوا لا نعطيك تمويل بنسبة 3:49 . ليه اللعب هذا بعد ماتعبت وحولت الراتب غيروا كلامهم . حسبي الله ونعم الوكيل</t>
         </is>
       </c>
       <c r="K43" t="b">
@@ -7373,56 +7355,64 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>['ZiadaKhalid']</t>
+          <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 6:22 AM UTC</t>
+          <t>Mar 31, 2026 · 12:21 PM UTC</t>
         </is>
       </c>
       <c r="P43" s="2" t="n">
-        <v>46112.26527777778</v>
+        <v>46112.51458333333</v>
       </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V43" t="n">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>ENBD</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Dear Customer, Thanks for getting in touch. We apologize for any inconvenience caused. Your privacy is important to us, and to ensure your confidentiality, we've sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr"/>
-      <c r="Z43" t="inlineStr"/>
+          <t>من اسوا البنوك . جيتهم باخذ تمويل وكان راتبي على الراجحي فقالوا اذا تحول الراتب علينا نعطيك نسبة 1:85 . ولما حولت الراتب عليهم قلت يلا ابغى التمويل على اساس انه 1:85  . فقالوا لا نعطيك تمويل بنسبة 3:49 . ليه اللعب هذا بعد ماتعبت وحولت الراتب غيروا كلامهم . حسبي الله ونعم الوكيل</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>https://x.com/SultanAlhreago/status/2038954812801191946</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE من اسوا البنوك . جيتهم باخذ تمويل وكان راتبي على الراجحي فقالوا اذا تحول الراتب علينا نعطيك نسبة 1:85 . ولما حولت الراتب عليهم قلت يلا ابغى التمويل على اساس انه 1:85  . فقالوا لا نعطيك تمويل بنسبة 3:49 . ليه اللعب هذا بعد ماتعبت وحولت الراتب غيروا كلامهم . حسبي الله ونعم الوكيل</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>Dear Customer, Thanks for getting in touch. We apologize for any inconvenience caused. Your privacy is important to us, and to ensure your confidentiality, we've sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
+          <t>@EmiratesNBD_AE من اسوا البنوك . جيتهم باخذ تمويل وكان راتبي على الراجحي فقالوا اذا تحول الراتب علينا نعطيك نسبة 1:85 . ولما حولت الراتب عليهم قلت يلا ابغى التمويل على اساس انه 1:85  . فقالوا لا نعطيك تمويل بنسبة 3:49 . ليه اللعب هذا بعد ماتعبت وحولت الراتب غيروا كلامهم . حسبي الله ونعم الوكيل</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>Dear Customer, Thanks for getting in touch. We apologize for any inconvenience caused. Your privacy is important to us, and to ensure your confidentiality, we've sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
+          <t>Emirates NBD is one of the worst banks. I went to them to get financing and my salary was with Al Rajhi, and they said if I transfer my salary to them, they would give me a ratio of 1:85. When I transferred my salary to them, I said I want the financing based on the 1:85 ratio. They then said no, we will give you financing at a ratio of 3:49. Why this game after I worked hard and transferred my salary, they changed their words. God is sufficient for me, and He is the best disposer of affairs.</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -7436,7 +7426,7 @@
         </is>
       </c>
       <c r="AE43" s="2" t="n">
-        <v>46112.43194444444</v>
+        <v>46112.68125</v>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
@@ -7445,22 +7435,22 @@
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>ENBD</t>
         </is>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
+          <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Your privacy is important to us, and to ensure your confidentiality, we've sent you a message requesting further details. • Please check your direct messages at your earliest convenience. • Dear Customer, Thanks for getting in touch.</t>
+          <t>I went to them to get financing and my salary was with Al Rajhi, and they said if I transfer my salary to them, they would give me a ratio of 1:85. • When I transferred my salary to them, I said I want the financing based on the 1:85 ratio. • They then said no, we will give you financing at a ratio of 3:49.</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>Emirates Islamic Bank (EIB)</t>
+          <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
       <c r="AK43" t="n">
@@ -7468,7 +7458,7 @@
       </c>
       <c r="AL43" t="inlineStr">
         <is>
-          <t>ZiadaKhalid</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
     </row>
@@ -7478,43 +7468,43 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2038817017201844492</t>
+          <t>2038864454222262474</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://x.com/nada_nz/status/2038817017201844492</t>
+          <t>https://x.com/emiratesislamic/status/2038864454222262474</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://x.com/nada_nz</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>nada_nz</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>nada_nz</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2663515949/5b7e64bc68780125ecdd0034e4ca0853_bigger.jpeg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE @SAMAcares بنك الامارات عمل لي شراء مديونية من شركة تمويل الاولى ..، وعند الذهاب لاخلاء الطرف مع شركة تمويل الاولى طلب مني اثبات السداد ..، وبنك الامارات رفض اعطائي اثبات السداد وتعطلت اعمالي بسبب عدم اعطائي مايثبت السداد</t>
+          <t>@emiratesislamic Very bad service i have credit card stuck for more than 3 weeks no one bother</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>افهم سياستهم كثير قبل لاتنقل لهم 😣</t>
+          <t>Dear Customer, Thanks for getting in touch. We apologize for any inconvenience caused. Your privacy is important to us, and to ensure your confidentiality, we&amp;#39;ve sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
         </is>
       </c>
       <c r="K44" t="b">
@@ -7523,21 +7513,21 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>['faris767652', 's2615456121049', 'EmiratesNBD_AE', 'SAMAcares']</t>
+          <t>['ZiadaKhalid']</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Mar 31</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 3:13 AM UTC</t>
+          <t>Mar 31, 2026 · 6:22 AM UTC</t>
         </is>
       </c>
       <c r="P44" s="2" t="n">
-        <v>46112.13402777778</v>
+        <v>46112.26527777778</v>
       </c>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
@@ -7551,36 +7541,36 @@
         <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>افهم سياستهم كثير قبل لاتنقل لهم 😣</t>
+          <t>Dear Customer, Thanks for getting in touch. We apologize for any inconvenience caused. Your privacy is important to us, and to ensure your confidentiality, we've sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>https://x.com/nada_nz/status/2038817017201844492</t>
+          <t>https://x.com/emiratesislamic/status/2038864454222262474</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE @SAMAcares بنك الامارات عمل لي شراء مديونية من شركة تمويل الاولى ..، وعند الذهاب لاخلاء الطرف مع شركة تمويل الاولى طلب مني اثبات السداد ..، وبنك الامارات رفض اعطائي اثبات السداد وتعطلت اعمالي بسبب عدم اعطائي مايثبت السداد</t>
+          <t>@emiratesislamic Very bad service i have credit card stuck for more than 3 weeks no one bother</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE @SAMAcares بنك الامارات عمل لي شراء مديونية من شركة تمويل الاولى ..، وعند الذهاب لاخلاء الطرف مع شركة تمويل الاولى طلب مني اثبات السداد ..، وبنك الامارات رفض اعطائي اثبات السداد وتعطلت اعمالي بسبب عدم اعطائي مايثبت السداد</t>
+          <t>@emiratesislamic Very bad service i have credit card stuck for more than 3 weeks no one bother</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank made a debt purchase for me from First Finance Company, and when I went to obtain a clearance certificate from First Finance Company, they asked me for proof of payment. However, Emirates NBD refused to provide me with proof of payment, and my business was disrupted due to not being given what proves the payment.</t>
+          <t>Very bad service, I have a credit card stuck for more than 3 weeks and no one bothers.</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -7594,7 +7584,7 @@
         </is>
       </c>
       <c r="AE44" s="2" t="n">
-        <v>46112.30069444444</v>
+        <v>46112.43194444444</v>
       </c>
       <c r="AF44" t="inlineStr">
         <is>
@@ -7603,28 +7593,186 @@
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
+          <t>2. Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank made a debt purchase for me from First Finance Company, and when I went to obtain a clearance certificate from First Finance Company, they asked me for proof of payment. • However, Emirates NBD refused to provide me with proof of payment, and my business was disrupted due to not being given what proves the payment.</t>
+          <t>Very bad service, I have a credit card stuck for more than 3 weeks and no one bothers.</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank (ENBD)</t>
+          <t>Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AK44" t="n">
         <v>2026</v>
       </c>
       <c r="AL44" t="inlineStr">
+        <is>
+          <t>ZiadaKhalid</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2038817017201844492</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>https://x.com/nada_nz/status/2038817017201844492</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://x.com/nada_nz</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>nada_nz</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>nada_nz</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2663515949/5b7e64bc68780125ecdd0034e4ca0853_bigger.jpeg</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE @SAMAcares بنك الامارات عمل لي شراء مديونية من شركة تمويل الاولى ..، وعند الذهاب لاخلاء الطرف مع شركة تمويل الاولى طلب مني اثبات السداد ..، وبنك الامارات رفض اعطائي اثبات السداد وتعطلت اعمالي بسبب عدم اعطائي مايثبت السداد</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>افهم سياستهم كثير قبل لاتنقل لهم 😣</t>
+        </is>
+      </c>
+      <c r="K45" t="b">
+        <v>0</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>['faris767652', 's2615456121049', 'EmiratesNBD_AE', 'SAMAcares']</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Mar 31</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Mar 31, 2026 · 3:13 AM UTC</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="n">
+        <v>46112.13402777778</v>
+      </c>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>8</v>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>افهم سياستهم كثير قبل لاتنقل لهم 😣</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>https://x.com/nada_nz/status/2038817017201844492</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE @SAMAcares بنك الامارات عمل لي شراء مديونية من شركة تمويل الاولى ..، وعند الذهاب لاخلاء الطرف مع شركة تمويل الاولى طلب مني اثبات السداد ..، وبنك الامارات رفض اعطائي اثبات السداد وتعطلت اعمالي بسبب عدم اعطائي مايثبت السداد</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE @SAMAcares بنك الامارات عمل لي شراء مديونية من شركة تمويل الاولى ..، وعند الذهاب لاخلاء الطرف مع شركة تمويل الاولى طلب مني اثبات السداد ..، وبنك الامارات رفض اعطائي اثبات السداد وتعطلت اعمالي بسبب عدم اعطائي مايثبت السداد</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank made a debt purchase for me from Al-Awwal Financing Company, and when I went to obtain a clearance certificate from Al-Awwal Financing Company, they asked me for proof of payment. However, Emirates NBD refused to provide me with proof of payment, and my business has been disrupted due to not being given proof of payment.</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AE45" s="2" t="n">
+        <v>46112.30069444444</v>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>31-03-2026</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank made a debt purchase for me from Al-Awwal Financing Company, and when I went to obtain a clearance certificate from Al-Awwal Financing Company, they asked me for proof of payment. • However, Emirates NBD refused to provide me with proof of payment, and my business has been disrupted due to not being given proof of payment.</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK45" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL45" t="inlineStr">
         <is>
           <t>faris767652, s2615456121049, EmiratesNBD_AE, SAMAcares</t>
         </is>

--- a/check2.xlsx
+++ b/check2.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>I keep hearing the claim that Dubai is dead and that all the wealth has fled the city. It couldn’t be the farthest thing from the truth.</t>
+          <t>I keep hearing the claim that Dubai is dead and that all the wealth has fled the city. It couldn’t be further from the truth.</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>I keep hearing the claim that Dubai is dead and that all the wealth has fled the city. • It couldn’t be the farthest thing from the truth.</t>
+          <t>I keep hearing the claim that Dubai is dead and that all the wealth has fled the city. • It couldn’t be further from the truth.</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>The UAE controls the banking system of Pakistan after bribing Pakistani leaders. Some banks owned by the UAE in Pakistan include: 1. Bank Alfalah 2. Dubai Islamic Bank 3. Mashreq Bank 4. Emirates NBD 5. Emirates Global Islamic Bank 6. First Women Bank 7. Al Baraka Bank.</t>
+          <t>UAE controls the banking system of Pakistan after bribing Pakistani leaders. Some banks owned by the UAE in Pakistan are: 1. Bank Alfalah 2. Dubai Islamic Bank 3. Mashreq Bank 4. Emirates NBD 5. Emirates Global Islamic Bank 6. First Women Bank 7. Al Baraka Bank.</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Emirates Global Islamic Bank 6. • The UAE controls the banking system of Pakistan after bribing Pakistani leaders. • Some banks owned by the UAE in Pakistan include: 1.</t>
+          <t>Emirates Global Islamic Bank 6. • UAE controls the banking system of Pakistan after bribing Pakistani leaders. • Some banks owned by the UAE in Pakistan are: 1.</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>If you run a remote agency making over $30,000 a month, you are likely losing between $120,000 and $200,000 a year to income tax. That money could be used to hire two senior team members or cover your entire annual profit margin. Here is why agency owners are discreetly moving to the UAE.</t>
+          <t>If you run a remote agency making over $30,000 a month, you are likely losing between $120,000 and $200,000 a year to income tax. That money could be used to hire two senior team members or could represent your entire annual profit margin. Here is why agency owners are discreetly moving to the UAE.</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>If you run a remote agency making over $30,000 a month, you are likely losing between $120,000 and $200,000 a year to income tax. • That money could be used to hire two senior team members or cover your entire annual profit margin. • Here is why agency owners are discreetly moving to the UAE.</t>
+          <t>If you run a remote agency making over $30,000 a month, you are likely losing between $120,000 and $200,000 a year to income tax. • That money could be used to hire two senior team members or could represent your entire annual profit margin. • Here is why agency owners are discreetly moving to the UAE.</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Hi, thank you for reaching out, please click the link below to know more.</t>
+          <t>Hi, thank you for reaching out. Please click the link below to learn more.</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Hi, thank you for reaching out, please click the link below to know more.</t>
+          <t>Please click the link below to learn more. • Hi, thank you for reaching out.</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>The text appears to be a series of Twitter handles and does not contain any language to translate.</t>
+          <t>The text appears to be a series of Twitter handles and does not require translation.</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>The text appears to be a series of Twitter handles and does not contain any language to translate.</t>
+          <t>The text appears to be a series of Twitter handles and does not require translation.</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -6060,9 +6060,9 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Get a guaranteed iPhone 17 when you apply for Emirates Islamic Personal Finance.
+          <t>Get a guaranteed iPhone 17 when you apply for an Emirates Islamic Personal Finance.
 Also, enjoy exclusive benefits:
-📊 Profit rates starting from 2.59% flat per annum (approximately equivalent to a 4.74% per annum reducing profit rate)
+📊 Profit rates starting from 2.59% flat per annum (approximately equivalent to 4.74% per annum reducing profit rate)
 🏦 Finance amount of up to AED 4,000,000</t>
         </is>
       </c>
@@ -6094,7 +6094,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Also, enjoy exclusive benefits: 📊 Profit rates starting from 2.59% flat per annum (approximately equivalent to a 4.74% per annum reducing profit rate) 🏦 Finance amount of up to AED 4,000,000 • Get a guaranteed iPhone 17 when you apply for Emirates Islamic Personal Finance.</t>
+          <t>Also, enjoy exclusive benefits: 📊 Profit rates starting from 2.59% flat per annum (approximately equivalent to 4.74% per annum reducing profit rate) 🏦 Finance amount of up to AED 4,000,000 • Get a guaranteed iPhone 17 when you apply for an Emirates Islamic Personal Finance.</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
@@ -6657,7 +6657,7 @@
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>بإيداع المبلغ و انصدم اليوم انه يقوم المصرف بأخذ القرض مرتيين في نفس الوقت يرجى الرد في اسرع وقت هاتفيأ لاني اريد النبلغ بسبب المعيشة  0569129222</t>
+          <t>@emiratesislamic بإيداع المبلغ و انصدم اليوم انه يقوم المصرف بأخذ القرض مرتيين في نفس الوقت يرجى الرد في اسرع وقت هاتفيأ لاني اريد النبلغ بسبب المعيشة  0569129222</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -6711,16 +6711,24 @@
           <t>بإيداع المبلغ و انصدم اليوم انه يقوم المصرف بأخذ القرض مرتيين في نفس الوقت يرجى الرد في اسرع وقت هاتفيأ لاني اريد النبلغ بسبب المعيشة  0569129222</t>
         </is>
       </c>
-      <c r="Y38" t="inlineStr"/>
-      <c r="Z38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>https://x.com/MatarAlAl/status/2040327735621656747</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>@emiratesislamic بإيداع المبلغ و انصدم اليوم انه يقوم المصرف بأخذ القرض مرتيين في نفس الوقت يرجى الرد في اسرع وقت هاتفيأ لاني اريد النبلغ بسبب المعيشة  0569129222</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>بإيداع المبلغ و انصدم اليوم انه يقوم المصرف بأخذ القرض مرتيين في نفس الوقت يرجى الرد في اسرع وقت هاتفيأ لاني اريد النبلغ بسبب المعيشة  0569129222</t>
+          <t>@emiratesislamic بإيداع المبلغ و انصدم اليوم انه يقوم المصرف بأخذ القرض مرتيين في نفس الوقت يرجى الرد في اسرع وقت هاتفيأ لاني اريد النبلغ بسبب المعيشة  0569129222</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>I deposited the amount and was shocked today to find that the bank is taking the loan twice at the same time. Please respond as soon as possible by phone because I need the amount due to living expenses 0569129222.</t>
+          <t>I was shocked today to find that the bank is taking the loan twice at the same time after depositing the amount. Please respond as soon as possible by phone because I need the money due to living expenses 0569129222.</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -6751,7 +6759,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Please respond as soon as possible by phone because I need the amount due to living expenses 0569129222. • I deposited the amount and was shocked today to find that the bank is taking the loan twice at the same time.</t>
+          <t>Please respond as soon as possible by phone because I need the money due to living expenses 0569129222. • I was shocked today to find that the bank is taking the loan twice at the same time after depositing the amount.</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
@@ -6868,7 +6876,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Your customer support is terrible. My flight was canceled and a refund was issued by Make My Trip on March 17, 2026. However, you have still not credited the refund. I am forced to tweet as there has been no response to multiple emails, direct messages, and WhatsApp just connects to a bot. Dispute (SR 234626561923)</t>
+          <t>Your customer support is terrible. My flight was canceled and a refund was issued by Make My Trip on March 17, 2026. But you have still not credited the refund. I am forced to tweet as there has been no response to multiple emails, direct messages, and WhatsApp just connects to a bot. Dispute (SR 234626561923)</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">

--- a/check2.xlsx
+++ b/check2.xlsx
@@ -734,9 +734,12 @@
 #India #UAE @rblbank @UAEembassyIndia</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>https://x.com/TheDailyMilap/status/2041364352121679973</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>امارات این بی ڈی کو آر بی آئی کی منظوری، آر بی ایل بینک میں حصص بڑھانے کی راہ ہموار
 نئی دہلی: متحدہ عرب امارات کے بڑے بینک امارات این بی ڈی (Emirates NBD) کو بھارتی مرکزی بینک (RBI) کی جانب سے آر بی ایل بینک میں اپنا حصہ بڑھانے کی منظوری مل گئی ہے، جس کے بعد یہ ڈیل بھارت کے بینکنگ سیکٹر کی بڑی غیر ملکی سرمایہ کاری میں شمار کی جا رہی ہے۔
@@ -749,13 +752,26 @@
 #India #UAE @rblbank @UAEembassyIndia</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>امارات این بی ڈی کو آر بی آئی کی منظوری، آر بی ایل بینک میں حصص بڑھانے کی راہ ہموار
+نئی دہلی: متحدہ عرب امارات کے بڑے بینک امارات این بی ڈی (Emirates NBD) کو بھارتی مرکزی بینک (RBI) کی جانب سے آر بی ایل بینک میں اپنا حصہ بڑھانے کی منظوری مل گئی ہے، جس کے بعد یہ ڈیل بھارت کے بینکنگ سیکٹر کی بڑی غیر ملکی سرمایہ کاری میں شمار کی جا رہی ہے۔
+رپورٹس کے مطابق، آر بی آئی نے امارات این بی ڈی کو آر بی ایل بینک میں 74 فیصد تک حصص خریدنے کی اجازت دی ہے، تاہم ووٹنگ رائٹس 26 فیصد تک محدود رہیں گے۔  ￼
+یہ سرمایہ کاری تقریباً 3 ارب ڈالر مالیت کی ہے اور اس کے تحت امارات این بی ڈی کو بینک کے بورڈ میں نمائندگی کا حق بھی حاصل ہوگا، جبکہ آر بی ایل بینک کو ایک غیر ملکی بینک کی ذیلی کمپنی کے طور پر درجہ دیا جائے گا۔  ￼
+ذرائع کے مطابق، یہ معاہدہ پہلی بار 2025 میں سامنے آیا تھا اور اب مختلف ریگولیٹری منظوریوں کے بعد حتمی مراحل میں داخل ہو چکا ہے، جس میں سیکیورٹیز اینڈ ایکسچینج بورڈ آف انڈیا (SEBI) کی منظوری بھی شامل ہے۔  ￼
+ماہرین کا کہنا ہے کہ اس ڈیل سے آر بی ایل بینک کو سرمایہ اور عالمی بینکنگ مہارت حاصل ہوگی، جبکہ امارات این بی ڈی کو بھارت جیسے بڑے اور تیزی سے بڑھتے مالیاتی بازار میں مضبوط قدم جمانے کا موقع ملے گا۔  ￼
+یہ پیش رفت بھارت اور یو اے ای کے درمیان بڑھتے مالیاتی اور اقتصادی تعاون کی بھی عکاسی کرتی ہے، جہاں خلیجی سرمایہ کاری بھارتی بینکنگ اور مالیاتی شعبے میں تیزی سے داخل ہو رہی ہے۔  ￼
+تجزیہ کاروں کے مطابق، اس معاہدے سے نہ صرف آر بی ایل بینک کی ملکیت اور حکمت عملی میں بڑی تبدیلی آئے گی بلکہ بھارت کے مالیاتی شعبے میں غیر ملکی بینکوں کے کردار میں بھی اضافہ دیکھنے کو مل سکتا ہے۔
+#India #UAE @rblbank @UAEembassyIndia</t>
+        </is>
+      </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Emirates NBD's approval by RBI paves the way for increasing stake in RBL Bank
+          <t>Emirates NBD's path to increasing its stake in RBL Bank approved by RBI
 New Delhi: Emirates NBD, a major bank in the United Arab Emirates, has received approval from the Reserve Bank of India (RBI) to increase its stake in RBL Bank, marking this deal as a significant foreign investment in India's banking sector.
-Reports indicate that the RBI has allowed Emirates NBD to purchase up to 74% of shares in RBL Bank, although voting rights will remain limited to 26%.
+According to reports, the RBI has allowed Emirates NBD to purchase up to 74% of shares in RBL Bank, although voting rights will remain limited to 26%.
 This investment is valued at approximately $3 billion and will grant Emirates NBD representation on the bank's board, while RBL Bank will be classified as a subsidiary of a foreign bank.
-According to sources, this agreement first emerged in 2025 and has now entered its final stages following various regulatory approvals, including that of the Securities and Exchange Board of India (SEBI).
+Sources indicate that this agreement first emerged in 2025 and has now entered its final stages following various regulatory approvals, including that of the Securities and Exchange Board of India (SEBI).
 Experts say that this deal will provide RBL Bank with capital and global banking expertise, while giving Emirates NBD an opportunity to establish a strong foothold in a large and rapidly growing financial market like India.
 This development also reflects the increasing financial and economic cooperation between India and the UAE, where Gulf investments are rapidly entering the Indian banking and financial sector.
 Analysts suggest that this agreement will not only bring significant changes to RBL Bank's ownership and strategy but may also enhance the role of foreign banks in India's financial sector.</t>
@@ -768,7 +784,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE2" s="2" t="n">
@@ -789,7 +805,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>This investment is valued at approximately $3 billion and will grant Emirates NBD representation on the bank's board, while RBL Bank will be classified as a subsidiary of a foreign bank. • Reports indicate that the RBI has allowed Emirates NBD to purchase up to 74% of shares in RBL Bank, although voting rights will remain limited to 26%. • Analysts suggest that this agreement will not only bring significant changes to RBL Bank's ownership and strategy but may also enhance the role of foreign banks in India's financial sector.</t>
+          <t>This investment is valued at approximately $3 billion and will grant Emirates NBD representation on the bank's board, while RBL Bank will be classified as a subsidiary of a foreign bank. • According to reports, the RBI has allowed Emirates NBD to purchase up to 74% of shares in RBL Bank, although voting rights will remain limited to 26%. • Analysts suggest that this agreement will not only bring significant changes to RBL Bank's ownership and strategy but may also enhance the role of foreign banks in India's financial sector.</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -1360,7 +1376,7 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE B- 1.89% @AyshaMoham64638 @Sarahfa40636602 @Umehanimuhamma1 
+          <t>B- 1.89% @AyshaMoham64638 @Sarahfa40636602 @Umehanimuhamma1 
 ,🇦🇪💸</t>
         </is>
       </c>
@@ -1421,26 +1437,17 @@
 ,🇦🇪💸</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>https://x.com/Bushrasabih2/status/2041244775110877490</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE B- 1.89% @AyshaMoham64638 @Sarahfa40636602 @Umehanimuhamma1 
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>B- 1.89% @AyshaMoham64638 @Sarahfa40636602 @Umehanimuhamma1 
 ,🇦🇪💸</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE B- 1.89% @AyshaMoham64638 @Sarahfa40636602 @Umehanimuhamma1 
-,🇦🇪💸</t>
-        </is>
-      </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>The text appears to be a mix of social media handles and symbols, with no specific language content to translate. Therefore, there is no translation needed.</t>
+          <t>The text appears to be a mix of numbers, usernames, and emojis, and does not contain any coherent language to translate. Therefore, there is no translation available.</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1471,7 +1478,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>The text appears to be a mix of social media handles and symbols, with no specific language content to translate. • Therefore, there is no translation needed.</t>
+          <t>The text appears to be a mix of numbers, usernames, and emojis, and does not contain any coherent language to translate. • Therefore, there is no translation available.</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1524,6 +1531,171 @@
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE B- 1.89% @AyshaMoham64638 @Sarahfa40636602 @Umehanimuhamma
+..1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>B- 1.89% &lt;a href="/AyshaMoham64638" title="Aysha Mohammad"&gt;@AyshaMoham64638&lt;/a&gt; &lt;a href="/Sarahfa40636602" title="Sarah_fares"&gt;@Sarahfa40636602&lt;/a&gt; @Umehanimuhamma
+..1</t>
+        </is>
+      </c>
+      <c r="K7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>8h</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Apr 6, 2026 · 8:00 PM UTC</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>46118.83333333334</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>['https://x.com/AyshaMoham64638', 'https://x.com/Sarahfa40636602']</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>3</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>B- 1.89% @AyshaMoham64638 @Sarahfa40636602 @Umehanimuhamma
+..1</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>https://x.com/Bushrasabih2/status/2041244708023017544</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE B- 1.89% @AyshaMoham64638 @Sarahfa40636602 @Umehanimuhamma
+..1</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE B- 1.89% @AyshaMoham64638 @Sarahfa40636602 @Umehanimuhamma
+..1</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>The text appears to be a social media post or message that includes usernames and a percentage. There is no translatable content in terms of language, as it primarily consists of usernames and a numerical value.</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE7" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="AF7" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>There is no translatable content in terms of language, as it primarily consists of usernames and a numerical value. • The text appears to be a social media post or message that includes usernames and a percentage.</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK7" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2041244659918471188</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://x.com/Bushrasabih2/status/2041244659918471188</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://x.com/Bushrasabih2</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Bushrasabih2</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Bu_shaikh🌸❤️</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2037057205510574080/OEGMy7R9_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
         <is>
           <t>حل اللغز واربح 10,000 درهم.
 أم علاوي تعبت من مشاكل السيارة، ومستعدة لسيارة جديدة بفضل قرض السيارات السريع منEmirates NBD ، من خلال طلب سهل وسريع عبر الإنترنت.
@@ -1533,69 +1705,67 @@
 حل اللغز لفرصة الفوز بـ ١٠ آلاف درهم. https://t.co/5GObMKmWvV</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>B- 1.89% &lt;a href="/AyshaMoham64638" title="Aysha Mohammad"&gt;@AyshaMoham64638&lt;/a&gt; &lt;a href="/Sarahfa40636602" title="Sarah_fares"&gt;@Sarahfa40636602&lt;/a&gt; @Umehanimuhamma
-..1</t>
-        </is>
-      </c>
-      <c r="K7" t="b">
-        <v>0</v>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>B- 1.89% &lt;a href="/AyshaMoham64638" title="Aysha Mohammad"&gt;@AyshaMoham64638&lt;/a&gt; &lt;a href="/Sarahfa40636602" title="Sarah_fares"&gt;@Sarahfa40636602&lt;/a&gt; &lt;a href="/Umehanimuhamma1" title="ام محمد احمد"&gt;@Umehanimuhamma1&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K8" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>8h</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Apr 6, 2026 · 8:00 PM UTC</t>
         </is>
       </c>
-      <c r="P7" s="2" t="n">
+      <c r="P8" s="2" t="n">
         <v>46118.83333333334</v>
       </c>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>['https://x.com/AyshaMoham64638', 'https://x.com/Sarahfa40636602']</t>
-        </is>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>['https://x.com/AyshaMoham64638', 'https://x.com/Sarahfa40636602', 'https://x.com/Umehanimuhamma1']</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
         <v>3</v>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>B- 1.89% @AyshaMoham64638 @Sarahfa40636602 @Umehanimuhamma
-..1</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>https://x.com/Bushrasabih2/status/2041244708023017544</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>B- 1.89% @AyshaMoham64638 @Sarahfa40636602 @Umehanimuhamma1</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>https://x.com/Bushrasabih2/status/2041244659918471188</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>حل اللغز واربح 10,000 درهم.
 أم علاوي تعبت من مشاكل السيارة، ومستعدة لسيارة جديدة بفضل قرض السيارات السريع منEmirates NBD ، من خلال طلب سهل وسريع عبر الإنترنت.
@@ -1605,7 +1775,7 @@
 حل اللغز لفرصة الفوز بـ ١٠ آلاف درهم. https://t.co/5GObMKmWvV</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>حل اللغز واربح 10,000 درهم.
 أم علاوي تعبت من مشاكل السيارة، ومستعدة لسيارة جديدة بفضل قرض السيارات السريع منEmirates NBD ، من خلال طلب سهل وسريع عبر الإنترنت.
@@ -1615,179 +1785,19 @@
 حل اللغز لفرصة الفوز بـ ١٠ آلاف درهم. https://t.co/5GObMKmWvV</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>Solve the puzzle and win 10,000 dirhams. Um Alawi is tired of car problems and is ready for a new car thanks to the quick car loan from Emirates NBD, through an easy and fast online application. Follow @EmiratesNBD_ae Tag 3 of your friends Solve the puzzle for a chance to win 10,000 dirhams.</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>Positive</t>
-        </is>
-      </c>
-      <c r="AE7" s="2" t="n">
-        <v>46119</v>
-      </c>
-      <c r="AF7" s="2" t="n">
-        <v>46119</v>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Um Alawi is tired of car problems and is ready for a new car thanks to the quick car loan from Emirates NBD, through an easy and fast online application. • Follow @EmiratesNBD_ae Tag 3 of your friends Solve the puzzle for a chance to win 10,000 dirhams. • Solve the puzzle and win 10,000 dirhams.</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AK7" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>EmiratesNBD_AE</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2041244659918471188</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>https://x.com/Bushrasabih2/status/2041244659918471188</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>https://x.com/Bushrasabih2</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Bushrasabih2</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Bu_shaikh🌸❤️</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2037057205510574080/OEGMy7R9_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE B- 1.89% @AyshaMoham64638 @Sarahfa40636602 @Umehanimuhamma1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>B- 1.89% &lt;a href="/AyshaMoham64638" title="Aysha Mohammad"&gt;@AyshaMoham64638&lt;/a&gt; &lt;a href="/Sarahfa40636602" title="Sarah_fares"&gt;@Sarahfa40636602&lt;/a&gt; &lt;a href="/Umehanimuhamma1" title="ام محمد احمد"&gt;@Umehanimuhamma1&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K8" t="b">
-        <v>0</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>8h</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Apr 6, 2026 · 8:00 PM UTC</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="n">
-        <v>46118.83333333334</v>
-      </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>['https://x.com/AyshaMoham64638', 'https://x.com/Sarahfa40636602', 'https://x.com/Umehanimuhamma1']</t>
-        </is>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>3</v>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>B- 1.89% @AyshaMoham64638 @Sarahfa40636602 @Umehanimuhamma1</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>https://x.com/Bushrasabih2/status/2041244659918471188</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE B- 1.89% @AyshaMoham64638 @Sarahfa40636602 @Umehanimuhamma1</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE B- 1.89% @AyshaMoham64638 @Sarahfa40636602 @Umehanimuhamma1</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>The text appears to be a mix of a social media handle and a percentage, rather than a coherent sentence in a specific language. Therefore, there is no translation needed.</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>Neutral</t>
         </is>
       </c>
       <c r="AE8" s="2" t="n">
@@ -1808,7 +1818,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>The text appears to be a mix of a social media handle and a percentage, rather than a coherent sentence in a specific language. • Therefore, there is no translation needed.</t>
+          <t>Um Alawi is tired of car problems and is ready for a new car thanks to the quick car loan from Emirates NBD, through an easy and fast online application. • Follow @EmiratesNBD_ae Tag 3 of your friends Solve the puzzle for a chance to win 10,000 dirhams. • Solve the puzzle and win 10,000 dirhams.</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1937,7 +1947,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>The text appears to be a mix of social media handles and a percentage, which does not require translation. The content does not contain any language that needs to be translated into English.</t>
+          <t>The text appears to be a social media post or message with usernames and a percentage. There is no translatable content in a specific language.</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1968,7 +1978,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>The text appears to be a mix of social media handles and a percentage, which does not require translation. • The content does not contain any language that needs to be translated into English.</t>
+          <t>The text appears to be a social media post or message with usernames and a percentage. • There is no translatable content in a specific language.</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -2888,29 +2898,10 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>نفذت أموال أم خماس قبل نهاية الشهر.
-هناك قاعدة بسيطة تُساعدها على إدارة أموالها بحكمة:
-%50 للاحتياجات الأساسية
-%30 للكماليات
-%20 للادخار
-خطة ذكية تمكّنك من الإنفاق والادخار والحفاظ على التحكم في ميزانيتك. هذه واحدة من العديد من النصائح التي يقدّمها لك برنامج البنك.
-شاهد الحلقة وأخبرنا ما اسم البرنامج؟
-للمشاركة:
-- تابع حساب بنك الإمارات دبي الوطني
-- قم بالإشارة إلى 3 من أصدقائك
-- اكتب إجابتك في التعليقات أدناه لفرصة الفوز 10,000
-Um Khammas ran out of cash before the month ended.
-A simple rule can help her stay on track:
-50% for needs
-30% for wants
-20% for savings
-A smart plan that helps you spend, save and stay in control.
-This is one of the many tips that the bank’s programme has in store.
-Watch the episode and tell us the name of the programme?
-To participate:
-- Follow Emirates NBD
-- Tag 3 friends
-- Drop your answer below for a chance to win AED 10,000</t>
+          <t>التثقيف المالي مع بنك الامارات دبي الوطني 
+@AyshaMoham64638 
+@SKamal354 
+@Umehanimuhamma1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2974,79 +2965,19 @@
 @Umehanimuhamma1</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>https://x.com/Bushrasabih2/status/2041243838434750619</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>نفذت أموال أم خماس قبل نهاية الشهر.
-هناك قاعدة بسيطة تُساعدها على إدارة أموالها بحكمة:
-%50 للاحتياجات الأساسية
-%30 للكماليات
-%20 للادخار
-خطة ذكية تمكّنك من الإنفاق والادخار والحفاظ على التحكم في ميزانيتك. هذه واحدة من العديد من النصائح التي يقدّمها لك برنامج البنك.
-شاهد الحلقة وأخبرنا ما اسم البرنامج؟
-للمشاركة:
-- تابع حساب بنك الإمارات دبي الوطني
-- قم بالإشارة إلى 3 من أصدقائك
-- اكتب إجابتك في التعليقات أدناه لفرصة الفوز 10,000
-Um Khammas ran out of cash before the month ended.
-A simple rule can help her stay on track:
-50% for needs
-30% for wants
-20% for savings
-A smart plan that helps you spend, save and stay in control.
-This is one of the many tips that the bank’s programme has in store.
-Watch the episode and tell us the name of the programme?
-To participate:
-- Follow Emirates NBD
-- Tag 3 friends
-- Drop your answer below for a chance to win AED 10,000</t>
-        </is>
-      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>نفذت أموال أم خماس قبل نهاية الشهر.
-هناك قاعدة بسيطة تُساعدها على إدارة أموالها بحكمة:
-%50 للاحتياجات الأساسية
-%30 للكماليات
-%20 للادخار
-خطة ذكية تمكّنك من الإنفاق والادخار والحفاظ على التحكم في ميزانيتك. هذه واحدة من العديد من النصائح التي يقدّمها لك برنامج البنك.
-شاهد الحلقة وأخبرنا ما اسم البرنامج؟
-للمشاركة:
-- تابع حساب بنك الإمارات دبي الوطني
-- قم بالإشارة إلى 3 من أصدقائك
-- اكتب إجابتك في التعليقات أدناه لفرصة الفوز 10,000
-Um Khammas ran out of cash before the month ended.
-A simple rule can help her stay on track:
-50% for needs
-30% for wants
-20% for savings
-A smart plan that helps you spend, save and stay in control.
-This is one of the many tips that the bank’s programme has in store.
-Watch the episode and tell us the name of the programme?
-To participate:
-- Follow Emirates NBD
-- Tag 3 friends
-- Drop your answer below for a chance to win AED 10,000</t>
+          <t>التثقيف المالي مع بنك الامارات دبي الوطني 
+@AyshaMoham64638 
+@SKamal354 
+@Umehanimuhamma1</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Um Khammas ran out of cash before the month ended.
-A simple rule can help her stay on track:
-50% for needs
-30% for wants
-20% for savings
-A smart plan that helps you spend, save, and stay in control.
-This is one of the many tips that the bank’s program has in store.
-Watch the episode and tell us the name of the program?
-To participate:
-- Follow Emirates NBD
-- Tag 3 friends
-- Drop your answer below for a chance to win AED 10,000</t>
+          <t>Financial education with Emirates NBD Bank</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -3077,7 +3008,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>A simple rule can help her stay on track: 50% for needs 30% for wants 20% for savings A smart plan that helps you spend, save, and stay in control. • To participate: - Follow Emirates NBD - Tag 3 friends - Drop your answer below for a chance to win AED 10,000 • This is one of the many tips that the bank’s program has in store.</t>
+          <t>Financial education with Emirates NBD Bank</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -3131,82 +3062,108 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
+          <t>اجعل مفاجآت العيد أكثر قيمة.
+من الفضة إلى الذهب، اكتشف طريقة أذكى لامتلاك أو إهداء شيء ثمين بحق.
+شاهد هذه الحلقة وأخبرنا:
+كيف يمكنك شراء الذهب والفضه من البنك؟
+للمشاركة:
+تابع حساب بنك الإمارات دبي الوطني 
+قم بالإشارة إلى 3 من أصدقائك
+اكتب إجابتك في التعليقات أدناه لفرصة ربح 10,000 درهم</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>through Emirates NBD, the fastest way is using the ENBD X mobile app.   &lt;a href="/AyshaMoham64638" title="Aysha Mohammad"&gt;@AyshaMoham64638&lt;/a&gt; 
+&lt;a href="/Sarahfa40636602" title="Sarah_fares"&gt;@Sarahfa40636602&lt;/a&gt; 
+&lt;a href="/Umehanimuhamma1" title="ام محمد احمد"&gt;@Umehanimuhamma1&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>8h</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Apr 6, 2026 · 7:56 PM UTC</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="n">
+        <v>46118.83055555556</v>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>['https://x.com/AyshaMoham64638', 'https://x.com/Sarahfa40636602', 'https://x.com/Umehanimuhamma1']</t>
+        </is>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>5</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
           <t>through Emirates NBD, the fastest way is using the ENBD X mobile app.   @AyshaMoham64638 
 @Sarahfa40636602 
 @Umehanimuhamma1</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>through Emirates NBD, the fastest way is using the ENBD X mobile app.   &lt;a href="/AyshaMoham64638" title="Aysha Mohammad"&gt;@AyshaMoham64638&lt;/a&gt; 
-&lt;a href="/Sarahfa40636602" title="Sarah_fares"&gt;@Sarahfa40636602&lt;/a&gt; 
-&lt;a href="/Umehanimuhamma1" title="ام محمد احمد"&gt;@Umehanimuhamma1&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K16" t="b">
-        <v>0</v>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>8h</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>Apr 6, 2026 · 7:56 PM UTC</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="n">
-        <v>46118.83055555556</v>
-      </c>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>['https://x.com/AyshaMoham64638', 'https://x.com/Sarahfa40636602', 'https://x.com/Umehanimuhamma1']</t>
-        </is>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>5</v>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>through Emirates NBD, the fastest way is using the ENBD X mobile app.   @AyshaMoham64638 
-@Sarahfa40636602 
-@Umehanimuhamma1</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>https://x.com/Bushrasabih2/status/2041243638504796469</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>اجعل مفاجآت العيد أكثر قيمة.
+من الفضة إلى الذهب، اكتشف طريقة أذكى لامتلاك أو إهداء شيء ثمين بحق.
+شاهد هذه الحلقة وأخبرنا:
+كيف يمكنك شراء الذهب والفضه من البنك؟
+للمشاركة:
+تابع حساب بنك الإمارات دبي الوطني 
+قم بالإشارة إلى 3 من أصدقائك
+اكتب إجابتك في التعليقات أدناه لفرصة ربح 10,000 درهم</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>through Emirates NBD, the fastest way is using the ENBD X mobile app.   @AyshaMoham64638 
-@Sarahfa40636602 
-@Umehanimuhamma1</t>
+          <t>اجعل مفاجآت العيد أكثر قيمة.
+من الفضة إلى الذهب، اكتشف طريقة أذكى لامتلاك أو إهداء شيء ثمين بحق.
+شاهد هذه الحلقة وأخبرنا:
+كيف يمكنك شراء الذهب والفضه من البنك؟
+للمشاركة:
+تابع حساب بنك الإمارات دبي الوطني 
+قم بالإشارة إلى 3 من أصدقائك
+اكتب إجابتك في التعليقات أدناه لفرصة ربح 10,000 درهم</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Through Emirates NBD, the fastest way is using the ENBD X mobile app.</t>
+          <t>Make holiday surprises more valuable. From silver to gold, discover a smarter way to own or gift something truly precious. Watch this episode and tell us: How can you buy gold and silver from the bank? 
+To participate: Follow the Emirates NBD account Tag 3 of your friends Write your answer in the comments below for a chance to win 10,000 dirhams.</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -3237,7 +3194,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Through Emirates NBD, the fastest way is using the ENBD X mobile app.</t>
+          <t>To participate: Follow the Emirates NBD account Tag 3 of your friends Write your answer in the comments below for a chance to win 10,000 dirhams. • From silver to gold, discover a smarter way to own or gift something truly precious. • Watch this episode and tell us: How can you buy gold and silver from the bank?</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -3864,7 +3821,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Sharjah Islamic Bank launches a strategic rights issue to raise proceeds of up to 2.59 billion AED. Thread with key details.</t>
+          <t>Sharjah Islamic Bank launches a strategic rights issue to raise proceeds of up to 2.59 billion UAE dirhams. Thread with the key details.</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3895,7 +3852,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Sharjah Islamic Bank launches a strategic rights issue to raise proceeds of up to 2.59 billion AED.</t>
+          <t>Sharjah Islamic Bank launches a strategic rights issue to raise proceeds of up to 2.59 billion UAE dirhams. • Thread with the key details.</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -4817,7 +4774,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026 is going to be very painful... Mashallah</t>
+          <t>2026 is going to be very difficult... Mashallah</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -4848,7 +4805,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>2026 is going to be very painful...</t>
+          <t>2026 is going to be very difficult...</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -5058,8 +5015,7 @@
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>فى ناس بتشكر فى بنك ابو ظبى و بنك دبى الوطنى أو اى بنك تانى فى مصر 🇪🇬 حد عنده سابقة تعامل معاهم؟
-علشان لما انزل مصر أتعامل معاهم</t>
+          <t>@7ego_gedan الاتنين كويسين شوف اللي فيه مميزات أكتر واتوكل على الله .. الاتنين الاونلاين بتاعهم ممتاز .. اتوقع تسهيلات ENBD أكتر من FAB</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -5120,19 +5076,17 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>فى ناس بتشكر فى بنك ابو ظبى و بنك دبى الوطنى أو اى بنك تانى فى مصر 🇪🇬 حد عنده سابقة تعامل معاهم؟
-علشان لما انزل مصر أتعامل معاهم</t>
+          <t>@7ego_gedan الاتنين كويسين شوف اللي فيه مميزات أكتر واتوكل على الله .. الاتنين الاونلاين بتاعهم ممتاز .. اتوقع تسهيلات ENBD أكتر من FAB</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>فى ناس بتشكر فى بنك ابو ظبى و بنك دبى الوطنى أو اى بنك تانى فى مصر 🇪🇬 حد عنده سابقة تعامل معاهم؟
-علشان لما انزل مصر أتعامل معاهم</t>
+          <t>@7ego_gedan الاتنين كويسين شوف اللي فيه مميزات أكتر واتوكل على الله .. الاتنين الاونلاين بتاعهم ممتاز .. اتوقع تسهيلات ENBD أكتر من FAB</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>There are people praising Abu Dhabi Bank and Dubai National Bank or any other bank in Egypt. Does anyone have previous experience dealing with them? Because when I go down to Egypt, I want to deal with them.</t>
+          <t>Both are good, see which one has more features and trust in God. Their online services are excellent. I expect ENBD's facilities to be better than FAB's.</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -5142,7 +5096,7 @@
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE28" s="2" t="n">
@@ -5163,7 +5117,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>There are people praising Abu Dhabi Bank and Dubai National Bank or any other bank in Egypt. • Does anyone have previous experience dealing with them? • Because when I go down to Egypt, I want to deal with them.</t>
+          <t>Both are good, see which one has more features and trust in God. • I expect ENBD's facilities to be better than FAB's. • Their online services are excellent.</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -5217,9 +5171,8 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>بنك الامارات دبي الوطني ENBD
-بنك أبوظبي الأول FAB
-دول التوب عندنا في الامارات، معرفش أخبارهم في مصر</t>
+          <t>فى ناس بتشكر فى بنك ابو ظبى و بنك دبى الوطنى أو اى بنك تانى فى مصر 🇪🇬 حد عنده سابقة تعامل معاهم؟
+علشان لما انزل مصر أتعامل معاهم</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -5277,20 +5230,26 @@
 دول التوب عندنا في الامارات، معرفش أخبارهم في مصر</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>https://x.com/noora_ahmed90/status/2041173531770466409</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>فى ناس بتشكر فى بنك ابو ظبى و بنك دبى الوطنى أو اى بنك تانى فى مصر 🇪🇬 حد عنده سابقة تعامل معاهم؟
+علشان لما انزل مصر أتعامل معاهم</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>بنك الامارات دبي الوطني ENBD
-بنك أبوظبي الأول FAB
-دول التوب عندنا في الامارات، معرفش أخبارهم في مصر</t>
+          <t>فى ناس بتشكر فى بنك ابو ظبى و بنك دبى الوطنى أو اى بنك تانى فى مصر 🇪🇬 حد عنده سابقة تعامل معاهم؟
+علشان لما انزل مصر أتعامل معاهم</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank  
-First Abu Dhabi Bank  
-The top countries for us in the UAE, I don't know their news in Egypt.</t>
+          <t>There are people praising Abu Dhabi Bank and Dubai National Bank or any other bank in Egypt. Does anyone have previous experience dealing with them? Because when I go to Egypt, I want to deal with them.</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -5321,7 +5280,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank First Abu Dhabi Bank The top countries for us in the UAE, I don't know their news in Egypt.</t>
+          <t>There are people praising Abu Dhabi Bank and Dubai National Bank or any other bank in Egypt. • Does anyone have previous experience dealing with them? • Because when I go to Egypt, I want to deal with them.</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -5798,7 +5757,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>Audience of Bo Saqr, get ready for an extraordinary night ❤️‍🔥🦅
+          <t>Audience of Bo Saqr, get ready for an exceptional night ❤️‍🔥🦅
 🎫👇🏻🔗 https://t.co/eEeydFxVFN
 #Rabeh_Saqer_in_Jeddah 
 #Jeddah_Season 
@@ -5837,7 +5796,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Audience of Bo Saqr, get ready for an extraordinary night ❤️‍🔥🦅 🎫👇🏻🔗 https://t.co/eEeydFxVFN #Rabeh_Saqer_in_Jeddah #Jed…</t>
+          <t>Audience of Bo Saqr, get ready for an exceptional night ❤️‍🔥🦅 🎫👇🏻🔗 https://t.co/eEeydFxVFN #Rabeh_Saqer_in_Jeddah #Jedda…</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -6139,7 +6098,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Hey, call me, I need something from your customer service.</t>
+          <t>Hey Emirates NBD, I want to contact your customer service.</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -6170,7 +6129,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Hey, call me, I need something from your customer service.</t>
+          <t>Hey Emirates NBD, I want to contact your customer service.</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
@@ -6321,12 +6280,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>RBL Bank: The central bank approved Emirates NBD Bank's acquisition of a 74% stake in the company, with voting rights limited to 26%.
+          <t>RBL Bank: The central bank approved Emirates NBD Bank to acquire a 74% stake in the company, with voting rights capped at 26%.
 ➡️ Additionally, the bank provided its business updates
 🔹Total deposits increased by 25% year-over-year, 16% quarter-over-quarter 
-🔹Gross Advances rose by 22% year-over-year, 11% quarter-over-quarter 
-🔹Liquidity Coverage Ratio: 130% compared to 133% year-over-year, 125% quarter-over-quarter 
-🔹CASA Ratio: 33.6% compared to 34.1% year-over-year, 30.9% quarter-over-quarter.
+🔹Gross advances rose by 22% year-over-year, 11% quarter-over-quarter 
+🔹Liquidity coverage ratio: 130% compared to 133% year-over-year, 125% quarter-over-quarter 
+🔹CASA ratio: 33.6% compared to 34.1% year-over-year, 30.9% quarter-over-quarter.
 The stock closed up 5.32%.</t>
         </is>
       </c>
@@ -6358,7 +6317,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>RBL Bank: The central bank approved Emirates NBD Bank's acquisition of a 74% stake in the company, with voting rights limited to 26%. • The stock closed up 5.32%.</t>
+          <t>RBL Bank: The central bank approved Emirates NBD Bank to acquire a 74% stake in the company, with voting rights capped at 26%. • The stock closed up 5.32%.</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -7075,9 +7034,7 @@
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Do you verify links?
-Stay Safe, Stay Vigilant. #UnitedAgainstFraud
-https://t.co/YpRWtBZrhq</t>
+          <t>@EmiratesNBD_AE When will you announce the Feb millionaire draw? Wasn’t this supposed to be announce on 26th of Feb?</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -7138,22 +7095,17 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>Do you verify links?
-Stay Safe, Stay Vigilant. #UnitedAgainstFraud
-https://t.co/YpRWtBZrhq</t>
+          <t>@EmiratesNBD_AE When will you announce the Feb millionaire draw? Wasn’t this supposed to be announce on 26th of Feb?</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>Do you verify links?
-Stay Safe, Stay Vigilant. #UnitedAgainstFraud
-https://t.co/YpRWtBZrhq</t>
+          <t>@EmiratesNBD_AE When will you announce the Feb millionaire draw? Wasn’t this supposed to be announce on 26th of Feb?</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>Do you verify links? 
-Stay Safe, Stay Vigilant. #UnitedAgainstFraud</t>
+          <t>When will you announce the February millionaire draw? Wasn’t this supposed to be announced on the 26th of February?</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -7184,7 +7136,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Stay Safe, Stay Vigilant.</t>
+          <t>Wasn’t this supposed to be announced on the 26th of February? • When will you announce the February millionaire draw?</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
@@ -8477,7 +8429,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>RBL Bank reaches an intraday high of ₹310 after the RBI approves the Emirates NBD acquisition, with management stating that the outlook for FY26 is positive, boosting investor sentiment.</t>
+          <t>RBL Bank reaches an intraday high of ₹310 after the RBI approves the Emirates NBD acquisition, with management stating that the FY26 outlook is positive, boosting investor sentiment.</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -8508,7 +8460,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>RBL Bank reaches an intraday high of ₹310 after the RBI approves the Emirates NBD acquisition, with management stating that the outlook for FY26 is positive, boosting investor sentiment.</t>
+          <t>RBL Bank reaches an intraday high of ₹310 after the RBI approves the Emirates NBD acquisition, with management stating that the FY26 outlook is positive, boosting investor sentiment.</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
@@ -8785,7 +8737,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>CITI on RBL BK Buy, TP Rs 390 RBL delivered robust business momentum, with a sharp acceleration in advances growth to 22% YoY/11% QoQ (from 13.5% YoY in 3Q). More prominently, retail advances grew 18% YoY/10% QoQ, led by a surge in secured retail by 36% YoY/17% QoQ (Prime LAP/Small).</t>
+          <t>CITI has a buy rating on RBL Bank with a target price of Rs 390. RBL has shown strong business momentum, with a significant increase in advances growth to 22% year-on-year and 11% quarter-on-quarter (up from 13.5% year-on-year in the third quarter). Notably, retail advances grew by 18% year-on-year and 10% quarter-on-quarter, driven by a 36% year-on-year and 17% quarter-on-quarter surge in secured retail.</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -8816,7 +8768,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>CITI on RBL BK Buy, TP Rs 390 RBL delivered robust business momentum, with a sharp acceleration in advances growth to 22% YoY/11% QoQ (from 13.5% YoY in 3Q). • More prominently, retail advances grew 18% YoY/10% QoQ, led by a surge in secured retail by 36% YoY/17% QoQ (Prime LAP/Small).</t>
+          <t>Notably, retail advances grew by 18% year-on-year and 10% quarter-on-quarter, driven by a 36% year-on-year and 17% quarter-on-quarter surge in secured retail. • RBL has shown strong business momentum, with a significant increase in advances growth to 22% year-on-year and 11% quarter-on-quarter (up from 13.5% year-on-year in the third quarter). • CITI has a buy rating on RBL Bank with a target price of Rs 390.</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
@@ -9131,7 +9083,7 @@
       <c r="AB52" t="inlineStr">
         <is>
           <t>A smarter way to pay your employees' salaries.
-You can now easily manage and pay the salaries of employees and domestic workers through the Abu Dhabi Islamic Bank app using the Wage Protection System.
+You can now easily manage and pay the salaries of employees and domestic workers through the Abu Dhabi Islamic Bank app via the Wage Protection System.
 ✔ Compliance with the Wage Protection System and the Ministry of Human Resources and Emiratisation
 ✔ Update employee and employer information
 ✔ Easily transfer salaries to an IBAN number or card
@@ -9170,7 +9122,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>You can now easily manage and pay the salaries of employees and domestic workers through the Abu Dhabi Islamic Bank app using the Wage Protection System. • A smarter way to pay your employees' salaries. • For more information: https://t.co/P8icnxmTW4 Terms and conditions apply.</t>
+          <t>You can now easily manage and pay the salaries of employees and domestic workers through the Abu Dhabi Islamic Bank app via the Wage Protection System. • A smarter way to pay your employees' salaries. • For more information: https://t.co/P8icnxmTW4 Terms and conditions apply.</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
@@ -9193,43 +9145,203 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2041148131039953343</t>
+          <t>2041054585297740229</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2041148131039953343</t>
+          <t>https://x.com/kmz1993/status/2041054585297740229</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/kmz1993</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>kmz1993</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t> خالد</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1475344667810349059/JlxW8n_8_bigger.jpg</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp;amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
-✅ No annual membership fee
-📈 Earn up to 3.75% EI SmartMiles back per AED spend https://t.co/w44IfzD38h</t>
+          <t>للأسف موظفينكم يخبصون في الشغل، أنا عندي موضوع قدمت عليه والتخبط واضح بين الموظفين وكل شخص يلوم القسم الآخر وفي النهاية القسم المختص لا يرد على إستفساراتنا ولا على المراسلات من الموظفين الآخرين
+أما @emiratesislamic خلصوا موضوعي بسهولة يوم طلبت منهم وهم بصراحة أفضل مصرف إسلامي 👏🏼</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
+        <is>
+          <t>للأسف موظفينكم يخبصون في الشغل، أنا عندي موضوع قدمت عليه والتخبط واضح بين الموظفين وكل شخص يلوم القسم الآخر وفي النهاية القسم المختص لا يرد على إستفساراتنا ولا على المراسلات من الموظفين الآخرين
+أما &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; خلصوا موضوعي بسهولة يوم طلبت منهم وهم بصراحة أفضل مصرف إسلامي 👏🏼</t>
+        </is>
+      </c>
+      <c r="K53" t="b">
+        <v>0</v>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>['ADIBTweets']</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Apr 6, 2026 · 7:25 AM UTC</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="n">
+        <v>46118.30902777778</v>
+      </c>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>['https://x.com/emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="S53" t="n">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" t="n">
+        <v>41</v>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>للأسف موظفينكم يخبصون في الشغل، أنا عندي موضوع قدمت عليه والتخبط واضح بين الموظفين وكل شخص يلوم القسم الآخر وفي النهاية القسم المختص لا يرد على إستفساراتنا ولا على المراسلات من الموظفين الآخرين
+أما @emiratesislamic خلصوا موضوعي بسهولة يوم طلبت منهم وهم بصراحة أفضل مصرف إسلامي 👏🏼</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>للأسف موظفينكم يخبصون في الشغل، أنا عندي موضوع قدمت عليه والتخبط واضح بين الموظفين وكل شخص يلوم القسم الآخر وفي النهاية القسم المختص لا يرد على إستفساراتنا ولا على المراسلات من الموظفين الآخرين
+أما @emiratesislamic خلصوا موضوعي بسهولة يوم طلبت منهم وهم بصراحة أفضل مصرف إسلامي 👏🏼</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>Unfortunately, your employees are messing up the work. I have a matter I submitted, and the confusion among the employees is clear, with each person blaming the other department. In the end, the relevant department does not respond to our inquiries or to the communications from other employees. As for @emiratesislamic, they resolved my issue easily when I asked them, and honestly, they are the best Islamic bank.</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AE53" s="2" t="n">
+        <v>46118.47569444445</v>
+      </c>
+      <c r="AF53" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>2. Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>I have a matter I submitted, and the confusion among the employees is clear, with each person blaming the other department. • In the end, the relevant department does not respond to our inquiries or to the communications from other employees. • As for @emiratesislamic, they resolved my issue easily when I asked them, and honestly, they are the best Islamic bank.</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AK53" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL53" t="inlineStr">
+        <is>
+          <t>ADIBTweets</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2041148131039953343</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041148131039953343</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>🍔 50% discount on talabat
+🚗 Complimentary valet parking
+✈️ Complimentary airport lounge access
+💳 Metal Card with unique design
+And much more!
+📅 Offer valid till 30 April 2026
+emiratesislamic.ae/en/offers…</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
         <is>
           <t>🍔 50% discount on talabat
 🚗 Complimentary valet parking
@@ -9240,48 +9352,48 @@
 &lt;a href="https://www.emiratesislamic.ae/en/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_emarati"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K53" t="b">
-        <v>0</v>
-      </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr">
+      <c r="K54" t="b">
+        <v>0</v>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
         <is>
           <t>14h</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>Apr 6, 2026 · 1:36 PM UTC</t>
         </is>
       </c>
-      <c r="P53" s="2" t="n">
+      <c r="P54" s="2" t="n">
         <v>46118.56666666667</v>
       </c>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr">
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr">
         <is>
           <t>['https://www.emiratesislamic.ae/en/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_emarati']</t>
         </is>
       </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" t="n">
-        <v>0</v>
-      </c>
-      <c r="U53" t="n">
-        <v>0</v>
-      </c>
-      <c r="V53" t="n">
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" t="n">
         <v>87</v>
       </c>
-      <c r="W53" t="inlineStr">
+      <c r="W54" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>🍔 50% discount on talabat
 🚗 Complimentary valet parking
@@ -9292,194 +9404,28 @@
 emiratesislamic.ae/en/offers…</t>
         </is>
       </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2041148131039953343</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp;amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
-✅ No annual membership fee
-📈 Earn up to 3.75% EI SmartMiles back per AED spend https://t.co/w44IfzD38h</t>
-        </is>
-      </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp;amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
-✅ No annual membership fee
-📈 Earn up to 3.75% EI SmartMiles back per AED spend https://t.co/w44IfzD38h</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>Exclusively for Emiratis. Apply for an Emirati Credit Card and get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
-✅ No annual membership fee
-📈 Earn up to 3.75% EI SmartMiles back per AED spent</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="AD53" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="AE53" s="2" t="n">
-        <v>46118.73333333333</v>
-      </c>
-      <c r="AF53" s="2" t="n">
-        <v>46118</v>
-      </c>
-      <c r="AG53" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>Apply for an Emirati Credit Card and get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500 ✅ No annual membership fee 📈 Earn up to 3.75% EI SmartMiles back per AED spent • Exclusively for Emiratis.</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AK53" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL53" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="n">
-        <v>52</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2041148122731004026</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2041148122731004026</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>حصرياً للإماراتيين. تقدم بطلب بطاقة إماراتي الائتمانية واحصل على مكافأة ترحيبية تصل الى 150,000 ميل من أميال سمارت مايلز بقيمة 1,500 درهم
-✅ بدون رسوم عضوية سنوية
-📈استرداد لغاية %3.75 ميل من أميال سمارت مايلز مقابل كل درهم إماراتي تنفقه https://t.co/FksiIpdGQE</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp;amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
-✅ No annual membership fee
-📈 Earn up to 3.75% EI SmartMiles back per AED spend</t>
-        </is>
-      </c>
-      <c r="K54" t="b">
-        <v>0</v>
-      </c>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>14h</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>Apr 6, 2026 · 1:36 PM UTC</t>
-        </is>
-      </c>
-      <c r="P54" s="2" t="n">
-        <v>46118.56666666667</v>
-      </c>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="n">
-        <v>1</v>
-      </c>
-      <c r="T54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U54" t="n">
-        <v>0</v>
-      </c>
-      <c r="V54" t="n">
-        <v>87</v>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
-✅ No annual membership fee
-📈 Earn up to 3.75% EI SmartMiles back per AED spend</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2041148122731004026</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>حصرياً للإماراتيين. تقدم بطلب بطاقة إماراتي الائتمانية واحصل على مكافأة ترحيبية تصل الى 150,000 ميل من أميال سمارت مايلز بقيمة 1,500 درهم
-✅ بدون رسوم عضوية سنوية
-📈استرداد لغاية %3.75 ميل من أميال سمارت مايلز مقابل كل درهم إماراتي تنفقه https://t.co/FksiIpdGQE</t>
-        </is>
-      </c>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>حصرياً للإماراتيين. تقدم بطلب بطاقة إماراتي الائتمانية واحصل على مكافأة ترحيبية تصل الى 150,000 ميل من أميال سمارت مايلز بقيمة 1,500 درهم
-✅ بدون رسوم عضوية سنوية
-📈استرداد لغاية %3.75 ميل من أميال سمارت مايلز مقابل كل درهم إماراتي تنفقه https://t.co/FksiIpdGQE</t>
+          <t>🍔 50% discount on talabat
+🚗 Complimentary valet parking
+✈️ Complimentary airport lounge access
+💳 Metal Card with unique design
+And much more!
+📅 Offer valid till 30 April 2026
+emiratesislamic.ae/en/offers…</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>Exclusively for Emiratis. Apply for the Emirati credit card and receive a welcome bonus of up to 150,000 Smart Miles worth 1,500 dirhams.
-✅ No annual membership fees
-📈 Earn up to 3.75% Smart Miles for every dirham you spend.</t>
+          <t>50% discount on talabat
+Complimentary valet parking
+Complimentary airport lounge access
+Metal Card with unique design
+And much more!
+Offer valid till 30 April 2026
+emiratesislamic.ae/en/offers…</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -9510,7 +9456,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Apply for the Emirati credit card and receive a welcome bonus of up to 150,000 Smart Miles worth 1,500 dirhams. • ✅ No annual membership fees 📈 Earn up to 3.75% Smart Miles for every dirham you spend. • Exclusively for Emiratis.</t>
+          <t>50% discount on talabat Complimentary valet parking Complimentary airport lounge access Metal Card with unique design And much more! • Offer valid till 30 April 2026 emiratesislamic.ae/en/offers…</t>
         </is>
       </c>
       <c r="AJ54" t="inlineStr">
@@ -9533,12 +9479,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2041148111138029956</t>
+          <t>2041148122731004026</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2041148111138029956</t>
+          <t>https://x.com/emiratesislamic/status/2041148122731004026</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9563,6 +9509,170 @@
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
+        <is>
+          <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp;amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
+✅ No annual membership fee
+📈 Earn up to 3.75% EI SmartMiles back per AED spend https://t.co/w44IfzD38h</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp;amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
+✅ No annual membership fee
+📈 Earn up to 3.75% EI SmartMiles back per AED spend</t>
+        </is>
+      </c>
+      <c r="K55" t="b">
+        <v>0</v>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>14h</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Apr 6, 2026 · 1:36 PM UTC</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="n">
+        <v>46118.56666666667</v>
+      </c>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="n">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" t="n">
+        <v>87</v>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
+✅ No annual membership fee
+📈 Earn up to 3.75% EI SmartMiles back per AED spend</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041148122731004026</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp;amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
+✅ No annual membership fee
+📈 Earn up to 3.75% EI SmartMiles back per AED spend https://t.co/w44IfzD38h</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp;amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
+✅ No annual membership fee
+📈 Earn up to 3.75% EI SmartMiles back per AED spend https://t.co/w44IfzD38h</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>Exclusively for Emiratis. Apply for an Emirati Credit Card and get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
+✅ No annual membership fee
+📈 Earn up to 3.75% EI SmartMiles back per AED spent</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Bank</t>
+        </is>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AE55" s="2" t="n">
+        <v>46118.73333333333</v>
+      </c>
+      <c r="AF55" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>2. Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>Apply for an Emirati Credit Card and get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500 ✅ No annual membership fee 📈 Earn up to 3.75% EI SmartMiles back per AED spent • Exclusively for Emiratis.</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AK55" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL55" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2041148111138029956</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041148111138029956</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
         <is>
           <t>🍔 خصم لغاية %50 على طلبات
  🚗 خدمة صف السيارات
@@ -9570,10 +9680,10 @@
 💳 بطاقة معدنية بتصميم فريد
 وغير ذلك الكثير
 📅 يسري العرض لغاية 30 أبريل 2026
-https://t.co/WJhVBxsiSW https://t.co/kIPLvmgc4i</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
+emiratesislamic.ae/ar/offers…</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
         <is>
           <t>🍔 خصم لغاية %50 على طلبات
  🚗 خدمة صف السيارات
@@ -9584,48 +9694,48 @@
 &lt;a href="https://www.emiratesislamic.ae/ar/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_emarati"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K55" t="b">
-        <v>0</v>
-      </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr">
+      <c r="K56" t="b">
+        <v>0</v>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
         <is>
           <t>14h</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>Apr 6, 2026 · 1:36 PM UTC</t>
         </is>
       </c>
-      <c r="P55" s="2" t="n">
+      <c r="P56" s="2" t="n">
         <v>46118.56666666667</v>
       </c>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr">
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr">
         <is>
           <t>['https://www.emiratesislamic.ae/ar/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_emarati']</t>
         </is>
       </c>
-      <c r="S55" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" t="n">
-        <v>0</v>
-      </c>
-      <c r="U55" t="n">
-        <v>0</v>
-      </c>
-      <c r="V55" t="n">
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" t="n">
         <v>84</v>
       </c>
-      <c r="W55" t="inlineStr">
+      <c r="W56" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>🍔 خصم لغاية %50 على طلبات
  🚗 خدمة صف السيارات
@@ -9636,12 +9746,9 @@
 emiratesislamic.ae/ar/offers…</t>
         </is>
       </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2041148111138029956</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr">
         <is>
           <t>🍔 خصم لغاية %50 على طلبات
  🚗 خدمة صف السيارات
@@ -9649,184 +9756,19 @@
 💳 بطاقة معدنية بتصميم فريد
 وغير ذلك الكثير
 📅 يسري العرض لغاية 30 أبريل 2026
-https://t.co/WJhVBxsiSW https://t.co/kIPLvmgc4i</t>
-        </is>
-      </c>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>🍔 خصم لغاية %50 على طلبات
- 🚗 خدمة صف السيارات
- 🛫 الدخول إلى صالات المطارات
-💳 بطاقة معدنية بتصميم فريد
-وغير ذلك الكثير
-📅 يسري العرض لغاية 30 أبريل 2026
-https://t.co/WJhVBxsiSW https://t.co/kIPLvmgc4i</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
+emiratesislamic.ae/ar/offers…</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
         <is>
           <t>Up to 50% discount on orders  
 Valet service  
 Access to airport lounges  
-Unique design metal card  
+Unique designed metal card  
 And much more  
 The offer is valid until April 30, 2026</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="AD55" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="AE55" s="2" t="n">
-        <v>46118.73333333333</v>
-      </c>
-      <c r="AF55" s="2" t="n">
-        <v>46118</v>
-      </c>
-      <c r="AG55" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t>Up to 50% discount on orders Valet service Access to airport lounges Unique design metal card And much more The offer is valid until April 30, 2026</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AK55" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL55" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="n">
-        <v>54</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2041148101944074609</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2041148101944074609</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>حصرياً للإماراتيين. تقدم بطلب بطاقة إماراتي الائتمانية واحصل على مكافأة ترحيبية تصل الى 150,000 ميل من أميال سمارت مايلز بقيمة 1,500 درهم
-✅ بدون رسوم عضوية سنوية
-📈استرداد لغاية %3.75 ميل من أميال سمارت مايلز مقابل كل درهم إماراتي تنفقه</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>حصرياً للإماراتيين. تقدم بطلب بطاقة إماراتي الائتمانية واحصل على مكافأة ترحيبية تصل الى 150,000 ميل من أميال سمارت مايلز بقيمة 1,500 درهم
-✅ بدون رسوم عضوية سنوية
-📈استرداد لغاية %3.75 ميل من أميال سمارت مايلز مقابل كل درهم إماراتي تنفقه</t>
-        </is>
-      </c>
-      <c r="K56" t="b">
-        <v>0</v>
-      </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>14h</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>Apr 6, 2026 · 1:36 PM UTC</t>
-        </is>
-      </c>
-      <c r="P56" s="2" t="n">
-        <v>46118.56666666667</v>
-      </c>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
-      <c r="S56" t="n">
-        <v>1</v>
-      </c>
-      <c r="T56" t="n">
-        <v>0</v>
-      </c>
-      <c r="U56" t="n">
-        <v>0</v>
-      </c>
-      <c r="V56" t="n">
-        <v>130</v>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>حصرياً للإماراتيين. تقدم بطلب بطاقة إماراتي الائتمانية واحصل على مكافأة ترحيبية تصل الى 150,000 ميل من أميال سمارت مايلز بقيمة 1,500 درهم
-✅ بدون رسوم عضوية سنوية
-📈استرداد لغاية %3.75 ميل من أميال سمارت مايلز مقابل كل درهم إماراتي تنفقه</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr"/>
-      <c r="Z56" t="inlineStr"/>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>حصرياً للإماراتيين. تقدم بطلب بطاقة إماراتي الائتمانية واحصل على مكافأة ترحيبية تصل الى 150,000 ميل من أميال سمارت مايلز بقيمة 1,500 درهم
-✅ بدون رسوم عضوية سنوية
-📈استرداد لغاية %3.75 ميل من أميال سمارت مايلز مقابل كل درهم إماراتي تنفقه</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>Exclusively for Emiratis. Apply for the Emirati credit card and receive a welcome bonus of up to 150,000 Smart Miles worth 1,500 dirhams.
-✅ No annual membership fees
-📈 Earn up to 3.75% Smart Miles for every dirham you spend.</t>
-        </is>
-      </c>
       <c r="AC56" t="inlineStr">
         <is>
           <t>Bank</t>
@@ -9855,7 +9797,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>Apply for the Emirati credit card and receive a welcome bonus of up to 150,000 Smart Miles worth 1,500 dirhams. • ✅ No annual membership fees 📈 Earn up to 3.75% Smart Miles for every dirham you spend. • Exclusively for Emiratis.</t>
+          <t>Up to 50% discount on orders Valet service Access to airport lounges Unique designed metal card And much more The offer is valid until April 30, 2026</t>
         </is>
       </c>
       <c r="AJ56" t="inlineStr">
@@ -9878,12 +9820,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2041106421236801624</t>
+          <t>2041148101944074609</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2041106421236801624</t>
+          <t>https://x.com/emiratesislamic/status/2041148101944074609</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9909,40 +9851,40 @@
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
-          <t>أهلاً وسهلاً بك ، يسعدنا دائمًا تقديم المساعده</t>
+          <t>حصرياً للإماراتيين. تقدم بطلب بطاقة إماراتي الائتمانية واحصل على مكافأة ترحيبية تصل الى 150,000 ميل من أميال سمارت مايلز بقيمة 1,500 درهم
+✅ بدون رسوم عضوية سنوية
+📈استرداد لغاية %3.75 ميل من أميال سمارت مايلز مقابل كل درهم إماراتي تنفقه https://t.co/FksiIpdGQE</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>أهلاً وسهلاً بك ، يسعدنا دائمًا تقديم المساعده</t>
+          <t>حصرياً للإماراتيين. تقدم بطلب بطاقة إماراتي الائتمانية واحصل على مكافأة ترحيبية تصل الى 150,000 ميل من أميال سمارت مايلز بقيمة 1,500 درهم
+✅ بدون رسوم عضوية سنوية
+📈استرداد لغاية %3.75 ميل من أميال سمارت مايلز مقابل كل درهم إماراتي تنفقه</t>
         </is>
       </c>
       <c r="K57" t="b">
         <v>0</v>
       </c>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>['kmz1993']</t>
-        </is>
-      </c>
+      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Apr 6, 2026 · 10:51 AM UTC</t>
+          <t>Apr 6, 2026 · 1:36 PM UTC</t>
         </is>
       </c>
       <c r="P57" s="2" t="n">
-        <v>46118.45208333333</v>
+        <v>46118.56666666667</v>
       </c>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T57" t="n">
         <v>0</v>
@@ -9951,7 +9893,7 @@
         <v>0</v>
       </c>
       <c r="V57" t="n">
-        <v>5</v>
+        <v>130</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
@@ -9960,33 +9902,49 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>أهلاً وسهلاً بك ، يسعدنا دائمًا تقديم المساعده</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr"/>
-      <c r="Z57" t="inlineStr"/>
+          <t>حصرياً للإماراتيين. تقدم بطلب بطاقة إماراتي الائتمانية واحصل على مكافأة ترحيبية تصل الى 150,000 ميل من أميال سمارت مايلز بقيمة 1,500 درهم
+✅ بدون رسوم عضوية سنوية
+📈استرداد لغاية %3.75 ميل من أميال سمارت مايلز مقابل كل درهم إماراتي تنفقه</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041148101944074609</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>حصرياً للإماراتيين. تقدم بطلب بطاقة إماراتي الائتمانية واحصل على مكافأة ترحيبية تصل الى 150,000 ميل من أميال سمارت مايلز بقيمة 1,500 درهم
+✅ بدون رسوم عضوية سنوية
+📈استرداد لغاية %3.75 ميل من أميال سمارت مايلز مقابل كل درهم إماراتي تنفقه https://t.co/FksiIpdGQE</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>أهلاً وسهلاً بك ، يسعدنا دائمًا تقديم المساعده</t>
+          <t>حصرياً للإماراتيين. تقدم بطلب بطاقة إماراتي الائتمانية واحصل على مكافأة ترحيبية تصل الى 150,000 ميل من أميال سمارت مايلز بقيمة 1,500 درهم
+✅ بدون رسوم عضوية سنوية
+📈استرداد لغاية %3.75 ميل من أميال سمارت مايلز مقابل كل درهم إماراتي تنفقه https://t.co/FksiIpdGQE</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>Welcome, we are always happy to help.</t>
+          <t>Exclusively for Emiratis. Apply for the Emirati credit card and receive a welcome bonus of up to 150,000 Smart Miles worth 1,500 dirhams.
+✅ No annual membership fees
+📈 Earn up to 3.75% Smart Miles for every dirham you spend.</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Cust</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE57" s="2" t="n">
-        <v>46118.61875</v>
+        <v>46118.73333333333</v>
       </c>
       <c r="AF57" s="2" t="n">
         <v>46118</v>
@@ -10003,7 +9961,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>Welcome, we are always happy to help.</t>
+          <t>Apply for the Emirati credit card and receive a welcome bonus of up to 150,000 Smart Miles worth 1,500 dirhams. • ✅ No annual membership fees 📈 Earn up to 3.75% Smart Miles for every dirham you spend. • Exclusively for Emiratis.</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
@@ -10016,7 +9974,7 @@
       </c>
       <c r="AL57" t="inlineStr">
         <is>
-          <t>kmz1993</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -10026,12 +9984,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2041069339676221766</t>
+          <t>2041106421236801624</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2041069339676221766</t>
+          <t>https://x.com/emiratesislamic/status/2041106421236801624</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -10057,12 +10015,12 @@
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
-          <t>عزيزنا المتعامل ، يسرنا أن نعرب لك عن جزيل شكرنا لهذه الكلمات الطيبة. 💜</t>
+          <t>أهلاً وسهلاً بك ، يسعدنا دائمًا تقديم المساعده</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>عزيزنا المتعامل ، يسرنا أن نعرب لك عن جزيل شكرنا لهذه الكلمات الطيبة. 💜</t>
+          <t>أهلاً وسهلاً بك ، يسعدنا دائمًا تقديم المساعده</t>
         </is>
       </c>
       <c r="K58" t="b">
@@ -10076,21 +10034,21 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Apr 6, 2026 · 8:23 AM UTC</t>
+          <t>Apr 6, 2026 · 10:51 AM UTC</t>
         </is>
       </c>
       <c r="P58" s="2" t="n">
-        <v>46118.34930555556</v>
+        <v>46118.45208333333</v>
       </c>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T58" t="n">
         <v>0</v>
@@ -10099,7 +10057,7 @@
         <v>0</v>
       </c>
       <c r="V58" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="W58" t="inlineStr">
         <is>
@@ -10108,19 +10066,19 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>عزيزنا المتعامل ، يسرنا أن نعرب لك عن جزيل شكرنا لهذه الكلمات الطيبة. 💜</t>
+          <t>أهلاً وسهلاً بك ، يسعدنا دائمًا تقديم المساعده</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr"/>
       <c r="Z58" t="inlineStr"/>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>عزيزنا المتعامل ، يسرنا أن نعرب لك عن جزيل شكرنا لهذه الكلمات الطيبة. 💜</t>
+          <t>أهلاً وسهلاً بك ، يسعدنا دائمًا تقديم المساعده</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>Dear valued customer, we are pleased to express our sincere gratitude for these kind words. 💜</t>
+          <t>Welcome, we are always happy to help.</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
@@ -10134,7 +10092,7 @@
         </is>
       </c>
       <c r="AE58" s="2" t="n">
-        <v>46118.51597222222</v>
+        <v>46118.61875</v>
       </c>
       <c r="AF58" s="2" t="n">
         <v>46118</v>
@@ -10151,7 +10109,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>Dear valued customer, we are pleased to express our sincere gratitude for these kind words.</t>
+          <t>Welcome, we are always happy to help.</t>
         </is>
       </c>
       <c r="AJ58" t="inlineStr">
@@ -10174,12 +10132,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2041060043106246934</t>
+          <t>2041069339676221766</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2041060043106246934</t>
+          <t>https://x.com/emiratesislamic/status/2041069339676221766</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -10204,6 +10162,154 @@
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
+        <is>
+          <t>عزيزنا المتعامل ، يسرنا أن نعرب لك عن جزيل شكرنا لهذه الكلمات الطيبة. 💜</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>عزيزنا المتعامل ، يسرنا أن نعرب لك عن جزيل شكرنا لهذه الكلمات الطيبة. 💜</t>
+        </is>
+      </c>
+      <c r="K59" t="b">
+        <v>0</v>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>['kmz1993']</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>19h</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Apr 6, 2026 · 8:23 AM UTC</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="n">
+        <v>46118.34930555556</v>
+      </c>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="n">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" t="n">
+        <v>11</v>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>عزيزنا المتعامل ، يسرنا أن نعرب لك عن جزيل شكرنا لهذه الكلمات الطيبة. 💜</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>عزيزنا المتعامل ، يسرنا أن نعرب لك عن جزيل شكرنا لهذه الكلمات الطيبة. 💜</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>Dear valued customer, we are pleased to express our sincere gratitude for these kind words. 💜</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AE59" s="2" t="n">
+        <v>46118.51597222222</v>
+      </c>
+      <c r="AF59" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="AG59" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>2. Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>Dear valued customer, we are pleased to express our sincere gratitude for these kind words.</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AK59" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL59" t="inlineStr">
+        <is>
+          <t>kmz1993</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2041060091449823599</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041060091449823599</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
         <is>
           <t>Get a guaranteed iPhone 17 when you apply for an Emirates Islamic Personal Finance.
 Also, enjoy exclusive benefits:
@@ -10211,65 +10317,65 @@
 🏦 Finance amount of up to AED 4,000,000 https://t.co/XHOglWcH6G</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
 رسالتك الخاصه.</t>
         </is>
       </c>
-      <c r="K59" t="b">
-        <v>0</v>
-      </c>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
+      <c r="K60" t="b">
+        <v>0</v>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
         <is>
           <t>['MatarAlAl']</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t>20h</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>Apr 6, 2026 · 7:46 AM UTC</t>
-        </is>
-      </c>
-      <c r="P59" s="2" t="n">
-        <v>46118.32361111111</v>
-      </c>
-      <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr"/>
-      <c r="S59" t="n">
-        <v>0</v>
-      </c>
-      <c r="T59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U59" t="n">
-        <v>0</v>
-      </c>
-      <c r="V59" t="n">
-        <v>18</v>
-      </c>
-      <c r="W59" t="inlineStr">
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Apr 6, 2026 · 7:47 AM UTC</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="n">
+        <v>46118.32430555556</v>
+      </c>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" t="n">
+        <v>15</v>
+      </c>
+      <c r="W60" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
+      <c r="X60" t="inlineStr">
         <is>
           <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
 رسالتك الخاصه.</t>
         </is>
       </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2041060043106246934</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041060091449823599</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
         <is>
           <t>Get a guaranteed iPhone 17 when you apply for an Emirates Islamic Personal Finance.
 Also, enjoy exclusive benefits:
@@ -10277,7 +10383,7 @@
 🏦 Finance amount of up to AED 4,000,000 https://t.co/XHOglWcH6G</t>
         </is>
       </c>
-      <c r="AA59" t="inlineStr">
+      <c r="AA60" t="inlineStr">
         <is>
           <t>Get a guaranteed iPhone 17 when you apply for an Emirates Islamic Personal Finance.
 Also, enjoy exclusive benefits:
@@ -10285,7 +10391,7 @@
 🏦 Finance amount of up to AED 4,000,000 https://t.co/XHOglWcH6G</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
+      <c r="AB60" t="inlineStr">
         <is>
           <t>Get a guaranteed iPhone 17 when you apply for an Emirates Islamic Personal Finance.
 Also, enjoy exclusive benefits:
@@ -10293,174 +10399,18 @@
 🏦 Finance amount of up to AED 4,000,000</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
+      <c r="AC60" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="AD59" t="inlineStr">
+      <c r="AD60" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="AE59" s="2" t="n">
-        <v>46118.49027777778</v>
-      </c>
-      <c r="AF59" s="2" t="n">
-        <v>46118</v>
-      </c>
-      <c r="AG59" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AI59" t="inlineStr">
-        <is>
-          <t>Also, enjoy exclusive benefits: 📊 Profit rates starting from 2.59% flat per annum (approximately equivalent to 4.74% per annum reducing profit rate) 🏦 Finance amount of up to AED 4,000,000 • Get a guaranteed iPhone 17 when you apply for an Emirates Islamic Personal Finance.</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AK59" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL59" t="inlineStr">
-        <is>
-          <t>MatarAlAl</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="1" t="n">
-        <v>58</v>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>2041055155320152414</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2041055155320152414</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>Keep your savings separate from daily spending and set clear financial goals, with the flexibility to access your money when needed.
-Strong financial well-being begins with consistent saving, no matter the amount.
-To know more visit  emiratesislamic.ae/en/Person…</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>Keep your savings separate from daily spending and set clear financial goals, with the flexibility to access your money when needed.
-Strong financial well-being begins with consistent saving, no matter the amount.
-To know more visit  &lt;a href="https://www.emiratesislamic.ae/en/Personal-Banking/accounts/savings-account?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=savings_account"&gt;emiratesislamic.ae/en/Person…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K60" t="b">
-        <v>0</v>
-      </c>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>20h</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>Apr 6, 2026 · 7:27 AM UTC</t>
-        </is>
-      </c>
-      <c r="P60" s="2" t="n">
-        <v>46118.31041666667</v>
-      </c>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/Personal-Banking/accounts/savings-account?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=savings_account']</t>
-        </is>
-      </c>
-      <c r="S60" t="n">
-        <v>0</v>
-      </c>
-      <c r="T60" t="n">
-        <v>0</v>
-      </c>
-      <c r="U60" t="n">
-        <v>0</v>
-      </c>
-      <c r="V60" t="n">
-        <v>41</v>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>Keep your savings separate from daily spending and set clear financial goals, with the flexibility to access your money when needed.
-Strong financial well-being begins with consistent saving, no matter the amount.
-To know more visit  emiratesislamic.ae/en/Person…</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr"/>
-      <c r="Z60" t="inlineStr"/>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>Keep your savings separate from daily spending and set clear financial goals, with the flexibility to access your money when needed.
-Strong financial well-being begins with consistent saving, no matter the amount.
-To know more visit  emiratesislamic.ae/en/Person…</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>Keep your savings separate from daily spending and set clear financial goals, with the flexibility to access your money when needed. Strong financial well-being begins with consistent saving, no matter the amount. To know more visit emiratesislamic.ae/en/Person…</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="AD60" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
       <c r="AE60" s="2" t="n">
-        <v>46118.47708333333</v>
+        <v>46118.49097222222</v>
       </c>
       <c r="AF60" s="2" t="n">
         <v>46118</v>
@@ -10477,7 +10427,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>Keep your savings separate from daily spending and set clear financial goals, with the flexibility to access your money when needed. • Strong financial well-being begins with consistent saving, no matter the amount. • To know more visit emiratesislamic.ae/en/Person…</t>
+          <t>Also, enjoy exclusive benefits: 📊 Profit rates starting from 2.59% flat per annum (approximately equivalent to 4.74% per annum reducing profit rate) 🏦 Finance amount of up to AED 4,000,000 • Get a guaranteed iPhone 17 when you apply for an Emirates Islamic Personal Finance.</t>
         </is>
       </c>
       <c r="AJ60" t="inlineStr">
@@ -10490,7 +10440,7 @@
       </c>
       <c r="AL60" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MatarAlAl</t>
         </is>
       </c>
     </row>
@@ -10500,12 +10450,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2041055153344651481</t>
+          <t>2041055155320152414</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2041055153344651481</t>
+          <t>https://x.com/emiratesislamic/status/2041055155320152414</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10531,12 +10481,16 @@
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
-          <t>سواء كنت تُخطط لنفقاتك الشهرية أو تعمل على تحقيق أهداف مالية طويلة المدى، فإن حساب التوفير المخصص يمنحك وضوحاً وانضباطاً في إدارة أموالك. يمكنك فصل مدّخراتك عن مصاريفك اليومية، ووضع أهدافاً مالية واضحة، مع مرونة الوصول إلى أموالك عند الحاجة.</t>
+          <t>Keep your savings separate from daily spending and set clear financial goals, with the flexibility to access your money when needed.
+Strong financial well-being begins with consistent saving, no matter the amount.
+To know more visit  emiratesislamic.ae/en/Person…</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Whether you&amp;#39;re budgeting for monthly expenses, or working towards long-term goals, a dedicated savings account helps you stay disciplined and organized.</t>
+          <t>Keep your savings separate from daily spending and set clear financial goals, with the flexibility to access your money when needed.
+Strong financial well-being begins with consistent saving, no matter the amount.
+To know more visit  &lt;a href="https://www.emiratesislamic.ae/en/Personal-Banking/accounts/savings-account?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=savings_account"&gt;emiratesislamic.ae/en/Person…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K61" t="b">
@@ -10558,9 +10512,13 @@
         <v>46118.31041666667</v>
       </c>
       <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/Personal-Banking/accounts/savings-account?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=savings_account']</t>
+        </is>
+      </c>
       <c r="S61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T61" t="n">
         <v>0</v>
@@ -10569,7 +10527,7 @@
         <v>0</v>
       </c>
       <c r="V61" t="n">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="W61" t="inlineStr">
         <is>
@@ -10578,27 +10536,23 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Whether you're budgeting for monthly expenses, or working towards long-term goals, a dedicated savings account helps you stay disciplined and organized.</t>
-        </is>
-      </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2041055153344651481</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>سواء كنت تُخطط لنفقاتك الشهرية أو تعمل على تحقيق أهداف مالية طويلة المدى، فإن حساب التوفير المخصص يمنحك وضوحاً وانضباطاً في إدارة أموالك. يمكنك فصل مدّخراتك عن مصاريفك اليومية، ووضع أهدافاً مالية واضحة، مع مرونة الوصول إلى أموالك عند الحاجة.</t>
-        </is>
-      </c>
+          <t>Keep your savings separate from daily spending and set clear financial goals, with the flexibility to access your money when needed.
+Strong financial well-being begins with consistent saving, no matter the amount.
+To know more visit  emiratesislamic.ae/en/Person…</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>سواء كنت تُخطط لنفقاتك الشهرية أو تعمل على تحقيق أهداف مالية طويلة المدى، فإن حساب التوفير المخصص يمنحك وضوحاً وانضباطاً في إدارة أموالك. يمكنك فصل مدّخراتك عن مصاريفك اليومية، ووضع أهدافاً مالية واضحة، مع مرونة الوصول إلى أموالك عند الحاجة.</t>
+          <t>Keep your savings separate from daily spending and set clear financial goals, with the flexibility to access your money when needed.
+Strong financial well-being begins with consistent saving, no matter the amount.
+To know more visit  emiratesislamic.ae/en/Person…</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>Whether you are planning your monthly expenses or working towards long-term financial goals, a dedicated savings account provides you with clarity and discipline in managing your money. You can separate your savings from your daily expenses, set clear financial goals, and have the flexibility to access your funds when needed.</t>
+          <t>Keep your savings separate from daily spending and set clear financial goals, with the flexibility to access your money when needed. Strong financial well-being begins with consistent saving, no matter the amount. To know more visit emiratesislamic.ae/en/Person…</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
@@ -10629,7 +10583,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Whether you are planning your monthly expenses or working towards long-term financial goals, a dedicated savings account provides you with clarity and discipline in managing your money. • You can separate your savings from your daily expenses, set clear financial goals, and have the flexibility to access your funds when needed.</t>
+          <t>Keep your savings separate from daily spending and set clear financial goals, with the flexibility to access your money when needed. • Strong financial well-being begins with consistent saving, no matter the amount. • To know more visit emiratesislamic.ae/en/Person…</t>
         </is>
       </c>
       <c r="AJ61" t="inlineStr">
@@ -10652,12 +10606,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2041055144217915495</t>
+          <t>2041055153344651481</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2041055144217915495</t>
+          <t>https://x.com/emiratesislamic/status/2041055153344651481</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10683,16 +10637,12 @@
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
-          <t>الاستقرار المالي يبدأ بالادّخار المنتظم، بغض النظر عن المبلغ.
-للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
-emiratesislamic.ae/ar/Person…</t>
+          <t>سواء كنت تُخطط لنفقاتك الشهرية أو تعمل على تحقيق أهداف مالية طويلة المدى، فإن حساب التوفير المخصص يمنحك وضوحاً وانضباطاً في إدارة أموالك. يمكنك فصل مدّخراتك عن مصاريفك اليومية، ووضع أهدافاً مالية واضحة، مع مرونة الوصول إلى أموالك عند الحاجة.</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>الاستقرار المالي يبدأ بالادّخار المنتظم، بغض النظر عن المبلغ.
-للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
-&lt;a href="https://www.emiratesislamic.ae/ar/Personal-Banking/accounts/savings-account?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=savings_account"&gt;emiratesislamic.ae/ar/Person…&lt;/a&gt;</t>
+          <t>Whether you&amp;#39;re budgeting for monthly expenses, or working towards long-term goals, a dedicated savings account helps you stay disciplined and organized.</t>
         </is>
       </c>
       <c r="K62" t="b">
@@ -10714,11 +10664,7 @@
         <v>46118.31041666667</v>
       </c>
       <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/ar/Personal-Banking/accounts/savings-account?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=savings_account']</t>
-        </is>
-      </c>
+      <c r="R62" t="inlineStr"/>
       <c r="S62" t="n">
         <v>1</v>
       </c>
@@ -10729,7 +10675,7 @@
         <v>0</v>
       </c>
       <c r="V62" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="W62" t="inlineStr">
         <is>
@@ -10738,23 +10684,27 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>الاستقرار المالي يبدأ بالادّخار المنتظم، بغض النظر عن المبلغ.
-للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
-emiratesislamic.ae/ar/Person…</t>
-        </is>
-      </c>
-      <c r="Y62" t="inlineStr"/>
-      <c r="Z62" t="inlineStr"/>
+          <t>Whether you're budgeting for monthly expenses, or working towards long-term goals, a dedicated savings account helps you stay disciplined and organized.</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041055153344651481</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>سواء كنت تُخطط لنفقاتك الشهرية أو تعمل على تحقيق أهداف مالية طويلة المدى، فإن حساب التوفير المخصص يمنحك وضوحاً وانضباطاً في إدارة أموالك. يمكنك فصل مدّخراتك عن مصاريفك اليومية، ووضع أهدافاً مالية واضحة، مع مرونة الوصول إلى أموالك عند الحاجة.</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>الاستقرار المالي يبدأ بالادّخار المنتظم، بغض النظر عن المبلغ.
-للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
-emiratesislamic.ae/ar/Person…</t>
+          <t>سواء كنت تُخطط لنفقاتك الشهرية أو تعمل على تحقيق أهداف مالية طويلة المدى، فإن حساب التوفير المخصص يمنحك وضوحاً وانضباطاً في إدارة أموالك. يمكنك فصل مدّخراتك عن مصاريفك اليومية، ووضع أهدافاً مالية واضحة، مع مرونة الوصول إلى أموالك عند الحاجة.</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>Financial stability begins with regular saving, regardless of the amount. For more information, please visit the following link: emiratesislamic.ae/ar/Person…</t>
+          <t>Whether you are planning your monthly expenses or working towards long-term financial goals, a dedicated savings account provides you with clarity and discipline in managing your money. You can separate your savings from your daily expenses, set clear financial goals, and have the flexibility to access your funds when needed.</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
@@ -10785,7 +10735,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>Financial stability begins with regular saving, regardless of the amount. • For more information, please visit the following link: emiratesislamic.ae/ar/Person…</t>
+          <t>Whether you are planning your monthly expenses or working towards long-term financial goals, a dedicated savings account provides you with clarity and discipline in managing your money. • You can separate your savings from your daily expenses, set clear financial goals, and have the flexibility to access your funds when needed.</t>
         </is>
       </c>
       <c r="AJ62" t="inlineStr">
@@ -10808,12 +10758,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2041055106427183208</t>
+          <t>2041055144217915495</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2041055106427183208</t>
+          <t>https://x.com/emiratesislamic/status/2041055144217915495</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10839,12 +10789,16 @@
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
-          <t>سواء كنت تُخطط لنفقاتك الشهرية أو تعمل على تحقيق أهداف مالية طويلة المدى، فإن حساب التوفير المخصص يمنحك وضوحاً وانضباطاً في إدارة أموالك. يمكنك فصل مدّخراتك عن مصاريفك اليومية، ووضع أهدافاً مالية واضحة، مع مرونة الوصول إلى أموالك عند الحاجة.</t>
+          <t>الاستقرار المالي يبدأ بالادّخار المنتظم، بغض النظر عن المبلغ.
+للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
+emiratesislamic.ae/ar/Person…</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>سواء كنت تُخطط لنفقاتك الشهرية أو تعمل على تحقيق أهداف مالية طويلة المدى، فإن حساب التوفير المخصص يمنحك وضوحاً وانضباطاً في إدارة أموالك. يمكنك فصل مدّخراتك عن مصاريفك اليومية، ووضع أهدافاً مالية واضحة، مع مرونة الوصول إلى أموالك عند الحاجة.</t>
+          <t>الاستقرار المالي يبدأ بالادّخار المنتظم، بغض النظر عن المبلغ.
+للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
+&lt;a href="https://www.emiratesislamic.ae/ar/Personal-Banking/accounts/savings-account?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=savings_account"&gt;emiratesislamic.ae/ar/Person…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K63" t="b">
@@ -10866,7 +10820,11 @@
         <v>46118.31041666667</v>
       </c>
       <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr"/>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/Personal-Banking/accounts/savings-account?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=savings_account']</t>
+        </is>
+      </c>
       <c r="S63" t="n">
         <v>1</v>
       </c>
@@ -10877,7 +10835,7 @@
         <v>0</v>
       </c>
       <c r="V63" t="n">
-        <v>109</v>
+        <v>54</v>
       </c>
       <c r="W63" t="inlineStr">
         <is>
@@ -10886,19 +10844,23 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>سواء كنت تُخطط لنفقاتك الشهرية أو تعمل على تحقيق أهداف مالية طويلة المدى، فإن حساب التوفير المخصص يمنحك وضوحاً وانضباطاً في إدارة أموالك. يمكنك فصل مدّخراتك عن مصاريفك اليومية، ووضع أهدافاً مالية واضحة، مع مرونة الوصول إلى أموالك عند الحاجة.</t>
+          <t>الاستقرار المالي يبدأ بالادّخار المنتظم، بغض النظر عن المبلغ.
+للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
+emiratesislamic.ae/ar/Person…</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr"/>
       <c r="Z63" t="inlineStr"/>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>سواء كنت تُخطط لنفقاتك الشهرية أو تعمل على تحقيق أهداف مالية طويلة المدى، فإن حساب التوفير المخصص يمنحك وضوحاً وانضباطاً في إدارة أموالك. يمكنك فصل مدّخراتك عن مصاريفك اليومية، ووضع أهدافاً مالية واضحة، مع مرونة الوصول إلى أموالك عند الحاجة.</t>
+          <t>الاستقرار المالي يبدأ بالادّخار المنتظم، بغض النظر عن المبلغ.
+للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
+emiratesislamic.ae/ar/Person…</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>Whether you are planning your monthly expenses or working towards long-term financial goals, a dedicated savings account provides you with clarity and discipline in managing your money. You can separate your savings from your daily expenses, set clear financial goals, and have the flexibility to access your funds when needed.</t>
+          <t>Financial stability begins with regular saving, regardless of the amount. For more information, please visit the following link: emiratesislamic.ae/ar/Person…</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
@@ -10929,7 +10891,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>Whether you are planning your monthly expenses or working towards long-term financial goals, a dedicated savings account provides you with clarity and discipline in managing your money. • You can separate your savings from your daily expenses, set clear financial goals, and have the flexibility to access your funds when needed.</t>
+          <t>Financial stability begins with regular saving, regardless of the amount. • For more information, please visit the following link: emiratesislamic.ae/ar/Person…</t>
         </is>
       </c>
       <c r="AJ63" t="inlineStr">
@@ -10952,12 +10914,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2041040982007861527</t>
+          <t>2041055106427183208</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2041040982007861527</t>
+          <t>https://x.com/emiratesislamic/status/2041055106427183208</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10982,6 +10944,150 @@
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
+        <is>
+          <t>سواء كنت تُخطط لنفقاتك الشهرية أو تعمل على تحقيق أهداف مالية طويلة المدى، فإن حساب التوفير المخصص يمنحك وضوحاً وانضباطاً في إدارة أموالك. يمكنك فصل مدّخراتك عن مصاريفك اليومية، ووضع أهدافاً مالية واضحة، مع مرونة الوصول إلى أموالك عند الحاجة.</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>سواء كنت تُخطط لنفقاتك الشهرية أو تعمل على تحقيق أهداف مالية طويلة المدى، فإن حساب التوفير المخصص يمنحك وضوحاً وانضباطاً في إدارة أموالك. يمكنك فصل مدّخراتك عن مصاريفك اليومية، ووضع أهدافاً مالية واضحة، مع مرونة الوصول إلى أموالك عند الحاجة.</t>
+        </is>
+      </c>
+      <c r="K64" t="b">
+        <v>0</v>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Apr 6, 2026 · 7:27 AM UTC</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="n">
+        <v>46118.31041666667</v>
+      </c>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="n">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" t="n">
+        <v>109</v>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>سواء كنت تُخطط لنفقاتك الشهرية أو تعمل على تحقيق أهداف مالية طويلة المدى، فإن حساب التوفير المخصص يمنحك وضوحاً وانضباطاً في إدارة أموالك. يمكنك فصل مدّخراتك عن مصاريفك اليومية، ووضع أهدافاً مالية واضحة، مع مرونة الوصول إلى أموالك عند الحاجة.</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr"/>
+      <c r="Z64" t="inlineStr"/>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>سواء كنت تُخطط لنفقاتك الشهرية أو تعمل على تحقيق أهداف مالية طويلة المدى، فإن حساب التوفير المخصص يمنحك وضوحاً وانضباطاً في إدارة أموالك. يمكنك فصل مدّخراتك عن مصاريفك اليومية، ووضع أهدافاً مالية واضحة، مع مرونة الوصول إلى أموالك عند الحاجة.</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>Whether you are planning your monthly expenses or working towards long-term financial goals, a dedicated savings account provides you with clarity and discipline in managing your money. You can separate your savings from your daily expenses, set clear financial goals, and have the flexibility to access your funds when needed.</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Bank</t>
+        </is>
+      </c>
+      <c r="AD64" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE64" s="2" t="n">
+        <v>46118.47708333333</v>
+      </c>
+      <c r="AF64" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="AG64" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>2. Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>Whether you are planning your monthly expenses or working towards long-term financial goals, a dedicated savings account provides you with clarity and discipline in managing your money. • You can separate your savings from your daily expenses, set clear financial goals, and have the flexibility to access your funds when needed.</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AK64" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2041040982007861527</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041040982007861527</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
         <is>
           <t>احصل على iPhone 17 مضمون عند التقدم بطلب تمويل شخصي من الإمارات الإسلامي.
 استمتع أيضاً بالمزايا الحصرية:
@@ -10989,63 +11095,63 @@
 🏦 مبلغ تمويلي يصل إلى 4,000,000 درهم https://t.co/e3mQDmNB0B</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>عزيزنا المتعامل لقد حاولنا التواصل معك برسالة خاصة و لم ننجح في ذلك بسبب قواعد عدم متباعة الصفحة يرجى مراسلتنا برسالة خاصة لنتمكن من مساعدتك بطريقة أسرع</t>
         </is>
       </c>
-      <c r="K64" t="b">
-        <v>0</v>
-      </c>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
+      <c r="K65" t="b">
+        <v>0</v>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
         <is>
           <t>['mubi_111']</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t>21h</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t>Apr 6, 2026 · 6:31 AM UTC</t>
         </is>
       </c>
-      <c r="P64" s="2" t="n">
+      <c r="P65" s="2" t="n">
         <v>46118.27152777778</v>
       </c>
-      <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr"/>
-      <c r="S64" t="n">
-        <v>0</v>
-      </c>
-      <c r="T64" t="n">
-        <v>0</v>
-      </c>
-      <c r="U64" t="n">
-        <v>0</v>
-      </c>
-      <c r="V64" t="n">
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" t="n">
         <v>12</v>
       </c>
-      <c r="W64" t="inlineStr">
+      <c r="W65" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr">
+      <c r="X65" t="inlineStr">
         <is>
           <t>عزيزنا المتعامل لقد حاولنا التواصل معك برسالة خاصة و لم ننجح في ذلك بسبب قواعد عدم متباعة الصفحة يرجى مراسلتنا برسالة خاصة لنتمكن من مساعدتك بطريقة أسرع</t>
         </is>
       </c>
-      <c r="Y64" t="inlineStr">
+      <c r="Y65" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2041040982007861527</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
+      <c r="Z65" t="inlineStr">
         <is>
           <t>احصل على iPhone 17 مضمون عند التقدم بطلب تمويل شخصي من الإمارات الإسلامي.
 استمتع أيضاً بالمزايا الحصرية:
@@ -11053,7 +11159,7 @@
 🏦 مبلغ تمويلي يصل إلى 4,000,000 درهم https://t.co/e3mQDmNB0B</t>
         </is>
       </c>
-      <c r="AA64" t="inlineStr">
+      <c r="AA65" t="inlineStr">
         <is>
           <t>احصل على iPhone 17 مضمون عند التقدم بطلب تمويل شخصي من الإمارات الإسلامي.
 استمتع أيضاً بالمزايا الحصرية:
@@ -11061,187 +11167,26 @@
 🏦 مبلغ تمويلي يصل إلى 4,000,000 درهم https://t.co/e3mQDmNB0B</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
+      <c r="AB65" t="inlineStr">
         <is>
           <t>Get a guaranteed iPhone 17 when applying for a personal loan from Emirates Islamic.
 Also enjoy exclusive benefits:
 📊 Profit rates starting from 2.59% fixed annually (equivalent to approximately 4.74% as a declining annual rate).
-🏦 Financing amount up to 4,000,000 AED</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
+🏦 Financing amount up to 4,000,000 AED.</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="AD64" t="inlineStr">
+      <c r="AD65" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="AE64" s="2" t="n">
+      <c r="AE65" s="2" t="n">
         <v>46118.43819444445</v>
-      </c>
-      <c r="AF64" s="2" t="n">
-        <v>46118</v>
-      </c>
-      <c r="AG64" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>Also enjoy exclusive benefits: 📊 Profit rates starting from 2.59% fixed annually (equivalent to approximately 4.74% as a declining annual rate). • 🏦 Financing amount up to 4,000,000 AED • Get a guaranteed iPhone 17 when applying for a personal loan from Emirates Islamic.</t>
-        </is>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AK64" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL64" t="inlineStr">
-        <is>
-          <t>mubi_111</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="1" t="n">
-        <v>63</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>2041040843369320743</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2041040843369320743</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>@mubi_111 مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
-رسالتك الخاصه.</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
-رسالتك الخاصه.</t>
-        </is>
-      </c>
-      <c r="K65" t="b">
-        <v>0</v>
-      </c>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>['mubi_111']</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>21h</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>Apr 6, 2026 · 6:30 AM UTC</t>
-        </is>
-      </c>
-      <c r="P65" s="2" t="n">
-        <v>46118.27083333334</v>
-      </c>
-      <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="inlineStr"/>
-      <c r="S65" t="n">
-        <v>0</v>
-      </c>
-      <c r="T65" t="n">
-        <v>0</v>
-      </c>
-      <c r="U65" t="n">
-        <v>0</v>
-      </c>
-      <c r="V65" t="n">
-        <v>20</v>
-      </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X65" t="inlineStr">
-        <is>
-          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
-رسالتك الخاصه.</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2041040843369320743</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>@mubi_111 مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
-رسالتك الخاصه.</t>
-        </is>
-      </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>@mubi_111 مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
-رسالتك الخاصه.</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>Hello dear customer. Thank you for contacting us. To protect your privacy, we would like to inform you that we have responded to you in the same message within the previous post. In order for us to serve you better, please check your private message.</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD65" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AE65" s="2" t="n">
-        <v>46118.4375</v>
       </c>
       <c r="AF65" s="2" t="n">
         <v>46118</v>
@@ -11258,7 +11203,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>To protect your privacy, we would like to inform you that we have responded to you in the same message within the previous post. • In order for us to serve you better, please check your private message. • Thank you for contacting us.</t>
+          <t>Also enjoy exclusive benefits: 📊 Profit rates starting from 2.59% fixed annually (equivalent to approximately 4.74% as a declining annual rate). • 🏦 Financing amount up to 4,000,000 AED. • Get a guaranteed iPhone 17 when applying for a personal loan from Emirates Islamic.</t>
         </is>
       </c>
       <c r="AJ65" t="inlineStr">
@@ -11281,42 +11226,203 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2040952398034735414</t>
+          <t>2041040843369320743</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://x.com/0_ab1172/status/2040952398034735414</t>
+          <t>https://x.com/emiratesislamic/status/2041040843369320743</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://x.com/0_ab1172</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0_ab1172</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Abdulrahman</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1951463642324467712/XQYKCCfL_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
+          <t>@mubi_111 مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="K66" t="b">
+        <v>0</v>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>['mubi_111']</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Apr 6, 2026 · 6:30 AM UTC</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="n">
+        <v>46118.27083333334</v>
+      </c>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
+      <c r="S66" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
+      </c>
+      <c r="V66" t="n">
+        <v>20</v>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041040843369320743</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>@mubi_111 مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>@mubi_111 مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>Hello dear customer. Thank you for contacting us. To protect your privacy, we would like to inform you that we have responded to you in the same message within the previous post. In order for us to serve you better, please check your private message.</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE66" s="2" t="n">
+        <v>46118.4375</v>
+      </c>
+      <c r="AF66" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="AG66" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>2. Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>To protect your privacy, we would like to inform you that we have responded to you in the same message within the previous post. • In order for us to serve you better, please check your private message. • Thank you for contacting us.</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AK66" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL66" t="inlineStr">
+        <is>
+          <t>mubi_111</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2040952398034735414</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>https://x.com/0_ab1172/status/2040952398034735414</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>https://x.com/0_ab1172</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0_ab1172</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Abdulrahman</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1951463642324467712/XQYKCCfL_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
           <t>الإخوة في بنك الإمارات 
 ثلاث ايام لا تواصل لحل المشكله</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t>&lt;a href="/EmiratesNBD_KSA" title="EmiratesNBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt; 
 يا اخوان ترا اللي يصير ماهو طبيعي 
@@ -11324,48 +11430,48 @@
 وبعدها حوله آخر توصل !!</t>
         </is>
       </c>
-      <c r="K66" t="b">
-        <v>0</v>
-      </c>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr">
+      <c r="K67" t="b">
+        <v>0</v>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
         <is>
           <t>Apr 6</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr">
+      <c r="O67" t="inlineStr">
         <is>
           <t>Apr 6, 2026 · 12:39 AM UTC</t>
         </is>
       </c>
-      <c r="P66" s="2" t="n">
+      <c r="P67" s="2" t="n">
         <v>46118.02708333333</v>
       </c>
-      <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="inlineStr">
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr">
         <is>
           <t>['https://x.com/EmiratesNBD_KSA']</t>
         </is>
       </c>
-      <c r="S66" t="n">
+      <c r="S67" t="n">
         <v>1</v>
       </c>
-      <c r="T66" t="n">
-        <v>0</v>
-      </c>
-      <c r="U66" t="n">
-        <v>0</v>
-      </c>
-      <c r="V66" t="n">
+      <c r="T67" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
+      </c>
+      <c r="V67" t="n">
         <v>55</v>
       </c>
-      <c r="W66" t="inlineStr">
+      <c r="W67" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="X66" t="inlineStr">
+      <c r="X67" t="inlineStr">
         <is>
           <t>@EmiratesNBD_KSA 
 يا اخوان ترا اللي يصير ماهو طبيعي 
@@ -11373,109 +11479,109 @@
 وبعدها حوله آخر توصل !!</t>
         </is>
       </c>
-      <c r="Y66" t="inlineStr">
+      <c r="Y67" t="inlineStr">
         <is>
           <t>https://x.com/0_ab1172/status/2040952398034735414</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
+      <c r="Z67" t="inlineStr">
         <is>
           <t>الإخوة في بنك الإمارات 
 ثلاث ايام لا تواصل لحل المشكله</t>
         </is>
       </c>
-      <c r="AA66" t="inlineStr">
+      <c r="AA67" t="inlineStr">
         <is>
           <t>الإخوة في بنك الإمارات 
 ثلاث ايام لا تواصل لحل المشكله</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
+      <c r="AB67" t="inlineStr">
         <is>
           <t>The brothers at Emirates Bank have not communicated for three days to resolve the issue.</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
+      <c r="AC67" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="AD66" t="inlineStr">
+      <c r="AD67" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="AE66" s="2" t="n">
+      <c r="AE67" s="2" t="n">
         <v>46118.19375</v>
       </c>
-      <c r="AF66" s="2" t="n">
+      <c r="AF67" s="2" t="n">
         <v>46118</v>
       </c>
-      <c r="AG66" t="inlineStr">
+      <c r="AG67" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="AH66" t="inlineStr">
+      <c r="AH67" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AI66" t="inlineStr">
+      <c r="AI67" t="inlineStr">
         <is>
           <t>The brothers at Emirates Bank have not communicated for three days to resolve the issue.</t>
         </is>
       </c>
-      <c r="AJ66" t="inlineStr">
+      <c r="AJ67" t="inlineStr">
         <is>
           <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AK66" t="n">
+      <c r="AK67" t="n">
         <v>2026</v>
       </c>
-      <c r="AL66" t="inlineStr">
+      <c r="AL67" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="1" t="n">
-        <v>65</v>
-      </c>
-      <c r="B67" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" t="inlineStr">
         <is>
           <t>2041292333480923631</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>https://x.com/MOHAMED45537856/status/2041292333480923631</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>https://x.com/MOHAMED45537856</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>MOHAMED45537856</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>MOHAMED</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/2032761005852471300/q49RSLF4_bigger.jpg</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr">
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
         <is>
           <t>هل لي ان اعرف ماسبب التأخير على الرد على الشكوى المقدمة على بنك الامارات دبي الوطني علما بأن جميع الادلة مرفقة ورد البنك علي بانه يتعذر عليهم ماحصل وسيتم حل الموضوع داخلي ولم يتم اعطائي المطلوب مبلغ الكاش باك ضمن عرض تحويل الراتب والقرض لديهم ولم يتم ذكر موضوع صرف المبلغ يرجى الافادة علما بأن الطلب اكمل اكثر عن شهر ونص !!!!! 
 @EmiratesNBD_AE 
@@ -11483,65 +11589,65 @@
 @AbuDhabi_TAMM</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t>السادة المحترمين 
 يرجى العلم بانه يتم تقديم استفسار عن الطلب ولا يوجد رد من قبل سندك</t>
         </is>
       </c>
-      <c r="K67" t="b">
-        <v>0</v>
-      </c>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
+      <c r="K68" t="b">
+        <v>0</v>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
         <is>
           <t>['centralbankuae', 'EmiratesNBD_AE', 'AbuDhabi_TAMM']</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr">
+      <c r="N68" t="inlineStr">
         <is>
           <t>4h</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr">
+      <c r="O68" t="inlineStr">
         <is>
           <t>Apr 6, 2026 · 11:09 PM UTC</t>
         </is>
       </c>
-      <c r="P67" s="2" t="n">
+      <c r="P68" s="2" t="n">
         <v>46118.96458333333</v>
       </c>
-      <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="inlineStr"/>
-      <c r="S67" t="n">
-        <v>0</v>
-      </c>
-      <c r="T67" t="n">
-        <v>0</v>
-      </c>
-      <c r="U67" t="n">
-        <v>0</v>
-      </c>
-      <c r="V67" t="n">
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
+      <c r="S68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
+      </c>
+      <c r="V68" t="n">
         <v>22</v>
       </c>
-      <c r="W67" t="inlineStr">
+      <c r="W68" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="X67" t="inlineStr">
+      <c r="X68" t="inlineStr">
         <is>
           <t>السادة المحترمين 
 يرجى العلم بانه يتم تقديم استفسار عن الطلب ولا يوجد رد من قبل سندك</t>
         </is>
       </c>
-      <c r="Y67" t="inlineStr">
+      <c r="Y68" t="inlineStr">
         <is>
           <t>https://x.com/MOHAMED45537856/status/2041292333480923631</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
+      <c r="Z68" t="inlineStr">
         <is>
           <t>هل لي ان اعرف ماسبب التأخير على الرد على الشكوى المقدمة على بنك الامارات دبي الوطني علما بأن جميع الادلة مرفقة ورد البنك علي بانه يتعذر عليهم ماحصل وسيتم حل الموضوع داخلي ولم يتم اعطائي المطلوب مبلغ الكاش باك ضمن عرض تحويل الراتب والقرض لديهم ولم يتم ذكر موضوع صرف المبلغ يرجى الافادة علما بأن الطلب اكمل اكثر عن شهر ونص !!!!! 
 @EmiratesNBD_AE 
@@ -11549,7 +11655,7 @@
 @AbuDhabi_TAMM</t>
         </is>
       </c>
-      <c r="AA67" t="inlineStr">
+      <c r="AA68" t="inlineStr">
         <is>
           <t>هل لي ان اعرف ماسبب التأخير على الرد على الشكوى المقدمة على بنك الامارات دبي الوطني علما بأن جميع الادلة مرفقة ورد البنك علي بانه يتعذر عليهم ماحصل وسيتم حل الموضوع داخلي ولم يتم اعطائي المطلوب مبلغ الكاش باك ضمن عرض تحويل الراتب والقرض لديهم ولم يتم ذكر موضوع صرف المبلغ يرجى الافادة علما بأن الطلب اكمل اكثر عن شهر ونص !!!!! 
 @EmiratesNBD_AE 
@@ -11557,196 +11663,40 @@
 @AbuDhabi_TAMM</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
+      <c r="AB68" t="inlineStr">
         <is>
           <t>Can I know the reason for the delay in responding to the complaint submitted against Emirates NBD Bank, noting that all evidence is attached? The bank's response was that they cannot address what happened and that the issue will be resolved internally. I have not received the required cashback amount as part of their salary transfer and loan offer, and there was no mention of the disbursement of the amount. Please provide clarification, noting that the request has been pending for more than a month and a half!!!!!</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
+      <c r="AC68" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="AD67" t="inlineStr">
+      <c r="AD68" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="AE67" s="2" t="n">
+      <c r="AE68" s="2" t="n">
         <v>46119.13125</v>
       </c>
-      <c r="AF67" s="2" t="n">
+      <c r="AF68" s="2" t="n">
         <v>46119</v>
       </c>
-      <c r="AG67" t="inlineStr">
+      <c r="AG68" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="AH67" t="inlineStr">
+      <c r="AH68" t="inlineStr">
         <is>
           <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
-      <c r="AI67" t="inlineStr">
+      <c r="AI68" t="inlineStr">
         <is>
           <t>Can I know the reason for the delay in responding to the complaint submitted against Emirates NBD Bank, noting that all evidence is attached? • I have not received the required cashback amount as part of their salary transfer and loan offer, and there was no mention of the disbursement of the amount. • The bank's response was that they cannot address what happened and that the issue will be resolved internally.</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AK67" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL67" t="inlineStr">
-        <is>
-          <t>centralbankuae, EmiratesNBD_AE, AbuDhabi_TAMM</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="1" t="n">
-        <v>66</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>2041134301979517322</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>https://x.com/Mohamme9Rashid_/status/2041134301979517322</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>https://x.com/Mohamme9Rashid_</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Mohamme9Rashid_</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Mohammed Rashid Vazhayil</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1996150605484797952/BhG7hLgQ_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE  My bank transfer is still pending and it’s causing a delay. Kindly look into this urgently and update me on the status. #EmiratesNBD #BankingIssue</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;  My bank transfer is still pending and it’s causing a delay. Kindly look into this urgently and update me on the status. &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBD"&gt;#EmiratesNBD&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23BankingIssue"&gt;#BankingIssue&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K68" t="b">
-        <v>0</v>
-      </c>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>15h</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>Apr 6, 2026 · 12:41 PM UTC</t>
-        </is>
-      </c>
-      <c r="P68" s="2" t="n">
-        <v>46118.52847222222</v>
-      </c>
-      <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="inlineStr">
-        <is>
-          <t>['https://x.com/EmiratesNBD_AE', 'https://x.com/search?f=tweets&amp;q=%23EmiratesNBD', 'https://x.com/search?f=tweets&amp;q=%23BankingIssue']</t>
-        </is>
-      </c>
-      <c r="S68" t="n">
-        <v>1</v>
-      </c>
-      <c r="T68" t="n">
-        <v>0</v>
-      </c>
-      <c r="U68" t="n">
-        <v>0</v>
-      </c>
-      <c r="V68" t="n">
-        <v>22</v>
-      </c>
-      <c r="W68" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X68" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE  My bank transfer is still pending and it’s causing a delay. Kindly look into this urgently and update me on the status. #EmiratesNBD #BankingIssue</t>
-        </is>
-      </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>https://x.com/Mohamme9Rashid_/status/2041134301979517322</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE  My bank transfer is still pending and it’s causing a delay. Kindly look into this urgently and update me on the status. #EmiratesNBD #BankingIssue</t>
-        </is>
-      </c>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE  My bank transfer is still pending and it’s causing a delay. Kindly look into this urgently and update me on the status. #EmiratesNBD #BankingIssue</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>My bank transfer is still pending and it’s causing a delay. Kindly look into this urgently and update me on the status.</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD68" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="AE68" s="2" t="n">
-        <v>46118.69513888889</v>
-      </c>
-      <c r="AF68" s="2" t="n">
-        <v>46118</v>
-      </c>
-      <c r="AG68" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AI68" t="inlineStr">
-        <is>
-          <t>My bank transfer is still pending and it’s causing a delay. • Kindly look into this urgently and update me on the status.</t>
         </is>
       </c>
       <c r="AJ68" t="inlineStr">
@@ -11759,7 +11709,7 @@
       </c>
       <c r="AL68" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>centralbankuae, EmiratesNBD_AE, AbuDhabi_TAMM</t>
         </is>
       </c>
     </row>
@@ -11769,70 +11719,69 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2041172230642471397</t>
+          <t>2041134301979517322</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya/status/2041172230642471397</t>
+          <t>https://x.com/Mohamme9Rashid_/status/2041134301979517322</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya</t>
+          <t>https://x.com/Mohamme9Rashid_</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RakshtVaghasiya</t>
+          <t>Mohamme9Rashid_</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rakshit Vaghasiya</t>
+          <t>Mohammed Rashid Vazhayil</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2030191909399105536/cFPhY9vR_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1996150605484797952/BhG7hLgQ_bigger.jpg</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA 
-I raised mail to customer care regarding flight amount deduction descripancy twice but didn't hear from Emirates NBD. This is not acceptable at all. I am very much disappointed with customer care service of Emirates NBD. Zero star.</t>
+          <t>@EmiratesNBD_AE  My bank transfer is still pending and it’s causing a delay. Kindly look into this urgently and update me on the status. #EmiratesNBD #BankingIssue</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>This is really frustrating from NBD. Nothing has progressed. No meaningful action yet ... Really disappointed from Emirates NBD</t>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;  My bank transfer is still pending and it’s causing a delay. Kindly look into this urgently and update me on the status. &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBD"&gt;#EmiratesNBD&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23BankingIssue"&gt;#BankingIssue&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K69" t="b">
         <v>0</v>
       </c>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_KSA']</t>
-        </is>
-      </c>
+      <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
-          <t>12h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Apr 6, 2026 · 3:12 PM UTC</t>
+          <t>Apr 6, 2026 · 12:41 PM UTC</t>
         </is>
       </c>
       <c r="P69" s="2" t="n">
-        <v>46118.63333333333</v>
+        <v>46118.52847222222</v>
       </c>
       <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="inlineStr"/>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_AE', 'https://x.com/search?f=tweets&amp;q=%23EmiratesNBD', 'https://x.com/search?f=tweets&amp;q=%23BankingIssue']</t>
+        </is>
+      </c>
       <c r="S69" t="n">
         <v>1</v>
       </c>
@@ -11843,7 +11792,7 @@
         <v>0</v>
       </c>
       <c r="V69" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="W69" t="inlineStr">
         <is>
@@ -11852,29 +11801,27 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>This is really frustrating from NBD. Nothing has progressed. No meaningful action yet ... Really disappointed from Emirates NBD</t>
+          <t>@EmiratesNBD_AE  My bank transfer is still pending and it’s causing a delay. Kindly look into this urgently and update me on the status. #EmiratesNBD #BankingIssue</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya/status/2041172230642471397</t>
+          <t>https://x.com/Mohamme9Rashid_/status/2041134301979517322</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA 
-I raised mail to customer care regarding flight amount deduction descripancy twice but didn't hear from Emirates NBD. This is not acceptable at all. I am very much disappointed with customer care service of Emirates NBD. Zero star.</t>
+          <t>@EmiratesNBD_AE  My bank transfer is still pending and it’s causing a delay. Kindly look into this urgently and update me on the status. #EmiratesNBD #BankingIssue</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA 
-I raised mail to customer care regarding flight amount deduction descripancy twice but didn't hear from Emirates NBD. This is not acceptable at all. I am very much disappointed with customer care service of Emirates NBD. Zero star.</t>
+          <t>@EmiratesNBD_AE  My bank transfer is still pending and it’s causing a delay. Kindly look into this urgently and update me on the status. #EmiratesNBD #BankingIssue</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>I raised an email to customer care regarding the discrepancy in the flight amount deduction twice but didn't hear from Emirates NBD. This is not acceptable at all. I am very disappointed with the customer care service of Emirates NBD. Zero stars.</t>
+          <t>My bank transfer is still pending and it’s causing a delay. Kindly look into this urgently and update me on the status.</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
@@ -11888,7 +11835,7 @@
         </is>
       </c>
       <c r="AE69" s="2" t="n">
-        <v>46118.8</v>
+        <v>46118.69513888889</v>
       </c>
       <c r="AF69" s="2" t="n">
         <v>46118</v>
@@ -11905,7 +11852,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>I raised an email to customer care regarding the discrepancy in the flight amount deduction twice but didn't hear from Emirates NBD. • I am very disappointed with the customer care service of Emirates NBD. • This is not acceptable at all.</t>
+          <t>My bank transfer is still pending and it’s causing a delay. • Kindly look into this urgently and update me on the status.</t>
         </is>
       </c>
       <c r="AJ69" t="inlineStr">
@@ -11918,7 +11865,7 @@
       </c>
       <c r="AL69" t="inlineStr">
         <is>
-          <t>EmiratesNBD_KSA</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -11928,36 +11875,195 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2041040799563915686</t>
+          <t>2041172230642471397</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2041040799563915686</t>
+          <t>https://x.com/RakshtVaghasiya/status/2041172230642471397</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/RakshtVaghasiya</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>RakshtVaghasiya</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Rakshit Vaghasiya</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2030191909399105536/cFPhY9vR_bigger.jpg</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA 
+I raised mail to customer care regarding flight amount deduction descripancy twice but didn't hear from Emirates NBD. This is not acceptable at all. I am very much disappointed with customer care service of Emirates NBD. Zero star.</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>This is really frustrating from NBD. Nothing has progressed. No meaningful action yet ... Really disappointed from Emirates NBD</t>
+        </is>
+      </c>
+      <c r="K70" t="b">
+        <v>0</v>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>12h</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Apr 6, 2026 · 3:12 PM UTC</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="n">
+        <v>46118.63333333333</v>
+      </c>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
+      <c r="S70" t="n">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
+      </c>
+      <c r="V70" t="n">
+        <v>13</v>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>This is really frustrating from NBD. Nothing has progressed. No meaningful action yet ... Really disappointed from Emirates NBD</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>https://x.com/RakshtVaghasiya/status/2041172230642471397</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA 
+I raised mail to customer care regarding flight amount deduction descripancy twice but didn't hear from Emirates NBD. This is not acceptable at all. I am very much disappointed with customer care service of Emirates NBD. Zero star.</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA 
+I raised mail to customer care regarding flight amount deduction descripancy twice but didn't hear from Emirates NBD. This is not acceptable at all. I am very much disappointed with customer care service of Emirates NBD. Zero star.</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>I raised an email to customer care regarding the discrepancy in the flight amount deduction twice but didn't hear from Emirates NBD. This is not acceptable at all. I am very disappointed with the customer care service of Emirates NBD. Zero stars.</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD70" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AE70" s="2" t="n">
+        <v>46118.8</v>
+      </c>
+      <c r="AF70" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="AG70" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>I raised an email to customer care regarding the discrepancy in the flight amount deduction twice but didn't hear from Emirates NBD. • I am very disappointed with the customer care service of Emirates NBD. • This is not acceptable at all.</t>
+        </is>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK70" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL70" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_KSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2041040799563915686</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041040799563915686</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
         <is>
           <t>تفاجأت اليوم بشيء غير مقبول من بنك الإمارات الإسلامي.
 تم التواصل معي سابقاً وعرض عليّ تأجيل الأقساط لمدة 6 أشهر، وبناءً على هذا الوعد رتبت التزاماتي المالية وخططي القادمة. لكن عند دخولي إلى التطبيق، صُدمت بأن التأجيل المطبق فعلياً هو 3 أشهر فقط!
@@ -11970,63 +12076,63 @@
 #بنك_الإمارات_الإسلامي #شكوى #حقوق_العملاء #</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
         </is>
       </c>
-      <c r="K70" t="b">
-        <v>0</v>
-      </c>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
+      <c r="K71" t="b">
+        <v>0</v>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
         <is>
           <t>['mubi_111']</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr">
+      <c r="N71" t="inlineStr">
         <is>
           <t>21h</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr">
+      <c r="O71" t="inlineStr">
         <is>
           <t>Apr 6, 2026 · 6:30 AM UTC</t>
         </is>
       </c>
-      <c r="P70" s="2" t="n">
+      <c r="P71" s="2" t="n">
         <v>46118.27083333334</v>
       </c>
-      <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="inlineStr"/>
-      <c r="S70" t="n">
-        <v>0</v>
-      </c>
-      <c r="T70" t="n">
-        <v>0</v>
-      </c>
-      <c r="U70" t="n">
-        <v>0</v>
-      </c>
-      <c r="V70" t="n">
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr"/>
+      <c r="S71" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" t="n">
         <v>10</v>
       </c>
-      <c r="W70" t="inlineStr">
+      <c r="W71" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr">
+      <c r="X71" t="inlineStr">
         <is>
           <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
         </is>
       </c>
-      <c r="Y70" t="inlineStr">
+      <c r="Y71" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2041040799563915686</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
+      <c r="Z71" t="inlineStr">
         <is>
           <t>تفاجأت اليوم بشيء غير مقبول من بنك الإمارات الإسلامي.
 تم التواصل معي سابقاً وعرض عليّ تأجيل الأقساط لمدة 6 أشهر، وبناءً على هذا الوعد رتبت التزاماتي المالية وخططي القادمة. لكن عند دخولي إلى التطبيق، صُدمت بأن التأجيل المطبق فعلياً هو 3 أشهر فقط!
@@ -12039,7 +12145,7 @@
 #بنك_الإمارات_الإسلامي #شكوى #حقوق_العملاء #</t>
         </is>
       </c>
-      <c r="AA70" t="inlineStr">
+      <c r="AA71" t="inlineStr">
         <is>
           <t>تفاجأت اليوم بشيء غير مقبول من بنك الإمارات الإسلامي.
 تم التواصل معي سابقاً وعرض عليّ تأجيل الأقساط لمدة 6 أشهر، وبناءً على هذا الوعد رتبت التزاماتي المالية وخططي القادمة. لكن عند دخولي إلى التطبيق، صُدمت بأن التأجيل المطبق فعلياً هو 3 أشهر فقط!
@@ -12052,208 +12158,52 @@
 #بنك_الإمارات_الإسلامي #شكوى #حقوق_العملاء #</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
+      <c r="AB71" t="inlineStr">
         <is>
           <t>I was shocked today by something unacceptable from Emirates Islamic Bank.
-I was previously contacted and offered a 6-month deferment on my installments, and based on this promise, I arranged my financial commitments and upcoming plans. However, when I logged into the app, I was stunned to find that the actual deferment applied is only 3 months!
+I was previously contacted and offered a deferral of installments for 6 months, and based on this promise, I arranged my financial commitments and upcoming plans. However, when I logged into the app, I was stunned to find that the actual deferral applied is only 3 months!
 This behavior raises many questions:
 Are the offers made to customers just inaccurate promises?
 Where is the transparency in dealings?
 And how can a financial decision be based on incorrect information?
-What happened is not just a minor mistake; it is a breach of trust and falls within the scope of misleading offers.
+What happened is not just a simple mistake; it is a breach of trust and falls within the scope of misleading offers.
 I demand an immediate clarification from Emirates Islamic Bank and a correction of this situation, adhering to what was agreed upon without any changes or manipulation.</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
+      <c r="AC71" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="AD70" t="inlineStr">
+      <c r="AD71" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="AE70" s="2" t="n">
+      <c r="AE71" s="2" t="n">
         <v>46118.4375</v>
-      </c>
-      <c r="AF70" s="2" t="n">
-        <v>46118</v>
-      </c>
-      <c r="AG70" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AI70" t="inlineStr">
-        <is>
-          <t>I demand an immediate clarification from Emirates Islamic Bank and a correction of this situation, adhering to what was agreed upon without any changes or manipulation. • I was previously contacted and offered a 6-month deferment on my installments, and based on this promise, I arranged my financial commitments and upcoming plans. • What happened is not just a minor mistake; it is a breach of trust and falls within the scope of misleading offers.</t>
-        </is>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AK70" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL70" t="inlineStr">
-        <is>
-          <t>mubi_111</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="1" t="n">
-        <v>69</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>2041195558942249396</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>https://x.com/everyonewuw/status/2041195558942249396</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>https://x.com/everyonewuw</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>everyonewuw</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>tothislyfeu</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1990843300203671552/lUaFLcam_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Hello … I'm having trouble receiving my transfer. It seems to be pending, but there's no notification. Would you like to help me?</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>Sorry but there’s no dm from nbd</t>
-        </is>
-      </c>
-      <c r="K71" t="b">
-        <v>0</v>
-      </c>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>11h</t>
-        </is>
-      </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>Apr 6, 2026 · 4:45 PM UTC</t>
-        </is>
-      </c>
-      <c r="P71" s="2" t="n">
-        <v>46118.69791666666</v>
-      </c>
-      <c r="Q71" t="inlineStr"/>
-      <c r="R71" t="inlineStr"/>
-      <c r="S71" t="n">
-        <v>1</v>
-      </c>
-      <c r="T71" t="n">
-        <v>0</v>
-      </c>
-      <c r="U71" t="n">
-        <v>0</v>
-      </c>
-      <c r="V71" t="n">
-        <v>13</v>
-      </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X71" t="inlineStr">
-        <is>
-          <t>Sorry but there’s no dm from nbd</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>https://x.com/everyonewuw/status/2041195558942249396</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Hello … I'm having trouble receiving my transfer. It seems to be pending, but there's no notification. Would you like to help me?</t>
-        </is>
-      </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Hello … I'm having trouble receiving my transfer. It seems to be pending, but there's no notification. Would you like to help me?</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>Hello … I'm having trouble receiving my transfer. It seems to be pending, but there's no notification. Would you like to help me?</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD71" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="AE71" s="2" t="n">
-        <v>46118.86458333334</v>
       </c>
       <c r="AF71" s="2" t="n">
         <v>46118</v>
       </c>
       <c r="AG71" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
+          <t>2. Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>Hello … I'm having trouble receiving my transfer. • It seems to be pending, but there's no notification. • Would you like to help me?</t>
+          <t>I demand an immediate clarification from Emirates Islamic Bank and a correction of this situation, adhering to what was agreed upon without any changes or manipulation. • I was previously contacted and offered a deferral of installments for 6 months, and based on this promise, I arranged my financial commitments and upcoming plans. • What happened is not just a simple mistake; it is a breach of trust and falls within the scope of misleading offers.</t>
         </is>
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank (ENBD)</t>
+          <t>Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AK71" t="n">
@@ -12261,7 +12211,7 @@
       </c>
       <c r="AL71" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>mubi_111</t>
         </is>
       </c>
     </row>
@@ -12271,45 +12221,43 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2041054585297740229</t>
+          <t>2041195558942249396</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://x.com/kmz1993/status/2041054585297740229</t>
+          <t>https://x.com/everyonewuw/status/2041195558942249396</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://x.com/kmz1993</t>
+          <t>https://x.com/everyonewuw</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>kmz1993</t>
+          <t>everyonewuw</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t> خالد</t>
+          <t>tothislyfeu</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1475344667810349059/JlxW8n_8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1990843300203671552/lUaFLcam_bigger.jpg</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
-          <t>للأسف موظفينكم يخبصون في الشغل، أنا عندي موضوع قدمت عليه والتخبط واضح بين الموظفين وكل شخص يلوم القسم الآخر وفي النهاية القسم المختص لا يرد على إستفساراتنا ولا على المراسلات من الموظفين الآخرين
-أما @emiratesislamic خلصوا موضوعي بسهولة يوم طلبت منهم وهم بصراحة أفضل مصرف إسلامي 👏🏼</t>
+          <t>@EmiratesNBD_AE Hello … I'm having trouble receiving my transfer. It seems to be pending, but there's no notification. Would you like to help me?</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>للأسف موظفينكم يخبصون في الشغل، أنا عندي موضوع قدمت عليه والتخبط واضح بين الموظفين وكل شخص يلوم القسم الآخر وفي النهاية القسم المختص لا يرد على إستفساراتنا ولا على المراسلات من الموظفين الآخرين
-أما &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; خلصوا موضوعي بسهولة يوم طلبت منهم وهم بصراحة أفضل مصرف إسلامي 👏🏼</t>
+          <t>Sorry but there’s no dm from nbd</t>
         </is>
       </c>
       <c r="K72" t="b">
@@ -12318,28 +12266,24 @@
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>['ADIBTweets']</t>
+          <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Apr 6, 2026 · 7:25 AM UTC</t>
+          <t>Apr 6, 2026 · 4:45 PM UTC</t>
         </is>
       </c>
       <c r="P72" s="2" t="n">
-        <v>46118.30902777778</v>
+        <v>46118.69791666666</v>
       </c>
       <c r="Q72" t="inlineStr"/>
-      <c r="R72" t="inlineStr">
-        <is>
-          <t>['https://x.com/emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="R72" t="inlineStr"/>
       <c r="S72" t="n">
         <v>1</v>
       </c>
@@ -12350,30 +12294,36 @@
         <v>0</v>
       </c>
       <c r="V72" t="n">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>ENBD</t>
         </is>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>للأسف موظفينكم يخبصون في الشغل، أنا عندي موضوع قدمت عليه والتخبط واضح بين الموظفين وكل شخص يلوم القسم الآخر وفي النهاية القسم المختص لا يرد على إستفساراتنا ولا على المراسلات من الموظفين الآخرين
-أما @emiratesislamic خلصوا موضوعي بسهولة يوم طلبت منهم وهم بصراحة أفضل مصرف إسلامي 👏🏼</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr"/>
-      <c r="Z72" t="inlineStr"/>
+          <t>Sorry but there’s no dm from nbd</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>https://x.com/everyonewuw/status/2041195558942249396</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Hello … I'm having trouble receiving my transfer. It seems to be pending, but there's no notification. Would you like to help me?</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>للأسف موظفينكم يخبصون في الشغل، أنا عندي موضوع قدمت عليه والتخبط واضح بين الموظفين وكل شخص يلوم القسم الآخر وفي النهاية القسم المختص لا يرد على إستفساراتنا ولا على المراسلات من الموظفين الآخرين
-أما @emiratesislamic خلصوا موضوعي بسهولة يوم طلبت منهم وهم بصراحة أفضل مصرف إسلامي 👏🏼</t>
+          <t>@EmiratesNBD_AE Hello … I'm having trouble receiving my transfer. It seems to be pending, but there's no notification. Would you like to help me?</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>Unfortunately, your employees are messing up the work. I have a matter I submitted, and the confusion among the employees is clear, with each person blaming the other department. In the end, the relevant department does not respond to our inquiries or to the communications from other employees. As for @emiratesislamic, they resolved my issue easily when I asked them, and honestly, they are the best Islamic bank.</t>
+          <t>Hello … I'm having trouble receiving my transfer. It seems to be pending, but there's no notification. Would you like to help me?</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
@@ -12387,29 +12337,29 @@
         </is>
       </c>
       <c r="AE72" s="2" t="n">
-        <v>46118.47569444445</v>
+        <v>46118.86458333334</v>
       </c>
       <c r="AF72" s="2" t="n">
         <v>46118</v>
       </c>
       <c r="AG72" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>ENBD</t>
         </is>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
+          <t>1. Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>I have a matter I submitted, and the confusion among the employees is clear, with each person blaming the other department. • In the end, the relevant department does not respond to our inquiries or to the communications from other employees. • As for @emiratesislamic, they resolved my issue easily when I asked them, and honestly, they are the best Islamic bank.</t>
+          <t>Hello … I'm having trouble receiving my transfer. • It seems to be pending, but there's no notification. • Would you like to help me?</t>
         </is>
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>Emirates Islamic Bank (EIB)</t>
+          <t>Emirates NBD Bank (ENBD)</t>
         </is>
       </c>
       <c r="AK72" t="n">
@@ -12417,7 +12367,7 @@
       </c>
       <c r="AL72" t="inlineStr">
         <is>
-          <t>ADIBTweets</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
     </row>
@@ -12529,7 +12479,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>I have been struggling with my Apple Wallet for 4 months now. Since I changed from iPhone 14 to 17, I cannot add my cards (contact issuer). I have spoken to both of you and the problem has not been resolved yet. All steps were done from both sides too!</t>
+          <t>I have been struggling with my Apple Wallet for 4 months now. Since I changed from iPhone 14 to 17, I cannot add my cards (contact issuer). I have spoken to both of you, and the problem has not been resolved yet. All steps were done from both sides too!</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
@@ -12560,7 +12510,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>Since I changed from iPhone 14 to 17, I cannot add my cards (contact issuer). • I have spoken to both of you and the problem has not been resolved yet. • I have been struggling with my Apple Wallet for 4 months now.</t>
+          <t>Since I changed from iPhone 14 to 17, I cannot add my cards (contact issuer). • I have spoken to both of you, and the problem has not been resolved yet. • I have been struggling with my Apple Wallet for 4 months now.</t>
         </is>
       </c>
       <c r="AJ73" t="inlineStr">

--- a/check2.xlsx
+++ b/check2.xlsx
@@ -656,7 +656,7 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Dubai Culture’s ‘The City Of Knowledge’ Turns Young Talent Into Storytellers https://t.co/MzLMyetr2I</t>
+          <t>Sundays Done Right With A Bavarian Brunch At Bruno’s Biergarten https://t.co/PV0Qsmd7Nt</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -717,17 +717,17 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Dubai Culture’s ‘The City Of Knowledge’ Turns Young Talent Into Storytellers https://t.co/MzLMyetr2I</t>
+          <t>Sundays Done Right With A Bavarian Brunch At Bruno’s Biergarten https://t.co/PV0Qsmd7Nt</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Dubai Culture’s ‘The City Of Knowledge’ Turns Young Talent Into Storytellers https://t.co/MzLMyetr2I</t>
+          <t>Sundays Done Right With A Bavarian Brunch At Bruno’s Biergarten https://t.co/PV0Qsmd7Nt</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Dubai Culture’s ‘The City Of Knowledge’ Turns Young Talent Into Storytellers</t>
+          <t>Sundays Done Right With A Bavarian Brunch At Bruno’s Biergarten</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Dubai Culture’s ‘The City Of Knowledge’ Turns Young Talent Into Storytellers</t>
+          <t>Sundays Done Right With A Bavarian Brunch At Bruno’s Biergarten</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -811,310 +811,6 @@
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>عندي اربعه تذاكر حفلة رابح صقر الي يبغا يكلمني خاص #رابح_صقر_في_جدة #رابح_صقر #جدة #بنش_مارك</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>عندي اربعه تذاكر حفلة رابح صقر الي يبغا يكلمني خاص &lt;a href="/search?f=tweets&amp;amp;q=%23رابح_صقر_في_جدة"&gt;#رابح_صقر_في_جدة&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23رابح_صقر"&gt;#رابح_صقر&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23جدة"&gt;#جدة&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23بنش_مارك"&gt;#بنش_مارك&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>['RotanaLive', 'RabehSaqer', 'JEDCalendar', 'EmiratesNBD_KSA']</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>43m</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Apr 9, 2026 · 3:18 AM UTC</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="n">
-        <v>46121.1375</v>
-      </c>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23رابح_صقر_في_جدة', 'https://x.com/search?f=tweets&amp;q=%23رابح_صقر', 'https://x.com/search?f=tweets&amp;q=%23جدة', 'https://x.com/search?f=tweets&amp;q=%23بنش_مارك']</t>
-        </is>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>22</v>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>عندي اربعه تذاكر حفلة رابح صقر الي يبغا يكلمني خاص #رابح_صقر_في_جدة #رابح_صقر #جدة #بنش_مارك</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>عندي اربعه تذاكر حفلة رابح صقر الي يبغا يكلمني خاص #رابح_صقر_في_جدة #رابح_صقر #جدة #بنش_مارك</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>I have four tickets for the Rabeh Saqer concert. Whoever wants to contact me privately. #Rabeh_Saqer_in_Jeddah #Rabeh_Saqer #Jeddah #Bench_Mark</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AE3" s="2" t="n">
-        <v>46121.30416666667</v>
-      </c>
-      <c r="AF3" s="2" t="n">
-        <v>46121</v>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>#Rabeh_Saqer_in_Jeddah #Rabeh_Saqer #Jeddah #Bench_Mark • I have four tickets for the Rabeh Saqer concert. • Whoever wants to contact me privately.</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AK3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>RotanaLive, RabehSaqer, JEDCalendar, EmiratesNBD_KSA</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2042074306663112932</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>https://x.com/CKwok_HK/status/2042074306663112932</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>https://x.com/CKwok_HK</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>CKwok_HK</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>C. Kwok 💹❇️</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1972311092337786880/LmDgqRGq_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>彭博社消息，渣打银行计划将旗下 Zodia Custody 的客户端托管业务收回至其企业与投资银行（CIB）的数字资产部门，最快本月宣布。重组后，Zodia 将仅作为独立的托管技术软件即服务（SaaS）平台继续运营。</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>渣打银行于 2020 年底通过创新部门 SC Ventures 与 Northern Trust 共同成立 Zodia Custody，后续吸引 SBI Holdings、澳大利亚国民银行与 Emirates NBD 等少数股权投资者，目前在全球七个办事处拥有约 150 名员工。</t>
-        </is>
-      </c>
-      <c r="K4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>1h</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Apr 9, 2026 · 2:57 AM UTC</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="n">
-        <v>46121.12291666667</v>
-      </c>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>15</v>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>渣打银行于 2020 年底通过创新部门 SC Ventures 与 Northern Trust 共同成立 Zodia Custody，后续吸引 SBI Holdings、澳大利亚国民银行与 Emirates NBD 等少数股权投资者，目前在全球七个办事处拥有约 150 名员工。</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>https://x.com/CKwok_HK/status/2042074306663112932</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>彭博社消息，渣打银行计划将旗下 Zodia Custody 的客户端托管业务收回至其企业与投资银行（CIB）的数字资产部门，最快本月宣布。重组后，Zodia 将仅作为独立的托管技术软件即服务（SaaS）平台继续运营。</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>彭博社消息，渣打银行计划将旗下 Zodia Custody 的客户端托管业务收回至其企业与投资银行（CIB）的数字资产部门，最快本月宣布。重组后，Zodia 将仅作为独立的托管技术软件即服务（SaaS）平台继续运营。</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>According to Bloomberg, Standard Chartered plans to bring the client custody business of its Zodia Custody back under its Corporate and Investment Banking (CIB) digital assets division, with an announcement expected as early as this month. After the restructuring, Zodia will continue to operate solely as an independent custody technology software-as-a-service (SaaS) platform.</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AE4" s="2" t="n">
-        <v>46121.28958333333</v>
-      </c>
-      <c r="AF4" s="2" t="n">
-        <v>46121</v>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>After the restructuring, Zodia will continue to operate solely as an independent custody technology software-as-a-service (SaaS) platform.</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AK4" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2042043377135292451</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://x.com/7732G/status/2042043377135292451</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>https://x.com/7732G</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>7732G</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>قمر 🫶🏻🍃</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2041848036750770176/WhDlFVh4_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
         <is>
           <t>جمهور صقر الأغنية الخليجية في جدة غير 😉
 🔥🔥 SOLD OUT 
@@ -1127,63 +823,67 @@
 @EmiratesNBD_KSA https://t.co/ushr2PgKVi</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>حسبي الله ع كل شخص ياخذ التذاكر ويبيعها بكيفه 💔 حرمتوني احضر الحفله</t>
-        </is>
-      </c>
-      <c r="K5" t="b">
-        <v>0</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>عندي اربعه تذاكر حفلة رابح صقر الي يبغا يكلمني خاص &lt;a href="/search?f=tweets&amp;amp;q=%23رابح_صقر_في_جدة"&gt;#رابح_صقر_في_جدة&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23رابح_صقر"&gt;#رابح_صقر&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23جدة"&gt;#جدة&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23بنش_مارك"&gt;#بنش_مارك&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
         <is>
           <t>['RotanaLive', 'RabehSaqer', 'JEDCalendar', 'EmiratesNBD_KSA']</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>3h</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Apr 9, 2026 · 12:54 AM UTC</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="n">
-        <v>46121.0375</v>
-      </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>30</v>
-      </c>
-      <c r="W5" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>43m</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Apr 9, 2026 · 3:18 AM UTC</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>46121.1375</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23رابح_صقر_في_جدة', 'https://x.com/search?f=tweets&amp;q=%23رابح_صقر', 'https://x.com/search?f=tweets&amp;q=%23جدة', 'https://x.com/search?f=tweets&amp;q=%23بنش_مارك']</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>22</v>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>حسبي الله ع كل شخص ياخذ التذاكر ويبيعها بكيفه 💔 حرمتوني احضر الحفله</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>https://x.com/7732G/status/2042043377135292451</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>عندي اربعه تذاكر حفلة رابح صقر الي يبغا يكلمني خاص #رابح_صقر_في_جدة #رابح_صقر #جدة #بنش_مارك</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>https://x.com/liil7ix/status/2042079677557121369</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
         <is>
           <t>جمهور صقر الأغنية الخليجية في جدة غير 😉
 🔥🔥 SOLD OUT 
@@ -1196,7 +896,7 @@
 @EmiratesNBD_KSA https://t.co/ushr2PgKVi</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>جمهور صقر الأغنية الخليجية في جدة غير 😉
 🔥🔥 SOLD OUT 
@@ -1209,7 +909,7 @@
 @EmiratesNBD_KSA https://t.co/ushr2PgKVi</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>The audience of the Gulf songbird in Jeddah is different 😉  
 🔥🔥 SOLD OUT  
@@ -1222,6 +922,314 @@
 @EmiratesNBD_KSA</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE3" s="2" t="n">
+        <v>46121.30416666667</v>
+      </c>
+      <c r="AF3" s="2" t="n">
+        <v>46121</v>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>The audience of the Gulf songbird in Jeddah is different 😉 🔥🔥 SOLD OUT An exceptional night awaits you on April 10✨🦅 #Ra…</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>RotanaLive, RabehSaqer, JEDCalendar, EmiratesNBD_KSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2042074306663112932</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://x.com/CKwok_HK/status/2042074306663112932</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://x.com/CKwok_HK</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>CKwok_HK</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>C. Kwok 💹❇️</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1972311092337786880/LmDgqRGq_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>彭博社消息，渣打银行计划将旗下 Zodia Custody 的客户端托管业务收回至其企业与投资银行（CIB）的数字资产部门，最快本月宣布。重组后，Zodia 将仅作为独立的托管技术软件即服务（SaaS）平台继续运营。</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>渣打银行于 2020 年底通过创新部门 SC Ventures 与 Northern Trust 共同成立 Zodia Custody，后续吸引 SBI Holdings、澳大利亚国民银行与 Emirates NBD 等少数股权投资者，目前在全球七个办事处拥有约 150 名员工。</t>
+        </is>
+      </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Apr 9, 2026 · 2:57 AM UTC</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>46121.12291666667</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>15</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>渣打银行于 2020 年底通过创新部门 SC Ventures 与 Northern Trust 共同成立 Zodia Custody，后续吸引 SBI Holdings、澳大利亚国民银行与 Emirates NBD 等少数股权投资者，目前在全球七个办事处拥有约 150 名员工。</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>https://x.com/CKwok_HK/status/2042074306663112932</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>彭博社消息，渣打银行计划将旗下 Zodia Custody 的客户端托管业务收回至其企业与投资银行（CIB）的数字资产部门，最快本月宣布。重组后，Zodia 将仅作为独立的托管技术软件即服务（SaaS）平台继续运营。</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>彭博社消息，渣打银行计划将旗下 Zodia Custody 的客户端托管业务收回至其企业与投资银行（CIB）的数字资产部门，最快本月宣布。重组后，Zodia 将仅作为独立的托管技术软件即服务（SaaS）平台继续运营。</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>According to Bloomberg, Standard Chartered plans to bring the client custody business of its Zodia Custody back under its Corporate and Investment Banking (CIB) digital assets division, with an announcement expected as early as this month. After the restructuring, Zodia will continue to operate solely as an independent custody technology software-as-a-service (SaaS) platform.</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE4" s="2" t="n">
+        <v>46121.28958333333</v>
+      </c>
+      <c r="AF4" s="2" t="n">
+        <v>46121</v>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>After the restructuring, Zodia will continue to operate solely as an independent custody technology software-as-a-service (SaaS) platform.</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK4" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2042043377135292451</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://x.com/7732G/status/2042043377135292451</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://x.com/7732G</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>7732G</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>قمر 🫶🏻🍃</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2041848036750770176/WhDlFVh4_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>@RotanaLive @RabehSaqer @JEDCalendar @EmiratesNBD_KSA حسبي الله ع كل شخص ياخذ التذاكر ويبيعها بكيفه 💔 حرمتوني احضر الحفله</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>حسبي الله ع كل شخص ياخذ التذاكر ويبيعها بكيفه 💔 حرمتوني احضر الحفله</t>
+        </is>
+      </c>
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>['RotanaLive', 'RabehSaqer', 'JEDCalendar', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>3h</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Apr 9, 2026 · 12:54 AM UTC</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>46121.0375</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>30</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>حسبي الله ع كل شخص ياخذ التذاكر ويبيعها بكيفه 💔 حرمتوني احضر الحفله</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>https://x.com/7732G/status/2042043377135292451</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>@RotanaLive @RabehSaqer @JEDCalendar @EmiratesNBD_KSA حسبي الله ع كل شخص ياخذ التذاكر ويبيعها بكيفه 💔 حرمتوني احضر الحفله</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>@RotanaLive @RabehSaqer @JEDCalendar @EmiratesNBD_KSA حسبي الله ع كل شخص ياخذ التذاكر ويبيعها بكيفه 💔 حرمتوني احضر الحفله</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>I trust in God for everyone who takes the tickets and sells them as they please 💔 You have deprived me of attending the concert.</t>
+        </is>
+      </c>
       <c r="AC5" t="inlineStr">
         <is>
           <t>Cust</t>
@@ -1250,7 +1258,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>The audience of the Gulf songbird in Jeddah is different 😉 🔥🔥 SOLD OUT An exceptional night awaits you on April 10✨🦅 #Ra…</t>
+          <t>I trust in God for everyone who takes the tickets and sells them as they please 💔 You have deprived me of attending the concert.</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1375,7 +1383,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Anyone who has two tickets for Rabeh at the same price, the lower category, please message me privately.</t>
+          <t>Anyone who has two tickets for Rabeh at the same price as the lower category, please message me privately.</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1406,7 +1414,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Anyone who has two tickets for Rabeh at the same price, the lower category, please message me privately.</t>
+          <t>Anyone who has two tickets for Rabeh at the same price as the lower category, please message me privately.</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1537,12 +1545,9 @@
 is having its best quarter ever. 🇦🇪</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>https://x.com/dubaihousingae/status/2041958539409944767</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Dubai this week:
 → Dh65.4M apartment sold — Palm Jumeirah
@@ -1556,20 +1561,6 @@
 is having its best quarter ever. 🇦🇪</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Dubai this week:
-→ Dh65.4M apartment sold — Palm Jumeirah
-→ $5B in deals in one week
-→ AED 176.7B Q1 2026 — record high
-→ UAE: 0% oil dependency vs Kuwait 78%
-→ 75% discount on business license renewals
-→ Emirates NBD: SME fee relief launched
-→ Nubank CEO met Abu Dhabi leadership
-The city that was "finished" —
-is having its best quarter ever. 🇦🇪</t>
-        </is>
-      </c>
       <c r="AB7" t="inlineStr">
         <is>
           <t>Dubai this week:
@@ -1732,7 +1723,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Emirates NBD receives RBI approval to acquire up to 74% stake in RBL Bank, making it a foreign bank after the acquisition.</t>
+          <t>Emirates NBD receives RBI approval to acquire up to a 74% stake in RBL Bank, making it a foreign bank after the acquisition.</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1763,7 +1754,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Emirates NBD receives RBI approval to acquire up to 74% stake in RBL Bank, making it a foreign bank after the acquisition.</t>
+          <t>Emirates NBD receives RBI approval to acquire up to a 74% stake in RBL Bank, making it a foreign bank after the acquisition.</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -2002,7 +1993,7 @@
         <is>
           <t>Dubai Chamber of Commerce organised a dialogue with Emirates NBD, bringing together 86 private sector representatives.
 Discussions focused on banking needs and financing solutions to support business resilience.
-#UAE | #nas_news_emirates https://t.co/wAoo9sMVqL</t>
+#UAE | #nas_news_emirates</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -2060,28 +2051,18 @@
 #UAE | #nas_news_emirates</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>https://x.com/nasnews_e/status/2041925717231894565</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Dubai Chamber of Commerce organised a dialogue with Emirates NBD, bringing together 86 private sector representatives.
 Discussions focused on banking needs and financing solutions to support business resilience.
-#UAE | #nas_news_emirates https://t.co/wAoo9sMVqL</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Dubai Chamber of Commerce organised a dialogue with Emirates NBD, bringing together 86 private sector representatives.
-Discussions focused on banking needs and financing solutions to support business resilience.
-#UAE | #nas_news_emirates https://t.co/wAoo9sMVqL</t>
+#UAE | #nas_news_emirates</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Dubai Chamber of Commerce organized a dialogue with Emirates NBD, bringing together 86 private sector representatives. Discussions focused on banking needs and financing solutions to support business resilience.</t>
+          <t>The Dubai Chamber of Commerce organized a dialogue with Emirates NBD, bringing together 86 private sector representatives. Discussions focused on banking needs and financing solutions to support business resilience.</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -2112,7 +2093,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Dubai Chamber of Commerce organized a dialogue with Emirates NBD, bringing together 86 private sector representatives. • Discussions focused on banking needs and financing solutions to support business resilience.</t>
+          <t>The Dubai Chamber of Commerce organized a dialogue with Emirates NBD, bringing together 86 private sector representatives. • Discussions focused on banking needs and financing solutions to support business resilience.</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -3059,7 +3040,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Where's the fool who said Rabeh has no popularity in Jeddah?🤣</t>
+          <t>Where is the fool who said Rabeh has no popularity in Jeddah?🤣</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -3090,7 +3071,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Where's the fool who said Rabeh has no popularity in Jeddah?🤣</t>
+          <t>Where is the fool who said Rabeh has no popularity in Jeddah?🤣</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -3144,7 +3125,7 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>عندي ثنتين b</t>
+          <t>@RotanaLive @RabehSaqer @JEDCalendar @EmiratesNBD_KSA عندي ثنتين b</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -3198,11 +3179,19 @@
           <t>عندي ثنتين b</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>https://x.com/MakeSunshine1/status/2041905098180227458</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>@RotanaLive @RabehSaqer @JEDCalendar @EmiratesNBD_KSA عندي ثنتين b</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>عندي ثنتين b</t>
+          <t>@RotanaLive @RabehSaqer @JEDCalendar @EmiratesNBD_KSA عندي ثنتين b</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -3695,7 +3684,7 @@
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE20" s="2" t="n">
@@ -4026,7 +4015,6 @@
 Download the Propt App for the full analysis! 
 Appstore: https://t.co/sq8ARTJUyH 
 Playstore: https://t.co/Ju874t25Gf 
-@SobhaRealtyDXB 
 #HomeFinancing #EmiratesNBD #SobhaRealty</t>
         </is>
       </c>
@@ -4058,7 +4046,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Appstore: https://t.co/sq8ARTJUyH Playstore: https://t.co/Ju874t25Gf @SobhaRealtyDXB #HomeFinancing #EmiratesNBD #SobhaRealty • Emirates NBD and Sobha Realty just transformed the home-buying game in Dubai! • Download the Propt App for the full analysis!</t>
+          <t>Appstore: https://t.co/sq8ARTJUyH Playstore: https://t.co/Ju874t25Gf #HomeFinancing #EmiratesNBD #SobhaRealty • Emirates NBD and Sobha Realty just transformed the home-buying game in Dubai! • Download the Propt App for the full analysis!</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
@@ -7684,7 +7672,8 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>United Against Fraud</t>
+          <t>@EmiratesNBD_AE SMS2
+#UnitedAgainstFraud</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -7715,7 +7704,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>United Against Fraud</t>
+          <t>@EmiratesNBD_AE SMS2 #UnitedAgainstFraud</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
@@ -7769,11 +7758,8 @@
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
-          <t>#أخبار | "التزامكم سعادة" تُقدم التوعية الرياضية في أكاديمية كرة القدم بنادي النصر
-التفاصيل:  
-https://t.co/DPYlmd7x04
-#التزامكم_سعادة
-#مجلس_دبي_الرياضي https://t.co/sN4e2Ahaw9</t>
+          <t>This 1 hour lecture from a Carnegie Mellon professor who had 3 months to live will teach you more about living than every self-help book you’ve ever read combined.
+Bookmark this &amp;amp; give it 1 hour today. It’s the most productive start you can give your week. https://t.co/JarVTUXTWu</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -7830,25 +7816,19 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>#أخبار | "التزامكم سعادة" تُقدم التوعية الرياضية في أكاديمية كرة القدم بنادي النصر
-التفاصيل:  
-https://t.co/DPYlmd7x04
-#التزامكم_سعادة
-#مجلس_دبي_الرياضي https://t.co/sN4e2Ahaw9</t>
+          <t>This 1 hour lecture from a Carnegie Mellon professor who had 3 months to live will teach you more about living than every self-help book you’ve ever read combined.
+Bookmark this &amp;amp; give it 1 hour today. It’s the most productive start you can give your week. https://t.co/JarVTUXTWu</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>#أخبار | "التزامكم سعادة" تُقدم التوعية الرياضية في أكاديمية كرة القدم بنادي النصر
-التفاصيل:  
-https://t.co/DPYlmd7x04
-#التزامكم_سعادة
-#مجلس_دبي_الرياضي https://t.co/sN4e2Ahaw9</t>
+          <t>This 1 hour lecture from a Carnegie Mellon professor who had 3 months to live will teach you more about living than every self-help book you’ve ever read combined.
+Bookmark this &amp;amp; give it 1 hour today. It’s the most productive start you can give your week. https://t.co/JarVTUXTWu</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>News | "Your Commitment is Happiness" presents sports awareness at the Al Nassr Football Club Academy</t>
+          <t>This 1 hour lecture from a Carnegie Mellon professor who had 3 months to live will teach you more about living than every self-help book you’ve ever read combined. Bookmark this and give it 1 hour today. It’s the most productive start you can give your week.</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -7879,7 +7859,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>News | "Your Commitment is Happiness" presents sports awareness at the Al Nassr Football Club Academy</t>
+          <t>This 1 hour lecture from a Carnegie Mellon professor who had 3 months to live will teach you more about living than every self-help book you’ve ever read combined. • Bookmark this and give it 1 hour today. • It’s the most productive start you can give your week.</t>
         </is>
       </c>
       <c r="AJ46" t="inlineStr">
@@ -7933,12 +7913,11 @@
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>The National Pavilion UAE (@pavilionuae) will present “Washwasha” from 9 May to 22 November 2026 at the 61st International Art Exhibition of La Biennale di Venezia, according to WAM. Curated by Bana Kattan, Curator and Associate Head of Exhibitions at the Guggenheim Abu Dhabi Project, with Tala Nassar, Assistant Curator, the exhibition brings together works by Alaa Edris, Mays Albaik, Jawad Al Malhi, Farah Al Qasimi, Lamya Gargash, and Taus Makhacheva to explore sound, memory, movement, migration, and cultural transformation. The project positions sound as a medium of collective expression, connecting contemporary artistic practices with traditions such as storytelling, poetry, and broadcasting.
-Sheikh Salem bin Khalid Al Qassimi(@Salemalq), Minister of Culture, said, “Since its inception, the National Pavilion UAE has served as a platform to nurture and showcase the country’s creative talent on the global stage of La Biennale di Venezia.” 
-Angela Migally, Executive Director of the Salama bint Hamdan Al Nahyan Foundation, said the exhibition “contributes meaningfully to global discourse while remaining deeply rooted in its cultural context,” while Bana Kattan, Curator of the exhibition, described “Washwasha” as an artist-led project shaped by distinct perspectives on intangible histories.
- Laila Binbrek, Director of the National Pavilion UAE – La Biennale di Venezia, said the exhibition reflects the UAE’s rich intangible heritage through contemporary artistic expression and highlights the impact of sustained investment in artistic development and collaboration.
-Read More: https://t.co/DjVBTo9Zkv
-#UAEArt #VeniceBiennale #NationalPavilionUAE #ContemporaryArt</t>
+          <t>Danube Group has reaffirmed its commitment to its workforce, with Founder and Chairman Rizwan Sajan confirming there will be no layoffs and salaries will continue to be paid on time for its 6,000+ employees, despite ongoing geopolitical uncertainty. The announcement comes as global and regional markets face increasing pressure, with businesses focusing on stability and continuity. Sajan emphasised the company’s long-standing resilience, referencing past crises including the Iraqi invasion of Kuwait, the 2008 financial crisis, and the COVID-19 pandemic.
+Rizwan Sajan said, “I’ve faced many challenging situations in the past - from the Iraqi invasion of Kuwait to the 2008 financial crisis and the COVID-19 pandemic. Despite these, we have always bounced back stronger, and I’m confident we will do so again. During the pandemic, I had committed to not letting go of any employees, and I stood by that promise. Similarly, there will be no layoffs at Danube Group this time as well.” He added, “Our 6000+ employees are not just our workforce - they are our family.
+They helped build Danube Group into what it is today. In times like these, we stand by them with the same commitment. All salaries will be paid on time, and we remain dedicated to serving our clients and customers.” The group’s diversified structure, spanning building materials, real estate, and home solutions, alongside projects like Greenz by Danube, continues to support operational resilience and long-term growth.
+Read More - Link in Bio! https://t.co/rURwbecMni
+#DubaiRealEstate #BusinessNews #Leadership #UAE</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -8005,29 +7984,27 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>The National Pavilion UAE (@pavilionuae) will present “Washwasha” from 9 May to 22 November 2026 at the 61st International Art Exhibition of La Biennale di Venezia, according to WAM. Curated by Bana Kattan, Curator and Associate Head of Exhibitions at the Guggenheim Abu Dhabi Project, with Tala Nassar, Assistant Curator, the exhibition brings together works by Alaa Edris, Mays Albaik, Jawad Al Malhi, Farah Al Qasimi, Lamya Gargash, and Taus Makhacheva to explore sound, memory, movement, migration, and cultural transformation. The project positions sound as a medium of collective expression, connecting contemporary artistic practices with traditions such as storytelling, poetry, and broadcasting.
-Sheikh Salem bin Khalid Al Qassimi(@Salemalq), Minister of Culture, said, “Since its inception, the National Pavilion UAE has served as a platform to nurture and showcase the country’s creative talent on the global stage of La Biennale di Venezia.” 
-Angela Migally, Executive Director of the Salama bint Hamdan Al Nahyan Foundation, said the exhibition “contributes meaningfully to global discourse while remaining deeply rooted in its cultural context,” while Bana Kattan, Curator of the exhibition, described “Washwasha” as an artist-led project shaped by distinct perspectives on intangible histories.
- Laila Binbrek, Director of the National Pavilion UAE – La Biennale di Venezia, said the exhibition reflects the UAE’s rich intangible heritage through contemporary artistic expression and highlights the impact of sustained investment in artistic development and collaboration.
-Read More: https://t.co/DjVBTo9Zkv
-#UAEArt #VeniceBiennale #NationalPavilionUAE #ContemporaryArt</t>
+          <t>Danube Group has reaffirmed its commitment to its workforce, with Founder and Chairman Rizwan Sajan confirming there will be no layoffs and salaries will continue to be paid on time for its 6,000+ employees, despite ongoing geopolitical uncertainty. The announcement comes as global and regional markets face increasing pressure, with businesses focusing on stability and continuity. Sajan emphasised the company’s long-standing resilience, referencing past crises including the Iraqi invasion of Kuwait, the 2008 financial crisis, and the COVID-19 pandemic.
+Rizwan Sajan said, “I’ve faced many challenging situations in the past - from the Iraqi invasion of Kuwait to the 2008 financial crisis and the COVID-19 pandemic. Despite these, we have always bounced back stronger, and I’m confident we will do so again. During the pandemic, I had committed to not letting go of any employees, and I stood by that promise. Similarly, there will be no layoffs at Danube Group this time as well.” He added, “Our 6000+ employees are not just our workforce - they are our family.
+They helped build Danube Group into what it is today. In times like these, we stand by them with the same commitment. All salaries will be paid on time, and we remain dedicated to serving our clients and customers.” The group’s diversified structure, spanning building materials, real estate, and home solutions, alongside projects like Greenz by Danube, continues to support operational resilience and long-term growth.
+Read More - Link in Bio! https://t.co/rURwbecMni
+#DubaiRealEstate #BusinessNews #Leadership #UAE</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>The National Pavilion UAE (@pavilionuae) will present “Washwasha” from 9 May to 22 November 2026 at the 61st International Art Exhibition of La Biennale di Venezia, according to WAM. Curated by Bana Kattan, Curator and Associate Head of Exhibitions at the Guggenheim Abu Dhabi Project, with Tala Nassar, Assistant Curator, the exhibition brings together works by Alaa Edris, Mays Albaik, Jawad Al Malhi, Farah Al Qasimi, Lamya Gargash, and Taus Makhacheva to explore sound, memory, movement, migration, and cultural transformation. The project positions sound as a medium of collective expression, connecting contemporary artistic practices with traditions such as storytelling, poetry, and broadcasting.
-Sheikh Salem bin Khalid Al Qassimi(@Salemalq), Minister of Culture, said, “Since its inception, the National Pavilion UAE has served as a platform to nurture and showcase the country’s creative talent on the global stage of La Biennale di Venezia.” 
-Angela Migally, Executive Director of the Salama bint Hamdan Al Nahyan Foundation, said the exhibition “contributes meaningfully to global discourse while remaining deeply rooted in its cultural context,” while Bana Kattan, Curator of the exhibition, described “Washwasha” as an artist-led project shaped by distinct perspectives on intangible histories.
- Laila Binbrek, Director of the National Pavilion UAE – La Biennale di Venezia, said the exhibition reflects the UAE’s rich intangible heritage through contemporary artistic expression and highlights the impact of sustained investment in artistic development and collaboration.
-Read More: https://t.co/DjVBTo9Zkv
-#UAEArt #VeniceBiennale #NationalPavilionUAE #ContemporaryArt</t>
+          <t>Danube Group has reaffirmed its commitment to its workforce, with Founder and Chairman Rizwan Sajan confirming there will be no layoffs and salaries will continue to be paid on time for its 6,000+ employees, despite ongoing geopolitical uncertainty. The announcement comes as global and regional markets face increasing pressure, with businesses focusing on stability and continuity. Sajan emphasised the company’s long-standing resilience, referencing past crises including the Iraqi invasion of Kuwait, the 2008 financial crisis, and the COVID-19 pandemic.
+Rizwan Sajan said, “I’ve faced many challenging situations in the past - from the Iraqi invasion of Kuwait to the 2008 financial crisis and the COVID-19 pandemic. Despite these, we have always bounced back stronger, and I’m confident we will do so again. During the pandemic, I had committed to not letting go of any employees, and I stood by that promise. Similarly, there will be no layoffs at Danube Group this time as well.” He added, “Our 6000+ employees are not just our workforce - they are our family.
+They helped build Danube Group into what it is today. In times like these, we stand by them with the same commitment. All salaries will be paid on time, and we remain dedicated to serving our clients and customers.” The group’s diversified structure, spanning building materials, real estate, and home solutions, alongside projects like Greenz by Danube, continues to support operational resilience and long-term growth.
+Read More - Link in Bio! https://t.co/rURwbecMni
+#DubaiRealEstate #BusinessNews #Leadership #UAE</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>The National Pavilion UAE will present “Washwasha” from 9 May to 22 November 2026 at the 61st International Art Exhibition of La Biennale di Venezia, according to WAM. Curated by Bana Kattan, Curator and Associate Head of Exhibitions at the Guggenheim Abu Dhabi Project, with Tala Nassar, Assistant Curator, the exhibition brings together works by Alaa Edris, Mays Albaik, Jawad Al Malhi, Farah Al Qasimi, Lamya Gargash, and Taus Makhacheva to explore sound, memory, movement, migration, and cultural transformation. The project positions sound as a medium of collective expression, connecting contemporary artistic practices with traditions such as storytelling, poetry, and broadcasting.
-Sheikh Salem bin Khalid Al Qassimi, Minister of Culture, said, “Since its inception, the National Pavilion UAE has served as a platform to nurture and showcase the country’s creative talent on the global stage of La Biennale di Venezia.” Angela Migally, Executive Director of the Salama bint Hamdan Al Nahyan Foundation, said the exhibition “contributes meaningfully to global discourse while remaining deeply rooted in its cultural context,” while Bana Kattan, Curator of the exhibition, described “Washwasha” as an artist-led project shaped by distinct perspectives on intangible histories.
-Laila Binbrek, Director of the National Pavilion UAE – La Biennale di Venezia, said the exhibition reflects the UAE’s rich intangible heritage through contemporary artistic expression and highlights the impact of sustained investment in artistic development and collaboration.</t>
+          <t>Danube Group has reaffirmed its commitment to its workforce, with Founder and Chairman Rizwan Sajan confirming there will be no layoffs and salaries will continue to be paid on time for its 6,000+ employees, despite ongoing geopolitical uncertainty. The announcement comes as global and regional markets face increasing pressure, with businesses focusing on stability and continuity. Sajan emphasized the company’s long-standing resilience, referencing past crises including the Iraqi invasion of Kuwait, the 2008 financial crisis, and the COVID-19 pandemic.
+Rizwan Sajan said, “I’ve faced many challenging situations in the past - from the Iraqi invasion of Kuwait to the 2008 financial crisis and the COVID-19 pandemic. Despite these, we have always bounced back stronger, and I’m confident we will do so again. During the pandemic, I had committed to not letting go of any employees, and I stood by that promise. Similarly, there will be no layoffs at Danube Group this time as well.” He added, “Our 6000+ employees are not just our workforce - they are our family.
+They helped build Danube Group into what it is today. In times like these, we stand by them with the same commitment. All salaries will be paid on time, and we remain dedicated to serving our clients and customers.” The group’s diversified structure, spanning building materials, real estate, and home solutions, alongside projects like Greenz by Danube, continues to support operational resilience and long-term growth.</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -8058,7 +8035,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>The National Pavilion UAE will present “Washwasha” from 9 May to 22 November 2026 at the 61st International Art Exhibition of La Biennale di Venezia, according to WAM. • The project positions sound as a medium of collective expression, connecting contemporary artistic practices with traditions such as storytelling, poetry, and broadcasting.</t>
+          <t>Sajan emphasized the company’s long-standing resilience, referencing past crises including the Iraqi invasion of Kuwait, the 2008 financial crisis, and the COVID-19 pandemic. • Rizwan Sajan said, “I’ve faced many challenging situations in the past - from the Iraqi invasion of Kuwait to the 2008 financial crisis and the COVID-19 pandemic. • Similarly, there will be no layoffs at Danube Group this time as well.” He added, “Our 6000+ employees are not just our workforce - they are our family.</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
@@ -8504,7 +8481,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>Emirates NBD SMS 2</t>
+          <t>Sms 2</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -8535,7 +8512,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Emirates NBD SMS 2</t>
+          <t>Sms 2</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
@@ -10657,7 +10634,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>Today's Gulf equity rally is not just a temporary bounce. With Dubai's DFM sharply up intraday, Emaar rising over 11% and Emirates NBD increasing nearly 14%, capital is quickly repricing lower shipping and energy risk. In this region, de-escalation immediately becomes a balance-sheet event.</t>
+          <t>Today's Gulf equity rally is not just a temporary bounce. With Dubai's DFM sharply up during the day, Emaar rising over 11% and Emirates NBD increasing nearly 14%, capital is quickly reassessing lower shipping and energy risks. In this region, de-escalation immediately impacts balance sheets.</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
@@ -10688,7 +10665,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>With Dubai's DFM sharply up intraday, Emaar rising over 11% and Emirates NBD increasing nearly 14%, capital is quickly repricing lower shipping and energy risk. • Today's Gulf equity rally is not just a temporary bounce. • In this region, de-escalation immediately becomes a balance-sheet event.</t>
+          <t>With Dubai's DFM sharply up during the day, Emaar rising over 11% and Emirates NBD increasing nearly 14%, capital is quickly reassessing lower shipping and energy risks. • Today's Gulf equity rally is not just a temporary bounce. • In this region, de-escalation immediately impacts balance sheets.</t>
         </is>
       </c>
       <c r="AJ63" t="inlineStr">
@@ -10976,7 +10953,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>AD Ports signs agreement with FAB, Emirates NBD Capital to refinance a $2.5 billion loan.</t>
+          <t>AD Ports signs agreement with FAB, Emirates NBD Capital to refinance $2.5 billion loan</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
@@ -11007,7 +10984,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>AD Ports signs agreement with FAB, Emirates NBD Capital to refinance a $2.5 billion loan.</t>
+          <t>AD Ports signs agreement with FAB, Emirates NBD Capital to refinance $2.5 billion loan</t>
         </is>
       </c>
       <c r="AJ65" t="inlineStr">
@@ -11907,7 +11884,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>I'm posting here because I don't have an option to reach out, SM team please look into it.</t>
+          <t>I'm posting here because I don't have an option to reach out, social media team please look into it.</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
@@ -11938,7 +11915,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>I'm posting here because I don't have an option to reach out, SM team please look into it.</t>
+          <t>I'm posting here because I don't have an option to reach out, social media team please look into it.</t>
         </is>
       </c>
       <c r="AJ71" t="inlineStr">
@@ -12069,8 +12046,8 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>Enjoy competitive profit rates when you avail an Auto Finance from Emirates Islamic.
-Profit rates starting from 1.89% flat per annum (equivalent to 3.61% reducing profit rate per annum). 
+          <t>Enjoy competitive profit rates when you take out an Auto Finance from Emirates Islamic.
+Profit rates starting from 1.89% flat per annum (equivalent to 3.61% reducing profit rate per annum).
 0% Easy Payment Plan on Emirates Islamic Credit Card spends.</t>
         </is>
       </c>
@@ -12102,7 +12079,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>Profit rates starting from 1.89% flat per annum (equivalent to 3.61% reducing profit rate per annum). • Enjoy competitive profit rates when you avail an Auto Finance from Emirates Islamic. • 0% Easy Payment Plan on Emirates Islamic Credit Card spends.</t>
+          <t>Profit rates starting from 1.89% flat per annum (equivalent to 3.61% reducing profit rate per annum). • Enjoy competitive profit rates when you take out an Auto Finance from Emirates Islamic. • 0% Easy Payment Plan on Emirates Islamic Credit Card spends.</t>
         </is>
       </c>
       <c r="AJ72" t="inlineStr">
@@ -12156,13 +12133,57 @@
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
+          <t>من مشترياتك اليومية إلى التسوق وحجوزات السفر، بطاقات الائتمانية من الإمارات الإسلامي تمنحك المكافآت التي تلبي احتياجاتك وتضيف قيمة لكل تجربة.
+✔️ استرداد نقدي ومكافآت على مشترياتك
+✔️ خدمة صف السيارات وخصومات حصرية على المطاعم</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
           <t>From day to day groceries to shopping and travel bookings, Emirates Islamic Credit Cards are designed to reward your lifestyle.
 ✔️Cashback and rewards on everyday spending
 ✔️Valet parking and special discounts on dining 
 ✔️Flexible payment options</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
+      <c r="K73" t="b">
+        <v>0</v>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Apr 8, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="n">
+        <v>46120.25</v>
+      </c>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
+      <c r="S73" t="n">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
+      </c>
+      <c r="V73" t="n">
+        <v>74</v>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
         <is>
           <t>From day to day groceries to shopping and travel bookings, Emirates Islamic Credit Cards are designed to reward your lifestyle.
 ✔️Cashback and rewards on everyday spending
@@ -12170,67 +12191,30 @@
 ✔️Flexible payment options</t>
         </is>
       </c>
-      <c r="K73" t="b">
-        <v>0</v>
-      </c>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>22h</t>
-        </is>
-      </c>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t>Apr 8, 2026 · 6:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P73" s="2" t="n">
-        <v>46120.25</v>
-      </c>
-      <c r="Q73" t="inlineStr"/>
-      <c r="R73" t="inlineStr"/>
-      <c r="S73" t="n">
-        <v>1</v>
-      </c>
-      <c r="T73" t="n">
-        <v>0</v>
-      </c>
-      <c r="U73" t="n">
-        <v>1</v>
-      </c>
-      <c r="V73" t="n">
-        <v>74</v>
-      </c>
-      <c r="W73" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X73" t="inlineStr">
-        <is>
-          <t>From day to day groceries to shopping and travel bookings, Emirates Islamic Credit Cards are designed to reward your lifestyle.
-✔️Cashback and rewards on everyday spending
-✔️Valet parking and special discounts on dining 
-✔️Flexible payment options</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr"/>
-      <c r="Z73" t="inlineStr"/>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041757945084453281</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>من مشترياتك اليومية إلى التسوق وحجوزات السفر، بطاقات الائتمانية من الإمارات الإسلامي تمنحك المكافآت التي تلبي احتياجاتك وتضيف قيمة لكل تجربة.
+✔️ استرداد نقدي ومكافآت على مشترياتك
+✔️ خدمة صف السيارات وخصومات حصرية على المطاعم</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>From day to day groceries to shopping and travel bookings, Emirates Islamic Credit Cards are designed to reward your lifestyle.
-✔️Cashback and rewards on everyday spending
-✔️Valet parking and special discounts on dining 
-✔️Flexible payment options</t>
+          <t>من مشترياتك اليومية إلى التسوق وحجوزات السفر، بطاقات الائتمانية من الإمارات الإسلامي تمنحك المكافآت التي تلبي احتياجاتك وتضيف قيمة لكل تجربة.
+✔️ استرداد نقدي ومكافآت على مشترياتك
+✔️ خدمة صف السيارات وخصومات حصرية على المطاعم</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>From day-to-day groceries to shopping and travel bookings, Emirates Islamic Credit Cards are designed to reward your lifestyle.
-✔️Cashback and rewards on everyday spending
-✔️Valet parking and special discounts on dining 
-✔️Flexible payment options</t>
+          <t>From your daily purchases to shopping and travel bookings, the credit cards from Emirates Islamic offer you rewards that meet your needs and add value to every experience.
+✔️ Cash back and rewards on your purchases
+✔️ Valet service and exclusive discounts at restaurants</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
@@ -12261,7 +12245,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>From day-to-day groceries to shopping and travel bookings, Emirates Islamic Credit Cards are designed to reward your lifestyle. • ✔️Cashback and rewards on everyday spending ✔️Valet parking and special discounts on dining ✔️Flexible payment options</t>
+          <t>From your daily purchases to shopping and travel bookings, the credit cards from Emirates Islamic offer you rewards that meet your needs and add value to every experience. • ✔️ Cash back and rewards on your purchases ✔️ Valet service and exclusive discounts at restaurants</t>
         </is>
       </c>
       <c r="AJ73" t="inlineStr">
@@ -12315,8 +12299,8 @@
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
-          <t>تسرنا زيارتكم لنا بفرعنا الجديد في سيليكون سنترال مول - دبي.
-نقدّم لكم خدمات مصرفية متكاملة مع ساعات عمل ممتدة عبر فترتين يومياً. نحن قريبين منكم في خدمتكم! https://t.co/TrLnjtiJhq</t>
+          <t>Our newest branch at Silicon Central Mall is open for business! 
+We offer banking solutions for all your lifestyle and business needs. We are open for extended hours across two shifts, so you can bank whenever it’s most convenient for you. Come visit us today!</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -12375,19 +12359,19 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>تسرنا زيارتكم لنا بفرعنا الجديد في سيليكون سنترال مول - دبي.
-نقدّم لكم خدمات مصرفية متكاملة مع ساعات عمل ممتدة عبر فترتين يومياً. نحن قريبين منكم في خدمتكم! https://t.co/TrLnjtiJhq</t>
+          <t>Our newest branch at Silicon Central Mall is open for business! 
+We offer banking solutions for all your lifestyle and business needs. We are open for extended hours across two shifts, so you can bank whenever it’s most convenient for you. Come visit us today!</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>تسرنا زيارتكم لنا بفرعنا الجديد في سيليكون سنترال مول - دبي.
-نقدّم لكم خدمات مصرفية متكاملة مع ساعات عمل ممتدة عبر فترتين يومياً. نحن قريبين منكم في خدمتكم! https://t.co/TrLnjtiJhq</t>
+          <t>Our newest branch at Silicon Central Mall is open for business! 
+We offer banking solutions for all your lifestyle and business needs. We are open for extended hours across two shifts, so you can bank whenever it’s most convenient for you. Come visit us today!</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>We are pleased to welcome you to our new branch at Silicon Central Mall - Dubai. We offer you comprehensive banking services with extended hours across two daily shifts. We are close to you and at your service!</t>
+          <t>Our newest branch at Silicon Central Mall is open for business! We offer banking solutions for all your lifestyle and business needs. We are open for extended hours across two shifts, so you can bank whenever it’s most convenient for you. Come visit us today!</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
@@ -12418,7 +12402,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>We offer you comprehensive banking services with extended hours across two daily shifts. • We are pleased to welcome you to our new branch at Silicon Central Mall - Dubai. • We are close to you and at your service!</t>
+          <t>We are open for extended hours across two shifts, so you can bank whenever it’s most convenient for you. • Our newest branch at Silicon Central Mall is open for business! • We offer banking solutions for all your lifestyle and business needs.</t>
         </is>
       </c>
       <c r="AJ74" t="inlineStr">
@@ -12621,7 +12605,7 @@
       <c r="I76" t="inlineStr">
         <is>
           <t>تسرنا زيارتكم لنا بفرعنا الجديد في سيليكون سنترال مول - دبي.
-نقدّم لكم خدمات مصرفية متكاملة مع ساعات عمل ممتدة عبر فترتين يومياً. نحن قريبين منكم في خدمتكم!</t>
+نقدّم لكم خدمات مصرفية متكاملة مع ساعات عمل ممتدة عبر فترتين يومياً. نحن قريبين منكم في خدمتكم! https://t.co/TrLnjtiJhq</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -12673,12 +12657,21 @@
 نقدّم لكم خدمات مصرفية متكاملة مع ساعات عمل ممتدة عبر فترتين يومياً. نحن قريبين منكم في خدمتكم!</t>
         </is>
       </c>
-      <c r="Y76" t="inlineStr"/>
-      <c r="Z76" t="inlineStr"/>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2041818196261372116</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>تسرنا زيارتكم لنا بفرعنا الجديد في سيليكون سنترال مول - دبي.
+نقدّم لكم خدمات مصرفية متكاملة مع ساعات عمل ممتدة عبر فترتين يومياً. نحن قريبين منكم في خدمتكم! https://t.co/TrLnjtiJhq</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>تسرنا زيارتكم لنا بفرعنا الجديد في سيليكون سنترال مول - دبي.
-نقدّم لكم خدمات مصرفية متكاملة مع ساعات عمل ممتدة عبر فترتين يومياً. نحن قريبين منكم في خدمتكم!</t>
+نقدّم لكم خدمات مصرفية متكاملة مع ساعات عمل ممتدة عبر فترتين يومياً. نحن قريبين منكم في خدمتكم! https://t.co/TrLnjtiJhq</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
@@ -12987,9 +12980,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>Valid until April 30, 2026. 
-Terms &amp; Conditions apply. 
-emiratesislamic.ae/en/offers…</t>
+          <t>Valid until April 30, 2026. Terms &amp; Conditions apply.</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
@@ -13020,7 +13011,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>Valid until April 30, 2026. • Terms &amp; Conditions apply. • emiratesislamic.ae/en/offers…</t>
+          <t>Valid until April 30, 2026. • Terms &amp; Conditions apply.</t>
         </is>
       </c>
       <c r="AJ78" t="inlineStr">
@@ -13399,7 +13390,7 @@
           <t>Discounts on flights and hotel bookings
 Airport lounge access, meet and greet services
 and much more.
-To know more visit https://t.co/JweLFHrkp9</t>
+To know more visit emiratesislamic.ae/en/Person…</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -13459,30 +13450,19 @@
 To know more visit emiratesislamic.ae/en/Person…</t>
         </is>
       </c>
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2041757946946666925</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr">
+      <c r="Y81" t="inlineStr"/>
+      <c r="Z81" t="inlineStr"/>
+      <c r="AA81" t="inlineStr">
         <is>
           <t>Discounts on flights and hotel bookings
 Airport lounge access, meet and greet services
 and much more.
-To know more visit https://t.co/JweLFHrkp9</t>
-        </is>
-      </c>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>Discounts on flights and hotel bookings
-Airport lounge access, meet and greet services
-and much more.
-To know more visit https://t.co/JweLFHrkp9</t>
+To know more visit emiratesislamic.ae/en/Person…</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>Discounts on flights and hotel bookings Airport lounge access, meet and greet services and much more. To know more visit https://t.co/JweLFHrkp9</t>
+          <t>Discounts on flights and hotel bookings Airport lounge access, meet and greet services and much more.</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
@@ -13513,7 +13493,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>Discounts on flights and hotel bookings Airport lounge access, meet and greet services and much more. • To know more visit https://t.co/JweLFHrkp9</t>
+          <t>Discounts on flights and hotel bookings Airport lounge access, meet and greet services and much more.</t>
         </is>
       </c>
       <c r="AJ81" t="inlineStr">
@@ -13567,9 +13547,12 @@
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
-          <t>من مشترياتك اليومية إلى التسوق وحجوزات السفر، بطاقات الائتمانية من الإمارات الإسلامي تمنحك المكافآت التي تلبي احتياجاتك وتضيف قيمة لكل تجربة.
-✔️ استرداد نقدي ومكافآت على مشترياتك
-✔️ خدمة صف السيارات وخصومات حصرية على المطاعم</t>
+          <t>✔️ خيارات سداد مرنة 
+✔️خصومات على حجوزات الطيران والفنادق
+الدخول إلى صالات المطارات وخدمات الاستقبال والترحيب
+وغير ذلك الكثير 
+للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
+emiratesislamic.ae/ar/Person…</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -13633,30 +13616,26 @@
 emiratesislamic.ae/ar/Person…</t>
         </is>
       </c>
-      <c r="Y82" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2041757941938725257</t>
-        </is>
-      </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>من مشترياتك اليومية إلى التسوق وحجوزات السفر، بطاقات الائتمانية من الإمارات الإسلامي تمنحك المكافآت التي تلبي احتياجاتك وتضيف قيمة لكل تجربة.
-✔️ استرداد نقدي ومكافآت على مشترياتك
-✔️ خدمة صف السيارات وخصومات حصرية على المطاعم</t>
-        </is>
-      </c>
+      <c r="Y82" t="inlineStr"/>
+      <c r="Z82" t="inlineStr"/>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>من مشترياتك اليومية إلى التسوق وحجوزات السفر، بطاقات الائتمانية من الإمارات الإسلامي تمنحك المكافآت التي تلبي احتياجاتك وتضيف قيمة لكل تجربة.
-✔️ استرداد نقدي ومكافآت على مشترياتك
-✔️ خدمة صف السيارات وخصومات حصرية على المطاعم</t>
+          <t>✔️ خيارات سداد مرنة 
+✔️خصومات على حجوزات الطيران والفنادق
+الدخول إلى صالات المطارات وخدمات الاستقبال والترحيب
+وغير ذلك الكثير 
+للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
+emiratesislamic.ae/ar/Person…</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>From your daily purchases to shopping and travel bookings, the credit cards from Emirates Islamic offer you rewards that meet your needs and add value to every experience.
-✔️ Cash back and rewards on your purchases
-✔️ Valet service and exclusive discounts at restaurants</t>
+          <t>✔️ Flexible payment options  
+✔️ Discounts on flight and hotel bookings  
+Access to airport lounges and reception and welcome services  
+and much more  
+For more information, please visit the following link:  
+emiratesislamic.ae/ar/Person…</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
@@ -13687,7 +13666,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>From your daily purchases to shopping and travel bookings, the credit cards from Emirates Islamic offer you rewards that meet your needs and add value to every experience. • ✔️ Cash back and rewards on your purchases ✔️ Valet service and exclusive discounts at restaurants</t>
+          <t>✔️ Flexible payment options ✔️ Discounts on flight and hotel bookings Access to airport lounges and reception and welcom…</t>
         </is>
       </c>
       <c r="AJ82" t="inlineStr">
@@ -14654,8 +14633,8 @@
           <t>Unsatisfactory experience with @EmiratesNBD_AE regarding the Union card, specifically concerning the mileage calculation mechanism.
 I converted a transaction into installments, and there was no clarification on the impact on the miles during the process. Later, I was surprised to find that the balance had gone negative, which raises serious questions about the clarity and mechanism of mileage calculation in such offers.
 It is unacceptable to provide a service or offer without a full explanation of its implications, especially when it comes to fundamental benefits that the customer relies on in their decisions.
-When I contacted them and opened a complaint, I was informed that the call recording was unavailable for technical reasons, and then the complaint was closed without a clear resolution, with a compensation offer that does not reflect the essence of the problem.
-This issue is not just about a single transaction, but about the transparency in the way miles are managed and calculated, which should be clear and fully understood by the customer.
+When I contacted them and filed a complaint, I was informed that the call recording was unavailable for technical reasons, and then the complaint was closed without a clear resolution, with a compensation offer that does not reflect the essence of the problem.
+This issue is not just about a single transaction, but about the transparency in the way miles are managed and calculated, which should be clear and understandable to the customer.
 We hope for a serious review of the case, a clear explanation of this mechanism, and a resolution that protects the customer's rights.</t>
         </is>
       </c>
@@ -14687,7 +14666,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>Later, I was surprised to find that the balance had gone negative, which raises serious questions about the clarity and mechanism of mileage calculation in such offers. • This issue is not just about a single transaction, but about the transparency in the way miles are managed and calculated, which should be clear and fully understood by the customer. • It is unacceptable to provide a service or offer without a full explanation of its implications, especially when it comes to fundamental benefits that the customer relies on in their decisions.</t>
+          <t>Later, I was surprised to find that the balance had gone negative, which raises serious questions about the clarity and mechanism of mileage calculation in such offers. • It is unacceptable to provide a service or offer without a full explanation of its implications, especially when it comes to fundamental benefits that the customer relies on in their decisions. • This issue is not just about a single transaction, but about the transparency in the way miles are managed and calculated, which should be clear and understandable to the customer.</t>
         </is>
       </c>
       <c r="AJ88" t="inlineStr">
@@ -14741,7 +14720,7 @@
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
-          <t>My digital wallet issue has been ongoing for months with no resolution. I keep getting calls from agents asking me to repeat the same steps I’ve already done multiple times.This needs escalation to IT/Business Ops not basic checklist troubleshooting. I want this formally raised.</t>
+          <t>@EmiratesNBD_AE @AppleSupport i have been struggling with my apple wallet for 4 months now. Since i changed from iphone14 to 17. I cannot add my cards (contact issuer) i have spoken to both of you &amp;amp; the problem has not been resolved yet. All steps were done from both sides too!</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -14795,16 +14774,24 @@
           <t>My digital wallet issue has been ongoing for months with no resolution. I keep getting calls from agents asking me to repeat the same steps I’ve already done multiple times.This needs escalation to IT/Business Ops not basic checklist troubleshooting. I want this formally raised.</t>
         </is>
       </c>
-      <c r="Y89" t="inlineStr"/>
-      <c r="Z89" t="inlineStr"/>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>https://x.com/koko_isa8/status/2041845502669680753</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE @AppleSupport i have been struggling with my apple wallet for 4 months now. Since i changed from iphone14 to 17. I cannot add my cards (contact issuer) i have spoken to both of you &amp;amp; the problem has not been resolved yet. All steps were done from both sides too!</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>My digital wallet issue has been ongoing for months with no resolution. I keep getting calls from agents asking me to repeat the same steps I’ve already done multiple times.This needs escalation to IT/Business Ops not basic checklist troubleshooting. I want this formally raised.</t>
+          <t>@EmiratesNBD_AE @AppleSupport i have been struggling with my apple wallet for 4 months now. Since i changed from iphone14 to 17. I cannot add my cards (contact issuer) i have spoken to both of you &amp;amp; the problem has not been resolved yet. All steps were done from both sides too!</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>My digital wallet issue has been ongoing for months with no resolution. I keep getting calls from agents asking me to repeat the same steps I’ve already done multiple times. This needs escalation to IT/Business Ops, not basic checklist troubleshooting. I want this formally raised.</t>
+          <t>I have been struggling with my Apple Wallet for 4 months now. Since I changed from iPhone 14 to 17, I cannot add my cards (contact issuer). I have spoken to both of you, and the problem has not been resolved yet. All steps were done from both sides too!</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
@@ -14835,7 +14822,7 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>I keep getting calls from agents asking me to repeat the same steps I’ve already done multiple times. • My digital wallet issue has been ongoing for months with no resolution. • This needs escalation to IT/Business Ops, not basic checklist troubleshooting.</t>
+          <t>Since I changed from iPhone 14 to 17, I cannot add my cards (contact issuer). • I have spoken to both of you, and the problem has not been resolved yet. • I have been struggling with my Apple Wallet for 4 months now.</t>
         </is>
       </c>
       <c r="AJ89" t="inlineStr">

--- a/check2.xlsx
+++ b/check2.xlsx
@@ -871,7 +871,7 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MY RELAXATION CORNER AT HOME. @LeaderOkkes @RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @KingSalman @DefensieMin @GiorgiaMeloni @PrimeministerGR @wef @wto @IMFNews @Davos @MarkJCarney @EmmanuelMacron @LulaOficial @JMilei @Jaemyung_Lee @scotgov @SwissGov @elonmusk https://t.co/IL54fs1InC</t>
+          <t>LOOK AT. I’M KING OF THE WORLD. @LeaderOkkes @airasia_indo @CebuPacificAir @airasia @usairforce @airtelindia @qatarairways @British_Airways @KenyaAirways @etihad @flysaa @KuwaitAirways @EmiratesNBD_AE @emirates @AmericanAir @AirCanada @airserbia @SaudiAirlinesEn @BritishArmy</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -929,24 +929,16 @@
           <t>LOOK AT. I’M KING OF THE WORLD. @LeaderOkkes @airasia_indo @CebuPacificAir @airasia @usairforce @airtelindia @qatarairways @British_Airways @KenyaAirways @etihad @flysaa @KuwaitAirways @EmiratesNBD_AE @emirates @AmericanAir @AirCanada @airserbia @SaudiAirlinesEn @BritishArmy</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>https://x.com/LeaderOkkes/status/2043465216571080917</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>MY RELAXATION CORNER AT HOME. @LeaderOkkes @RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @KingSalman @DefensieMin @GiorgiaMeloni @PrimeministerGR @wef @wto @IMFNews @Davos @MarkJCarney @EmmanuelMacron @LulaOficial @JMilei @Jaemyung_Lee @scotgov @SwissGov @elonmusk https://t.co/IL54fs1InC</t>
-        </is>
-      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>MY RELAXATION CORNER AT HOME. @LeaderOkkes @RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @KingSalman @DefensieMin @GiorgiaMeloni @PrimeministerGR @wef @wto @IMFNews @Davos @MarkJCarney @EmmanuelMacron @LulaOficial @JMilei @Jaemyung_Lee @scotgov @SwissGov @elonmusk https://t.co/IL54fs1InC</t>
+          <t>LOOK AT. I’M KING OF THE WORLD. @LeaderOkkes @airasia_indo @CebuPacificAir @airasia @usairforce @airtelindia @qatarairways @British_Airways @KenyaAirways @etihad @flysaa @KuwaitAirways @EmiratesNBD_AE @emirates @AmericanAir @AirCanada @airserbia @SaudiAirlinesEn @BritishArmy</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>MY RELAXATION CORNER AT HOME.</t>
+          <t>LOOK AT. I’M KING OF THE WORLD.</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -977,7 +969,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>MY RELAXATION CORNER AT HOME.</t>
+          <t>LOOK AT. I’M KING OF THE WORLD.</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1452,10 +1444,10 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Rabeh Saqer addressed His Excellency Advisor Turki Al-Sheikh from "Jeddah Season" and presented an impressive concert with Rotana, confirming that "Jeddah is different" and promising "an album like no other."
-In a massive concert where tickets sold out before the event, "Jeddah Season" celebrated with the "Gulf Songbird," the great artist Rabeh Saqer, the tremendous success he achieved as he soared with his voice, music, and creativity in front of his large audience that filled the "Abadi Al-Johar Arena" in Jeddah, as well as those who followed the live broadcast of the concert through Rotana channels. Rabeh's artistic performance on stage harmonized with his melodic, rhythmic, social, emotional, and patriotic songs, aligning with the season's slogan "Jeddah is different," and he indeed delivered something "different," which delighted everyone who watched the concert and ignited social media with clips captured by his fans, showcasing Rabeh singing with full musical and physical vigor throughout two singing sets, interspersed with a short break for the large musical band accompanying him, led by Maestro Hani Farhat.
-Mr. Salem Al-Hindi, Chairman and CEO of Rotana Music Group, was the first to welcome Rabeh Saqer upon his arrival at the concert venue and also the first to congratulate him on the success as he left the stage. However, between the beginning and the end, Rabeh Saqer crafted a success story for an artist armed with exceptional musical talent, a large, loyal, and loving audience. Before taking the stage, Rabeh met with Mr. Salem in front of the Media Wall with media representatives, and in response to a question about the message he sends from "Jeddah Season" to His Excellency Advisor Turki bin Abdul Mohsen Al-Sheikh, Chairman of the General Entertainment Authority, Rabeh conveyed a message of love, gratitude, and appreciation, saying: "His Excellency the Advisor is always with us in our hearts wherever we are in the Kingdom and outside it... not just in the Riyadh and Jeddah seasons." Rabeh also revealed that he is still working on and preparing his upcoming album produced by Rotana, which will include a group of prominent poets and composers as well as several talented individuals, emphasizing his commitment to musical diversity in these works to make his album, as usual, unique.
-On stage, Rabeh Saqer entertained his audience with a large number of his 30 songs that he rehearsed with his band, including: (Abarak Al-Saat, Sudfa, Afahemak, Enti Helwa, Taqdar Te'eed, Alf Min Yashhad, Khalna Kitha Helween, Kitha (Takhleen Al-Sahar), Al-Bashara, Al-Abaya Al-Raheefa, Al-Hikaya, Sadiqini, Gharam Atfal, Khalas, Wash Rayik Al-Laila, Awjah Al-Ma'na, Al-Rasas, La Tamnin, Yuhibunuh, Al-Dhahab Asli, Al-Waqi', Ya Dar, Ma Ad Tas'al, Sarra Al-Layl, Maghroura, Az'al Aleik). He concluded by bidding farewell to the audience of Jeddah and thanking those responsible for Jeddah Season and Rotana for their efforts in making this event a success.</t>
+          <t>Rabeh Saqer addressed His Excellency Counselor Turki Al-Sheikh from "Jeddah Season" and presented an impressive concert with Rotana, confirming that "Jeddah is different" and promising "an album like no other."
+In a massive concert where tickets sold out before the event, "Jeddah Season" celebrated with the "Saqer of Gulf Music," the great artist Rabeh Saqer, the tremendous success he achieved as he soared with his voice, music, and creativity in front of his large audience that filled the "Abadi Al-Johar Arena" in Jeddah. Those who followed the live broadcast of the concert on Rotana channels also enjoyed Rabeh's artistic performance on stage with his melodic, rhythmic, social, emotional, and patriotic songs, aligning with the season's slogan "Jeddah is different." Rabeh indeed delivered something "different," which delighted everyone who watched the concert and ignited social media with clips captured by his fans, showcasing Rabeh singing with full musical and physical vigor throughout two singing sets, interspersed with a short break for the large accompanying band led by Maestro Hani Farhat.
+Mr. Salem Al-Hindi, Chairman and CEO of Rotana Music Group, was the first to welcome Rabeh Saqer upon his arrival at the concert venue and the first to congratulate him after the conclusion of the event as he left the stage. However, between the beginning and the end, Rabeh Saqer crafted a success story for an artist armed with exceptional musical talent, a large, loyal, and loving audience. Before taking the stage, Rabeh met with Mr. Salem in front of the Media Wall with media representatives. In response to a question about the message he sends from "Jeddah Season" to His Excellency Counselor Turki bin Abdul Mohsen Al-Sheikh, Chairman of the General Entertainment Authority, Rabeh conveyed a message of love, gratitude, and appreciation, saying: "His Excellency the Counselor is always with us in our hearts wherever we are in the Kingdom and outside it... not just in the Riyadh and Jeddah seasons." Rabeh also revealed that he is still working on his upcoming album produced by Rotana, which will include a group of prominent poets and composers as well as several talented individuals, emphasizing his commitment to musical diversity in these works to make his album, as usual, unique.
+On stage, Rabeh Saqer entertained his audience with a large number of his 30 songs that he rehearsed with his band, including: (Abarak Al-Sa'at, Sudfa, Afahemak, Enti Helwa, Taqdar Te'eed, Alf Min Yashhad, Khalna Kitha Helween, Kitha (Takhleen Al-Sahar), Al-Basharah, Al-Abayah Al-Raheefa, Al-Hikayah, Sadiqini, Gharam Atfal, Khalas, Wash Rayik Al-Laylah, Awjah Al-Ma'na, Al-Rasas, La Tamnin, Yuhibunuh, Al-Dhahab Asli, Al-Waqi', Ya Dar, Ma Ad Tas'al, Sarra Al-Layl, Maghrurah, Az'al Alayk). He concluded by bidding farewell to the audience of Jeddah and thanking those responsible for Jeddah Season and Rotana for their efforts in making this event a success.</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -2647,7 +2639,7 @@
         <is>
           <t>Three messages say your Emirates ID or residence visa needs to be renewed. 
 Two are genuine and one is a trap designed to steal your data. Can you spot the fake message? 
-Share your answer in the comments, put your scam detection skills to the test and stand the chance to win AED 2,000.
+Share your answer in the comments, put your scam detection skills to the test and stand the chance to win AED 2,000. 
 #UnitedAgainstFraud</t>
         </is>
       </c>
@@ -2733,7 +2725,13 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>@KishSiff Try remarriage with a daughter of retired judge.</t>
+          <t>My career growth story 📈😀 
+- 2008 campus interview Infosys 25k salary
+- 2012 Emirates NBD Dubai 12k AED
+- 2013 IT Manager role in Dubai (18k AED)
+- 2015, married, ~23k AED in Dubai based startup
+- 2019 lost all as alimony &amp; fake cases stuck here
+Moral : Dont marry bro. 🥹</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2795,24 +2793,28 @@
 Moral : Dont marry bro. 🥹</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>https://x.com/KishSiff/status/2043299071918813643</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>@KishSiff Try remarriage with a daughter of retired judge.</t>
-        </is>
-      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>@KishSiff Try remarriage with a daughter of retired judge.</t>
+          <t>My career growth story 📈😀 
+- 2008 campus interview Infosys 25k salary
+- 2012 Emirates NBD Dubai 12k AED
+- 2013 IT Manager role in Dubai (18k AED)
+- 2015, married, ~23k AED in Dubai based startup
+- 2019 lost all as alimony &amp; fake cases stuck here
+Moral : Dont marry bro. 🥹</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Try remarriage with the daughter of a retired judge.</t>
+          <t>My career growth story 📈😀 
+- 2008 campus interview at Infosys with a salary of 25k
+- 2012 Emirates NBD in Dubai with a salary of 12k AED
+- 2013 IT Manager role in Dubai with a salary of 18k AED
+- 2015, got married, earning around 23k AED in a Dubai-based startup
+- 2019 lost everything due to alimony and false cases that left me stuck here
+Moral: Don't get married, bro. 🥹</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2843,7 +2845,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Try remarriage with the daughter of a retired judge.</t>
+          <t>My career growth story 📈😀 - 2008 campus interview at Infosys with a salary of 25k - 2012 Emirates NBD in Dubai with a sa…</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -3808,8 +3810,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Thursday is a special day 🤩 Buy your coffee from Molten and get the second one free with Emirates NBD cards 💳 
-For details: https://t.co/e7pJxUCJeB https://t.co/zoLns3Ls04</t>
+          <t>Thursday is fun 🤩 Buy your coffee from Molten and get the second one free with #Emirates_NBD cards 💳 For details: https://t.co/e7pJxUCJeB https://t.co/zoLns3Ls04</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3840,7 +3841,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Thursday is a special day 🤩 Buy your coffee from Molten and get the second one free with Emirates NBD cards 💳 For details: https://t.co/e7pJxUCJeB https://t.co/zoLns3Ls04</t>
+          <t>Thursday is fun 🤩 Buy your coffee from Molten and get the second one free with #Emirates_NBD cards 💳 For details: https://t.co/e7pJxUCJeB https://t.co/zoLns3Ls04</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">

--- a/check2.xlsx
+++ b/check2.xlsx
@@ -1414,9 +1414,9 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>Dear all,  
-The only reason for the rises in the markets is the influx of strong liquidity (regardless of the mechanism) coinciding with company results, which is a period that the market never misses, neither in good times nor in bad.  
+The only reason for the rises in the markets is the influx of strong liquidity (regardless of the mechanism) coinciding with company results, which is a period the market never misses, neither in good times nor in bad.  
 Come back to me in two weeks, so we can talk about the "earthquake of logic."  
-On top of that, I am a girl. ☹️</t>
+Additionally, I am a girl. ☹️</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Come back to me in two weeks, so we can talk about the "earthquake of logic." On top of that, I am a girl.</t>
+          <t>Come back to me in two weeks, so we can talk about the "earthquake of logic." Additionally, I am a girl.</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1470,12 +1470,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2044077090039873867</t>
+          <t>2044078376982319373</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044077090039873867</t>
+          <t>https://x.com/attas_2010/status/2044078376982319373</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>وحاليا بعد ماكان عندي قرض عقاري في بنك الرياض راح ارجعه مليون٦٠٠ ألف على ١٥ سنةصرت مديون للبنك الفرنسي مليونين ٣٠٠ ألف والصك مرهون عندهم وكل الي سوه سددو لبنك الرياض مليون ٧٠الف قيمة السداد المبكر فقط والفائض الي وعدني فيه سحب علي ومايرد</t>
+          <t>فوق ١٠ مرات ارفع شكاوي هذا الرد</t>
         </is>
       </c>
       <c r="K7" t="b">
@@ -1523,21 +1523,21 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 3:35 PM UTC</t>
+          <t>Apr 14, 2026 · 3:40 PM UTC</t>
         </is>
       </c>
       <c r="P7" s="2" t="n">
-        <v>46126.64930555555</v>
+        <v>46126.65277777778</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1546,7 +1546,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>101</v>
+        <v>39</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1555,12 +1555,12 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>وحاليا بعد ماكان عندي قرض عقاري في بنك الرياض راح ارجعه مليون٦٠٠ ألف على ١٥ سنةصرت مديون للبنك الفرنسي مليونين ٣٠٠ ألف والصك مرهون عندهم وكل الي سوه سددو لبنك الرياض مليون ٧٠الف قيمة السداد المبكر فقط والفائض الي وعدني فيه سحب علي ومايرد</t>
+          <t>فوق ١٠ مرات ارفع شكاوي هذا الرد</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044077090039873867</t>
+          <t>https://x.com/attas_2010/status/2044078376982319373</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1597,7 +1597,7 @@
         </is>
       </c>
       <c r="AE7" s="2" t="n">
-        <v>46126.81597222222</v>
+        <v>46126.81944444445</v>
       </c>
       <c r="AF7" s="2" t="n">
         <v>46126</v>
@@ -1830,9 +1830,9 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>#DWTCFreeZone Partners with @WioBank to Provide Digital Banking Solutions for Businesses.
-#DWTC #WioBank #Dubai #UAE #DXB @DWTCOfficial
-https://t.co/GIjGf2VZ0q</t>
+          <t>@EmiratesNBD_AE and @SobhaRealtyDXB partner to offer integrated home financing solutions for off-plan projects in #Dubai .
+#EmiratesNBD #SobhaRealty #UAE #Dubairealestate #realestate
+https://t.co/ukweMYki3P</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1897,21 +1897,21 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>#DWTCFreeZone Partners with @WioBank to Provide Digital Banking Solutions for Businesses.
-#DWTC #WioBank #Dubai #UAE #DXB @DWTCOfficial
-https://t.co/GIjGf2VZ0q</t>
+          <t>@EmiratesNBD_AE and @SobhaRealtyDXB partner to offer integrated home financing solutions for off-plan projects in #Dubai .
+#EmiratesNBD #SobhaRealty #UAE #Dubairealestate #realestate
+https://t.co/ukweMYki3P</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>#DWTCFreeZone Partners with @WioBank to Provide Digital Banking Solutions for Businesses.
-#DWTC #WioBank #Dubai #UAE #DXB @DWTCOfficial
-https://t.co/GIjGf2VZ0q</t>
+          <t>@EmiratesNBD_AE and @SobhaRealtyDXB partner to offer integrated home financing solutions for off-plan projects in #Dubai .
+#EmiratesNBD #SobhaRealty #UAE #Dubairealestate #realestate
+https://t.co/ukweMYki3P</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>#DWTCFreeZone partners with @WioBank to provide digital banking solutions for businesses.</t>
+          <t>Emirates NBD and Sobha Realty partner to offer integrated home financing solutions for off-plan projects in Dubai.</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE9" s="2" t="n">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>#DWTCFreeZone partners with @WioBank to provide digital banking solutions for businesses.</t>
+          <t>Emirates NBD and Sobha Realty partner to offer integrated home financing solutions for off-plan projects in Dubai.</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1996,9 +1996,20 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>التقى سمو الشيخ خالد بن محمد بن زايد آل نهيان قادة شركات صينية، في إطار تعزيز الشراكة الاستراتيجية بين البلدين.
-📌 ركزت اللقاءات على استكشاف فرص جديدة للتعاون الاقتصادي والتنموي، بما يدعم توسيع الاستثمارات وتعزيز العلاقات الثنائية.
-#الإمارات #الصين #الاستثمار #الاقتصاد #الشبكة_الاقتصادية</t>
+          <t>القيمة السوقية لأكبر 10 شركات عامة في الإمارات تبلغ 692.3 مليار دولار في 2026، تتصدرها "الشركة العالمية القابضة" مستحوذة وحدها على نحو 34% من إجمالي القيمة السوقية.
+@ihc__official
+@TAQAGroup
+@ADNOCGas
+@FABConnects
+@EmiratesNBD_AE
+@eAndUAE
+@DEWAOfficial
+@emaardubai
+@OfficialADCB
+@adhuae
+@ADX_AE
+@DFMalerts
+#الإمارات #أدنوك #الطاقة #IHC  #الشبكة_الاقتصادية</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -2078,29 +2089,29 @@
 #الإمارات #أدنوك #الطاقة #IHC  #الشبكة_الاقتصادية</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>https://x.com/Net_eqtisad/status/2044043515546800261</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>التقى سمو الشيخ خالد بن محمد بن زايد آل نهيان قادة شركات صينية، في إطار تعزيز الشراكة الاستراتيجية بين البلدين.
-📌 ركزت اللقاءات على استكشاف فرص جديدة للتعاون الاقتصادي والتنموي، بما يدعم توسيع الاستثمارات وتعزيز العلاقات الثنائية.
-#الإمارات #الصين #الاستثمار #الاقتصاد #الشبكة_الاقتصادية</t>
-        </is>
-      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>التقى سمو الشيخ خالد بن محمد بن زايد آل نهيان قادة شركات صينية، في إطار تعزيز الشراكة الاستراتيجية بين البلدين.
-📌 ركزت اللقاءات على استكشاف فرص جديدة للتعاون الاقتصادي والتنموي، بما يدعم توسيع الاستثمارات وتعزيز العلاقات الثنائية.
-#الإمارات #الصين #الاستثمار #الاقتصاد #الشبكة_الاقتصادية</t>
+          <t>القيمة السوقية لأكبر 10 شركات عامة في الإمارات تبلغ 692.3 مليار دولار في 2026، تتصدرها "الشركة العالمية القابضة" مستحوذة وحدها على نحو 34% من إجمالي القيمة السوقية.
+@ihc__official
+@TAQAGroup
+@ADNOCGas
+@FABConnects
+@EmiratesNBD_AE
+@eAndUAE
+@DEWAOfficial
+@emaardubai
+@OfficialADCB
+@adhuae
+@ADX_AE
+@DFMalerts
+#الإمارات #أدنوك #الطاقة #IHC  #الشبكة_الاقتصادية</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>His Highness Sheikh Khalid bin Mohammed bin Zayed Al Nahyan met with leaders of Chinese companies as part of enhancing the strategic partnership between the two countries. 
-The meetings focused on exploring new opportunities for economic and developmental cooperation, supporting the expansion of investments and strengthening bilateral relations.</t>
+          <t>The market value of the largest 10 public companies in the UAE is expected to reach $692.3 billion in 2026, led by "International Holding Company," which alone accounts for about 34% of the total market value.</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -2131,7 +2142,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>His Highness Sheikh Khalid bin Mohammed bin Zayed Al Nahyan met with leaders of Chinese companies as part of enhancing the strategic partnership between the two countries. • The meetings focused on exploring new opportunities for economic and developmental cooperation, supporting the expansion of investments and strengthening bilateral relations.</t>
+          <t>The market value of the largest 10 public companies in the UAE is expected to reach $692.3 billion in 2026, led by "Inte…</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -2341,78 +2352,88 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
+          <t>“Ya Biladi”… A Song That Feels Like Home, Bringing the UAE’s Spirit to Life 
+#YaBiladi #UAE #Dubai #Song #HussainAlJassmi @7sainaljassmi #محمد_بن_زايد #الامارات_العربية_المتحدة 
+https://t.co/TqZCzfMs1b via @onevillenews https://t.co/lrW3u4M1bq</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Emirates NBD and Sobha Realty partner to offer integrated home financing solutions for off-plan projects in Dubai 
+&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBD"&gt;#EmiratesNBD&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SobhaRealty"&gt;#SobhaRealty&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Dubai"&gt;#Dubai&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23UAE"&gt;#UAE&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Business"&gt;#Business&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Partnership"&gt;#Partnership&lt;/a&gt; &lt;a href="/SobhaRealtyDXB" title="Sobha Realty"&gt;@SobhaRealtyDXB&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23OneVilleNews"&gt;#OneVilleNews&lt;/a&gt;
+&lt;a href="https://onevillenews.com/2026/04/14/emirates-nbd-and-sobha-realty-partner-to-offer-integrated-home-financing-solutions-for-off-plan-projects-in-dubai/"&gt;onevillenews.com/2026/04/14/…&lt;/a&gt; via &lt;a href="/OneVilleNews" title="One Ville News"&gt;@onevillenews&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>14h</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Apr 14, 2026 · 11:57 AM UTC</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="n">
+        <v>46126.49791666667</v>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EmiratesNBD', 'https://x.com/search?f=tweets&amp;q=%23SobhaRealty', 'https://x.com/search?f=tweets&amp;q=%23Dubai', 'https://x.com/search?f=tweets&amp;q=%23UAE', 'https://x.com/search?f=tweets&amp;q=%23Business', 'https://x.com/search?f=tweets&amp;q=%23Partnership', 'https://x.com/SobhaRealtyDXB', 'https://x.com/search?f=tweets&amp;q=%23OneVilleNews', 'https://onevillenews.com/2026/04/14/emirates-nbd-and-sobha-realty-partner-to-offer-integrated-home-financing-solutions-for-off-plan-projects-in-dubai/', 'https://x.com/OneVilleNews']</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>36</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
           <t>Emirates NBD and Sobha Realty partner to offer integrated home financing solutions for off-plan projects in Dubai 
 #EmiratesNBD #SobhaRealty #Dubai #UAE #Business #Partnership @SobhaRealtyDXB #OneVilleNews
 onevillenews.com/2026/04/14/… via @onevillenews</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Emirates NBD and Sobha Realty partner to offer integrated home financing solutions for off-plan projects in Dubai 
-&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBD"&gt;#EmiratesNBD&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SobhaRealty"&gt;#SobhaRealty&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Dubai"&gt;#Dubai&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23UAE"&gt;#UAE&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Business"&gt;#Business&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Partnership"&gt;#Partnership&lt;/a&gt; &lt;a href="/SobhaRealtyDXB" title="Sobha Realty"&gt;@SobhaRealtyDXB&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23OneVilleNews"&gt;#OneVilleNews&lt;/a&gt;
-&lt;a href="https://onevillenews.com/2026/04/14/emirates-nbd-and-sobha-realty-partner-to-offer-integrated-home-financing-solutions-for-off-plan-projects-in-dubai/"&gt;onevillenews.com/2026/04/14/…&lt;/a&gt; via &lt;a href="/OneVilleNews" title="One Ville News"&gt;@onevillenews&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K12" t="b">
-        <v>0</v>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>14h</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Apr 14, 2026 · 11:57 AM UTC</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="n">
-        <v>46126.49791666667</v>
-      </c>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EmiratesNBD', 'https://x.com/search?f=tweets&amp;q=%23SobhaRealty', 'https://x.com/search?f=tweets&amp;q=%23Dubai', 'https://x.com/search?f=tweets&amp;q=%23UAE', 'https://x.com/search?f=tweets&amp;q=%23Business', 'https://x.com/search?f=tweets&amp;q=%23Partnership', 'https://x.com/SobhaRealtyDXB', 'https://x.com/search?f=tweets&amp;q=%23OneVilleNews', 'https://onevillenews.com/2026/04/14/emirates-nbd-and-sobha-realty-partner-to-offer-integrated-home-financing-solutions-for-off-plan-projects-in-dubai/', 'https://x.com/OneVilleNews']</t>
-        </is>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>36</v>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>Emirates NBD and Sobha Realty partner to offer integrated home financing solutions for off-plan projects in Dubai 
-#EmiratesNBD #SobhaRealty #Dubai #UAE #Business #Partnership @SobhaRealtyDXB #OneVilleNews
-onevillenews.com/2026/04/14/… via @onevillenews</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>https://x.com/OneVilleNews/status/2044022292972482932</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>“Ya Biladi”… A Song That Feels Like Home, Bringing the UAE’s Spirit to Life 
+#YaBiladi #UAE #Dubai #Song #HussainAlJassmi @7sainaljassmi #محمد_بن_زايد #الامارات_العربية_المتحدة 
+https://t.co/TqZCzfMs1b via @onevillenews https://t.co/lrW3u4M1bq</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Emirates NBD and Sobha Realty partner to offer integrated home financing solutions for off-plan projects in Dubai 
-#EmiratesNBD #SobhaRealty #Dubai #UAE #Business #Partnership @SobhaRealtyDXB #OneVilleNews
-onevillenews.com/2026/04/14/… via @onevillenews</t>
+          <t>“Ya Biladi”… A Song That Feels Like Home, Bringing the UAE’s Spirit to Life 
+#YaBiladi #UAE #Dubai #Song #HussainAlJassmi @7sainaljassmi #محمد_بن_زايد #الامارات_العربية_المتحدة 
+https://t.co/TqZCzfMs1b via @onevillenews https://t.co/lrW3u4M1bq</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Emirates NBD and Sobha Realty partner to offer integrated home financing solutions for off-plan projects in Dubai.</t>
+          <t>"Ya Biladi"... A Song That Feels Like Home, Bringing the UAE’s Spirit to Life</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2422,7 +2443,7 @@
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE12" s="2" t="n">
@@ -2443,7 +2464,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Emirates NBD and Sobha Realty partner to offer integrated home financing solutions for off-plan projects in Dubai.</t>
+          <t>A Song That Feels Like Home, Bringing the UAE’s Spirit to Life</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -3948,339 +3969,370 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
+          <t>Money grows best when given time, balance, and the right mix.
+Spreading investments and thinking long term can help create steadier progress along the way.
+Small steps today can support stronger outcomes tomorrow.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Money grows best when given time, balance, and the right mix.
+Spreading investments and thinking long term can help create steadier progress along the way.
+Small steps today can support stronger outcomes tomorrow.</t>
+        </is>
+      </c>
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Apr 14, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="n">
+        <v>46126.25</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>85</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Money grows best when given time, balance, and the right mix.
+Spreading investments and thinking long term can help create steadier progress along the way.
+Small steps today can support stronger outcomes tomorrow.</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>Money grows best when given time, balance, and the right mix.
+Spreading investments and thinking long term can help create steadier progress along the way.
+Small steps today can support stronger outcomes tomorrow.</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>Money grows best when given time, balance, and the right mix. Spreading investments and thinking long term can help create steadier progress along the way. Small steps today can support stronger outcomes tomorrow.</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Bank</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE22" s="2" t="n">
+        <v>46126.41666666666</v>
+      </c>
+      <c r="AF22" s="2" t="n">
+        <v>46126</v>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>2. Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Spreading investments and thinking long term can help create steadier progress along the way. • Money grows best when given time, balance, and the right mix. • Small steps today can support stronger outcomes tomorrow.</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AK22" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2043932263449006494</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2043932263449006494</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>كيف تدفع نفقاتك عادةً؟
+#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
+emiratesislamic.ae/ar/key-in…</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>كيف تدفع نفقاتك عادةً؟
+&lt;a href="/search?f=tweets&amp;amp;q=%23نظرتك_المالية"&gt;#نظرتك_المالية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التثقيف_المالي"&gt;#التثقيف_المالي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/ar/key-in…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K23" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Apr 14, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="n">
+        <v>46126.25</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23نظرتك_المالية', 'https://x.com/search?f=tweets&amp;q=%23التثقيف_المالي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+        </is>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>73</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>كيف تدفع نفقاتك عادةً؟
+#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
+emiratesislamic.ae/ar/key-in…</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>كيف تدفع نفقاتك عادةً؟
+#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
+emiratesislamic.ae/ar/key-in…</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>How do you usually pay your expenses?</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Bank</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE23" s="2" t="n">
+        <v>46126.41666666666</v>
+      </c>
+      <c r="AF23" s="2" t="n">
+        <v>46126</v>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>2. Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>How do you usually pay your expenses?</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AK23" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2043932263386157239</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2043932263386157239</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>كيف تدفع نفقاتك عادةً؟
+#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
+https://t.co/mgtIcQsyLZ</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
           <t>ينمو المال بشكل أفضل مع الوقت، والتوازن، والتنوّع المناسب.
 تنويع الاستثمارات والتفكير على المدى الطويل يساعدان على تحقيق استقرار أكبر.
 خطوات صغيرة اليوم قد تصنع نتائج أقوى في المستقبل.
 للمزيد: 
-https://t.co/mgtIcQsyLZ https://t.co/Eh7yupmtiG</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Money grows best when given time, balance, and the right mix.
-Spreading investments and thinking long term can help create steadier progress along the way.
-Small steps today can support stronger outcomes tomorrow.</t>
-        </is>
-      </c>
-      <c r="K22" t="b">
-        <v>0</v>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
+&lt;a href="https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/ar/key-in…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K24" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
         <is>
           <t>20h</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>Apr 14, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
-      <c r="P22" s="2" t="n">
+      <c r="P24" s="2" t="n">
         <v>46126.25</v>
       </c>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="n">
-        <v>1</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>85</v>
-      </c>
-      <c r="W22" t="inlineStr">
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+        </is>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>52</v>
+      </c>
+      <c r="W24" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>Money grows best when given time, balance, and the right mix.
-Spreading investments and thinking long term can help create steadier progress along the way.
-Small steps today can support stronger outcomes tomorrow.</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932263725854816</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>ينمو المال بشكل أفضل مع الوقت، والتوازن، والتنوّع المناسب.
-تنويع الاستثمارات والتفكير على المدى الطويل يساعدان على تحقيق استقرار أكبر.
-خطوات صغيرة اليوم قد تصنع نتائج أقوى في المستقبل.
-للمزيد: 
-https://t.co/mgtIcQsyLZ https://t.co/Eh7yupmtiG</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>ينمو المال بشكل أفضل مع الوقت، والتوازن، والتنوّع المناسب.
-تنويع الاستثمارات والتفكير على المدى الطويل يساعدان على تحقيق استقرار أكبر.
-خطوات صغيرة اليوم قد تصنع نتائج أقوى في المستقبل.
-للمزيد: 
-https://t.co/mgtIcQsyLZ https://t.co/Eh7yupmtiG</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>Money grows better with time, balance, and the right diversification. Diversifying investments and thinking long-term help achieve greater stability. Small steps today can lead to stronger results in the future.</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AE22" s="2" t="n">
-        <v>46126.41666666666</v>
-      </c>
-      <c r="AF22" s="2" t="n">
-        <v>46126</v>
-      </c>
-      <c r="AG22" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Diversifying investments and thinking long-term help achieve greater stability. • Small steps today can lead to stronger results in the future. • Money grows better with time, balance, and the right diversification.</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AK22" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2043932263449006494</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932263449006494</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>كيف تدفع نفقاتك عادةً؟
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-https://t.co/mgtIcQsyLZ</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>كيف تدفع نفقاتك عادةً؟
-&lt;a href="/search?f=tweets&amp;amp;q=%23نظرتك_المالية"&gt;#نظرتك_المالية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التثقيف_المالي"&gt;#التثقيف_المالي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/ar/key-in…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K23" t="b">
-        <v>0</v>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>20h</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>Apr 14, 2026 · 6:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="n">
-        <v>46126.25</v>
-      </c>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23نظرتك_المالية', 'https://x.com/search?f=tweets&amp;q=%23التثقيف_المالي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
-        </is>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>73</v>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>كيف تدفع نفقاتك عادةً؟
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-emiratesislamic.ae/ar/key-in…</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932263449006494</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>كيف تدفع نفقاتك عادةً؟
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-https://t.co/mgtIcQsyLZ</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>كيف تدفع نفقاتك عادةً؟
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-https://t.co/mgtIcQsyLZ</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>How do you usually pay your expenses?</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="AD23" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AE23" s="2" t="n">
-        <v>46126.41666666666</v>
-      </c>
-      <c r="AF23" s="2" t="n">
-        <v>46126</v>
-      </c>
-      <c r="AG23" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>How do you usually pay your expenses?</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AK23" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2043932263386157239</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932263386157239</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>ينمو المال بشكل أفضل مع الوقت، والتوازن، والتنوّع المناسب.
 تنويع الاستثمارات والتفكير على المدى الطويل يساعدان على تحقيق استقرار أكبر.
@@ -4289,79 +4341,28 @@
 emiratesislamic.ae/ar/key-in…</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>ينمو المال بشكل أفضل مع الوقت، والتوازن، والتنوّع المناسب.
-تنويع الاستثمارات والتفكير على المدى الطويل يساعدان على تحقيق استقرار أكبر.
-خطوات صغيرة اليوم قد تصنع نتائج أقوى في المستقبل.
-للمزيد: 
-&lt;a href="https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/ar/key-in…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K24" t="b">
-        <v>0</v>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>20h</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>Apr 14, 2026 · 6:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="n">
-        <v>46126.25</v>
-      </c>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
-        </is>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>52</v>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>ينمو المال بشكل أفضل مع الوقت، والتوازن، والتنوّع المناسب.
-تنويع الاستثمارات والتفكير على المدى الطويل يساعدان على تحقيق استقرار أكبر.
-خطوات صغيرة اليوم قد تصنع نتائج أقوى في المستقبل.
-للمزيد: 
-emiratesislamic.ae/ar/key-in…</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2043932263386157239</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>كيف تدفع نفقاتك عادةً؟
+#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
+https://t.co/mgtIcQsyLZ</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>ينمو المال بشكل أفضل مع الوقت، والتوازن، والتنوّع المناسب.
-تنويع الاستثمارات والتفكير على المدى الطويل يساعدان على تحقيق استقرار أكبر.
-خطوات صغيرة اليوم قد تصنع نتائج أقوى في المستقبل.
-للمزيد: 
-emiratesislamic.ae/ar/key-in…</t>
+          <t>كيف تدفع نفقاتك عادةً؟
+#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
+https://t.co/mgtIcQsyLZ</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Money grows better over time, with balance and the right diversification. Diversifying investments and thinking long-term help achieve greater stability. Small steps today can lead to stronger results in the future.</t>
+          <t>How do you usually pay your expenses?</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -4392,7 +4393,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Diversifying investments and thinking long-term help achieve greater stability. • Small steps today can lead to stronger results in the future. • Money grows better over time, with balance and the right diversification.</t>
+          <t>How do you usually pay your expenses?</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">

--- a/check2.xlsx
+++ b/check2.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL27"/>
+  <dimension ref="A1:AL31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,43 +625,43 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044612515498496366</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/DustshotW/status/2044612515498496366</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes</t>
+          <t>https://x.com/DustshotW</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LeaderOkkes</t>
+          <t>DustshotW</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN</t>
+          <t>justice gaming</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2035156091634380800/0oGW-_Z4_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2042550502014193664/yhlYRmG6_bigger.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ÖKKEŞ ŞAHİN'S INTERNATIONAL RECIPE: POWER SOUP. YOU WILL BOIL ONE CARROT, ONE GREEN PEPPER, AND ONE RED ONION. YOU WILL EAT IT LIKE THIS FOR A WHILE. LATER, YOU CAN ADD MEAT, FISH, AND CHICKEN TO IT. @LeaderOkkes @RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X https://t.co/UBoi80xAg0</t>
+          <t>anyone.....olease ......</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>A MINHA SOPA DE PODER. MY POWER SOUP. I’M KING OF THE WORLD. &lt;a href="/LeaderOkkes" title="THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN"&gt;@LeaderOkkes&lt;/a&gt; &lt;a href="/airasia_indo" title="AirAsia Indonesia"&gt;@airasia_indo&lt;/a&gt; &lt;a href="/IAF_MCC" title="Indian Air Force"&gt;@IAF_MCC&lt;/a&gt; &lt;a href="/CebuPacificAir" title="Cebu Pacific Air"&gt;@CebuPacificAir&lt;/a&gt; &lt;a href="/airasia" title="AirAsia"&gt;@airasia&lt;/a&gt; &lt;a href="/usairforce" title="U.S. Air Force"&gt;@usairforce&lt;/a&gt; &lt;a href="/airtelindia" title="airtel India"&gt;@airtelindia&lt;/a&gt; &lt;a href="/British_Airways" title="British Airways"&gt;@British_Airways&lt;/a&gt; &lt;a href="/KenyaAirways" title="Official Kenya Airways"&gt;@KenyaAirways&lt;/a&gt; &lt;a href="/etihad" title="Etihad Airways"&gt;@etihad&lt;/a&gt; &lt;a href="/flysaa" title="SAA - South African Airways"&gt;@flysaa&lt;/a&gt; &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; &lt;a href="/emirates" title="Emirates"&gt;@emirates&lt;/a&gt; &lt;a href="/AmericanAir" title="americanair"&gt;@AmericanAir&lt;/a&gt; &lt;a href="/AirCanada" title="Air Canada"&gt;@AirCanada&lt;/a&gt; &lt;a href="/airserbia" title="Air Serbia"&gt;@airserbia&lt;/a&gt; &lt;a href="/SaudiAirlinesEn" title="Saudia"&gt;@SaudiAirlinesEn&lt;/a&gt; &lt;a href="/X" title="X"&gt;@X&lt;/a&gt;</t>
+          <t>s enbd</t>
         </is>
       </c>
       <c r="K2" t="b">
@@ -670,39 +670,35 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>['LeaderOkkes', 'RoyalFamily', 'MonarchieBe', 'koninklijkhuis', 'KensingtonRoyal', 'DefensieMin', 'FratellidItalia', 'GiorgiaMeloni', 'Pontifex', 'MarkJCarney', 'EmmanuelMacron', 'PrimeministerGR', 'netanyahu', 'LulaOficial', 'JMilei', 'Jaemyung_Lee', 'chrisluxonmp', 'ParmelinG', 'scotgov', 'SwissGov', 'lemondefr', 'TheEconomist', 'iaeaorg', 'wef', 'wto', 'IMFNews', 'WorldBankGroup', 'Davos', 'nikkei', 'NYSE', 'BentleyMotors', 'UniofOxford', 'LeaderOkkes']</t>
+          <t>['dorienotfish']</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>7h</t>
+          <t>58m</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 7:22 PM UTC</t>
+          <t>Apr 16, 2026 · 3:03 AM UTC</t>
         </is>
       </c>
       <c r="P2" s="2" t="n">
-        <v>46126.80694444444</v>
+        <v>46128.12708333333</v>
       </c>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>['https://x.com/LeaderOkkes', 'https://x.com/airasia_indo', 'https://x.com/IAF_MCC', 'https://x.com/CebuPacificAir', 'https://x.com/airasia', 'https://x.com/usairforce', 'https://x.com/airtelindia', 'https://x.com/British_Airways', 'https://x.com/KenyaAirways', 'https://x.com/etihad', 'https://x.com/flysaa', 'https://x.com/EmiratesNBD_AE', 'https://x.com/emirates', 'https://x.com/AmericanAir', 'https://x.com/AirCanada', 'https://x.com/airserbia', 'https://x.com/SaudiAirlinesEn', 'https://x.com/X']</t>
-        </is>
-      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>94</v>
+        <v>14</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -711,27 +707,27 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>A MINHA SOPA DE PODER. MY POWER SOUP. I’M KING OF THE WORLD. @LeaderOkkes @airasia_indo @IAF_MCC @CebuPacificAir @airasia @usairforce @airtelindia @British_Airways @KenyaAirways @etihad @flysaa @EmiratesNBD_AE @emirates @AmericanAir @AirCanada @airserbia @SaudiAirlinesEn @X</t>
+          <t>s enbd</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/DustshotW/status/2044612515498496366</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>ÖKKEŞ ŞAHİN'S INTERNATIONAL RECIPE: POWER SOUP. YOU WILL BOIL ONE CARROT, ONE GREEN PEPPER, AND ONE RED ONION. YOU WILL EAT IT LIKE THIS FOR A WHILE. LATER, YOU CAN ADD MEAT, FISH, AND CHICKEN TO IT. @LeaderOkkes @RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X https://t.co/UBoi80xAg0</t>
+          <t>anyone.....olease ......</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>ÖKKEŞ ŞAHİN'S INTERNATIONAL RECIPE: POWER SOUP. YOU WILL BOIL ONE CARROT, ONE GREEN PEPPER, AND ONE RED ONION. YOU WILL EAT IT LIKE THIS FOR A WHILE. LATER, YOU CAN ADD MEAT, FISH, AND CHICKEN TO IT. @LeaderOkkes @RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X https://t.co/UBoi80xAg0</t>
+          <t>anyone.....olease ......</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Ökkeş Şahin's international recipe: power soup. You will boil one carrot, one green pepper, and one red onion. You will eat it like this for a while. Later, you can add meat, fish, and chicken to it.</t>
+          <t>anyone.....please ......</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -745,10 +741,10 @@
         </is>
       </c>
       <c r="AE2" s="2" t="n">
-        <v>46126.97361111111</v>
+        <v>46128.29375</v>
       </c>
       <c r="AF2" s="2" t="n">
-        <v>46126</v>
+        <v>46128</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
@@ -762,7 +758,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>You will boil one carrot, one green pepper, and one red onion. • Ökkeş Şahin's international recipe: power soup. • Later, you can add meat, fish, and chicken to it.</t>
+          <t>anyone.....please ......</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -775,7 +771,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>LeaderOkkes, RoyalFamily, MonarchieBe, koninklijkhuis, KensingtonRoyal, DefensieMin, FratellidItalia, GiorgiaMeloni, Pontifex, MarkJCarney, EmmanuelMacron, PrimeministerGR, netanyahu, LulaOficial, JMilei, Jaemyung_Lee, chrisluxonmp, ParmelinG, scotgov, SwissGov, lemondefr, TheEconomist, iaeaorg, wef, wto, IMFNews, WorldBankGroup, Davos, nikkei, NYSE, BentleyMotors, UniofOxford, LeaderOkkes</t>
+          <t>dorienotfish</t>
         </is>
       </c>
     </row>
@@ -785,47 +781,57 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2044132083443155222</t>
+          <t>2044611289733878057</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://x.com/metrixyo/status/2044132083443155222</t>
+          <t>https://x.com/BehindNums/status/2044611289733878057</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://x.com/metrixyo</t>
+          <t>https://x.com/BehindNums</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>metrixyo</t>
+          <t>BehindNums</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Metrix</t>
+          <t>BehindNums | Business &amp; Data</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1920369464379383808/skWlialk_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2025763865783345152/vXOr5RDQ_bigger.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>$QBTS 16% ⬆️ 
-$BE 21% ⬆️
-💵💵💵💵💵💵💵💵💵💵💵💵
-#qbts #quantum #dwave #Bloom #NASdaq #Nyse</t>
+          <t>Top 5 Companies by Revenue 
+By Revenue (annual)
+1️⃣ Walmart — ~$650B
+2️⃣ Amazon — ~$575B
+3️⃣ Saudi Aramco — ~$500B
+4️⃣ China State Grid — ~$480B
+5️⃣ Apple — ~$390B
+@BehindNums</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Pattern Day Trader (PDT) rule is soon going. No 25K USD limit for day trading : SEC
-&lt;a href="/search?f=tweets&amp;amp;q=%23WIO"&gt;#WIO&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23NASDAQ"&gt;#NASDAQ&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23ROBINHOOD"&gt;#ROBINHOOD&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23ENBD"&gt;#ENBD&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23NYSE"&gt;#NYSE&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23IG"&gt;#IG&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23IBKR"&gt;#IBKR&lt;/a&gt;</t>
+          <t>Top 5 Richest Companies in the Middle East 
+1️⃣ Saudi Aramco — ~$1.5T+
+2️⃣ International Holding Co (UAE) — ~$240B+
+3️⃣ QNB (Qatar National Bank) — ~$150B+
+4️⃣ Al Rajhi Bank (Saudi) — ~$100B+
+5️⃣ Emirates NBD (UAE) — ~$80B+
+Oil wealth meets financial power.
+&lt;a href="/BehindNums" title="BehindNums | Business &amp;amp; Data"&gt;@BehindNums&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K3" t="b">
@@ -835,21 +841,21 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>7h</t>
+          <t>1h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 7:14 PM UTC</t>
+          <t>Apr 16, 2026 · 2:58 AM UTC</t>
         </is>
       </c>
       <c r="P3" s="2" t="n">
-        <v>46126.80138888889</v>
+        <v>46128.12361111111</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23WIO', 'https://x.com/search?f=tweets&amp;q=%23NASDAQ', 'https://x.com/search?f=tweets&amp;q=%23ROBINHOOD', 'https://x.com/search?f=tweets&amp;q=%23ENBD', 'https://x.com/search?f=tweets&amp;q=%23NYSE', 'https://x.com/search?f=tweets&amp;q=%23IG', 'https://x.com/search?f=tweets&amp;q=%23IBKR']</t>
+          <t>['https://x.com/BehindNums']</t>
         </is>
       </c>
       <c r="S3" t="n">
@@ -862,7 +868,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>154</v>
+        <v>6</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -871,37 +877,55 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Pattern Day Trader (PDT) rule is soon going. No 25K USD limit for day trading : SEC
-#WIO #NASDAQ #ROBINHOOD #ENBD #NYSE #IG #IBKR</t>
+          <t>Top 5 Richest Companies in the Middle East 
+1️⃣ Saudi Aramco — ~$1.5T+
+2️⃣ International Holding Co (UAE) — ~$240B+
+3️⃣ QNB (Qatar National Bank) — ~$150B+
+4️⃣ Al Rajhi Bank (Saudi) — ~$100B+
+5️⃣ Emirates NBD (UAE) — ~$80B+
+Oil wealth meets financial power.
+@BehindNums</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>https://x.com/metrixyo/status/2044132083443155222</t>
+          <t>https://x.com/BehindNums/status/2044611289733878057</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>$QBTS 16% ⬆️ 
-$BE 21% ⬆️
-💵💵💵💵💵💵💵💵💵💵💵💵
-#qbts #quantum #dwave #Bloom #NASdaq #Nyse</t>
+          <t>Top 5 Companies by Revenue 
+By Revenue (annual)
+1️⃣ Walmart — ~$650B
+2️⃣ Amazon — ~$575B
+3️⃣ Saudi Aramco — ~$500B
+4️⃣ China State Grid — ~$480B
+5️⃣ Apple — ~$390B
+@BehindNums</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>$QBTS 16% ⬆️ 
-$BE 21% ⬆️
-💵💵💵💵💵💵💵💵💵💵💵💵
-#qbts #quantum #dwave #Bloom #NASdaq #Nyse</t>
+          <t>Top 5 Companies by Revenue 
+By Revenue (annual)
+1️⃣ Walmart — ~$650B
+2️⃣ Amazon — ~$575B
+3️⃣ Saudi Aramco — ~$500B
+4️⃣ China State Grid — ~$480B
+5️⃣ Apple — ~$390B
+@BehindNums</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>$QBTS 16% up  
-$BE 21% up  
-💵💵💵💵💵💵💵💵💵💵💵💵  
-#qbts #quantum #dwave #Bloom #NASDAQ #NYSE</t>
+          <t>Top 5 Companies by Revenue
+By Revenue (annual)
+1️⃣ Walmart — ~$650B
+2️⃣ Amazon — ~$575B
+3️⃣ Saudi Aramco — ~$500B
+4️⃣ China State Grid — ~$480B
+5️⃣ Apple — ~$390B
+@BehindNums</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -915,10 +939,10 @@
         </is>
       </c>
       <c r="AE3" s="2" t="n">
-        <v>46126.96805555555</v>
+        <v>46128.29027777778</v>
       </c>
       <c r="AF3" s="2" t="n">
-        <v>46126</v>
+        <v>46128</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
@@ -932,7 +956,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>$QBTS 16% up $BE 21% up 💵💵💵💵💵💵💵💵💵💵💵💵 #qbts #quantum #dwave #Bloom #NASDAQ #NYSE</t>
+          <t>Top 5 Companies by Revenue By Revenue (annual) 1️⃣ Walmart — ~$650B 2️⃣ Amazon — ~$575B 3️⃣ Saudi Aramco — ~$500B 4️⃣ China State Grid — ~$480B 5️⃣ Apple — ~$390B @BehindNums</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -955,49 +979,44 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2044090446926823921</t>
+          <t>2044582261102956879</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/AlAjlansambrfi/status/2044090446926823921</t>
+          <t>https://x.com/zaydaklabhoqx/status/2044582261102956879</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://x.com/AlAjlansambrfi</t>
+          <t>https://x.com/zaydaklabhoqx</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AlAjlansambrfi</t>
+          <t>zaydaklabhoqx</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>طموح العجلان</t>
+          <t>زيد أكلب</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2034995732173004803/dk7uz4Ir_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2035350140782002176/Clcsao6J_bigger.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>جمهور جدة غير ومع الصقر غير🦅
-#رابح_صقر_في_جدة
-#موسم_جدة
-#روتانا_لايف
-@RabehSaqer 
-@JEDCalendar 
-@EmiratesNBD_KSA https://t.co/3mI6SdN1pE</t>
+          <t>🚨 JUST IN: 🇦🇪 EMIRATES NBD ELIMINATES ATM WITHDRAWAL &amp;amp; DEBIT CARD FEES ACROSS THE UAE &amp;amp; GCC UNTIL MARCH 31, 2026! 💳🔥
+#UAE #EmiratesNBD #Banking #Finance #ATM #NoFees #GCC #MoneySmart https://t.co/aI9H5crVgx</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>رائع، الجوهرة تتألق في جدة! 🦅</t>
+          <t>ماذا عن مجانيّة سحب النقود؟ مبروك لعملاء Emirates NBD في الإمارات ودول الخليج</t>
         </is>
       </c>
       <c r="K4" t="b">
@@ -1006,21 +1025,21 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>['RotanaLive', 'RabehSaqer', 'JEDCalendar', 'EmiratesNBD_KSA']</t>
+          <t>['CryptoNewsHntrs']</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>2h</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 4:28 PM UTC</t>
+          <t>Apr 16, 2026 · 1:02 AM UTC</t>
         </is>
       </c>
       <c r="P4" s="2" t="n">
-        <v>46126.68611111111</v>
+        <v>46128.04305555556</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
@@ -1031,10 +1050,10 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -1043,39 +1062,29 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>رائع، الجوهرة تتألق في جدة! 🦅</t>
+          <t>ماذا عن مجانيّة سحب النقود؟ مبروك لعملاء Emirates NBD في الإمارات ودول الخليج</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>https://x.com/AlAjlansambrfi/status/2044090446926823921</t>
+          <t>https://x.com/zaydaklabhoqx/status/2044582261102956879</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>جمهور جدة غير ومع الصقر غير🦅
-#رابح_صقر_في_جدة
-#موسم_جدة
-#روتانا_لايف
-@RabehSaqer 
-@JEDCalendar 
-@EmiratesNBD_KSA https://t.co/3mI6SdN1pE</t>
+          <t>🚨 JUST IN: 🇦🇪 EMIRATES NBD ELIMINATES ATM WITHDRAWAL &amp;amp; DEBIT CARD FEES ACROSS THE UAE &amp;amp; GCC UNTIL MARCH 31, 2026! 💳🔥
+#UAE #EmiratesNBD #Banking #Finance #ATM #NoFees #GCC #MoneySmart https://t.co/aI9H5crVgx</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>جمهور جدة غير ومع الصقر غير🦅
-#رابح_صقر_في_جدة
-#موسم_جدة
-#روتانا_لايف
-@RabehSaqer 
-@JEDCalendar 
-@EmiratesNBD_KSA https://t.co/3mI6SdN1pE</t>
+          <t>🚨 JUST IN: 🇦🇪 EMIRATES NBD ELIMINATES ATM WITHDRAWAL &amp;amp; DEBIT CARD FEES ACROSS THE UAE &amp;amp; GCC UNTIL MARCH 31, 2026! 💳🔥
+#UAE #EmiratesNBD #Banking #Finance #ATM #NoFees #GCC #MoneySmart https://t.co/aI9H5crVgx</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>The audience in Jeddah is different, and with the falcon, it's different.</t>
+          <t>JUST IN: EMIRATES NBD ELIMINATES ATM WITHDRAWAL &amp; DEBIT CARD FEES ACROSS THE UAE &amp; GCC UNTIL MARCH 31, 2026!</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1085,14 +1094,14 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE4" s="2" t="n">
-        <v>46126.85277777778</v>
+        <v>46128.20972222222</v>
       </c>
       <c r="AF4" s="2" t="n">
-        <v>46126</v>
+        <v>46128</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
@@ -1106,7 +1115,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>The audience in Jeddah is different, and with the falcon, it's different.</t>
+          <t>JUST IN: EMIRATES NBD ELIMINATES ATM WITHDRAWAL &amp; DEBIT CARD FEES ACROSS THE UAE &amp; GCC UNTIL MARCH 31, 2026!</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1119,7 +1128,7 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>RotanaLive, RabehSaqer, JEDCalendar, EmiratesNBD_KSA</t>
+          <t>CryptoNewsHntrs</t>
         </is>
       </c>
     </row>
@@ -1129,69 +1138,75 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2044082383205609853</t>
+          <t>2044433219693466085</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://x.com/SunnyLusty/status/2044082383205609853</t>
+          <t>https://x.com/STFU1346/status/2044433219693466085</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/SunnyLusty</t>
+          <t>https://x.com/STFU1346</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SunnyLusty</t>
+          <t>STFU1346</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>आदियोगी</t>
+          <t>BraveFart🏴󠁧󠁢󠁳󠁣󠁴󠁿</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1799284544987615232/-AKwVwdx_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1691103462870650880/Mk3r6EQC_bigger.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Is there any updates or changes regarding Installment deferment for the personal loan due to current geopolitical circumstances,</t>
+          <t>🚨 Mark Clattenburg on Lisandro Martínez’s red card:
+“I was surprised that such an experienced referee considered this a red card offence. It was clearly a 50/50 challenge for the ball. 
+I think the referee’s seniority within the VAR group may have made others hesitant to overturn his on-field decision.
+In my opinion, this was a clear mistake. When we talk about ‘clear and obvious errors’, most referees would not have sent him off for that challenge.”</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; Is there any updates or changes regarding Installment deferment for the personal loan due to current geopolitical circumstances,</t>
+          <t>PepsiCo: Noted for regional arrangements in the Middle East and Asia. 
+Emirates NBD for the United Arab Emirates.
+Saudi Telecom Co.
+So, what&amp;#39;s your point?</t>
         </is>
       </c>
       <c r="K5" t="b">
         <v>0</v>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>['STFU1346', 'Cle_Etc', 'JeetyJeeterson', 'Brockutd']</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>12h</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 3:56 PM UTC</t>
+          <t>Apr 15, 2026 · 3:10 PM UTC</t>
         </is>
       </c>
       <c r="P5" s="2" t="n">
-        <v>46126.66388888889</v>
+        <v>46127.63194444445</v>
       </c>
       <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>['https://x.com/EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
         <v>1</v>
       </c>
@@ -1202,7 +1217,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -1211,27 +1226,39 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Is there any updates or changes regarding Installment deferment for the personal loan due to current geopolitical circumstances,</t>
+          <t>PepsiCo: Noted for regional arrangements in the Middle East and Asia. 
+Emirates NBD for the United Arab Emirates.
+Saudi Telecom Co.
+So, what's your point?</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>https://x.com/SunnyLusty/status/2044082383205609853</t>
+          <t>https://x.com/STFU1346/status/2044433219693466085</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Is there any updates or changes regarding Installment deferment for the personal loan due to current geopolitical circumstances,</t>
+          <t>🚨 Mark Clattenburg on Lisandro Martínez’s red card:
+“I was surprised that such an experienced referee considered this a red card offence. It was clearly a 50/50 challenge for the ball. 
+I think the referee’s seniority within the VAR group may have made others hesitant to overturn his on-field decision.
+In my opinion, this was a clear mistake. When we talk about ‘clear and obvious errors’, most referees would not have sent him off for that challenge.”</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Is there any updates or changes regarding Installment deferment for the personal loan due to current geopolitical circumstances,</t>
+          <t>🚨 Mark Clattenburg on Lisandro Martínez’s red card:
+“I was surprised that such an experienced referee considered this a red card offence. It was clearly a 50/50 challenge for the ball. 
+I think the referee’s seniority within the VAR group may have made others hesitant to overturn his on-field decision.
+In my opinion, this was a clear mistake. When we talk about ‘clear and obvious errors’, most referees would not have sent him off for that challenge.”</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Is there any updates or changes regarding installment deferment for the personal loan due to current geopolitical circumstances?</t>
+          <t>Mark Clattenburg on Lisandro Martínez’s red card:
+“I was surprised that such an experienced referee considered this a red card offence. It was clearly a 50/50 challenge for the ball.
+I think the referee’s seniority within the VAR group may have made others hesitant to overturn his on-field decision.
+In my opinion, this was a clear mistake. When we talk about ‘clear and obvious errors’, most referees would not have sent him off for that challenge.”</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1245,10 +1272,10 @@
         </is>
       </c>
       <c r="AE5" s="2" t="n">
-        <v>46126.83055555556</v>
+        <v>46127.79861111111</v>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
@@ -1262,7 +1289,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Is there any updates or changes regarding installment deferment for the personal loan due to current geopolitical circumstances?</t>
+          <t>Mark Clattenburg on Lisandro Martínez’s red card: “I was surprised that such an experienced referee considered this a red card offence. • I think the referee’s seniority within the VAR group may have made others hesitant to overturn his on-field decision. • When we talk about ‘clear and obvious errors’, most referees would not have sent him off for that challenge.”</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1275,7 +1302,7 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>STFU1346, Cle_Etc, JeetyJeeterson, Brockutd</t>
         </is>
       </c>
     </row>
@@ -1285,78 +1312,70 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2044082310447018168</t>
+          <t>2044430548727128554</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://x.com/ChirinAsadi/status/2044082310447018168</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2044430548727128554</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://x.com/ChirinAsadi</t>
+          <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ChirinAsadi</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chirin Al Asadi</t>
+          <t>Emirates NBD</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2035029628335923200/lkGmKuGp_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2042294543308242946/ScvMjarh_bigger.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>أعزائي ..
-السبب الوحيد للارتفاعات في الاسواق 
-هو دخول سيولة قوية ( بغض النظر عن الآلية) 
-تتزامن مع نتائج الشركات
-وهي الفترة التي لا يفوتها السوق أبداً
-لا في سراء ولا في ضراء 
-عُدْ إلي بعد أسبوعين،
-حتى نتحدث عن " زلزال المنطق "
-أضف الى ذلك .. أنا بِنْت ☹️</t>
+          <t>We are together against Fraud. @UAEBF #FightFraud #UAEBF #togetheragainstfraud #UnitedAgainstFraud https://t.co/CqApZaCAFO</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>اعتقد بنك دبي الامارات الوطني ENBD استفاد من اللخبطة التي حصلت في مارس
-بينما كان دبي الاسلامي DIB محافظاً في الانتقاء</t>
+          <t>Manage your wealth with expertise you can trust. Contact us today &lt;a href="https://www.emiratesnbd.com/en/priority-banking/wealth-management-solutions"&gt;emiratesnbd.com/en/priority-…&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBD"&gt;#EmiratesNBD&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23WealthManagement"&gt;#WealthManagement&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K6" t="b">
         <v>0</v>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>['alnuaimi_bader']</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 3:56 PM UTC</t>
+          <t>Apr 15, 2026 · 3:00 PM UTC</t>
         </is>
       </c>
       <c r="P6" s="2" t="n">
-        <v>46126.66388888889</v>
+        <v>46127.625</v>
       </c>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesnbd.com/en/priority-banking/wealth-management-solutions', 'https://x.com/search?f=tweets&amp;q=%23EmiratesNBD', 'https://x.com/search?f=tweets&amp;q=%23WealthManagement']</t>
+        </is>
+      </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
@@ -1364,10 +1383,10 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V6" t="n">
-        <v>90</v>
+        <v>1284</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1376,52 +1395,33 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>اعتقد بنك دبي الامارات الوطني ENBD استفاد من اللخبطة التي حصلت في مارس
-بينما كان دبي الاسلامي DIB محافظاً في الانتقاء</t>
+          <t>Manage your wealth with expertise you can trust. Contact us today emiratesnbd.com/en/priority-…
+#EmiratesNBD #WealthManagement</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>https://x.com/ChirinAsadi/status/2044082310447018168</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2044430548727128554</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>أعزائي ..
-السبب الوحيد للارتفاعات في الاسواق 
-هو دخول سيولة قوية ( بغض النظر عن الآلية) 
-تتزامن مع نتائج الشركات
-وهي الفترة التي لا يفوتها السوق أبداً
-لا في سراء ولا في ضراء 
-عُدْ إلي بعد أسبوعين،
-حتى نتحدث عن " زلزال المنطق "
-أضف الى ذلك .. أنا بِنْت ☹️</t>
+          <t>We are together against Fraud. @UAEBF #FightFraud #UAEBF #togetheragainstfraud #UnitedAgainstFraud https://t.co/CqApZaCAFO</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>أعزائي ..
-السبب الوحيد للارتفاعات في الاسواق 
-هو دخول سيولة قوية ( بغض النظر عن الآلية) 
-تتزامن مع نتائج الشركات
-وهي الفترة التي لا يفوتها السوق أبداً
-لا في سراء ولا في ضراء 
-عُدْ إلي بعد أسبوعين،
-حتى نتحدث عن " زلزال المنطق "
-أضف الى ذلك .. أنا بِنْت ☹️</t>
+          <t>We are together against Fraud. @UAEBF #FightFraud #UAEBF #togetheragainstfraud #UnitedAgainstFraud https://t.co/CqApZaCAFO</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Dear all,  
-The only reason for the rises in the markets is the influx of strong liquidity (regardless of the mechanism) coinciding with company results, which is a period the market never misses, neither in good times nor in bad.  
-Come back to me in two weeks, so we can talk about the "earthquake of logic."  
-Additionally, I am a girl. ☹️</t>
+          <t>We are together against Fraud.</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Cust</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -1430,10 +1430,10 @@
         </is>
       </c>
       <c r="AE6" s="2" t="n">
-        <v>46126.83055555556</v>
+        <v>46127.79166666666</v>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Come back to me in two weeks, so we can talk about the "earthquake of logic." Additionally, I am a girl.</t>
+          <t>We are together against Fraud.</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>alnuaimi_bader</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1470,72 +1470,79 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2044078376982319373</t>
+          <t>2044410083262734349</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044078376982319373</t>
+          <t>https://x.com/ibmag_magazine/status/2044410083262734349</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010</t>
+          <t>https://x.com/ibmag_magazine</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>attas_2010</t>
+          <t>ibmag_magazine</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>محمد</t>
+          <t>International Business Magazine</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1581396792075247620/ZCrbkCda_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1017739481749655553/2mtvJ3Sb_bigger.jpg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>سؤال:
-ماهو افضل بنك يشتري مديونية ؟!
-قرض عقاري + قرض شخصي .
-@alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE</t>
+          <t>To find the trending news on Corporate, Technology, Banking and Finance for #April14, check the links below:
+https://t.co/wCnnEeLf7A
+https://t.co/5jczPIqAT3
+https://t.co/X0IupL4wiw
+https://t.co/amPUbrkpdI
+#Intlbm #telecoms #Investment #MiddleEast #Banking #Finance #Innovation</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>فوق ١٠ مرات ارفع شكاوي هذا الرد</t>
+          <t>To find the trending news on Real estate, finance, and Technology for April 15, check the news links and the video link below:
+&lt;a href="https://tinyurl.com/4f7v9hen"&gt;tinyurl.com/4f7v9hen&lt;/a&gt;
+&lt;a href="https://tinyurl.com/2s3e7u9d"&gt;tinyurl.com/2s3e7u9d&lt;/a&gt;
+&lt;a href="https://tinyurl.com/mt35nuky"&gt;tinyurl.com/mt35nuky&lt;/a&gt;
+&lt;a href="https://tinyurl.com/55cdu3ep"&gt;tinyurl.com/55cdu3ep&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23INTLBM"&gt;#INTLBM&lt;/a&gt;  &lt;a href="/search?f=tweets&amp;amp;q=%23Sohar"&gt;#Sohar&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EToro"&gt;#EToro&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBD"&gt;#EmiratesNBD&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Sobha"&gt;#Sobha&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Headlines"&gt;#Headlines&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K7" t="b">
         <v>0</v>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>['attas_2010', 'KhalidSaeedR', 'amsh75', 'alrajhibank', 'BSF_sa', 'alinma', 'BankAlbilad', 'snbalahli', 'GulfIntlBank', 'EmiratesNBD_AE', 'BankAlJazira', 'RiyadBank', 'alawwalsab', 'SAIBLIVE']</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 3:40 PM UTC</t>
+          <t>Apr 15, 2026 · 1:38 PM UTC</t>
         </is>
       </c>
       <c r="P7" s="2" t="n">
-        <v>46126.65277777778</v>
+        <v>46127.56805555556</v>
       </c>
       <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>['https://tinyurl.com/4f7v9hen', 'https://tinyurl.com/2s3e7u9d', 'https://tinyurl.com/mt35nuky', 'https://tinyurl.com/55cdu3ep', 'https://x.com/search?f=tweets&amp;q=%23INTLBM', 'https://x.com/search?f=tweets&amp;q=%23Sohar', 'https://x.com/search?f=tweets&amp;q=%23EToro', 'https://x.com/search?f=tweets&amp;q=%23EmiratesNBD', 'https://x.com/search?f=tweets&amp;q=%23Sobha', 'https://x.com/search?f=tweets&amp;q=%23Headlines']</t>
+        </is>
+      </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
@@ -1543,10 +1550,10 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1555,35 +1562,42 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>فوق ١٠ مرات ارفع شكاوي هذا الرد</t>
+          <t>To find the trending news on Real estate, finance, and Technology for April 15, check the news links and the video link below:
+tinyurl.com/4f7v9hen
+tinyurl.com/2s3e7u9d
+tinyurl.com/mt35nuky
+tinyurl.com/55cdu3ep
+#INTLBM  #Sohar #EToro #EmiratesNBD #Sobha #Headlines</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044078376982319373</t>
+          <t>https://x.com/ibmag_magazine/status/2044410083262734349</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>سؤال:
-ماهو افضل بنك يشتري مديونية ؟!
-قرض عقاري + قرض شخصي .
-@alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE</t>
+          <t>To find the trending news on Corporate, Technology, Banking and Finance for #April14, check the links below:
+https://t.co/wCnnEeLf7A
+https://t.co/5jczPIqAT3
+https://t.co/X0IupL4wiw
+https://t.co/amPUbrkpdI
+#Intlbm #telecoms #Investment #MiddleEast #Banking #Finance #Innovation</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>سؤال:
-ماهو افضل بنك يشتري مديونية ؟!
-قرض عقاري + قرض شخصي .
-@alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE</t>
+          <t>To find the trending news on Corporate, Technology, Banking and Finance for #April14, check the links below:
+https://t.co/wCnnEeLf7A
+https://t.co/5jczPIqAT3
+https://t.co/X0IupL4wiw
+https://t.co/amPUbrkpdI
+#Intlbm #telecoms #Investment #MiddleEast #Banking #Finance #Innovation</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Question:
-What is the best bank to buy a debt?! 
-Mortgage loan + personal loan.</t>
+          <t>To find the trending news on Corporate, Technology, Banking, and Finance for April 14, check the links below:</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1597,10 +1611,10 @@
         </is>
       </c>
       <c r="AE7" s="2" t="n">
-        <v>46126.81944444445</v>
+        <v>46127.73472222222</v>
       </c>
       <c r="AF7" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
@@ -1614,7 +1628,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Question: What is the best bank to buy a debt?! • Mortgage loan + personal loan.</t>
+          <t>To find the trending news on Corporate, Technology, Banking, and Finance for April 14, check the links below:</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1627,7 +1641,7 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>attas_2010, KhalidSaeedR, amsh75, alrajhibank, BSF_sa, alinma, BankAlbilad, snbalahli, GulfIntlBank, EmiratesNBD_AE, BankAlJazira, RiyadBank, alawwalsab, SAIBLIVE</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1637,73 +1651,75 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2044075725334954107</t>
+          <t>2044390258528395378</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044075725334954107</t>
+          <t>https://x.com/Gulf_const/status/2044390258528395378</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010</t>
+          <t>https://x.com/Gulf_const</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>attas_2010</t>
+          <t>Gulf_const</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>محمد</t>
+          <t>Gulf Construction</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1581396792075247620/ZCrbkCda_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/3497523518/ff8c5dd3c169b9bb1240a76dd5f61a37_bigger.jpeg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>عميلنا العزيز ، نود التوضيح بأن منصات التواصل الاجتماعي مخصصة للاستفسارات العامة فقط.
-ولضمان خصوصيتكم وحماية بياناتكم، نرجو عدم مشاركة أي معلومات شخصية أو مصرفية (مثل رقم الهوية، رقم الحساب، كلمة المرور، رقم الجوال أو الأرقام السرية) عبر هذه المنصات.
-يرجى استخدام البريد الإلكتروني أو القنوات الرسمية للبنك لمعالجة الطلبات بأمان وسرية تامة.</t>
+          <t>Mered, the award-winning developer based in UAE, has announced that main piling operations are now progressing at Riviera Residences, a waterfront residential tower in Abu Dhabi, Al Reem Island.
+Read more on https://t.co/xGW6cvJ1Nc
+#GCnews #developer #UAE #residences https://t.co/bFrmFMn6HS</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>والله من خلال تجربتي مع البنك السعودي الفرنسي لا انصح ابدا بشراء مديونية منه اتفقت مع الموظف على اعادة تمويل وكنت في بنك الرياض علي قرض شخصي وعقاري اتفقت مع الموظف بعد ماشاف راتبي والعقار المرهون لبنك الرياض قيمته ٣ مليون  قدروه عمارة ٢٥ شقة المهم موظف البنك الفرنسي</t>
+          <t>Emirates NBD has announced a strategic partnership with Sobha Realty to provide integrated home financing solutions for buyers of the premium luxury developer’s off-plan residential developments across Dubai.
+Read more on &lt;a href="https://gulfconstructiononline.com/ArticleTA/414024"&gt;gulfconstructiononline.com/A…&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23GCnews"&gt;#GCnews&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23emirates"&gt;#emirates&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23MENA"&gt;#MENA&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K8" t="b">
         <v>0</v>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>['KhalidSaeedR', 'amsh75', 'alrajhibank', 'BSF_sa', 'alinma', 'BankAlbilad', 'snbalahli', 'GulfIntlBank', 'EmiratesNBD_AE', 'BankAlJazira', 'RiyadBank', 'alawwalsab', 'SAIBLIVE']</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 3:30 PM UTC</t>
+          <t>Apr 15, 2026 · 12:19 PM UTC</t>
         </is>
       </c>
       <c r="P8" s="2" t="n">
-        <v>46126.64583333334</v>
+        <v>46127.51319444444</v>
       </c>
       <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>['https://gulfconstructiononline.com/ArticleTA/414024', 'https://x.com/search?f=tweets&amp;q=%23GCnews', 'https://x.com/search?f=tweets&amp;q=%23emirates', 'https://x.com/search?f=tweets&amp;q=%23MENA']</t>
+        </is>
+      </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1712,7 +1728,7 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>135</v>
+        <v>22</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1721,31 +1737,33 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>والله من خلال تجربتي مع البنك السعودي الفرنسي لا انصح ابدا بشراء مديونية منه اتفقت مع الموظف على اعادة تمويل وكنت في بنك الرياض علي قرض شخصي وعقاري اتفقت مع الموظف بعد ماشاف راتبي والعقار المرهون لبنك الرياض قيمته ٣ مليون  قدروه عمارة ٢٥ شقة المهم موظف البنك الفرنسي</t>
+          <t>Emirates NBD has announced a strategic partnership with Sobha Realty to provide integrated home financing solutions for buyers of the premium luxury developer’s off-plan residential developments across Dubai.
+Read more on gulfconstructiononline.com/A…
+#GCnews #emirates #MENA</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044075725334954107</t>
+          <t>https://x.com/Gulf_const/status/2044390258528395378</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>عميلنا العزيز ، نود التوضيح بأن منصات التواصل الاجتماعي مخصصة للاستفسارات العامة فقط.
-ولضمان خصوصيتكم وحماية بياناتكم، نرجو عدم مشاركة أي معلومات شخصية أو مصرفية (مثل رقم الهوية، رقم الحساب، كلمة المرور، رقم الجوال أو الأرقام السرية) عبر هذه المنصات.
-يرجى استخدام البريد الإلكتروني أو القنوات الرسمية للبنك لمعالجة الطلبات بأمان وسرية تامة.</t>
+          <t>Mered, the award-winning developer based in UAE, has announced that main piling operations are now progressing at Riviera Residences, a waterfront residential tower in Abu Dhabi, Al Reem Island.
+Read more on https://t.co/xGW6cvJ1Nc
+#GCnews #developer #UAE #residences https://t.co/bFrmFMn6HS</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>عميلنا العزيز ، نود التوضيح بأن منصات التواصل الاجتماعي مخصصة للاستفسارات العامة فقط.
-ولضمان خصوصيتكم وحماية بياناتكم، نرجو عدم مشاركة أي معلومات شخصية أو مصرفية (مثل رقم الهوية، رقم الحساب، كلمة المرور، رقم الجوال أو الأرقام السرية) عبر هذه المنصات.
-يرجى استخدام البريد الإلكتروني أو القنوات الرسمية للبنك لمعالجة الطلبات بأمان وسرية تامة.</t>
+          <t>Mered, the award-winning developer based in UAE, has announced that main piling operations are now progressing at Riviera Residences, a waterfront residential tower in Abu Dhabi, Al Reem Island.
+Read more on https://t.co/xGW6cvJ1Nc
+#GCnews #developer #UAE #residences https://t.co/bFrmFMn6HS</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Dear valued customer, we would like to clarify that social media platforms are intended for general inquiries only. To ensure your privacy and protect your data, please do not share any personal or banking information (such as ID number, account number, password, mobile number, or PINs) through these platforms. Please use email or the bank's official channels to process requests securely and confidentially.</t>
+          <t>Mered, the award-winning developer based in the UAE, has announced that main piling operations are now progressing at Riviera Residences, a waterfront residential tower in Abu Dhabi, Al Reem Island.</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1759,10 +1777,10 @@
         </is>
       </c>
       <c r="AE8" s="2" t="n">
-        <v>46126.8125</v>
+        <v>46127.67986111111</v>
       </c>
       <c r="AF8" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
@@ -1776,7 +1794,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>To ensure your privacy and protect your data, please do not share any personal or banking information (such as ID number, account number, password, mobile number, or PINs) through these platforms. • Dear valued customer, we would like to clarify that social media platforms are intended for general inquiries only. • Please use email or the bank's official channels to process requests securely and confidentially.</t>
+          <t>Mered, the award-winning developer based in the UAE, has announced that main piling operations are now progressing at Riviera Residences, a waterfront residential tower in Abu Dhabi, Al Reem Island.</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1789,7 +1807,7 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>KhalidSaeedR, amsh75, alrajhibank, BSF_sa, alinma, BankAlbilad, snbalahli, GulfIntlBank, EmiratesNBD_AE, BankAlJazira, RiyadBank, alawwalsab, SAIBLIVE</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1799,47 +1817,49 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2044047297034760542</t>
+          <t>2044377290952364098</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://x.com/biztoday_intl/status/2044047297034760542</t>
+          <t>https://x.com/khir_llnas/status/2044377290952364098</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://x.com/biztoday_intl</t>
+          <t>https://x.com/khir_llnas</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>biztoday_intl</t>
+          <t>khir_llnas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Biz Today Intl</t>
+          <t>خير للناس للتنمية</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/948095006644097024/ns0iZtDe_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1823295456106930177/7M4AerkA_bigger.jpg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE and @SobhaRealtyDXB partner to offer integrated home financing solutions for off-plan projects in #Dubai .
-#EmiratesNBD #SobhaRealty #UAE #Dubairealestate #realestate
-https://t.co/ukweMYki3P</t>
+          <t>شكرا Emirates NBD بنك الإمارات دبي الوطني
+على دعمكم الإنساني في نجاح أنشطة المؤسسة لدعم الأسر المحتاجة..
+#متبرعين_خير_للناس
+#مؤسسة_خير_للناس https://t.co/5PUxmmX1mn</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; and &lt;a href="/SobhaRealtyDXB" title="Sobha Realty"&gt;@SobhaRealtyDXB&lt;/a&gt; partner to offer integrated home financing solutions for off-plan projects in &lt;a href="/search?f=tweets&amp;amp;q=%23Dubai"&gt;#Dubai&lt;/a&gt; .
-&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBD"&gt;#EmiratesNBD&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SobhaRealty"&gt;#SobhaRealty&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23UAE"&gt;#UAE&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Dubairealestate"&gt;#Dubairealestate&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23realestate"&gt;#realestate&lt;/a&gt;
-&lt;a href="https://www.biztoday.news/2026/04/14/emirates-nbd-and-sobha-realty-partner-to-offer-integrated-home-financing-solutions-for-off-plan-projects-in-dubai/"&gt;biztoday.news/2026/04/14/emi…&lt;/a&gt;</t>
+          <t>شكرا Emirates NBD بنك الإمارات دبي الوطني
+على دعمكم الإنساني في نجاح أنشطة المؤسسة لدعم الأسر المحتاجة..
+&lt;a href="/search?f=tweets&amp;amp;q=%23متبرعين_خير_للناس"&gt;#متبرعين_خير_للناس&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23مؤسسة_خير_للناس"&gt;#مؤسسة_خير_للناس&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K9" t="b">
@@ -1849,34 +1869,34 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 1:37 PM UTC</t>
+          <t>Apr 15, 2026 · 11:28 AM UTC</t>
         </is>
       </c>
       <c r="P9" s="2" t="n">
-        <v>46126.56736111111</v>
+        <v>46127.47777777778</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
-          <t>['https://x.com/EmiratesNBD_AE', 'https://x.com/SobhaRealtyDXB', 'https://x.com/search?f=tweets&amp;q=%23Dubai', 'https://x.com/search?f=tweets&amp;q=%23EmiratesNBD', 'https://x.com/search?f=tweets&amp;q=%23SobhaRealty', 'https://x.com/search?f=tweets&amp;q=%23UAE', 'https://x.com/search?f=tweets&amp;q=%23Dubairealestate', 'https://x.com/search?f=tweets&amp;q=%23realestate', 'https://www.biztoday.news/2026/04/14/emirates-nbd-and-sobha-realty-partner-to-offer-integrated-home-financing-solutions-for-off-plan-projects-in-dubai/']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23متبرعين_خير_للناس', 'https://x.com/search?f=tweets&amp;q=%23مؤسسة_خير_للناس']</t>
         </is>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1885,33 +1905,36 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE and @SobhaRealtyDXB partner to offer integrated home financing solutions for off-plan projects in #Dubai .
-#EmiratesNBD #SobhaRealty #UAE #Dubairealestate #realestate
-biztoday.news/2026/04/14/emi…</t>
+          <t>شكرا Emirates NBD بنك الإمارات دبي الوطني
+على دعمكم الإنساني في نجاح أنشطة المؤسسة لدعم الأسر المحتاجة..
+#متبرعين_خير_للناس
+#مؤسسة_خير_للناس</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>https://x.com/biztoday_intl/status/2044047297034760542</t>
+          <t>https://x.com/khir_llnas/status/2044377290952364098</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE and @SobhaRealtyDXB partner to offer integrated home financing solutions for off-plan projects in #Dubai .
-#EmiratesNBD #SobhaRealty #UAE #Dubairealestate #realestate
-https://t.co/ukweMYki3P</t>
+          <t>شكرا Emirates NBD بنك الإمارات دبي الوطني
+على دعمكم الإنساني في نجاح أنشطة المؤسسة لدعم الأسر المحتاجة..
+#متبرعين_خير_للناس
+#مؤسسة_خير_للناس https://t.co/5PUxmmX1mn</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE and @SobhaRealtyDXB partner to offer integrated home financing solutions for off-plan projects in #Dubai .
-#EmiratesNBD #SobhaRealty #UAE #Dubairealestate #realestate
-https://t.co/ukweMYki3P</t>
+          <t>شكرا Emirates NBD بنك الإمارات دبي الوطني
+على دعمكم الإنساني في نجاح أنشطة المؤسسة لدعم الأسر المحتاجة..
+#متبرعين_خير_للناس
+#مؤسسة_خير_للناس https://t.co/5PUxmmX1mn</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Emirates NBD and Sobha Realty partner to offer integrated home financing solutions for off-plan projects in Dubai.</t>
+          <t>Thank you Emirates NBD for your humanitarian support in the success of the organization's activities to support needy families.</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1925,10 +1948,10 @@
         </is>
       </c>
       <c r="AE9" s="2" t="n">
-        <v>46126.73402777778</v>
+        <v>46127.64444444444</v>
       </c>
       <c r="AF9" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
@@ -1942,7 +1965,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Emirates NBD and Sobha Realty partner to offer integrated home financing solutions for off-plan projects in Dubai.</t>
+          <t>Thank you Emirates NBD for your humanitarian support in the success of the organization's activities to support needy families.</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1965,95 +1988,69 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2044043515546800261</t>
+          <t>2044363346460172688</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://x.com/Net_eqtisad/status/2044043515546800261</t>
+          <t>https://x.com/Sems3499/status/2044363346460172688</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://x.com/Net_eqtisad</t>
+          <t>https://x.com/Sems3499</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Net_eqtisad</t>
+          <t>Sems3499</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>الشبكة الاقتصادية</t>
+          <t>Sem</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1892643729745317888/Zh1HkNvX_bigger.jpg</t>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>القيمة السوقية لأكبر 10 شركات عامة في الإمارات تبلغ 692.3 مليار دولار في 2026، تتصدرها "الشركة العالمية القابضة" مستحوذة وحدها على نحو 34% من إجمالي القيمة السوقية.
-@ihc__official
-@TAQAGroup
-@ADNOCGas
-@FABConnects
-@EmiratesNBD_AE
-@eAndUAE
-@DEWAOfficial
-@emaardubai
-@OfficialADCB
-@adhuae
-@ADX_AE
-@DFMalerts
-#الإمارات #أدنوك #الطاقة #IHC  #الشبكة_الاقتصادية</t>
+          <t>@nurkanaydogan Enbd bankalarında çalışanlar için 1. Şık olduğunu düşünüyorum (:</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>القيمة السوقية لأكبر 10 شركات عامة في الإمارات تبلغ 692.3 مليار دولار في 2026، تتصدرها &amp;#34;الشركة العالمية القابضة&amp;#34; مستحوذة وحدها على نحو 34% من إجمالي القيمة السوقية.
-&lt;a href="/ihc__official" title="IHC"&gt;@ihc__official&lt;/a&gt;
-&lt;a href="/TAQAGroup" title="TAQA"&gt;@TAQAGroup&lt;/a&gt;
-&lt;a href="/ADNOCGas" title="ADNOC Gas"&gt;@ADNOCGas&lt;/a&gt;
-&lt;a href="/FABConnects" title="FAB Connects"&gt;@FABConnects&lt;/a&gt;
-&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;
-&lt;a href="/eAndUAE" title="e&amp;amp; UAE"&gt;@eAndUAE&lt;/a&gt;
-&lt;a href="/DEWAOfficial" title="DEWA | Official Page"&gt;@DEWAOfficial&lt;/a&gt;
-&lt;a href="/emaardubai" title="Emaar Dubai"&gt;@emaardubai&lt;/a&gt;
-&lt;a href="/OfficialADCB" title="ADCB بنك أبوظبي التجاري"&gt;@OfficialADCB&lt;/a&gt;
-&lt;a href="/adhuae" title="Moon"&gt;@adhuae&lt;/a&gt;
-&lt;a href="/ADX_AE" title="سوق أبوظبي للأوراق المالية"&gt;@ADX_AE&lt;/a&gt;
-&lt;a href="/DFMalerts" title="Dubai Financial Market"&gt;@DFMalerts&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات"&gt;#الإمارات&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23أدنوك"&gt;#أدنوك&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الطاقة"&gt;#الطاقة&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23IHC"&gt;#IHC&lt;/a&gt;  &lt;a href="/search?f=tweets&amp;amp;q=%23الشبكة_الاقتصادية"&gt;#الشبكة_الاقتصادية&lt;/a&gt;</t>
+          <t>Enbd bankalarında çalışanlar için 1. Şık olduğunu düşünüyorum (:</t>
         </is>
       </c>
       <c r="K10" t="b">
         <v>0</v>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>['nurkanaydogan']</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 1:22 PM UTC</t>
+          <t>Apr 15, 2026 · 10:32 AM UTC</t>
         </is>
       </c>
       <c r="P10" s="2" t="n">
-        <v>46126.55694444444</v>
+        <v>46127.43888888889</v>
       </c>
       <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>['https://x.com/ihc__official', 'https://x.com/TAQAGroup', 'https://x.com/ADNOCGas', 'https://x.com/FABConnects', 'https://x.com/EmiratesNBD_AE', 'https://x.com/eAndUAE', 'https://x.com/DEWAOfficial', 'https://x.com/emaardubai', 'https://x.com/OfficialADCB', 'https://x.com/adhuae', 'https://x.com/ADX_AE', 'https://x.com/DFMalerts', 'https://x.com/search?f=tweets&amp;q=%23الإمارات', 'https://x.com/search?f=tweets&amp;q=%23أدنوك', 'https://x.com/search?f=tweets&amp;q=%23الطاقة', 'https://x.com/search?f=tweets&amp;q=%23IHC', 'https://x.com/search?f=tweets&amp;q=%23الشبكة_الاقتصادية']</t>
-        </is>
-      </c>
+      <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
         <v>0</v>
       </c>
@@ -2061,10 +2058,10 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -2073,45 +2070,27 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>القيمة السوقية لأكبر 10 شركات عامة في الإمارات تبلغ 692.3 مليار دولار في 2026، تتصدرها "الشركة العالمية القابضة" مستحوذة وحدها على نحو 34% من إجمالي القيمة السوقية.
-@ihc__official
-@TAQAGroup
-@ADNOCGas
-@FABConnects
-@EmiratesNBD_AE
-@eAndUAE
-@DEWAOfficial
-@emaardubai
-@OfficialADCB
-@adhuae
-@ADX_AE
-@DFMalerts
-#الإمارات #أدنوك #الطاقة #IHC  #الشبكة_الاقتصادية</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
+          <t>Enbd bankalarında çalışanlar için 1. Şık olduğunu düşünüyorum (:</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>https://x.com/Sems3499/status/2044363346460172688</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>@nurkanaydogan Enbd bankalarında çalışanlar için 1. Şık olduğunu düşünüyorum (:</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>القيمة السوقية لأكبر 10 شركات عامة في الإمارات تبلغ 692.3 مليار دولار في 2026، تتصدرها "الشركة العالمية القابضة" مستحوذة وحدها على نحو 34% من إجمالي القيمة السوقية.
-@ihc__official
-@TAQAGroup
-@ADNOCGas
-@FABConnects
-@EmiratesNBD_AE
-@eAndUAE
-@DEWAOfficial
-@emaardubai
-@OfficialADCB
-@adhuae
-@ADX_AE
-@DFMalerts
-#الإمارات #أدنوك #الطاقة #IHC  #الشبكة_الاقتصادية</t>
+          <t>@nurkanaydogan Enbd bankalarında çalışanlar için 1. Şık olduğunu düşünüyorum (:</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>The market value of the largest 10 public companies in the UAE is expected to reach $692.3 billion in 2026, led by "International Holding Company," which alone accounts for about 34% of the total market value.</t>
+          <t>I think it's stylish for employees working at Enbd banks.</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -2121,14 +2100,14 @@
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE10" s="2" t="n">
-        <v>46126.72361111111</v>
+        <v>46127.60555555556</v>
       </c>
       <c r="AF10" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
@@ -2142,7 +2121,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>The market value of the largest 10 public companies in the UAE is expected to reach $692.3 billion in 2026, led by "Inte…</t>
+          <t>I think it's stylish for employees working at Enbd banks.</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -2155,7 +2134,7 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>nurkanaydogan</t>
         </is>
       </c>
     </row>
@@ -2165,43 +2144,46 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2044025847523487886</t>
+          <t>2044351837869105398</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide/status/2044025847523487886</t>
+          <t>https://x.com/titledeednews/status/2044351837869105398</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide</t>
+          <t>https://x.com/titledeednews</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>dcgguide</t>
+          <t>titledeednews</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>DUBAI CITY GUIDE from Cyber Gear</t>
+          <t>The Title Deed</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1780203891230945280/ODQLZiT__bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2032863974820294659/y_r3-sNy_bigger.jpg</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Emirates NBD And Sobha Realty Partner To Offer Integrated Home Financing Solutions For Off-Plan Projects In Dubai https://t.co/fVBST6NQ7A</t>
+          <t>Al Habtoor Group is committing over AED 5 billion to a new commercial tower in Dubai. Another strong indicator of sustained demand for Grade A office space and long-term market confidence.
+#DubaiRealEstate #CommercialRealEstate #InvestInDubai #DubaiBrokers #RealEstateNews https://t.co/kHUr6Xe7wr</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Emirates NBD And Sobha Realty Partner To Offer Integrated Home Financing Solutions For Off-Plan Projects In Dubai &lt;a href="https://dubaipropertyguide.io/emirates-nbd-and-sobha-realty-partner-to-offer-integrated-home-financing-solutions-for-off-plan-projects-in-dubai-2/"&gt;dubaipropertyguide.io/emirat…&lt;/a&gt;</t>
+          <t>Sobha Realty is making off-plan investing in Dubai more accessible.
+In partnership with Emirates NBD, Sobha Realty introduces flexible financing solutions, giving investors easier access to high-potential opportunities.
+&lt;a href="/search?f=tweets&amp;amp;q=%23DubaiInvestors"&gt;#DubaiInvestors&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23OffPlanDubai"&gt;#OffPlanDubai&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23RealEstateInvesting"&gt;#RealEstateInvesting&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Dubai"&gt;#Dubai&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K11" t="b">
@@ -2211,34 +2193,34 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 12:11 PM UTC</t>
+          <t>Apr 15, 2026 · 9:47 AM UTC</t>
         </is>
       </c>
       <c r="P11" s="2" t="n">
-        <v>46126.50763888889</v>
+        <v>46127.40763888889</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>['https://dubaipropertyguide.io/emirates-nbd-and-sobha-realty-partner-to-offer-integrated-home-financing-solutions-for-off-plan-projects-in-dubai-2/']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23DubaiInvestors', 'https://x.com/search?f=tweets&amp;q=%23OffPlanDubai', 'https://x.com/search?f=tweets&amp;q=%23RealEstateInvesting', 'https://x.com/search?f=tweets&amp;q=%23Dubai']</t>
         </is>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -2247,27 +2229,31 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Emirates NBD And Sobha Realty Partner To Offer Integrated Home Financing Solutions For Off-Plan Projects In Dubai dubaipropertyguide.io/emirat…</t>
+          <t>Sobha Realty is making off-plan investing in Dubai more accessible.
+In partnership with Emirates NBD, Sobha Realty introduces flexible financing solutions, giving investors easier access to high-potential opportunities.
+#DubaiInvestors #OffPlanDubai #RealEstateInvesting #Dubai</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide/status/2044025847523487886</t>
+          <t>https://x.com/titledeednews/status/2044351837869105398</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>Emirates NBD And Sobha Realty Partner To Offer Integrated Home Financing Solutions For Off-Plan Projects In Dubai https://t.co/fVBST6NQ7A</t>
+          <t>Al Habtoor Group is committing over AED 5 billion to a new commercial tower in Dubai. Another strong indicator of sustained demand for Grade A office space and long-term market confidence.
+#DubaiRealEstate #CommercialRealEstate #InvestInDubai #DubaiBrokers #RealEstateNews https://t.co/kHUr6Xe7wr</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Emirates NBD And Sobha Realty Partner To Offer Integrated Home Financing Solutions For Off-Plan Projects In Dubai https://t.co/fVBST6NQ7A</t>
+          <t>Al Habtoor Group is committing over AED 5 billion to a new commercial tower in Dubai. Another strong indicator of sustained demand for Grade A office space and long-term market confidence.
+#DubaiRealEstate #CommercialRealEstate #InvestInDubai #DubaiBrokers #RealEstateNews https://t.co/kHUr6Xe7wr</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Emirates NBD and Sobha Realty have partnered to provide integrated home financing solutions for off-plan projects in Dubai.</t>
+          <t>Al Habtoor Group is committing over AED 5 billion to a new commercial tower in Dubai. This is another strong indicator of sustained demand for Grade A office space and long-term market confidence.</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2277,14 +2263,14 @@
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE11" s="2" t="n">
-        <v>46126.67430555556</v>
+        <v>46127.57430555556</v>
       </c>
       <c r="AF11" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
@@ -2298,7 +2284,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Emirates NBD and Sobha Realty have partnered to provide integrated home financing solutions for off-plan projects in Dubai.</t>
+          <t>This is another strong indicator of sustained demand for Grade A office space and long-term market confidence. • Al Habtoor Group is committing over AED 5 billion to a new commercial tower in Dubai.</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -2321,47 +2307,43 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2044022292972482932</t>
+          <t>2044283005183857003</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://x.com/OneVilleNews/status/2044022292972482932</t>
+          <t>https://x.com/Eisa_Shj/status/2044283005183857003</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://x.com/OneVilleNews</t>
+          <t>https://x.com/Eisa_Shj</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>OneVilleNews</t>
+          <t>Eisa_Shj</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>One Ville News</t>
+          <t>عـيـســى الأمـيــري</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1662461555869470723/h7J9k2pB_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2042552022017413120/xLRIeU1C_bigger.jpg</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>“Ya Biladi”… A Song That Feels Like Home, Bringing the UAE’s Spirit to Life 
-#YaBiladi #UAE #Dubai #Song #HussainAlJassmi @7sainaljassmi #محمد_بن_زايد #الامارات_العربية_المتحدة 
-https://t.co/TqZCzfMs1b via @onevillenews https://t.co/lrW3u4M1bq</t>
+          <t>ماعرف ليش اغلب الناس لين الحين تفتح عندهم و هم من اكثر البنوك في تعقيد الامور الحمدالله على نعمه ENBD الصراحة🦦</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Emirates NBD and Sobha Realty partner to offer integrated home financing solutions for off-plan projects in Dubai 
-&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBD"&gt;#EmiratesNBD&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SobhaRealty"&gt;#SobhaRealty&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Dubai"&gt;#Dubai&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23UAE"&gt;#UAE&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Business"&gt;#Business&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Partnership"&gt;#Partnership&lt;/a&gt; &lt;a href="/SobhaRealtyDXB" title="Sobha Realty"&gt;@SobhaRealtyDXB&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23OneVilleNews"&gt;#OneVilleNews&lt;/a&gt;
-&lt;a href="https://onevillenews.com/2026/04/14/emirates-nbd-and-sobha-realty-partner-to-offer-integrated-home-financing-solutions-for-off-plan-projects-in-dubai/"&gt;onevillenews.com/2026/04/14/…&lt;/a&gt; via &lt;a href="/OneVilleNews" title="One Ville News"&gt;@onevillenews&lt;/a&gt;</t>
+          <t>ماعرف ليش اغلب الناس لين الحين تفتح عندهم و هم من اكثر البنوك في تعقيد الامور الحمدالله على نعمه ENBD الصراحة🦦</t>
         </is>
       </c>
       <c r="K12" t="b">
@@ -2371,23 +2353,19 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 11:57 AM UTC</t>
+          <t>Apr 15, 2026 · 5:13 AM UTC</t>
         </is>
       </c>
       <c r="P12" s="2" t="n">
-        <v>46126.49791666667</v>
+        <v>46127.21736111111</v>
       </c>
       <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EmiratesNBD', 'https://x.com/search?f=tweets&amp;q=%23SobhaRealty', 'https://x.com/search?f=tweets&amp;q=%23Dubai', 'https://x.com/search?f=tweets&amp;q=%23UAE', 'https://x.com/search?f=tweets&amp;q=%23Business', 'https://x.com/search?f=tweets&amp;q=%23Partnership', 'https://x.com/SobhaRealtyDXB', 'https://x.com/search?f=tweets&amp;q=%23OneVilleNews', 'https://onevillenews.com/2026/04/14/emirates-nbd-and-sobha-realty-partner-to-offer-integrated-home-financing-solutions-for-off-plan-projects-in-dubai/', 'https://x.com/OneVilleNews']</t>
-        </is>
-      </c>
+      <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
         <v>0</v>
       </c>
@@ -2398,7 +2376,7 @@
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -2407,33 +2385,27 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Emirates NBD and Sobha Realty partner to offer integrated home financing solutions for off-plan projects in Dubai 
-#EmiratesNBD #SobhaRealty #Dubai #UAE #Business #Partnership @SobhaRealtyDXB #OneVilleNews
-onevillenews.com/2026/04/14/… via @onevillenews</t>
+          <t>ماعرف ليش اغلب الناس لين الحين تفتح عندهم و هم من اكثر البنوك في تعقيد الامور الحمدالله على نعمه ENBD الصراحة🦦</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>https://x.com/OneVilleNews/status/2044022292972482932</t>
+          <t>https://x.com/Eisa_Shj/status/2044283005183857003</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>“Ya Biladi”… A Song That Feels Like Home, Bringing the UAE’s Spirit to Life 
-#YaBiladi #UAE #Dubai #Song #HussainAlJassmi @7sainaljassmi #محمد_بن_زايد #الامارات_العربية_المتحدة 
-https://t.co/TqZCzfMs1b via @onevillenews https://t.co/lrW3u4M1bq</t>
+          <t>ماعرف ليش اغلب الناس لين الحين تفتح عندهم و هم من اكثر البنوك في تعقيد الامور الحمدالله على نعمه ENBD الصراحة🦦</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>“Ya Biladi”… A Song That Feels Like Home, Bringing the UAE’s Spirit to Life 
-#YaBiladi #UAE #Dubai #Song #HussainAlJassmi @7sainaljassmi #محمد_بن_زايد #الامارات_العربية_المتحدة 
-https://t.co/TqZCzfMs1b via @onevillenews https://t.co/lrW3u4M1bq</t>
+          <t>ماعرف ليش اغلب الناس لين الحين تفتح عندهم و هم من اكثر البنوك في تعقيد الامور الحمدالله على نعمه ENBD الصراحة🦦</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>"Ya Biladi"... A Song That Feels Like Home, Bringing the UAE’s Spirit to Life</t>
+          <t>I don't know why most people still open accounts with them when they are one of the most complicated banks. Thank God for the blessing of ENBD, honestly.</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2443,14 +2415,14 @@
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE12" s="2" t="n">
-        <v>46126.66458333333</v>
+        <v>46127.38402777778</v>
       </c>
       <c r="AF12" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
@@ -2464,7 +2436,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>A Song That Feels Like Home, Bringing the UAE’s Spirit to Life</t>
+          <t>I don't know why most people still open accounts with them when they are one of the most complicated banks. • Thank God for the blessing of ENBD, honestly.</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2487,69 +2459,69 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2044003893114232972</t>
+          <t>2044447495619547616</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://x.com/nabilal_rawi/status/2044003893114232972</t>
+          <t>https://x.com/gold_hadas/status/2044447495619547616</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://x.com/nabilal_rawi</t>
+          <t>https://x.com/gold_hadas</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>nabilal_rawi</t>
+          <t>gold_hadas</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nabil Smarter</t>
+          <t>Nicholas MOLODYKO, writer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1920220852898967552/0V_1IXmc_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2026237940993552385/baDKDoMV_bigger.jpg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>While regional tensions are driving higher volatility and risk premiums, the #banking sector in the GCC remains fundamentally sound, with Saudi and UAE institutions still offering upside even under adverse scenarios, according to CI Capital https://t.co/BjQ424Gns3</t>
+          <t>Emirates Islamic launches AED1m campaign for SME customers  https://t.co/7gX7HHRcOh</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Emirates NBD and ADCB demonstrate the UAE&amp;#39;s institutional strength. Free zones and global market access create a financial anchor for entrepreneurs navigating regional volatility.</t>
+          <t>Emirates Islamic launches AED1m campaign for SME customers  &lt;a href="https://www.arabianbusiness.com/finance/emirates-islamic-launches-aed1m-campaign-for-sme-customers"&gt;arabianbusiness.com/finance/…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K13" t="b">
         <v>0</v>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>['Zawya']</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 10:44 AM UTC</t>
+          <t>Apr 15, 2026 · 4:07 PM UTC</t>
         </is>
       </c>
       <c r="P13" s="2" t="n">
-        <v>46126.44722222222</v>
+        <v>46127.67152777778</v>
       </c>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>['https://www.arabianbusiness.com/finance/emirates-islamic-launches-aed1m-campaign-for-sme-customers']</t>
+        </is>
+      </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
@@ -2560,36 +2532,36 @@
         <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Emirates NBD and ADCB demonstrate the UAE's institutional strength. Free zones and global market access create a financial anchor for entrepreneurs navigating regional volatility.</t>
+          <t>Emirates Islamic launches AED1m campaign for SME customers  arabianbusiness.com/finance/…</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>https://x.com/nabilal_rawi/status/2044003893114232972</t>
+          <t>https://x.com/gold_hadas/status/2044447495619547616</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>While regional tensions are driving higher volatility and risk premiums, the #banking sector in the GCC remains fundamentally sound, with Saudi and UAE institutions still offering upside even under adverse scenarios, according to CI Capital https://t.co/BjQ424Gns3</t>
+          <t>Emirates Islamic launches AED1m campaign for SME customers  https://t.co/7gX7HHRcOh</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>While regional tensions are driving higher volatility and risk premiums, the #banking sector in the GCC remains fundamentally sound, with Saudi and UAE institutions still offering upside even under adverse scenarios, according to CI Capital https://t.co/BjQ424Gns3</t>
+          <t>Emirates Islamic launches AED1m campaign for SME customers  https://t.co/7gX7HHRcOh</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>While regional tensions are driving higher volatility and risk premiums, the banking sector in the GCC remains fundamentally sound, with Saudi and UAE institutions still offering upside even under adverse scenarios, according to CI Capital.</t>
+          <t>Emirates Islamic launches a AED1 million campaign for SME customers.</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2599,33 +2571,33 @@
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE13" s="2" t="n">
-        <v>46126.61388888889</v>
+        <v>46127.83819444444</v>
       </c>
       <c r="AF13" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
+          <t>2. Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>While regional tensions are driving higher volatility and risk premiums, the banking sector in the GCC remains fundament…</t>
+          <t>Emirates Islamic launches a AED1 million campaign for SME customers.</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank (ENBD)</t>
+          <t>Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AK13" t="n">
@@ -2633,7 +2605,7 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>Zawya</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2643,47 +2615,47 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2043984421192077650</t>
+          <t>2044341445717610661</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals/status/2043984421192077650</t>
+          <t>https://x.com/EntAlArabiya/status/2044341445717610661</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals</t>
+          <t>https://x.com/EntAlArabiya</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ENBDdeals</t>
+          <t>EntAlArabiya</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Emirates NBD Deals</t>
+          <t>Entrepreneur العربية</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1763624422294814720/EmRI1Aqu_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1514308412343033862/Cl9tt_tx_bigger.jpg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Travel more, earn more miles ✈️
-Earn bonus Skywards Miles on Emirates Holidays bookings when you pay with your Emirates NBD card. Offer valid until 30 April 2026. T&amp;amp;Cs apply.
-https://t.co/HWEZythYdM https://t.co/z5yAeQRQdC</t>
+          <t>الإمارات الإسلامي @emiratesislamic  يعزز قطاع الأعمال بحملة للشركات الصغيرة
+#الإمارات #دبي #بنوك #شركات #مشاريع_صغيرة #تمويل #اقتصاد #استثمار #نمو #entalarabiya
+https://t.co/XNTvseOsQ0</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Travel more, earn more miles ✈️
-Earn bonus Skywards Miles on Emirates Holidays bookings when you pay with your Emirates NBD card. Offer valid until 30 April 2026. T&amp;amp;Cs apply.
-&lt;a href="https://www.emiratesnbd.com/en/promotions/emirates-holidays-skywards-bonus-miles"&gt;emiratesnbd.com/en/promotion…&lt;/a&gt;</t>
+          <t>الإمارات الإسلامي &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt;  يعزز قطاع الأعمال بحملة للشركات الصغيرة
+&lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات"&gt;#الإمارات&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23دبي"&gt;#دبي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23بنوك"&gt;#بنوك&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23شركات"&gt;#شركات&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23مشاريع_صغيرة"&gt;#مشاريع_صغيرة&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23تمويل"&gt;#تمويل&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23اقتصاد"&gt;#اقتصاد&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23استثمار"&gt;#استثمار&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23نمو"&gt;#نمو&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23entalarabiya"&gt;#entalarabiya&lt;/a&gt;
+&lt;a href="https://entrepreneuralarabiya.com/2026/04/15/77826/%d8%a7%d9%84%d8%a5%d9%85%d8%a7%d8%b1%d8%a7%d8%aa-%d8%a7%d9%84%d8%a5%d8%b3%d9%84%d8%a7%d9%85%d9%8a-%d9%8a%d8%af%d8%b9%d9%85-%d8%a7%d9%84%d8%b4%d8%b1%d9%83%d8%a7%d8%aa-%d8%a7%d9%84%d8%b5%d8%ba%d9%8a/"&gt;entrepreneuralarabiya.com/20…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K14" t="b">
@@ -2693,74 +2665,74 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 9:27 AM UTC</t>
+          <t>Apr 15, 2026 · 9:05 AM UTC</t>
         </is>
       </c>
       <c r="P14" s="2" t="n">
-        <v>46126.39375</v>
+        <v>46127.37847222222</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
-          <t>['https://www.emiratesnbd.com/en/promotions/emirates-holidays-skywards-bonus-miles']</t>
+          <t>['https://x.com/emiratesislamic', 'https://x.com/search?f=tweets&amp;q=%23الإمارات', 'https://x.com/search?f=tweets&amp;q=%23دبي', 'https://x.com/search?f=tweets&amp;q=%23بنوك', 'https://x.com/search?f=tweets&amp;q=%23شركات', 'https://x.com/search?f=tweets&amp;q=%23مشاريع_صغيرة', 'https://x.com/search?f=tweets&amp;q=%23تمويل', 'https://x.com/search?f=tweets&amp;q=%23اقتصاد', 'https://x.com/search?f=tweets&amp;q=%23استثمار', 'https://x.com/search?f=tweets&amp;q=%23نمو', 'https://x.com/search?f=tweets&amp;q=%23entalarabiya', 'https://entrepreneuralarabiya.com/2026/04/15/77826/%d8%a7%d9%84%d8%a5%d9%85%d8%a7%d8%b1%d8%a7%d8%aa-%d8%a7%d9%84%d8%a5%d8%b3%d9%84%d8%a7%d9%85%d9%8a-%d9%8a%d8%af%d8%b9%d9%85-%d8%a7%d9%84%d8%b4%d8%b1%d9%83%d8%a7%d8%aa-%d8%a7%d9%84%d8%b5%d8%ba%d9%8a/']</t>
         </is>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V14" t="n">
-        <v>149</v>
+        <v>80</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Travel more, earn more miles ✈️
-Earn bonus Skywards Miles on Emirates Holidays bookings when you pay with your Emirates NBD card. Offer valid until 30 April 2026. T&amp;Cs apply.
-emiratesnbd.com/en/promotion…</t>
+          <t>الإمارات الإسلامي @emiratesislamic  يعزز قطاع الأعمال بحملة للشركات الصغيرة
+#الإمارات #دبي #بنوك #شركات #مشاريع_صغيرة #تمويل #اقتصاد #استثمار #نمو #entalarabiya
+entrepreneuralarabiya.com/20…</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals/status/2043984421192077650</t>
+          <t>https://x.com/EntAlArabiya/status/2044341445717610661</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>Travel more, earn more miles ✈️
-Earn bonus Skywards Miles on Emirates Holidays bookings when you pay with your Emirates NBD card. Offer valid until 30 April 2026. T&amp;amp;Cs apply.
-https://t.co/HWEZythYdM https://t.co/z5yAeQRQdC</t>
+          <t>الإمارات الإسلامي @emiratesislamic  يعزز قطاع الأعمال بحملة للشركات الصغيرة
+#الإمارات #دبي #بنوك #شركات #مشاريع_صغيرة #تمويل #اقتصاد #استثمار #نمو #entalarabiya
+https://t.co/XNTvseOsQ0</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Travel more, earn more miles ✈️
-Earn bonus Skywards Miles on Emirates Holidays bookings when you pay with your Emirates NBD card. Offer valid until 30 April 2026. T&amp;amp;Cs apply.
-https://t.co/HWEZythYdM https://t.co/z5yAeQRQdC</t>
+          <t>الإمارات الإسلامي @emiratesislamic  يعزز قطاع الأعمال بحملة للشركات الصغيرة
+#الإمارات #دبي #بنوك #شركات #مشاريع_صغيرة #تمويل #اقتصاد #استثمار #نمو #entalarabiya
+https://t.co/XNTvseOsQ0</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Travel more, earn more miles ✈️ Earn bonus Skywards Miles on Emirates Holidays bookings when you pay with your Emirates NBD card. Offer valid until 30 April 2026. Terms and conditions apply.</t>
+          <t>Emirates Islamic @emiratesislamic strengthens the business sector with a campaign for small companies.</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Cust</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -2769,29 +2741,29 @@
         </is>
       </c>
       <c r="AE14" s="2" t="n">
-        <v>46126.56041666667</v>
+        <v>46127.54513888889</v>
       </c>
       <c r="AF14" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
+          <t>2. Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Travel more, earn more miles ✈️ Earn bonus Skywards Miles on Emirates Holidays bookings when you pay with your Emirates NBD card. • Offer valid until 30 April 2026. • Terms and conditions apply.</t>
+          <t>Emirates Islamic @emiratesislamic strengthens the business sector with a campaign for small companies.</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank (ENBD)</t>
+          <t>Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AK14" t="n">
@@ -2809,75 +2781,69 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2043855961165623417</t>
+          <t>2044340590037655768</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://x.com/FirasAlin3va/status/2043855961165623417</t>
+          <t>https://x.com/dcgguide/status/2044340590037655768</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://x.com/FirasAlin3va</t>
+          <t>https://x.com/dcgguide</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>FirasAlin3va</t>
+          <t>dcgguide</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>فراس علي</t>
+          <t>DUBAI CITY GUIDE from Cyber Gear</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2036473244753207299/AACRtj0p_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1780203891230945280/ODQLZiT__bigger.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>ليلة استثنائية حلق فيها صقر الغناء في #موسم_جدة 🦅
-والجمهور ولعها حماس من أول لحظة لآخرها 🔥
-#رابح_صقر
-#روتانا_لايف
-@RabehSaqer 
-@JEDCalendar 
-@EmiratesNBD_KSA https://t.co/2PHoXVNSf7</t>
+          <t>Emirates Islamic Drives SME Growth And Engagement Through AED 1 Million Business Banking Campaign https://t.co/lYSRNGGq3N</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>أداء ساحر لطيور الغناء في موسم جدة!</t>
+          <t>Emirates Islamic Drives SME Growth And Engagement Through AED 1 Million Business Banking Campaign &lt;a href="https://blog.dubaicityguide.com/site/emirates-islamic-drives-sme-growth-and-engagement-through-aed-1-million-business-banking-campaign/"&gt;blog.dubaicityguide.com/site…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K15" t="b">
         <v>0</v>
       </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>['RotanaLive', 'RabehSaqer', 'JEDCalendar', 'EmiratesNBD_KSA']</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Apr 14</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 12:56 AM UTC</t>
+          <t>Apr 15, 2026 · 9:02 AM UTC</t>
         </is>
       </c>
       <c r="P15" s="2" t="n">
-        <v>46126.03888888889</v>
+        <v>46127.37638888889</v>
       </c>
       <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>['https://blog.dubaicityguide.com/site/emirates-islamic-drives-sme-growth-and-engagement-through-aed-1-million-business-banking-campaign/']</t>
+        </is>
+      </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
@@ -2885,51 +2851,39 @@
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>أداء ساحر لطيور الغناء في موسم جدة!</t>
+          <t>Emirates Islamic Drives SME Growth And Engagement Through AED 1 Million Business Banking Campaign blog.dubaicityguide.com/site…</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>https://x.com/FirasAlin3va/status/2043855961165623417</t>
+          <t>https://x.com/dcgguide/status/2044340590037655768</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>ليلة استثنائية حلق فيها صقر الغناء في #موسم_جدة 🦅
-والجمهور ولعها حماس من أول لحظة لآخرها 🔥
-#رابح_صقر
-#روتانا_لايف
-@RabehSaqer 
-@JEDCalendar 
-@EmiratesNBD_KSA https://t.co/2PHoXVNSf7</t>
+          <t>Emirates Islamic Drives SME Growth And Engagement Through AED 1 Million Business Banking Campaign https://t.co/lYSRNGGq3N</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>ليلة استثنائية حلق فيها صقر الغناء في #موسم_جدة 🦅
-والجمهور ولعها حماس من أول لحظة لآخرها 🔥
-#رابح_صقر
-#روتانا_لايف
-@RabehSaqer 
-@JEDCalendar 
-@EmiratesNBD_KSA https://t.co/2PHoXVNSf7</t>
+          <t>Emirates Islamic Drives SME Growth And Engagement Through AED 1 Million Business Banking Campaign https://t.co/lYSRNGGq3N</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>An exceptional night where the singing falcon soared in #Jeddah_Season 🦅 and the audience was excited from the very first moment to the last 🔥</t>
+          <t>Emirates Islamic Drives SME Growth And Engagement Through AED 1 Million Business Banking Campaign</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2939,33 +2893,33 @@
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE15" s="2" t="n">
-        <v>46126.20555555556</v>
+        <v>46127.54305555556</v>
       </c>
       <c r="AF15" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
+          <t>2. Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>An exceptional night where the singing falcon soared in #Jeddah_Season 🦅 and the audience was excited from the very first moment to the last 🔥</t>
+          <t>Emirates Islamic Drives SME Growth And Engagement Through AED 1 Million Business Banking Campaign</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank (ENBD)</t>
+          <t>Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AK15" t="n">
@@ -2973,7 +2927,7 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>RotanaLive, RabehSaqer, JEDCalendar, EmiratesNBD_KSA</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2983,45 +2937,49 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2044143965486948528</t>
+          <t>2044312732879728677</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://x.com/GidwaniHero/status/2044143965486948528</t>
+          <t>https://x.com/EntMagazineME/status/2044312732879728677</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://x.com/GidwaniHero</t>
+          <t>https://x.com/EntMagazineME</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>GidwaniHero</t>
+          <t>EntMagazineME</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hero Gidwani</t>
+          <t>Entrepreneur Middle East</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1924556859526283267/UcvezR38_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1514494189895049219/SrZOixX4_bigger.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>@HHShkMohd @ENBDdeals @FABConnects @MashreqTweets @emiratesislamic 
-Dear uae government what is daily lime to deposit in machine if I have 100k to deposit and machine is slow and behind me standing In Q Are arguing what to do who deposit black money no one question them why</t>
+          <t>@emiratesislamic has announced the launch of a new Business Banking campaign aimed at supporting 3SME customers and strengthening #business resilience across the #UAE.
+Running until June 30, 2026, the campaign allows businesses to participate by increasing and maintaining their average balances in their Business Banking Accounts.
+The initiative offers a total prize pool of AED1 million and will reward 55 winners over three months, providing multiple opportunities for customers to win cash prizes while encouraging sustainable growth.
+🔗Read more HERE: https://t.co/j0Wq0RjPdm</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>&lt;a href="/HHShkMohd" title="HH Sheikh Mohammed"&gt;@HHShkMohd&lt;/a&gt; &lt;a href="/ENBDdeals" title="Emirates NBD Deals"&gt;@ENBDdeals&lt;/a&gt; &lt;a href="/FABConnects" title="FAB Connects"&gt;@FABConnects&lt;/a&gt; &lt;a href="/MashreqTweets" title="Mashreq"&gt;@MashreqTweets&lt;/a&gt; &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; 
-Dear uae government what is daily lime to deposit in machine if I have 100k to deposit and machine is slow and behind me standing In Q Are arguing what to do who deposit black money no one question them why</t>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; has announced the launch of a new Business Banking campaign aimed at supporting 3SME customers and strengthening &lt;a href="/search?f=tweets&amp;amp;q=%23business"&gt;#business&lt;/a&gt; resilience across the &lt;a href="/search?f=tweets&amp;amp;q=%23UAE"&gt;#UAE&lt;/a&gt;.
+Running until June 30, 2026, the campaign allows businesses to participate by increasing and maintaining their average balances in their Business Banking Accounts.
+The initiative offers a total prize pool of AED1 million and will reward 55 winners over three months, providing multiple opportunities for customers to win cash prizes while encouraging sustainable growth.
+🔗Read more HERE: &lt;a href="https://mena.entrepreneur.com/business-news/emirates-islamic-launches-business-banking-campaign-with-aed1-million-prize-pool-to-support-uae-smes"&gt;mena.entrepreneur.com/busine…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K16" t="b">
@@ -3031,34 +2989,34 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>6h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 8:01 PM UTC</t>
+          <t>Apr 15, 2026 · 7:11 AM UTC</t>
         </is>
       </c>
       <c r="P16" s="2" t="n">
-        <v>46126.83402777778</v>
+        <v>46127.29930555556</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
-          <t>['https://x.com/HHShkMohd', 'https://x.com/ENBDdeals', 'https://x.com/FABConnects', 'https://x.com/MashreqTweets', 'https://x.com/emiratesislamic']</t>
+          <t>['https://x.com/emiratesislamic', 'https://x.com/search?f=tweets&amp;q=%23business', 'https://x.com/search?f=tweets&amp;q=%23UAE', 'https://mena.entrepreneur.com/business-news/emirates-islamic-launches-business-banking-campaign-with-aed1-million-prize-pool-to-support-uae-smes']</t>
         </is>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V16" t="n">
-        <v>3</v>
+        <v>105</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -3067,30 +3025,39 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>@HHShkMohd @ENBDdeals @FABConnects @MashreqTweets @emiratesislamic 
-Dear uae government what is daily lime to deposit in machine if I have 100k to deposit and machine is slow and behind me standing In Q Are arguing what to do who deposit black money no one question them why</t>
+          <t>@emiratesislamic has announced the launch of a new Business Banking campaign aimed at supporting 3SME customers and strengthening #business resilience across the #UAE.
+Running until June 30, 2026, the campaign allows businesses to participate by increasing and maintaining their average balances in their Business Banking Accounts.
+The initiative offers a total prize pool of AED1 million and will reward 55 winners over three months, providing multiple opportunities for customers to win cash prizes while encouraging sustainable growth.
+🔗Read more HERE: mena.entrepreneur.com/busine…</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>https://x.com/GidwaniHero/status/2044143965486948528</t>
+          <t>https://x.com/EntMagazineME/status/2044312732879728677</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>@HHShkMohd @ENBDdeals @FABConnects @MashreqTweets @emiratesislamic 
-Dear uae government what is daily lime to deposit in machine if I have 100k to deposit and machine is slow and behind me standing In Q Are arguing what to do who deposit black money no one question them why</t>
+          <t>@emiratesislamic has announced the launch of a new Business Banking campaign aimed at supporting 3SME customers and strengthening #business resilience across the #UAE.
+Running until June 30, 2026, the campaign allows businesses to participate by increasing and maintaining their average balances in their Business Banking Accounts.
+The initiative offers a total prize pool of AED1 million and will reward 55 winners over three months, providing multiple opportunities for customers to win cash prizes while encouraging sustainable growth.
+🔗Read more HERE: https://t.co/j0Wq0RjPdm</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>@HHShkMohd @ENBDdeals @FABConnects @MashreqTweets @emiratesislamic 
-Dear uae government what is daily lime to deposit in machine if I have 100k to deposit and machine is slow and behind me standing In Q Are arguing what to do who deposit black money no one question them why</t>
+          <t>@emiratesislamic has announced the launch of a new Business Banking campaign aimed at supporting 3SME customers and strengthening #business resilience across the #UAE.
+Running until June 30, 2026, the campaign allows businesses to participate by increasing and maintaining their average balances in their Business Banking Accounts.
+The initiative offers a total prize pool of AED1 million and will reward 55 winners over three months, providing multiple opportunities for customers to win cash prizes while encouraging sustainable growth.
+🔗Read more HERE: https://t.co/j0Wq0RjPdm</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Dear UAE government, what is the daily limit to deposit in the machine if I have 100k to deposit and the machine is slow? There are people behind me in line arguing about what to do, while no one questions those depositing black money. Why is that?</t>
+          <t>@emiratesislamic has announced the launch of a new Business Banking campaign aimed at supporting SME customers and strengthening business resilience across the UAE. 
+Running until June 30, 2026, the campaign allows businesses to participate by increasing and maintaining their average balances in their Business Banking Accounts. 
+The initiative offers a total prize pool of AED 1 million and will reward 55 winners over three months, providing multiple opportunities for customers to win cash prizes while encouraging sustainable growth. 
+Read more HERE: https://t.co/j0Wq0RjPdm</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -3100,11 +3067,11 @@
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE16" s="2" t="n">
-        <v>46127.00069444445</v>
+        <v>46127.46597222222</v>
       </c>
       <c r="AF16" s="2" t="n">
         <v>46127</v>
@@ -3121,7 +3088,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Dear UAE government, what is the daily limit to deposit in the machine if I have 100k to deposit and the machine is slow? • There are people behind me in line arguing about what to do, while no one questions those depositing black money.</t>
+          <t>Running until June 30, 2026, the campaign allows businesses to participate by increasing and maintaining their average balances in their Business Banking Accounts. • @emiratesislamic has announced the launch of a new Business Banking campaign aimed at supporting SME customers and strengthening business resilience across the UAE. • Read more HERE: https://t.co/j0Wq0RjPdm</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -3144,12 +3111,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2043932263390310621</t>
+          <t>2044294659795513346</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043932263390310621</t>
+          <t>https://x.com/emiratesislamic/status/2044294659795513346</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3175,16 +3142,18 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>How do you usually pay for your expenses?
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
-https://t.co/XvyZgR87nM</t>
+          <t>من “يوماً ما” إلى يوم الانتقال!
+التمويل السكني من الإمارات الإسلامي يجعل حلم امتلاك منزلك حقيقة، مع المرونة والوضوح في كل خطوة من رحلتك.
+استمتع بحلول تمويلية مصممة خصيصاً لك، ودعم متكامل طوال الطريق، لتصبح تجربة امتلاك المنزل سلسة وميسرة.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>How do you usually pay for your expenses?
-&lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialWellbeing"&gt;#EIFinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
+          <t>From “one day” to move-in day.
+Emirates Islamic Home Finance helps turn home ownership into reality, with the flexibility and clarity you need at every step.
+With tailored finance solutions and guided support throughout,
+Your home journey starts here.
+&lt;a href="https://www.emiratesislamic.ae/en/Personal-Banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=home_finance"&gt;emiratesislamic.ae/en/Person…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K17" t="b">
@@ -3194,21 +3163,21 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 6:00 AM UTC</t>
+          <t>Apr 15, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P17" s="2" t="n">
-        <v>46126.25</v>
+        <v>46127.25</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EIFinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+          <t>['https://www.emiratesislamic.ae/en/Personal-Banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=home_finance']</t>
         </is>
       </c>
       <c r="S17" t="n">
@@ -3221,7 +3190,7 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>49</v>
+        <v>119</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
@@ -3230,33 +3199,37 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>How do you usually pay for your expenses?
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
-emiratesislamic.ae/en/key-in…</t>
+          <t>From “one day” to move-in day.
+Emirates Islamic Home Finance helps turn home ownership into reality, with the flexibility and clarity you need at every step.
+With tailored finance solutions and guided support throughout,
+Your home journey starts here.
+emiratesislamic.ae/en/Person…</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043932263390310621</t>
+          <t>https://x.com/emiratesislamic/status/2044294659795513346</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>How do you usually pay for your expenses?
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
-https://t.co/XvyZgR87nM</t>
+          <t>من “يوماً ما” إلى يوم الانتقال!
+التمويل السكني من الإمارات الإسلامي يجعل حلم امتلاك منزلك حقيقة، مع المرونة والوضوح في كل خطوة من رحلتك.
+استمتع بحلول تمويلية مصممة خصيصاً لك، ودعم متكامل طوال الطريق، لتصبح تجربة امتلاك المنزل سلسة وميسرة.</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>How do you usually pay for your expenses?
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
-https://t.co/XvyZgR87nM</t>
+          <t>من “يوماً ما” إلى يوم الانتقال!
+التمويل السكني من الإمارات الإسلامي يجعل حلم امتلاك منزلك حقيقة، مع المرونة والوضوح في كل خطوة من رحلتك.
+استمتع بحلول تمويلية مصممة خصيصاً لك، ودعم متكامل طوال الطريق، لتصبح تجربة امتلاك المنزل سلسة وميسرة.</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>How do you usually pay for your expenses?</t>
+          <t>From "one day" to the day of moving in! 
+Emirates Islamic home financing makes your dream of owning a home a reality, with flexibility and clarity at every step of your journey. 
+Enjoy financing solutions tailored just for you, with comprehensive support along the way, making the homeownership experience smooth and accessible.</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -3266,14 +3239,14 @@
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE17" s="2" t="n">
-        <v>46126.41666666666</v>
+        <v>46127.41666666666</v>
       </c>
       <c r="AF17" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
@@ -3287,7 +3260,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>How do you usually pay for your expenses?</t>
+          <t>Emirates Islamic home financing makes your dream of owning a home a reality, with flexibility and clarity at every step of your journey. • Enjoy financing solutions tailored just for you, with comprehensive support along the way, making the homeownership experience smooth and accessible. • From "one day" to the day of moving in!</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -3310,12 +3283,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2043917165502316982</t>
+          <t>2044471342880170391</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043917165502316982</t>
+          <t>https://x.com/emiratesislamic/status/2044471342880170391</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3341,18 +3314,18 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>نظرتك الأسبوعية… لحياة أكثر وعياً واتزاناً مالياً.
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-Your Weekly Perspective. A step toward a more mindful financial week.
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic https://t.co/48pYcSntb5</t>
+          <t>احصل على فرصة الفوز بحصة من الجوائز النقدية قيمتها تصل إلى 1,000,000 درهم. كل زيادة بقيمة 100,000 درهم في حسابك المصرفي للأعمال تمنحك فرصة واحدة للدخول في السحب.
+اجعل شركتك إحدى الشركات الـ 55 الفائزة. فهل ستكون من بينها؟ https://t.co/zGFXn2y3iT</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>نظرتك الأسبوعية… لحياة أكثر وعياً واتزاناً مالياً.
-&lt;a href="/search?f=tweets&amp;amp;q=%23نظرتك_المالية"&gt;#نظرتك_المالية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التثقيف_المالي"&gt;#التثقيف_المالي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;
-Your Weekly Perspective. A step toward a more mindful financial week.
-&lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialWellbeing"&gt;#EIFinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;</t>
+          <t>الجائزة النقدية الكبرى: 250,000 درهم (فائز واحد) 
+الجائزة النقدية الثانية: 100,000 درهم (فائزان اثنان)
+الجوائز النقدية الشهرية: تصل إلى 25 ألف درهم (52 فائز)
+يسري العرض لغاية 30 يونيو 2026.
+تطبق الشروط والأحكام.
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/exclusive-business-banking-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=bb_offer"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K18" t="b">
@@ -3362,21 +3335,21 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 5:00 AM UTC</t>
+          <t>Apr 15, 2026 · 5:42 PM UTC</t>
         </is>
       </c>
       <c r="P18" s="2" t="n">
-        <v>46126.20833333334</v>
+        <v>46127.7375</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23نظرتك_المالية', 'https://x.com/search?f=tweets&amp;q=%23التثقيف_المالي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://x.com/search?f=tweets&amp;q=%23EIFinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic']</t>
+          <t>['https://www.emiratesislamic.ae/ar/offers/exclusive-business-banking-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=bb_offer']</t>
         </is>
       </c>
       <c r="S18" t="n">
@@ -3389,7 +3362,7 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>56</v>
+        <v>147</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -3398,36 +3371,35 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>نظرتك الأسبوعية… لحياة أكثر وعياً واتزاناً مالياً.
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-Your Weekly Perspective. A step toward a more mindful financial week.
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic</t>
+          <t>الجائزة النقدية الكبرى: 250,000 درهم (فائز واحد) 
+الجائزة النقدية الثانية: 100,000 درهم (فائزان اثنان)
+الجوائز النقدية الشهرية: تصل إلى 25 ألف درهم (52 فائز)
+يسري العرض لغاية 30 يونيو 2026.
+تطبق الشروط والأحكام.
+emiratesislamic.ae/ar/offers…</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043917165502316982</t>
+          <t>https://x.com/emiratesislamic/status/2044471342880170391</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>نظرتك الأسبوعية… لحياة أكثر وعياً واتزاناً مالياً.
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-Your Weekly Perspective. A step toward a more mindful financial week.
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic https://t.co/48pYcSntb5</t>
+          <t>احصل على فرصة الفوز بحصة من الجوائز النقدية قيمتها تصل إلى 1,000,000 درهم. كل زيادة بقيمة 100,000 درهم في حسابك المصرفي للأعمال تمنحك فرصة واحدة للدخول في السحب.
+اجعل شركتك إحدى الشركات الـ 55 الفائزة. فهل ستكون من بينها؟ https://t.co/zGFXn2y3iT</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>نظرتك الأسبوعية… لحياة أكثر وعياً واتزاناً مالياً.
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-Your Weekly Perspective. A step toward a more mindful financial week.
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic https://t.co/48pYcSntb5</t>
+          <t>احصل على فرصة الفوز بحصة من الجوائز النقدية قيمتها تصل إلى 1,000,000 درهم. كل زيادة بقيمة 100,000 درهم في حسابك المصرفي للأعمال تمنحك فرصة واحدة للدخول في السحب.
+اجعل شركتك إحدى الشركات الـ 55 الفائزة. فهل ستكون من بينها؟ https://t.co/zGFXn2y3iT</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Your weekly perspective… for a more conscious and financially balanced life.</t>
+          <t>Get a chance to win a share of cash prizes worth up to 1,000,000 dirhams. Every increase of 100,000 dirhams in your business bank account gives you one entry into the draw.
+Make your company one of the 55 winning companies. Will you be among them?</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -3437,14 +3409,14 @@
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE18" s="2" t="n">
-        <v>46126.375</v>
+        <v>46127.90416666667</v>
       </c>
       <c r="AF18" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
@@ -3458,7 +3430,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Your weekly perspective… for a more conscious and financially balanced life.</t>
+          <t>Get a chance to win a share of cash prizes worth up to 1,000,000 dirhams. • Every increase of 100,000 dirhams in your business bank account gives you one entry into the draw. • Make your company one of the 55 winning companies.</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -3481,12 +3453,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2044023053797953761</t>
+          <t>2044471339784810653</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044023053797953761</t>
+          <t>https://x.com/emiratesislamic/status/2044471339784810653</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3512,49 +3484,48 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Dear Zahara,we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
+          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
+⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.
+⭐️Shariah-compliant offering https://t.co/lsN56x6Joc</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Dear Zahara,we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
+          <t>احصل على فرصة الفوز بحصة من الجوائز النقدية قيمتها تصل إلى 1,000,000 درهم. كل زيادة بقيمة 100,000 درهم في حسابك المصرفي للأعمال تمنحك فرصة واحدة للدخول في السحب.
+اجعل شركتك إحدى الشركات الـ 55 الفائزة. فهل ستكون من بينها؟</t>
         </is>
       </c>
       <c r="K19" t="b">
         <v>0</v>
       </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>['ZaharaMMalik']</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 12:00 PM UTC</t>
+          <t>Apr 15, 2026 · 5:42 PM UTC</t>
         </is>
       </c>
       <c r="P19" s="2" t="n">
-        <v>46126.5</v>
+        <v>46127.7375</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" t="n">
-        <v>65</v>
+        <v>147</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -3563,36 +3534,51 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Dear Zahara,we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
+          <t>احصل على فرصة الفوز بحصة من الجوائز النقدية قيمتها تصل إلى 1,000,000 درهم. كل زيادة بقيمة 100,000 درهم في حسابك المصرفي للأعمال تمنحك فرصة واحدة للدخول في السحب.
+اجعل شركتك إحدى الشركات الـ 55 الفائزة. فهل ستكون من بينها؟</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044471339784810653</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
+⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.
+⭐️Shariah-compliant offering https://t.co/lsN56x6Joc</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Dear Zahara,we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
+          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
+⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.
+⭐️Shariah-compliant offering https://t.co/lsN56x6Joc</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Dear Zahara, we have tried to reach you through direct message, but unfortunately, we were not successful because you are not following our page. Please DM us back so we can assist you better.</t>
+          <t>Invest in gold and silver easily and digitally with the EI + Mobile Banking App
+⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.
+⭐️Shariah-compliant offering</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Cust</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE19" s="2" t="n">
-        <v>46126.66666666666</v>
+        <v>46127.90416666667</v>
       </c>
       <c r="AF19" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
@@ -3606,7 +3592,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Dear Zahara, we have tried to reach you through direct message, but unfortunately, we were not successful because you are not following our page. • Please DM us back so we can assist you better.</t>
+          <t>Invest in gold and silver easily and digitally with the EI + Mobile Banking App ⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly. • ⭐️Shariah-compliant offering</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -3619,7 +3605,7 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>ZaharaMMalik</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3629,12 +3615,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2043955058459467807</t>
+          <t>2044471329382900119</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043955058459467807</t>
+          <t>https://x.com/emiratesislamic/status/2044471329382900119</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3660,38 +3646,44 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better.</t>
+          <t>Get a chance to win a total of AED 1,000,000 in cash prizes! Every AED 100,000 increase in your Business Banking account earns you one entry into the draw.
+55 businesses will be winners. Will you be one of them?
+Grand cash prize: AED 250,000 (1 winner) https://t.co/PtTMEJsQ5k</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better.</t>
+          <t>Second cash prize: AED 100,000 each (2 winners)
+Monthly cash prizes: up to AED 25,000 (52 winners)
+Valid until 30 June 2026.
+Terms and conditions apply.
+&lt;a href="https://www.emiratesislamic.ae/en/offers/exclusive-business-banking-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=bb_offer"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K20" t="b">
         <v>0</v>
       </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>['aswanikumartst5']</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 7:30 AM UTC</t>
+          <t>Apr 15, 2026 · 5:42 PM UTC</t>
         </is>
       </c>
       <c r="P20" s="2" t="n">
-        <v>46126.3125</v>
+        <v>46127.7375</v>
       </c>
       <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/offers/exclusive-business-banking-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=bb_offer']</t>
+        </is>
+      </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
@@ -3702,7 +3694,7 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>6</v>
+        <v>73</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
@@ -3711,36 +3703,54 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better.</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
+          <t>Second cash prize: AED 100,000 each (2 winners)
+Monthly cash prizes: up to AED 25,000 (52 winners)
+Valid until 30 June 2026.
+Terms and conditions apply.
+emiratesislamic.ae/en/offers…</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044471329382900119</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>Get a chance to win a total of AED 1,000,000 in cash prizes! Every AED 100,000 increase in your Business Banking account earns you one entry into the draw.
+55 businesses will be winners. Will you be one of them?
+Grand cash prize: AED 250,000 (1 winner) https://t.co/PtTMEJsQ5k</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better.</t>
+          <t>Get a chance to win a total of AED 1,000,000 in cash prizes! Every AED 100,000 increase in your Business Banking account earns you one entry into the draw.
+55 businesses will be winners. Will you be one of them?
+Grand cash prize: AED 250,000 (1 winner) https://t.co/PtTMEJsQ5k</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you through private messaging to serve you better.</t>
+          <t>Get a chance to win a total of AED 1,000,000 in cash prizes! Every AED 100,000 increase in your Business Banking account earns you one entry into the draw. 
+55 businesses will be winners. Will you be one of them? 
+Grand cash prize: AED 250,000 (1 winner)</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Cust</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE20" s="2" t="n">
-        <v>46126.47916666666</v>
+        <v>46127.90416666667</v>
       </c>
       <c r="AF20" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
@@ -3754,7 +3764,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you through private messaging to serve you better.</t>
+          <t>Get a chance to win a total of AED 1,000,000 in cash prizes! • Every AED 100,000 increase in your Business Banking account earns you one entry into the draw. • Grand cash prize: AED 250,000 (1 winner)</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3767,7 +3777,7 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>aswanikumartst5</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3777,12 +3787,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2043932266456367150</t>
+          <t>2044471327159996698</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043932266456367150</t>
+          <t>https://x.com/emiratesislamic/status/2044471327159996698</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3808,14 +3818,16 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>To know more:
-https://t.co/XvyZgR87nM</t>
+          <t>Get a chance to win a total of AED 1,000,000 in cash prizes! Every AED 100,000 increase in your Business Banking account earns you one entry into the draw.
+55 businesses will be winners. Will you be one of them?
+Grand cash prize: AED 250,000 (1 winner)</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>To know more:
-&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
+          <t>Get a chance to win a total of AED 1,000,000 in cash prizes! Every AED 100,000 increase in your Business Banking account earns you one entry into the draw.
+55 businesses will be winners. Will you be one of them?
+Grand cash prize: AED 250,000 (1 winner)</t>
         </is>
       </c>
       <c r="K21" t="b">
@@ -3825,25 +3837,21 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 6:00 AM UTC</t>
+          <t>Apr 15, 2026 · 5:42 PM UTC</t>
         </is>
       </c>
       <c r="P21" s="2" t="n">
-        <v>46126.25</v>
+        <v>46127.7375</v>
       </c>
       <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
-        </is>
-      </c>
+      <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
@@ -3852,7 +3860,7 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
@@ -3861,30 +3869,25 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>To know more:
-emiratesislamic.ae/en/key-in…</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932266456367150</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>To know more:
-https://t.co/XvyZgR87nM</t>
-        </is>
-      </c>
+          <t>Get a chance to win a total of AED 1,000,000 in cash prizes! Every AED 100,000 increase in your Business Banking account earns you one entry into the draw.
+55 businesses will be winners. Will you be one of them?
+Grand cash prize: AED 250,000 (1 winner)</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>To know more:
-https://t.co/XvyZgR87nM</t>
+          <t>Get a chance to win a total of AED 1,000,000 in cash prizes! Every AED 100,000 increase in your Business Banking account earns you one entry into the draw.
+55 businesses will be winners. Will you be one of them?
+Grand cash prize: AED 250,000 (1 winner)</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>To know more: https://t.co/XvyZgR87nM</t>
+          <t>Get a chance to win a total of AED 1,000,000 in cash prizes! Every AED 100,000 increase in your Business Banking account earns you one entry into the draw. 
+55 businesses will be winners. Will you be one of them? 
+Grand cash prize: AED 250,000 (1 winner)</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3894,14 +3897,14 @@
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE21" s="2" t="n">
-        <v>46126.41666666666</v>
+        <v>46127.90416666667</v>
       </c>
       <c r="AF21" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
@@ -3915,7 +3918,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>To know more: https://t.co/XvyZgR87nM</t>
+          <t>Get a chance to win a total of AED 1,000,000 in cash prizes! • Every AED 100,000 increase in your Business Banking account earns you one entry into the draw. • Grand cash prize: AED 250,000 (1 winner)</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -3938,12 +3941,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2043932263725854816</t>
+          <t>2044322414310367621</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043932263725854816</t>
+          <t>https://x.com/emiratesislamic/status/2044322414310367621</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3969,16 +3972,18 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Money grows best when given time, balance, and the right mix.
-Spreading investments and thinking long term can help create steadier progress along the way.
-Small steps today can support stronger outcomes tomorrow.</t>
+          <t>⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
+⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
+Terms and conditions apply.
+https://t.co/w5RtLlrqm8</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Money grows best when given time, balance, and the right mix.
-Spreading investments and thinking long term can help create steadier progress along the way.
-Small steps today can support stronger outcomes tomorrow.</t>
+          <t>⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
+⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
+Terms and conditions apply.
+&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=psb_wealth"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K22" t="b">
@@ -3993,16 +3998,20 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 6:00 AM UTC</t>
+          <t>Apr 15, 2026 · 7:50 AM UTC</t>
         </is>
       </c>
       <c r="P22" s="2" t="n">
-        <v>46126.25</v>
+        <v>46127.32638888889</v>
       </c>
       <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=psb_wealth']</t>
+        </is>
+      </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -4011,7 +4020,7 @@
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>85</v>
+        <v>142</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -4020,23 +4029,36 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Money grows best when given time, balance, and the right mix.
-Spreading investments and thinking long term can help create steadier progress along the way.
-Small steps today can support stronger outcomes tomorrow.</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
+          <t>⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
+⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
+Terms and conditions apply.
+emiratesislamic.ae/en/person…</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044322414310367621</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
+⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
+Terms and conditions apply.
+https://t.co/w5RtLlrqm8</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>Money grows best when given time, balance, and the right mix.
-Spreading investments and thinking long term can help create steadier progress along the way.
-Small steps today can support stronger outcomes tomorrow.</t>
+          <t>⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
+⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
+Terms and conditions apply.
+https://t.co/w5RtLlrqm8</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>Money grows best when given time, balance, and the right mix. Spreading investments and thinking long term can help create steadier progress along the way. Small steps today can support stronger outcomes tomorrow.</t>
+          <t>Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards Certified silver bars compliant with UAE Good Delivery (UAE GD) standards Terms and conditions apply.</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -4050,10 +4072,10 @@
         </is>
       </c>
       <c r="AE22" s="2" t="n">
-        <v>46126.41666666666</v>
+        <v>46127.49305555555</v>
       </c>
       <c r="AF22" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
@@ -4067,7 +4089,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Spreading investments and thinking long term can help create steadier progress along the way. • Money grows best when given time, balance, and the right mix. • Small steps today can support stronger outcomes tomorrow.</t>
+          <t>Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards Certified s…</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
@@ -4090,12 +4112,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2043932263449006494</t>
+          <t>2044322412007735394</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043932263449006494</t>
+          <t>https://x.com/emiratesislamic/status/2044322412007735394</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4121,16 +4143,16 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>كيف تدفع نفقاتك عادةً؟
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-emiratesislamic.ae/ar/key-in…</t>
+          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
+⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.
+⭐️Shariah-compliant offering</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>كيف تدفع نفقاتك عادةً؟
-&lt;a href="/search?f=tweets&amp;amp;q=%23نظرتك_المالية"&gt;#نظرتك_المالية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التثقيف_المالي"&gt;#التثقيف_المالي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/ar/key-in…&lt;/a&gt;</t>
+          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
+⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.
+⭐️Shariah-compliant offering</t>
         </is>
       </c>
       <c r="K23" t="b">
@@ -4145,29 +4167,25 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 6:00 AM UTC</t>
+          <t>Apr 15, 2026 · 7:50 AM UTC</t>
         </is>
       </c>
       <c r="P23" s="2" t="n">
-        <v>46126.25</v>
+        <v>46127.32638888889</v>
       </c>
       <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23نظرتك_المالية', 'https://x.com/search?f=tweets&amp;q=%23التثقيف_المالي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
-        </is>
-      </c>
+      <c r="R23" t="inlineStr"/>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" t="n">
-        <v>73</v>
+        <v>204</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -4176,23 +4194,25 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>كيف تدفع نفقاتك عادةً؟
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-emiratesislamic.ae/ar/key-in…</t>
+          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
+⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.
+⭐️Shariah-compliant offering</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>كيف تدفع نفقاتك عادةً؟
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-emiratesislamic.ae/ar/key-in…</t>
+          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
+⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.
+⭐️Shariah-compliant offering</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>How do you usually pay your expenses?</t>
+          <t>Invest in gold and silver easily and digitally with the EI + Mobile Banking App. 
+Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly. 
+Shariah-compliant offering.</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -4202,14 +4222,14 @@
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE23" s="2" t="n">
-        <v>46126.41666666666</v>
+        <v>46127.49305555555</v>
       </c>
       <c r="AF23" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
@@ -4223,7 +4243,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>How do you usually pay your expenses?</t>
+          <t>Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly. • Invest in gold and silver easily and digitally with the EI + Mobile Banking App. • Shariah-compliant offering.</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -4246,12 +4266,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2043932263386157239</t>
+          <t>2044322403761697193</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043932263386157239</t>
+          <t>https://x.com/emiratesislamic/status/2044322403761697193</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4277,18 +4297,18 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>كيف تدفع نفقاتك عادةً؟
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-https://t.co/mgtIcQsyLZ</t>
+          <t>⭐️سبائك ذهب معتمدة ومطابقة لمعايير جمعية سوق لندن للسبائك ودبي للتسليم الجيد
+⭐️سبائك فضة معتمدة ومتوافقة مع معايير الإمارات للتسليم الجيد
+تطبق الشروط والأحكام.
+emiratesislamic.ae/ar/person…</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>ينمو المال بشكل أفضل مع الوقت، والتوازن، والتنوّع المناسب.
-تنويع الاستثمارات والتفكير على المدى الطويل يساعدان على تحقيق استقرار أكبر.
-خطوات صغيرة اليوم قد تصنع نتائج أقوى في المستقبل.
-للمزيد: 
-&lt;a href="https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/ar/key-in…&lt;/a&gt;</t>
+          <t>⭐️سبائك ذهب معتمدة ومطابقة لمعايير جمعية سوق لندن للسبائك ودبي للتسليم الجيد
+⭐️سبائك فضة معتمدة ومتوافقة مع معايير الإمارات للتسليم الجيد
+تطبق الشروط والأحكام.
+&lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organiic-twitter&amp;amp;utm_medium=socal&amp;amp;utm_campaign=psb_wealth"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K24" t="b">
@@ -4303,16 +4323,16 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 6:00 AM UTC</t>
+          <t>Apr 15, 2026 · 7:50 AM UTC</t>
         </is>
       </c>
       <c r="P24" s="2" t="n">
-        <v>46126.25</v>
+        <v>46127.32638888889</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+          <t>['https://www.emiratesislamic.ae/ar/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organiic-twitter&amp;utm_medium=socal&amp;utm_campaign=psb_wealth']</t>
         </is>
       </c>
       <c r="S24" t="n">
@@ -4325,7 +4345,7 @@
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>52</v>
+        <v>115</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
@@ -4334,35 +4354,27 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>ينمو المال بشكل أفضل مع الوقت، والتوازن، والتنوّع المناسب.
-تنويع الاستثمارات والتفكير على المدى الطويل يساعدان على تحقيق استقرار أكبر.
-خطوات صغيرة اليوم قد تصنع نتائج أقوى في المستقبل.
-للمزيد: 
-emiratesislamic.ae/ar/key-in…</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932263386157239</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>كيف تدفع نفقاتك عادةً؟
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-https://t.co/mgtIcQsyLZ</t>
-        </is>
-      </c>
+          <t>⭐️سبائك ذهب معتمدة ومطابقة لمعايير جمعية سوق لندن للسبائك ودبي للتسليم الجيد
+⭐️سبائك فضة معتمدة ومتوافقة مع معايير الإمارات للتسليم الجيد
+تطبق الشروط والأحكام.
+emiratesislamic.ae/ar/person…</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>كيف تدفع نفقاتك عادةً؟
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-https://t.co/mgtIcQsyLZ</t>
+          <t>⭐️سبائك ذهب معتمدة ومطابقة لمعايير جمعية سوق لندن للسبائك ودبي للتسليم الجيد
+⭐️سبائك فضة معتمدة ومتوافقة مع معايير الإمارات للتسليم الجيد
+تطبق الشروط والأحكام.
+emiratesislamic.ae/ar/person…</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>How do you usually pay your expenses?</t>
+          <t>Certified gold bars that meet the standards of the London Bullion Market Association and Dubai Good Delivery.
+Certified silver bars that comply with the UAE Good Delivery standards.
+Terms and conditions apply.</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -4376,10 +4388,10 @@
         </is>
       </c>
       <c r="AE24" s="2" t="n">
-        <v>46126.41666666666</v>
+        <v>46127.49305555555</v>
       </c>
       <c r="AF24" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
@@ -4393,7 +4405,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>How do you usually pay your expenses?</t>
+          <t>Certified gold bars that meet the standards of the London Bullion Market Association and Dubai Good Delivery. • Certified silver bars that comply with the UAE Good Delivery standards. • Terms and conditions apply.</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -4416,43 +4428,49 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2044011613422834071</t>
+          <t>2044322401052250291</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://x.com/ZaharaMMalik/status/2044011613422834071</t>
+          <t>https://x.com/emiratesislamic/status/2044322401052250291</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://x.com/ZaharaMMalik</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ZaharaMMalik</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Zahara Sadiq</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1123139785072304129/0KaXZD52_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Really struggling to get hold of @emiratesislamic I’ve called the international line and emailed and really need to get hold of someone. Please help 😭</t>
+          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
+EI + للخدمات المصرفية عبر الهاتف المتحرك
+⭐️ادخل إلى منصة "الثروات" في تطبيق + EI  للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان.
+⭐️منتج متوافق مع أحكام الشريعة الإسلامية https://t.co/CZe51naJfQ</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Really struggling to get hold of &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; I’ve called the international line and emailed and really need to get hold of someone. Please help 😭</t>
+          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
+EI + للخدمات المصرفية عبر الهاتف المتحرك
+⭐️ادخل إلى منصة &amp;#34;الثروات&amp;#34; في تطبيق + EI  للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان.
+⭐️منتج متوافق مع أحكام الشريعة الإسلامية</t>
         </is>
       </c>
       <c r="K25" t="b">
@@ -4462,23 +4480,19 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 11:15 AM UTC</t>
+          <t>Apr 15, 2026 · 7:50 AM UTC</t>
         </is>
       </c>
       <c r="P25" s="2" t="n">
-        <v>46126.46875</v>
+        <v>46127.32638888889</v>
       </c>
       <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>['https://x.com/emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="R25" t="inlineStr"/>
       <c r="S25" t="n">
         <v>1</v>
       </c>
@@ -4489,7 +4503,7 @@
         <v>1</v>
       </c>
       <c r="V25" t="n">
-        <v>93</v>
+        <v>201</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -4498,44 +4512,55 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Really struggling to get hold of @emiratesislamic I’ve called the international line and emailed and really need to get hold of someone. Please help 😭</t>
+          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
+EI + للخدمات المصرفية عبر الهاتف المتحرك
+⭐️ادخل إلى منصة "الثروات" في تطبيق + EI  للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان.
+⭐️منتج متوافق مع أحكام الشريعة الإسلامية</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>https://x.com/ZaharaMMalik/status/2044011613422834071</t>
+          <t>https://x.com/emiratesislamic/status/2044322401052250291</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>Really struggling to get hold of @emiratesislamic I’ve called the international line and emailed and really need to get hold of someone. Please help 😭</t>
+          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
+EI + للخدمات المصرفية عبر الهاتف المتحرك
+⭐️ادخل إلى منصة "الثروات" في تطبيق + EI  للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان.
+⭐️منتج متوافق مع أحكام الشريعة الإسلامية https://t.co/CZe51naJfQ</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>Really struggling to get hold of @emiratesislamic I’ve called the international line and emailed and really need to get hold of someone. Please help 😭</t>
+          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
+EI + للخدمات المصرفية عبر الهاتف المتحرك
+⭐️ادخل إلى منصة "الثروات" في تطبيق + EI  للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان.
+⭐️منتج متوافق مع أحكام الشريعة الإسلامية https://t.co/CZe51naJfQ</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Really struggling to get in touch with @emiratesislamic. I've called the international line and emailed, and I really need to reach someone. Please help.</t>
+          <t>Invest in gold and silver digitally and easily on the EI+ mobile banking app.
+⭐️Access the "Wealth" platform in the EI+ mobile banking app and start investing with utmost ease and security. 
+⭐️Product compliant with Islamic law.</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Cust</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE25" s="2" t="n">
-        <v>46126.63541666666</v>
+        <v>46127.49305555555</v>
       </c>
       <c r="AF25" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
@@ -4549,7 +4574,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>I've called the international line and emailed, and I really need to reach someone. • Really struggling to get in touch with @emiratesislamic.</t>
+          <t>⭐️Access the "Wealth" platform in the EI+ mobile banking app and start investing with utmost ease and security. • Invest in gold and silver digitally and easily on the EI+ mobile banking app. • ⭐️Product compliant with Islamic law.</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
@@ -4572,69 +4597,71 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2043951228640747823</t>
+          <t>2044294656716836969</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://x.com/aswanikumartst5/status/2043951228640747823</t>
+          <t>https://x.com/emiratesislamic/status/2044294656716836969</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://x.com/aswanikumartst5</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>aswanikumartst5</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>TS Aswani Kumar</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1412710891515092994/OVnKv5t7_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>@emiratesislamic I have already cleared a personal loan and approached your Phone Banking &amp;amp; WhatsApp channel for issue of NIL LIABILITY LETTER..but no concrete response .Not feasible to obtain through your application as well.Can u please check&amp;amp; revert ASAP. Thank You.</t>
+          <t>ابدأ رحلتك نحو منزل أحلامك اليوم.
+emiratesislamic.ae/ar/Person…</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>How many days more you require to issue a NIL LIABILITY LETTER...?</t>
+          <t>ابدأ رحلتك نحو منزل أحلامك اليوم.
+&lt;a href="https://www.emiratesislamic.ae/ar/Personal-Banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=home_finance"&gt;emiratesislamic.ae/ar/Person…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K26" t="b">
         <v>0</v>
       </c>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>['emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 7:15 AM UTC</t>
+          <t>Apr 15, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P26" s="2" t="n">
-        <v>46126.30208333334</v>
+        <v>46127.25</v>
       </c>
       <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/Personal-Banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=home_finance']</t>
+        </is>
+      </c>
       <c r="S26" t="n">
         <v>1</v>
       </c>
@@ -4645,7 +4672,7 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>5</v>
+        <v>127</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
@@ -4654,44 +4681,38 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>How many days more you require to issue a NIL LIABILITY LETTER...?</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>https://x.com/aswanikumartst5/status/2043951228640747823</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>@emiratesislamic I have already cleared a personal loan and approached your Phone Banking &amp;amp; WhatsApp channel for issue of NIL LIABILITY LETTER..but no concrete response .Not feasible to obtain through your application as well.Can u please check&amp;amp; revert ASAP. Thank You.</t>
-        </is>
-      </c>
+          <t>ابدأ رحلتك نحو منزل أحلامك اليوم.
+emiratesislamic.ae/ar/Person…</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>@emiratesislamic I have already cleared a personal loan and approached your Phone Banking &amp;amp; WhatsApp channel for issue of NIL LIABILITY LETTER..but no concrete response .Not feasible to obtain through your application as well.Can u please check&amp;amp; revert ASAP. Thank You.</t>
+          <t>ابدأ رحلتك نحو منزل أحلامك اليوم.
+emiratesislamic.ae/ar/Person…</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>I have already cleared a personal loan and approached your Phone Banking and WhatsApp channel for the issuance of a NIL LIABILITY LETTER, but I have not received a concrete response. It is also not feasible to obtain it through your application. Can you please check and respond as soon as possible? Thank you.</t>
+          <t>Start your journey towards your dream home today.</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Cust</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE26" s="2" t="n">
-        <v>46126.46875</v>
+        <v>46127.41666666666</v>
       </c>
       <c r="AF26" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
@@ -4705,7 +4726,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>I have already cleared a personal loan and approached your Phone Banking and WhatsApp channel for the issuance of a NIL LIABILITY LETTER, but I have not received a concrete response. • Can you please check and respond as soon as possible? • It is also not feasible to obtain it through your application.</t>
+          <t>Start your journey towards your dream home today.</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -4718,7 +4739,7 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -4728,68 +4749,66 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2044076340891009154</t>
+          <t>2044294653097156714</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044076340891009154</t>
+          <t>https://x.com/emiratesislamic/status/2044294653097156714</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>attas_2010</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>محمد</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1581396792075247620/ZCrbkCda_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>موظف البنك الفرنسي قال نعطيك اعادة تمويل ويطلع لك فائض بالشخصي٧٥٠٠٠ وفعلا تحولت لي والعقاري قال يفيض لك٢٥٥٠٠٠ وسحب علي وماعاد يرد وحتى اليوم فوق ١٠ مرات احاول ارفع شكوى من التطبيق مايقبلون الشكوى 
-اصلا</t>
+          <t>من “يوماً ما” إلى يوم الانتقال!
+التمويل السكني من الإمارات الإسلامي يجعل حلم امتلاك منزلك حقيقة، مع المرونة والوضوح في كل خطوة من رحلتك.
+استمتع بحلول تمويلية مصممة خصيصاً لك، ودعم متكامل طوال الطريق، لتصبح تجربة امتلاك المنزل سلسة وميسرة.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>موظف البنك الفرنسي قال نعطيك اعادة تمويل ويطلع لك فائض بالشخصي٧٥٠٠٠ وفعلا تحولت لي والعقاري قال يفيض لك٢٥٥٠٠٠ وسحب علي وماعاد يرد وحتى اليوم فوق ١٠ مرات احاول ارفع شكوى من التطبيق مايقبلون الشكوى 
-اصلا</t>
+          <t>من “يوماً ما” إلى يوم الانتقال!
+التمويل السكني من الإمارات الإسلامي يجعل حلم امتلاك منزلك حقيقة، مع المرونة والوضوح في كل خطوة من رحلتك.
+استمتع بحلول تمويلية مصممة خصيصاً لك، ودعم متكامل طوال الطريق، لتصبح تجربة امتلاك المنزل سلسة وميسرة.</t>
         </is>
       </c>
       <c r="K27" t="b">
         <v>0</v>
       </c>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>['attas_2010', 'KhalidSaeedR', 'amsh75', 'alrajhibank', 'BSF_sa', 'alinma', 'BankAlbilad', 'snbalahli', 'GulfIntlBank', 'EmiratesNBD_AE', 'BankAlJazira', 'RiyadBank', 'alawwalsab', 'SAIBLIVE']</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 3:32 PM UTC</t>
+          <t>Apr 15, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P27" s="2" t="n">
-        <v>46126.64722222222</v>
+        <v>46127.25</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
@@ -4803,66 +4822,70 @@
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>76</v>
+        <v>194</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>موظف البنك الفرنسي قال نعطيك اعادة تمويل ويطلع لك فائض بالشخصي٧٥٠٠٠ وفعلا تحولت لي والعقاري قال يفيض لك٢٥٥٠٠٠ وسحب علي وماعاد يرد وحتى اليوم فوق ١٠ مرات احاول ارفع شكوى من التطبيق مايقبلون الشكوى 
-اصلا</t>
+          <t>من “يوماً ما” إلى يوم الانتقال!
+التمويل السكني من الإمارات الإسلامي يجعل حلم امتلاك منزلك حقيقة، مع المرونة والوضوح في كل خطوة من رحلتك.
+استمتع بحلول تمويلية مصممة خصيصاً لك، ودعم متكامل طوال الطريق، لتصبح تجربة امتلاك المنزل سلسة وميسرة.</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>موظف البنك الفرنسي قال نعطيك اعادة تمويل ويطلع لك فائض بالشخصي٧٥٠٠٠ وفعلا تحولت لي والعقاري قال يفيض لك٢٥٥٠٠٠ وسحب علي وماعاد يرد وحتى اليوم فوق ١٠ مرات احاول ارفع شكوى من التطبيق مايقبلون الشكوى 
-اصلا</t>
+          <t>من “يوماً ما” إلى يوم الانتقال!
+التمويل السكني من الإمارات الإسلامي يجعل حلم امتلاك منزلك حقيقة، مع المرونة والوضوح في كل خطوة من رحلتك.
+استمتع بحلول تمويلية مصممة خصيصاً لك، ودعم متكامل طوال الطريق، لتصبح تجربة امتلاك المنزل سلسة وميسرة.</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>The French bank employee said they would give you refinancing and you would have a surplus of 75,000 in personal loans, and indeed it was transferred to me, and the real estate loan said it would give you a surplus of 255,000. They stopped responding to me, and even today I have tried to file a complaint through the app more than 10 times, but they do not accept the complaint at all.</t>
+          <t>From "one day" to the day of moving in! 
+Emirates Islamic home financing makes your dream of owning a home a reality, with flexibility and clarity at every step of your journey. 
+Enjoy financing solutions tailored just for you, with comprehensive support along the way, making the homeownership experience smooth and accessible.</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Cust</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE27" s="2" t="n">
-        <v>46126.81388888889</v>
+        <v>46127.41666666666</v>
       </c>
       <c r="AF27" s="2" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
+          <t>2. Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>They stopped responding to me, and even today I have tried to file a complaint through the app more than 10 times, but they do not accept the complaint at all.</t>
+          <t>Emirates Islamic home financing makes your dream of owning a home a reality, with flexibility and clarity at every step of your journey. • Enjoy financing solutions tailored just for you, with comprehensive support along the way, making the homeownership experience smooth and accessible. • From "one day" to the day of moving in!</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank (ENBD)</t>
+          <t>Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AK27" t="n">
@@ -4870,7 +4893,672 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>attas_2010, KhalidSaeedR, amsh75, alrajhibank, BSF_sa, alinma, BankAlbilad, snbalahli, GulfIntlBank, EmiratesNBD_AE, BankAlJazira, RiyadBank, alawwalsab, SAIBLIVE</t>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2044356621351149946</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://x.com/HarshGada76429/status/2044356621351149946</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://x.com/HarshGada76429</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>HarshGada76429</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Harsh Gada</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>@RBLBankCares
+@rblbank
+I have been a loyal customer for last 3yrs using your world safari credit card I have achieved the milestone but missed the redemption date by 7 days 
+Request you to send me new redemption link for 10000rs voucher or I will have to end the relationship now</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>I haven&amp;#39;t got the resolution yet 
+On technical terms you are denying me the voucher
+What about last 3 years of harassment where you guys were denying for voucher which i have earned by reaching milestone?
+&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;   be careful with tie up with
+RBL Bank</t>
+        </is>
+      </c>
+      <c r="K28" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>['HarshGada76429', 'RBLBankCares', 'rblbank']</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Apr 15, 2026 · 10:06 AM UTC</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="n">
+        <v>46127.42083333333</v>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="S28" t="n">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>8</v>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>I haven't got the resolution yet 
+On technical terms you are denying me the voucher
+What about last 3 years of harassment where you guys were denying for voucher which i have earned by reaching milestone?
+@EmiratesNBD_AE   be careful with tie up with
+RBL Bank</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>https://x.com/HarshGada76429/status/2044356621351149946</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>@RBLBankCares
+@rblbank
+I have been a loyal customer for last 3yrs using your world safari credit card I have achieved the milestone but missed the redemption date by 7 days 
+Request you to send me new redemption link for 10000rs voucher or I will have to end the relationship now</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>@RBLBankCares
+@rblbank
+I have been a loyal customer for last 3yrs using your world safari credit card I have achieved the milestone but missed the redemption date by 7 days 
+Request you to send me new redemption link for 10000rs voucher or I will have to end the relationship now</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>I have been a loyal customer for the last 3 years using your World Safari credit card. I have achieved the milestone but missed the redemption date by 7 days. I request you to send me a new redemption link for a 10,000 INR voucher, or I will have to end the relationship now.</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AE28" s="2" t="n">
+        <v>46127.5875</v>
+      </c>
+      <c r="AF28" s="2" t="n">
+        <v>46127</v>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>I request you to send me a new redemption link for a 10,000 INR voucher, or I will have to end the relationship now. • I have been a loyal customer for the last 3 years using your World Safari credit card. • I have achieved the milestone but missed the redemption date by 7 days.</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK28" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>HarshGada76429, RBLBankCares, rblbank</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2044369434362753181</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://x.com/iRonyForChange/status/2044369434362753181</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://x.com/iRonyForChange</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>iRonyForChange</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Preetam Chakraborty</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2032194835424423936/eNr4L0LS_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE 
+You kept pushing to take the Share Credit Card,finally I applied and then you rejected citing “internal policies” despite having higher eligibility than required.
+Now your agents are calling and saying it’s a miss &amp;amp; to resubmit documents.
+Are you serious?</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; 
+You kept pushing to take the Share Credit Card,finally I applied and then you rejected citing “internal policies” despite having higher eligibility than required.
+Now your agents are calling and saying it’s a miss &amp;amp; to resubmit documents.
+Are you serious?</t>
+        </is>
+      </c>
+      <c r="K29" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Apr 15, 2026 · 10:57 AM UTC</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="n">
+        <v>46127.45625</v>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="S29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>2</v>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE 
+You kept pushing to take the Share Credit Card,finally I applied and then you rejected citing “internal policies” despite having higher eligibility than required.
+Now your agents are calling and saying it’s a miss &amp; to resubmit documents.
+Are you serious?</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>https://x.com/iRonyForChange/status/2044369434362753181</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE 
+You kept pushing to take the Share Credit Card,finally I applied and then you rejected citing “internal policies” despite having higher eligibility than required.
+Now your agents are calling and saying it’s a miss &amp;amp; to resubmit documents.
+Are you serious?</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE 
+You kept pushing to take the Share Credit Card,finally I applied and then you rejected citing “internal policies” despite having higher eligibility than required.
+Now your agents are calling and saying it’s a miss &amp;amp; to resubmit documents.
+Are you serious?</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>You kept pushing me to take the Share Credit Card, and I finally applied, but you rejected it citing "internal policies" despite my eligibility being higher than required. Now your agents are calling and saying it was a mistake and to resubmit documents. Are you serious?</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AE29" s="2" t="n">
+        <v>46127.62291666667</v>
+      </c>
+      <c r="AF29" s="2" t="n">
+        <v>46127</v>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>You kept pushing me to take the Share Credit Card, and I finally applied, but you rejected it citing "internal policies" despite my eligibility being higher than required. • Now your agents are calling and saying it was a mistake and to resubmit documents.</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK29" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2044307778140025041</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://x.com/metakixakbar/status/2044307778140025041</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://x.com/metakixakbar</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>metakixakbar</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Akbar Syed</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1478686329114267649/s_YERTLm_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>@ENBDdeals
+Took a Takaful policy from ENBD back in 2012. 15 year policy. Was supposed to mature in 2027. Policy was issued from Aman insurances. ENBD was distributor. Being told now to contact Aman insurance directly. Aman is as good as closed. ENBD is not taking responsibility.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>&lt;a href="/ENBDdeals" title="Emirates NBD Deals"&gt;@ENBDdeals&lt;/a&gt;
+Took a Takaful policy from ENBD back in 2012. 15 year policy. Was supposed to mature in 2027. Policy was issued from Aman insurances. ENBD was distributor. Being told now to contact Aman insurance directly. Aman is as good as closed. ENBD is not taking responsibility.</t>
+        </is>
+      </c>
+      <c r="K30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Apr 15, 2026 · 6:52 AM UTC</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="n">
+        <v>46127.28611111111</v>
+      </c>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>['https://x.com/ENBDdeals']</t>
+        </is>
+      </c>
+      <c r="S30" t="n">
+        <v>2</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>10</v>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>@ENBDdeals
+Took a Takaful policy from ENBD back in 2012. 15 year policy. Was supposed to mature in 2027. Policy was issued from Aman insurances. ENBD was distributor. Being told now to contact Aman insurance directly. Aman is as good as closed. ENBD is not taking responsibility.</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>https://x.com/metakixakbar/status/2044307778140025041</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>@ENBDdeals
+Took a Takaful policy from ENBD back in 2012. 15 year policy. Was supposed to mature in 2027. Policy was issued from Aman insurances. ENBD was distributor. Being told now to contact Aman insurance directly. Aman is as good as closed. ENBD is not taking responsibility.</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>@ENBDdeals
+Took a Takaful policy from ENBD back in 2012. 15 year policy. Was supposed to mature in 2027. Policy was issued from Aman insurances. ENBD was distributor. Being told now to contact Aman insurance directly. Aman is as good as closed. ENBD is not taking responsibility.</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>I took a Takaful policy from ENBD back in 2012. It is a 15-year policy that was supposed to mature in 2027. The policy was issued by Aman Insurance, and ENBD was the distributor. I am now being told to contact Aman Insurance directly, but Aman is practically closed. ENBD is not taking responsibility.</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AE30" s="2" t="n">
+        <v>46127.45277777778</v>
+      </c>
+      <c r="AF30" s="2" t="n">
+        <v>46127</v>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>I took a Takaful policy from ENBD back in 2012. • It is a 15-year policy that was supposed to mature in 2027. • I am now being told to contact Aman Insurance directly, but Aman is practically closed.</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK30" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2044301025142513927</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://x.com/oras_2030/status/2044301025142513927</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://x.com/oras_2030</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>oras_2030</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>oras2030</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2043694467731886080/mS-jeUsJ_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA اسوء تجربة من البنك في خدمة العملاء ولا ادارة التحصيل الي اسلوبه زي الزفت تخيلو طلبت خطاب عدم مومانعه  من شراء المديونية لك وشو يسوي البنك يتصل على البنك الثاني ويتاكد متى تتغير النسبه ويتاخر الطلب لي ثلاث ايام وانا اتصل على ادارة التحصيل وخدمه العملاء اخر شي</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>هل تنصح اخ علي@ انقل راتبي عندهم عشان قرض شخصي لان نسبتهم اقل من البنوك الاخرى؟</t>
+        </is>
+      </c>
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>['AliAhmedk66633', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Apr 15, 2026 · 6:25 AM UTC</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="n">
+        <v>46127.26736111111</v>
+      </c>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>20</v>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>هل تنصح اخ علي@ انقل راتبي عندهم عشان قرض شخصي لان نسبتهم اقل من البنوك الاخرى؟</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>https://x.com/oras_2030/status/2044301025142513927</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA اسوء تجربة من البنك في خدمة العملاء ولا ادارة التحصيل الي اسلوبه زي الزفت تخيلو طلبت خطاب عدم مومانعه  من شراء المديونية لك وشو يسوي البنك يتصل على البنك الثاني ويتاكد متى تتغير النسبه ويتاخر الطلب لي ثلاث ايام وانا اتصل على ادارة التحصيل وخدمه العملاء اخر شي</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA اسوء تجربة من البنك في خدمة العملاء ولا ادارة التحصيل الي اسلوبه زي الزفت تخيلو طلبت خطاب عدم مومانعه  من شراء المديونية لك وشو يسوي البنك يتصل على البنك الثاني ويتاكد متى تتغير النسبه ويتاخر الطلب لي ثلاث ايام وانا اتصل على ادارة التحصيل وخدمه العملاء اخر شي</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>The worst experience with the bank in customer service and the collection management is terrible. Imagine I requested a letter of no objection to purchase the debt, and what does the bank do? It calls the other bank to confirm when the rate changes, and the request is delayed for three days while I keep calling the collection management and customer service.</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AE31" s="2" t="n">
+        <v>46127.43402777778</v>
+      </c>
+      <c r="AF31" s="2" t="n">
+        <v>46127</v>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>It calls the other bank to confirm when the rate changes, and the request is delayed for three days while I keep calling the collection management and customer service. • The worst experience with the bank in customer service and the collection management is terrible. • Imagine I requested a letter of no objection to purchase the debt, and what does the bank do?</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK31" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>AliAhmedk66633, EmiratesNBD_KSA</t>
         </is>
       </c>
     </row>

--- a/check2.xlsx
+++ b/check2.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL51"/>
+  <dimension ref="A1:AL52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1082,9 +1082,9 @@
 The rules are simple:
 1. Retweet this tweet.
 2. Comment A LOT with the tags #iFoodNoBBB26 and #BBB26 responding to this tweet.
-The @ with THE MOST COMMENTS on this post is the winner!
+The @ with the MOST COMMENTS on this post is the winner!
 Let's go? It's on! Tomorrow we will have the champion.
-Check the rules in the bio.
+Check the regulations in the bio.
 Valid comments until 04/16/2026 at 6:30 PM.</t>
         </is>
       </c>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>I am new here in Dubai @DubaiPoliceHQ, @DXBMediaOffice. Please inform me if using a VPN to call my home country on WhatsApp due to restrictions is illegal, and if there is a penalty for it, or are there only penalties for using a VPN for illegal activities? Thank you.</t>
+          <t>I am new here in Dubai @DubaiPoliceHQ, @DXBMediaOffice. Please inform me if using a VPN to call my home country on WhatsApp due to restrictions is illegal, and if there is a penalty for it, or if penalties only apply when someone uses a VPN for illegal activities. Thank you.</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>You can own the car of your dreams, whether new or used. We can finance it for you with the car leasing financing from Emirates NBD.</t>
+          <t>You can own the car of your dreams, whether new or used. We can finance it for you with the car leasing financing from Emirates NBD Bank.</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>You can own the car of your dreams, whether new or used. • We can finance it for you with the car leasing financing from Emirates NBD.</t>
+          <t>We can finance it for you with the car leasing financing from Emirates NBD Bank. • You can own the car of your dreams, whether new or used.</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1829,7 +1829,7 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Sometimes, all you need is a quiet escape into a great story. 🎞️🤍 Use your Emirates NBD card at Novo Cinemas to enjoy 15% off tickets any day of the week. A simple way to reward yourself with a moment of peace. Book your tickets now by visiting NovoCinemas.com or the App</t>
+          <t>The kings of comedy and horror are reunited 👻🤣 #AkshayKumar and #Priyadarshan return with #BhootBangla, bringing haunted-palace chaos, laughs and scares with #PareshRawal and #Tabu. Now Showing at Novo Cinemas. Book now at https://t.co/w2yAiSn6ht or the Novo App. https://t.co/vHPASzr5Pa</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1883,16 +1883,24 @@
           <t>Sometimes, all you need is a quiet escape into a great story. 🎞️🤍 Use your Emirates NBD card at Novo Cinemas to enjoy 15% off tickets any day of the week. A simple way to reward yourself with a moment of peace. Book your tickets now by visiting NovoCinemas.com or the App</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>https://x.com/NovoCinemas/status/2044762914725277798</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>The kings of comedy and horror are reunited 👻🤣 #AkshayKumar and #Priyadarshan return with #BhootBangla, bringing haunted-palace chaos, laughs and scares with #PareshRawal and #Tabu. Now Showing at Novo Cinemas. Book now at https://t.co/w2yAiSn6ht or the Novo App. https://t.co/vHPASzr5Pa</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Sometimes, all you need is a quiet escape into a great story. 🎞️🤍 Use your Emirates NBD card at Novo Cinemas to enjoy 15% off tickets any day of the week. A simple way to reward yourself with a moment of peace. Book your tickets now by visiting NovoCinemas.com or the App</t>
+          <t>The kings of comedy and horror are reunited 👻🤣 #AkshayKumar and #Priyadarshan return with #BhootBangla, bringing haunted-palace chaos, laughs and scares with #PareshRawal and #Tabu. Now Showing at Novo Cinemas. Book now at https://t.co/w2yAiSn6ht or the Novo App. https://t.co/vHPASzr5Pa</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Sometimes, all you need is a quiet escape into a great story. Use your Emirates NBD card at Novo Cinemas to enjoy 15% off tickets any day of the week. A simple way to reward yourself with a moment of peace. Book your tickets now by visiting NovoCinemas.com or the App.</t>
+          <t>The kings of comedy and horror are reunited 👻🤣 #AkshayKumar and #Priyadarshan return with #BhootBangla, bringing haunted-palace chaos, laughs, and scares with #PareshRawal and #Tabu. Now showing at Novo Cinemas. Book now at https://t.co/w2yAiSn6ht or the Novo App. https://t.co/vHPASzr5Pa</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1902,7 +1910,7 @@
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE9" s="2" t="n">
@@ -1923,7 +1931,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Use your Emirates NBD card at Novo Cinemas to enjoy 15% off tickets any day of the week. • Book your tickets now by visiting NovoCinemas.com or the App. • Sometimes, all you need is a quiet escape into a great story.</t>
+          <t>The kings of comedy and horror are reunited 👻🤣 #AkshayKumar and #Priyadarshan return with #BhootBangla, bringing haunted-palace chaos, laughs, and scares with #PareshRawal and #Tabu. • Book now at https://t.co/w2yAiSn6ht or the Novo App. • Now showing at Novo Cinemas.</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -2145,7 +2153,7 @@
         <is>
           <t>استثمر في الأسهم و الصكوك و السندات و المعادن الثمينة (الذهب و الفضة)، كل ذلك من خلال تطبيق ENBD X.
 فرص استثمارية لا حصر لها، ابدأ الاستثمار اليوم
-emiratesnbd.com/ar/ways-of-b…</t>
+https://t.co/6sm1UoslrI https://t.co/XdDf9aQ6x7</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -2203,13 +2211,23 @@
 emiratesnbd.com/ar/ways-of-b…</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2044743592040595538</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
         <is>
           <t>استثمر في الأسهم و الصكوك و السندات و المعادن الثمينة (الذهب و الفضة)، كل ذلك من خلال تطبيق ENBD X.
 فرص استثمارية لا حصر لها، ابدأ الاستثمار اليوم
-emiratesnbd.com/ar/ways-of-b…</t>
+https://t.co/6sm1UoslrI https://t.co/XdDf9aQ6x7</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>استثمر في الأسهم و الصكوك و السندات و المعادن الثمينة (الذهب و الفضة)، كل ذلك من خلال تطبيق ENBD X.
+فرص استثمارية لا حصر لها، ابدأ الاستثمار اليوم
+https://t.co/6sm1UoslrI https://t.co/XdDf9aQ6x7</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -3120,11 +3138,11 @@
       <c r="I17" t="inlineStr">
         <is>
           <t>«الإمارات دبي الوطني» ينفذ تسهيلات قرض مشترك بقيمة 250 مليون دولار لصالح «دار جلوبال»
-https://t.co/t5ea8OOIgX | التفاصيل 
+fintechgate.net/8hpf | التفاصيل 
 @EmiratesNBD_AE
 @dar_global
 #fintech_gate
-#الإمارات_دبي_الوطني #دار_جلوبال https://t.co/o7GYOB2HP9</t>
+#الإمارات_دبي_الوطني #دار_جلوبال</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -3188,34 +3206,21 @@
 #الإمارات_دبي_الوطني #دار_جلوبال</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>https://x.com/FintechGate1/status/2044721846457655694</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr">
         <is>
           <t>«الإمارات دبي الوطني» ينفذ تسهيلات قرض مشترك بقيمة 250 مليون دولار لصالح «دار جلوبال»
-https://t.co/t5ea8OOIgX | التفاصيل 
+fintechgate.net/8hpf | التفاصيل 
 @EmiratesNBD_AE
 @dar_global
 #fintech_gate
-#الإمارات_دبي_الوطني #دار_جلوبال https://t.co/o7GYOB2HP9</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>«الإمارات دبي الوطني» ينفذ تسهيلات قرض مشترك بقيمة 250 مليون دولار لصالح «دار جلوبال»
-https://t.co/t5ea8OOIgX | التفاصيل 
-@EmiratesNBD_AE
-@dar_global
-#fintech_gate
-#الإمارات_دبي_الوطني #دار_جلوبال https://t.co/o7GYOB2HP9</t>
+#الإمارات_دبي_الوطني #دار_جلوبال</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Emirates NBD is implementing a syndicated loan facility worth $250 million for Dar Global.</t>
+          <t>Emirates NBD implements a syndicated loan facility worth $250 million for Dar Global.</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -3246,7 +3251,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Emirates NBD is implementing a syndicated loan facility worth $250 million for Dar Global.</t>
+          <t>Emirates NBD implements a syndicated loan facility worth $250 million for Dar Global.</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -3637,8 +3642,7 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>سافر لوجهتك، وقسط دفعاتها مع 0% هامش ربح ✈️
-على طيران الإمارات باستخدام بطاقات #بنك_الإمارات_دبي_الوطني الائتمانية</t>
+          <t>الرسائل الخاصه مقفله لديكم</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3692,26 +3696,16 @@
           <t>الرسائل الخاصه مقفله لديكم</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>https://x.com/msa3474/status/2044694547498696848</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>سافر لوجهتك، وقسط دفعاتها مع 0% هامش ربح ✈️
-على طيران الإمارات باستخدام بطاقات #بنك_الإمارات_دبي_الوطني الائتمانية</t>
-        </is>
-      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>سافر لوجهتك، وقسط دفعاتها مع 0% هامش ربح ✈️
-على طيران الإمارات باستخدام بطاقات #بنك_الإمارات_دبي_الوطني الائتمانية</t>
+          <t>الرسائل الخاصه مقفله لديكم</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Travel to your destination and pay in installments with 0% profit margin ✈️ on Emirates Airlines using #Emirates_NBD credit cards.</t>
+          <t>Private messages are closed for you.</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3721,7 +3715,7 @@
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE20" s="2" t="n">
@@ -3742,7 +3736,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Travel to your destination and pay in installments with 0% profit margin ✈️ on Emirates Airlines using #Emirates_NBD credit cards.</t>
+          <t>Private messages are closed for you.</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3796,7 +3790,8 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA الرجاء إرسال رسالة خاصة لكي ارد عليكم</t>
+          <t>سافر لوجهتك، وقسط دفعاتها مع 0% هامش ربح ✈️
+على طيران الإمارات باستخدام بطاقات #بنك_الإمارات_دبي_الوطني الائتمانية</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3857,17 +3852,19 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA الرجاء إرسال رسالة خاصة لكي ارد عليكم</t>
+          <t>سافر لوجهتك، وقسط دفعاتها مع 0% هامش ربح ✈️
+على طيران الإمارات باستخدام بطاقات #بنك_الإمارات_دبي_الوطني الائتمانية</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA الرجاء إرسال رسالة خاصة لكي ارد عليكم</t>
+          <t>سافر لوجهتك، وقسط دفعاتها مع 0% هامش ربح ✈️
+على طيران الإمارات باستخدام بطاقات #بنك_الإمارات_دبي_الوطني الائتمانية</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA please send a private message so I can respond to you.</t>
+          <t>Travel to your destination and pay in installments with 0% profit margin ✈️ on Emirates Airlines using #Emirates_NBD credit cards.</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3877,7 +3874,7 @@
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE21" s="2" t="n">
@@ -3898,7 +3895,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA please send a private message so I can respond to you.</t>
+          <t>Travel to your destination and pay in installments with 0% profit margin ✈️ on Emirates Airlines using #Emirates_NBD credit cards.</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -3952,7 +3949,7 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Best Foods High in Fiber https://t.co/j3Qv2TBkZl</t>
+          <t>The Golden Elixir https://t.co/LGgbrnkX3c</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -4015,17 +4012,17 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>Best Foods High in Fiber https://t.co/j3Qv2TBkZl</t>
+          <t>The Golden Elixir https://t.co/LGgbrnkX3c</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>Best Foods High in Fiber https://t.co/j3Qv2TBkZl</t>
+          <t>The Golden Elixir https://t.co/LGgbrnkX3c</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>Best Foods High in Fiber</t>
+          <t>The Golden Elixir</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -4056,7 +4053,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Best Foods High in Fiber</t>
+          <t>The Golden Elixir</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
@@ -4862,7 +4859,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>The answer is simple interest.</t>
+          <t>The answer is Simple Interest.</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4893,7 +4890,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>The answer is simple interest.</t>
+          <t>The answer is Simple Interest.</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -5420,6 +5417,71 @@
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
+        <is>
+          <t>Top 5 Companies by Revenue 
+By Revenue (annual)
+1️⃣ Walmart — ~$650B
+2️⃣ Amazon — ~$575B
+3️⃣ Saudi Aramco — ~$500B
+4️⃣ China State Grid — ~$480B
+5️⃣ Apple — ~$390B
+@BehindNums</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Top 5 Richest Companies in the Middle East 
+1️⃣ Saudi Aramco — ~$1.5T+
+2️⃣ International Holding Co (UAE) — ~$240B+
+3️⃣ QNB (Qatar National Bank) — ~$150B+
+4️⃣ Al Rajhi Bank (Saudi) — ~$100B+
+5️⃣ Emirates NBD (UAE) — ~$80B+
+Oil wealth meets financial power.
+&lt;a href="/BehindNums" title="BehindNums | Business &amp;amp; Data"&gt;@BehindNums&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>23h</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Apr 16, 2026 · 2:58 AM UTC</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="n">
+        <v>46128.12361111111</v>
+      </c>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>['https://x.com/BehindNums']</t>
+        </is>
+      </c>
+      <c r="S31" t="n">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>29</v>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
         <is>
           <t>Top 5 Richest Companies in the Middle East 
 1️⃣ Saudi Aramco — ~$1.5T+
@@ -5431,94 +5493,45 @@
 @BehindNums</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Top 5 Richest Companies in the Middle East 
-1️⃣ Saudi Aramco — ~$1.5T+
-2️⃣ International Holding Co (UAE) — ~$240B+
-3️⃣ QNB (Qatar National Bank) — ~$150B+
-4️⃣ Al Rajhi Bank (Saudi) — ~$100B+
-5️⃣ Emirates NBD (UAE) — ~$80B+
-Oil wealth meets financial power.
-&lt;a href="/BehindNums" title="BehindNums | Business &amp;amp; Data"&gt;@BehindNums&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K31" t="b">
-        <v>0</v>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>23h</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>Apr 16, 2026 · 2:58 AM UTC</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="n">
-        <v>46128.12361111111</v>
-      </c>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>['https://x.com/BehindNums']</t>
-        </is>
-      </c>
-      <c r="S31" t="n">
-        <v>1</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>29</v>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>Top 5 Richest Companies in the Middle East 
-1️⃣ Saudi Aramco — ~$1.5T+
-2️⃣ International Holding Co (UAE) — ~$240B+
-3️⃣ QNB (Qatar National Bank) — ~$150B+
-4️⃣ Al Rajhi Bank (Saudi) — ~$100B+
-5️⃣ Emirates NBD (UAE) — ~$80B+
-Oil wealth meets financial power.
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>https://x.com/BehindNums/status/2044611289733878057</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>Top 5 Companies by Revenue 
+By Revenue (annual)
+1️⃣ Walmart — ~$650B
+2️⃣ Amazon — ~$575B
+3️⃣ Saudi Aramco — ~$500B
+4️⃣ China State Grid — ~$480B
+5️⃣ Apple — ~$390B
 @BehindNums</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr"/>
-      <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>Top 5 Richest Companies in the Middle East 
-1️⃣ Saudi Aramco — ~$1.5T+
-2️⃣ International Holding Co (UAE) — ~$240B+
-3️⃣ QNB (Qatar National Bank) — ~$150B+
-4️⃣ Al Rajhi Bank (Saudi) — ~$100B+
-5️⃣ Emirates NBD (UAE) — ~$80B+
-Oil wealth meets financial power.
+          <t>Top 5 Companies by Revenue 
+By Revenue (annual)
+1️⃣ Walmart — ~$650B
+2️⃣ Amazon — ~$575B
+3️⃣ Saudi Aramco — ~$500B
+4️⃣ China State Grid — ~$480B
+5️⃣ Apple — ~$390B
 @BehindNums</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>Top 5 Richest Companies in the Middle East
-1. Saudi Aramco — ~$1.5T+
-2. International Holding Co (UAE) — ~$240B+
-3. QNB (Qatar National Bank) — ~$150B+
-4. Al Rajhi Bank (Saudi) — ~$100B+
-5. Emirates NBD (UAE) — ~$80B+
-Oil wealth meets financial power.</t>
+          <t>Top 5 Companies by Revenue
+By Revenue (annual)
+1️⃣ Walmart — ~$650B
+2️⃣ Amazon — ~$575B
+3️⃣ Saudi Aramco — ~$500B
+4️⃣ China State Grid — ~$480B
+5️⃣ Apple — ~$390B
+@BehindNums</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -5549,7 +5562,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Emirates NBD (UAE) — ~$80B+ Oil wealth meets financial power. • QNB (Qatar National Bank) — ~$150B+ 4. • Al Rajhi Bank (Saudi) — ~$100B+ 5.</t>
+          <t>Top 5 Companies by Revenue By Revenue (annual) 1️⃣ Walmart — ~$650B 2️⃣ Amazon — ~$575B 3️⃣ Saudi Aramco — ~$500B 4️⃣ China State Grid — ~$480B 5️⃣ Apple — ~$390B @BehindNums</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -5677,7 +5690,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>JUST IN: Emirates NBD eliminates ATM withdrawal and debit card fees across the UAE and GCC until March 31, 2026!</t>
+          <t>JUST IN: EMIRATES NBD ELIMINATES ATM WITHDRAWAL &amp; DEBIT CARD FEES ACROSS THE UAE &amp; GCC UNTIL MARCH 31, 2026!</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -5708,7 +5721,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>JUST IN: Emirates NBD eliminates ATM withdrawal and debit card fees across the UAE and GCC until March 31, 2026!</t>
+          <t>JUST IN: EMIRATES NBD ELIMINATES ATM WITHDRAWAL &amp; DEBIT CARD FEES ACROSS THE UAE &amp; GCC UNTIL MARCH 31, 2026!</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -6041,48 +6054,49 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2044717394669502695</t>
+          <t>2044732404938702855</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044717394669502695</t>
+          <t>https://x.com/aaditsh/status/2044732404938702855</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/aaditsh</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>aaditsh</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Aadit Sheth</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1989274279947694081/ggQkOhbP_bigger.jpg</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>💸 Save AED 20,000 or more to start earning miles based on your average quarterly savings
-🌟 Get a complimentary Debit Card that is internationally recognized
-Offer valid till 30 June 2026
-Terms &amp;amp; Conditions apply
-https://t.co/6VJUgOMZYN</t>
+          <t>This is one of my favorite ideas in all of writing.
+Ed Sheeran calls it the dirty tap.
+Turn it on, dirty water flows out for a long time. Eventually clean water starts coming. He's talking about songs but it's true for all creative work.
+Every CEO memo that got quoted. Every keynote that landed. Every email that actually changed someone's mind. All of it came out of a dozen bad drafts first.
+The dirty water is necessary. You need to get the bad ideas out before the good ones come. That's just how it works.</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Save and earn with your Emirates Islamic Super Savings Etihad Guest Account!
-💸 Get up to 750,000 Etihad Guest Miles every quarter and up to 3 million Etihad Guest Miles in a year</t>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; probably the worst customer experience I’ve had in my life.
+Tried cancelling my cards. Have received 10+ phone calls from them trying to retain. Confirmed each time that I want to cancel (on call and on email confirmation). It’s been 4-5 months since I raised this complaint. No resolution yet.
+Impressed with how difficult they make this process. Wow!</t>
         </is>
       </c>
       <c r="K35" t="b">
@@ -6092,19 +6106,23 @@
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Apr 16, 2026 · 9:59 AM UTC</t>
+          <t>Apr 16, 2026 · 10:59 AM UTC</t>
         </is>
       </c>
       <c r="P35" s="2" t="n">
-        <v>46128.41597222222</v>
+        <v>46128.45763888889</v>
       </c>
       <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>['https://x.com/emiratesislamic']</t>
+        </is>
+      </c>
       <c r="S35" t="n">
         <v>2</v>
       </c>
@@ -6112,10 +6130,10 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V35" t="n">
-        <v>253</v>
+        <v>5653</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
@@ -6124,50 +6142,51 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Save and earn with your Emirates Islamic Super Savings Etihad Guest Account!
-💸 Get up to 750,000 Etihad Guest Miles every quarter and up to 3 million Etihad Guest Miles in a year</t>
+          <t>@emiratesislamic probably the worst customer experience I’ve had in my life.
+Tried cancelling my cards. Have received 10+ phone calls from them trying to retain. Confirmed each time that I want to cancel (on call and on email confirmation). It’s been 4-5 months since I raised this complaint. No resolution yet.
+Impressed with how difficult they make this process. Wow!</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044717394669502695</t>
+          <t>https://x.com/aaditsh/status/2044732404938702855</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>💸 Save AED 20,000 or more to start earning miles based on your average quarterly savings
-🌟 Get a complimentary Debit Card that is internationally recognized
-Offer valid till 30 June 2026
-Terms &amp;amp; Conditions apply
-https://t.co/6VJUgOMZYN</t>
+          <t>This is one of my favorite ideas in all of writing.
+Ed Sheeran calls it the dirty tap.
+Turn it on, dirty water flows out for a long time. Eventually clean water starts coming. He's talking about songs but it's true for all creative work.
+Every CEO memo that got quoted. Every keynote that landed. Every email that actually changed someone's mind. All of it came out of a dozen bad drafts first.
+The dirty water is necessary. You need to get the bad ideas out before the good ones come. That's just how it works.</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>💸 Save AED 20,000 or more to start earning miles based on your average quarterly savings
-🌟 Get a complimentary Debit Card that is internationally recognized
-Offer valid till 30 June 2026
-Terms &amp;amp; Conditions apply
-https://t.co/6VJUgOMZYN</t>
+          <t>This is one of my favorite ideas in all of writing.
+Ed Sheeran calls it the dirty tap.
+Turn it on, dirty water flows out for a long time. Eventually clean water starts coming. He's talking about songs but it's true for all creative work.
+Every CEO memo that got quoted. Every keynote that landed. Every email that actually changed someone's mind. All of it came out of a dozen bad drafts first.
+The dirty water is necessary. You need to get the bad ideas out before the good ones come. That's just how it works.</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Save AED 20,000 or more to start earning miles based on your average quarterly savings. Get a complimentary Debit Card that is internationally recognized. Offer valid until 30 June 2026. Terms and Conditions apply.</t>
+          <t>This is one of my favorite ideas in all of writing. Ed Sheeran calls it the dirty tap. Turn it on, dirty water flows out for a long time. Eventually clean water starts coming. He's talking about songs but it's true for all creative work. Every CEO memo that got quoted. Every keynote that landed. Every email that actually changed someone's mind. All of it came out of a dozen bad drafts first. The dirty water is necessary. You need to get the bad ideas out before the good ones come. That's just how it works.</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Cust</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE35" s="2" t="n">
-        <v>46128.58263888889</v>
+        <v>46128.62430555555</v>
       </c>
       <c r="AF35" s="2" t="n">
         <v>46128</v>
@@ -6184,7 +6203,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Save AED 20,000 or more to start earning miles based on your average quarterly savings. • Offer valid until 30 June 2026. • Get a complimentary Debit Card that is internationally recognized.</t>
+          <t>Turn it on, dirty water flows out for a long time. • You need to get the bad ideas out before the good ones come. • He's talking about songs but it's true for all creative work.</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -6207,45 +6226,45 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2044704123199554019</t>
+          <t>2044717394669502695</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://x.com/startupsceneme/status/2044704123199554019</t>
+          <t>https://x.com/emiratesislamic/status/2044717394669502695</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://x.com/startupsceneme</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>startupsceneme</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Startup Scene ME</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1221420632044462085/G_yAYsR8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Emirates Islamic, a Dubai-based Islamic bank offering Sharia-compliant financial services, has launched a Business Banking campaign aimed at supporting small and medium enterprises in the United Arab Emirates, offering a total prize pool of Dhs 1 million.
-https://t.co/NGMGwUvZfs</t>
+          <t>ادخر واكسب مع حساب ضيف الاتحاد سوبر للتوفير من الإمارات الإسلامي
+💸 اكسب ما يصل إلى 750,000 ميل من أميال ضيف الاتحاد كل ربع سنة ولغاية 3,000,000 ميل من أميال ضيف الاتحاد سنوياً https://t.co/QZie703oFv</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Emirates Islamic, a Dubai-based Islamic bank offering Sharia-compliant financial services, has launched a Business Banking campaign aimed at supporting small and medium enterprises in the United Arab Emirates, offering a total prize pool of Dhs 1 million.
-&lt;a href="https://thestartupscene.me/OPPORTUNITIES/Emirates-Islamic-Bank-Launches-AED-1M-Campaign-for-SMEs"&gt;thestartupscene.me/OPPORTUNI…&lt;/a&gt;</t>
+          <t>Save and earn with your Emirates Islamic Super Savings Etihad Guest Account!
+💸 Get up to 750,000 Etihad Guest Miles every quarter and up to 3 million Etihad Guest Miles in a year</t>
         </is>
       </c>
       <c r="K36" t="b">
@@ -6255,34 +6274,30 @@
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Apr 16, 2026 · 9:07 AM UTC</t>
+          <t>Apr 16, 2026 · 9:59 AM UTC</t>
         </is>
       </c>
       <c r="P36" s="2" t="n">
-        <v>46128.37986111111</v>
+        <v>46128.41597222222</v>
       </c>
       <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>['https://thestartupscene.me/OPPORTUNITIES/Emirates-Islamic-Bank-Launches-AED-1M-Campaign-for-SMEs']</t>
-        </is>
-      </c>
+      <c r="R36" t="inlineStr"/>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>38</v>
+        <v>253</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
@@ -6291,35 +6306,36 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Emirates Islamic, a Dubai-based Islamic bank offering Sharia-compliant financial services, has launched a Business Banking campaign aimed at supporting small and medium enterprises in the United Arab Emirates, offering a total prize pool of Dhs 1 million.
-thestartupscene.me/OPPORTUNI…</t>
+          <t>Save and earn with your Emirates Islamic Super Savings Etihad Guest Account!
+💸 Get up to 750,000 Etihad Guest Miles every quarter and up to 3 million Etihad Guest Miles in a year</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>https://x.com/startupsceneme/status/2044704123199554019</t>
+          <t>https://x.com/emiratesislamic/status/2044717394669502695</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>Emirates Islamic, a Dubai-based Islamic bank offering Sharia-compliant financial services, has launched a Business Banking campaign aimed at supporting small and medium enterprises in the United Arab Emirates, offering a total prize pool of Dhs 1 million.
-https://t.co/NGMGwUvZfs</t>
+          <t>ادخر واكسب مع حساب ضيف الاتحاد سوبر للتوفير من الإمارات الإسلامي
+💸 اكسب ما يصل إلى 750,000 ميل من أميال ضيف الاتحاد كل ربع سنة ولغاية 3,000,000 ميل من أميال ضيف الاتحاد سنوياً https://t.co/QZie703oFv</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>Emirates Islamic, a Dubai-based Islamic bank offering Sharia-compliant financial services, has launched a Business Banking campaign aimed at supporting small and medium enterprises in the United Arab Emirates, offering a total prize pool of Dhs 1 million.
-https://t.co/NGMGwUvZfs</t>
+          <t>ادخر واكسب مع حساب ضيف الاتحاد سوبر للتوفير من الإمارات الإسلامي
+💸 اكسب ما يصل إلى 750,000 ميل من أميال ضيف الاتحاد كل ربع سنة ولغاية 3,000,000 ميل من أميال ضيف الاتحاد سنوياً https://t.co/QZie703oFv</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>Emirates Islamic, a Dubai-based Islamic bank offering Sharia-compliant financial services, has launched a Business Banking campaign aimed at supporting small and medium enterprises in the United Arab Emirates, offering a total prize pool of 1 million dirhams.</t>
+          <t>Save and earn with the Emirates Islamic Super Guest Account for savings. 
+💸 Earn up to 750,000 Etihad Guest Miles every quarter and up to 3,000,000 Etihad Guest Miles annually.</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Cust</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr">
@@ -6328,7 +6344,7 @@
         </is>
       </c>
       <c r="AE36" s="2" t="n">
-        <v>46128.54652777778</v>
+        <v>46128.58263888889</v>
       </c>
       <c r="AF36" s="2" t="n">
         <v>46128</v>
@@ -6345,7 +6361,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Emirates Islamic, a Dubai-based Islamic bank offering Sharia-compliant financial services, has launched a Business Banki…</t>
+          <t>💸 Earn up to 750,000 Etihad Guest Miles every quarter and up to 3,000,000 Etihad Guest Miles annually. • Save and earn with the Emirates Islamic Super Guest Account for savings.</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
@@ -6368,46 +6384,45 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2044701412848705623</t>
+          <t>2044704123199554019</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044701412848705623</t>
+          <t>https://x.com/startupsceneme/status/2044704123199554019</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/startupsceneme</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>startupsceneme</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Startup Scene ME</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1221420632044462085/G_yAYsR8_bigger.jpg</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>مع الإمارات الإسلامي، تتحوّل طموحات الشركات الصغيرة والمتوسطة إلى فرص حقيقية للنمو. من خلال إطلاق حملة جديدة تضيف قيمة ملموسة لمتعاملينا، نفتح الباب للفوز بجوائز يصل مجموعها إلى مليون درهم إماراتي. 
-نرافق رحلتكم، ندعم توسّعكم، ونمنح أفكاركم المساحة لتكبر.
-معا نصنع نجاح أعمالكم. https://t.co/0uN1xuq5rX</t>
+          <t>Emirates Islamic, a Dubai-based Islamic bank offering Sharia-compliant financial services, has launched a Business Banking campaign aimed at supporting small and medium enterprises in the United Arab Emirates, offering a total prize pool of Dhs 1 million.
+thestartupscene.me/OPPORTUNI…</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Emirates Islamic empowers SME growth with a campaign that brings added value to customers and an opportunity to win from a total prize pool of AED 1 million. Driving ambition. Enabling expansion. Unlocking new opportunities.
-&lt;a href="/search?f=tweets&amp;amp;q=%23SME"&gt;#SME&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23businessbanking"&gt;#businessbanking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23emiratesislamic"&gt;#emiratesislamic&lt;/a&gt;</t>
+          <t>Emirates Islamic, a Dubai-based Islamic bank offering Sharia-compliant financial services, has launched a Business Banking campaign aimed at supporting small and medium enterprises in the United Arab Emirates, offering a total prize pool of Dhs 1 million.
+&lt;a href="https://thestartupscene.me/OPPORTUNITIES/Emirates-Islamic-Bank-Launches-AED-1M-Campaign-for-SMEs"&gt;thestartupscene.me/OPPORTUNI…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K37" t="b">
@@ -6422,29 +6437,29 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Apr 16, 2026 · 8:56 AM UTC</t>
+          <t>Apr 16, 2026 · 9:07 AM UTC</t>
         </is>
       </c>
       <c r="P37" s="2" t="n">
-        <v>46128.37222222222</v>
+        <v>46128.37986111111</v>
       </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23SME', 'https://x.com/search?f=tweets&amp;q=%23businessbanking', 'https://x.com/search?f=tweets&amp;q=%23emiratesislamic']</t>
+          <t>['https://thestartupscene.me/OPPORTUNITIES/Emirates-Islamic-Bank-Launches-AED-1M-Campaign-for-SMEs']</t>
         </is>
       </c>
       <c r="S37" t="n">
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
@@ -6453,37 +6468,26 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Emirates Islamic empowers SME growth with a campaign that brings added value to customers and an opportunity to win from a total prize pool of AED 1 million. Driving ambition. Enabling expansion. Unlocking new opportunities.
-#SME #businessbanking #emiratesislamic</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2044701412848705623</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>مع الإمارات الإسلامي، تتحوّل طموحات الشركات الصغيرة والمتوسطة إلى فرص حقيقية للنمو. من خلال إطلاق حملة جديدة تضيف قيمة ملموسة لمتعاملينا، نفتح الباب للفوز بجوائز يصل مجموعها إلى مليون درهم إماراتي. 
-نرافق رحلتكم، ندعم توسّعكم، ونمنح أفكاركم المساحة لتكبر.
-معا نصنع نجاح أعمالكم. https://t.co/0uN1xuq5rX</t>
-        </is>
-      </c>
+          <t>Emirates Islamic, a Dubai-based Islamic bank offering Sharia-compliant financial services, has launched a Business Banking campaign aimed at supporting small and medium enterprises in the United Arab Emirates, offering a total prize pool of Dhs 1 million.
+thestartupscene.me/OPPORTUNI…</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>مع الإمارات الإسلامي، تتحوّل طموحات الشركات الصغيرة والمتوسطة إلى فرص حقيقية للنمو. من خلال إطلاق حملة جديدة تضيف قيمة ملموسة لمتعاملينا، نفتح الباب للفوز بجوائز يصل مجموعها إلى مليون درهم إماراتي. 
-نرافق رحلتكم، ندعم توسّعكم، ونمنح أفكاركم المساحة لتكبر.
-معا نصنع نجاح أعمالكم. https://t.co/0uN1xuq5rX</t>
+          <t>Emirates Islamic, a Dubai-based Islamic bank offering Sharia-compliant financial services, has launched a Business Banking campaign aimed at supporting small and medium enterprises in the United Arab Emirates, offering a total prize pool of Dhs 1 million.
+thestartupscene.me/OPPORTUNI…</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>With Emirates Islamic, the ambitions of small and medium-sized enterprises turn into real growth opportunities. By launching a new campaign that adds tangible value to our clients, we open the door to win prizes totaling up to one million dirhams. We accompany your journey, support your expansion, and give your ideas the space to grow. Together, we create the success of your business.</t>
+          <t>Emirates Islamic, a Dubai-based Islamic bank offering Sharia-compliant financial services, has launched a Business Banking campaign aimed at supporting small and medium enterprises in the United Arab Emirates, offering a total prize pool of 1 million dirhams.</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Cust</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr">
@@ -6492,7 +6496,7 @@
         </is>
       </c>
       <c r="AE37" s="2" t="n">
-        <v>46128.53888888889</v>
+        <v>46128.54652777778</v>
       </c>
       <c r="AF37" s="2" t="n">
         <v>46128</v>
@@ -6509,7 +6513,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>By launching a new campaign that adds tangible value to our clients, we open the door to win prizes totaling up to one million dirhams. • With Emirates Islamic, the ambitions of small and medium-sized enterprises turn into real growth opportunities. • We accompany your journey, support your expansion, and give your ideas the space to grow.</t>
+          <t>Emirates Islamic, a Dubai-based Islamic bank offering Sharia-compliant financial services, has launched a Business Banki…</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -6532,12 +6536,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2044657039872237722</t>
+          <t>2044701412848705623</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044657039872237722</t>
+          <t>https://x.com/emiratesislamic/status/2044701412848705623</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6562,6 +6566,170 @@
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
+        <is>
+          <t>مع الإمارات الإسلامي، تتحوّل طموحات الشركات الصغيرة والمتوسطة إلى فرص حقيقية للنمو. من خلال إطلاق حملة جديدة تضيف قيمة ملموسة لمتعاملينا، نفتح الباب للفوز بجوائز يصل مجموعها إلى مليون درهم إماراتي. 
+نرافق رحلتكم، ندعم توسّعكم، ونمنح أفكاركم المساحة لتكبر.
+معا نصنع نجاح أعمالكم. https://t.co/0uN1xuq5rX</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Emirates Islamic empowers SME growth with a campaign that brings added value to customers and an opportunity to win from a total prize pool of AED 1 million. Driving ambition. Enabling expansion. Unlocking new opportunities.
+&lt;a href="/search?f=tweets&amp;amp;q=%23SME"&gt;#SME&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23businessbanking"&gt;#businessbanking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23emiratesislamic"&gt;#emiratesislamic&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K38" t="b">
+        <v>0</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Apr 16, 2026 · 8:56 AM UTC</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="n">
+        <v>46128.37222222222</v>
+      </c>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23SME', 'https://x.com/search?f=tweets&amp;q=%23businessbanking', 'https://x.com/search?f=tweets&amp;q=%23emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>64</v>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Emirates Islamic empowers SME growth with a campaign that brings added value to customers and an opportunity to win from a total prize pool of AED 1 million. Driving ambition. Enabling expansion. Unlocking new opportunities.
+#SME #businessbanking #emiratesislamic</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044701412848705623</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>مع الإمارات الإسلامي، تتحوّل طموحات الشركات الصغيرة والمتوسطة إلى فرص حقيقية للنمو. من خلال إطلاق حملة جديدة تضيف قيمة ملموسة لمتعاملينا، نفتح الباب للفوز بجوائز يصل مجموعها إلى مليون درهم إماراتي. 
+نرافق رحلتكم، ندعم توسّعكم، ونمنح أفكاركم المساحة لتكبر.
+معا نصنع نجاح أعمالكم. https://t.co/0uN1xuq5rX</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>مع الإمارات الإسلامي، تتحوّل طموحات الشركات الصغيرة والمتوسطة إلى فرص حقيقية للنمو. من خلال إطلاق حملة جديدة تضيف قيمة ملموسة لمتعاملينا، نفتح الباب للفوز بجوائز يصل مجموعها إلى مليون درهم إماراتي. 
+نرافق رحلتكم، ندعم توسّعكم، ونمنح أفكاركم المساحة لتكبر.
+معا نصنع نجاح أعمالكم. https://t.co/0uN1xuq5rX</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>With Emirates Islamic, the ambitions of small and medium-sized enterprises turn into real growth opportunities. By launching a new campaign that adds tangible value to our clients, we open the door to win prizes totaling up to one million dirhams. We accompany your journey, support your expansion, and give your ideas the space to grow. Together, we create the success of your business.</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Bank</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AE38" s="2" t="n">
+        <v>46128.53888888889</v>
+      </c>
+      <c r="AF38" s="2" t="n">
+        <v>46128</v>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>2. Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>By launching a new campaign that adds tangible value to our clients, we open the door to win prizes totaling up to one million dirhams. • With Emirates Islamic, the ambitions of small and medium-sized enterprises turn into real growth opportunities. • We accompany your journey, support your expansion, and give your ideas the space to grow.</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AK38" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL38" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2044657039872237722</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044657039872237722</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
         <is>
           <t>You don’t have a spending problem, you have invisible spending.
 Track what feels “too small to matter.”
@@ -6570,7 +6738,7 @@
 https://t.co/XvyZgR87nM"</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>You don’t have a spending problem, you have invisible spending.
 Track what feels “too small to matter.”
@@ -6579,48 +6747,48 @@
 &lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;&amp;#34;</t>
         </is>
       </c>
-      <c r="K38" t="b">
-        <v>0</v>
-      </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr">
+      <c r="K39" t="b">
+        <v>0</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
         <is>
           <t>20h</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>Apr 16, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
-      <c r="P38" s="2" t="n">
+      <c r="P39" s="2" t="n">
         <v>46128.25</v>
       </c>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr">
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr">
         <is>
           <t>['https://x.com/search?f=tweets&amp;q=%23EIFinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
         </is>
       </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" t="n">
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
         <v>53</v>
       </c>
-      <c r="W38" t="inlineStr">
+      <c r="W39" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>You don’t have a spending problem, you have invisible spending.
 Track what feels “too small to matter.”
@@ -6629,12 +6797,12 @@
 emiratesislamic.ae/en/key-in…"</t>
         </is>
       </c>
-      <c r="Y38" t="inlineStr">
+      <c r="Y39" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2044657039872237722</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
+      <c r="Z39" t="inlineStr">
         <is>
           <t>You don’t have a spending problem, you have invisible spending.
 Track what feels “too small to matter.”
@@ -6643,7 +6811,7 @@
 https://t.co/XvyZgR87nM"</t>
         </is>
       </c>
-      <c r="AA38" t="inlineStr">
+      <c r="AA39" t="inlineStr">
         <is>
           <t>You don’t have a spending problem, you have invisible spending.
 Track what feels “too small to matter.”
@@ -6652,180 +6820,23 @@
 https://t.co/XvyZgR87nM"</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
+      <c r="AB39" t="inlineStr">
         <is>
           <t>You don’t have a spending problem, you have invisible spending. Track what feels “too small to matter.” Because that’s usually where your money goes.</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
+      <c r="AC39" t="inlineStr">
         <is>
           <t>Bank</t>
         </is>
       </c>
-      <c r="AD38" t="inlineStr">
+      <c r="AD39" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="AE38" s="2" t="n">
+      <c r="AE39" s="2" t="n">
         <v>46128.41666666666</v>
-      </c>
-      <c r="AF38" s="2" t="n">
-        <v>46128</v>
-      </c>
-      <c r="AG38" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>You don’t have a spending problem, you have invisible spending. • Track what feels “too small to matter.” Because that’s usually where your money goes.</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AK38" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL38" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="n">
-        <v>37</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2044836542028320968</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2044836542028320968</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>تشهد التحديثات الوهمية على أجهزة أندرويد تزايداً ملحوظاً، وقد تُستخدم لخداعك لتثبيت تطبيقات غير آمنة أو مشاركة البيانات.
-احم حسابك من خلال تفعيل ميزة اللمس الذكي والتعرّف على الوجه لتسجيل دخول أكثر أماناً. https://t.co/ZOt8O2bR9J</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>Fake Android updates are rising. They can trick you into installing unsafe apps or sharing details.
-Turn on Smart Touch and Face Pass for secure login.</t>
-        </is>
-      </c>
-      <c r="K39" t="b">
-        <v>0</v>
-      </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>8h</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>Apr 16, 2026 · 5:53 PM UTC</t>
-        </is>
-      </c>
-      <c r="P39" s="2" t="n">
-        <v>46128.74513888889</v>
-      </c>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>60</v>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>Fake Android updates are rising. They can trick you into installing unsafe apps or sharing details.
-Turn on Smart Touch and Face Pass for secure login.</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2044836542028320968</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>تشهد التحديثات الوهمية على أجهزة أندرويد تزايداً ملحوظاً، وقد تُستخدم لخداعك لتثبيت تطبيقات غير آمنة أو مشاركة البيانات.
-احم حسابك من خلال تفعيل ميزة اللمس الذكي والتعرّف على الوجه لتسجيل دخول أكثر أماناً. https://t.co/ZOt8O2bR9J</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>تشهد التحديثات الوهمية على أجهزة أندرويد تزايداً ملحوظاً، وقد تُستخدم لخداعك لتثبيت تطبيقات غير آمنة أو مشاركة البيانات.
-احم حسابك من خلال تفعيل ميزة اللمس الذكي والتعرّف على الوجه لتسجيل دخول أكثر أماناً. https://t.co/ZOt8O2bR9J</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>Fake updates on Android devices are noticeably increasing, and they may be used to trick you into installing unsafe applications or sharing data. Protect your account by enabling smart touch and facial recognition for a more secure login.</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="AD39" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AE39" s="2" t="n">
-        <v>46128.91180555556</v>
       </c>
       <c r="AF39" s="2" t="n">
         <v>46128</v>
@@ -6842,7 +6853,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Fake updates on Android devices are noticeably increasing, and they may be used to trick you into installing unsafe applications or sharing data. • Protect your account by enabling smart touch and facial recognition for a more secure login.</t>
+          <t>You don’t have a spending problem, you have invisible spending. • Track what feels “too small to matter.” Because that’s usually where your money goes.</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
@@ -6865,12 +6876,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2044836538958200892</t>
+          <t>2044836542028320968</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044836538958200892</t>
+          <t>https://x.com/emiratesislamic/status/2044836542028320968</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6896,14 +6907,14 @@
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>ادخر واكسب مع حساب ضيف الاتحاد سوبر للتوفير من الإمارات الإسلامي
-💸 اكسب ما يصل إلى 750,000 ميل من أميال ضيف الاتحاد كل ربع سنة ولغاية 3,000,000 ميل من أميال ضيف الاتحاد سنوياً https://t.co/QZie703oFv</t>
+          <t>Fake Android updates are rising. They can trick you into installing unsafe apps or sharing details.
+Turn on Smart Touch and Face Pass for secure login.</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>تشهد التحديثات الوهمية على أجهزة أندرويد تزايداً ملحوظاً، وقد تُستخدم لخداعك لتثبيت تطبيقات غير آمنة أو مشاركة البيانات.
-احم حسابك من خلال تفعيل ميزة اللمس الذكي والتعرّف على الوجه لتسجيل دخول أكثر أماناً.</t>
+          <t>Fake Android updates are rising. They can trick you into installing unsafe apps or sharing details.
+Turn on Smart Touch and Face Pass for secure login.</t>
         </is>
       </c>
       <c r="K40" t="b">
@@ -6927,7 +6938,7 @@
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -6936,7 +6947,7 @@
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
@@ -6945,31 +6956,21 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>تشهد التحديثات الوهمية على أجهزة أندرويد تزايداً ملحوظاً، وقد تُستخدم لخداعك لتثبيت تطبيقات غير آمنة أو مشاركة البيانات.
-احم حسابك من خلال تفعيل ميزة اللمس الذكي والتعرّف على الوجه لتسجيل دخول أكثر أماناً.</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2044836538958200892</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>ادخر واكسب مع حساب ضيف الاتحاد سوبر للتوفير من الإمارات الإسلامي
-💸 اكسب ما يصل إلى 750,000 ميل من أميال ضيف الاتحاد كل ربع سنة ولغاية 3,000,000 ميل من أميال ضيف الاتحاد سنوياً https://t.co/QZie703oFv</t>
-        </is>
-      </c>
+          <t>Fake Android updates are rising. They can trick you into installing unsafe apps or sharing details.
+Turn on Smart Touch and Face Pass for secure login.</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>ادخر واكسب مع حساب ضيف الاتحاد سوبر للتوفير من الإمارات الإسلامي
-💸 اكسب ما يصل إلى 750,000 ميل من أميال ضيف الاتحاد كل ربع سنة ولغاية 3,000,000 ميل من أميال ضيف الاتحاد سنوياً https://t.co/QZie703oFv</t>
+          <t>Fake Android updates are rising. They can trick you into installing unsafe apps or sharing details.
+Turn on Smart Touch and Face Pass for secure login.</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>Save and earn with the Emirates Islamic Super Guest Account for savings. 
-💸 Earn up to 750,000 Etihad Guest Miles every quarter and up to 3,000,000 Etihad Guest Miles annually.</t>
+          <t>Fake Android updates are on the rise. They can deceive you into installing unsafe apps or sharing your information. Enable Smart Touch and Face Pass for secure login.</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -6979,7 +6980,7 @@
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE40" s="2" t="n">
@@ -7000,7 +7001,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>💸 Earn up to 750,000 Etihad Guest Miles every quarter and up to 3,000,000 Etihad Guest Miles annually. • Save and earn with the Emirates Islamic Super Guest Account for savings.</t>
+          <t>They can deceive you into installing unsafe apps or sharing your information. • Enable Smart Touch and Face Pass for secure login. • Fake Android updates are on the rise.</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
@@ -7023,12 +7024,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2044717396758303206</t>
+          <t>2044836538958200892</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044717396758303206</t>
+          <t>https://x.com/emiratesislamic/status/2044836538958200892</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -7053,6 +7054,163 @@
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
+        <is>
+          <t>تشهد التحديثات الوهمية على أجهزة أندرويد تزايداً ملحوظاً، وقد تُستخدم لخداعك لتثبيت تطبيقات غير آمنة أو مشاركة البيانات.
+احم حسابك من خلال تفعيل ميزة اللمس الذكي والتعرّف على الوجه لتسجيل دخول أكثر أماناً. https://t.co/ZOt8O2bR9J</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>تشهد التحديثات الوهمية على أجهزة أندرويد تزايداً ملحوظاً، وقد تُستخدم لخداعك لتثبيت تطبيقات غير آمنة أو مشاركة البيانات.
+احم حسابك من خلال تفعيل ميزة اللمس الذكي والتعرّف على الوجه لتسجيل دخول أكثر أماناً.</t>
+        </is>
+      </c>
+      <c r="K41" t="b">
+        <v>0</v>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>8h</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Apr 16, 2026 · 5:53 PM UTC</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="n">
+        <v>46128.74513888889</v>
+      </c>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="n">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>80</v>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>تشهد التحديثات الوهمية على أجهزة أندرويد تزايداً ملحوظاً، وقد تُستخدم لخداعك لتثبيت تطبيقات غير آمنة أو مشاركة البيانات.
+احم حسابك من خلال تفعيل ميزة اللمس الذكي والتعرّف على الوجه لتسجيل دخول أكثر أماناً.</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044836538958200892</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>تشهد التحديثات الوهمية على أجهزة أندرويد تزايداً ملحوظاً، وقد تُستخدم لخداعك لتثبيت تطبيقات غير آمنة أو مشاركة البيانات.
+احم حسابك من خلال تفعيل ميزة اللمس الذكي والتعرّف على الوجه لتسجيل دخول أكثر أماناً. https://t.co/ZOt8O2bR9J</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>تشهد التحديثات الوهمية على أجهزة أندرويد تزايداً ملحوظاً، وقد تُستخدم لخداعك لتثبيت تطبيقات غير آمنة أو مشاركة البيانات.
+احم حسابك من خلال تفعيل ميزة اللمس الذكي والتعرّف على الوجه لتسجيل دخول أكثر أماناً. https://t.co/ZOt8O2bR9J</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>Fake updates on Android devices are noticeably increasing and may be used to trick you into installing unsafe applications or sharing data. Protect your account by enabling smart touch and facial recognition for more secure login.</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Bank</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="AE41" s="2" t="n">
+        <v>46128.91180555556</v>
+      </c>
+      <c r="AF41" s="2" t="n">
+        <v>46128</v>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>2. Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Fake updates on Android devices are noticeably increasing and may be used to trick you into installing unsafe applications or sharing data. • Protect your account by enabling smart touch and facial recognition for more secure login.</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AK41" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL41" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2044717396758303206</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044717396758303206</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
         <is>
           <t>💸 Save AED 20,000 or more to start earning miles based on your average quarterly savings
 🌟 Get a complimentary Debit Card that is internationally recognized
@@ -7061,7 +7219,7 @@
 emiratesislamic.ae/en/accoun…</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>💸 Save AED 20,000 or more to start earning miles based on your average quarterly savings
 🌟 Get a complimentary Debit Card that is internationally recognized
@@ -7070,48 +7228,48 @@
 &lt;a href="https://www.emiratesislamic.ae/en/accounts/savings-accounts/super-savings-etihad-guest-account?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=etihad_guest_account"&gt;emiratesislamic.ae/en/accoun…&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K41" t="b">
-        <v>0</v>
-      </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr">
+      <c r="K42" t="b">
+        <v>0</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
         <is>
           <t>16h</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>Apr 16, 2026 · 9:59 AM UTC</t>
         </is>
       </c>
-      <c r="P41" s="2" t="n">
+      <c r="P42" s="2" t="n">
         <v>46128.41597222222</v>
       </c>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr">
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr">
         <is>
           <t>['https://www.emiratesislamic.ae/en/accounts/savings-accounts/super-savings-etihad-guest-account?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=etihad_guest_account']</t>
         </is>
       </c>
-      <c r="S41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" t="n">
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
         <v>134</v>
       </c>
-      <c r="W41" t="inlineStr">
+      <c r="W42" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
+      <c r="X42" t="inlineStr">
         <is>
           <t>💸 Save AED 20,000 or more to start earning miles based on your average quarterly savings
 🌟 Get a complimentary Debit Card that is internationally recognized
@@ -7120,9 +7278,9 @@
 emiratesislamic.ae/en/accoun…</t>
         </is>
       </c>
-      <c r="Y41" t="inlineStr"/>
-      <c r="Z41" t="inlineStr"/>
-      <c r="AA41" t="inlineStr">
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr">
         <is>
           <t>💸 Save AED 20,000 or more to start earning miles based on your average quarterly savings
 🌟 Get a complimentary Debit Card that is internationally recognized
@@ -7131,92 +7289,92 @@
 emiratesislamic.ae/en/accoun…</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>Save AED 20,000 or more to start earning miles based on your average quarterly savings. Get a complimentary Debit Card that is internationally recognized. Offer valid till 30 June 2026. Terms &amp; Conditions apply.</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>Save AED 20,000 or more to start earning miles based on your average quarterly savings. Get a complimentary Debit Card that is internationally recognized. Offer valid until 30 June 2026. Terms &amp; Conditions apply.</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
         <is>
           <t>Bank</t>
         </is>
       </c>
-      <c r="AD41" t="inlineStr">
+      <c r="AD42" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="AE41" s="2" t="n">
+      <c r="AE42" s="2" t="n">
         <v>46128.58263888889</v>
       </c>
-      <c r="AF41" s="2" t="n">
+      <c r="AF42" s="2" t="n">
         <v>46128</v>
       </c>
-      <c r="AG41" t="inlineStr">
+      <c r="AG42" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="AH41" t="inlineStr">
+      <c r="AH42" t="inlineStr">
         <is>
           <t>2. Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>Save AED 20,000 or more to start earning miles based on your average quarterly savings. • Offer valid till 30 June 2026. • Get a complimentary Debit Card that is internationally recognized.</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Save AED 20,000 or more to start earning miles based on your average quarterly savings. • Offer valid until 30 June 2026. • Get a complimentary Debit Card that is internationally recognized.</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
         <is>
           <t>Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
-      <c r="AK41" t="n">
+      <c r="AK42" t="n">
         <v>2026</v>
       </c>
-      <c r="AL41" t="inlineStr">
+      <c r="AL42" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="1" t="n">
-        <v>40</v>
-      </c>
-      <c r="B42" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" t="inlineStr">
         <is>
           <t>2044717367842816367</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2044717367842816367</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>emiratesislamic</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>emiratesislamic</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr">
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
         <is>
           <t>💸 ادخر 20,000 درهم أو أكثر للبدء باكتساب الأميال بناءً على متوسط مدخراتك ربع السنوي! 
 🌟 احصل على بطاقة خصم معترف بها دولياً
@@ -7225,7 +7383,7 @@
 https://t.co/csC9BzTLNy</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>💸 ادخر 20,000 درهم أو أكثر للبدء باكتساب الأميال بناءً على متوسط مدخراتك ربع السنوي! 
 🌟 احصل على بطاقة خصم معترف بها دولياً
@@ -7234,48 +7392,48 @@
 &lt;a href="https://www.emiratesislamic.ae/ar/accounts/savings-accounts/super-savings-etihad-guest-account?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=etihad_guest_account"&gt;emiratesislamic.ae/ar/accoun…&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K42" t="b">
-        <v>0</v>
-      </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr">
+      <c r="K43" t="b">
+        <v>0</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
         <is>
           <t>16h</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>Apr 16, 2026 · 9:59 AM UTC</t>
         </is>
       </c>
-      <c r="P42" s="2" t="n">
+      <c r="P43" s="2" t="n">
         <v>46128.41597222222</v>
       </c>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr">
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr">
         <is>
           <t>['https://www.emiratesislamic.ae/ar/accounts/savings-accounts/super-savings-etihad-guest-account?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=etihad_guest_account']</t>
         </is>
       </c>
-      <c r="S42" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" t="n">
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
         <v>66</v>
       </c>
-      <c r="W42" t="inlineStr">
+      <c r="W43" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>💸 ادخر 20,000 درهم أو أكثر للبدء باكتساب الأميال بناءً على متوسط مدخراتك ربع السنوي! 
 🌟 احصل على بطاقة خصم معترف بها دولياً
@@ -7284,12 +7442,12 @@
 emiratesislamic.ae/ar/accoun…</t>
         </is>
       </c>
-      <c r="Y42" t="inlineStr">
+      <c r="Y43" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2044717367842816367</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
+      <c r="Z43" t="inlineStr">
         <is>
           <t>💸 ادخر 20,000 درهم أو أكثر للبدء باكتساب الأميال بناءً على متوسط مدخراتك ربع السنوي! 
 🌟 احصل على بطاقة خصم معترف بها دولياً
@@ -7298,7 +7456,7 @@
 https://t.co/csC9BzTLNy</t>
         </is>
       </c>
-      <c r="AA42" t="inlineStr">
+      <c r="AA43" t="inlineStr">
         <is>
           <t>💸 ادخر 20,000 درهم أو أكثر للبدء باكتساب الأميال بناءً على متوسط مدخراتك ربع السنوي! 
 🌟 احصل على بطاقة خصم معترف بها دولياً
@@ -7307,7 +7465,7 @@
 https://t.co/csC9BzTLNy</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
+      <c r="AB43" t="inlineStr">
         <is>
           <t>Save 20,000 dirhams or more to start earning miles based on your average quarterly savings! 
 Get an internationally recognized debit card.
@@ -7315,155 +7473,6 @@
 Terms and conditions apply.</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Bank</t>
-        </is>
-      </c>
-      <c r="AD42" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="AE42" s="2" t="n">
-        <v>46128.58263888889</v>
-      </c>
-      <c r="AF42" s="2" t="n">
-        <v>46128</v>
-      </c>
-      <c r="AG42" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>Save 20,000 dirhams or more to start earning miles based on your average quarterly savings! • The offer is valid until June 30, 2026. • Get an internationally recognized debit card.</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AK42" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL42" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="n">
-        <v>41</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2044717365380739467</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2044717365380739467</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>ادخر واكسب مع حساب ضيف الاتحاد سوبر للتوفير من الإمارات الإسلامي
-💸 اكسب ما يصل إلى 750,000 ميل من أميال ضيف الاتحاد كل ربع سنة ولغاية 3,000,000 ميل من أميال ضيف الاتحاد سنوياً</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>ادخر واكسب مع حساب ضيف الاتحاد سوبر للتوفير من الإمارات الإسلامي
-💸 اكسب ما يصل إلى 750,000 ميل من أميال ضيف الاتحاد كل ربع سنة ولغاية 3,000,000 ميل من أميال ضيف الاتحاد سنوياً</t>
-        </is>
-      </c>
-      <c r="K43" t="b">
-        <v>0</v>
-      </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>16h</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>Apr 16, 2026 · 9:59 AM UTC</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="n">
-        <v>46128.41597222222</v>
-      </c>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="n">
-        <v>1</v>
-      </c>
-      <c r="T43" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1</v>
-      </c>
-      <c r="V43" t="n">
-        <v>95</v>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>ادخر واكسب مع حساب ضيف الاتحاد سوبر للتوفير من الإمارات الإسلامي
-💸 اكسب ما يصل إلى 750,000 ميل من أميال ضيف الاتحاد كل ربع سنة ولغاية 3,000,000 ميل من أميال ضيف الاتحاد سنوياً</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr"/>
-      <c r="Z43" t="inlineStr"/>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>ادخر واكسب مع حساب ضيف الاتحاد سوبر للتوفير من الإمارات الإسلامي
-💸 اكسب ما يصل إلى 750,000 ميل من أميال ضيف الاتحاد كل ربع سنة ولغاية 3,000,000 ميل من أميال ضيف الاتحاد سنوياً</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>Save and earn with the Emirates Islamic Super Guest Account for savings. 
-💸 Earn up to 750,000 Etihad Guest Miles every quarter and up to 3,000,000 Etihad Guest Miles annually.</t>
-        </is>
-      </c>
       <c r="AC43" t="inlineStr">
         <is>
           <t>Bank</t>
@@ -7492,7 +7501,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>💸 Earn up to 750,000 Etihad Guest Miles every quarter and up to 3,000,000 Etihad Guest Miles annually. • Save and earn with the Emirates Islamic Super Guest Account for savings.</t>
+          <t>Save 20,000 dirhams or more to start earning miles based on your average quarterly savings! • The offer is valid until June 30, 2026. • Get an internationally recognized debit card.</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
@@ -7515,12 +7524,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2044701403591983546</t>
+          <t>2044717365380739467</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044701403591983546</t>
+          <t>https://x.com/emiratesislamic/status/2044717365380739467</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7546,16 +7555,14 @@
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>مع الإمارات الإسلامي، تتحوّل طموحات الشركات الصغيرة والمتوسطة إلى فرص حقيقية للنمو. من خلال إطلاق حملة جديدة تضيف قيمة ملموسة لمتعاملينا، نفتح الباب للفوز بجوائز يصل مجموعها إلى مليون درهم إماراتي. 
-نرافق رحلتكم، ندعم توسّعكم، ونمنح أفكاركم المساحة لتكبر.
-معا نصنع نجاح أعمالكم.</t>
+          <t>ادخر واكسب مع حساب ضيف الاتحاد سوبر للتوفير من الإمارات الإسلامي
+💸 اكسب ما يصل إلى 750,000 ميل من أميال ضيف الاتحاد كل ربع سنة ولغاية 3,000,000 ميل من أميال ضيف الاتحاد سنوياً</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>مع الإمارات الإسلامي، تتحوّل طموحات الشركات الصغيرة والمتوسطة إلى فرص حقيقية للنمو. من خلال إطلاق حملة جديدة تضيف قيمة ملموسة لمتعاملينا، نفتح الباب للفوز بجوائز يصل مجموعها إلى مليون درهم إماراتي. 
-نرافق رحلتكم، ندعم توسّعكم، ونمنح أفكاركم المساحة لتكبر.
-معا نصنع نجاح أعمالكم.</t>
+          <t>ادخر واكسب مع حساب ضيف الاتحاد سوبر للتوفير من الإمارات الإسلامي
+💸 اكسب ما يصل إلى 750,000 ميل من أميال ضيف الاتحاد كل ربع سنة ولغاية 3,000,000 ميل من أميال ضيف الاتحاد سنوياً</t>
         </is>
       </c>
       <c r="K44" t="b">
@@ -7565,16 +7572,16 @@
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Apr 16, 2026 · 8:56 AM UTC</t>
+          <t>Apr 16, 2026 · 9:59 AM UTC</t>
         </is>
       </c>
       <c r="P44" s="2" t="n">
-        <v>46128.37222222222</v>
+        <v>46128.41597222222</v>
       </c>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
@@ -7585,10 +7592,10 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V44" t="n">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
@@ -7597,23 +7604,22 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>مع الإمارات الإسلامي، تتحوّل طموحات الشركات الصغيرة والمتوسطة إلى فرص حقيقية للنمو. من خلال إطلاق حملة جديدة تضيف قيمة ملموسة لمتعاملينا، نفتح الباب للفوز بجوائز يصل مجموعها إلى مليون درهم إماراتي. 
-نرافق رحلتكم، ندعم توسّعكم، ونمنح أفكاركم المساحة لتكبر.
-معا نصنع نجاح أعمالكم.</t>
+          <t>ادخر واكسب مع حساب ضيف الاتحاد سوبر للتوفير من الإمارات الإسلامي
+💸 اكسب ما يصل إلى 750,000 ميل من أميال ضيف الاتحاد كل ربع سنة ولغاية 3,000,000 ميل من أميال ضيف الاتحاد سنوياً</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>مع الإمارات الإسلامي، تتحوّل طموحات الشركات الصغيرة والمتوسطة إلى فرص حقيقية للنمو. من خلال إطلاق حملة جديدة تضيف قيمة ملموسة لمتعاملينا، نفتح الباب للفوز بجوائز يصل مجموعها إلى مليون درهم إماراتي. 
-نرافق رحلتكم، ندعم توسّعكم، ونمنح أفكاركم المساحة لتكبر.
-معا نصنع نجاح أعمالكم.</t>
+          <t>ادخر واكسب مع حساب ضيف الاتحاد سوبر للتوفير من الإمارات الإسلامي
+💸 اكسب ما يصل إلى 750,000 ميل من أميال ضيف الاتحاد كل ربع سنة ولغاية 3,000,000 ميل من أميال ضيف الاتحاد سنوياً</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>With Emirates Islamic, the ambitions of small and medium-sized enterprises turn into real growth opportunities. By launching a new campaign that adds tangible value to our clients, we open the door to win prizes totaling up to one million dirhams. We accompany your journey, support your expansion, and give your ideas the space to grow. Together, we create the success of your business.</t>
+          <t>Save and earn with the Emirates Islamic Super Guest Account for savings. 
+💸 Earn up to 750,000 Etihad Guest Miles every quarter and up to 3,000,000 Etihad Guest Miles annually.</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -7627,7 +7633,7 @@
         </is>
       </c>
       <c r="AE44" s="2" t="n">
-        <v>46128.53888888889</v>
+        <v>46128.58263888889</v>
       </c>
       <c r="AF44" s="2" t="n">
         <v>46128</v>
@@ -7644,7 +7650,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>By launching a new campaign that adds tangible value to our clients, we open the door to win prizes totaling up to one million dirhams. • With Emirates Islamic, the ambitions of small and medium-sized enterprises turn into real growth opportunities. • We accompany your journey, support your expansion, and give your ideas the space to grow.</t>
+          <t>💸 Earn up to 750,000 Etihad Guest Miles every quarter and up to 3,000,000 Etihad Guest Miles annually. • Save and earn with the Emirates Islamic Super Guest Account for savings.</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
@@ -7667,12 +7673,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2044657039859757511</t>
+          <t>2044701403591983546</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044657039859757511</t>
+          <t>https://x.com/emiratesislamic/status/2044701403591983546</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7697,6 +7703,158 @@
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
+        <is>
+          <t>مع الإمارات الإسلامي، تتحوّل طموحات الشركات الصغيرة والمتوسطة إلى فرص حقيقية للنمو. من خلال إطلاق حملة جديدة تضيف قيمة ملموسة لمتعاملينا، نفتح الباب للفوز بجوائز يصل مجموعها إلى مليون درهم إماراتي. 
+نرافق رحلتكم، ندعم توسّعكم، ونمنح أفكاركم المساحة لتكبر.
+معا نصنع نجاح أعمالكم.</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>مع الإمارات الإسلامي، تتحوّل طموحات الشركات الصغيرة والمتوسطة إلى فرص حقيقية للنمو. من خلال إطلاق حملة جديدة تضيف قيمة ملموسة لمتعاملينا، نفتح الباب للفوز بجوائز يصل مجموعها إلى مليون درهم إماراتي. 
+نرافق رحلتكم، ندعم توسّعكم، ونمنح أفكاركم المساحة لتكبر.
+معا نصنع نجاح أعمالكم.</t>
+        </is>
+      </c>
+      <c r="K45" t="b">
+        <v>0</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Apr 16, 2026 · 8:56 AM UTC</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="n">
+        <v>46128.37222222222</v>
+      </c>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="n">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>86</v>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>مع الإمارات الإسلامي، تتحوّل طموحات الشركات الصغيرة والمتوسطة إلى فرص حقيقية للنمو. من خلال إطلاق حملة جديدة تضيف قيمة ملموسة لمتعاملينا، نفتح الباب للفوز بجوائز يصل مجموعها إلى مليون درهم إماراتي. 
+نرافق رحلتكم، ندعم توسّعكم، ونمنح أفكاركم المساحة لتكبر.
+معا نصنع نجاح أعمالكم.</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>مع الإمارات الإسلامي، تتحوّل طموحات الشركات الصغيرة والمتوسطة إلى فرص حقيقية للنمو. من خلال إطلاق حملة جديدة تضيف قيمة ملموسة لمتعاملينا، نفتح الباب للفوز بجوائز يصل مجموعها إلى مليون درهم إماراتي. 
+نرافق رحلتكم، ندعم توسّعكم، ونمنح أفكاركم المساحة لتكبر.
+معا نصنع نجاح أعمالكم.</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>With Emirates Islamic, the ambitions of small and medium-sized enterprises turn into real growth opportunities. By launching a new campaign that adds tangible value to our clients, we open the door to win prizes totaling up to one million dirhams. We accompany your journey, support your expansion, and give your ideas the space to grow. Together, we create the success of your business.</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Bank</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AE45" s="2" t="n">
+        <v>46128.53888888889</v>
+      </c>
+      <c r="AF45" s="2" t="n">
+        <v>46128</v>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>2. Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>By launching a new campaign that adds tangible value to our clients, we open the door to win prizes totaling up to one million dirhams. • With Emirates Islamic, the ambitions of small and medium-sized enterprises turn into real growth opportunities. • We accompany your journey, support your expansion, and give your ideas the space to grow.</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AK45" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL45" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2044657039859757511</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044657039859757511</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
         <is>
           <t>ليست المشكلة فيما تنفقه، بل في ما يتسرّب منه بصمت.
 فالمبالغ الصغيرة التي نظنها "غير مهمّة"، هي غالباً ما تتراكم وتؤثر على ميزانيتك أكثر مما تتوقع.
@@ -7704,7 +7862,7 @@
 https://t.co/mgtIcQsyLZ</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>ليست المشكلة فيما تنفقه، بل في ما يتسرّب منه بصمت.
 فالمبالغ الصغيرة التي نظنها &amp;#34;غير مهمّة&amp;#34;، هي غالباً ما تتراكم وتؤثر على ميزانيتك أكثر مما تتوقع.
@@ -7712,48 +7870,48 @@
 &lt;a href="https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/ar/key-in…&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K45" t="b">
-        <v>0</v>
-      </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr">
+      <c r="K46" t="b">
+        <v>0</v>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
         <is>
           <t>20h</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>Apr 16, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
-      <c r="P45" s="2" t="n">
+      <c r="P46" s="2" t="n">
         <v>46128.25</v>
       </c>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr">
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr">
         <is>
           <t>['https://x.com/search?f=tweets&amp;q=%23نظرتك_المالية', 'https://x.com/search?f=tweets&amp;q=%23التثقيف_المالي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
         </is>
       </c>
-      <c r="S45" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" t="n">
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
         <v>53</v>
       </c>
-      <c r="W45" t="inlineStr">
+      <c r="W46" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>ليست المشكلة فيما تنفقه، بل في ما يتسرّب منه بصمت.
 فالمبالغ الصغيرة التي نظنها "غير مهمّة"، هي غالباً ما تتراكم وتؤثر على ميزانيتك أكثر مما تتوقع.
@@ -7761,12 +7919,12 @@
 emiratesislamic.ae/ar/key-in…</t>
         </is>
       </c>
-      <c r="Y45" t="inlineStr">
+      <c r="Y46" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2044657039859757511</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
+      <c r="Z46" t="inlineStr">
         <is>
           <t>ليست المشكلة فيما تنفقه، بل في ما يتسرّب منه بصمت.
 فالمبالغ الصغيرة التي نظنها "غير مهمّة"، هي غالباً ما تتراكم وتؤثر على ميزانيتك أكثر مما تتوقع.
@@ -7774,7 +7932,7 @@
 https://t.co/mgtIcQsyLZ</t>
         </is>
       </c>
-      <c r="AA45" t="inlineStr">
+      <c r="AA46" t="inlineStr">
         <is>
           <t>ليست المشكلة فيما تنفقه، بل في ما يتسرّب منه بصمت.
 فالمبالغ الصغيرة التي نظنها "غير مهمّة"، هي غالباً ما تتراكم وتؤثر على ميزانيتك أكثر مما تتوقع.
@@ -7782,186 +7940,24 @@
 https://t.co/mgtIcQsyLZ</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
+      <c r="AB46" t="inlineStr">
         <is>
           <t>The problem is not in what you spend, but in what silently leaks away.
 The small amounts that we think are "insignificant" often accumulate and affect your budget more than you expect.</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
+      <c r="AC46" t="inlineStr">
         <is>
           <t>Bank</t>
         </is>
       </c>
-      <c r="AD45" t="inlineStr">
+      <c r="AD46" t="inlineStr">
         <is>
           <t>Neutral</t>
         </is>
       </c>
-      <c r="AE45" s="2" t="n">
+      <c r="AE46" s="2" t="n">
         <v>46128.41666666666</v>
-      </c>
-      <c r="AF45" s="2" t="n">
-        <v>46128</v>
-      </c>
-      <c r="AG45" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>2. Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>The problem is not in what you spend, but in what silently leaks away. • The small amounts that we think are "insignificant" often accumulate and affect your budget more than you expect.</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>Emirates Islamic Bank (EIB)</t>
-        </is>
-      </c>
-      <c r="AK45" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL45" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="n">
-        <v>44</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2044832798670995759</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>https://x.com/RakeshMavath/status/2044832798670995759</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>https://x.com/RakeshMavath</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>RakeshMavath</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Rakesh Mavath</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2013866142125957122/nsrKPIws_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>@emiratesislamic probably the worst customer experience I’ve had in my life.
-Tried cancelling my cards. Have received 10+ phone calls from them trying to retain. Confirmed each time that I want to cancel (on call and on email confirmation). It’s been 4-5 months since I raised this complaint. No resolution yet.
-Impressed with how difficult they make this process. Wow!</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Grab screenshots of when they have called you and the following messages include that to your complaint to UAECB and they will fine the bank</t>
-        </is>
-      </c>
-      <c r="K46" t="b">
-        <v>0</v>
-      </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>['aaditsh', 'emiratesislamic']</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>8h</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>Apr 16, 2026 · 5:38 PM UTC</t>
-        </is>
-      </c>
-      <c r="P46" s="2" t="n">
-        <v>46128.73472222222</v>
-      </c>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" t="n">
-        <v>13</v>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>Grab screenshots of when they have called you and the following messages include that to your complaint to UAECB and they will fine the bank</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>https://x.com/RakeshMavath/status/2044832798670995759</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>@emiratesislamic probably the worst customer experience I’ve had in my life.
-Tried cancelling my cards. Have received 10+ phone calls from them trying to retain. Confirmed each time that I want to cancel (on call and on email confirmation). It’s been 4-5 months since I raised this complaint. No resolution yet.
-Impressed with how difficult they make this process. Wow!</t>
-        </is>
-      </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>@emiratesislamic probably the worst customer experience I’ve had in my life.
-Tried cancelling my cards. Have received 10+ phone calls from them trying to retain. Confirmed each time that I want to cancel (on call and on email confirmation). It’s been 4-5 months since I raised this complaint. No resolution yet.
-Impressed with how difficult they make this process. Wow!</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>probably the worst customer experience I’ve had in my life. Tried cancelling my cards. Have received 10+ phone calls from them trying to retain. Confirmed each time that I want to cancel (on call and on email confirmation). It’s been 4-5 months since I raised this complaint. No resolution yet. Impressed with how difficult they make this process. Wow!</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD46" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="AE46" s="2" t="n">
-        <v>46128.90138888889</v>
       </c>
       <c r="AF46" s="2" t="n">
         <v>46128</v>
@@ -7978,7 +7974,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>Have received 10+ phone calls from them trying to retain. • Confirmed each time that I want to cancel (on call and on email confirmation). • It’s been 4-5 months since I raised this complaint.</t>
+          <t>The problem is not in what you spend, but in what silently leaks away. • The small amounts that we think are "insignificant" often accumulate and affect your budget more than you expect.</t>
         </is>
       </c>
       <c r="AJ46" t="inlineStr">
@@ -7991,7 +7987,7 @@
       </c>
       <c r="AL46" t="inlineStr">
         <is>
-          <t>aaditsh, emiratesislamic</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -8001,32 +7997,32 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2044732404938702855</t>
+          <t>2044832798670995759</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://x.com/aaditsh/status/2044732404938702855</t>
+          <t>https://x.com/RakeshMavath/status/2044832798670995759</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://x.com/aaditsh</t>
+          <t>https://x.com/RakeshMavath</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>aaditsh</t>
+          <t>RakeshMavath</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Aadit Sheth</t>
+          <t>Rakesh Mavath</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1989274279947694081/ggQkOhbP_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2013866142125957122/nsrKPIws_bigger.jpg</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
@@ -8039,46 +8035,44 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; probably the worst customer experience I’ve had in my life.
-Tried cancelling my cards. Have received 10+ phone calls from them trying to retain. Confirmed each time that I want to cancel (on call and on email confirmation). It’s been 4-5 months since I raised this complaint. No resolution yet.
-Impressed with how difficult they make this process. Wow!</t>
+          <t>Grab screenshots of when they have called you and the following messages include that to your complaint to UAECB and they will fine the bank</t>
         </is>
       </c>
       <c r="K47" t="b">
         <v>0</v>
       </c>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>['aaditsh', 'emiratesislamic']</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>8h</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Apr 16, 2026 · 10:59 AM UTC</t>
+          <t>Apr 16, 2026 · 5:38 PM UTC</t>
         </is>
       </c>
       <c r="P47" s="2" t="n">
-        <v>46128.45763888889</v>
+        <v>46128.73472222222</v>
       </c>
       <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>['https://x.com/emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="R47" t="inlineStr"/>
       <c r="S47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
         <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>5653</v>
+        <v>13</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
@@ -8086,14 +8080,22 @@
         </is>
       </c>
       <c r="X47" t="inlineStr">
+        <is>
+          <t>Grab screenshots of when they have called you and the following messages include that to your complaint to UAECB and they will fine the bank</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>https://x.com/RakeshMavath/status/2044832798670995759</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
         <is>
           <t>@emiratesislamic probably the worst customer experience I’ve had in my life.
 Tried cancelling my cards. Have received 10+ phone calls from them trying to retain. Confirmed each time that I want to cancel (on call and on email confirmation). It’s been 4-5 months since I raised this complaint. No resolution yet.
 Impressed with how difficult they make this process. Wow!</t>
         </is>
       </c>
-      <c r="Y47" t="inlineStr"/>
-      <c r="Z47" t="inlineStr"/>
       <c r="AA47" t="inlineStr">
         <is>
           <t>@emiratesislamic probably the worst customer experience I’ve had in my life.
@@ -8117,7 +8119,7 @@
         </is>
       </c>
       <c r="AE47" s="2" t="n">
-        <v>46128.62430555555</v>
+        <v>46128.90138888889</v>
       </c>
       <c r="AF47" s="2" t="n">
         <v>46128</v>
@@ -8147,7 +8149,7 @@
       </c>
       <c r="AL47" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>aaditsh, emiratesislamic</t>
         </is>
       </c>
     </row>
@@ -8157,43 +8159,45 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2044734739718824109</t>
+          <t>2044759599656689929</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044734739718824109</t>
+          <t>https://x.com/aaditsh/status/2044759599656689929</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/aaditsh</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>aaditsh</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Aadit Sheth</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1989274279947694081/ggQkOhbP_bigger.jpg</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+          <t>Will do! So frustrating. They will call me, I’ll pick up. They will end the call within 10 seconds and message me “we called you. You didn’t pick up”.
+And it’s been extended like this for the past 4-5 months. What a joke.</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+          <t>Will do! So frustrating. They will call me, I’ll pick up. They will end the call within 10 seconds and message me “we called you. You didn’t pick up”.
+And it’s been extended like this for the past 4-5 months. What a joke.</t>
         </is>
       </c>
       <c r="K48" t="b">
@@ -8202,35 +8206,35 @@
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>['alsajwani1']</t>
+          <t>['RakeshMavath', 'emiratesislamic']</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Apr 16, 2026 · 11:08 AM UTC</t>
+          <t>Apr 16, 2026 · 12:47 PM UTC</t>
         </is>
       </c>
       <c r="P48" s="2" t="n">
-        <v>46128.46388888889</v>
+        <v>46128.53263888889</v>
       </c>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T48" t="n">
         <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V48" t="n">
-        <v>3</v>
+        <v>140</v>
       </c>
       <c r="W48" t="inlineStr">
         <is>
@@ -8239,19 +8243,22 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+          <t>Will do! So frustrating. They will call me, I’ll pick up. They will end the call within 10 seconds and message me “we called you. You didn’t pick up”.
+And it’s been extended like this for the past 4-5 months. What a joke.</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+          <t>Will do! So frustrating. They will call me, I’ll pick up. They will end the call within 10 seconds and message me “we called you. You didn’t pick up”.
+And it’s been extended like this for the past 4-5 months. What a joke.</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>Hello, we are sorry to hear about your experience! Our team is committed to addressing this matter immediately. To protect your privacy, we will contact you via private messages to assist you better. Your satisfaction is our priority.</t>
+          <t>Will do! So frustrating. They will call me, I’ll pick up. They will end the call within 10 seconds and message me “we called you. You didn’t pick up”. 
+And it’s been like this for the past 4-5 months. What a joke.</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -8265,7 +8272,7 @@
         </is>
       </c>
       <c r="AE48" s="2" t="n">
-        <v>46128.63055555556</v>
+        <v>46128.69930555556</v>
       </c>
       <c r="AF48" s="2" t="n">
         <v>46128</v>
@@ -8282,7 +8289,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>To protect your privacy, we will contact you via private messages to assist you better. • Our team is committed to addressing this matter immediately. • Hello, we are sorry to hear about your experience!</t>
+          <t>They will end the call within 10 seconds and message me “we called you. • They will call me, I’ll pick up. • And it’s been like this for the past 4-5 months.</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
@@ -8295,7 +8302,7 @@
       </c>
       <c r="AL48" t="inlineStr">
         <is>
-          <t>alsajwani1</t>
+          <t>RakeshMavath, emiratesislamic</t>
         </is>
       </c>
     </row>
@@ -8305,43 +8312,49 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2044781883184316706</t>
+          <t>2044734739718824109</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://x.com/huss23/status/2044781883184316706</t>
+          <t>https://x.com/emiratesislamic/status/2044734739718824109</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://x.com/huss23</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>huss23</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Huss</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2691682144/840d131cc8397f1c15b0a611bec833b2_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>I had the same issue. @emiratesislamic has the worst Customer service centre and its literally unreachable and unreliable. After 2 years of request, they still haven’t cancelled my Credit card.</t>
+          <t>@emiratesislamic 
+السلام عليكم
+زرت فرع 06 مول يوم الثلاثاء الماضى من اجل كسر الوديعة ودفع مبلغ القرض المتبقي علي
+أخبرتني الموظفة المحترمة بانه سوف يتم إرسال أميل الى الإدارة  لمعرفة الخطوات
+والى اليوم الخميس الإدارة لم ترد عليهم 
+هل هذ التأخير له مبرر
+او عدم هو اهتمام بالعملاء</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>I had the same issue. &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; has the worst Customer service centre and its literally unreachable and unreliable. After 2 years of request, they still haven’t cancelled my Credit card.</t>
+          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
         </is>
       </c>
       <c r="K49" t="b">
@@ -8350,39 +8363,35 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>['aaditsh']</t>
+          <t>['alsajwani1']</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>12h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Apr 16, 2026 · 2:16 PM UTC</t>
+          <t>Apr 16, 2026 · 11:08 AM UTC</t>
         </is>
       </c>
       <c r="P49" s="2" t="n">
-        <v>46128.59444444445</v>
+        <v>46128.46388888889</v>
       </c>
       <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t>['https://x.com/emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="R49" t="inlineStr"/>
       <c r="S49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
         <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>88</v>
+        <v>3</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
@@ -8391,19 +8400,39 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>I had the same issue. @emiratesislamic has the worst Customer service centre and its literally unreachable and unreliable. After 2 years of request, they still haven’t cancelled my Credit card.</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr"/>
-      <c r="Z49" t="inlineStr"/>
+          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044734739718824109</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>@emiratesislamic 
+السلام عليكم
+زرت فرع 06 مول يوم الثلاثاء الماضى من اجل كسر الوديعة ودفع مبلغ القرض المتبقي علي
+أخبرتني الموظفة المحترمة بانه سوف يتم إرسال أميل الى الإدارة  لمعرفة الخطوات
+والى اليوم الخميس الإدارة لم ترد عليهم 
+هل هذ التأخير له مبرر
+او عدم هو اهتمام بالعملاء</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>I had the same issue. @emiratesislamic has the worst Customer service centre and its literally unreachable and unreliable. After 2 years of request, they still haven’t cancelled my Credit card.</t>
+          <t>@emiratesislamic 
+السلام عليكم
+زرت فرع 06 مول يوم الثلاثاء الماضى من اجل كسر الوديعة ودفع مبلغ القرض المتبقي علي
+أخبرتني الموظفة المحترمة بانه سوف يتم إرسال أميل الى الإدارة  لمعرفة الخطوات
+والى اليوم الخميس الإدارة لم ترد عليهم 
+هل هذ التأخير له مبرر
+او عدم هو اهتمام بالعملاء</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>I had the same issue. Emirates Islamic has the worst customer service center and it's literally unreachable and unreliable. After 2 years of requests, they still haven’t canceled my credit card.</t>
+          <t>Peace be upon you. I visited branch 06 at the mall last Tuesday to break the deposit and pay the remaining loan amount. The respectful employee informed me that an email would be sent to the management to find out the steps, and as of today, Thursday, the management has not responded to them. Is this delay justified or a lack of concern for customers?</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -8417,7 +8446,7 @@
         </is>
       </c>
       <c r="AE49" s="2" t="n">
-        <v>46128.76111111111</v>
+        <v>46128.63055555556</v>
       </c>
       <c r="AF49" s="2" t="n">
         <v>46128</v>
@@ -8434,7 +8463,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Emirates Islamic has the worst customer service center and it's literally unreachable and unreliable. • After 2 years of requests, they still haven’t canceled my credit card.</t>
+          <t>The respectful employee informed me that an email would be sent to the management to find out the steps, and as of today, Thursday, the management has not responded to them. • I visited branch 06 at the mall last Tuesday to break the deposit and pay the remaining loan amount. • Is this delay justified or a lack of concern for customers?</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
@@ -8447,7 +8476,7 @@
       </c>
       <c r="AL49" t="inlineStr">
         <is>
-          <t>aaditsh</t>
+          <t>alsajwani1</t>
         </is>
       </c>
     </row>
@@ -8457,36 +8486,196 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2044777257898578369</t>
+          <t>2044781883184316706</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://x.com/mohamed50575321/status/2044777257898578369</t>
+          <t>https://x.com/huss23/status/2044781883184316706</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://x.com/mohamed50575321</t>
+          <t>https://x.com/huss23</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>mohamed50575321</t>
+          <t>huss23</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Alaa</t>
+          <t>Huss</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1651667220303429632/pOQsNF9e_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/2691682144/840d131cc8397f1c15b0a611bec833b2_bigger.png</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
+        <is>
+          <t>@aaditsh @emiratesislamic I had the same issue. @emiratesislamic has the worst Customer service centre and its literally unreachable and unreliable. After 2 years of request, they still haven’t cancelled my Credit card.</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>I had the same issue. &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; has the worst Customer service centre and its literally unreachable and unreliable. After 2 years of request, they still haven’t cancelled my Credit card.</t>
+        </is>
+      </c>
+      <c r="K50" t="b">
+        <v>0</v>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>['aaditsh']</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>12h</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Apr 16, 2026 · 2:16 PM UTC</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="n">
+        <v>46128.59444444445</v>
+      </c>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>['https://x.com/emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="S50" t="n">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
+      </c>
+      <c r="V50" t="n">
+        <v>88</v>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>I had the same issue. @emiratesislamic has the worst Customer service centre and its literally unreachable and unreliable. After 2 years of request, they still haven’t cancelled my Credit card.</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>https://x.com/huss23/status/2044781883184316706</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>@aaditsh @emiratesislamic I had the same issue. @emiratesislamic has the worst Customer service centre and its literally unreachable and unreliable. After 2 years of request, they still haven’t cancelled my Credit card.</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>@aaditsh @emiratesislamic I had the same issue. @emiratesislamic has the worst Customer service centre and its literally unreachable and unreliable. After 2 years of request, they still haven’t cancelled my Credit card.</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>I had the same issue. Emirates Islamic has the worst customer service center and it's literally unreachable and unreliable. After 2 years of requests, they still haven’t canceled my credit card.</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AE50" s="2" t="n">
+        <v>46128.76111111111</v>
+      </c>
+      <c r="AF50" s="2" t="n">
+        <v>46128</v>
+      </c>
+      <c r="AG50" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>2. Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>Emirates Islamic has the worst customer service center and it's literally unreachable and unreliable. • After 2 years of requests, they still haven’t canceled my credit card.</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>Emirates Islamic Bank (EIB)</t>
+        </is>
+      </c>
+      <c r="AK50" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL50" t="inlineStr">
+        <is>
+          <t>aaditsh</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2044777257898578369</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://x.com/mohamed50575321/status/2044777257898578369</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://x.com/mohamed50575321</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>mohamed50575321</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Alaa</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1651667220303429632/pOQsNF9e_bigger.png</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
         <is>
           <t>@EmiratesNBD_SA
 حدد visa campain
@@ -8497,7 +8686,7 @@
 طريقه احتيال يجب فيها التحقيق</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; تواصلت مع visa airport campain
 و اكدوا عدم خصم اى رسوم من قبلهم
@@ -8506,48 +8695,48 @@
 لانه البنك الوحيد اللى فعل هذا</t>
         </is>
       </c>
-      <c r="K50" t="b">
-        <v>0</v>
-      </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr">
+      <c r="K51" t="b">
+        <v>0</v>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
         <is>
           <t>12h</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>Apr 16, 2026 · 1:57 PM UTC</t>
         </is>
       </c>
-      <c r="P50" s="2" t="n">
+      <c r="P51" s="2" t="n">
         <v>46128.58125</v>
       </c>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr">
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr">
         <is>
           <t>['https://x.com/EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="S50" t="n">
+      <c r="S51" t="n">
         <v>1</v>
       </c>
-      <c r="T50" t="n">
-        <v>0</v>
-      </c>
-      <c r="U50" t="n">
-        <v>0</v>
-      </c>
-      <c r="V50" t="n">
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" t="n">
         <v>11</v>
       </c>
-      <c r="W50" t="inlineStr">
+      <c r="W51" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>@EmiratesNBD_AE تواصلت مع visa airport campain
 و اكدوا عدم خصم اى رسوم من قبلهم
@@ -8556,12 +8745,12 @@
 لانه البنك الوحيد اللى فعل هذا</t>
         </is>
       </c>
-      <c r="Y50" t="inlineStr">
+      <c r="Y51" t="inlineStr">
         <is>
           <t>https://x.com/mohamed50575321/status/2044777257898578369</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
+      <c r="Z51" t="inlineStr">
         <is>
           <t>@EmiratesNBD_SA
 حدد visa campain
@@ -8572,7 +8761,7 @@
 طريقه احتيال يجب فيها التحقيق</t>
         </is>
       </c>
-      <c r="AA50" t="inlineStr">
+      <c r="AA51" t="inlineStr">
         <is>
           <t>@EmiratesNBD_SA
 حدد visa campain
@@ -8583,171 +8772,24 @@
 طريقه احتيال يجب فيها التحقيق</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>The visa campaign requires spending $100 to access the lounges, making the card valid for 90 days for entry. Meanwhile, Emirates NBD Saudi Arabia has imposed its own condition of spending 3,000 riyals in the same month. Additionally, the bank charged me a fee of $32 without justification. This is a fraudulent practice that needs to be investigated.</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>Emirates NBD_SA
+The visa campaign requires spending $100 to access the lounges, making the card valid for 90 days for lounge entry. Meanwhile, Emirates NBD Saudi Arabia has imposed its own condition of spending 3,000 riyals in the same month. Additionally, the bank charged me a fee of $32 without justification. This is a fraudulent practice that needs to be investigated.</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
         <is>
           <t>Cust</t>
         </is>
       </c>
-      <c r="AD50" t="inlineStr">
+      <c r="AD51" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="AE50" s="2" t="n">
+      <c r="AE51" s="2" t="n">
         <v>46128.74791666667</v>
-      </c>
-      <c r="AF50" s="2" t="n">
-        <v>46128</v>
-      </c>
-      <c r="AG50" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>Meanwhile, Emirates NBD Saudi Arabia has imposed its own condition of spending 3,000 riyals in the same month. • The visa campaign requires spending $100 to access the lounges, making the card valid for 90 days for entry. • Additionally, the bank charged me a fee of $32 without justification.</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AK50" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL50" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="n">
-        <v>49</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2044676172248690733</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>https://x.com/msa3474/status/2044676172248690733</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>https://x.com/msa3474</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>msa3474</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>AHMARI</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1943001907854802944/sB6fjZIf_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>السلام عليكم ورحمه الله وبركاته الساده بنك الإمارات دبي الوطني المحترمين الرجاء حل مشكلتي مع فرع شارع الامير سلطان بجدة حيث انني طلبت منهم إيصال سداد مديونية ولي الى الآن اسبوع كامل لم يصلني الرد.</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>السلام عليكم ورحمه الله وبركاته الساده بنك الإمارات دبي الوطني المحترمين الرجاء حل مشكلتي مع فرع شارع الامير سلطان بجدة حيث انني طلبت منهم إيصال سداد مديونية ولي الى الآن اسبوع كامل لم يصلني الرد.</t>
-        </is>
-      </c>
-      <c r="K51" t="b">
-        <v>0</v>
-      </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_KSA']</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>19h</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>Apr 16, 2026 · 7:16 AM UTC</t>
-        </is>
-      </c>
-      <c r="P51" s="2" t="n">
-        <v>46128.30277777778</v>
-      </c>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="n">
-        <v>1</v>
-      </c>
-      <c r="T51" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" t="n">
-        <v>71</v>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>السلام عليكم ورحمه الله وبركاته الساده بنك الإمارات دبي الوطني المحترمين الرجاء حل مشكلتي مع فرع شارع الامير سلطان بجدة حيث انني طلبت منهم إيصال سداد مديونية ولي الى الآن اسبوع كامل لم يصلني الرد.</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr"/>
-      <c r="Z51" t="inlineStr"/>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>السلام عليكم ورحمه الله وبركاته الساده بنك الإمارات دبي الوطني المحترمين الرجاء حل مشكلتي مع فرع شارع الامير سلطان بجدة حيث انني طلبت منهم إيصال سداد مديونية ولي الى الآن اسبوع كامل لم يصلني الرد.</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>Peace be upon you. Dear respected Emirates NBD Bank, please resolve my issue with the Prince Sultan Street branch in Jeddah, as I requested a payment receipt for my debt and have not received a response for a whole week.</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD51" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="AE51" s="2" t="n">
-        <v>46128.46944444445</v>
       </c>
       <c r="AF51" s="2" t="n">
         <v>46128</v>
@@ -8764,7 +8806,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Peace be upon you. Dear respected Emirates NBD Bank, please resolve my issue with the Prince Sultan Street branch in Jed…</t>
+          <t>Emirates NBD_SA The visa campaign requires spending $100 to access the lounges, making the card valid for 90 days for lounge entry. • Meanwhile, Emirates NBD Saudi Arabia has imposed its own condition of spending 3,000 riyals in the same month. • Additionally, the bank charged me a fee of $32 without justification.</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
@@ -8776,6 +8818,154 @@
         <v>2026</v>
       </c>
       <c r="AL51" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2044676172248690733</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://x.com/msa3474/status/2044676172248690733</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://x.com/msa3474</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>msa3474</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>AHMARI</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1943001907854802944/sB6fjZIf_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>السلام عليكم ورحمه الله وبركاته الساده بنك الإمارات دبي الوطني المحترمين الرجاء حل مشكلتي مع فرع شارع الامير سلطان بجدة حيث انني طلبت منهم إيصال سداد مديونية ولي الى الآن اسبوع كامل لم يصلني الرد.</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>السلام عليكم ورحمه الله وبركاته الساده بنك الإمارات دبي الوطني المحترمين الرجاء حل مشكلتي مع فرع شارع الامير سلطان بجدة حيث انني طلبت منهم إيصال سداد مديونية ولي الى الآن اسبوع كامل لم يصلني الرد.</t>
+        </is>
+      </c>
+      <c r="K52" t="b">
+        <v>0</v>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>19h</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Apr 16, 2026 · 7:16 AM UTC</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="n">
+        <v>46128.30277777778</v>
+      </c>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="n">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" t="n">
+        <v>71</v>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>السلام عليكم ورحمه الله وبركاته الساده بنك الإمارات دبي الوطني المحترمين الرجاء حل مشكلتي مع فرع شارع الامير سلطان بجدة حيث انني طلبت منهم إيصال سداد مديونية ولي الى الآن اسبوع كامل لم يصلني الرد.</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>السلام عليكم ورحمه الله وبركاته الساده بنك الإمارات دبي الوطني المحترمين الرجاء حل مشكلتي مع فرع شارع الامير سلطان بجدة حيث انني طلبت منهم إيصال سداد مديونية ولي الى الآن اسبوع كامل لم يصلني الرد.</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>Peace be upon you. Dear Emirates NBD Bank, I kindly request your assistance in resolving my issue with the Prince Sultan Street branch in Jeddah, as I requested a payment receipt for my debt and have not received a response for a full week.</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AE52" s="2" t="n">
+        <v>46128.46944444445</v>
+      </c>
+      <c r="AF52" s="2" t="n">
+        <v>46128</v>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Peace be upon you. Dear Emirates NBD Bank, I kindly request your assistance in resolving my issue with the Prince Sultan…</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK52" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL52" t="inlineStr">
         <is>
           <t>EmiratesNBD_KSA</t>
         </is>

--- a/check2.xlsx
+++ b/check2.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL29"/>
+  <dimension ref="A1:AL22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,217 +625,36 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2045277395985526953</t>
+          <t>2046061240511082734</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/InnerSunshine9/status/2045277395985526953</t>
+          <t>https://x.com/she7ii88/status/2046061240511082734</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/InnerSunshine9</t>
+          <t>https://x.com/she7ii88</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>InnerSunshine9</t>
+          <t>she7ii88</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>InnerSunshine</t>
+          <t>Rashed Sem</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1988072486542733312/nEKgrRmJ_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1752368468144316416/8qdE3N-C_bigger.png</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
-        <is>
-          <t>Animated Kindness Video, share!
-CGI Animated Short Film: "Mr Indifferent" by Aryasb Feiz | CGMeetup
-https://t.co/jqAIbUi4ot
-Made for Emirates NBD Bank.
-Agency: Leo Burnett, Dubai
-Celebrating World Kindness Day</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Animated Kindness Video, share!
-CGI Animated Short Film: &amp;#34;Mr Indifferent&amp;#34; by Aryasb Feiz | CGMeetup
-&lt;a href="https://invidious.tiekoetter.com/watch?v=qLGNj-xrgvY"&gt;invidious.tiekoetter.com/watch?v=qLGNj-xr…&lt;/a&gt;
-Made for Emirates NBD Bank.
-Agency: Leo Burnett, Dubai
-Celebrating World Kindness Day</t>
-        </is>
-      </c>
-      <c r="K2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>4h</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Apr 17, 2026 · 11:05 PM UTC</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="n">
-        <v>46129.96180555555</v>
-      </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>['https://invidious.tiekoetter.com/watch?v=qLGNj-xrgvY']</t>
-        </is>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>20</v>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>Animated Kindness Video, share!
-CGI Animated Short Film: "Mr Indifferent" by Aryasb Feiz | CGMeetup
-invidious.tiekoetter.com/watch?v=qLGNj-xr…
-Made for Emirates NBD Bank.
-Agency: Leo Burnett, Dubai
-Celebrating World Kindness Day</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>https://x.com/InnerSunshine9/status/2045277395985526953</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Animated Kindness Video, share!
-CGI Animated Short Film: "Mr Indifferent" by Aryasb Feiz | CGMeetup
-https://t.co/jqAIbUi4ot
-Made for Emirates NBD Bank.
-Agency: Leo Burnett, Dubai
-Celebrating World Kindness Day</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Animated Kindness Video, share!
-CGI Animated Short Film: "Mr Indifferent" by Aryasb Feiz | CGMeetup
-https://t.co/jqAIbUi4ot
-Made for Emirates NBD Bank.
-Agency: Leo Burnett, Dubai
-Celebrating World Kindness Day</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Animated Kindness Video, share! CGI Animated Short Film: "Mr Indifferent" by Aryasb Feiz | CGMeetup Made for Emirates NBD Bank. Agency: Leo Burnett, Dubai Celebrating World Kindness Day</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Cust</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="AE2" s="2" t="n">
-        <v>46130.12847222222</v>
-      </c>
-      <c r="AF2" s="2" t="n">
-        <v>46130</v>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>CGI Animated Short Film: "Mr Indifferent" by Aryasb Feiz | CGMeetup Made for Emirates NBD Bank. • Agency: Leo Burnett, Dubai Celebrating World Kindness Day • Animated Kindness Video, share!</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>Emirates NBD Bank (ENBD)</t>
-        </is>
-      </c>
-      <c r="AK2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2045251200086663547</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>https://x.com/xmn9oori/status/2045251200086663547</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>https://x.com/xmn9oori</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>xmn9oori</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>بوسلطان 💜</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2034089445235036165/s553Bp_u_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
         <is>
           <t>ندعم من يحمون الوطن
 مجموعة من مزايا الدعم المالي والخدمات المصرفية المخصصة للعاملين في الصفوف الأمامية
@@ -849,63 +668,67 @@
 https://t.co/I7DGlib9vt</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>لمدة كم الاسترداد؟</t>
-        </is>
-      </c>
-      <c r="K3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>هذا عرض صدق ؟! 
+٦% ؟! سلامات البنوك الاسلاميه المرابحه الثابته ٢.٧% ؟! 
+ولو سمحتوا علم الامارات و لبس القوات المسلحه ... ليست دعايه</t>
+        </is>
+      </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>6h</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Apr 17, 2026 · 9:20 PM UTC</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="n">
-        <v>46129.88888888889</v>
-      </c>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>70</v>
-      </c>
-      <c r="W3" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 2:59 AM UTC</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>46132.12430555555</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>11</v>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>لمدة كم الاسترداد؟</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>https://x.com/xmn9oori/status/2045251200086663547</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>هذا عرض صدق ؟! 
+٦% ؟! سلامات البنوك الاسلاميه المرابحه الثابته ٢.٧% ؟! 
+ولو سمحتوا علم الامارات و لبس القوات المسلحه ... ليست دعايه</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>https://x.com/she7ii88/status/2046061240511082734</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>ندعم من يحمون الوطن
 مجموعة من مزايا الدعم المالي والخدمات المصرفية المخصصة للعاملين في الصفوف الأمامية
@@ -919,7 +742,7 @@
 https://t.co/I7DGlib9vt</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>ندعم من يحمون الوطن
 مجموعة من مزايا الدعم المالي والخدمات المصرفية المخصصة للعاملين في الصفوف الأمامية
@@ -933,7 +756,7 @@
 https://t.co/I7DGlib9vt</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>We support those who protect the homeland
 A range of financial support and banking services dedicated to frontline workers
@@ -946,6 +769,167 @@
 Terms and conditions apply.</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Cust</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AE2" s="2" t="n">
+        <v>46132.29097222222</v>
+      </c>
+      <c r="AF2" s="2" t="n">
+        <v>46132</v>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>1. Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Terms and conditions apply.</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>Emirates NBD Bank (ENBD)</t>
+        </is>
+      </c>
+      <c r="AK2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2046033950339166455</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://x.com/Kyodonews_JBN/status/2046033950339166455</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://x.com/Kyodonews_JBN</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Kyodonews_JBN</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>KYODONEWS JBN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2003285704613462020/Gn9wk2B__bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Emirates NBD、Dar Global向け2億5,000万米ドルのシンジケート・タームローンを実行し、世界的な成長と事業拡大を加速【Dar Global】
+https://t.co/H82MnfRa04</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Emirates NBD、Dar Global向け2億5,000万米ドルのシンジケート・タームローンを実行し、世界的な成長と事業拡大を加速【Dar Global】
+&lt;a href="https://kyodonewsprwire.jp/release/202604177681"&gt;kyodonewsprwire.jp/release/2…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2h</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 1:11 AM UTC</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>46132.04930555556</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>['https://kyodonewsprwire.jp/release/202604177681']</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>4</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Emirates NBD、Dar Global向け2億5,000万米ドルのシンジケート・タームローンを実行し、世界的な成長と事業拡大を加速【Dar Global】
+kyodonewsprwire.jp/release/2…</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>https://x.com/Kyodonews_JBN/status/2046033950339166455</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Emirates NBD、Dar Global向け2億5,000万米ドルのシンジケート・タームローンを実行し、世界的な成長と事業拡大を加速【Dar Global】
+https://t.co/H82MnfRa04</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Emirates NBD、Dar Global向け2億5,000万米ドルのシンジケート・タームローンを実行し、世界的な成長と事業拡大を加速【Dar Global】
+https://t.co/H82MnfRa04</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Emirates NBD executed a $250 million syndicated term loan for Dar Global to accelerate global growth and business expansion.</t>
+        </is>
+      </c>
       <c r="AC3" t="inlineStr">
         <is>
           <t>Cust</t>
@@ -957,10 +941,10 @@
         </is>
       </c>
       <c r="AE3" s="2" t="n">
-        <v>46130.05555555555</v>
+        <v>46132.21597222222</v>
       </c>
       <c r="AF3" s="2" t="n">
-        <v>46130</v>
+        <v>46132</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
@@ -974,7 +958,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Terms and conditions apply.</t>
+          <t>Emirates NBD executed a $250 million syndicated term loan for Dar Global to accelerate global growth and business expansion.</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -987,7 +971,7 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -997,44 +981,48 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2045169182015139851</t>
+          <t>2045894623957278735</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/MC81236843/status/2045169182015139851</t>
+          <t>https://x.com/almidfa75/status/2045894623957278735</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://x.com/MC81236843</t>
+          <t>https://x.com/almidfa75</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MC81236843</t>
+          <t>almidfa75</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>M C</t>
+          <t>Faisal Al Midfa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1163517530822119426/IK5LwgTg_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/692030305365000192/rYQ6PWnr_bigger.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>🤫🤫🤫😉</t>
+          <t>🧵 1/
+في خطوة تعكس تطور المنتجات المالية في السوق العقاري بدولة الإمارات، أعلن بنك Emirates NBD عن إطلاق نموذج تمويل مبكر للعقارات قيد الإنشاء (Off-plan)، بالتعاون مع Dubai Holding Real Estate.
+#دبي #القطاع_العقاري #التمويل https://t.co/qdzz3FJ7io</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Emirates NBD und Nium bündeln ihre Kräfte, um den globalen grenzüberschreitenden Zahlungsverkehr im Nahen Osten zu transformieren
-&lt;a href="https://www.worldfinanceinforms.com/cards-payments/emirates-nbd-and-nium-join-forces-to-transform-global-cross-border-payments-in-the-middle-east"&gt;worldfinanceinforms.com/card…&lt;/a&gt;</t>
+          <t>🧵 6/
+🎯 خلاصة:
+يمثل هذا الإعلان خطوة نوعية في تطوير حلول التمويل العقاري، ويعكس توجه المؤسسات المالية نحو تقديم منتجات أكثر مرونة تدعم نمو واستدامة السوق العقاري في دولة الإمارات.
+&lt;a href="/search?f=tweets&amp;amp;q=%23دبي"&gt;#دبي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التمويل_العقاري"&gt;#التمويل_العقاري&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23استثمار"&gt;#استثمار&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBD"&gt;#EmiratesNBD&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23DubaiHolding"&gt;#DubaiHolding&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K4" t="b">
@@ -1049,29 +1037,29 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 3:55 PM UTC</t>
+          <t>Apr 19, 2026 · 3:57 PM UTC</t>
         </is>
       </c>
       <c r="P4" s="2" t="n">
-        <v>46129.66319444445</v>
+        <v>46131.66458333333</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
-          <t>['https://www.worldfinanceinforms.com/cards-payments/emirates-nbd-and-nium-join-forces-to-transform-global-cross-border-payments-in-the-middle-east']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23دبي', 'https://x.com/search?f=tweets&amp;q=%23التمويل_العقاري', 'https://x.com/search?f=tweets&amp;q=%23استثمار', 'https://x.com/search?f=tweets&amp;q=%23EmiratesNBD', 'https://x.com/search?f=tweets&amp;q=%23DubaiHolding']</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>102</v>
+        <v>38</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -1080,28 +1068,34 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Emirates NBD und Nium bündeln ihre Kräfte, um den globalen grenzüberschreitenden Zahlungsverkehr im Nahen Osten zu transformieren
-worldfinanceinforms.com/card…</t>
+          <t>🧵 6/
+🎯 خلاصة:
+يمثل هذا الإعلان خطوة نوعية في تطوير حلول التمويل العقاري، ويعكس توجه المؤسسات المالية نحو تقديم منتجات أكثر مرونة تدعم نمو واستدامة السوق العقاري في دولة الإمارات.
+#دبي #التمويل_العقاري #استثمار #EmiratesNBD #DubaiHolding</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>https://x.com/MC81236843/status/2045169182015139851</t>
+          <t>https://x.com/almidfa75/status/2045894623957278735</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>🤫🤫🤫😉</t>
+          <t>🧵 1/
+في خطوة تعكس تطور المنتجات المالية في السوق العقاري بدولة الإمارات، أعلن بنك Emirates NBD عن إطلاق نموذج تمويل مبكر للعقارات قيد الإنشاء (Off-plan)، بالتعاون مع Dubai Holding Real Estate.
+#دبي #القطاع_العقاري #التمويل https://t.co/qdzz3FJ7io</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>🤫🤫🤫😉</t>
+          <t>🧵 1/
+في خطوة تعكس تطور المنتجات المالية في السوق العقاري بدولة الإمارات، أعلن بنك Emirates NBD عن إطلاق نموذج تمويل مبكر للعقارات قيد الإنشاء (Off-plan)، بالتعاون مع Dubai Holding Real Estate.
+#دبي #القطاع_العقاري #التمويل https://t.co/qdzz3FJ7io</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>The text does not contain any language to translate, as it consists solely of emojis.</t>
+          <t>In a move that reflects the evolution of financial products in the real estate market in the UAE, Emirates NBD Bank announced the launch of an early financing model for off-plan properties, in collaboration with Dubai Holding Real Estate.</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1111,14 +1105,14 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE4" s="2" t="n">
-        <v>46129.82986111111</v>
+        <v>46131.83125</v>
       </c>
       <c r="AF4" s="2" t="n">
-        <v>46129</v>
+        <v>46131</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
@@ -1132,7 +1126,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>The text does not contain any language to translate, as it consists solely of emojis.</t>
+          <t>In a move that reflects the evolution of financial products in the real estate market in the UAE, Emirates NBD Bank anno…</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1155,45 +1149,47 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2045169009662763334</t>
+          <t>2045894611756048610</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://x.com/MC81236843/status/2045169009662763334</t>
+          <t>https://x.com/almidfa75/status/2045894611756048610</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/MC81236843</t>
+          <t>https://x.com/almidfa75</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MC81236843</t>
+          <t>almidfa75</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>M C</t>
+          <t>Faisal Al Midfa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1163517530822119426/IK5LwgTg_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/692030305365000192/rYQ6PWnr_bigger.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank PJSC und Berbank of Russia beziehen sich auf die Ankündigung vom 30. Juni 2019 bezüglich der Genehmigung durch die Bankenaufsichtsbehörden in den Vereinigten Arabischen Emiraten, der Türkei, Österreich und Russland
-emiratesnbd.com/en/media-cen…</t>
+          <t>🧵 1/
+في خطوة تعكس تطور المنتجات المالية في السوق العقاري بدولة الإمارات، أعلن بنك Emirates NBD عن إطلاق نموذج تمويل مبكر للعقارات قيد الإنشاء (Off-plan)، بالتعاون مع Dubai Holding Real Estate.
+#دبي #القطاع_العقاري #التمويل</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank PJSC und Berbank of Russia beziehen sich auf die Ankündigung vom 30. Juni 2019 bezüglich der Genehmigung durch die Bankenaufsichtsbehörden in den Vereinigten Arabischen Emiraten, der Türkei, Österreich und Russland
-&lt;a href="https://www.emiratesnbd.com/en/media-center/completion-of-the-sale-and-purchase-of-9985-of-the-shares-in-denizbank-as-by-emirates-nbd-from-sberb"&gt;emiratesnbd.com/en/media-cen…&lt;/a&gt;</t>
+          <t>🧵 1/
+في خطوة تعكس تطور المنتجات المالية في السوق العقاري بدولة الإمارات، أعلن بنك Emirates NBD عن إطلاق نموذج تمويل مبكر للعقارات قيد الإنشاء (Off-plan)، بالتعاون مع Dubai Holding Real Estate.
+&lt;a href="/search?f=tweets&amp;amp;q=%23دبي"&gt;#دبي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23القطاع_العقاري"&gt;#القطاع_العقاري&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التمويل"&gt;#التمويل&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K5" t="b">
@@ -1208,29 +1204,29 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 3:54 PM UTC</t>
+          <t>Apr 19, 2026 · 3:57 PM UTC</t>
         </is>
       </c>
       <c r="P5" s="2" t="n">
-        <v>46129.6625</v>
+        <v>46131.66458333333</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
-          <t>['https://www.emiratesnbd.com/en/media-center/completion-of-the-sale-and-purchase-of-9985-of-the-shares-in-denizbank-as-by-emirates-nbd-from-sberb']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23دبي', 'https://x.com/search?f=tweets&amp;q=%23القطاع_العقاري', 'https://x.com/search?f=tweets&amp;q=%23التمويل']</t>
         </is>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
         <v>1</v>
       </c>
-      <c r="U5" t="n">
-        <v>3</v>
-      </c>
       <c r="V5" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -1239,21 +1235,23 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank PJSC und Berbank of Russia beziehen sich auf die Ankündigung vom 30. Juni 2019 bezüglich der Genehmigung durch die Bankenaufsichtsbehörden in den Vereinigten Arabischen Emiraten, der Türkei, Österreich und Russland
-emiratesnbd.com/en/media-cen…</t>
+          <t>🧵 1/
+في خطوة تعكس تطور المنتجات المالية في السوق العقاري بدولة الإمارات، أعلن بنك Emirates NBD عن إطلاق نموذج تمويل مبكر للعقارات قيد الإنشاء (Off-plan)، بالتعاون مع Dubai Holding Real Estate.
+#دبي #القطاع_العقاري #التمويل</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank PJSC und Berbank of Russia beziehen sich auf die Ankündigung vom 30. Juni 2019 bezüglich der Genehmigung durch die Bankenaufsichtsbehörden in den Vereinigten Arabischen Emiraten, der Türkei, Österreich und Russland
-emiratesnbd.com/en/media-cen…</t>
+          <t>🧵 1/
+في خطوة تعكس تطور المنتجات المالية في السوق العقاري بدولة الإمارات، أعلن بنك Emirates NBD عن إطلاق نموذج تمويل مبكر للعقارات قيد الإنشاء (Off-plan)، بالتعاون مع Dubai Holding Real Estate.
+#دبي #القطاع_العقاري #التمويل</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank PJSC and Sberbank of Russia refer to the announcement from June 30, 2019, regarding the approval by the banking regulatory authorities in the United Arab Emirates, Turkey, Austria, and Russia.</t>
+          <t>In a move that reflects the evolution of financial products in the real estate market in the UAE, Emirates NBD Bank announced the launch of an early financing model for off-plan properties, in collaboration with Dubai Holding Real Estate.</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1263,14 +1261,14 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE5" s="2" t="n">
-        <v>46129.82916666667</v>
+        <v>46131.83125</v>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>46129</v>
+        <v>46131</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
@@ -1284,7 +1282,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank PJSC and Sberbank of Russia refer to the announcement from June 30, 2019, regarding the approval by th…</t>
+          <t>In a move that reflects the evolution of financial products in the real estate market in the UAE, Emirates NBD Bank anno…</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1307,50 +1305,54 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2045166464181702828</t>
+          <t>2045881062304456946</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://x.com/MBS_20121/status/2045166464181702828</t>
+          <t>https://x.com/ThisMadEngineer/status/2045881062304456946</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://x.com/MBS_20121</t>
+          <t>https://x.com/ThisMadEngineer</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MBS_20121</t>
+          <t>ThisMadEngineer</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>A h m a d A l h ar b i</t>
+          <t>Ankesh / MadEngineer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1357665933368696832/CgwgbAyQ_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/677437091211530240/U61xnBOL_bigger.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA متى يتم دعم إضافة بطاقة مزيد الي قوقل باي Google pay</t>
+          <t>Thanks!</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>&lt;a href="/EmiratesNBD_KSA" title="Emirates NBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt; متى يتم دعم إضافة بطاقة مزيد الي قوقل باي Google pay</t>
+          <t>Thanks!</t>
         </is>
       </c>
       <c r="K6" t="b">
         <v>0</v>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>12h</t>
@@ -1358,20 +1360,16 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 3:44 PM UTC</t>
+          <t>Apr 19, 2026 · 3:03 PM UTC</t>
         </is>
       </c>
       <c r="P6" s="2" t="n">
-        <v>46129.65555555555</v>
+        <v>46131.62708333333</v>
       </c>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>['https://x.com/EmiratesNBD_KSA']</t>
-        </is>
-      </c>
+      <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1380,7 +1378,7 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>36</v>
+        <v>287</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1389,27 +1387,19 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA متى يتم دعم إضافة بطاقة مزيد الي قوقل باي Google pay</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>https://x.com/MBS_20121/status/2045166464181702828</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_KSA متى يتم دعم إضافة بطاقة مزيد الي قوقل باي Google pay</t>
-        </is>
-      </c>
+          <t>Thanks!</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA متى يتم دعم إضافة بطاقة مزيد الي قوقل باي Google pay</t>
+          <t>Thanks!</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>When will support for adding Mazid card to Google Pay be available?</t>
+          <t>Thank you!</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1423,10 +1413,10 @@
         </is>
       </c>
       <c r="AE6" s="2" t="n">
-        <v>46129.82222222222</v>
+        <v>46131.79375</v>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>46129</v>
+        <v>46131</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
@@ -1440,7 +1430,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>When will support for adding Mazid card to Google Pay be available?</t>
+          <t>Thank you!</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1453,7 +1443,7 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
     </row>
@@ -1463,49 +1453,43 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2045155322356961286</t>
+          <t>2045850840196694451</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_EGY/status/2045155322356961286</t>
+          <t>https://x.com/r35sk/status/2045850840196694451</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_EGY</t>
+          <t>https://x.com/r35sk</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>EmiratesNBD_EGY</t>
+          <t>r35sk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>ريم</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427526482108416/qjFPlJ1n_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1976063720942968832/0TB4sf0G_bigger.jpg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Your phone, Your smarter way to pay.
-Activate Apple Pay with your Emirates NBD cards in your Apple devices and enjoy fast, secure payments every day.
-Terms &amp;amp; Conditions Apply.
-Tax registration number: 204-897-319 https://t.co/uyaLjydHaw</t>
+          <t>الوداعيةةة https://t.co/p08tSNxQZ3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Your phone, Your smarter way to pay.
-Activate Apple Pay with your Emirates NBD cards in your Apple devices and enjoy fast, secure payments every day.
-Terms &amp;amp; Conditions Apply.
-Tax registration number: 204-897-319</t>
+          <t>الحمدلله الحمرا فيها صرافة enbd</t>
         </is>
       </c>
       <c r="K7" t="b">
@@ -1515,16 +1499,16 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 3:00 PM UTC</t>
+          <t>Apr 19, 2026 · 1:03 PM UTC</t>
         </is>
       </c>
       <c r="P7" s="2" t="n">
-        <v>46129.625</v>
+        <v>46131.54375</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
@@ -1538,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1547,53 +1531,44 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Your phone, Your smarter way to pay.
-Activate Apple Pay with your Emirates NBD cards in your Apple devices and enjoy fast, secure payments every day.
-Terms &amp; Conditions Apply.
-Tax registration number: 204-897-319</t>
+          <t>الحمدلله الحمرا فيها صرافة enbd</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_EGY/status/2045155322356961286</t>
+          <t>https://x.com/r35sk/status/2045850840196694451</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>Your phone, Your smarter way to pay.
-Activate Apple Pay with your Emirates NBD cards in your Apple devices and enjoy fast, secure payments every day.
-Terms &amp;amp; Conditions Apply.
-Tax registration number: 204-897-319 https://t.co/uyaLjydHaw</t>
+          <t>الوداعيةةة https://t.co/p08tSNxQZ3</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Your phone, Your smarter way to pay.
-Activate Apple Pay with your Emirates NBD cards in your Apple devices and enjoy fast, secure payments every day.
-Terms &amp;amp; Conditions Apply.
-Tax registration number: 204-897-319 https://t.co/uyaLjydHaw</t>
+          <t>الوداعيةةة https://t.co/p08tSNxQZ3</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Your phone, your smarter way to pay. Activate Apple Pay with your Emirates NBD cards on your Apple devices and enjoy fast, secure payments every day. Terms &amp; Conditions Apply. Tax registration number: 204-897-319</t>
+          <t>Farewell</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Cust</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE7" s="2" t="n">
-        <v>46129.79166666666</v>
+        <v>46131.71041666667</v>
       </c>
       <c r="AF7" s="2" t="n">
-        <v>46129</v>
+        <v>46131</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
@@ -1607,7 +1582,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Tax registration number: 204-897-319 • Activate Apple Pay with your Emirates NBD cards on your Apple devices and enjoy fast, secure payments every day. • Your phone, your smarter way to pay.</t>
+          <t>Farewell</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1630,49 +1605,43 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2045138554464915956</t>
+          <t>2045850184811422052</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://x.com/yallaweb/status/2045138554464915956</t>
+          <t>https://x.com/AhmedAlhaq79518/status/2045850184811422052</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://x.com/yallaweb</t>
+          <t>https://x.com/AhmedAlhaq79518</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>yallaweb</t>
+          <t>AhmedAlhaq79518</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>M.G.</t>
+          <t>Ahmed Alhaìqi</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1840606846068875264/V7l0ThZZ_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2015365820088803328/seUb2ZG5_bigger.jpg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>اطلعت اليوم على سير العمل في أول محطة للإقلاع والهبوط العمودي للتاكسي الجوي في دبي، الأولى من نوعها على مستوى العالم، والتي تم تنفيذها بالقرب من مطار دبي الدولي… المحطة جاهزة، وهي ضمن شبكة تشمل محطات في داون تاون ونخلة جميرا ومرسى دبي ستكون جاهزة مع نهاية العام الجاري. 
-ستخدم المحطة الأولى نحو 170 ألف راكب سنوياً، ووجهنا بتشغيل الخدمة وإطلاقها للجمهور خلال العام الجاري وفقاً لأرقى المعايير الدولية. 
-هذا المشروع خطوة مفصلية في مسيرة دبي نحو ريادة مستقبل التنقل الحضري عالمياً، واختصار الزمن وتقريب المسافات، ونشكر فريق هيئة الطرق والمواصلات والشركاء المحليين والعالميين على جهودهم في إنجاز هذا المشروع النوعي الذي يأتي تزامناً مع النسخة الأولى من اليوم العالمي للمواصلات العامة في 17 أبريل سنوياً.
-في دبي نحول الأفكار والطموحات إلى واقع ملموس… فدبي تجيد التحليق.</t>
+          <t>@EmiratesNBD_AE فعلا بنك مميز بمعني الكلمه والصقه بهم متوفره عندي علاجه.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>ابرؤا ذمتكم واعيدوا لنا ما سرقتموه من أموالنا لترضوا اسيادكم من حفدة القردة و الخنازير.
-&lt;a href="/search?f=tweets&amp;amp;q=%23الامارات"&gt;#الامارات&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23دبي"&gt;#دبي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23ابوظبي"&gt;#ابوظبي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23UAE"&gt;#UAE&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Dubai"&gt;#Dubai&lt;/a&gt;    
-&lt;a href="/search?f=tweets&amp;amp;q=%23AbuDhabi"&gt;#AbuDhabi&lt;/a&gt; &lt;a href="/HHShkMohd" title="HH Sheikh Mohammed"&gt;@HHShkMohd&lt;/a&gt; 
-&lt;a href="/MohamedBinZayed" title="محمد بن زايد"&gt;@MohamedBinZayed&lt;/a&gt; &lt;a href="/emirates" title="Emirates"&gt;@emirates&lt;/a&gt; &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; &lt;a href="/WPP" title="WPP"&gt;@WPP&lt;/a&gt;</t>
+          <t>فعلا بنك مميز بمعني الكلمه والصقه بهم متوفره عندي علاجه.</t>
         </is>
       </c>
       <c r="K8" t="b">
@@ -1681,28 +1650,24 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>['HamdanMohammed']</t>
+          <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 1:53 PM UTC</t>
+          <t>Apr 19, 2026 · 1:01 PM UTC</t>
         </is>
       </c>
       <c r="P8" s="2" t="n">
-        <v>46129.57847222222</v>
+        <v>46131.54236111111</v>
       </c>
       <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23الامارات', 'https://x.com/search?f=tweets&amp;q=%23دبي', 'https://x.com/search?f=tweets&amp;q=%23ابوظبي', 'https://x.com/search?f=tweets&amp;q=%23UAE', 'https://x.com/search?f=tweets&amp;q=%23Dubai', 'https://x.com/search?f=tweets&amp;q=%23AbuDhabi', 'https://x.com/HHShkMohd', 'https://x.com/MohamedBinZayed', 'https://x.com/emirates', 'https://x.com/EmiratesNBD_AE', 'https://x.com/WPP']</t>
-        </is>
-      </c>
+      <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
         <v>0</v>
       </c>
@@ -1710,10 +1675,10 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1722,39 +1687,27 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>ابرؤا ذمتكم واعيدوا لنا ما سرقتموه من أموالنا لترضوا اسيادكم من حفدة القردة و الخنازير.
-#الامارات #دبي #ابوظبي #UAE #Dubai    
-#AbuDhabi @HHShkMohd 
-@MohamedBinZayed @emirates @EmiratesNBD_AE @WPP</t>
+          <t>فعلا بنك مميز بمعني الكلمه والصقه بهم متوفره عندي علاجه.</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>https://x.com/yallaweb/status/2045138554464915956</t>
+          <t>https://x.com/AhmedAlhaq79518/status/2045850184811422052</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>اطلعت اليوم على سير العمل في أول محطة للإقلاع والهبوط العمودي للتاكسي الجوي في دبي، الأولى من نوعها على مستوى العالم، والتي تم تنفيذها بالقرب من مطار دبي الدولي… المحطة جاهزة، وهي ضمن شبكة تشمل محطات في داون تاون ونخلة جميرا ومرسى دبي ستكون جاهزة مع نهاية العام الجاري. 
-ستخدم المحطة الأولى نحو 170 ألف راكب سنوياً، ووجهنا بتشغيل الخدمة وإطلاقها للجمهور خلال العام الجاري وفقاً لأرقى المعايير الدولية. 
-هذا المشروع خطوة مفصلية في مسيرة دبي نحو ريادة مستقبل التنقل الحضري عالمياً، واختصار الزمن وتقريب المسافات، ونشكر فريق هيئة الطرق والمواصلات والشركاء المحليين والعالميين على جهودهم في إنجاز هذا المشروع النوعي الذي يأتي تزامناً مع النسخة الأولى من اليوم العالمي للمواصلات العامة في 17 أبريل سنوياً.
-في دبي نحول الأفكار والطموحات إلى واقع ملموس… فدبي تجيد التحليق.</t>
+          <t>@EmiratesNBD_AE فعلا بنك مميز بمعني الكلمه والصقه بهم متوفره عندي علاجه.</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>اطلعت اليوم على سير العمل في أول محطة للإقلاع والهبوط العمودي للتاكسي الجوي في دبي، الأولى من نوعها على مستوى العالم، والتي تم تنفيذها بالقرب من مطار دبي الدولي… المحطة جاهزة، وهي ضمن شبكة تشمل محطات في داون تاون ونخلة جميرا ومرسى دبي ستكون جاهزة مع نهاية العام الجاري. 
-ستخدم المحطة الأولى نحو 170 ألف راكب سنوياً، ووجهنا بتشغيل الخدمة وإطلاقها للجمهور خلال العام الجاري وفقاً لأرقى المعايير الدولية. 
-هذا المشروع خطوة مفصلية في مسيرة دبي نحو ريادة مستقبل التنقل الحضري عالمياً، واختصار الزمن وتقريب المسافات، ونشكر فريق هيئة الطرق والمواصلات والشركاء المحليين والعالميين على جهودهم في إنجاز هذا المشروع النوعي الذي يأتي تزامناً مع النسخة الأولى من اليوم العالمي للمواصلات العامة في 17 أبريل سنوياً.
-في دبي نحول الأفكار والطموحات إلى واقع ملموس… فدبي تجيد التحليق.</t>
+          <t>@EmiratesNBD_AE فعلا بنك مميز بمعني الكلمه والصقه بهم متوفره عندي علاجه.</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Today, I reviewed the progress of the first vertical takeoff and landing air taxi station in Dubai, the first of its kind in the world, which has been implemented near Dubai International Airport. The station is ready and is part of a network that includes stations in Downtown, Palm Jumeirah, and Dubai Marina, which will be ready by the end of this year.
-The first station will serve about 170,000 passengers annually, and we have directed the operation and launch of the service to the public this year according to the highest international standards.
-This project is a pivotal step in Dubai's journey towards leading the future of urban mobility globally, shortening travel time and bridging distances. We thank the team from the Roads and Transport Authority and our local and global partners for their efforts in completing this innovative project, which coincides with the first edition of World Public Transport Day on April 17 each year.
-In Dubai, we turn ideas and ambitions into tangible reality... for Dubai knows how to soar.</t>
+          <t>Emirates NBD is truly a distinguished bank in every sense of the word, and I have their sticker available for my treatment.</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1764,14 +1717,14 @@
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE8" s="2" t="n">
-        <v>46129.74513888889</v>
+        <v>46131.70902777778</v>
       </c>
       <c r="AF8" s="2" t="n">
-        <v>46129</v>
+        <v>46131</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
@@ -1785,7 +1738,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Today, I reviewed the progress of the first vertical takeoff and landing air taxi station in Dubai, the first of its kind in the world, which has been implemented near Dubai International Airport. • The first station will serve about 170,000 passengers annually, and we have directed the operation and launch of the service to the public this year according to the highest international standards. • The station is ready and is part of a network that includes stations in Downtown, Palm Jumeirah, and Dubai Marina, which will be ready by the end of this year.</t>
+          <t>Emirates NBD is truly a distinguished bank in every sense of the word, and I have their sticker available for my treatment.</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1798,7 +1751,7 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>HamdanMohammed</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
     </row>
@@ -1808,43 +1761,47 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2045130309323071836</t>
+          <t>2045821589539733783</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://x.com/dar_global/status/2045130309323071836</t>
+          <t>https://x.com/CWSaudi/status/2045821589539733783</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://x.com/dar_global</t>
+          <t>https://x.com/CWSaudi</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>dar_global</t>
+          <t>CWSaudi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>DarGlobal</t>
+          <t>Construction Week Saudi</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1904290533372985344/OQZ0hS5Q_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1494269682098089989/5bK0V1be_bigger.jpg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Emirates NBD successfully executes USD 250 Million Syndicated Term Loan facility for Dar Global, Accelerating Global Growth and Expansion bebeez.eu/2026/04/16/emirate…</t>
+          <t>#SaudiArabia extends the Landbridge rail bid deadline to April 29 as #Hormuz disruptions highlight its lack of a direct east–west freight rail link.
+Read more ll
+https://t.co/UvrhC24nWJ</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Emirates NBD successfully executes USD 250 Million Syndicated Term Loan facility for Dar Global, Accelerating Global Growth and Expansion &lt;a href="https://bebeez.eu/2026/04/16/emirates-nbd-successfully-executes-usd-250-million-syndicated-term-loan-facility-for-dar-global-accelerating-global-growth-and-expansion/"&gt;bebeez.eu/2026/04/16/emirate…&lt;/a&gt;</t>
+          <t>. &lt;a href="/dar_global" title="DarGlobal"&gt;@dar_global&lt;/a&gt;  has secured a $250M loan arranged by &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; , as the &lt;a href="/search?f=tweets&amp;amp;q=%23London"&gt;#London&lt;/a&gt; -listed developer behind &lt;a href="/realDonaldTrump" title="Donald J. Trump"&gt;@realDonaldTrump&lt;/a&gt; -branded projects expands its pipeline.
+Read more:
+&lt;a href="https://www.constructionweeksaudi.com/business/real-estate-darglobal-trump"&gt;constructionweeksaudi.com/bu…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K9" t="b">
@@ -1854,21 +1811,21 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 1:20 PM UTC</t>
+          <t>Apr 19, 2026 · 11:07 AM UTC</t>
         </is>
       </c>
       <c r="P9" s="2" t="n">
-        <v>46129.55555555555</v>
+        <v>46131.46319444444</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
-          <t>['https://bebeez.eu/2026/04/16/emirates-nbd-successfully-executes-usd-250-million-syndicated-term-loan-facility-for-dar-global-accelerating-global-growth-and-expansion/']</t>
+          <t>['https://x.com/dar_global', 'https://x.com/EmiratesNBD_AE', 'https://x.com/search?f=tweets&amp;q=%23London', 'https://x.com/realDonaldTrump', 'https://www.constructionweeksaudi.com/business/real-estate-darglobal-trump']</t>
         </is>
       </c>
       <c r="S9" t="n">
@@ -1881,7 +1838,7 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1890,19 +1847,33 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Emirates NBD successfully executes USD 250 Million Syndicated Term Loan facility for Dar Global, Accelerating Global Growth and Expansion bebeez.eu/2026/04/16/emirate…</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
+          <t>. @dar_global  has secured a $250M loan arranged by @EmiratesNBD_AE , as the #London -listed developer behind @realDonaldTrump -branded projects expands its pipeline.
+Read more:
+constructionweeksaudi.com/bu…</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>https://x.com/CWSaudi/status/2045821589539733783</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>#SaudiArabia extends the Landbridge rail bid deadline to April 29 as #Hormuz disruptions highlight its lack of a direct east–west freight rail link.
+Read more ll
+https://t.co/UvrhC24nWJ</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Emirates NBD successfully executes USD 250 Million Syndicated Term Loan facility for Dar Global, Accelerating Global Growth and Expansion bebeez.eu/2026/04/16/emirate…</t>
+          <t>#SaudiArabia extends the Landbridge rail bid deadline to April 29 as #Hormuz disruptions highlight its lack of a direct east–west freight rail link.
+Read more ll
+https://t.co/UvrhC24nWJ</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Emirates NBD successfully executes a USD 250 million syndicated term loan facility for Dar Global, accelerating global growth and expansion.</t>
+          <t>Saudi Arabia extends the Landbridge rail bid deadline to April 29 as Hormuz disruptions highlight its lack of a direct east–west freight rail link.</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1912,14 +1883,14 @@
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE9" s="2" t="n">
-        <v>46129.72222222222</v>
+        <v>46131.62986111111</v>
       </c>
       <c r="AF9" s="2" t="n">
-        <v>46129</v>
+        <v>46131</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
@@ -1933,7 +1904,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Emirates NBD successfully executes a USD 250 million syndicated term loan facility for Dar Global, accelerating global growth and expansion.</t>
+          <t>Saudi Arabia extends the Landbridge rail bid deadline to April 29 as Hormuz disruptions highlight its lack of a direct east–west freight rail link.</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1956,50 +1927,45 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2045118948694470845</t>
+          <t>2045805999718903933</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://x.com/GeorgeDon5181/status/2045118948694470845</t>
+          <t>https://x.com/abasetaljanahi/status/2045805999718903933</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://x.com/GeorgeDon5181</t>
+          <t>https://x.com/abasetaljanahi</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>GeorgeDon5181</t>
+          <t>abasetaljanahi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Don George</t>
+          <t>Abdulbaset Al Janahi</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1997686160211243008/2Cf-bh5c_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1572294225240231936/Ew_orY09_bigger.jpg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Fake Android updates are rising. They can trick you into installing unsafe apps or sharing details. 
-Turn on Smart Touch and Face Pass for secure login.
-تشهد التحديثات الوهمية على أجهزة أندرويد تزايداً ملحوظاً، وقد تُستخدم لخداعك لتثبيت تطبيقات غير آمنة أو مشاركة البيانات.
-احمِ حسابك من خلال تفعيل ميزة اللمس الذكي والتعرّف على الوجه
-لتسجيل دخول أكثر أماناً.</t>
+          <t>@EmiratesNBD_AE بس! 
+وايد عليكم</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>good (Iin in it+i8 
-I8. 8iii cf CT  FB
- FC m
- , (? +II in IIWII îîctffze</t>
+          <t>بس! 
+وايد عليكم</t>
         </is>
       </c>
       <c r="K10" t="b">
@@ -2013,21 +1979,21 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 12:35 PM UTC</t>
+          <t>Apr 19, 2026 · 10:05 AM UTC</t>
         </is>
       </c>
       <c r="P10" s="2" t="n">
-        <v>46129.52430555555</v>
+        <v>46131.42013888889</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -2036,7 +2002,7 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>4</v>
+        <v>211</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -2045,39 +2011,30 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>good (Iin in it+i8 
-I8. 8iii cf CT  FB
- FC m
- , (? +II in IIWII îîctffze</t>
+          <t>بس! 
+وايد عليكم</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>https://x.com/GeorgeDon5181/status/2045118948694470845</t>
+          <t>https://x.com/abasetaljanahi/status/2045805999718903933</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>Fake Android updates are rising. They can trick you into installing unsafe apps or sharing details. 
-Turn on Smart Touch and Face Pass for secure login.
-تشهد التحديثات الوهمية على أجهزة أندرويد تزايداً ملحوظاً، وقد تُستخدم لخداعك لتثبيت تطبيقات غير آمنة أو مشاركة البيانات.
-احمِ حسابك من خلال تفعيل ميزة اللمس الذكي والتعرّف على الوجه
-لتسجيل دخول أكثر أماناً.</t>
+          <t>@EmiratesNBD_AE بس! 
+وايد عليكم</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Fake Android updates are rising. They can trick you into installing unsafe apps or sharing details. 
-Turn on Smart Touch and Face Pass for secure login.
-تشهد التحديثات الوهمية على أجهزة أندرويد تزايداً ملحوظاً، وقد تُستخدم لخداعك لتثبيت تطبيقات غير آمنة أو مشاركة البيانات.
-احمِ حسابك من خلال تفعيل ميزة اللمس الذكي والتعرّف على الوجه
-لتسجيل دخول أكثر أماناً.</t>
+          <t>@EmiratesNBD_AE بس! 
+وايد عليكم</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Fake Android updates are on the rise. They can trick you into installing unsafe apps or sharing your details. 
-Protect your account by enabling Smart Touch and Face Recognition for a more secure login.</t>
+          <t>That's enough! You're overdoing it.</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -2091,10 +2048,10 @@
         </is>
       </c>
       <c r="AE10" s="2" t="n">
-        <v>46129.69097222222</v>
+        <v>46131.58680555555</v>
       </c>
       <c r="AF10" s="2" t="n">
-        <v>46129</v>
+        <v>46131</v>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
@@ -2108,7 +2065,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Protect your account by enabling Smart Touch and Face Recognition for a more secure login. • They can trick you into installing unsafe apps or sharing your details. • Fake Android updates are on the rise.</t>
+          <t>That's enough! You're overdoing it.</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -2131,92 +2088,80 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2045086967533031764</t>
+          <t>2045786366504796559</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2045086967533031764</t>
+          <t>https://x.com/SultanAbdu70381/status/2045786366504796559</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/SultanAbdu70381</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>SultanAbdu70381</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>Sultan Abdullah</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2042294543308242946/ScvMjarh_bigger.jpg</t>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Emirates NBD has successfully executed a USD 250 million syndicated term loan facility for @dar_global , strengthening its financial flexibility to support ongoing international development activity.
-This transaction reflects our continued role in structuring and delivering cross-border financing solutions for leading real estate developers, supported  by strong distribution capabilities and established lender relationships.
-We remain focused on helping clients scale with clarity, speed and disciplined access to capital across key markets.
-Read more here:
-https://t.co/91twU74VX9
-https://t.co/hfV7wLDhaI
-#EmiratesNBD #SyndicatedLoan #CapitalMarkets #Banking #Dubai</t>
+          <t>نحتاج تأجيل 3 شهور للازمه</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Emirates NBD has successfully executed a USD 250 million syndicated term loan facility for &lt;a href="/dar_global" title="DarGlobal"&gt;@dar_global&lt;/a&gt; , strengthening its financial flexibility to support ongoing international development activity.
-This transaction reflects our continued role in structuring and delivering cross-border financing solutions for leading real estate developers, supported  by strong distribution capabilities and established lender relationships.
-We remain focused on helping clients scale with clarity, speed and disciplined access to capital across key markets.
-Read more here:
-&lt;a href="https://www.emiratesnbd.com/en/media-center/emirates-nbd-successfully-executes-usd-250-million-syndicated-term-loan-facility-for-dar-global"&gt;emiratesnbd.com/en/media-cen…&lt;/a&gt;
-&lt;a href="https://www.emiratesnbd.com/ar/media-center/emirates-nbd-successfully-executes-usd-250-million-syndicated-term-loan-facility-for-dar-global"&gt;emiratesnbd.com/ar/media-cen…&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBD"&gt;#EmiratesNBD&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SyndicatedLoan"&gt;#SyndicatedLoan&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23CapitalMarkets"&gt;#CapitalMarkets&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Banking"&gt;#Banking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Dubai"&gt;#Dubai&lt;/a&gt;</t>
+          <t>اكثر البنوك فالدولة تساهلت مع متعامليها لتوفير راحتهم واحتياجاتهم وليس لزياده ضغط عليهم حيث قامو بتأجيل قروض لهم ٣ اشهر مساعده لهم لضروفهم خاصه دفاع الأول وشكرا لكم</t>
         </is>
       </c>
       <c r="K11" t="b">
         <v>0</v>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 10:28 AM UTC</t>
+          <t>Apr 19, 2026 · 8:47 AM UTC</t>
         </is>
       </c>
       <c r="P11" s="2" t="n">
-        <v>46129.43611111111</v>
+        <v>46131.36597222222</v>
       </c>
       <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>['https://x.com/dar_global', 'https://www.emiratesnbd.com/en/media-center/emirates-nbd-successfully-executes-usd-250-million-syndicated-term-loan-facility-for-dar-global', 'https://www.emiratesnbd.com/ar/media-center/emirates-nbd-successfully-executes-usd-250-million-syndicated-term-loan-facility-for-dar-global', 'https://x.com/search?f=tweets&amp;q=%23EmiratesNBD', 'https://x.com/search?f=tweets&amp;q=%23SyndicatedLoan', 'https://x.com/search?f=tweets&amp;q=%23CapitalMarkets', 'https://x.com/search?f=tweets&amp;q=%23Banking', 'https://x.com/search?f=tweets&amp;q=%23Dubai']</t>
-        </is>
-      </c>
+      <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>530</v>
+        <v>6</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -2225,62 +2170,44 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Emirates NBD has successfully executed a USD 250 million syndicated term loan facility for @dar_global , strengthening its financial flexibility to support ongoing international development activity.
-This transaction reflects our continued role in structuring and delivering cross-border financing solutions for leading real estate developers, supported  by strong distribution capabilities and established lender relationships.
-We remain focused on helping clients scale with clarity, speed and disciplined access to capital across key markets.
-Read more here:
-emiratesnbd.com/en/media-cen…
-emiratesnbd.com/ar/media-cen…
-#EmiratesNBD #SyndicatedLoan #CapitalMarkets #Banking #Dubai</t>
+          <t>اكثر البنوك فالدولة تساهلت مع متعامليها لتوفير راحتهم واحتياجاتهم وليس لزياده ضغط عليهم حيث قامو بتأجيل قروض لهم ٣ اشهر مساعده لهم لضروفهم خاصه دفاع الأول وشكرا لكم</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2045086967533031764</t>
+          <t>https://x.com/SultanAbdu70381/status/2045786366504796559</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>Emirates NBD has successfully executed a USD 250 million syndicated term loan facility for @dar_global , strengthening its financial flexibility to support ongoing international development activity.
-This transaction reflects our continued role in structuring and delivering cross-border financing solutions for leading real estate developers, supported  by strong distribution capabilities and established lender relationships.
-We remain focused on helping clients scale with clarity, speed and disciplined access to capital across key markets.
-Read more here:
-https://t.co/91twU74VX9
-https://t.co/hfV7wLDhaI
-#EmiratesNBD #SyndicatedLoan #CapitalMarkets #Banking #Dubai</t>
+          <t>نحتاج تأجيل 3 شهور للازمه</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Emirates NBD has successfully executed a USD 250 million syndicated term loan facility for @dar_global , strengthening its financial flexibility to support ongoing international development activity.
-This transaction reflects our continued role in structuring and delivering cross-border financing solutions for leading real estate developers, supported  by strong distribution capabilities and established lender relationships.
-We remain focused on helping clients scale with clarity, speed and disciplined access to capital across key markets.
-Read more here:
-https://t.co/91twU74VX9
-https://t.co/hfV7wLDhaI
-#EmiratesNBD #SyndicatedLoan #CapitalMarkets #Banking #Dubai</t>
+          <t>نحتاج تأجيل 3 شهور للازمه</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Emirates NBD has successfully executed a USD 250 million syndicated term loan facility for @dar_global, strengthening its financial flexibility to support ongoing international development activity. This transaction reflects our continued role in structuring and delivering cross-border financing solutions for leading real estate developers, supported by strong distribution capabilities and established lender relationships. We remain focused on helping clients scale with clarity, speed, and disciplined access to capital across key markets.</t>
+          <t>We need a 3-month postponement for the necessity.</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Cust</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AE11" s="2" t="n">
-        <v>46129.60277777778</v>
+        <v>46131.53263888889</v>
       </c>
       <c r="AF11" s="2" t="n">
-        <v>46129</v>
+        <v>46131</v>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
@@ -2294,7 +2221,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Emirates NBD has successfully executed a USD 250 million syndicated term loan facility for @dar_global, strengthening its financial flexibility to support ongoing international development activity. • We remain focused on helping clients scale with clarity, speed, and disciplined access to capital across key markets.</t>
+          <t>We need a 3-month postponement for the necessity.</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -2307,7 +2234,7 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
     </row>
@@ -2317,74 +2244,69 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2045079926013837337</t>
+          <t>2045785730023301620</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals/status/2045079926013837337</t>
+          <t>https://x.com/SultanAbdu70381/status/2045785730023301620</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals</t>
+          <t>https://x.com/SultanAbdu70381</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ENBDdeals</t>
+          <t>SultanAbdu70381</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Emirates NBD Deals</t>
+          <t>Sultan Abdullah</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1763624422294814720/EmRI1Aqu_bigger.jpg</t>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>دلّل نفسك مع جراند فلورا سبا 💅
-احصل على خصم 15% على فاتورتك بقيمة 150 درهم أو أكثر، حصريًا عبر تطبيق تستاهل.
-لمعرفة المزيد:
-https://t.co/NILbsZvhfk https://t.co/Elvcoo2HNL</t>
+          <t>@EmiratesNBD_AE عند الإعلان يجب وضع التوضيح وليس وضع إعلان بموضوع واتخاذ إجراءات وأوامر أخرى شكرا لكم</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Turn your bills into rewards
-Get AED 500 worth of Majid Al Futtaim voucher when you apply for an Emirates NBD SHARE Visa Credit Card.
-Apply Now: &lt;a href="https://apply.emiratesnbd.com/en/credit-card/maf"&gt;apply.emiratesnbd.com/en/cre…&lt;/a&gt;</t>
+          <t>عند الإعلان يجب وضع التوضيح وليس وضع إعلان بموضوع واتخاذ إجراءات وأوامر أخرى شكرا لكم</t>
         </is>
       </c>
       <c r="K12" t="b">
         <v>0</v>
       </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 10:00 AM UTC</t>
+          <t>Apr 19, 2026 · 8:45 AM UTC</t>
         </is>
       </c>
       <c r="P12" s="2" t="n">
-        <v>46129.41666666666</v>
+        <v>46131.36458333334</v>
       </c>
       <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>['https://apply.emiratesnbd.com/en/credit-card/maf']</t>
-        </is>
-      </c>
+      <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
         <v>0</v>
       </c>
@@ -2392,10 +2314,10 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>108</v>
+        <v>11</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -2404,40 +2326,32 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Turn your bills into rewards
-Get AED 500 worth of Majid Al Futtaim voucher when you apply for an Emirates NBD SHARE Visa Credit Card.
-Apply Now: apply.emiratesnbd.com/en/cre…</t>
+          <t>عند الإعلان يجب وضع التوضيح وليس وضع إعلان بموضوع واتخاذ إجراءات وأوامر أخرى شكرا لكم</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals/status/2045079926013837337</t>
+          <t>https://x.com/SultanAbdu70381/status/2045785730023301620</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>دلّل نفسك مع جراند فلورا سبا 💅
-احصل على خصم 15% على فاتورتك بقيمة 150 درهم أو أكثر، حصريًا عبر تطبيق تستاهل.
-لمعرفة المزيد:
-https://t.co/NILbsZvhfk https://t.co/Elvcoo2HNL</t>
+          <t>@EmiratesNBD_AE عند الإعلان يجب وضع التوضيح وليس وضع إعلان بموضوع واتخاذ إجراءات وأوامر أخرى شكرا لكم</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>دلّل نفسك مع جراند فلورا سبا 💅
-احصل على خصم 15% على فاتورتك بقيمة 150 درهم أو أكثر، حصريًا عبر تطبيق تستاهل.
-لمعرفة المزيد:
-https://t.co/NILbsZvhfk https://t.co/Elvcoo2HNL</t>
+          <t>@EmiratesNBD_AE عند الإعلان يجب وضع التوضيح وليس وضع إعلان بموضوع واتخاذ إجراءات وأوامر أخرى شكرا لكم</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Indulge yourself at Grand Flora Spa 💅 Get a 15% discount on your bill of 150 dirhams or more, exclusively through the Testahl app. To learn more:</t>
+          <t>When announcing, clarification should be provided instead of just making an announcement on the subject and taking other actions and orders. Thank you.</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Cust</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -2446,10 +2360,10 @@
         </is>
       </c>
       <c r="AE12" s="2" t="n">
-        <v>46129.58333333334</v>
+        <v>46131.53125</v>
       </c>
       <c r="AF12" s="2" t="n">
-        <v>46129</v>
+        <v>46131</v>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
@@ -2463,7 +2377,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Indulge yourself at Grand Flora Spa 💅 Get a 15% discount on your bill of 150 dirhams or more, exclusively through the Testahl app.</t>
+          <t>When announcing, clarification should be provided instead of just making an announcement on the subject and taking other actions and orders.</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2476,7 +2390,7 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
     </row>
@@ -2486,81 +2400,80 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2045067912894201918</t>
+          <t>2045755517948272900</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://x.com/ForumRemittance/status/2045067912894201918</t>
+          <t>https://x.com/girluae11/status/2045755517948272900</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://x.com/ForumRemittance</t>
+          <t>https://x.com/girluae11</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ForumRemittance</t>
+          <t>girluae11</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>World Remittance Action Forum</t>
+          <t>girl</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1942959686417891328/FNdImGgE_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2043687946625368066/wksZEFYW_bigger.jpg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Atradius, a global leader in trade credit insurance and risk management, has established operations in the Dubai International Financial Centre (DIFC), marking a key milestone in its Middle East growth strategy.#Atradius #DIFC #MiddleEast #Insurance #RiskManagement #TradeCredit https://t.co/0x6KlHhlpo</t>
+          <t>@EmiratesNBD_AE من هم حماه الوطن؟ الفئات ؟</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Emirates NBD, a leading banking group across the MENAT region, has successfully executed a USD 250 million syndicated term loan facility, “Project Radium II,” for DarGlobal.
-&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBD"&gt;#EmiratesNBD&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23DarGlobal"&gt;#DarGlobal&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SyndicatedLoan"&gt;#SyndicatedLoan&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23RealEstate"&gt;#RealEstate&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23MENAT"&gt;#MENAT&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23BankingNews"&gt;#BankingNews&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Finance"&gt;#Finance&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23GlobalMarkets"&gt;#GlobalMarkets&lt;/a&gt;</t>
+          <t>من هم حماه الوطن؟ الفئات ؟</t>
         </is>
       </c>
       <c r="K13" t="b">
         <v>0</v>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 9:12 AM UTC</t>
+          <t>Apr 19, 2026 · 6:44 AM UTC</t>
         </is>
       </c>
       <c r="P13" s="2" t="n">
-        <v>46129.38333333333</v>
+        <v>46131.28055555555</v>
       </c>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EmiratesNBD', 'https://x.com/search?f=tweets&amp;q=%23DarGlobal', 'https://x.com/search?f=tweets&amp;q=%23SyndicatedLoan', 'https://x.com/search?f=tweets&amp;q=%23RealEstate', 'https://x.com/search?f=tweets&amp;q=%23MENAT', 'https://x.com/search?f=tweets&amp;q=%23BankingNews', 'https://x.com/search?f=tweets&amp;q=%23Finance', 'https://x.com/search?f=tweets&amp;q=%23GlobalMarkets']</t>
-        </is>
-      </c>
+      <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>164</v>
+        <v>137</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -2569,28 +2482,27 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Emirates NBD, a leading banking group across the MENAT region, has successfully executed a USD 250 million syndicated term loan facility, “Project Radium II,” for DarGlobal.
-#EmiratesNBD #DarGlobal #SyndicatedLoan #RealEstate #MENAT #BankingNews #Finance #GlobalMarkets</t>
+          <t>من هم حماه الوطن؟ الفئات ؟</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>https://x.com/ForumRemittance/status/2045067912894201918</t>
+          <t>https://x.com/girluae11/status/2045755517948272900</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>Atradius, a global leader in trade credit insurance and risk management, has established operations in the Dubai International Financial Centre (DIFC), marking a key milestone in its Middle East growth strategy.#Atradius #DIFC #MiddleEast #Insurance #RiskManagement #TradeCredit https://t.co/0x6KlHhlpo</t>
+          <t>@EmiratesNBD_AE من هم حماه الوطن؟ الفئات ؟</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Atradius, a global leader in trade credit insurance and risk management, has established operations in the Dubai International Financial Centre (DIFC), marking a key milestone in its Middle East growth strategy.#Atradius #DIFC #MiddleEast #Insurance #RiskManagement #TradeCredit https://t.co/0x6KlHhlpo</t>
+          <t>@EmiratesNBD_AE من هم حماه الوطن؟ الفئات ؟</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Atradius, a global leader in trade credit insurance and risk management, has established operations in the Dubai International Financial Centre (DIFC), marking a key milestone in its Middle East growth strategy.</t>
+          <t>Who are the guardians of the homeland? The categories?</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2604,10 +2516,10 @@
         </is>
       </c>
       <c r="AE13" s="2" t="n">
-        <v>46129.55</v>
+        <v>46131.44722222222</v>
       </c>
       <c r="AF13" s="2" t="n">
-        <v>46129</v>
+        <v>46131</v>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
@@ -2621,7 +2533,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Atradius, a global leader in trade credit insurance and risk management, has established operations in the Dubai Interna…</t>
+          <t>Who are the guardians of the homeland?</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2634,7 +2546,7 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
     </row>
@@ -2644,69 +2556,69 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2045063430139433260</t>
+          <t>2045729029614129456</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide/status/2045063430139433260</t>
+          <t>https://x.com/bu_rashed98/status/2045729029614129456</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide</t>
+          <t>https://x.com/bu_rashed98</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>dcgguide</t>
+          <t>bu_rashed98</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>DUBAI CITY GUIDE from Cyber Gear</t>
+          <t>﮼💛🇦🇪الامبراطور 🇦🇪💛</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1780203891230945280/ODQLZiT__bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2042287480335187974/x8vTEs88_bigger.jpg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Dubai Holding Real Estate And Emirates NBD Partner To Introduce Integrated Off-Plan Mortgage Financing https://t.co/Iica48plSc</t>
+          <t>@EmiratesNBD_AE أنا وياهم 😁</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Dubai Holding Real Estate And Emirates NBD Partner To Introduce Integrated Off-Plan Mortgage Financing &lt;a href="https://dubaipropertyguide.io/dubai-holding-real-estate-and-emirates-nbd-partner-to-introduce-integrated-off-plan-mortgage-financing/"&gt;dubaipropertyguide.io/dubai-…&lt;/a&gt;</t>
+          <t>أنا وياهم 😁</t>
         </is>
       </c>
       <c r="K14" t="b">
         <v>0</v>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 8:54 AM UTC</t>
+          <t>Apr 19, 2026 · 4:59 AM UTC</t>
         </is>
       </c>
       <c r="P14" s="2" t="n">
-        <v>46129.37083333333</v>
+        <v>46131.20763888889</v>
       </c>
       <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>['https://dubaipropertyguide.io/dubai-holding-real-estate-and-emirates-nbd-partner-to-introduce-integrated-off-plan-mortgage-financing/']</t>
-        </is>
-      </c>
+      <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
         <v>0</v>
       </c>
@@ -2717,7 +2629,7 @@
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>34</v>
+        <v>141</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -2726,27 +2638,27 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Dubai Holding Real Estate And Emirates NBD Partner To Introduce Integrated Off-Plan Mortgage Financing dubaipropertyguide.io/dubai-…</t>
+          <t>أنا وياهم 😁</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide/status/2045063430139433260</t>
+          <t>https://x.com/bu_rashed98/status/2045729029614129456</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>Dubai Holding Real Estate And Emirates NBD Partner To Introduce Integrated Off-Plan Mortgage Financing https://t.co/Iica48plSc</t>
+          <t>@EmiratesNBD_AE أنا وياهم 😁</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Dubai Holding Real Estate And Emirates NBD Partner To Introduce Integrated Off-Plan Mortgage Financing https://t.co/Iica48plSc</t>
+          <t>@EmiratesNBD_AE أنا وياهم 😁</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Dubai Holding Real Estate and Emirates NBD partner to introduce integrated off-plan mortgage financing.</t>
+          <t>I am with them 😁</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2760,10 +2672,10 @@
         </is>
       </c>
       <c r="AE14" s="2" t="n">
-        <v>46129.5375</v>
+        <v>46131.37430555555</v>
       </c>
       <c r="AF14" s="2" t="n">
-        <v>46129</v>
+        <v>46131</v>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
@@ -2777,7 +2689,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Dubai Holding Real Estate and Emirates NBD partner to introduce integrated off-plan mortgage financing.</t>
+          <t>I am with them 😁</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2790,7 +2702,7 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
     </row>
@@ -2800,76 +2712,73 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2045051886051688548</t>
+          <t>2045771180469272971</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://x.com/AdnanAf33353686/status/2045051886051688548</t>
+          <t>https://x.com/firstdiver4ever/status/2045771180469272971</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://x.com/AdnanAf33353686</t>
+          <t>https://x.com/firstdiver4ever</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AdnanAf33353686</t>
+          <t>firstdiver4ever</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Adnan Afridi</t>
+          <t>اماراتى وافتخر</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1695298421714804736/A6PpWdw3_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1974542718652280832/oqepMvc3_bigger.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>في إطار مبادرة #متحدون_ضد_الاحتيال، قمنا بزيارة مجمّع إقامة عاملات من أجل رفع مستوى الوعي لديهن عن عمليات الاحتيال الإلكتروني وكيفية تجنبها.
-ومن خلال جلسات تفاعلية، ومسابقات، ونقاشات مفتوحة، تعرّفت المُشارِكات على كيفية اكتشاف عمليات الاحتيال، وتجنّبها وطرق الإبلاغ عنها.
-الوعي هو الخطوة الأولى نحو الحماية.
-ابقَ آمناً. كن متيقظاً.
-#متحدون_ضد_الاحتيال</t>
+          <t>@emiratesislamic أتقدم لجميع العاملين في مصرف الإمارات الإسلامي بجزيل الشكر والتقدير على جهودهم وعملهم الدؤوب الذي قاموا به ، حيث تم مشكلتي في زمن قياسي بالوقت الذي كان من المفروض ان يتم انجازه خلال سبعة ايام عمل .
+شكرا من القلب مرة اخرى .</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Hi I want to open account in nbd but my application was rejected 
-Live account is free with no minimum balance or need minimum balance</t>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; أتقدم لجميع العاملين في مصرف الإمارات الإسلامي بجزيل الشكر والتقدير على جهودهم وعملهم الدؤوب الذي قاموا به ، حيث تم مشكلتي في زمن قياسي بالوقت الذي كان من المفروض ان يتم انجازه خلال سبعة ايام عمل .
+شكرا من القلب مرة اخرى .</t>
         </is>
       </c>
       <c r="K15" t="b">
         <v>0</v>
       </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 8:08 AM UTC</t>
+          <t>Apr 19, 2026 · 7:47 AM UTC</t>
         </is>
       </c>
       <c r="P15" s="2" t="n">
-        <v>46129.33888888889</v>
+        <v>46131.32430555556</v>
       </c>
       <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>['https://x.com/emiratesislamic']</t>
+        </is>
+      </c>
       <c r="S15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
@@ -2878,45 +2787,39 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Hi I want to open account in nbd but my application was rejected 
-Live account is free with no minimum balance or need minimum balance</t>
+          <t>@emiratesislamic أتقدم لجميع العاملين في مصرف الإمارات الإسلامي بجزيل الشكر والتقدير على جهودهم وعملهم الدؤوب الذي قاموا به ، حيث تم مشكلتي في زمن قياسي بالوقت الذي كان من المفروض ان يتم انجازه خلال سبعة ايام عمل .
+شكرا من القلب مرة اخرى .</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>https://x.com/AdnanAf33353686/status/2045051886051688548</t>
+          <t>https://x.com/firstdiver4ever/status/2045771180469272971</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>في إطار مبادرة #متحدون_ضد_الاحتيال، قمنا بزيارة مجمّع إقامة عاملات من أجل رفع مستوى الوعي لديهن عن عمليات الاحتيال الإلكتروني وكيفية تجنبها.
-ومن خلال جلسات تفاعلية، ومسابقات، ونقاشات مفتوحة، تعرّفت المُشارِكات على كيفية اكتشاف عمليات الاحتيال، وتجنّبها وطرق الإبلاغ عنها.
-الوعي هو الخطوة الأولى نحو الحماية.
-ابقَ آمناً. كن متيقظاً.
-#متحدون_ضد_الاحتيال</t>
+          <t>@emiratesislamic أتقدم لجميع العاملين في مصرف الإمارات الإسلامي بجزيل الشكر والتقدير على جهودهم وعملهم الدؤوب الذي قاموا به ، حيث تم مشكلتي في زمن قياسي بالوقت الذي كان من المفروض ان يتم انجازه خلال سبعة ايام عمل .
+شكرا من القلب مرة اخرى .</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>في إطار مبادرة #متحدون_ضد_الاحتيال، قمنا بزيارة مجمّع إقامة عاملات من أجل رفع مستوى الوعي لديهن عن عمليات الاحتيال الإلكتروني وكيفية تجنبها.
-ومن خلال جلسات تفاعلية، ومسابقات، ونقاشات مفتوحة، تعرّفت المُشارِكات على كيفية اكتشاف عمليات الاحتيال، وتجنّبها وطرق الإبلاغ عنها.
-الوعي هو الخطوة الأولى نحو الحماية.
-ابقَ آمناً. كن متيقظاً.
-#متحدون_ضد_الاحتيال</t>
+          <t>@emiratesislamic أتقدم لجميع العاملين في مصرف الإمارات الإسلامي بجزيل الشكر والتقدير على جهودهم وعملهم الدؤوب الذي قاموا به ، حيث تم مشكلتي في زمن قياسي بالوقت الذي كان من المفروض ان يتم انجازه خلال سبعة ايام عمل .
+شكرا من القلب مرة اخرى .</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>As part of the #United_Against_Fraud initiative, we visited a residence for female workers to raise their awareness about online fraud and how to avoid it. Through interactive sessions, competitions, and open discussions, the participants learned how to detect fraud, avoid it, and report it. Awareness is the first step towards protection. Stay safe. Be vigilant. #United_Against_Fraud</t>
+          <t>I would like to extend my heartfelt thanks and appreciation to all the employees of Emirates Islamic Bank for their efforts and hard work, as my issue was resolved in a record time that was supposed to take seven working days. Thank you from the heart once again.</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2926,33 +2829,33 @@
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AE15" s="2" t="n">
-        <v>46129.50555555556</v>
+        <v>46131.49097222222</v>
       </c>
       <c r="AF15" s="2" t="n">
-        <v>46129</v>
+        <v>46131</v>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
+          <t>2. Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>As part of the #United_Against_Fraud initiative, we visited a residence for female workers to raise their awareness about online fraud and how to avoid it. • Through interactive sessions, competitions, and open discussions, the participants learned how to detect fraud, avoid it, and report it. • Awareness is the first step towards protection.</t>
+          <t>Thank you from the heart once again.</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank (ENBD)</t>
+          <t>Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AK15" t="n">
@@ -2960,7 +2863,7 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2970,70 +2873,77 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2045041596106781053</t>
+          <t>2045744202382807549</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://x.com/AnasYousiftpy0/status/2045041596106781053</t>
+          <t>https://x.com/emiratesislamic/status/2045744202382807549</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://x.com/AnasYousiftpy0</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AnasYousiftpy0</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Anas Yousif</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2020265249027289088/ZwoWrEZ3_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>🚨 JUST IN: 🇦🇪 EMIRATES NBD ELIMINATES ATM WITHDRAWAL &amp;amp; DEBIT CARD FEES ACROSS THE UAE &amp;amp; GCC UNTIL MARCH 31, 2026! 💳🔥
-#UAE #EmiratesNBD #Banking #Finance #ATM #NoFees #GCC #MoneySmart https://t.co/aI9H5crVgx</t>
+          <t>Get a chance to win a total of AED 1,000,000 in cash prizes.
+55 businesses will be winners. Will you be one of them?
+⭐️Grand cash prize: AED 250,000 (1 winner)
+💸 Second cash prize: AED 100,000 each (2 winners) https://t.co/V52QeTxHT6</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>هذه أخبار رائعة لعملاء Emirates NBD في المنطقة</t>
+          <t>Outstanding payments = constant stress.
+💡 Tip:
+Write everything down in one place
+Clarity makes it feel manageable.
+&lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialWellbeing"&gt;#EIFinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K16" t="b">
         <v>0</v>
       </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>['CryptoNewsHntrs']</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 7:28 AM UTC</t>
+          <t>Apr 19, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P16" s="2" t="n">
-        <v>46129.31111111111</v>
+        <v>46131.25</v>
       </c>
       <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EIFinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+        </is>
+      </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
@@ -3041,46 +2951,55 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>هذه أخبار رائعة لعملاء Emirates NBD في المنطقة</t>
+          <t>Outstanding payments = constant stress.
+💡 Tip:
+Write everything down in one place
+Clarity makes it feel manageable.
+#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
+emiratesislamic.ae/en/key-in…</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>https://x.com/AnasYousiftpy0/status/2045041596106781053</t>
+          <t>https://x.com/emiratesislamic/status/2045744202382807549</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>🚨 JUST IN: 🇦🇪 EMIRATES NBD ELIMINATES ATM WITHDRAWAL &amp;amp; DEBIT CARD FEES ACROSS THE UAE &amp;amp; GCC UNTIL MARCH 31, 2026! 💳🔥
-#UAE #EmiratesNBD #Banking #Finance #ATM #NoFees #GCC #MoneySmart https://t.co/aI9H5crVgx</t>
+          <t>Get a chance to win a total of AED 1,000,000 in cash prizes.
+55 businesses will be winners. Will you be one of them?
+⭐️Grand cash prize: AED 250,000 (1 winner)
+💸 Second cash prize: AED 100,000 each (2 winners) https://t.co/V52QeTxHT6</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>🚨 JUST IN: 🇦🇪 EMIRATES NBD ELIMINATES ATM WITHDRAWAL &amp;amp; DEBIT CARD FEES ACROSS THE UAE &amp;amp; GCC UNTIL MARCH 31, 2026! 💳🔥
-#UAE #EmiratesNBD #Banking #Finance #ATM #NoFees #GCC #MoneySmart https://t.co/aI9H5crVgx</t>
+          <t>Get a chance to win a total of AED 1,000,000 in cash prizes.
+55 businesses will be winners. Will you be one of them?
+⭐️Grand cash prize: AED 250,000 (1 winner)
+💸 Second cash prize: AED 100,000 each (2 winners) https://t.co/V52QeTxHT6</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>JUST IN: EMIRATES NBD ELIMINATES ATM WITHDRAWAL &amp; DEBIT CARD FEES ACROSS THE UAE &amp; GCC UNTIL MARCH 31, 2026!</t>
+          <t>Get a chance to win a total of AED 1,000,000 in cash prizes. 55 businesses will be winners. Will you be one of them? ⭐️Grand cash prize: AED 250,000 (1 winner) 💸 Second cash prize: AED 100,000 each (2 winners)</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Cust</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -3089,29 +3008,29 @@
         </is>
       </c>
       <c r="AE16" s="2" t="n">
-        <v>46129.47777777778</v>
+        <v>46131.41666666666</v>
       </c>
       <c r="AF16" s="2" t="n">
-        <v>46129</v>
+        <v>46131</v>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
+          <t>2. Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>JUST IN: EMIRATES NBD ELIMINATES ATM WITHDRAWAL &amp; DEBIT CARD FEES ACROSS THE UAE &amp; GCC UNTIL MARCH 31, 2026!</t>
+          <t>⭐️Grand cash prize: AED 250,000 (1 winner) 💸 Second cash prize: AED 100,000 each (2 winners) • Get a chance to win a total of AED 1,000,000 in cash prizes. • 55 businesses will be winners.</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank (ENBD)</t>
+          <t>Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AK16" t="n">
@@ -3119,7 +3038,7 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>CryptoNewsHntrs</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3129,69 +3048,51 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2045034471821549807</t>
+          <t>2045744202651226430</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://x.com/Net_eqtisad/status/2045034471821549807</t>
+          <t>https://x.com/emiratesislamic/status/2045744202651226430</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://x.com/Net_eqtisad</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Net_eqtisad</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>الشبكة الاقتصادية</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1892643729745317888/Zh1HkNvX_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>يتصدرها بنك الإمارات دبي الوطني .. أداء أكبر الأسهم الإماراتية خلال شهر أبريل 2026
-@ihc__official
-@TAQAGroup
-@ADNOCGas
-@FABConnects
-@EmiratesNBD_AE 
-@eAndUAE
-@DEWAOfficial
-@emaardubai
-@OfficialADCB
-@adnocdrillinguae
-#الإمارات 
-#الأسواق #أدنوك
-#الشبكة_الاقتصادية https://t.co/rO2sscergA</t>
+          <t>المدفوعات المستحقة تعني ضغطاً مستمراً.
+💡نصيحة: دوّن كل مدفوعاتك في مكان واحد.
+الوضوح يجعل الأمر أسهل في الإدارة. 
+#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
+https://t.co/mgtIcQsyLZ</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>يتصدرها بنك الإمارات دبي الوطني .. أداء أكبر الأسهم الإماراتية خلال شهر أبريل 2026
-&lt;a href="/ihc__official" title="IHC"&gt;@ihc__official&lt;/a&gt;
-&lt;a href="/TAQAGroup" title="TAQA"&gt;@TAQAGroup&lt;/a&gt;
-&lt;a href="/ADNOCGas" title="ADNOC Gas"&gt;@ADNOCGas&lt;/a&gt;
-&lt;a href="/FABConnects" title="FAB Connects"&gt;@FABConnects&lt;/a&gt;
-&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; 
-&lt;a href="/eAndUAE" title="e&amp;amp; UAE"&gt;@eAndUAE&lt;/a&gt;
-&lt;a href="/DEWAOfficial" title="DEWA | Official Page"&gt;@DEWAOfficial&lt;/a&gt;
-&lt;a href="/emaardubai" title="Emaar Dubai"&gt;@emaardubai&lt;/a&gt;
-&lt;a href="/OfficialADCB" title="ADCB بنك أبوظبي التجاري"&gt;@OfficialADCB&lt;/a&gt;
-@adnocdrillinguae
-&lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات"&gt;#الإمارات&lt;/a&gt; 
-&lt;a href="/search?f=tweets&amp;amp;q=%23الأسواق"&gt;#الأسواق&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23أدنوك"&gt;#أدنوك&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23الشبكة_الاقتصادية"&gt;#الشبكة_الاقتصادية&lt;/a&gt;</t>
+          <t>المدفوعات المستحقة تعني ضغطاً مستمراً.
+💡نصيحة: دوّن كل مدفوعاتك في مكان واحد.
+الوضوح يجعل الأمر أسهل في الإدارة. 
+&lt;a href="/search?f=tweets&amp;amp;q=%23نظرتك_المالية"&gt;#نظرتك_المالية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التثقيف_المالي"&gt;#التثقيف_المالي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/ar/key-in…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K17" t="b">
@@ -3201,21 +3102,21 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 6:59 AM UTC</t>
+          <t>Apr 19, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P17" s="2" t="n">
-        <v>46129.29097222222</v>
+        <v>46131.25</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
-          <t>['https://x.com/ihc__official', 'https://x.com/TAQAGroup', 'https://x.com/ADNOCGas', 'https://x.com/FABConnects', 'https://x.com/EmiratesNBD_AE', 'https://x.com/eAndUAE', 'https://x.com/DEWAOfficial', 'https://x.com/emaardubai', 'https://x.com/OfficialADCB', 'https://x.com/search?f=tweets&amp;q=%23الإمارات', 'https://x.com/search?f=tweets&amp;q=%23الأسواق', 'https://x.com/search?f=tweets&amp;q=%23أدنوك', 'https://x.com/search?f=tweets&amp;q=%23الشبكة_الاقتصادية']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23نظرتك_المالية', 'https://x.com/search?f=tweets&amp;q=%23التثقيف_المالي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
         </is>
       </c>
       <c r="S17" t="n">
@@ -3225,83 +3126,59 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>121</v>
+        <v>60</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>يتصدرها بنك الإمارات دبي الوطني .. أداء أكبر الأسهم الإماراتية خلال شهر أبريل 2026
-@ihc__official
-@TAQAGroup
-@ADNOCGas
-@FABConnects
-@EmiratesNBD_AE 
-@eAndUAE
-@DEWAOfficial
-@emaardubai
-@OfficialADCB
-@adnocdrillinguae
-#الإمارات 
-#الأسواق #أدنوك
-#الشبكة_الاقتصادية</t>
+          <t>المدفوعات المستحقة تعني ضغطاً مستمراً.
+💡نصيحة: دوّن كل مدفوعاتك في مكان واحد.
+الوضوح يجعل الأمر أسهل في الإدارة. 
+#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
+emiratesislamic.ae/ar/key-in…</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>https://x.com/Net_eqtisad/status/2045034471821549807</t>
+          <t>https://x.com/emiratesislamic/status/2045744202651226430</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>يتصدرها بنك الإمارات دبي الوطني .. أداء أكبر الأسهم الإماراتية خلال شهر أبريل 2026
-@ihc__official
-@TAQAGroup
-@ADNOCGas
-@FABConnects
-@EmiratesNBD_AE 
-@eAndUAE
-@DEWAOfficial
-@emaardubai
-@OfficialADCB
-@adnocdrillinguae
-#الإمارات 
-#الأسواق #أدنوك
-#الشبكة_الاقتصادية https://t.co/rO2sscergA</t>
+          <t>المدفوعات المستحقة تعني ضغطاً مستمراً.
+💡نصيحة: دوّن كل مدفوعاتك في مكان واحد.
+الوضوح يجعل الأمر أسهل في الإدارة. 
+#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
+https://t.co/mgtIcQsyLZ</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>يتصدرها بنك الإمارات دبي الوطني .. أداء أكبر الأسهم الإماراتية خلال شهر أبريل 2026
-@ihc__official
-@TAQAGroup
-@ADNOCGas
-@FABConnects
-@EmiratesNBD_AE 
-@eAndUAE
-@DEWAOfficial
-@emaardubai
-@OfficialADCB
-@adnocdrillinguae
-#الإمارات 
-#الأسواق #أدنوك
-#الشبكة_الاقتصادية https://t.co/rO2sscergA</t>
+          <t>المدفوعات المستحقة تعني ضغطاً مستمراً.
+💡نصيحة: دوّن كل مدفوعاتك في مكان واحد.
+الوضوح يجعل الأمر أسهل في الإدارة. 
+#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
+https://t.co/mgtIcQsyLZ</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>The performance of the largest Emirati stocks in April 2026 is led by Emirates NBD Bank.</t>
+          <t>Outstanding payments mean continuous pressure.
+💡Tip: Write down all your payments in one place.
+Clarity makes it easier to manage. 
+#YourFinancialPerspective #FinancialEducation #EmiratesIslamic</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Cust</t>
+          <t>Bank</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -3310,29 +3187,29 @@
         </is>
       </c>
       <c r="AE17" s="2" t="n">
-        <v>46129.45763888889</v>
+        <v>46131.41666666666</v>
       </c>
       <c r="AF17" s="2" t="n">
-        <v>46129</v>
+        <v>46131</v>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>1. Emirates NBD Bank (ENBD)</t>
+          <t>2. Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>The performance of the largest Emirati stocks in April 2026 is led by Emirates NBD Bank.</t>
+          <t>💡Tip: Write down all your payments in one place. • Outstanding payments mean continuous pressure. • Clarity makes it easier to manage.</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank (ENBD)</t>
+          <t>Emirates Islamic Bank (EIB)</t>
         </is>
       </c>
       <c r="AK17" t="n">
@@ -3350,80 +3227,88 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2045015539907772833</t>
+          <t>2045814764828516809</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide/status/2045015539907772833</t>
+          <t>https://x.com/UaeAlteneiji/status/2045814764828516809</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide</t>
+          <t>https://x.com/UaeAlteneiji</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>dcgguide</t>
+          <t>UaeAlteneiji</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>DUBAI CITY GUIDE from Cyber Gear</t>
+          <t>أبو عمر ، عبدالرحمن الطنيجي</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1780203891230945280/ODQLZiT__bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1906440728953204736/EXccdOZS_bigger.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Emirates NBD Successfully Executes USD 250 Million Syndicated Term Loan Facility For DAR Global, Accelerating Global Growth And Expansion https://t.co/ukTtwwan5a</t>
+          <t>@EmiratesNBD_AE من شكل الاعلان باين انه مجرد دعاية للبنك وليس دعماً لحماة الوطن
+اعلان غير موفق
+اعلان محدد بتاريخ صلاحية 
+اعلان تحكمه الشروط والاحكام المجهولة
+هنالك بنوك أخرى تقدم عروض تتافسية جذابة أكثر ومزايا أفضل وأحسن وتقدم لجميع العملاء ولعامة الشعب دون منية</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Emirates NBD Successfully Executes USD 250 Million Syndicated Term Loan Facility For DAR Global, Accelerating Global Growth And Expansion &lt;a href="https://blog.dubaicityguide.com/site/emirates-nbd-successfully-executes-usd-250-million-syndicated-term-loan-facility-for-dar-global-accelerating-global-growth-and-expansion/"&gt;blog.dubaicityguide.com/site…&lt;/a&gt;</t>
+          <t>من شكل الاعلان باين انه مجرد دعاية للبنك وليس دعماً لحماة الوطن
+اعلان غير موفق
+اعلان محدد بتاريخ صلاحية 
+اعلان تحكمه الشروط والاحكام المجهولة
+هنالك بنوك أخرى تقدم عروض تتافسية جذابة أكثر ومزايا أفضل وأحسن وتقدم لجميع العملاء ولعامة الشعب دون منية</t>
         </is>
       </c>
       <c r="K18" t="b">
         <v>0</v>
       </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 5:44 AM UTC</t>
+          <t>Apr 19, 2026 · 10:40 AM UTC</t>
         </is>
       </c>
       <c r="P18" s="2" t="n">
-        <v>46129.23888888889</v>
+        <v>46131.44444444445</v>
       </c>
       <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>['https://blog.dubaicityguide.com/site/emirates-nbd-successfully-executes-usd-250-million-syndicated-term-loan-facility-for-dar-global-accelerating-global-growth-and-expansion/']</t>
-        </is>
-      </c>
+      <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>138</v>
+        <v>20</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -3432,27 +3317,39 @@
       </c>
       <c r="X18" t="inlineStr